--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
@@ -857,139 +857,139 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="G2" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="H2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K2" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M2" t="n">
         <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O2" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R2" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="T2" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U2" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W2" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="X2" t="n">
         <v>22</v>
       </c>
       <c r="Y2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z2" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AA2" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AB2" t="n">
         <v>11</v>
       </c>
       <c r="AC2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE2" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AF2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG2" t="n">
         <v>11</v>
       </c>
       <c r="AH2" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AI2" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ2" t="n">
         <v>17.5</v>
       </c>
       <c r="AK2" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AL2" t="n">
         <v>32</v>
       </c>
       <c r="AM2" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AN2" t="n">
         <v>7.8</v>
       </c>
       <c r="AO2" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AP2" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AR2" t="n">
-        <v>8.6</v>
+        <v>36</v>
       </c>
       <c r="AS2" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AT2" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AU2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV2" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX2" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY2" t="n">
         <v>8.6</v>
@@ -998,89 +998,89 @@
         <v>16</v>
       </c>
       <c r="BA2" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BC2" t="n">
         <v>13.5</v>
       </c>
       <c r="BD2" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG2" t="n">
         <v>7.8</v>
       </c>
-      <c r="BE2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>9</v>
-      </c>
       <c r="BH2" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="BJ2" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>2.72</v>
+        <v>7.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>3.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>11</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>23</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>46</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>48</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>16</v>
+      </c>
+      <c r="CA2" t="n">
         <v>5.9</v>
       </c>
-      <c r="BO2" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>30</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>21</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>2.96</v>
-      </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="G6" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="H6" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="I6" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="J6" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="K6" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1903,10 +1903,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.28</v>
+        <v>2.54</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>1.31</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="J10" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2919,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
         <v>2.06</v>
       </c>
       <c r="J11" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K11" t="n">
         <v>3.5</v>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="G2" t="n">
         <v>1.7</v>
@@ -869,7 +869,7 @@
         <v>6.4</v>
       </c>
       <c r="J2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K2" t="n">
         <v>4.7</v>
@@ -884,10 +884,10 @@
         <v>4.8</v>
       </c>
       <c r="O2" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P2" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q2" t="n">
         <v>1.66</v>
@@ -896,7 +896,7 @@
         <v>1.53</v>
       </c>
       <c r="S2" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T2" t="n">
         <v>1.73</v>
@@ -905,7 +905,7 @@
         <v>2.16</v>
       </c>
       <c r="V2" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W2" t="n">
         <v>2.42</v>
@@ -929,7 +929,7 @@
         <v>11</v>
       </c>
       <c r="AD2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE2" t="n">
         <v>80</v>
@@ -941,10 +941,10 @@
         <v>11</v>
       </c>
       <c r="AH2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI2" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AJ2" t="n">
         <v>17.5</v>
@@ -974,7 +974,7 @@
         <v>36</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AT2" t="n">
         <v>9.199999999999999</v>
@@ -986,7 +986,7 @@
         <v>18.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AX2" t="n">
         <v>9.4</v>
@@ -998,7 +998,7 @@
         <v>16</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB2" t="n">
         <v>14</v>
@@ -1010,22 +1010,22 @@
         <v>22</v>
       </c>
       <c r="BE2" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BF2" t="n">
         <v>6.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI2" t="n">
         <v>3.55</v>
       </c>
       <c r="BJ2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK2" t="n">
         <v>7.6</v>
@@ -1034,7 +1034,7 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN2" t="n">
         <v>4.6</v>
@@ -1046,41 +1046,41 @@
         <v>11</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BR2" t="n">
         <v>23</v>
       </c>
       <c r="BS2" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BV2" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX2" t="n">
         <v>46</v>
       </c>
-      <c r="BW2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>48</v>
-      </c>
       <c r="BY2" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ2" t="n">
         <v>16</v>
       </c>
       <c r="CA2" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -1873,16 +1873,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="H6" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I6" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="J6" t="n">
         <v>2.98</v>
@@ -1903,7 +1903,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Q6" t="n">
         <v>2.54</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G8" t="n">
         <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I8" t="n">
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -2635,19 +2635,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G9" t="n">
         <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="G10" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="H10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I10" t="n">
-        <v>17.5</v>
+        <v>27</v>
       </c>
       <c r="J10" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="K10" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2919,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="G11" t="n">
         <v>4.8</v>
@@ -3152,10 +3152,10 @@
         <v>1.99</v>
       </c>
       <c r="I11" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="J11" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K11" t="n">
         <v>3.5</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB14"/>
+  <dimension ref="A1:CB13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -872,10 +872,10 @@
         <v>4.4</v>
       </c>
       <c r="K2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="M2" t="n">
         <v>1.04</v>
@@ -884,16 +884,16 @@
         <v>4.8</v>
       </c>
       <c r="O2" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P2" t="n">
         <v>2.28</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="R2" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S2" t="n">
         <v>2.6</v>
@@ -902,7 +902,7 @@
         <v>1.73</v>
       </c>
       <c r="U2" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V2" t="n">
         <v>1.19</v>
@@ -965,7 +965,7 @@
         <v>75</v>
       </c>
       <c r="AP2" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AQ2" t="n">
         <v>20</v>
@@ -977,7 +977,7 @@
         <v>9</v>
       </c>
       <c r="AT2" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU2" t="n">
         <v>8.800000000000001</v>
@@ -1001,10 +1001,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BB2" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BD2" t="n">
         <v>22</v>
@@ -1019,68 +1019,68 @@
         <v>8.4</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="BJ2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>7.6</v>
+        <v>5</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN2" t="n">
         <v>4.6</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="BP2" t="n">
         <v>11</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BR2" t="n">
         <v>23</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT2" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BV2" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BX2" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BZ2" t="n">
         <v>16</v>
       </c>
       <c r="CA2" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="P3" t="n">
-        <v>1.07</v>
+        <v>1.62</v>
       </c>
       <c r="Q3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK3" t="n">
         <v>1.01</v>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0</v>
-      </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -1365,230 +1365,230 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.81</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -1619,230 +1619,230 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.66</v>
       </c>
       <c r="Q5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK5" t="n">
         <v>1.01</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>0</v>
-      </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G6" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="H6" t="n">
         <v>3.9</v>
       </c>
       <c r="I6" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J6" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>1.53</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -3149,13 +3149,13 @@
         <v>4.8</v>
       </c>
       <c r="H11" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="I11" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="J11" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K11" t="n">
         <v>3.5</v>
@@ -3173,7 +3173,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q11" t="n">
         <v>2.08</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -3388,12 +3388,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>Operario PR</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -3427,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.25</v>
+        <v>1.9</v>
       </c>
       <c r="Q12" t="n">
         <v>1.01</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -3637,17 +3637,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Operario PR</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -3874,261 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Brazilian Serie B</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Goias</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Sport Recife</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB14" t="inlineStr">
-        <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB13"/>
+  <dimension ref="A1:CB14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H2" t="n">
         <v>5.3</v>
@@ -875,19 +875,19 @@
         <v>4.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M2" t="n">
         <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O2" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P2" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
         <v>1.64</v>
@@ -896,7 +896,7 @@
         <v>1.52</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T2" t="n">
         <v>1.73</v>
@@ -908,7 +908,7 @@
         <v>1.19</v>
       </c>
       <c r="W2" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="X2" t="n">
         <v>22</v>
@@ -947,10 +947,10 @@
         <v>75</v>
       </c>
       <c r="AJ2" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AK2" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL2" t="n">
         <v>32</v>
@@ -959,7 +959,7 @@
         <v>100</v>
       </c>
       <c r="AN2" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AO2" t="n">
         <v>75</v>
@@ -974,7 +974,7 @@
         <v>36</v>
       </c>
       <c r="AS2" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT2" t="n">
         <v>9</v>
@@ -986,7 +986,7 @@
         <v>18.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX2" t="n">
         <v>9.4</v>
@@ -998,7 +998,7 @@
         <v>16</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BB2" t="n">
         <v>12.5</v>
@@ -1010,77 +1010,77 @@
         <v>22</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF2" t="n">
         <v>6.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH2" t="n">
         <v>4.3</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK2" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN2" t="n">
         <v>4.6</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="BR2" t="n">
         <v>23</v>
       </c>
       <c r="BS2" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BV2" t="n">
         <v>46</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX2" t="n">
         <v>48</v>
       </c>
       <c r="BY2" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="CA2" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H3" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="I3" t="n">
         <v>2.9</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -1135,16 +1135,16 @@
         <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="O3" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="P3" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="R3" t="n">
         <v>1.23</v>
@@ -1162,7 +1162,7 @@
         <v>1.52</v>
       </c>
       <c r="W3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X3" t="n">
         <v>14.5</v>
@@ -1180,7 +1180,7 @@
         <v>16.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD3" t="n">
         <v>1000</v>
@@ -1222,55 +1222,55 @@
         <v>1.36</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="BH3" t="n">
         <v>3.35</v>
@@ -1282,59 +1282,59 @@
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -1365,25 +1365,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="G4" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="I4" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="J4" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="L4" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="M4" t="n">
         <v>1.08</v>
@@ -1395,16 +1395,16 @@
         <v>1.37</v>
       </c>
       <c r="P4" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R4" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S4" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T4" t="n">
         <v>1.96</v>
@@ -1413,10 +1413,10 @@
         <v>1.92</v>
       </c>
       <c r="V4" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="W4" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X4" t="n">
         <v>14.5</v>
@@ -1455,7 +1455,7 @@
         <v>42</v>
       </c>
       <c r="AJ4" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AK4" t="n">
         <v>80</v>
@@ -1470,7 +1470,7 @@
         <v>120</v>
       </c>
       <c r="AO4" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AP4" t="n">
         <v>11</v>
@@ -1482,7 +1482,7 @@
         <v>9.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT4" t="n">
         <v>13.5</v>
@@ -1497,7 +1497,7 @@
         <v>7.4</v>
       </c>
       <c r="AX4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AY4" t="n">
         <v>17.5</v>
@@ -1506,19 +1506,19 @@
         <v>7.4</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BC4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BD4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BE4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF4" t="n">
         <v>10</v>
@@ -1530,7 +1530,7 @@
         <v>3.2</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BJ4" t="n">
         <v>11</v>
@@ -1566,7 +1566,7 @@
         <v>4.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="BV4" t="n">
         <v>13.5</v>
@@ -1584,11 +1584,11 @@
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="G5" t="n">
         <v>1.97</v>
@@ -1631,16 +1631,16 @@
         <v>5.6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
@@ -1652,10 +1652,10 @@
         <v>1.66</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
         <v>4.4</v>
@@ -1667,7 +1667,7 @@
         <v>1.81</v>
       </c>
       <c r="V5" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W5" t="n">
         <v>2.02</v>
@@ -1790,59 +1790,59 @@
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>1.53</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -2892,19 +2892,19 @@
         <v>1.19</v>
       </c>
       <c r="G10" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="H10" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="I10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J10" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="K10" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2922,7 +2922,7 @@
         <v>2.34</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -3143,10 +3143,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="G11" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H11" t="n">
         <v>1.98</v>
@@ -3155,10 +3155,10 @@
         <v>2.1</v>
       </c>
       <c r="J11" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K11" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -3388,12 +3388,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Operario PR</t>
+          <t>Ceara SC Fortaleza</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -3427,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.9</v>
+        <v>1.25</v>
       </c>
       <c r="Q12" t="n">
         <v>1.01</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -3637,244 +3637,498 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Operario PR</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-07-20 10:18:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Goias</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Sport Recife</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="Q14" t="n">
         <v>1.01</v>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB13" t="inlineStr">
-        <is>
-          <t>2026-07-20 08:08:17</t>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="G2" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="H2" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="I2" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J2" t="n">
         <v>4.4</v>
       </c>
       <c r="K2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L2" t="n">
         <v>1.27</v>
@@ -887,28 +887,28 @@
         <v>1.22</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R2" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="S2" t="n">
         <v>2.62</v>
       </c>
       <c r="T2" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U2" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V2" t="n">
         <v>1.19</v>
       </c>
       <c r="W2" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="X2" t="n">
         <v>22</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="G3" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="H3" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="J3" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="K3" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -1135,142 +1135,142 @@
         <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="O3" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P3" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="R3" t="n">
         <v>1.23</v>
       </c>
       <c r="S3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U3" t="n">
         <v>1.91</v>
       </c>
-      <c r="U3" t="n">
-        <v>1.87</v>
-      </c>
       <c r="V3" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W3" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="X3" t="n">
-        <v>14.5</v>
+        <v>10</v>
       </c>
       <c r="Y3" t="n">
-        <v>14.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>55</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AK3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX3" t="n">
         <v>16.5</v>
       </c>
-      <c r="AC3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AY3" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.5</v>
+        <v>18</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.5</v>
+        <v>8</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.5</v>
+        <v>7.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.5</v>
+        <v>7.8</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.47</v>
+        <v>8</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.5</v>
+        <v>8.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.5</v>
+        <v>7.8</v>
       </c>
       <c r="BH3" t="n">
         <v>3.35</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="G4" t="n">
         <v>5.4</v>
@@ -1389,16 +1389,16 @@
         <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O4" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P4" t="n">
         <v>1.78</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="R4" t="n">
         <v>1.3</v>
@@ -1431,7 +1431,7 @@
         <v>21</v>
       </c>
       <c r="AB4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC4" t="n">
         <v>8.4</v>
@@ -1443,10 +1443,10 @@
         <v>22</v>
       </c>
       <c r="AF4" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AG4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH4" t="n">
         <v>22</v>
@@ -1458,7 +1458,7 @@
         <v>150</v>
       </c>
       <c r="AK4" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AL4" t="n">
         <v>85</v>
@@ -1482,7 +1482,7 @@
         <v>9.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.4</v>
+        <v>18</v>
       </c>
       <c r="AT4" t="n">
         <v>13.5</v>
@@ -1494,34 +1494,34 @@
         <v>9</v>
       </c>
       <c r="AW4" t="n">
-        <v>7.4</v>
+        <v>18.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AY4" t="n">
         <v>17.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB4" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC4" t="n">
         <v>10</v>
       </c>
-      <c r="BC4" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BD4" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BE4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG4" t="n">
         <v>13</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -1619,16 +1619,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="G5" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I5" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J5" t="n">
         <v>3.5</v>
@@ -1640,16 +1640,16 @@
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="O5" t="n">
         <v>1.45</v>
       </c>
       <c r="P5" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q5" t="n">
         <v>2.3</v>
@@ -1667,10 +1667,10 @@
         <v>1.81</v>
       </c>
       <c r="V5" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W5" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G6" t="n">
         <v>2.34</v>
@@ -1888,7 +1888,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>1.53</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -2895,16 +2895,16 @@
         <v>1.29</v>
       </c>
       <c r="H10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J10" t="n">
         <v>6</v>
       </c>
       <c r="K10" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2919,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -3149,16 +3149,16 @@
         <v>4.9</v>
       </c>
       <c r="H11" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="J11" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K11" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
         <v>1.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB14"/>
+  <dimension ref="A1:CB16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G2" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="H2" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J2" t="n">
         <v>4.4</v>
@@ -881,31 +881,31 @@
         <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P2" t="n">
         <v>2.34</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="R2" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S2" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="T2" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="U2" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V2" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W2" t="n">
         <v>2.5</v>
@@ -917,7 +917,7 @@
         <v>25</v>
       </c>
       <c r="Z2" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA2" t="n">
         <v>160</v>
@@ -938,10 +938,10 @@
         <v>11.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI2" t="n">
         <v>75</v>
@@ -971,52 +971,52 @@
         <v>20</v>
       </c>
       <c r="AR2" t="n">
-        <v>36</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS2" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV2" t="n">
         <v>18.5</v>
       </c>
       <c r="AW2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY2" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>8.6</v>
       </c>
       <c r="AZ2" t="n">
         <v>16</v>
       </c>
       <c r="BA2" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BC2" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>22</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE2" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH2" t="n">
         <v>4.3</v>
@@ -1028,13 +1028,13 @@
         <v>10</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN2" t="n">
         <v>4.6</v>
@@ -1043,44 +1043,44 @@
         <v>3.6</v>
       </c>
       <c r="BP2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BQ2" t="n">
-        <v>8</v>
+        <v>5.2</v>
       </c>
       <c r="BR2" t="n">
         <v>23</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BT2" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BV2" t="n">
         <v>46</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX2" t="n">
         <v>48</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ2" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="CA2" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-20 12:28:57</t>
+          <t>2026-07-20 14:38:58</t>
         </is>
       </c>
     </row>
@@ -1120,13 +1120,13 @@
         <v>2.74</v>
       </c>
       <c r="I3" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="J3" t="n">
         <v>3.1</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -1141,10 +1141,10 @@
         <v>1.49</v>
       </c>
       <c r="P3" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="R3" t="n">
         <v>1.23</v>
@@ -1153,22 +1153,22 @@
         <v>4.9</v>
       </c>
       <c r="T3" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
         <v>1.91</v>
       </c>
       <c r="V3" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W3" t="n">
         <v>1.47</v>
       </c>
       <c r="X3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z3" t="n">
         <v>20</v>
@@ -1183,7 +1183,7 @@
         <v>7</v>
       </c>
       <c r="AD3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE3" t="n">
         <v>44</v>
@@ -1192,10 +1192,10 @@
         <v>19</v>
       </c>
       <c r="AG3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI3" t="n">
         <v>70</v>
@@ -1222,25 +1222,25 @@
         <v>9</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AR3" t="n">
         <v>15.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU3" t="n">
         <v>6.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AX3" t="n">
         <v>16.5</v>
@@ -1252,25 +1252,25 @@
         <v>18</v>
       </c>
       <c r="BA3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB3" t="n">
         <v>8</v>
       </c>
-      <c r="BB3" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BC3" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BE3" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG3" t="n">
         <v>8.6</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>7.8</v>
       </c>
       <c r="BH3" t="n">
         <v>3.35</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-20 12:28:57</t>
+          <t>2026-07-20 14:38:58</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="G4" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="H4" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="I4" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="J4" t="n">
         <v>3.5</v>
@@ -1383,7 +1383,7 @@
         <v>3.75</v>
       </c>
       <c r="L4" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="M4" t="n">
         <v>1.08</v>
@@ -1395,10 +1395,10 @@
         <v>1.38</v>
       </c>
       <c r="P4" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="R4" t="n">
         <v>1.3</v>
@@ -1407,7 +1407,7 @@
         <v>3.9</v>
       </c>
       <c r="T4" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="U4" t="n">
         <v>1.92</v>
@@ -1416,52 +1416,52 @@
         <v>2.06</v>
       </c>
       <c r="W4" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X4" t="n">
         <v>14.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="Z4" t="n">
         <v>11</v>
       </c>
       <c r="AA4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AB4" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AC4" t="n">
         <v>8.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AF4" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AG4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AH4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AI4" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AJ4" t="n">
         <v>150</v>
       </c>
       <c r="AK4" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AL4" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AM4" t="n">
         <v>160</v>
@@ -1470,7 +1470,7 @@
         <v>120</v>
       </c>
       <c r="AO4" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AP4" t="n">
         <v>11</v>
@@ -1482,7 +1482,7 @@
         <v>9.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>18</v>
+        <v>5.5</v>
       </c>
       <c r="AT4" t="n">
         <v>13.5</v>
@@ -1491,37 +1491,37 @@
         <v>7.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW4" t="n">
-        <v>18.5</v>
+        <v>5.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>17.5</v>
+        <v>5.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>7.6</v>
+        <v>5.6</v>
       </c>
       <c r="BA4" t="n">
-        <v>9.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>11</v>
+        <v>6.8</v>
       </c>
       <c r="BC4" t="n">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="BD4" t="n">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>11</v>
+        <v>6.8</v>
       </c>
       <c r="BF4" t="n">
-        <v>10.5</v>
+        <v>6.8</v>
       </c>
       <c r="BG4" t="n">
         <v>13</v>
@@ -1530,7 +1530,7 @@
         <v>3.2</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BJ4" t="n">
         <v>11</v>
@@ -1566,7 +1566,7 @@
         <v>4.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BV4" t="n">
         <v>13.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-20 12:28:57</t>
+          <t>2026-07-20 14:38:58</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G5" t="n">
         <v>1.96</v>
@@ -1628,22 +1628,22 @@
         <v>4.9</v>
       </c>
       <c r="I5" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M5" t="n">
         <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="O5" t="n">
         <v>1.45</v>
@@ -1658,7 +1658,7 @@
         <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T5" t="n">
         <v>2.06</v>
@@ -1673,183 +1673,183 @@
         <v>2.04</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC5" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AD5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX5" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AD5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AY5" t="n">
-        <v>1.3</v>
+        <v>9.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.3</v>
+        <v>20</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.3</v>
+        <v>6.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.3</v>
+        <v>16.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.3</v>
+        <v>18</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.3</v>
+        <v>6.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.3</v>
+        <v>6.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.3</v>
+        <v>14</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.3</v>
+        <v>6.4</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.55</v>
+        <v>2.98</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.42</v>
+        <v>2.72</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.4</v>
+        <v>6.4</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.4</v>
+        <v>13.5</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.4</v>
+        <v>7.4</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.4</v>
+        <v>10.5</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.4</v>
+        <v>11.5</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.4</v>
+        <v>12</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.4</v>
+        <v>10</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-20 12:28:57</t>
+          <t>2026-07-20 14:38:58</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,251 +1859,251 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Macara</t>
+          <t>Lillestrom</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.14</v>
+        <v>3.25</v>
       </c>
       <c r="G6" t="n">
-        <v>2.34</v>
+        <v>3.3</v>
       </c>
       <c r="H6" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J6" t="n">
         <v>3.9</v>
       </c>
-      <c r="I6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3</v>
-      </c>
       <c r="K6" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P6" t="n">
-        <v>1.53</v>
+        <v>2.52</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.52</v>
+        <v>1.59</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-20 12:28:57</t>
+          <t>2026-07-20 14:38:58</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,251 +2113,251 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Botafogo FR</t>
+          <t>Bodo Glimt</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Ham-Kam</t>
         </is>
       </c>
       <c r="F7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="H7" t="n">
+        <v>23</v>
+      </c>
+      <c r="I7" t="n">
+        <v>27</v>
+      </c>
+      <c r="J7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>13</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="P7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>1.02</v>
       </c>
-      <c r="G7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="BA7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI7" t="n">
         <v>1.01</v>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>0</v>
-      </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-20 12:28:57</t>
+          <t>2026-07-20 14:38:58</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,36 +2367,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EC Vitoria Salvador</t>
+          <t>Macara</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vasco Da Gama</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.02</v>
+        <v>2.14</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>2.34</v>
       </c>
       <c r="H8" t="n">
-        <v>1.02</v>
+        <v>3.9</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="J8" t="n">
-        <v>1.02</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2411,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.05</v>
+        <v>1.53</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-20 12:28:57</t>
+          <t>2026-07-20 14:38:58</t>
         </is>
       </c>
     </row>
@@ -2626,12 +2626,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Botafogo FR</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gremio</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -2858,14 +2858,14 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-20 12:28:57</t>
+          <t>2026-07-20 14:38:58</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,36 +2875,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Independiente (Ecu)</t>
+          <t>EC Vitoria Salvador</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tecnico Universitario</t>
+          <t>Vasco Da Gama</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.19</v>
+        <v>1.02</v>
       </c>
       <c r="G10" t="n">
-        <v>1.29</v>
+        <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>18</v>
+        <v>1.02</v>
       </c>
       <c r="I10" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>6</v>
+        <v>1.02</v>
       </c>
       <c r="K10" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2919,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.36</v>
+        <v>1.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-20 12:28:57</t>
+          <t>2026-07-20 14:38:58</t>
         </is>
       </c>
     </row>
@@ -3129,36 +3129,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>Gremio</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.4</v>
+        <v>1.02</v>
       </c>
       <c r="G11" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>1.02</v>
       </c>
       <c r="I11" t="n">
-        <v>2.08</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>3.4</v>
+        <v>1.02</v>
       </c>
       <c r="K11" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.68</v>
+        <v>1.07</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3366,14 +3366,14 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-20 12:28:57</t>
+          <t>2026-07-20 14:38:58</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,36 +3383,36 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>Independiente (Ecu)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Tecnico Universitario</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -3427,10 +3427,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.25</v>
+        <v>2.36</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-20 12:28:57</t>
+          <t>2026-07-20 14:38:58</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3642,31 +3642,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Operario PR</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -3681,10 +3681,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-20 12:28:57</t>
+          <t>2026-07-20 14:38:58</t>
         </is>
       </c>
     </row>
@@ -3891,17 +3891,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Ceara SC Fortaleza</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -4128,7 +4128,515 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-20 12:28:57</t>
+          <t>2026-07-20 14:38:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Operario PR</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>2026-07-20 14:38:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Goias</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>2026-07-20 14:38:58</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
@@ -857,82 +857,82 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="G2" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="H2" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="J2" t="n">
         <v>4.4</v>
       </c>
       <c r="K2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L2" t="n">
         <v>1.27</v>
       </c>
       <c r="M2" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O2" t="n">
         <v>1.23</v>
       </c>
       <c r="P2" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="R2" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="S2" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="T2" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U2" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W2" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="X2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Z2" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AA2" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AB2" t="n">
         <v>11</v>
       </c>
       <c r="AC2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE2" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AF2" t="n">
         <v>11.5</v>
@@ -944,79 +944,79 @@
         <v>19.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AJ2" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AK2" t="n">
         <v>16.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM2" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AN2" t="n">
         <v>7.4</v>
       </c>
       <c r="AO2" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AP2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AQ2" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>9.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="AS2" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AT2" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV2" t="n">
         <v>18.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>9.6</v>
+        <v>50</v>
       </c>
       <c r="AX2" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ2" t="n">
         <v>16</v>
       </c>
       <c r="BA2" t="n">
-        <v>9.6</v>
+        <v>50</v>
       </c>
       <c r="BB2" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BE2" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG2" t="n">
-        <v>9.6</v>
+        <v>46</v>
       </c>
       <c r="BH2" t="n">
         <v>4.3</v>
@@ -1034,7 +1034,7 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BN2" t="n">
         <v>4.6</v>
@@ -1046,22 +1046,22 @@
         <v>11</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BR2" t="n">
         <v>23</v>
       </c>
       <c r="BS2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BT2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BU2" t="n">
         <v>4.9</v>
       </c>
       <c r="BV2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BW2" t="n">
         <v>8.199999999999999</v>
@@ -1070,17 +1070,17 @@
         <v>48</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ2" t="n">
         <v>16</v>
       </c>
       <c r="CA2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-20 14:38:58</t>
+          <t>2026-07-20 16:48:27</t>
         </is>
       </c>
     </row>
@@ -1114,10 +1114,10 @@
         <v>2.96</v>
       </c>
       <c r="G3" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H3" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="I3" t="n">
         <v>2.9</v>
@@ -1126,7 +1126,7 @@
         <v>3.1</v>
       </c>
       <c r="K3" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -1150,7 +1150,7 @@
         <v>1.23</v>
       </c>
       <c r="S3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="T3" t="n">
         <v>2</v>
@@ -1177,7 +1177,7 @@
         <v>48</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC3" t="n">
         <v>7</v>
@@ -1195,7 +1195,7 @@
         <v>15.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI3" t="n">
         <v>70</v>
@@ -1222,13 +1222,13 @@
         <v>9</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR3" t="n">
         <v>15.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT3" t="n">
         <v>8.4</v>
@@ -1255,7 +1255,7 @@
         <v>8.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC3" t="n">
         <v>8.6</v>
@@ -1264,10 +1264,10 @@
         <v>8.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG3" t="n">
         <v>8.6</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-20 14:38:58</t>
+          <t>2026-07-20 16:48:27</t>
         </is>
       </c>
     </row>
@@ -1371,19 +1371,19 @@
         <v>5.5</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="I4" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K4" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="M4" t="n">
         <v>1.08</v>
@@ -1392,13 +1392,13 @@
         <v>3.25</v>
       </c>
       <c r="O4" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="P4" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="R4" t="n">
         <v>1.3</v>
@@ -1413,7 +1413,7 @@
         <v>1.92</v>
       </c>
       <c r="V4" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="W4" t="n">
         <v>1.22</v>
@@ -1437,7 +1437,7 @@
         <v>8.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE4" t="n">
         <v>25</v>
@@ -1449,7 +1449,7 @@
         <v>24</v>
       </c>
       <c r="AH4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI4" t="n">
         <v>50</v>
@@ -1461,13 +1461,13 @@
         <v>80</v>
       </c>
       <c r="AL4" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AM4" t="n">
         <v>160</v>
       </c>
       <c r="AN4" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AO4" t="n">
         <v>17</v>
@@ -1479,49 +1479,49 @@
         <v>6.8</v>
       </c>
       <c r="AR4" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AT4" t="n">
         <v>13.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BC4" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG4" t="n">
         <v>13</v>
@@ -1536,31 +1536,31 @@
         <v>11</v>
       </c>
       <c r="BK4" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>22</v>
+        <v>13.5</v>
       </c>
       <c r="BN4" t="n">
         <v>8.4</v>
       </c>
       <c r="BO4" t="n">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>34</v>
+        <v>11.5</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="BT4" t="n">
         <v>4.4</v>
@@ -1572,23 +1572,23 @@
         <v>13.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BX4" t="n">
         <v>32</v>
       </c>
       <c r="BY4" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>21</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-20 14:38:58</t>
+          <t>2026-07-20 16:48:27</t>
         </is>
       </c>
     </row>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="G5" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="H5" t="n">
         <v>4.9</v>
@@ -1631,7 +1631,7 @@
         <v>5.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
         <v>3.7</v>
@@ -1670,7 +1670,7 @@
         <v>1.23</v>
       </c>
       <c r="W5" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X5" t="n">
         <v>12.5</v>
@@ -1682,7 +1682,7 @@
         <v>44</v>
       </c>
       <c r="AA5" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AB5" t="n">
         <v>7.2</v>
@@ -1814,25 +1814,25 @@
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT5" t="n">
         <v>8.4</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-20 14:38:58</t>
+          <t>2026-07-20 16:48:27</t>
         </is>
       </c>
     </row>
@@ -1876,13 +1876,13 @@
         <v>3.25</v>
       </c>
       <c r="G6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H6" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="I6" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="J6" t="n">
         <v>3.9</v>
@@ -1897,13 +1897,13 @@
         <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O6" t="n">
         <v>1.2</v>
       </c>
       <c r="P6" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="n">
         <v>1.59</v>
@@ -1915,188 +1915,188 @@
         <v>2.44</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="U6" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y6" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE6" t="n">
         <v>21</v>
       </c>
-      <c r="Z6" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB6" t="n">
+      <c r="AF6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS6" t="n">
         <v>26</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AT6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AY6" t="n">
         <v>13.5</v>
       </c>
-      <c r="AD6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE6" t="n">
+      <c r="AZ6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>46</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD6" t="n">
         <v>30</v>
       </c>
-      <c r="AF6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AY6" t="n">
+      <c r="BE6" t="n">
+        <v>46</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BG6" t="n">
         <v>10</v>
       </c>
-      <c r="AZ6" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>2.18</v>
-      </c>
       <c r="BH6" t="n">
         <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-20 14:38:58</t>
+          <t>2026-07-20 16:48:27</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="G7" t="n">
         <v>1.16</v>
@@ -2142,7 +2142,7 @@
         <v>10.5</v>
       </c>
       <c r="K7" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -2154,7 +2154,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="P7" t="n">
         <v>4.1</v>
@@ -2163,194 +2163,194 @@
         <v>1.25</v>
       </c>
       <c r="R7" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="S7" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="T7" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W7" t="n">
         <v>1.01</v>
       </c>
-      <c r="U7" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W7" t="n">
-        <v>6.4</v>
-      </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AA7" t="n">
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AC7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>410</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>70</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>250</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL7" t="n">
         <v>40</v>
       </c>
-      <c r="AD7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1000</v>
-      </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>2.42</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="AU7" t="n">
         <v>18</v>
       </c>
       <c r="AV7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>28</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI7" t="n">
         <v>1.04</v>
       </c>
-      <c r="AW7" t="n">
+      <c r="BJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK7" t="n">
         <v>1.04</v>
       </c>
-      <c r="AX7" t="n">
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
         <v>1.04</v>
       </c>
-      <c r="AY7" t="n">
+      <c r="BN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO7" t="n">
         <v>1.04</v>
       </c>
-      <c r="AZ7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="BA7" t="n">
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
         <v>1.04</v>
       </c>
-      <c r="BB7" t="n">
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
         <v>1.04</v>
       </c>
-      <c r="BC7" t="n">
+      <c r="BT7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU7" t="n">
         <v>1.04</v>
       </c>
-      <c r="BD7" t="n">
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
         <v>1.04</v>
       </c>
-      <c r="BE7" t="n">
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
         <v>1.04</v>
       </c>
-      <c r="BF7" t="n">
+      <c r="BZ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA7" t="n">
         <v>1.04</v>
       </c>
-      <c r="BG7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>1.01</v>
-      </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-20 14:38:58</t>
+          <t>2026-07-20 16:48:27</t>
         </is>
       </c>
     </row>
@@ -2399,16 +2399,16 @@
         <v>3.4</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P8" t="n">
         <v>1.53</v>
@@ -2417,194 +2417,194 @@
         <v>2.52</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="BH8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BP8" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-20 14:38:58</t>
+          <t>2026-07-20 16:48:27</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-20 14:38:58</t>
+          <t>2026-07-20 16:48:27</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-20 14:38:58</t>
+          <t>2026-07-20 16:48:27</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-20 14:38:58</t>
+          <t>2026-07-20 16:48:27</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
         <v>1.19</v>
       </c>
       <c r="G12" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="H12" t="n">
         <v>18</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-20 14:38:58</t>
+          <t>2026-07-20 16:48:27</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3651,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G13" t="n">
         <v>4.9</v>
       </c>
       <c r="H13" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="I13" t="n">
         <v>2</v>
@@ -3666,7 +3666,7 @@
         <v>3.45</v>
       </c>
       <c r="K13" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -3681,10 +3681,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-20 14:38:58</t>
+          <t>2026-07-20 16:48:27</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-20 14:38:58</t>
+          <t>2026-07-20 16:48:27</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-20 14:38:58</t>
+          <t>2026-07-20 16:48:27</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-20 14:38:58</t>
+          <t>2026-07-20 16:48:27</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
@@ -367,7 +367,7 @@
     <t>Gremio</t>
   </si>
   <si>
-    <t>2026-07-20 18:05:15</t>
+    <t>2026-07-20 18:26:24</t>
   </si>
 </sst>
 </file>
@@ -961,7 +961,7 @@
         <v>105</v>
       </c>
       <c r="F2">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1341,7 +1341,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ3">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="BA3">
         <v>40</v>
@@ -1353,7 +1353,7 @@
         <v>13</v>
       </c>
       <c r="BD3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE3">
         <v>44</v>
@@ -1445,19 +1445,19 @@
         <v>107</v>
       </c>
       <c r="F4">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="G4">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="H4">
         <v>5.5</v>
       </c>
       <c r="I4">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J4">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K4">
         <v>4.6</v>
@@ -1493,7 +1493,7 @@
         <v>2.2</v>
       </c>
       <c r="V4">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W4">
         <v>2.46</v>
@@ -1520,7 +1520,7 @@
         <v>22</v>
       </c>
       <c r="AE4">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF4">
         <v>11.5</v>
@@ -1532,7 +1532,7 @@
         <v>19.5</v>
       </c>
       <c r="AI4">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AJ4">
         <v>17.5</v>
@@ -1541,7 +1541,7 @@
         <v>16.5</v>
       </c>
       <c r="AL4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM4">
         <v>85</v>
@@ -1601,7 +1601,7 @@
         <v>60</v>
       </c>
       <c r="BF4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG4">
         <v>46</v>
@@ -1634,7 +1634,7 @@
         <v>11</v>
       </c>
       <c r="BQ4">
-        <v>5.3</v>
+        <v>8</v>
       </c>
       <c r="BR4">
         <v>23</v>
@@ -1741,10 +1741,10 @@
         <v>1.47</v>
       </c>
       <c r="X5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y5">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z5">
         <v>20</v>
@@ -1756,7 +1756,7 @@
         <v>9.4</v>
       </c>
       <c r="AC5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AD5">
         <v>15.5</v>
@@ -1804,7 +1804,7 @@
         <v>15.5</v>
       </c>
       <c r="AS5">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT5">
         <v>8.4</v>
@@ -1828,19 +1828,19 @@
         <v>18</v>
       </c>
       <c r="BA5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB5">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC5">
         <v>8.6</v>
       </c>
       <c r="BD5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF5">
         <v>9.199999999999999</v>
@@ -1944,10 +1944,10 @@
         <v>3.45</v>
       </c>
       <c r="K6">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L6">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="M6">
         <v>1.08</v>
@@ -1959,10 +1959,10 @@
         <v>1.36</v>
       </c>
       <c r="P6">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q6">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="R6">
         <v>1.3</v>
@@ -2186,7 +2186,7 @@
         <v>3.5</v>
       </c>
       <c r="K7">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L7">
         <v>1.5</v>
@@ -2939,10 +2939,10 @@
         <v>4.5</v>
       </c>
       <c r="T10">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U10">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="V10">
         <v>1.28</v>
@@ -3139,19 +3139,19 @@
         <v>114</v>
       </c>
       <c r="F11">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="G11">
         <v>1000</v>
       </c>
       <c r="H11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="I11">
         <v>1000</v>
       </c>
       <c r="J11">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K11">
         <v>1000</v>
@@ -3172,7 +3172,7 @@
         <v>1.08</v>
       </c>
       <c r="Q11">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R11">
         <v>1.08</v>
@@ -3190,7 +3190,7 @@
         <v>1.01</v>
       </c>
       <c r="W11">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3381,19 +3381,19 @@
         <v>115</v>
       </c>
       <c r="F12">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="G12">
         <v>1000</v>
       </c>
       <c r="H12">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I12">
         <v>1000</v>
       </c>
       <c r="J12">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K12">
         <v>1000</v>
@@ -3414,7 +3414,7 @@
         <v>1.08</v>
       </c>
       <c r="Q12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R12">
         <v>1.08</v>
@@ -3429,10 +3429,10 @@
         <v>1.11</v>
       </c>
       <c r="V12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3647,7 +3647,7 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="O13">
         <v>1.01</v>
@@ -3656,7 +3656,7 @@
         <v>1.08</v>
       </c>
       <c r="Q13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R13">
         <v>1.08</v>
@@ -3674,7 +3674,7 @@
         <v>1.01</v>
       </c>
       <c r="W13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X13">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
@@ -367,7 +367,7 @@
     <t>Gremio</t>
   </si>
   <si>
-    <t>2026-07-20 18:26:24</t>
+    <t>2026-07-20 20:33:00</t>
   </si>
 </sst>
 </file>
@@ -1000,7 +1000,7 @@
         <v>1.29</v>
       </c>
       <c r="S2">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="T2">
         <v>1.91</v>
@@ -1021,7 +1021,7 @@
         <v>15</v>
       </c>
       <c r="Z2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA2">
         <v>120</v>
@@ -1066,7 +1066,7 @@
         <v>17</v>
       </c>
       <c r="AO2">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AP2">
         <v>10.5</v>
@@ -1090,7 +1090,7 @@
         <v>16</v>
       </c>
       <c r="AW2">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AX2">
         <v>10</v>
@@ -1203,13 +1203,13 @@
         <v>106</v>
       </c>
       <c r="F3">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="G3">
         <v>1.37</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I3">
         <v>10.5</v>
@@ -1218,7 +1218,7 @@
         <v>6</v>
       </c>
       <c r="K3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="L3">
         <v>1.27</v>
@@ -1233,46 +1233,46 @@
         <v>1.23</v>
       </c>
       <c r="P3">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q3">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="R3">
         <v>1.55</v>
       </c>
       <c r="S3">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="T3">
         <v>2.1</v>
       </c>
       <c r="U3">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V3">
         <v>1.11</v>
       </c>
       <c r="W3">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="X3">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z3">
         <v>100</v>
       </c>
       <c r="AA3">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="AB3">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC3">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AD3">
         <v>38</v>
@@ -1281,13 +1281,13 @@
         <v>180</v>
       </c>
       <c r="AF3">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AG3">
         <v>10.5</v>
       </c>
       <c r="AH3">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AI3">
         <v>140</v>
@@ -1296,19 +1296,19 @@
         <v>11</v>
       </c>
       <c r="AK3">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AL3">
         <v>38</v>
       </c>
       <c r="AM3">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN3">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AO3">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AP3">
         <v>21</v>
@@ -1341,7 +1341,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA3">
         <v>40</v>
@@ -1356,7 +1356,7 @@
         <v>32</v>
       </c>
       <c r="BE3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BF3">
         <v>4.9</v>
@@ -1374,13 +1374,13 @@
         <v>12.5</v>
       </c>
       <c r="BK3">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BN3">
         <v>3.8</v>
@@ -1392,34 +1392,34 @@
         <v>7.6</v>
       </c>
       <c r="BQ3">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BR3">
         <v>24</v>
       </c>
       <c r="BS3">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT3">
         <v>14</v>
       </c>
       <c r="BU3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BZ3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="CA3">
         <v>6.8</v>
@@ -1445,73 +1445,73 @@
         <v>107</v>
       </c>
       <c r="F4">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="G4">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="H4">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I4">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J4">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K4">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L4">
         <v>1.27</v>
       </c>
       <c r="M4">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N4">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="O4">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P4">
+        <v>2.38</v>
+      </c>
+      <c r="Q4">
+        <v>1.67</v>
+      </c>
+      <c r="R4">
+        <v>1.56</v>
+      </c>
+      <c r="S4">
+        <v>2.66</v>
+      </c>
+      <c r="T4">
+        <v>1.7</v>
+      </c>
+      <c r="U4">
         <v>2.3</v>
       </c>
-      <c r="Q4">
-        <v>1.7</v>
-      </c>
-      <c r="R4">
-        <v>1.54</v>
-      </c>
-      <c r="S4">
-        <v>2.72</v>
-      </c>
-      <c r="T4">
-        <v>1.77</v>
-      </c>
-      <c r="U4">
-        <v>2.2</v>
-      </c>
       <c r="V4">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W4">
         <v>2.46</v>
       </c>
       <c r="X4">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Y4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Z4">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AA4">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AB4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC4">
         <v>10.5</v>
@@ -1526,22 +1526,22 @@
         <v>11.5</v>
       </c>
       <c r="AG4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH4">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI4">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ4">
         <v>17.5</v>
       </c>
       <c r="AK4">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AL4">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM4">
         <v>85</v>
@@ -1565,10 +1565,10 @@
         <v>13</v>
       </c>
       <c r="AT4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU4">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV4">
         <v>18.5</v>
@@ -1577,10 +1577,10 @@
         <v>50</v>
       </c>
       <c r="AX4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY4">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ4">
         <v>16</v>
@@ -1592,10 +1592,10 @@
         <v>15</v>
       </c>
       <c r="BC4">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD4">
-        <v>10.5</v>
+        <v>25</v>
       </c>
       <c r="BE4">
         <v>60</v>
@@ -1634,7 +1634,7 @@
         <v>11</v>
       </c>
       <c r="BQ4">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR4">
         <v>23</v>
@@ -1696,7 +1696,7 @@
         <v>2.72</v>
       </c>
       <c r="I5">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="J5">
         <v>3.1</v>
@@ -1711,13 +1711,13 @@
         <v>1.11</v>
       </c>
       <c r="N5">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O5">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P5">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q5">
         <v>2.44</v>
@@ -1726,16 +1726,16 @@
         <v>1.23</v>
       </c>
       <c r="S5">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="T5">
         <v>2</v>
       </c>
       <c r="U5">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V5">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="W5">
         <v>1.47</v>
@@ -1750,13 +1750,13 @@
         <v>20</v>
       </c>
       <c r="AA5">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AB5">
         <v>9.4</v>
       </c>
       <c r="AC5">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD5">
         <v>15.5</v>
@@ -1804,7 +1804,7 @@
         <v>15.5</v>
       </c>
       <c r="AS5">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT5">
         <v>8.4</v>
@@ -1816,7 +1816,7 @@
         <v>11.5</v>
       </c>
       <c r="AW5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX5">
         <v>16.5</v>
@@ -1828,25 +1828,25 @@
         <v>18</v>
       </c>
       <c r="BA5">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BB5">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD5">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BE5">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF5">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH5">
         <v>3.35</v>
@@ -1932,37 +1932,37 @@
         <v>4.8</v>
       </c>
       <c r="G6">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="H6">
         <v>1.86</v>
       </c>
       <c r="I6">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="J6">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K6">
         <v>3.75</v>
       </c>
       <c r="L6">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="M6">
         <v>1.08</v>
       </c>
       <c r="N6">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="O6">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="P6">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q6">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R6">
         <v>1.3</v>
@@ -1971,82 +1971,82 @@
         <v>3.9</v>
       </c>
       <c r="T6">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="U6">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V6">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="W6">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X6">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y6">
         <v>8</v>
       </c>
       <c r="Z6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AA6">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AB6">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC6">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD6">
         <v>10.5</v>
       </c>
       <c r="AE6">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AF6">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AG6">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AH6">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI6">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="AJ6">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AL6">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AO6">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AP6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ6">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR6">
         <v>9.6</v>
       </c>
       <c r="AS6">
-        <v>5.8</v>
+        <v>17.5</v>
       </c>
       <c r="AT6">
         <v>13.5</v>
@@ -2058,34 +2058,34 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW6">
-        <v>5.9</v>
+        <v>15</v>
       </c>
       <c r="AX6">
-        <v>6.6</v>
+        <v>21</v>
       </c>
       <c r="AY6">
-        <v>5.8</v>
+        <v>16.5</v>
       </c>
       <c r="AZ6">
-        <v>5.9</v>
+        <v>19</v>
       </c>
       <c r="BA6">
-        <v>6.8</v>
+        <v>32</v>
       </c>
       <c r="BB6">
-        <v>7.4</v>
+        <v>40</v>
       </c>
       <c r="BC6">
-        <v>7.2</v>
+        <v>32</v>
       </c>
       <c r="BD6">
-        <v>7.2</v>
+        <v>34</v>
       </c>
       <c r="BE6">
-        <v>7.4</v>
+        <v>44</v>
       </c>
       <c r="BF6">
-        <v>7.2</v>
+        <v>36</v>
       </c>
       <c r="BG6">
         <v>13</v>
@@ -2100,13 +2100,13 @@
         <v>11</v>
       </c>
       <c r="BK6">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN6">
         <v>8.4</v>
@@ -2130,13 +2130,13 @@
         <v>4.4</v>
       </c>
       <c r="BU6">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BV6">
         <v>13.5</v>
       </c>
       <c r="BW6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX6">
         <v>32</v>
@@ -2145,7 +2145,7 @@
         <v>10</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="CA6">
         <v>9.800000000000001</v>
@@ -2177,31 +2177,31 @@
         <v>1.93</v>
       </c>
       <c r="H7">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I7">
         <v>5.4</v>
       </c>
       <c r="J7">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K7">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L7">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="M7">
         <v>1.1</v>
       </c>
       <c r="N7">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O7">
         <v>1.45</v>
       </c>
       <c r="P7">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q7">
         <v>2.3</v>
@@ -2213,10 +2213,10 @@
         <v>4.5</v>
       </c>
       <c r="T7">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U7">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V7">
         <v>1.23</v>
@@ -2279,13 +2279,13 @@
         <v>150</v>
       </c>
       <c r="AP7">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ7">
         <v>12.5</v>
       </c>
       <c r="AR7">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS7">
         <v>6.4</v>
@@ -2297,10 +2297,10 @@
         <v>7.2</v>
       </c>
       <c r="AV7">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AW7">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX7">
         <v>9.199999999999999</v>
@@ -2315,19 +2315,19 @@
         <v>6.2</v>
       </c>
       <c r="BB7">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC7">
         <v>18</v>
       </c>
       <c r="BD7">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE7">
         <v>6.4</v>
       </c>
       <c r="BF7">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BG7">
         <v>6.4</v>
@@ -2416,13 +2416,13 @@
         <v>3.25</v>
       </c>
       <c r="G8">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H8">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="I8">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="J8">
         <v>3.9</v>
@@ -2446,7 +2446,7 @@
         <v>2.5</v>
       </c>
       <c r="Q8">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R8">
         <v>1.62</v>
@@ -2491,7 +2491,7 @@
         <v>21</v>
       </c>
       <c r="AF8">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AG8">
         <v>14.5</v>
@@ -2509,7 +2509,7 @@
         <v>32</v>
       </c>
       <c r="AL8">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM8">
         <v>55</v>
@@ -2694,7 +2694,7 @@
         <v>2.26</v>
       </c>
       <c r="S9">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="T9">
         <v>2.04</v>
@@ -2924,7 +2924,7 @@
         <v>2.36</v>
       </c>
       <c r="O10">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="P10">
         <v>1.53</v>
@@ -2942,7 +2942,7 @@
         <v>2.06</v>
       </c>
       <c r="U10">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="V10">
         <v>1.28</v>
@@ -2987,7 +2987,7 @@
         <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AK10">
         <v>44</v>
@@ -3005,7 +3005,7 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AQ10">
         <v>8.800000000000001</v>
@@ -3014,7 +3014,7 @@
         <v>18.5</v>
       </c>
       <c r="AS10">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="AT10">
         <v>5.9</v>
@@ -3026,7 +3026,7 @@
         <v>13.5</v>
       </c>
       <c r="AW10">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="AX10">
         <v>9.4</v>
@@ -3038,25 +3038,25 @@
         <v>18</v>
       </c>
       <c r="BA10">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="BB10">
-        <v>2.76</v>
+        <v>23</v>
       </c>
       <c r="BC10">
         <v>22</v>
       </c>
       <c r="BD10">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="BE10">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="BF10">
         <v>19</v>
       </c>
       <c r="BG10">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="BH10">
         <v>3.2</v>
@@ -3139,22 +3139,22 @@
         <v>114</v>
       </c>
       <c r="F11">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="G11">
         <v>1000</v>
       </c>
       <c r="H11">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="I11">
         <v>1000</v>
       </c>
       <c r="J11">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K11">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3178,7 +3178,7 @@
         <v>1.08</v>
       </c>
       <c r="S11">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T11">
         <v>1.11</v>
@@ -3187,10 +3187,10 @@
         <v>1.11</v>
       </c>
       <c r="V11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W11">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3381,22 +3381,22 @@
         <v>115</v>
       </c>
       <c r="F12">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="G12">
         <v>1000</v>
       </c>
       <c r="H12">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="I12">
         <v>1000</v>
       </c>
       <c r="J12">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K12">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3405,7 +3405,7 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="O12">
         <v>1.01</v>
@@ -3420,7 +3420,7 @@
         <v>1.08</v>
       </c>
       <c r="S12">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T12">
         <v>1.11</v>
@@ -3432,7 +3432,7 @@
         <v>1.02</v>
       </c>
       <c r="W12">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3623,7 +3623,7 @@
         <v>116</v>
       </c>
       <c r="F13">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="G13">
         <v>1000</v>
@@ -3638,7 +3638,7 @@
         <v>1.03</v>
       </c>
       <c r="K13">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -3647,7 +3647,7 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="O13">
         <v>1.01</v>
@@ -3662,7 +3662,7 @@
         <v>1.08</v>
       </c>
       <c r="S13">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T13">
         <v>1.11</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
@@ -367,7 +367,7 @@
     <t>Gremio</t>
   </si>
   <si>
-    <t>2026-07-20 20:33:00</t>
+    <t>2026-07-20 22:39:05</t>
   </si>
 </sst>
 </file>
@@ -970,10 +970,10 @@
         <v>4.4</v>
       </c>
       <c r="I2">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J2">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K2">
         <v>3.65</v>
@@ -991,7 +991,7 @@
         <v>1.37</v>
       </c>
       <c r="P2">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q2">
         <v>2.1</v>
@@ -1003,7 +1003,7 @@
         <v>3.95</v>
       </c>
       <c r="T2">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U2">
         <v>1.95</v>
@@ -1018,10 +1018,10 @@
         <v>12.5</v>
       </c>
       <c r="Y2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA2">
         <v>120</v>
@@ -1033,7 +1033,7 @@
         <v>8</v>
       </c>
       <c r="AD2">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE2">
         <v>70</v>
@@ -1042,7 +1042,7 @@
         <v>12</v>
       </c>
       <c r="AG2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH2">
         <v>21</v>
@@ -1078,13 +1078,13 @@
         <v>29</v>
       </c>
       <c r="AS2">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AT2">
         <v>7.2</v>
       </c>
       <c r="AU2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV2">
         <v>16</v>
@@ -1114,7 +1114,7 @@
         <v>36</v>
       </c>
       <c r="BE2">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BF2">
         <v>14.5</v>
@@ -1206,7 +1206,7 @@
         <v>1.34</v>
       </c>
       <c r="G3">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="H3">
         <v>8.800000000000001</v>
@@ -1215,10 +1215,10 @@
         <v>10.5</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="K3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="L3">
         <v>1.27</v>
@@ -1242,7 +1242,7 @@
         <v>1.55</v>
       </c>
       <c r="S3">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="T3">
         <v>2.1</v>
@@ -1251,7 +1251,7 @@
         <v>1.86</v>
       </c>
       <c r="V3">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W3">
         <v>3.75</v>
@@ -1266,10 +1266,10 @@
         <v>100</v>
       </c>
       <c r="AA3">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="AB3">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC3">
         <v>14.5</v>
@@ -1296,7 +1296,7 @@
         <v>11</v>
       </c>
       <c r="AK3">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL3">
         <v>38</v>
@@ -1314,7 +1314,7 @@
         <v>21</v>
       </c>
       <c r="AQ3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AR3">
         <v>36</v>
@@ -1332,13 +1332,13 @@
         <v>28</v>
       </c>
       <c r="AW3">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AX3">
         <v>7.8</v>
       </c>
       <c r="AY3">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ3">
         <v>21</v>
@@ -1445,7 +1445,7 @@
         <v>107</v>
       </c>
       <c r="F4">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="G4">
         <v>1.68</v>
@@ -1478,7 +1478,7 @@
         <v>2.38</v>
       </c>
       <c r="Q4">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="R4">
         <v>1.56</v>
@@ -1487,7 +1487,7 @@
         <v>2.66</v>
       </c>
       <c r="T4">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U4">
         <v>2.3</v>
@@ -1514,7 +1514,7 @@
         <v>11.5</v>
       </c>
       <c r="AC4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD4">
         <v>22</v>
@@ -1526,7 +1526,7 @@
         <v>11.5</v>
       </c>
       <c r="AG4">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH4">
         <v>18.5</v>
@@ -1562,7 +1562,7 @@
         <v>38</v>
       </c>
       <c r="AS4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT4">
         <v>10</v>
@@ -1604,7 +1604,7 @@
         <v>6.8</v>
       </c>
       <c r="BG4">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BH4">
         <v>4.3</v>
@@ -1929,55 +1929,55 @@
         <v>109</v>
       </c>
       <c r="F6">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="G6">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="H6">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="I6">
         <v>1.94</v>
       </c>
       <c r="J6">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K6">
         <v>3.75</v>
       </c>
       <c r="L6">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="M6">
         <v>1.08</v>
       </c>
       <c r="N6">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O6">
         <v>1.38</v>
       </c>
       <c r="P6">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q6">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R6">
         <v>1.3</v>
       </c>
       <c r="S6">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T6">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U6">
         <v>1.94</v>
       </c>
       <c r="V6">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="W6">
         <v>1.24</v>
@@ -1995,7 +1995,7 @@
         <v>21</v>
       </c>
       <c r="AB6">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC6">
         <v>8.199999999999999</v>
@@ -2007,13 +2007,13 @@
         <v>23</v>
       </c>
       <c r="AF6">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AG6">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AH6">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AI6">
         <v>150</v>
@@ -2034,31 +2034,31 @@
         <v>1000</v>
       </c>
       <c r="AO6">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AP6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ6">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AR6">
         <v>9.6</v>
       </c>
       <c r="AS6">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AT6">
         <v>13.5</v>
       </c>
       <c r="AU6">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV6">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AW6">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AX6">
         <v>21</v>
@@ -2067,10 +2067,10 @@
         <v>16.5</v>
       </c>
       <c r="AZ6">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA6">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="BB6">
         <v>40</v>
@@ -2094,13 +2094,13 @@
         <v>3.2</v>
       </c>
       <c r="BI6">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BJ6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK6">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL6">
         <v>1000</v>
@@ -2109,10 +2109,10 @@
         <v>14</v>
       </c>
       <c r="BN6">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO6">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BP6">
         <v>1000</v>
@@ -2127,13 +2127,13 @@
         <v>12</v>
       </c>
       <c r="BT6">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BU6">
         <v>3.55</v>
       </c>
       <c r="BV6">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BW6">
         <v>7.2</v>
@@ -2145,7 +2145,7 @@
         <v>10</v>
       </c>
       <c r="BZ6">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
         <v>9.800000000000001</v>
@@ -2183,13 +2183,13 @@
         <v>5.4</v>
       </c>
       <c r="J7">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K7">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L7">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="M7">
         <v>1.1</v>
@@ -2210,7 +2210,7 @@
         <v>1.25</v>
       </c>
       <c r="S7">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T7">
         <v>2.08</v>
@@ -2285,13 +2285,13 @@
         <v>12.5</v>
       </c>
       <c r="AR7">
+        <v>6.8</v>
+      </c>
+      <c r="AS7">
+        <v>7.6</v>
+      </c>
+      <c r="AT7">
         <v>6.4</v>
-      </c>
-      <c r="AS7">
-        <v>6.4</v>
-      </c>
-      <c r="AT7">
-        <v>6.2</v>
       </c>
       <c r="AU7">
         <v>7.2</v>
@@ -2300,7 +2300,7 @@
         <v>18</v>
       </c>
       <c r="AW7">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AX7">
         <v>9.199999999999999</v>
@@ -2312,7 +2312,7 @@
         <v>20</v>
       </c>
       <c r="BA7">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB7">
         <v>17.5</v>
@@ -2321,16 +2321,16 @@
         <v>18</v>
       </c>
       <c r="BD7">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE7">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF7">
         <v>16</v>
       </c>
       <c r="BG7">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH7">
         <v>2.98</v>
@@ -2434,19 +2434,19 @@
         <v>1.01</v>
       </c>
       <c r="M8">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N8">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O8">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P8">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="Q8">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R8">
         <v>1.62</v>
@@ -2458,10 +2458,10 @@
         <v>1.54</v>
       </c>
       <c r="U8">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="V8">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W8">
         <v>1.34</v>
@@ -2479,7 +2479,7 @@
         <v>29</v>
       </c>
       <c r="AB8">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AC8">
         <v>9.4</v>
@@ -2524,7 +2524,7 @@
         <v>21</v>
       </c>
       <c r="AQ8">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR8">
         <v>15.5</v>
@@ -2533,7 +2533,7 @@
         <v>26</v>
       </c>
       <c r="AT8">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AU8">
         <v>8.6</v>
@@ -2661,7 +2661,7 @@
         <v>1.14</v>
       </c>
       <c r="H9">
-        <v>24</v>
+        <v>15.5</v>
       </c>
       <c r="I9">
         <v>30</v>
@@ -2688,7 +2688,7 @@
         <v>4.1</v>
       </c>
       <c r="Q9">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="R9">
         <v>2.26</v>
@@ -2912,7 +2912,7 @@
         <v>3</v>
       </c>
       <c r="K10">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -2921,13 +2921,13 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="O10">
         <v>1.51</v>
       </c>
       <c r="P10">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Q10">
         <v>2.52</v>
@@ -3023,7 +3023,7 @@
         <v>5.9</v>
       </c>
       <c r="AV10">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW10">
         <v>2.86</v>
@@ -3139,19 +3139,19 @@
         <v>114</v>
       </c>
       <c r="F11">
-        <v>1.06</v>
+        <v>1.23</v>
       </c>
       <c r="G11">
         <v>1000</v>
       </c>
       <c r="H11">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="I11">
         <v>1000</v>
       </c>
       <c r="J11">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="K11">
         <v>100</v>
@@ -3187,7 +3187,7 @@
         <v>1.11</v>
       </c>
       <c r="V11">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W11">
         <v>1.03</v>
@@ -3381,19 +3381,19 @@
         <v>115</v>
       </c>
       <c r="F12">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="G12">
         <v>1000</v>
       </c>
       <c r="H12">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="I12">
         <v>1000</v>
       </c>
       <c r="J12">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="K12">
         <v>100</v>
@@ -3405,7 +3405,7 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="O12">
         <v>1.01</v>
@@ -3426,10 +3426,10 @@
         <v>1.11</v>
       </c>
       <c r="U12">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V12">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W12">
         <v>1.03</v>
@@ -3653,19 +3653,19 @@
         <v>1.01</v>
       </c>
       <c r="P13">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Q13">
         <v>1.02</v>
       </c>
       <c r="R13">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="S13">
         <v>1.05</v>
       </c>
       <c r="T13">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U13">
         <v>1.11</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="147">
   <si>
     <t>League</t>
   </si>
@@ -271,6 +271,15 @@
     <t>Brazilian Serie A</t>
   </si>
   <si>
+    <t>Brazilian Serie B</t>
+  </si>
+  <si>
+    <t>US United Soccer League</t>
+  </si>
+  <si>
+    <t>US MLS</t>
+  </si>
+  <si>
     <t>2026-07-22</t>
   </si>
   <si>
@@ -295,6 +304,18 @@
     <t>20:00:00</t>
   </si>
   <si>
+    <t>21:30:00</t>
+  </si>
+  <si>
+    <t>22:30:00</t>
+  </si>
+  <si>
+    <t>23:00:00</t>
+  </si>
+  <si>
+    <t>23:30:00</t>
+  </si>
+  <si>
     <t>Univ Catolica (Ecu)</t>
   </si>
   <si>
@@ -322,13 +343,46 @@
     <t>Macara</t>
   </si>
   <si>
+    <t>EC Vitoria Salvador</t>
+  </si>
+  <si>
+    <t>Mirassol</t>
+  </si>
+  <si>
     <t>Botafogo FR</t>
   </si>
   <si>
-    <t>EC Vitoria Salvador</t>
-  </si>
-  <si>
-    <t>Mirassol</t>
+    <t>Independiente (Ecu)</t>
+  </si>
+  <si>
+    <t>Coritiba</t>
+  </si>
+  <si>
+    <t>Ceara SC Fortaleza</t>
+  </si>
+  <si>
+    <t>Operario PR</t>
+  </si>
+  <si>
+    <t>Lexington SC</t>
+  </si>
+  <si>
+    <t>FC Cincinnati</t>
+  </si>
+  <si>
+    <t>Goias</t>
+  </si>
+  <si>
+    <t>Columbus</t>
+  </si>
+  <si>
+    <t>New England Revolution</t>
+  </si>
+  <si>
+    <t>Philadelphia</t>
+  </si>
+  <si>
+    <t>Inter Miami CF</t>
   </si>
   <si>
     <t>Barcelona (Ecu)</t>
@@ -358,16 +412,49 @@
     <t>Deportivo Cuenca</t>
   </si>
   <si>
+    <t>Vasco Da Gama</t>
+  </si>
+  <si>
+    <t>Gremio</t>
+  </si>
+  <si>
     <t>Santos</t>
   </si>
   <si>
-    <t>Vasco Da Gama</t>
-  </si>
-  <si>
-    <t>Gremio</t>
-  </si>
-  <si>
-    <t>2026-07-20 22:39:05</t>
+    <t>Tecnico Universitario</t>
+  </si>
+  <si>
+    <t>SE Palmeiras</t>
+  </si>
+  <si>
+    <t>CRB</t>
+  </si>
+  <si>
+    <t>Ponte Preta</t>
+  </si>
+  <si>
+    <t>Oakland Roots</t>
+  </si>
+  <si>
+    <t>Vancouver Whitecaps</t>
+  </si>
+  <si>
+    <t>Sport Recife</t>
+  </si>
+  <si>
+    <t>New York City</t>
+  </si>
+  <si>
+    <t>Toronto FC</t>
+  </si>
+  <si>
+    <t>New York Red Bulls</t>
+  </si>
+  <si>
+    <t>Chicago Fire</t>
+  </si>
+  <si>
+    <t>2026-07-21 00:46:03</t>
   </si>
 </sst>
 </file>
@@ -699,7 +786,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB13"/>
+  <dimension ref="A1:CB24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -949,22 +1036,22 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="E2" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="F2">
         <v>1.92</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H2">
         <v>4.4</v>
@@ -979,31 +1066,31 @@
         <v>3.65</v>
       </c>
       <c r="L2">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M2">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N2">
         <v>3.25</v>
       </c>
       <c r="O2">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P2">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="Q2">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="R2">
         <v>1.29</v>
       </c>
       <c r="S2">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="T2">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U2">
         <v>1.95</v>
@@ -1015,7 +1102,7 @@
         <v>2</v>
       </c>
       <c r="X2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y2">
         <v>14.5</v>
@@ -1027,7 +1114,7 @@
         <v>120</v>
       </c>
       <c r="AB2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC2">
         <v>8</v>
@@ -1039,7 +1126,7 @@
         <v>70</v>
       </c>
       <c r="AF2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG2">
         <v>10.5</v>
@@ -1051,7 +1138,7 @@
         <v>75</v>
       </c>
       <c r="AJ2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK2">
         <v>23</v>
@@ -1060,13 +1147,13 @@
         <v>44</v>
       </c>
       <c r="AM2">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN2">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AO2">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AP2">
         <v>10.5</v>
@@ -1078,19 +1165,19 @@
         <v>29</v>
       </c>
       <c r="AS2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT2">
         <v>7.2</v>
       </c>
       <c r="AU2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV2">
         <v>16</v>
       </c>
       <c r="AW2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX2">
         <v>10</v>
@@ -1114,7 +1201,7 @@
         <v>36</v>
       </c>
       <c r="BE2">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF2">
         <v>14.5</v>
@@ -1123,10 +1210,10 @@
         <v>38</v>
       </c>
       <c r="BH2">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI2">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="BJ2">
         <v>10.5</v>
@@ -1138,7 +1225,7 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN2">
         <v>4.6</v>
@@ -1150,13 +1237,13 @@
         <v>14.5</v>
       </c>
       <c r="BQ2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR2">
         <v>32</v>
       </c>
       <c r="BS2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT2">
         <v>8</v>
@@ -1168,22 +1255,22 @@
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="CA2">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CB2" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1191,16 +1278,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="E3" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="F3">
         <v>1.34</v>
@@ -1209,7 +1296,7 @@
         <v>1.36</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="I3">
         <v>10.5</v>
@@ -1242,7 +1329,7 @@
         <v>1.55</v>
       </c>
       <c r="S3">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="T3">
         <v>2.1</v>
@@ -1296,7 +1383,7 @@
         <v>11</v>
       </c>
       <c r="AK3">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AL3">
         <v>38</v>
@@ -1335,7 +1422,7 @@
         <v>42</v>
       </c>
       <c r="AX3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY3">
         <v>9.6</v>
@@ -1353,13 +1440,13 @@
         <v>13</v>
       </c>
       <c r="BD3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE3">
         <v>46</v>
       </c>
       <c r="BF3">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BG3">
         <v>46</v>
@@ -1374,16 +1461,16 @@
         <v>12.5</v>
       </c>
       <c r="BK3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN3">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BO3">
         <v>3.1</v>
@@ -1398,34 +1485,34 @@
         <v>24</v>
       </c>
       <c r="BS3">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT3">
         <v>14</v>
       </c>
       <c r="BU3">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
+        <v>13.5</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
         <v>13</v>
-      </c>
-      <c r="BX3">
-        <v>1000</v>
-      </c>
-      <c r="BY3">
-        <v>12.5</v>
       </c>
       <c r="BZ3">
         <v>12.5</v>
       </c>
       <c r="CA3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB3" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1433,28 +1520,28 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="E4" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="F4">
         <v>1.64</v>
       </c>
       <c r="G4">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="H4">
         <v>5.4</v>
       </c>
       <c r="I4">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J4">
         <v>4.5</v>
@@ -1475,7 +1562,7 @@
         <v>1.22</v>
       </c>
       <c r="P4">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="Q4">
         <v>1.66</v>
@@ -1487,7 +1574,7 @@
         <v>2.66</v>
       </c>
       <c r="T4">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U4">
         <v>2.3</v>
@@ -1496,7 +1583,7 @@
         <v>1.21</v>
       </c>
       <c r="W4">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="X4">
         <v>23</v>
@@ -1505,7 +1592,7 @@
         <v>25</v>
       </c>
       <c r="Z4">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA4">
         <v>150</v>
@@ -1514,13 +1601,13 @@
         <v>11.5</v>
       </c>
       <c r="AC4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD4">
         <v>22</v>
       </c>
       <c r="AE4">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF4">
         <v>11.5</v>
@@ -1541,7 +1628,7 @@
         <v>15.5</v>
       </c>
       <c r="AL4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM4">
         <v>85</v>
@@ -1562,13 +1649,13 @@
         <v>38</v>
       </c>
       <c r="AS4">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AT4">
         <v>10</v>
       </c>
       <c r="AU4">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV4">
         <v>18.5</v>
@@ -1580,7 +1667,7 @@
         <v>10</v>
       </c>
       <c r="AY4">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ4">
         <v>16</v>
@@ -1628,13 +1715,13 @@
         <v>4.6</v>
       </c>
       <c r="BO4">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="BP4">
         <v>11</v>
       </c>
       <c r="BQ4">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BR4">
         <v>23</v>
@@ -1667,7 +1754,7 @@
         <v>6.2</v>
       </c>
       <c r="CB4" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1675,16 +1762,16 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="E5" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="F5">
         <v>2.96</v>
@@ -1696,7 +1783,7 @@
         <v>2.72</v>
       </c>
       <c r="I5">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="J5">
         <v>3.1</v>
@@ -1711,37 +1798,37 @@
         <v>1.11</v>
       </c>
       <c r="N5">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="O5">
         <v>1.48</v>
       </c>
       <c r="P5">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="Q5">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R5">
         <v>1.23</v>
       </c>
       <c r="S5">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="T5">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U5">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V5">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W5">
         <v>1.47</v>
       </c>
       <c r="X5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y5">
         <v>8.800000000000001</v>
@@ -1771,7 +1858,7 @@
         <v>15.5</v>
       </c>
       <c r="AH5">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI5">
         <v>70</v>
@@ -1804,7 +1891,7 @@
         <v>15.5</v>
       </c>
       <c r="AS5">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AT5">
         <v>8.4</v>
@@ -1816,7 +1903,7 @@
         <v>11.5</v>
       </c>
       <c r="AW5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AX5">
         <v>16.5</v>
@@ -1828,25 +1915,25 @@
         <v>18</v>
       </c>
       <c r="BA5">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB5">
+        <v>9</v>
+      </c>
+      <c r="BC5">
+        <v>8.6</v>
+      </c>
+      <c r="BD5">
         <v>9.199999999999999</v>
-      </c>
-      <c r="BC5">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BD5">
-        <v>9.6</v>
       </c>
       <c r="BE5">
         <v>10</v>
       </c>
       <c r="BF5">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BG5">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BH5">
         <v>3.35</v>
@@ -1909,7 +1996,7 @@
         <v>1.44</v>
       </c>
       <c r="CB5" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1917,28 +2004,28 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="E6" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="F6">
         <v>4.7</v>
       </c>
       <c r="G6">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="H6">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="I6">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="J6">
         <v>3.5</v>
@@ -1959,10 +2046,10 @@
         <v>1.38</v>
       </c>
       <c r="P6">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q6">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R6">
         <v>1.3</v>
@@ -1971,13 +2058,13 @@
         <v>3.95</v>
       </c>
       <c r="T6">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="U6">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="V6">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="W6">
         <v>1.24</v>
@@ -1989,13 +2076,13 @@
         <v>8</v>
       </c>
       <c r="Z6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AA6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC6">
         <v>8.199999999999999</v>
@@ -2007,16 +2094,16 @@
         <v>23</v>
       </c>
       <c r="AF6">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AG6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH6">
         <v>24</v>
       </c>
       <c r="AI6">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AJ6">
         <v>1000</v>
@@ -2034,7 +2121,7 @@
         <v>1000</v>
       </c>
       <c r="AO6">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AP6">
         <v>11</v>
@@ -2046,10 +2133,10 @@
         <v>9.6</v>
       </c>
       <c r="AS6">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AT6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AU6">
         <v>7.4</v>
@@ -2106,7 +2193,7 @@
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BN6">
         <v>8.199999999999999</v>
@@ -2118,7 +2205,7 @@
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BR6">
         <v>1000</v>
@@ -2130,7 +2217,7 @@
         <v>4.5</v>
       </c>
       <c r="BU6">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BV6">
         <v>14</v>
@@ -2145,13 +2232,13 @@
         <v>10</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA6">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CB6" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2159,16 +2246,16 @@
         <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="E7" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="F7">
         <v>1.86</v>
@@ -2177,7 +2264,7 @@
         <v>1.93</v>
       </c>
       <c r="H7">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I7">
         <v>5.4</v>
@@ -2195,7 +2282,7 @@
         <v>1.1</v>
       </c>
       <c r="N7">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O7">
         <v>1.45</v>
@@ -2231,7 +2318,7 @@
         <v>16.5</v>
       </c>
       <c r="Z7">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA7">
         <v>160</v>
@@ -2249,13 +2336,13 @@
         <v>100</v>
       </c>
       <c r="AF7">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AG7">
         <v>12.5</v>
       </c>
       <c r="AH7">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI7">
         <v>110</v>
@@ -2393,7 +2480,7 @@
         <v>10</v>
       </c>
       <c r="CB7" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2401,22 +2488,22 @@
         <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E8" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="F8">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G8">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H8">
         <v>2.22</v>
@@ -2476,7 +2563,7 @@
         <v>17.5</v>
       </c>
       <c r="AA8">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AB8">
         <v>19.5</v>
@@ -2488,7 +2575,7 @@
         <v>11.5</v>
       </c>
       <c r="AE8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF8">
         <v>30</v>
@@ -2572,7 +2659,7 @@
         <v>18.5</v>
       </c>
       <c r="BG8">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2635,7 +2722,7 @@
         <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2643,16 +2730,16 @@
         <v>83</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="E9" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="F9">
         <v>1.12</v>
@@ -2661,16 +2748,16 @@
         <v>1.14</v>
       </c>
       <c r="H9">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="I9">
         <v>30</v>
       </c>
       <c r="J9">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="K9">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2694,7 +2781,7 @@
         <v>2.26</v>
       </c>
       <c r="S9">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="T9">
         <v>2.04</v>
@@ -2709,7 +2796,7 @@
         <v>1.01</v>
       </c>
       <c r="X9">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="Y9">
         <v>950</v>
@@ -2721,10 +2808,10 @@
         <v>1000</v>
       </c>
       <c r="AB9">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC9">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AD9">
         <v>950</v>
@@ -2733,7 +2820,7 @@
         <v>400</v>
       </c>
       <c r="AF9">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG9">
         <v>15.5</v>
@@ -2769,7 +2856,7 @@
         <v>10</v>
       </c>
       <c r="AR9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS9">
         <v>11</v>
@@ -2778,13 +2865,13 @@
         <v>12.5</v>
       </c>
       <c r="AU9">
-        <v>18</v>
+        <v>8.6</v>
       </c>
       <c r="AV9">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX9">
         <v>8.199999999999999</v>
@@ -2805,16 +2892,16 @@
         <v>10</v>
       </c>
       <c r="BD9">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE9">
         <v>10.5</v>
       </c>
       <c r="BF9">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="BG9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -2877,7 +2964,7 @@
         <v>1.04</v>
       </c>
       <c r="CB9" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2885,22 +2972,22 @@
         <v>80</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="E10" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="F10">
         <v>2.14</v>
       </c>
       <c r="G10">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="H10">
         <v>3.9</v>
@@ -2918,7 +3005,7 @@
         <v>1.01</v>
       </c>
       <c r="M10">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N10">
         <v>2.4</v>
@@ -2948,7 +3035,7 @@
         <v>1.28</v>
       </c>
       <c r="W10">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="X10">
         <v>12.5</v>
@@ -3068,7 +3155,7 @@
         <v>16</v>
       </c>
       <c r="BK10">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="BL10">
         <v>1000</v>
@@ -3083,7 +3170,7 @@
         <v>3.2</v>
       </c>
       <c r="BP10">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BQ10">
         <v>3.15</v>
@@ -3092,7 +3179,7 @@
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BT10">
         <v>10</v>
@@ -3104,22 +3191,22 @@
         <v>1000</v>
       </c>
       <c r="BW10">
+        <v>3.35</v>
+      </c>
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
         <v>3.4</v>
       </c>
-      <c r="BX10">
-        <v>1000</v>
-      </c>
-      <c r="BY10">
-        <v>3.45</v>
-      </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="CB10" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3127,31 +3214,31 @@
         <v>84</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E11" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="F11">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="G11">
         <v>1000</v>
       </c>
       <c r="H11">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="I11">
         <v>1000</v>
       </c>
       <c r="J11">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="K11">
         <v>100</v>
@@ -3163,7 +3250,7 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="O11">
         <v>1.01</v>
@@ -3184,10 +3271,10 @@
         <v>1.11</v>
       </c>
       <c r="U11">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V11">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W11">
         <v>1.03</v>
@@ -3361,7 +3448,7 @@
         <v>1.04</v>
       </c>
       <c r="CB11" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3369,31 +3456,31 @@
         <v>84</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="E12" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="F12">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="G12">
         <v>1000</v>
       </c>
       <c r="H12">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="I12">
         <v>1000</v>
       </c>
       <c r="J12">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="K12">
         <v>100</v>
@@ -3405,34 +3492,34 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="O12">
         <v>1.01</v>
       </c>
       <c r="P12">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Q12">
         <v>1.02</v>
       </c>
       <c r="R12">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="S12">
         <v>1.05</v>
       </c>
       <c r="T12">
+        <v>1.01</v>
+      </c>
+      <c r="U12">
         <v>1.11</v>
       </c>
-      <c r="U12">
-        <v>1.01</v>
-      </c>
       <c r="V12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W12">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3603,7 +3690,7 @@
         <v>1.04</v>
       </c>
       <c r="CB12" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3611,31 +3698,31 @@
         <v>84</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D13" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="E13" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="F13">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="G13">
         <v>1000</v>
       </c>
       <c r="H13">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="I13">
         <v>1000</v>
       </c>
       <c r="J13">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="K13">
         <v>100</v>
@@ -3647,34 +3734,34 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="O13">
         <v>1.01</v>
       </c>
       <c r="P13">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q13">
         <v>1.02</v>
       </c>
       <c r="R13">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="S13">
         <v>1.05</v>
       </c>
       <c r="T13">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U13">
         <v>1.11</v>
       </c>
       <c r="V13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W13">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -3845,7 +3932,2669 @@
         <v>1.04</v>
       </c>
       <c r="CB13" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" t="s">
+        <v>112</v>
+      </c>
+      <c r="E14" t="s">
+        <v>135</v>
+      </c>
+      <c r="F14">
+        <v>1.19</v>
+      </c>
+      <c r="G14">
+        <v>1.25</v>
+      </c>
+      <c r="H14">
+        <v>18.5</v>
+      </c>
+      <c r="I14">
+        <v>28</v>
+      </c>
+      <c r="J14">
+        <v>6.8</v>
+      </c>
+      <c r="K14">
+        <v>8.6</v>
+      </c>
+      <c r="L14">
+        <v>1.01</v>
+      </c>
+      <c r="M14">
+        <v>1.01</v>
+      </c>
+      <c r="N14">
+        <v>4.7</v>
+      </c>
+      <c r="O14">
+        <v>1.18</v>
+      </c>
+      <c r="P14">
+        <v>2.38</v>
+      </c>
+      <c r="Q14">
+        <v>1.57</v>
+      </c>
+      <c r="R14">
+        <v>1.51</v>
+      </c>
+      <c r="S14">
+        <v>2.3</v>
+      </c>
+      <c r="T14">
+        <v>1.11</v>
+      </c>
+      <c r="U14">
+        <v>1.11</v>
+      </c>
+      <c r="V14">
+        <v>1.04</v>
+      </c>
+      <c r="W14">
+        <v>5</v>
+      </c>
+      <c r="X14">
+        <v>950</v>
+      </c>
+      <c r="Y14">
+        <v>1000</v>
+      </c>
+      <c r="Z14">
+        <v>1000</v>
+      </c>
+      <c r="AA14">
+        <v>1000</v>
+      </c>
+      <c r="AB14">
+        <v>11.5</v>
+      </c>
+      <c r="AC14">
+        <v>22</v>
+      </c>
+      <c r="AD14">
+        <v>950</v>
+      </c>
+      <c r="AE14">
+        <v>1000</v>
+      </c>
+      <c r="AF14">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG14">
+        <v>1000</v>
+      </c>
+      <c r="AH14">
+        <v>1000</v>
+      </c>
+      <c r="AI14">
+        <v>1000</v>
+      </c>
+      <c r="AJ14">
+        <v>11</v>
+      </c>
+      <c r="AK14">
+        <v>19.5</v>
+      </c>
+      <c r="AL14">
+        <v>65</v>
+      </c>
+      <c r="AM14">
+        <v>1000</v>
+      </c>
+      <c r="AN14">
+        <v>5</v>
+      </c>
+      <c r="AO14">
+        <v>1000</v>
+      </c>
+      <c r="AP14">
+        <v>2.56</v>
+      </c>
+      <c r="AQ14">
+        <v>2.78</v>
+      </c>
+      <c r="AR14">
+        <v>2.78</v>
+      </c>
+      <c r="AS14">
+        <v>2.78</v>
+      </c>
+      <c r="AT14">
+        <v>2.24</v>
+      </c>
+      <c r="AU14">
+        <v>2.46</v>
+      </c>
+      <c r="AV14">
+        <v>2.7</v>
+      </c>
+      <c r="AW14">
+        <v>2.78</v>
+      </c>
+      <c r="AX14">
+        <v>2.14</v>
+      </c>
+      <c r="AY14">
+        <v>2.78</v>
+      </c>
+      <c r="AZ14">
+        <v>2.78</v>
+      </c>
+      <c r="BA14">
+        <v>2.78</v>
+      </c>
+      <c r="BB14">
+        <v>2.22</v>
+      </c>
+      <c r="BC14">
+        <v>10.5</v>
+      </c>
+      <c r="BD14">
+        <v>2.66</v>
+      </c>
+      <c r="BE14">
+        <v>2.78</v>
+      </c>
+      <c r="BF14">
+        <v>1.79</v>
+      </c>
+      <c r="BG14">
+        <v>2.78</v>
+      </c>
+      <c r="BH14">
+        <v>6</v>
+      </c>
+      <c r="BI14">
+        <v>3</v>
+      </c>
+      <c r="BJ14">
+        <v>22</v>
+      </c>
+      <c r="BK14">
+        <v>2.64</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>3</v>
+      </c>
+      <c r="BN14">
+        <v>4.8</v>
+      </c>
+      <c r="BO14">
+        <v>2.54</v>
+      </c>
+      <c r="BP14">
+        <v>9</v>
+      </c>
+      <c r="BQ14">
+        <v>4.1</v>
+      </c>
+      <c r="BR14">
+        <v>38</v>
+      </c>
+      <c r="BS14">
+        <v>2.8</v>
+      </c>
+      <c r="BT14">
+        <v>29</v>
+      </c>
+      <c r="BU14">
+        <v>2.72</v>
+      </c>
+      <c r="BV14">
+        <v>1000</v>
+      </c>
+      <c r="BW14">
+        <v>3</v>
+      </c>
+      <c r="BX14">
+        <v>1000</v>
+      </c>
+      <c r="BY14">
+        <v>3</v>
+      </c>
+      <c r="BZ14">
+        <v>13.5</v>
+      </c>
+      <c r="CA14">
+        <v>2.46</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" t="s">
+        <v>97</v>
+      </c>
+      <c r="D15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" t="s">
+        <v>136</v>
+      </c>
+      <c r="F15">
+        <v>4.6</v>
+      </c>
+      <c r="G15">
+        <v>4.8</v>
+      </c>
+      <c r="H15">
+        <v>1.99</v>
+      </c>
+      <c r="I15">
+        <v>2</v>
+      </c>
+      <c r="J15">
+        <v>3.45</v>
+      </c>
+      <c r="K15">
+        <v>3.55</v>
+      </c>
+      <c r="L15">
+        <v>1.36</v>
+      </c>
+      <c r="M15">
+        <v>1.1</v>
+      </c>
+      <c r="N15">
+        <v>3.15</v>
+      </c>
+      <c r="O15">
+        <v>1.41</v>
+      </c>
+      <c r="P15">
+        <v>1.73</v>
+      </c>
+      <c r="Q15">
+        <v>2.28</v>
+      </c>
+      <c r="R15">
+        <v>1.26</v>
+      </c>
+      <c r="S15">
+        <v>4.3</v>
+      </c>
+      <c r="T15">
+        <v>2.02</v>
+      </c>
+      <c r="U15">
+        <v>1.89</v>
+      </c>
+      <c r="V15">
+        <v>2</v>
+      </c>
+      <c r="W15">
+        <v>1.26</v>
+      </c>
+      <c r="X15">
+        <v>11</v>
+      </c>
+      <c r="Y15">
+        <v>7.8</v>
+      </c>
+      <c r="Z15">
+        <v>11</v>
+      </c>
+      <c r="AA15">
+        <v>25</v>
+      </c>
+      <c r="AB15">
+        <v>14</v>
+      </c>
+      <c r="AC15">
+        <v>7.6</v>
+      </c>
+      <c r="AD15">
+        <v>11</v>
+      </c>
+      <c r="AE15">
+        <v>24</v>
+      </c>
+      <c r="AF15">
+        <v>34</v>
+      </c>
+      <c r="AG15">
+        <v>19</v>
+      </c>
+      <c r="AH15">
+        <v>22</v>
+      </c>
+      <c r="AI15">
+        <v>160</v>
+      </c>
+      <c r="AJ15">
+        <v>120</v>
+      </c>
+      <c r="AK15">
+        <v>70</v>
+      </c>
+      <c r="AL15">
+        <v>1000</v>
+      </c>
+      <c r="AM15">
+        <v>1000</v>
+      </c>
+      <c r="AN15">
+        <v>95</v>
+      </c>
+      <c r="AO15">
+        <v>20</v>
+      </c>
+      <c r="AP15">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ15">
+        <v>7.2</v>
+      </c>
+      <c r="AR15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS15">
+        <v>20</v>
+      </c>
+      <c r="AT15">
+        <v>12.5</v>
+      </c>
+      <c r="AU15">
+        <v>7</v>
+      </c>
+      <c r="AV15">
+        <v>9</v>
+      </c>
+      <c r="AW15">
+        <v>16</v>
+      </c>
+      <c r="AX15">
+        <v>19.5</v>
+      </c>
+      <c r="AY15">
+        <v>17</v>
+      </c>
+      <c r="AZ15">
+        <v>19.5</v>
+      </c>
+      <c r="BA15">
+        <v>40</v>
+      </c>
+      <c r="BB15">
+        <v>38</v>
+      </c>
+      <c r="BC15">
+        <v>42</v>
+      </c>
+      <c r="BD15">
+        <v>36</v>
+      </c>
+      <c r="BE15">
+        <v>42</v>
+      </c>
+      <c r="BF15">
+        <v>34</v>
+      </c>
+      <c r="BG15">
+        <v>15.5</v>
+      </c>
+      <c r="BH15">
+        <v>1000</v>
+      </c>
+      <c r="BI15">
+        <v>1.86</v>
+      </c>
+      <c r="BJ15">
+        <v>14.5</v>
+      </c>
+      <c r="BK15">
+        <v>1.65</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>1.86</v>
+      </c>
+      <c r="BN15">
+        <v>10</v>
+      </c>
+      <c r="BO15">
+        <v>5.1</v>
+      </c>
+      <c r="BP15">
+        <v>1000</v>
+      </c>
+      <c r="BQ15">
+        <v>1.8</v>
+      </c>
+      <c r="BR15">
+        <v>1000</v>
+      </c>
+      <c r="BS15">
+        <v>1.81</v>
+      </c>
+      <c r="BT15">
+        <v>6</v>
+      </c>
+      <c r="BU15">
+        <v>3.2</v>
+      </c>
+      <c r="BV15">
+        <v>20</v>
+      </c>
+      <c r="BW15">
+        <v>1.7</v>
+      </c>
+      <c r="BX15">
+        <v>46</v>
+      </c>
+      <c r="BY15">
+        <v>1.79</v>
+      </c>
+      <c r="BZ15">
+        <v>44</v>
+      </c>
+      <c r="CA15">
+        <v>1.78</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" t="s">
+        <v>114</v>
+      </c>
+      <c r="E16" t="s">
+        <v>137</v>
+      </c>
+      <c r="F16">
+        <v>2.22</v>
+      </c>
+      <c r="G16">
+        <v>2.32</v>
+      </c>
+      <c r="H16">
+        <v>3.6</v>
+      </c>
+      <c r="I16">
+        <v>3.95</v>
+      </c>
+      <c r="J16">
+        <v>3.2</v>
+      </c>
+      <c r="K16">
+        <v>3.45</v>
+      </c>
+      <c r="L16">
+        <v>1.35</v>
+      </c>
+      <c r="M16">
+        <v>1.09</v>
+      </c>
+      <c r="N16">
+        <v>3.05</v>
+      </c>
+      <c r="O16">
+        <v>1.42</v>
+      </c>
+      <c r="P16">
+        <v>1.72</v>
+      </c>
+      <c r="Q16">
+        <v>2.24</v>
+      </c>
+      <c r="R16">
+        <v>1.27</v>
+      </c>
+      <c r="S16">
+        <v>4.2</v>
+      </c>
+      <c r="T16">
+        <v>1.92</v>
+      </c>
+      <c r="U16">
+        <v>1.96</v>
+      </c>
+      <c r="V16">
+        <v>1.34</v>
+      </c>
+      <c r="W16">
+        <v>1.76</v>
+      </c>
+      <c r="X16">
+        <v>11.5</v>
+      </c>
+      <c r="Y16">
+        <v>12</v>
+      </c>
+      <c r="Z16">
+        <v>27</v>
+      </c>
+      <c r="AA16">
+        <v>80</v>
+      </c>
+      <c r="AB16">
+        <v>8.4</v>
+      </c>
+      <c r="AC16">
+        <v>7.6</v>
+      </c>
+      <c r="AD16">
+        <v>950</v>
+      </c>
+      <c r="AE16">
+        <v>55</v>
+      </c>
+      <c r="AF16">
+        <v>14</v>
+      </c>
+      <c r="AG16">
+        <v>11.5</v>
+      </c>
+      <c r="AH16">
+        <v>950</v>
+      </c>
+      <c r="AI16">
+        <v>70</v>
+      </c>
+      <c r="AJ16">
+        <v>32</v>
+      </c>
+      <c r="AK16">
+        <v>28</v>
+      </c>
+      <c r="AL16">
+        <v>48</v>
+      </c>
+      <c r="AM16">
+        <v>150</v>
+      </c>
+      <c r="AN16">
+        <v>25</v>
+      </c>
+      <c r="AO16">
+        <v>65</v>
+      </c>
+      <c r="AP16">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ16">
+        <v>10.5</v>
+      </c>
+      <c r="AR16">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS16">
+        <v>11</v>
+      </c>
+      <c r="AT16">
+        <v>7.4</v>
+      </c>
+      <c r="AU16">
+        <v>6.6</v>
+      </c>
+      <c r="AV16">
+        <v>14</v>
+      </c>
+      <c r="AW16">
+        <v>10.5</v>
+      </c>
+      <c r="AX16">
+        <v>12</v>
+      </c>
+      <c r="AY16">
+        <v>10</v>
+      </c>
+      <c r="AZ16">
+        <v>7.8</v>
+      </c>
+      <c r="BA16">
+        <v>11</v>
+      </c>
+      <c r="BB16">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC16">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD16">
+        <v>10</v>
+      </c>
+      <c r="BE16">
+        <v>12</v>
+      </c>
+      <c r="BF16">
+        <v>18.5</v>
+      </c>
+      <c r="BG16">
+        <v>10.5</v>
+      </c>
+      <c r="BH16">
+        <v>1000</v>
+      </c>
+      <c r="BI16">
+        <v>1.04</v>
+      </c>
+      <c r="BJ16">
+        <v>1000</v>
+      </c>
+      <c r="BK16">
+        <v>1.04</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>1.04</v>
+      </c>
+      <c r="BN16">
+        <v>1000</v>
+      </c>
+      <c r="BO16">
+        <v>1.04</v>
+      </c>
+      <c r="BP16">
+        <v>1000</v>
+      </c>
+      <c r="BQ16">
+        <v>1.04</v>
+      </c>
+      <c r="BR16">
+        <v>1000</v>
+      </c>
+      <c r="BS16">
+        <v>1.04</v>
+      </c>
+      <c r="BT16">
+        <v>1000</v>
+      </c>
+      <c r="BU16">
+        <v>1.04</v>
+      </c>
+      <c r="BV16">
+        <v>1000</v>
+      </c>
+      <c r="BW16">
+        <v>1.04</v>
+      </c>
+      <c r="BX16">
+        <v>1000</v>
+      </c>
+      <c r="BY16">
+        <v>1.04</v>
+      </c>
+      <c r="BZ16">
+        <v>1000</v>
+      </c>
+      <c r="CA16">
+        <v>1.04</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
+        <v>85</v>
+      </c>
+      <c r="B17" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" t="s">
+        <v>115</v>
+      </c>
+      <c r="E17" t="s">
+        <v>138</v>
+      </c>
+      <c r="F17">
+        <v>1.39</v>
+      </c>
+      <c r="G17">
+        <v>1.47</v>
+      </c>
+      <c r="H17">
+        <v>9.4</v>
+      </c>
+      <c r="I17">
+        <v>13</v>
+      </c>
+      <c r="J17">
+        <v>4.5</v>
+      </c>
+      <c r="K17">
+        <v>5.1</v>
+      </c>
+      <c r="L17">
+        <v>1.25</v>
+      </c>
+      <c r="M17">
+        <v>1.07</v>
+      </c>
+      <c r="N17">
+        <v>3.55</v>
+      </c>
+      <c r="O17">
+        <v>1.33</v>
+      </c>
+      <c r="P17">
+        <v>1.9</v>
+      </c>
+      <c r="Q17">
+        <v>1.98</v>
+      </c>
+      <c r="R17">
+        <v>1.33</v>
+      </c>
+      <c r="S17">
+        <v>3.6</v>
+      </c>
+      <c r="T17">
+        <v>2.26</v>
+      </c>
+      <c r="U17">
+        <v>1.64</v>
+      </c>
+      <c r="V17">
+        <v>1.09</v>
+      </c>
+      <c r="W17">
+        <v>3.15</v>
+      </c>
+      <c r="X17">
+        <v>17.5</v>
+      </c>
+      <c r="Y17">
+        <v>34</v>
+      </c>
+      <c r="Z17">
+        <v>120</v>
+      </c>
+      <c r="AA17">
+        <v>590</v>
+      </c>
+      <c r="AB17">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC17">
+        <v>13.5</v>
+      </c>
+      <c r="AD17">
+        <v>50</v>
+      </c>
+      <c r="AE17">
+        <v>270</v>
+      </c>
+      <c r="AF17">
+        <v>9</v>
+      </c>
+      <c r="AG17">
+        <v>12.5</v>
+      </c>
+      <c r="AH17">
+        <v>40</v>
+      </c>
+      <c r="AI17">
+        <v>230</v>
+      </c>
+      <c r="AJ17">
+        <v>14.5</v>
+      </c>
+      <c r="AK17">
+        <v>21</v>
+      </c>
+      <c r="AL17">
+        <v>60</v>
+      </c>
+      <c r="AM17">
+        <v>290</v>
+      </c>
+      <c r="AN17">
+        <v>10</v>
+      </c>
+      <c r="AO17">
+        <v>480</v>
+      </c>
+      <c r="AP17">
+        <v>12</v>
+      </c>
+      <c r="AQ17">
+        <v>3.9</v>
+      </c>
+      <c r="AR17">
+        <v>4.2</v>
+      </c>
+      <c r="AS17">
+        <v>4.4</v>
+      </c>
+      <c r="AT17">
+        <v>5.9</v>
+      </c>
+      <c r="AU17">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV17">
+        <v>4</v>
+      </c>
+      <c r="AW17">
+        <v>4.3</v>
+      </c>
+      <c r="AX17">
+        <v>6.4</v>
+      </c>
+      <c r="AY17">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ17">
+        <v>4</v>
+      </c>
+      <c r="BA17">
+        <v>4.3</v>
+      </c>
+      <c r="BB17">
+        <v>10</v>
+      </c>
+      <c r="BC17">
+        <v>14.5</v>
+      </c>
+      <c r="BD17">
+        <v>4.1</v>
+      </c>
+      <c r="BE17">
+        <v>4.3</v>
+      </c>
+      <c r="BF17">
+        <v>6.2</v>
+      </c>
+      <c r="BG17">
+        <v>4.4</v>
+      </c>
+      <c r="BH17">
+        <v>4</v>
+      </c>
+      <c r="BI17">
+        <v>2.6</v>
+      </c>
+      <c r="BJ17">
+        <v>1000</v>
+      </c>
+      <c r="BK17">
+        <v>1.34</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
+        <v>1.34</v>
+      </c>
+      <c r="BN17">
+        <v>1000</v>
+      </c>
+      <c r="BO17">
+        <v>1.34</v>
+      </c>
+      <c r="BP17">
+        <v>1000</v>
+      </c>
+      <c r="BQ17">
+        <v>1.34</v>
+      </c>
+      <c r="BR17">
+        <v>1000</v>
+      </c>
+      <c r="BS17">
+        <v>1.34</v>
+      </c>
+      <c r="BT17">
+        <v>1000</v>
+      </c>
+      <c r="BU17">
+        <v>1.34</v>
+      </c>
+      <c r="BV17">
+        <v>1000</v>
+      </c>
+      <c r="BW17">
+        <v>1.34</v>
+      </c>
+      <c r="BX17">
+        <v>1000</v>
+      </c>
+      <c r="BY17">
+        <v>1.34</v>
+      </c>
+      <c r="BZ17">
+        <v>1000</v>
+      </c>
+      <c r="CA17">
+        <v>1.34</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80">
+      <c r="A18" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" t="s">
+        <v>88</v>
+      </c>
+      <c r="C18" t="s">
+        <v>98</v>
+      </c>
+      <c r="D18" t="s">
+        <v>116</v>
+      </c>
+      <c r="E18" t="s">
+        <v>139</v>
+      </c>
+      <c r="F18">
+        <v>1.8</v>
+      </c>
+      <c r="G18">
+        <v>1.9</v>
+      </c>
+      <c r="H18">
+        <v>4.2</v>
+      </c>
+      <c r="I18">
+        <v>4.9</v>
+      </c>
+      <c r="J18">
+        <v>3.9</v>
+      </c>
+      <c r="K18">
+        <v>4.5</v>
+      </c>
+      <c r="L18">
+        <v>1.01</v>
+      </c>
+      <c r="M18">
+        <v>1.05</v>
+      </c>
+      <c r="N18">
+        <v>3.95</v>
+      </c>
+      <c r="O18">
+        <v>1.21</v>
+      </c>
+      <c r="P18">
+        <v>2.12</v>
+      </c>
+      <c r="Q18">
+        <v>1.75</v>
+      </c>
+      <c r="R18">
+        <v>1.39</v>
+      </c>
+      <c r="S18">
+        <v>2.8</v>
+      </c>
+      <c r="T18">
+        <v>1.71</v>
+      </c>
+      <c r="U18">
+        <v>2.18</v>
+      </c>
+      <c r="V18">
+        <v>1.25</v>
+      </c>
+      <c r="W18">
+        <v>2.1</v>
+      </c>
+      <c r="X18">
+        <v>1000</v>
+      </c>
+      <c r="Y18">
+        <v>1000</v>
+      </c>
+      <c r="Z18">
+        <v>1000</v>
+      </c>
+      <c r="AA18">
+        <v>1000</v>
+      </c>
+      <c r="AB18">
+        <v>1000</v>
+      </c>
+      <c r="AC18">
+        <v>1000</v>
+      </c>
+      <c r="AD18">
+        <v>1000</v>
+      </c>
+      <c r="AE18">
+        <v>1000</v>
+      </c>
+      <c r="AF18">
+        <v>1000</v>
+      </c>
+      <c r="AG18">
+        <v>1000</v>
+      </c>
+      <c r="AH18">
+        <v>1000</v>
+      </c>
+      <c r="AI18">
+        <v>1000</v>
+      </c>
+      <c r="AJ18">
+        <v>1000</v>
+      </c>
+      <c r="AK18">
+        <v>1000</v>
+      </c>
+      <c r="AL18">
+        <v>1000</v>
+      </c>
+      <c r="AM18">
+        <v>1000</v>
+      </c>
+      <c r="AN18">
+        <v>1000</v>
+      </c>
+      <c r="AO18">
+        <v>1000</v>
+      </c>
+      <c r="AP18">
+        <v>1.03</v>
+      </c>
+      <c r="AQ18">
+        <v>1.03</v>
+      </c>
+      <c r="AR18">
+        <v>1.03</v>
+      </c>
+      <c r="AS18">
+        <v>1.03</v>
+      </c>
+      <c r="AT18">
+        <v>1.03</v>
+      </c>
+      <c r="AU18">
+        <v>1.03</v>
+      </c>
+      <c r="AV18">
+        <v>1.03</v>
+      </c>
+      <c r="AW18">
+        <v>1.03</v>
+      </c>
+      <c r="AX18">
+        <v>1.03</v>
+      </c>
+      <c r="AY18">
+        <v>1.03</v>
+      </c>
+      <c r="AZ18">
+        <v>1.03</v>
+      </c>
+      <c r="BA18">
+        <v>1.03</v>
+      </c>
+      <c r="BB18">
+        <v>1.03</v>
+      </c>
+      <c r="BC18">
+        <v>1.03</v>
+      </c>
+      <c r="BD18">
+        <v>1.03</v>
+      </c>
+      <c r="BE18">
+        <v>1.03</v>
+      </c>
+      <c r="BF18">
+        <v>1.01</v>
+      </c>
+      <c r="BG18">
+        <v>1.01</v>
+      </c>
+      <c r="BH18">
+        <v>1000</v>
+      </c>
+      <c r="BI18">
+        <v>1.01</v>
+      </c>
+      <c r="BJ18">
+        <v>1000</v>
+      </c>
+      <c r="BK18">
+        <v>1.01</v>
+      </c>
+      <c r="BL18">
+        <v>1000</v>
+      </c>
+      <c r="BM18">
+        <v>1.01</v>
+      </c>
+      <c r="BN18">
+        <v>1000</v>
+      </c>
+      <c r="BO18">
+        <v>1.01</v>
+      </c>
+      <c r="BP18">
+        <v>1000</v>
+      </c>
+      <c r="BQ18">
+        <v>1.01</v>
+      </c>
+      <c r="BR18">
+        <v>1000</v>
+      </c>
+      <c r="BS18">
+        <v>1.01</v>
+      </c>
+      <c r="BT18">
+        <v>1000</v>
+      </c>
+      <c r="BU18">
+        <v>1.01</v>
+      </c>
+      <c r="BV18">
+        <v>1000</v>
+      </c>
+      <c r="BW18">
+        <v>1.01</v>
+      </c>
+      <c r="BX18">
+        <v>1000</v>
+      </c>
+      <c r="BY18">
+        <v>1.01</v>
+      </c>
+      <c r="BZ18">
+        <v>1000</v>
+      </c>
+      <c r="CA18">
+        <v>1.01</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="19" spans="1:80">
+      <c r="A19" t="s">
+        <v>87</v>
+      </c>
+      <c r="B19" t="s">
+        <v>88</v>
+      </c>
+      <c r="C19" t="s">
+        <v>99</v>
+      </c>
+      <c r="D19" t="s">
         <v>117</v>
+      </c>
+      <c r="E19" t="s">
+        <v>140</v>
+      </c>
+      <c r="F19">
+        <v>3.95</v>
+      </c>
+      <c r="G19">
+        <v>4.1</v>
+      </c>
+      <c r="H19">
+        <v>1.85</v>
+      </c>
+      <c r="I19">
+        <v>1.9</v>
+      </c>
+      <c r="J19">
+        <v>4.3</v>
+      </c>
+      <c r="K19">
+        <v>4.7</v>
+      </c>
+      <c r="L19">
+        <v>1.23</v>
+      </c>
+      <c r="M19">
+        <v>1.02</v>
+      </c>
+      <c r="N19">
+        <v>7.4</v>
+      </c>
+      <c r="O19">
+        <v>1.14</v>
+      </c>
+      <c r="P19">
+        <v>3.15</v>
+      </c>
+      <c r="Q19">
+        <v>1.43</v>
+      </c>
+      <c r="R19">
+        <v>1.88</v>
+      </c>
+      <c r="S19">
+        <v>2.06</v>
+      </c>
+      <c r="T19">
+        <v>1.44</v>
+      </c>
+      <c r="U19">
+        <v>2.96</v>
+      </c>
+      <c r="V19">
+        <v>2.1</v>
+      </c>
+      <c r="W19">
+        <v>1.32</v>
+      </c>
+      <c r="X19">
+        <v>44</v>
+      </c>
+      <c r="Y19">
+        <v>18.5</v>
+      </c>
+      <c r="Z19">
+        <v>18.5</v>
+      </c>
+      <c r="AA19">
+        <v>30</v>
+      </c>
+      <c r="AB19">
+        <v>34</v>
+      </c>
+      <c r="AC19">
+        <v>13.5</v>
+      </c>
+      <c r="AD19">
+        <v>13.5</v>
+      </c>
+      <c r="AE19">
+        <v>17.5</v>
+      </c>
+      <c r="AF19">
+        <v>48</v>
+      </c>
+      <c r="AG19">
+        <v>22</v>
+      </c>
+      <c r="AH19">
+        <v>15.5</v>
+      </c>
+      <c r="AI19">
+        <v>27</v>
+      </c>
+      <c r="AJ19">
+        <v>80</v>
+      </c>
+      <c r="AK19">
+        <v>40</v>
+      </c>
+      <c r="AL19">
+        <v>44</v>
+      </c>
+      <c r="AM19">
+        <v>55</v>
+      </c>
+      <c r="AN19">
+        <v>27</v>
+      </c>
+      <c r="AO19">
+        <v>6.6</v>
+      </c>
+      <c r="AP19">
+        <v>5.3</v>
+      </c>
+      <c r="AQ19">
+        <v>15</v>
+      </c>
+      <c r="AR19">
+        <v>15</v>
+      </c>
+      <c r="AS19">
+        <v>21</v>
+      </c>
+      <c r="AT19">
+        <v>5.1</v>
+      </c>
+      <c r="AU19">
+        <v>9.6</v>
+      </c>
+      <c r="AV19">
+        <v>9.6</v>
+      </c>
+      <c r="AW19">
+        <v>13.5</v>
+      </c>
+      <c r="AX19">
+        <v>5.4</v>
+      </c>
+      <c r="AY19">
+        <v>15</v>
+      </c>
+      <c r="AZ19">
+        <v>12</v>
+      </c>
+      <c r="BA19">
+        <v>19</v>
+      </c>
+      <c r="BB19">
+        <v>5.6</v>
+      </c>
+      <c r="BC19">
+        <v>5.3</v>
+      </c>
+      <c r="BD19">
+        <v>5.3</v>
+      </c>
+      <c r="BE19">
+        <v>5.5</v>
+      </c>
+      <c r="BF19">
+        <v>16</v>
+      </c>
+      <c r="BG19">
+        <v>6</v>
+      </c>
+      <c r="BH19">
+        <v>1000</v>
+      </c>
+      <c r="BI19">
+        <v>1.01</v>
+      </c>
+      <c r="BJ19">
+        <v>12.5</v>
+      </c>
+      <c r="BK19">
+        <v>5.3</v>
+      </c>
+      <c r="BL19">
+        <v>1000</v>
+      </c>
+      <c r="BM19">
+        <v>21</v>
+      </c>
+      <c r="BN19">
+        <v>11.5</v>
+      </c>
+      <c r="BO19">
+        <v>5.1</v>
+      </c>
+      <c r="BP19">
+        <v>38</v>
+      </c>
+      <c r="BQ19">
+        <v>15.5</v>
+      </c>
+      <c r="BR19">
+        <v>40</v>
+      </c>
+      <c r="BS19">
+        <v>16.5</v>
+      </c>
+      <c r="BT19">
+        <v>7.6</v>
+      </c>
+      <c r="BU19">
+        <v>3.55</v>
+      </c>
+      <c r="BV19">
+        <v>17</v>
+      </c>
+      <c r="BW19">
+        <v>7.2</v>
+      </c>
+      <c r="BX19">
+        <v>26</v>
+      </c>
+      <c r="BY19">
+        <v>11</v>
+      </c>
+      <c r="BZ19">
+        <v>16</v>
+      </c>
+      <c r="CA19">
+        <v>7</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80">
+      <c r="A20" t="s">
+        <v>85</v>
+      </c>
+      <c r="B20" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20" t="s">
+        <v>99</v>
+      </c>
+      <c r="D20" t="s">
+        <v>118</v>
+      </c>
+      <c r="E20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F20">
+        <v>2.3</v>
+      </c>
+      <c r="G20">
+        <v>2.46</v>
+      </c>
+      <c r="H20">
+        <v>3.45</v>
+      </c>
+      <c r="I20">
+        <v>3.75</v>
+      </c>
+      <c r="J20">
+        <v>3.2</v>
+      </c>
+      <c r="K20">
+        <v>3.45</v>
+      </c>
+      <c r="L20">
+        <v>1.35</v>
+      </c>
+      <c r="M20">
+        <v>1.1</v>
+      </c>
+      <c r="N20">
+        <v>3</v>
+      </c>
+      <c r="O20">
+        <v>1.41</v>
+      </c>
+      <c r="P20">
+        <v>1.7</v>
+      </c>
+      <c r="Q20">
+        <v>2.16</v>
+      </c>
+      <c r="R20">
+        <v>1.17</v>
+      </c>
+      <c r="S20">
+        <v>3.95</v>
+      </c>
+      <c r="T20">
+        <v>1.92</v>
+      </c>
+      <c r="U20">
+        <v>1.92</v>
+      </c>
+      <c r="V20">
+        <v>1.36</v>
+      </c>
+      <c r="W20">
+        <v>1.68</v>
+      </c>
+      <c r="X20">
+        <v>1000</v>
+      </c>
+      <c r="Y20">
+        <v>1000</v>
+      </c>
+      <c r="Z20">
+        <v>1000</v>
+      </c>
+      <c r="AA20">
+        <v>1000</v>
+      </c>
+      <c r="AB20">
+        <v>1000</v>
+      </c>
+      <c r="AC20">
+        <v>1000</v>
+      </c>
+      <c r="AD20">
+        <v>1000</v>
+      </c>
+      <c r="AE20">
+        <v>1000</v>
+      </c>
+      <c r="AF20">
+        <v>1000</v>
+      </c>
+      <c r="AG20">
+        <v>1000</v>
+      </c>
+      <c r="AH20">
+        <v>1000</v>
+      </c>
+      <c r="AI20">
+        <v>1000</v>
+      </c>
+      <c r="AJ20">
+        <v>1000</v>
+      </c>
+      <c r="AK20">
+        <v>1000</v>
+      </c>
+      <c r="AL20">
+        <v>1000</v>
+      </c>
+      <c r="AM20">
+        <v>1000</v>
+      </c>
+      <c r="AN20">
+        <v>1000</v>
+      </c>
+      <c r="AO20">
+        <v>1000</v>
+      </c>
+      <c r="AP20">
+        <v>1.03</v>
+      </c>
+      <c r="AQ20">
+        <v>1.03</v>
+      </c>
+      <c r="AR20">
+        <v>1.03</v>
+      </c>
+      <c r="AS20">
+        <v>1.03</v>
+      </c>
+      <c r="AT20">
+        <v>1.03</v>
+      </c>
+      <c r="AU20">
+        <v>1.03</v>
+      </c>
+      <c r="AV20">
+        <v>1.03</v>
+      </c>
+      <c r="AW20">
+        <v>1.03</v>
+      </c>
+      <c r="AX20">
+        <v>1.03</v>
+      </c>
+      <c r="AY20">
+        <v>1.03</v>
+      </c>
+      <c r="AZ20">
+        <v>1.03</v>
+      </c>
+      <c r="BA20">
+        <v>1.03</v>
+      </c>
+      <c r="BB20">
+        <v>1.03</v>
+      </c>
+      <c r="BC20">
+        <v>1.03</v>
+      </c>
+      <c r="BD20">
+        <v>1.03</v>
+      </c>
+      <c r="BE20">
+        <v>1.03</v>
+      </c>
+      <c r="BF20">
+        <v>1.01</v>
+      </c>
+      <c r="BG20">
+        <v>1.01</v>
+      </c>
+      <c r="BH20">
+        <v>1000</v>
+      </c>
+      <c r="BI20">
+        <v>1.01</v>
+      </c>
+      <c r="BJ20">
+        <v>1000</v>
+      </c>
+      <c r="BK20">
+        <v>1.01</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>1.01</v>
+      </c>
+      <c r="BN20">
+        <v>1000</v>
+      </c>
+      <c r="BO20">
+        <v>1.01</v>
+      </c>
+      <c r="BP20">
+        <v>1000</v>
+      </c>
+      <c r="BQ20">
+        <v>1.01</v>
+      </c>
+      <c r="BR20">
+        <v>1000</v>
+      </c>
+      <c r="BS20">
+        <v>1.01</v>
+      </c>
+      <c r="BT20">
+        <v>1000</v>
+      </c>
+      <c r="BU20">
+        <v>1.01</v>
+      </c>
+      <c r="BV20">
+        <v>1000</v>
+      </c>
+      <c r="BW20">
+        <v>1.01</v>
+      </c>
+      <c r="BX20">
+        <v>1000</v>
+      </c>
+      <c r="BY20">
+        <v>1.01</v>
+      </c>
+      <c r="BZ20">
+        <v>1000</v>
+      </c>
+      <c r="CA20">
+        <v>1.01</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="21" spans="1:80">
+      <c r="A21" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" t="s">
+        <v>99</v>
+      </c>
+      <c r="D21" t="s">
+        <v>119</v>
+      </c>
+      <c r="E21" t="s">
+        <v>142</v>
+      </c>
+      <c r="F21">
+        <v>2.02</v>
+      </c>
+      <c r="G21">
+        <v>2.08</v>
+      </c>
+      <c r="H21">
+        <v>3.8</v>
+      </c>
+      <c r="I21">
+        <v>3.9</v>
+      </c>
+      <c r="J21">
+        <v>3.8</v>
+      </c>
+      <c r="K21">
+        <v>4</v>
+      </c>
+      <c r="L21">
+        <v>1.35</v>
+      </c>
+      <c r="M21">
+        <v>1.05</v>
+      </c>
+      <c r="N21">
+        <v>4.4</v>
+      </c>
+      <c r="O21">
+        <v>1.27</v>
+      </c>
+      <c r="P21">
+        <v>2.18</v>
+      </c>
+      <c r="Q21">
+        <v>1.81</v>
+      </c>
+      <c r="R21">
+        <v>1.46</v>
+      </c>
+      <c r="S21">
+        <v>3.05</v>
+      </c>
+      <c r="T21">
+        <v>1.7</v>
+      </c>
+      <c r="U21">
+        <v>2.2</v>
+      </c>
+      <c r="V21">
+        <v>1.34</v>
+      </c>
+      <c r="W21">
+        <v>1.92</v>
+      </c>
+      <c r="X21">
+        <v>22</v>
+      </c>
+      <c r="Y21">
+        <v>19.5</v>
+      </c>
+      <c r="Z21">
+        <v>36</v>
+      </c>
+      <c r="AA21">
+        <v>90</v>
+      </c>
+      <c r="AB21">
+        <v>13</v>
+      </c>
+      <c r="AC21">
+        <v>11</v>
+      </c>
+      <c r="AD21">
+        <v>19.5</v>
+      </c>
+      <c r="AE21">
+        <v>55</v>
+      </c>
+      <c r="AF21">
+        <v>16.5</v>
+      </c>
+      <c r="AG21">
+        <v>13.5</v>
+      </c>
+      <c r="AH21">
+        <v>21</v>
+      </c>
+      <c r="AI21">
+        <v>60</v>
+      </c>
+      <c r="AJ21">
+        <v>30</v>
+      </c>
+      <c r="AK21">
+        <v>25</v>
+      </c>
+      <c r="AL21">
+        <v>40</v>
+      </c>
+      <c r="AM21">
+        <v>95</v>
+      </c>
+      <c r="AN21">
+        <v>15</v>
+      </c>
+      <c r="AO21">
+        <v>46</v>
+      </c>
+      <c r="AP21">
+        <v>15.5</v>
+      </c>
+      <c r="AQ21">
+        <v>14</v>
+      </c>
+      <c r="AR21">
+        <v>3.85</v>
+      </c>
+      <c r="AS21">
+        <v>4.1</v>
+      </c>
+      <c r="AT21">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU21">
+        <v>7.8</v>
+      </c>
+      <c r="AV21">
+        <v>13.5</v>
+      </c>
+      <c r="AW21">
+        <v>4</v>
+      </c>
+      <c r="AX21">
+        <v>11.5</v>
+      </c>
+      <c r="AY21">
+        <v>9.4</v>
+      </c>
+      <c r="AZ21">
+        <v>14</v>
+      </c>
+      <c r="BA21">
+        <v>4</v>
+      </c>
+      <c r="BB21">
+        <v>20</v>
+      </c>
+      <c r="BC21">
+        <v>17</v>
+      </c>
+      <c r="BD21">
+        <v>3.9</v>
+      </c>
+      <c r="BE21">
+        <v>4.1</v>
+      </c>
+      <c r="BF21">
+        <v>10.5</v>
+      </c>
+      <c r="BG21">
+        <v>3.95</v>
+      </c>
+      <c r="BH21">
+        <v>1000</v>
+      </c>
+      <c r="BI21">
+        <v>1.01</v>
+      </c>
+      <c r="BJ21">
+        <v>13</v>
+      </c>
+      <c r="BK21">
+        <v>5.8</v>
+      </c>
+      <c r="BL21">
+        <v>1000</v>
+      </c>
+      <c r="BM21">
+        <v>21</v>
+      </c>
+      <c r="BN21">
+        <v>7</v>
+      </c>
+      <c r="BO21">
+        <v>3.35</v>
+      </c>
+      <c r="BP21">
+        <v>20</v>
+      </c>
+      <c r="BQ21">
+        <v>8.4</v>
+      </c>
+      <c r="BR21">
+        <v>38</v>
+      </c>
+      <c r="BS21">
+        <v>15</v>
+      </c>
+      <c r="BT21">
+        <v>10.5</v>
+      </c>
+      <c r="BU21">
+        <v>4.7</v>
+      </c>
+      <c r="BV21">
+        <v>44</v>
+      </c>
+      <c r="BW21">
+        <v>17.5</v>
+      </c>
+      <c r="BX21">
+        <v>50</v>
+      </c>
+      <c r="BY21">
+        <v>21</v>
+      </c>
+      <c r="BZ21">
+        <v>29</v>
+      </c>
+      <c r="CA21">
+        <v>12</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="22" spans="1:80">
+      <c r="A22" t="s">
+        <v>87</v>
+      </c>
+      <c r="B22" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" t="s">
+        <v>99</v>
+      </c>
+      <c r="D22" t="s">
+        <v>120</v>
+      </c>
+      <c r="E22" t="s">
+        <v>143</v>
+      </c>
+      <c r="F22">
+        <v>1.97</v>
+      </c>
+      <c r="G22">
+        <v>2</v>
+      </c>
+      <c r="H22">
+        <v>3.95</v>
+      </c>
+      <c r="I22">
+        <v>4.2</v>
+      </c>
+      <c r="J22">
+        <v>4</v>
+      </c>
+      <c r="K22">
+        <v>4.1</v>
+      </c>
+      <c r="L22">
+        <v>1.36</v>
+      </c>
+      <c r="M22">
+        <v>1.05</v>
+      </c>
+      <c r="N22">
+        <v>4.3</v>
+      </c>
+      <c r="O22">
+        <v>1.27</v>
+      </c>
+      <c r="P22">
+        <v>2.14</v>
+      </c>
+      <c r="Q22">
+        <v>1.83</v>
+      </c>
+      <c r="R22">
+        <v>1.44</v>
+      </c>
+      <c r="S22">
+        <v>3.15</v>
+      </c>
+      <c r="T22">
+        <v>1.71</v>
+      </c>
+      <c r="U22">
+        <v>2.14</v>
+      </c>
+      <c r="V22">
+        <v>1.32</v>
+      </c>
+      <c r="W22">
+        <v>2</v>
+      </c>
+      <c r="X22">
+        <v>1000</v>
+      </c>
+      <c r="Y22">
+        <v>1000</v>
+      </c>
+      <c r="Z22">
+        <v>1000</v>
+      </c>
+      <c r="AA22">
+        <v>1000</v>
+      </c>
+      <c r="AB22">
+        <v>1000</v>
+      </c>
+      <c r="AC22">
+        <v>9.4</v>
+      </c>
+      <c r="AD22">
+        <v>1000</v>
+      </c>
+      <c r="AE22">
+        <v>1000</v>
+      </c>
+      <c r="AF22">
+        <v>1000</v>
+      </c>
+      <c r="AG22">
+        <v>1000</v>
+      </c>
+      <c r="AH22">
+        <v>1000</v>
+      </c>
+      <c r="AI22">
+        <v>1000</v>
+      </c>
+      <c r="AJ22">
+        <v>1000</v>
+      </c>
+      <c r="AK22">
+        <v>1000</v>
+      </c>
+      <c r="AL22">
+        <v>1000</v>
+      </c>
+      <c r="AM22">
+        <v>1000</v>
+      </c>
+      <c r="AN22">
+        <v>1000</v>
+      </c>
+      <c r="AO22">
+        <v>1000</v>
+      </c>
+      <c r="AP22">
+        <v>1.11</v>
+      </c>
+      <c r="AQ22">
+        <v>1.11</v>
+      </c>
+      <c r="AR22">
+        <v>1.11</v>
+      </c>
+      <c r="AS22">
+        <v>1.11</v>
+      </c>
+      <c r="AT22">
+        <v>1.11</v>
+      </c>
+      <c r="AU22">
+        <v>8</v>
+      </c>
+      <c r="AV22">
+        <v>1.11</v>
+      </c>
+      <c r="AW22">
+        <v>1.11</v>
+      </c>
+      <c r="AX22">
+        <v>1.11</v>
+      </c>
+      <c r="AY22">
+        <v>1.11</v>
+      </c>
+      <c r="AZ22">
+        <v>1.11</v>
+      </c>
+      <c r="BA22">
+        <v>1.11</v>
+      </c>
+      <c r="BB22">
+        <v>1.11</v>
+      </c>
+      <c r="BC22">
+        <v>1.11</v>
+      </c>
+      <c r="BD22">
+        <v>1.11</v>
+      </c>
+      <c r="BE22">
+        <v>1.11</v>
+      </c>
+      <c r="BF22">
+        <v>1.11</v>
+      </c>
+      <c r="BG22">
+        <v>1.11</v>
+      </c>
+      <c r="BH22">
+        <v>1000</v>
+      </c>
+      <c r="BI22">
+        <v>1.01</v>
+      </c>
+      <c r="BJ22">
+        <v>13.5</v>
+      </c>
+      <c r="BK22">
+        <v>5.8</v>
+      </c>
+      <c r="BL22">
+        <v>1000</v>
+      </c>
+      <c r="BM22">
+        <v>21</v>
+      </c>
+      <c r="BN22">
+        <v>6.8</v>
+      </c>
+      <c r="BO22">
+        <v>3.25</v>
+      </c>
+      <c r="BP22">
+        <v>20</v>
+      </c>
+      <c r="BQ22">
+        <v>8.4</v>
+      </c>
+      <c r="BR22">
+        <v>38</v>
+      </c>
+      <c r="BS22">
+        <v>15.5</v>
+      </c>
+      <c r="BT22">
+        <v>10.5</v>
+      </c>
+      <c r="BU22">
+        <v>4.8</v>
+      </c>
+      <c r="BV22">
+        <v>46</v>
+      </c>
+      <c r="BW22">
+        <v>18.5</v>
+      </c>
+      <c r="BX22">
+        <v>1000</v>
+      </c>
+      <c r="BY22">
+        <v>21</v>
+      </c>
+      <c r="BZ22">
+        <v>30</v>
+      </c>
+      <c r="CA22">
+        <v>12.5</v>
+      </c>
+      <c r="CB22" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80">
+      <c r="A23" t="s">
+        <v>87</v>
+      </c>
+      <c r="B23" t="s">
+        <v>88</v>
+      </c>
+      <c r="C23" t="s">
+        <v>99</v>
+      </c>
+      <c r="D23" t="s">
+        <v>121</v>
+      </c>
+      <c r="E23" t="s">
+        <v>144</v>
+      </c>
+      <c r="F23">
+        <v>1.81</v>
+      </c>
+      <c r="G23">
+        <v>1.87</v>
+      </c>
+      <c r="H23">
+        <v>4.3</v>
+      </c>
+      <c r="I23">
+        <v>4.5</v>
+      </c>
+      <c r="J23">
+        <v>4.3</v>
+      </c>
+      <c r="K23">
+        <v>4.6</v>
+      </c>
+      <c r="L23">
+        <v>1.26</v>
+      </c>
+      <c r="M23">
+        <v>1.03</v>
+      </c>
+      <c r="N23">
+        <v>6.2</v>
+      </c>
+      <c r="O23">
+        <v>1.17</v>
+      </c>
+      <c r="P23">
+        <v>2.8</v>
+      </c>
+      <c r="Q23">
+        <v>1.52</v>
+      </c>
+      <c r="R23">
+        <v>1.72</v>
+      </c>
+      <c r="S23">
+        <v>2.3</v>
+      </c>
+      <c r="T23">
+        <v>1.55</v>
+      </c>
+      <c r="U23">
+        <v>2.6</v>
+      </c>
+      <c r="V23">
+        <v>1.29</v>
+      </c>
+      <c r="W23">
+        <v>2.14</v>
+      </c>
+      <c r="X23">
+        <v>32</v>
+      </c>
+      <c r="Y23">
+        <v>28</v>
+      </c>
+      <c r="Z23">
+        <v>44</v>
+      </c>
+      <c r="AA23">
+        <v>95</v>
+      </c>
+      <c r="AB23">
+        <v>16.5</v>
+      </c>
+      <c r="AC23">
+        <v>12.5</v>
+      </c>
+      <c r="AD23">
+        <v>21</v>
+      </c>
+      <c r="AE23">
+        <v>48</v>
+      </c>
+      <c r="AF23">
+        <v>17.5</v>
+      </c>
+      <c r="AG23">
+        <v>12.5</v>
+      </c>
+      <c r="AH23">
+        <v>18</v>
+      </c>
+      <c r="AI23">
+        <v>48</v>
+      </c>
+      <c r="AJ23">
+        <v>24</v>
+      </c>
+      <c r="AK23">
+        <v>19.5</v>
+      </c>
+      <c r="AL23">
+        <v>29</v>
+      </c>
+      <c r="AM23">
+        <v>65</v>
+      </c>
+      <c r="AN23">
+        <v>7.4</v>
+      </c>
+      <c r="AO23">
+        <v>36</v>
+      </c>
+      <c r="AP23">
+        <v>5</v>
+      </c>
+      <c r="AQ23">
+        <v>21</v>
+      </c>
+      <c r="AR23">
+        <v>5.2</v>
+      </c>
+      <c r="AS23">
+        <v>5.6</v>
+      </c>
+      <c r="AT23">
+        <v>12.5</v>
+      </c>
+      <c r="AU23">
+        <v>9.6</v>
+      </c>
+      <c r="AV23">
+        <v>15.5</v>
+      </c>
+      <c r="AW23">
+        <v>5.3</v>
+      </c>
+      <c r="AX23">
+        <v>13</v>
+      </c>
+      <c r="AY23">
+        <v>9.6</v>
+      </c>
+      <c r="AZ23">
+        <v>13.5</v>
+      </c>
+      <c r="BA23">
+        <v>34</v>
+      </c>
+      <c r="BB23">
+        <v>18</v>
+      </c>
+      <c r="BC23">
+        <v>14.5</v>
+      </c>
+      <c r="BD23">
+        <v>21</v>
+      </c>
+      <c r="BE23">
+        <v>5.4</v>
+      </c>
+      <c r="BF23">
+        <v>6.4</v>
+      </c>
+      <c r="BG23">
+        <v>5</v>
+      </c>
+      <c r="BH23">
+        <v>1000</v>
+      </c>
+      <c r="BI23">
+        <v>1.01</v>
+      </c>
+      <c r="BJ23">
+        <v>12</v>
+      </c>
+      <c r="BK23">
+        <v>5.8</v>
+      </c>
+      <c r="BL23">
+        <v>1000</v>
+      </c>
+      <c r="BM23">
+        <v>21</v>
+      </c>
+      <c r="BN23">
+        <v>6.6</v>
+      </c>
+      <c r="BO23">
+        <v>3.45</v>
+      </c>
+      <c r="BP23">
+        <v>15.5</v>
+      </c>
+      <c r="BQ23">
+        <v>7.2</v>
+      </c>
+      <c r="BR23">
+        <v>28</v>
+      </c>
+      <c r="BS23">
+        <v>12.5</v>
+      </c>
+      <c r="BT23">
+        <v>11</v>
+      </c>
+      <c r="BU23">
+        <v>5.4</v>
+      </c>
+      <c r="BV23">
+        <v>40</v>
+      </c>
+      <c r="BW23">
+        <v>17.5</v>
+      </c>
+      <c r="BX23">
+        <v>46</v>
+      </c>
+      <c r="BY23">
+        <v>19</v>
+      </c>
+      <c r="BZ23">
+        <v>18</v>
+      </c>
+      <c r="CA23">
+        <v>8.4</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="24" spans="1:80">
+      <c r="A24" t="s">
+        <v>87</v>
+      </c>
+      <c r="B24" t="s">
+        <v>88</v>
+      </c>
+      <c r="C24" t="s">
+        <v>99</v>
+      </c>
+      <c r="D24" t="s">
+        <v>122</v>
+      </c>
+      <c r="E24" t="s">
+        <v>145</v>
+      </c>
+      <c r="F24">
+        <v>2.16</v>
+      </c>
+      <c r="G24">
+        <v>2.2</v>
+      </c>
+      <c r="H24">
+        <v>3.15</v>
+      </c>
+      <c r="I24">
+        <v>3.25</v>
+      </c>
+      <c r="J24">
+        <v>4.4</v>
+      </c>
+      <c r="K24">
+        <v>4.5</v>
+      </c>
+      <c r="L24">
+        <v>1.21</v>
+      </c>
+      <c r="M24">
+        <v>1.02</v>
+      </c>
+      <c r="N24">
+        <v>8.4</v>
+      </c>
+      <c r="O24">
+        <v>1.12</v>
+      </c>
+      <c r="P24">
+        <v>3.4</v>
+      </c>
+      <c r="Q24">
+        <v>1.38</v>
+      </c>
+      <c r="R24">
+        <v>1.99</v>
+      </c>
+      <c r="S24">
+        <v>1.95</v>
+      </c>
+      <c r="T24">
+        <v>1.39</v>
+      </c>
+      <c r="U24">
+        <v>3.25</v>
+      </c>
+      <c r="V24">
+        <v>1.44</v>
+      </c>
+      <c r="W24">
+        <v>1.83</v>
+      </c>
+      <c r="X24">
+        <v>42</v>
+      </c>
+      <c r="Y24">
+        <v>44</v>
+      </c>
+      <c r="Z24">
+        <v>34</v>
+      </c>
+      <c r="AA24">
+        <v>60</v>
+      </c>
+      <c r="AB24">
+        <v>26</v>
+      </c>
+      <c r="AC24">
+        <v>12</v>
+      </c>
+      <c r="AD24">
+        <v>15.5</v>
+      </c>
+      <c r="AE24">
+        <v>29</v>
+      </c>
+      <c r="AF24">
+        <v>22</v>
+      </c>
+      <c r="AG24">
+        <v>12.5</v>
+      </c>
+      <c r="AH24">
+        <v>14</v>
+      </c>
+      <c r="AI24">
+        <v>28</v>
+      </c>
+      <c r="AJ24">
+        <v>32</v>
+      </c>
+      <c r="AK24">
+        <v>19</v>
+      </c>
+      <c r="AL24">
+        <v>22</v>
+      </c>
+      <c r="AM24">
+        <v>42</v>
+      </c>
+      <c r="AN24">
+        <v>7.6</v>
+      </c>
+      <c r="AO24">
+        <v>14</v>
+      </c>
+      <c r="AP24">
+        <v>34</v>
+      </c>
+      <c r="AQ24">
+        <v>24</v>
+      </c>
+      <c r="AR24">
+        <v>29</v>
+      </c>
+      <c r="AS24">
+        <v>46</v>
+      </c>
+      <c r="AT24">
+        <v>19.5</v>
+      </c>
+      <c r="AU24">
+        <v>10.5</v>
+      </c>
+      <c r="AV24">
+        <v>13.5</v>
+      </c>
+      <c r="AW24">
+        <v>25</v>
+      </c>
+      <c r="AX24">
+        <v>19</v>
+      </c>
+      <c r="AY24">
+        <v>11</v>
+      </c>
+      <c r="AZ24">
+        <v>12</v>
+      </c>
+      <c r="BA24">
+        <v>24</v>
+      </c>
+      <c r="BB24">
+        <v>27</v>
+      </c>
+      <c r="BC24">
+        <v>16.5</v>
+      </c>
+      <c r="BD24">
+        <v>19</v>
+      </c>
+      <c r="BE24">
+        <v>34</v>
+      </c>
+      <c r="BF24">
+        <v>6.8</v>
+      </c>
+      <c r="BG24">
+        <v>12</v>
+      </c>
+      <c r="BH24">
+        <v>1000</v>
+      </c>
+      <c r="BI24">
+        <v>1.01</v>
+      </c>
+      <c r="BJ24">
+        <v>11.5</v>
+      </c>
+      <c r="BK24">
+        <v>5.1</v>
+      </c>
+      <c r="BL24">
+        <v>1000</v>
+      </c>
+      <c r="BM24">
+        <v>21</v>
+      </c>
+      <c r="BN24">
+        <v>8.6</v>
+      </c>
+      <c r="BO24">
+        <v>3.95</v>
+      </c>
+      <c r="BP24">
+        <v>19</v>
+      </c>
+      <c r="BQ24">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR24">
+        <v>26</v>
+      </c>
+      <c r="BS24">
+        <v>11</v>
+      </c>
+      <c r="BT24">
+        <v>10.5</v>
+      </c>
+      <c r="BU24">
+        <v>4.8</v>
+      </c>
+      <c r="BV24">
+        <v>29</v>
+      </c>
+      <c r="BW24">
+        <v>12</v>
+      </c>
+      <c r="BX24">
+        <v>32</v>
+      </c>
+      <c r="BY24">
+        <v>13.5</v>
+      </c>
+      <c r="BZ24">
+        <v>15</v>
+      </c>
+      <c r="CA24">
+        <v>6.8</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
@@ -454,7 +454,7 @@
     <t>Chicago Fire</t>
   </si>
   <si>
-    <t>2026-07-21 00:46:03</t>
+    <t>2026-07-21 02:53:07</t>
   </si>
 </sst>
 </file>
@@ -1048,7 +1048,7 @@
         <v>123</v>
       </c>
       <c r="F2">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="G2">
         <v>2.02</v>
@@ -1060,10 +1060,10 @@
         <v>4.9</v>
       </c>
       <c r="J2">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K2">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L2">
         <v>1.46</v>
@@ -1072,34 +1072,34 @@
         <v>1.09</v>
       </c>
       <c r="N2">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="O2">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P2">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Q2">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R2">
         <v>1.29</v>
       </c>
       <c r="S2">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T2">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="U2">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V2">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W2">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X2">
         <v>12</v>
@@ -1111,7 +1111,7 @@
         <v>34</v>
       </c>
       <c r="AA2">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB2">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>18.5</v>
       </c>
       <c r="AE2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF2">
         <v>11.5</v>
@@ -1135,10 +1135,10 @@
         <v>21</v>
       </c>
       <c r="AI2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK2">
         <v>23</v>
@@ -1147,13 +1147,13 @@
         <v>44</v>
       </c>
       <c r="AM2">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN2">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AP2">
         <v>10.5</v>
@@ -1162,10 +1162,10 @@
         <v>13</v>
       </c>
       <c r="AR2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AS2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT2">
         <v>7.2</v>
@@ -1201,7 +1201,7 @@
         <v>36</v>
       </c>
       <c r="BE2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BF2">
         <v>14.5</v>
@@ -1210,10 +1210,10 @@
         <v>38</v>
       </c>
       <c r="BH2">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BI2">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="BJ2">
         <v>10.5</v>
@@ -1246,7 +1246,7 @@
         <v>10.5</v>
       </c>
       <c r="BT2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU2">
         <v>6.2</v>
@@ -1255,7 +1255,7 @@
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BX2">
         <v>1000</v>
@@ -1264,7 +1264,7 @@
         <v>12</v>
       </c>
       <c r="BZ2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="CA2">
         <v>10</v>
@@ -1290,142 +1290,142 @@
         <v>124</v>
       </c>
       <c r="F3">
+        <v>1.38</v>
+      </c>
+      <c r="G3">
+        <v>1.4</v>
+      </c>
+      <c r="H3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J3">
+        <v>5.9</v>
+      </c>
+      <c r="K3">
+        <v>6.4</v>
+      </c>
+      <c r="L3">
         <v>1.34</v>
       </c>
-      <c r="G3">
-        <v>1.36</v>
-      </c>
-      <c r="H3">
-        <v>9</v>
-      </c>
-      <c r="I3">
-        <v>10.5</v>
-      </c>
-      <c r="J3">
-        <v>6.2</v>
-      </c>
-      <c r="K3">
-        <v>6.8</v>
-      </c>
-      <c r="L3">
-        <v>1.27</v>
-      </c>
       <c r="M3">
         <v>1.04</v>
       </c>
       <c r="N3">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O3">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P3">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="Q3">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="R3">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="S3">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="T3">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="U3">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="V3">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="W3">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="X3">
         <v>25</v>
       </c>
       <c r="Y3">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Z3">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AA3">
-        <v>430</v>
+        <v>340</v>
       </c>
       <c r="AB3">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC3">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AD3">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AE3">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="AF3">
         <v>8.4</v>
       </c>
       <c r="AG3">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH3">
         <v>34</v>
       </c>
       <c r="AI3">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AJ3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK3">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL3">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM3">
+        <v>150</v>
+      </c>
+      <c r="AN3">
+        <v>5.9</v>
+      </c>
+      <c r="AO3">
         <v>170</v>
-      </c>
-      <c r="AN3">
-        <v>5.1</v>
-      </c>
-      <c r="AO3">
-        <v>200</v>
       </c>
       <c r="AP3">
         <v>21</v>
       </c>
       <c r="AQ3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AR3">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AS3">
         <v>55</v>
       </c>
       <c r="AT3">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU3">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AV3">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AW3">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AX3">
         <v>7.6</v>
       </c>
       <c r="AY3">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ3">
         <v>21</v>
@@ -1434,7 +1434,7 @@
         <v>40</v>
       </c>
       <c r="BB3">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BC3">
         <v>13</v>
@@ -1446,22 +1446,22 @@
         <v>46</v>
       </c>
       <c r="BF3">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BG3">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BH3">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="BI3">
         <v>3.35</v>
       </c>
       <c r="BJ3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK3">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BL3">
         <v>1000</v>
@@ -1470,28 +1470,28 @@
         <v>14.5</v>
       </c>
       <c r="BN3">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="BO3">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="BP3">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BQ3">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BR3">
         <v>24</v>
       </c>
       <c r="BS3">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BT3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BU3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BV3">
         <v>1000</v>
@@ -1503,13 +1503,13 @@
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BZ3">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="CA3">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="CB3" t="s">
         <v>146</v>
@@ -1532,70 +1532,70 @@
         <v>125</v>
       </c>
       <c r="F4">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="G4">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="H4">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="I4">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J4">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K4">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L4">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="M4">
         <v>1.04</v>
       </c>
       <c r="N4">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="O4">
         <v>1.22</v>
       </c>
       <c r="P4">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q4">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="R4">
         <v>1.56</v>
       </c>
       <c r="S4">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="T4">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U4">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V4">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W4">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="X4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z4">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA4">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AB4">
         <v>11.5</v>
@@ -1604,7 +1604,7 @@
         <v>10.5</v>
       </c>
       <c r="AD4">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE4">
         <v>65</v>
@@ -1613,13 +1613,13 @@
         <v>11.5</v>
       </c>
       <c r="AG4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH4">
         <v>18.5</v>
       </c>
       <c r="AI4">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ4">
         <v>17.5</v>
@@ -1634,10 +1634,10 @@
         <v>85</v>
       </c>
       <c r="AN4">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AO4">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AP4">
         <v>18</v>
@@ -1649,7 +1649,7 @@
         <v>38</v>
       </c>
       <c r="AS4">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT4">
         <v>10</v>
@@ -1667,7 +1667,7 @@
         <v>10</v>
       </c>
       <c r="AY4">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ4">
         <v>16</v>
@@ -1682,13 +1682,13 @@
         <v>14</v>
       </c>
       <c r="BD4">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BE4">
         <v>60</v>
       </c>
       <c r="BF4">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG4">
         <v>44</v>
@@ -1697,7 +1697,7 @@
         <v>4.3</v>
       </c>
       <c r="BI4">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BJ4">
         <v>10</v>
@@ -1709,46 +1709,46 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BN4">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO4">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BP4">
         <v>11</v>
       </c>
       <c r="BQ4">
-        <v>8</v>
+        <v>5.2</v>
       </c>
       <c r="BR4">
         <v>23</v>
       </c>
       <c r="BS4">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BT4">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BU4">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BV4">
         <v>44</v>
       </c>
       <c r="BW4">
+        <v>8</v>
+      </c>
+      <c r="BX4">
+        <v>46</v>
+      </c>
+      <c r="BY4">
         <v>8.199999999999999</v>
       </c>
-      <c r="BX4">
-        <v>48</v>
-      </c>
-      <c r="BY4">
-        <v>8.4</v>
-      </c>
       <c r="BZ4">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="CA4">
         <v>6.2</v>
@@ -1804,7 +1804,7 @@
         <v>1.48</v>
       </c>
       <c r="P5">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q5">
         <v>2.46</v>
@@ -1813,7 +1813,7 @@
         <v>1.23</v>
       </c>
       <c r="S5">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="T5">
         <v>2.02</v>
@@ -1858,7 +1858,7 @@
         <v>15.5</v>
       </c>
       <c r="AH5">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI5">
         <v>70</v>
@@ -1879,7 +1879,7 @@
         <v>60</v>
       </c>
       <c r="AO5">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AP5">
         <v>9</v>
@@ -1891,7 +1891,7 @@
         <v>15.5</v>
       </c>
       <c r="AS5">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT5">
         <v>8.4</v>
@@ -1903,7 +1903,7 @@
         <v>11.5</v>
       </c>
       <c r="AW5">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX5">
         <v>16.5</v>
@@ -1915,25 +1915,25 @@
         <v>18</v>
       </c>
       <c r="BA5">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB5">
+        <v>9.4</v>
+      </c>
+      <c r="BC5">
         <v>9</v>
       </c>
-      <c r="BC5">
-        <v>8.6</v>
-      </c>
       <c r="BD5">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF5">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BG5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH5">
         <v>3.35</v>
@@ -2022,16 +2022,16 @@
         <v>5.1</v>
       </c>
       <c r="H6">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="I6">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="J6">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K6">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L6">
         <v>1.39</v>
@@ -2043,34 +2043,34 @@
         <v>3.4</v>
       </c>
       <c r="O6">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P6">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q6">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R6">
         <v>1.3</v>
       </c>
       <c r="S6">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T6">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="U6">
         <v>1.93</v>
       </c>
       <c r="V6">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="W6">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X6">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Y6">
         <v>8</v>
@@ -2121,7 +2121,7 @@
         <v>1000</v>
       </c>
       <c r="AO6">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AP6">
         <v>11</v>
@@ -2232,7 +2232,7 @@
         <v>10</v>
       </c>
       <c r="BZ6">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
         <v>10</v>
@@ -2258,19 +2258,19 @@
         <v>128</v>
       </c>
       <c r="F7">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="G7">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="H7">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I7">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J7">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K7">
         <v>3.7</v>
@@ -2282,13 +2282,13 @@
         <v>1.1</v>
       </c>
       <c r="N7">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="O7">
         <v>1.45</v>
       </c>
       <c r="P7">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q7">
         <v>2.3</v>
@@ -2300,22 +2300,22 @@
         <v>4.6</v>
       </c>
       <c r="T7">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U7">
         <v>1.82</v>
       </c>
       <c r="V7">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W7">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="X7">
         <v>12.5</v>
       </c>
       <c r="Y7">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="Z7">
         <v>42</v>
@@ -2327,13 +2327,13 @@
         <v>7.2</v>
       </c>
       <c r="AC7">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD7">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE7">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AF7">
         <v>11</v>
@@ -2351,7 +2351,7 @@
         <v>26</v>
       </c>
       <c r="AK7">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL7">
         <v>55</v>
@@ -2363,19 +2363,19 @@
         <v>21</v>
       </c>
       <c r="AO7">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AP7">
         <v>9.6</v>
       </c>
       <c r="AQ7">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR7">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AS7">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT7">
         <v>6.4</v>
@@ -2387,7 +2387,7 @@
         <v>18</v>
       </c>
       <c r="AW7">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX7">
         <v>9.199999999999999</v>
@@ -2399,25 +2399,25 @@
         <v>20</v>
       </c>
       <c r="BA7">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB7">
-        <v>17.5</v>
+        <v>7.2</v>
       </c>
       <c r="BC7">
         <v>18</v>
       </c>
       <c r="BD7">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BE7">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF7">
         <v>16</v>
       </c>
       <c r="BG7">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH7">
         <v>2.98</v>
@@ -2429,34 +2429,34 @@
         <v>11.5</v>
       </c>
       <c r="BK7">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN7">
         <v>4.4</v>
       </c>
       <c r="BO7">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BP7">
         <v>14.5</v>
       </c>
       <c r="BQ7">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT7">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU7">
         <v>5.4</v>
@@ -2465,19 +2465,19 @@
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB7" t="s">
         <v>146</v>
@@ -2500,55 +2500,55 @@
         <v>129</v>
       </c>
       <c r="F8">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G8">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="H8">
+        <v>2.18</v>
+      </c>
+      <c r="I8">
         <v>2.22</v>
       </c>
-      <c r="I8">
-        <v>2.28</v>
-      </c>
       <c r="J8">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K8">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L8">
         <v>1.01</v>
       </c>
       <c r="M8">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N8">
         <v>5.7</v>
       </c>
       <c r="O8">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P8">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="Q8">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R8">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="S8">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T8">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U8">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="V8">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="W8">
         <v>1.34</v>
@@ -2560,13 +2560,13 @@
         <v>15</v>
       </c>
       <c r="Z8">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AA8">
         <v>28</v>
       </c>
       <c r="AB8">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AC8">
         <v>9.4</v>
@@ -2578,7 +2578,7 @@
         <v>20</v>
       </c>
       <c r="AF8">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AG8">
         <v>14.5</v>
@@ -2593,28 +2593,28 @@
         <v>55</v>
       </c>
       <c r="AK8">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL8">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM8">
         <v>55</v>
       </c>
       <c r="AN8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AP8">
         <v>21</v>
       </c>
       <c r="AQ8">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR8">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AS8">
         <v>26</v>
@@ -2626,10 +2626,10 @@
         <v>8.6</v>
       </c>
       <c r="AV8">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW8">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AX8">
         <v>24</v>
@@ -2653,7 +2653,7 @@
         <v>30</v>
       </c>
       <c r="BE8">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BF8">
         <v>18.5</v>
@@ -2745,13 +2745,13 @@
         <v>1.12</v>
       </c>
       <c r="G9">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="H9">
         <v>16</v>
       </c>
       <c r="I9">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J9">
         <v>11</v>
@@ -2784,10 +2784,10 @@
         <v>1.66</v>
       </c>
       <c r="T9">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U9">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="V9">
         <v>1.03</v>
@@ -2826,13 +2826,13 @@
         <v>15.5</v>
       </c>
       <c r="AH9">
-        <v>70</v>
+        <v>950</v>
       </c>
       <c r="AI9">
         <v>250</v>
       </c>
       <c r="AJ9">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK9">
         <v>15</v>
@@ -2844,64 +2844,64 @@
         <v>220</v>
       </c>
       <c r="AN9">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AO9">
         <v>400</v>
       </c>
       <c r="AP9">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AQ9">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AR9">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS9">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AT9">
         <v>12.5</v>
       </c>
       <c r="AU9">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV9">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW9">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AX9">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AY9">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ9">
         <v>28</v>
       </c>
       <c r="BA9">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BB9">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BC9">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BD9">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE9">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BF9">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="BG9">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -2987,19 +2987,19 @@
         <v>2.14</v>
       </c>
       <c r="G10">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H10">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="I10">
         <v>4.5</v>
       </c>
       <c r="J10">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K10">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3008,148 +3008,148 @@
         <v>1.12</v>
       </c>
       <c r="N10">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="O10">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P10">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q10">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="R10">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S10">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="T10">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U10">
         <v>1.77</v>
       </c>
       <c r="V10">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W10">
         <v>1.72</v>
       </c>
       <c r="X10">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y10">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z10">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AA10">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB10">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AC10">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="AD10">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="AE10">
         <v>95</v>
       </c>
       <c r="AF10">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG10">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AH10">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="AI10">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ10">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AK10">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AL10">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AM10">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN10">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AO10">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP10">
-        <v>2.38</v>
+        <v>7.8</v>
       </c>
       <c r="AQ10">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AR10">
-        <v>18.5</v>
+        <v>6.4</v>
       </c>
       <c r="AS10">
-        <v>2.94</v>
+        <v>7.6</v>
       </c>
       <c r="AT10">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AU10">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AV10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AW10">
-        <v>2.86</v>
+        <v>7.2</v>
       </c>
       <c r="AX10">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AY10">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ10">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BA10">
-        <v>2.94</v>
+        <v>7.6</v>
       </c>
       <c r="BB10">
-        <v>23</v>
+        <v>6.6</v>
       </c>
       <c r="BC10">
-        <v>22</v>
+        <v>6.6</v>
       </c>
       <c r="BD10">
-        <v>2.84</v>
+        <v>7.2</v>
       </c>
       <c r="BE10">
-        <v>2.94</v>
+        <v>7.8</v>
       </c>
       <c r="BF10">
-        <v>19</v>
+        <v>6.4</v>
       </c>
       <c r="BG10">
-        <v>2.94</v>
+        <v>7.6</v>
       </c>
       <c r="BH10">
         <v>3.2</v>
       </c>
       <c r="BI10">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="BJ10">
         <v>16</v>
@@ -3232,13 +3232,13 @@
         <v>1000</v>
       </c>
       <c r="H11">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I11">
         <v>1000</v>
       </c>
       <c r="J11">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="K11">
         <v>100</v>
@@ -3474,7 +3474,7 @@
         <v>1000</v>
       </c>
       <c r="H12">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="I12">
         <v>1000</v>
@@ -3519,7 +3519,7 @@
         <v>1.02</v>
       </c>
       <c r="W12">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3716,13 +3716,13 @@
         <v>1000</v>
       </c>
       <c r="H13">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="I13">
         <v>1000</v>
       </c>
       <c r="J13">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="K13">
         <v>100</v>
@@ -3955,13 +3955,13 @@
         <v>1.19</v>
       </c>
       <c r="G14">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="H14">
         <v>18.5</v>
       </c>
       <c r="I14">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J14">
         <v>6.8</v>
@@ -3976,202 +3976,202 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O14">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P14">
         <v>2.38</v>
       </c>
       <c r="Q14">
+        <v>1.58</v>
+      </c>
+      <c r="R14">
+        <v>1.55</v>
+      </c>
+      <c r="S14">
+        <v>2.42</v>
+      </c>
+      <c r="T14">
+        <v>2.38</v>
+      </c>
+      <c r="U14">
         <v>1.57</v>
       </c>
-      <c r="R14">
-        <v>1.51</v>
-      </c>
-      <c r="S14">
-        <v>2.3</v>
-      </c>
-      <c r="T14">
-        <v>1.11</v>
-      </c>
-      <c r="U14">
-        <v>1.11</v>
-      </c>
       <c r="V14">
         <v>1.04</v>
       </c>
       <c r="W14">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="X14">
-        <v>950</v>
+        <v>27</v>
       </c>
       <c r="Y14">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="Z14">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AA14">
         <v>1000</v>
       </c>
       <c r="AB14">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AD14">
-        <v>950</v>
+        <v>90</v>
       </c>
       <c r="AE14">
-        <v>1000</v>
+        <v>520</v>
       </c>
       <c r="AF14">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AG14">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH14">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AI14">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="AJ14">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AK14">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="AL14">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM14">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AN14">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="AO14">
         <v>1000</v>
       </c>
       <c r="AP14">
-        <v>2.56</v>
+        <v>21</v>
       </c>
       <c r="AQ14">
-        <v>2.78</v>
+        <v>7</v>
       </c>
       <c r="AR14">
-        <v>2.78</v>
+        <v>7.6</v>
       </c>
       <c r="AS14">
-        <v>2.78</v>
+        <v>7.8</v>
       </c>
       <c r="AT14">
-        <v>2.24</v>
+        <v>7.6</v>
       </c>
       <c r="AU14">
-        <v>2.46</v>
+        <v>14.5</v>
       </c>
       <c r="AV14">
-        <v>2.7</v>
+        <v>7.2</v>
       </c>
       <c r="AW14">
-        <v>2.78</v>
+        <v>7.6</v>
       </c>
       <c r="AX14">
-        <v>2.14</v>
+        <v>6.2</v>
       </c>
       <c r="AY14">
-        <v>2.78</v>
+        <v>10</v>
       </c>
       <c r="AZ14">
-        <v>2.78</v>
+        <v>6.8</v>
       </c>
       <c r="BA14">
-        <v>2.78</v>
+        <v>7.6</v>
       </c>
       <c r="BB14">
-        <v>2.22</v>
+        <v>7.2</v>
       </c>
       <c r="BC14">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD14">
-        <v>2.66</v>
+        <v>6.8</v>
       </c>
       <c r="BE14">
-        <v>2.78</v>
+        <v>7.6</v>
       </c>
       <c r="BF14">
-        <v>1.79</v>
+        <v>3.55</v>
       </c>
       <c r="BG14">
-        <v>2.78</v>
+        <v>7.8</v>
       </c>
       <c r="BH14">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BI14">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="BJ14">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BK14">
-        <v>2.64</v>
+        <v>1.04</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="BN14">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BO14">
-        <v>2.54</v>
+        <v>1.04</v>
       </c>
       <c r="BP14">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BR14">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>2.8</v>
+        <v>1.04</v>
       </c>
       <c r="BT14">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BU14">
-        <v>2.72</v>
+        <v>1.04</v>
       </c>
       <c r="BV14">
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="CA14">
-        <v>2.46</v>
+        <v>1.04</v>
       </c>
       <c r="CB14" t="s">
         <v>146</v>
@@ -4203,7 +4203,7 @@
         <v>1.99</v>
       </c>
       <c r="I15">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="J15">
         <v>3.45</v>
@@ -4242,7 +4242,7 @@
         <v>1.89</v>
       </c>
       <c r="V15">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="W15">
         <v>1.26</v>
@@ -4311,7 +4311,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AS15">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AT15">
         <v>12.5</v>
@@ -4323,7 +4323,7 @@
         <v>9</v>
       </c>
       <c r="AW15">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AX15">
         <v>19.5</v>
@@ -4353,7 +4353,7 @@
         <v>34</v>
       </c>
       <c r="BG15">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4475,7 +4475,7 @@
         <v>1.27</v>
       </c>
       <c r="S16">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T16">
         <v>1.92</v>
@@ -4523,7 +4523,7 @@
         <v>950</v>
       </c>
       <c r="AI16">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ16">
         <v>32</v>
@@ -4532,13 +4532,13 @@
         <v>28</v>
       </c>
       <c r="AL16">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM16">
         <v>150</v>
       </c>
       <c r="AN16">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO16">
         <v>65</v>
@@ -4550,10 +4550,10 @@
         <v>10.5</v>
       </c>
       <c r="AR16">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AS16">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT16">
         <v>7.4</v>
@@ -4565,7 +4565,7 @@
         <v>14</v>
       </c>
       <c r="AW16">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX16">
         <v>12</v>
@@ -4574,28 +4574,28 @@
         <v>10</v>
       </c>
       <c r="AZ16">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BA16">
         <v>11</v>
       </c>
       <c r="BB16">
+        <v>9.6</v>
+      </c>
+      <c r="BC16">
         <v>9.199999999999999</v>
       </c>
-      <c r="BC16">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BD16">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BE16">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF16">
         <v>18.5</v>
       </c>
       <c r="BG16">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4681,13 +4681,13 @@
         <v>1.39</v>
       </c>
       <c r="G17">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="H17">
         <v>9.4</v>
       </c>
       <c r="I17">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="J17">
         <v>4.5</v>
@@ -4711,7 +4711,7 @@
         <v>1.9</v>
       </c>
       <c r="Q17">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="R17">
         <v>1.33</v>
@@ -4723,7 +4723,7 @@
         <v>2.26</v>
       </c>
       <c r="U17">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="V17">
         <v>1.09</v>
@@ -4741,19 +4741,19 @@
         <v>120</v>
       </c>
       <c r="AA17">
-        <v>590</v>
+        <v>560</v>
       </c>
       <c r="AB17">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC17">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD17">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AE17">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AF17">
         <v>9</v>
@@ -4765,10 +4765,10 @@
         <v>40</v>
       </c>
       <c r="AI17">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AJ17">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AK17">
         <v>21</v>
@@ -4777,25 +4777,25 @@
         <v>60</v>
       </c>
       <c r="AM17">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AN17">
         <v>10</v>
       </c>
       <c r="AO17">
-        <v>480</v>
+        <v>450</v>
       </c>
       <c r="AP17">
         <v>12</v>
       </c>
       <c r="AQ17">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AR17">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AS17">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AT17">
         <v>5.9</v>
@@ -4804,10 +4804,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV17">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AW17">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AX17">
         <v>6.4</v>
@@ -4816,10 +4816,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ17">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BA17">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BB17">
         <v>10</v>
@@ -4828,16 +4828,16 @@
         <v>14.5</v>
       </c>
       <c r="BD17">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BE17">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BF17">
         <v>6.2</v>
       </c>
       <c r="BG17">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BH17">
         <v>4</v>
@@ -4923,7 +4923,7 @@
         <v>1.8</v>
       </c>
       <c r="G18">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="H18">
         <v>4.2</v>
@@ -4932,7 +4932,7 @@
         <v>4.9</v>
       </c>
       <c r="J18">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="K18">
         <v>4.5</v>
@@ -4944,94 +4944,94 @@
         <v>1.05</v>
       </c>
       <c r="N18">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O18">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="P18">
         <v>2.12</v>
       </c>
       <c r="Q18">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R18">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="S18">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="T18">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U18">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="V18">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W18">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="X18">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y18">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z18">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA18">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB18">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC18">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD18">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE18">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF18">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG18">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH18">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI18">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ18">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK18">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL18">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM18">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN18">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AO18">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP18">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AQ18">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AR18">
         <v>1.03</v>
@@ -5040,34 +5040,34 @@
         <v>1.03</v>
       </c>
       <c r="AT18">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AU18">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AV18">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AW18">
         <v>1.03</v>
       </c>
       <c r="AX18">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AY18">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AZ18">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BA18">
         <v>1.03</v>
       </c>
       <c r="BB18">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BC18">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BD18">
         <v>1.03</v>
@@ -5076,10 +5076,10 @@
         <v>1.03</v>
       </c>
       <c r="BF18">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG18">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5162,16 +5162,16 @@
         <v>140</v>
       </c>
       <c r="F19">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="G19">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="H19">
         <v>1.85</v>
       </c>
       <c r="I19">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="J19">
         <v>4.3</v>
@@ -5207,13 +5207,13 @@
         <v>1.44</v>
       </c>
       <c r="U19">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="V19">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="W19">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="X19">
         <v>44</v>
@@ -5252,7 +5252,7 @@
         <v>27</v>
       </c>
       <c r="AJ19">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AK19">
         <v>40</v>
@@ -5294,7 +5294,7 @@
         <v>13.5</v>
       </c>
       <c r="AX19">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AY19">
         <v>15</v>
@@ -5309,13 +5309,13 @@
         <v>5.6</v>
       </c>
       <c r="BC19">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BD19">
         <v>5.3</v>
       </c>
       <c r="BE19">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BF19">
         <v>16</v>
@@ -5324,64 +5324,64 @@
         <v>6</v>
       </c>
       <c r="BH19">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BI19">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BJ19">
-        <v>12.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK19">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BL19">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BM19">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="BN19">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="BO19">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BP19">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="BQ19">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BR19">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="BS19">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="BT19">
-        <v>7.6</v>
+        <v>5.6</v>
       </c>
       <c r="BU19">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="BV19">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BW19">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BX19">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="BY19">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BZ19">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="CA19">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB19" t="s">
         <v>146</v>
@@ -5404,7 +5404,7 @@
         <v>141</v>
       </c>
       <c r="F20">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G20">
         <v>2.46</v>
@@ -5419,37 +5419,37 @@
         <v>3.2</v>
       </c>
       <c r="K20">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L20">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="M20">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N20">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O20">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P20">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q20">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="R20">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="S20">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="T20">
         <v>1.92</v>
       </c>
       <c r="U20">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="V20">
         <v>1.36</v>
@@ -5458,172 +5458,172 @@
         <v>1.68</v>
       </c>
       <c r="X20">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y20">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z20">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA20">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB20">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC20">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD20">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE20">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF20">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG20">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH20">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI20">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ20">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK20">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL20">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM20">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN20">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO20">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP20">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AQ20">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AR20">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AS20">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AT20">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AU20">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV20">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AW20">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AX20">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AY20">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ20">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BA20">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BB20">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BC20">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BD20">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BE20">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BF20">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BG20">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH20">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI20">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="BJ20">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK20">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN20">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO20">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP20">
         <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BR20">
         <v>1000</v>
       </c>
       <c r="BS20">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BT20">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU20">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BV20">
         <v>1000</v>
       </c>
       <c r="BW20">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BX20">
         <v>1000</v>
       </c>
       <c r="BY20">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BZ20">
         <v>1000</v>
       </c>
       <c r="CA20">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="CB20" t="s">
         <v>146</v>
@@ -5655,7 +5655,7 @@
         <v>3.8</v>
       </c>
       <c r="I21">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="J21">
         <v>3.8</v>
@@ -5664,7 +5664,7 @@
         <v>4</v>
       </c>
       <c r="L21">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M21">
         <v>1.05</v>
@@ -5676,7 +5676,7 @@
         <v>1.27</v>
       </c>
       <c r="P21">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q21">
         <v>1.81</v>
@@ -5688,7 +5688,7 @@
         <v>3.05</v>
       </c>
       <c r="T21">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U21">
         <v>2.2</v>
@@ -5700,10 +5700,10 @@
         <v>1.92</v>
       </c>
       <c r="X21">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y21">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z21">
         <v>36</v>
@@ -5712,10 +5712,10 @@
         <v>90</v>
       </c>
       <c r="AB21">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC21">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD21">
         <v>19.5</v>
@@ -5727,7 +5727,7 @@
         <v>16.5</v>
       </c>
       <c r="AG21">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH21">
         <v>21</v>
@@ -5736,7 +5736,7 @@
         <v>60</v>
       </c>
       <c r="AJ21">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK21">
         <v>25</v>
@@ -5760,10 +5760,10 @@
         <v>14</v>
       </c>
       <c r="AR21">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AS21">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AT21">
         <v>9.199999999999999</v>
@@ -5775,7 +5775,7 @@
         <v>13.5</v>
       </c>
       <c r="AW21">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AX21">
         <v>11.5</v>
@@ -5787,7 +5787,7 @@
         <v>14</v>
       </c>
       <c r="BA21">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BB21">
         <v>20</v>
@@ -5796,16 +5796,16 @@
         <v>17</v>
       </c>
       <c r="BD21">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BE21">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BF21">
         <v>10.5</v>
       </c>
       <c r="BG21">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BH21">
         <v>1000</v>
@@ -5814,7 +5814,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ21">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK21">
         <v>5.8</v>
@@ -5862,7 +5862,7 @@
         <v>21</v>
       </c>
       <c r="BZ21">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="CA21">
         <v>12</v>
@@ -5891,7 +5891,7 @@
         <v>1.97</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H22">
         <v>3.95</v>
@@ -5906,13 +5906,13 @@
         <v>4.1</v>
       </c>
       <c r="L22">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M22">
         <v>1.05</v>
       </c>
       <c r="N22">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O22">
         <v>1.27</v>
@@ -5924,142 +5924,142 @@
         <v>1.83</v>
       </c>
       <c r="R22">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S22">
         <v>3.15</v>
       </c>
       <c r="T22">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U22">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="V22">
         <v>1.32</v>
       </c>
       <c r="W22">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X22">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y22">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z22">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA22">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB22">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC22">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD22">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE22">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF22">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG22">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH22">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI22">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ22">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK22">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL22">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM22">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN22">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO22">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP22">
-        <v>1.11</v>
+        <v>3.8</v>
       </c>
       <c r="AQ22">
-        <v>1.11</v>
+        <v>14</v>
       </c>
       <c r="AR22">
-        <v>1.11</v>
+        <v>4.1</v>
       </c>
       <c r="AS22">
-        <v>1.11</v>
+        <v>4.4</v>
       </c>
       <c r="AT22">
-        <v>1.11</v>
+        <v>9</v>
       </c>
       <c r="AU22">
         <v>8</v>
       </c>
       <c r="AV22">
-        <v>1.11</v>
+        <v>14</v>
       </c>
       <c r="AW22">
-        <v>1.11</v>
+        <v>4.3</v>
       </c>
       <c r="AX22">
-        <v>1.11</v>
+        <v>11</v>
       </c>
       <c r="AY22">
-        <v>1.11</v>
+        <v>9</v>
       </c>
       <c r="AZ22">
-        <v>1.11</v>
+        <v>14.5</v>
       </c>
       <c r="BA22">
-        <v>1.11</v>
+        <v>4.3</v>
       </c>
       <c r="BB22">
-        <v>1.11</v>
+        <v>19.5</v>
       </c>
       <c r="BC22">
-        <v>1.11</v>
+        <v>16.5</v>
       </c>
       <c r="BD22">
-        <v>1.11</v>
+        <v>4.2</v>
       </c>
       <c r="BE22">
-        <v>1.11</v>
+        <v>4.4</v>
       </c>
       <c r="BF22">
-        <v>1.11</v>
+        <v>10</v>
       </c>
       <c r="BG22">
-        <v>1.11</v>
+        <v>4.3</v>
       </c>
       <c r="BH22">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI22">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BJ22">
-        <v>13.5</v>
+        <v>9.6</v>
       </c>
       <c r="BK22">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BL22">
         <v>1000</v>
@@ -6068,31 +6068,31 @@
         <v>21</v>
       </c>
       <c r="BN22">
-        <v>6.8</v>
+        <v>5.1</v>
       </c>
       <c r="BO22">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="BP22">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="BQ22">
         <v>8.4</v>
       </c>
       <c r="BR22">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="BS22">
         <v>15.5</v>
       </c>
       <c r="BT22">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="BU22">
         <v>4.8</v>
       </c>
       <c r="BV22">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="BW22">
         <v>18.5</v>
@@ -6104,7 +6104,7 @@
         <v>21</v>
       </c>
       <c r="BZ22">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="CA22">
         <v>12.5</v>
@@ -6133,10 +6133,10 @@
         <v>1.81</v>
       </c>
       <c r="G23">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H23">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I23">
         <v>4.5</v>
@@ -6145,7 +6145,7 @@
         <v>4.3</v>
       </c>
       <c r="K23">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L23">
         <v>1.26</v>
@@ -6160,16 +6160,16 @@
         <v>1.17</v>
       </c>
       <c r="P23">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="Q23">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R23">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="S23">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="T23">
         <v>1.55</v>
@@ -6181,7 +6181,7 @@
         <v>1.29</v>
       </c>
       <c r="W23">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X23">
         <v>32</v>
@@ -6214,7 +6214,7 @@
         <v>12.5</v>
       </c>
       <c r="AH23">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI23">
         <v>48</v>
@@ -6238,16 +6238,16 @@
         <v>36</v>
       </c>
       <c r="AP23">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AQ23">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR23">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AS23">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AT23">
         <v>12.5</v>
@@ -6259,7 +6259,7 @@
         <v>15.5</v>
       </c>
       <c r="AW23">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX23">
         <v>13</v>
@@ -6271,7 +6271,7 @@
         <v>13.5</v>
       </c>
       <c r="BA23">
-        <v>34</v>
+        <v>5.4</v>
       </c>
       <c r="BB23">
         <v>18</v>
@@ -6283,13 +6283,13 @@
         <v>21</v>
       </c>
       <c r="BE23">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF23">
         <v>6.4</v>
       </c>
       <c r="BG23">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6378,13 +6378,13 @@
         <v>2.2</v>
       </c>
       <c r="H24">
+        <v>3.1</v>
+      </c>
+      <c r="I24">
         <v>3.15</v>
       </c>
-      <c r="I24">
-        <v>3.25</v>
-      </c>
       <c r="J24">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K24">
         <v>4.5</v>
@@ -6396,7 +6396,7 @@
         <v>1.02</v>
       </c>
       <c r="N24">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O24">
         <v>1.12</v>
@@ -6405,22 +6405,22 @@
         <v>3.4</v>
       </c>
       <c r="Q24">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="R24">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="S24">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="T24">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="U24">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="V24">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W24">
         <v>1.83</v>
@@ -6429,7 +6429,7 @@
         <v>42</v>
       </c>
       <c r="Y24">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="Z24">
         <v>34</v>
@@ -6438,7 +6438,7 @@
         <v>60</v>
       </c>
       <c r="AB24">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AC24">
         <v>12</v>
@@ -6468,7 +6468,7 @@
         <v>19</v>
       </c>
       <c r="AL24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM24">
         <v>42</v>
@@ -6519,7 +6519,7 @@
         <v>27</v>
       </c>
       <c r="BC24">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD24">
         <v>19</v>
@@ -6528,7 +6528,7 @@
         <v>34</v>
       </c>
       <c r="BF24">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG24">
         <v>12</v>
@@ -6555,10 +6555,10 @@
         <v>8.6</v>
       </c>
       <c r="BO24">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BP24">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BQ24">
         <v>8.199999999999999</v>
@@ -6588,7 +6588,7 @@
         <v>13.5</v>
       </c>
       <c r="BZ24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CA24">
         <v>6.8</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
@@ -454,7 +454,7 @@
     <t>Chicago Fire</t>
   </si>
   <si>
-    <t>2026-07-21 02:53:07</t>
+    <t>2026-07-21 05:00:08</t>
   </si>
 </sst>
 </file>
@@ -1048,64 +1048,64 @@
         <v>123</v>
       </c>
       <c r="F2">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="G2">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H2">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I2">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J2">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K2">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L2">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="M2">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="O2">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="P2">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="Q2">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="R2">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S2">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="T2">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="U2">
+        <v>2</v>
+      </c>
+      <c r="V2">
+        <v>1.27</v>
+      </c>
+      <c r="W2">
         <v>1.96</v>
       </c>
-      <c r="V2">
-        <v>1.26</v>
-      </c>
-      <c r="W2">
-        <v>1.98</v>
-      </c>
       <c r="X2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z2">
         <v>34</v>
@@ -1114,10 +1114,10 @@
         <v>110</v>
       </c>
       <c r="AB2">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AC2">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AD2">
         <v>18.5</v>
@@ -1126,13 +1126,13 @@
         <v>65</v>
       </c>
       <c r="AF2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG2">
         <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI2">
         <v>80</v>
@@ -1141,19 +1141,19 @@
         <v>23</v>
       </c>
       <c r="AK2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM2">
         <v>140</v>
       </c>
       <c r="AN2">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AO2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP2">
         <v>10.5</v>
@@ -1162,22 +1162,22 @@
         <v>13</v>
       </c>
       <c r="AR2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AS2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AT2">
         <v>7.2</v>
       </c>
       <c r="AU2">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV2">
         <v>16</v>
       </c>
       <c r="AW2">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AX2">
         <v>10</v>
@@ -1189,37 +1189,37 @@
         <v>17</v>
       </c>
       <c r="BA2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BB2">
         <v>20</v>
       </c>
       <c r="BC2">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BD2">
         <v>36</v>
       </c>
       <c r="BE2">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="BF2">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG2">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="BH2">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="BI2">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="BJ2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -1231,19 +1231,19 @@
         <v>4.6</v>
       </c>
       <c r="BO2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ2">
         <v>7.4</v>
       </c>
       <c r="BR2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT2">
         <v>7.8</v>
@@ -1252,10 +1252,10 @@
         <v>6.2</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX2">
         <v>1000</v>
@@ -1264,7 +1264,7 @@
         <v>12</v>
       </c>
       <c r="BZ2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="CA2">
         <v>10</v>
@@ -1290,175 +1290,175 @@
         <v>124</v>
       </c>
       <c r="F3">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="G3">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="H3">
         <v>8.199999999999999</v>
       </c>
       <c r="I3">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J3">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="K3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="L3">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="M3">
         <v>1.04</v>
       </c>
       <c r="N3">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="O3">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="P3">
-        <v>2.34</v>
+        <v>2.52</v>
       </c>
       <c r="Q3">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="R3">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="S3">
-        <v>2.86</v>
+        <v>2.6</v>
       </c>
       <c r="T3">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="U3">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="V3">
         <v>1.12</v>
       </c>
       <c r="W3">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="X3">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="Y3">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Z3">
         <v>85</v>
       </c>
       <c r="AA3">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="AB3">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC3">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AD3">
         <v>34</v>
       </c>
       <c r="AE3">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AF3">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG3">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AH3">
+        <v>32</v>
+      </c>
+      <c r="AI3">
+        <v>110</v>
+      </c>
+      <c r="AJ3">
+        <v>11.5</v>
+      </c>
+      <c r="AK3">
+        <v>14</v>
+      </c>
+      <c r="AL3">
         <v>34</v>
       </c>
-      <c r="AI3">
-        <v>120</v>
-      </c>
-      <c r="AJ3">
-        <v>12</v>
-      </c>
-      <c r="AK3">
-        <v>14.5</v>
-      </c>
-      <c r="AL3">
-        <v>36</v>
-      </c>
       <c r="AM3">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN3">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="AO3">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AP3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR3">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AS3">
         <v>55</v>
       </c>
       <c r="AT3">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU3">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AV3">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AW3">
         <v>40</v>
       </c>
       <c r="AX3">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AY3">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ3">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BA3">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB3">
         <v>10.5</v>
       </c>
       <c r="BC3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BD3">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="BE3">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="BF3">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="BG3">
         <v>48</v>
       </c>
       <c r="BH3">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BI3">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="BJ3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK3">
         <v>6.8</v>
@@ -1467,31 +1467,31 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN3">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BO3">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BP3">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BQ3">
         <v>5.4</v>
       </c>
       <c r="BR3">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BS3">
         <v>9.6</v>
       </c>
       <c r="BT3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BU3">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BV3">
         <v>1000</v>
@@ -1506,10 +1506,10 @@
         <v>13.5</v>
       </c>
       <c r="BZ3">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="CA3">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="CB3" t="s">
         <v>146</v>
@@ -1532,16 +1532,16 @@
         <v>125</v>
       </c>
       <c r="F4">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="G4">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="H4">
         <v>5.1</v>
       </c>
       <c r="I4">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J4">
         <v>4.4</v>
@@ -1574,7 +1574,7 @@
         <v>2.74</v>
       </c>
       <c r="T4">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U4">
         <v>2.32</v>
@@ -1583,7 +1583,7 @@
         <v>1.22</v>
       </c>
       <c r="W4">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="X4">
         <v>22</v>
@@ -1649,13 +1649,13 @@
         <v>38</v>
       </c>
       <c r="AS4">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AT4">
         <v>10</v>
       </c>
       <c r="AU4">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV4">
         <v>18.5</v>
@@ -1688,7 +1688,7 @@
         <v>60</v>
       </c>
       <c r="BF4">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG4">
         <v>44</v>
@@ -1774,7 +1774,7 @@
         <v>126</v>
       </c>
       <c r="F5">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G5">
         <v>3.15</v>
@@ -1783,7 +1783,7 @@
         <v>2.72</v>
       </c>
       <c r="I5">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="J5">
         <v>3.1</v>
@@ -1792,7 +1792,7 @@
         <v>3.3</v>
       </c>
       <c r="L5">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M5">
         <v>1.11</v>
@@ -1801,7 +1801,7 @@
         <v>2.88</v>
       </c>
       <c r="O5">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P5">
         <v>1.63</v>
@@ -1813,7 +1813,7 @@
         <v>1.23</v>
       </c>
       <c r="S5">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="T5">
         <v>2.02</v>
@@ -1822,7 +1822,7 @@
         <v>1.9</v>
       </c>
       <c r="V5">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W5">
         <v>1.47</v>
@@ -1936,64 +1936,64 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BH5">
-        <v>3.35</v>
+        <v>2.84</v>
       </c>
       <c r="BI5">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="BJ5">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK5">
-        <v>1.44</v>
+        <v>6.4</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.44</v>
+        <v>14.5</v>
       </c>
       <c r="BN5">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO5">
-        <v>1.44</v>
+        <v>4.7</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BQ5">
-        <v>1.44</v>
+        <v>10</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>1.44</v>
+        <v>11.5</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BU5">
-        <v>1.44</v>
+        <v>4.4</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW5">
-        <v>1.44</v>
+        <v>9.6</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY5">
-        <v>1.44</v>
+        <v>11.5</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="CA5">
-        <v>1.44</v>
+        <v>11.5</v>
       </c>
       <c r="CB5" t="s">
         <v>146</v>
@@ -2019,22 +2019,22 @@
         <v>4.7</v>
       </c>
       <c r="G6">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="H6">
         <v>1.89</v>
       </c>
       <c r="I6">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="J6">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K6">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L6">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="M6">
         <v>1.08</v>
@@ -2058,13 +2058,13 @@
         <v>4</v>
       </c>
       <c r="T6">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="U6">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V6">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="W6">
         <v>1.25</v>
@@ -2121,7 +2121,7 @@
         <v>1000</v>
       </c>
       <c r="AO6">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP6">
         <v>11</v>
@@ -2130,7 +2130,7 @@
         <v>7.4</v>
       </c>
       <c r="AR6">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS6">
         <v>17.5</v>
@@ -2258,22 +2258,22 @@
         <v>128</v>
       </c>
       <c r="F7">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="G7">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H7">
         <v>4.8</v>
       </c>
       <c r="I7">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J7">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K7">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L7">
         <v>1.5</v>
@@ -2318,7 +2318,7 @@
         <v>14</v>
       </c>
       <c r="Z7">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA7">
         <v>160</v>
@@ -2342,7 +2342,7 @@
         <v>12.5</v>
       </c>
       <c r="AH7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI7">
         <v>110</v>
@@ -2503,22 +2503,22 @@
         <v>3.4</v>
       </c>
       <c r="G8">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="H8">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="I8">
         <v>2.22</v>
       </c>
       <c r="J8">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K8">
         <v>4</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M8">
         <v>1.04</v>
@@ -2530,7 +2530,7 @@
         <v>1.2</v>
       </c>
       <c r="P8">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="Q8">
         <v>1.6</v>
@@ -2548,7 +2548,7 @@
         <v>2.66</v>
       </c>
       <c r="V8">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W8">
         <v>1.34</v>
@@ -2560,10 +2560,10 @@
         <v>15</v>
       </c>
       <c r="Z8">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AB8">
         <v>20</v>
@@ -2578,7 +2578,7 @@
         <v>20</v>
       </c>
       <c r="AF8">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AG8">
         <v>14.5</v>
@@ -2590,7 +2590,7 @@
         <v>27</v>
       </c>
       <c r="AJ8">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AK8">
         <v>34</v>
@@ -2602,7 +2602,7 @@
         <v>55</v>
       </c>
       <c r="AN8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO8">
         <v>10.5</v>
@@ -2620,7 +2620,7 @@
         <v>26</v>
       </c>
       <c r="AT8">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AU8">
         <v>8.6</v>
@@ -2659,67 +2659,67 @@
         <v>18.5</v>
       </c>
       <c r="BG8">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI8">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BK8">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BL8">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BM8">
-        <v>1.04</v>
+        <v>13</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO8">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ8">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS8">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BU8">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BW8">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BY8">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="CA8">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="CB8" t="s">
         <v>146</v>
@@ -2742,25 +2742,25 @@
         <v>130</v>
       </c>
       <c r="F9">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="G9">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="H9">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I9">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J9">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="K9">
         <v>13</v>
       </c>
       <c r="L9">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="M9">
         <v>1.01</v>
@@ -2784,10 +2784,10 @@
         <v>1.66</v>
       </c>
       <c r="T9">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U9">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="V9">
         <v>1.03</v>
@@ -2811,67 +2811,67 @@
         <v>17.5</v>
       </c>
       <c r="AC9">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AD9">
         <v>950</v>
       </c>
       <c r="AE9">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="AF9">
         <v>11.5</v>
       </c>
       <c r="AG9">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH9">
         <v>950</v>
       </c>
       <c r="AI9">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AJ9">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AK9">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL9">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM9">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AN9">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AO9">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="AP9">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ9">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR9">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS9">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AT9">
         <v>12.5</v>
       </c>
       <c r="AU9">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AV9">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW9">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AX9">
         <v>9.6</v>
@@ -2880,10 +2880,10 @@
         <v>12.5</v>
       </c>
       <c r="AZ9">
-        <v>28</v>
+        <v>10.5</v>
       </c>
       <c r="BA9">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BB9">
         <v>8.4</v>
@@ -2892,76 +2892,76 @@
         <v>12</v>
       </c>
       <c r="BD9">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BE9">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF9">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="BG9">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BH9">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BI9">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK9">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO9">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BQ9">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BS9">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BU9">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="CA9">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="CB9" t="s">
         <v>146</v>
@@ -2984,22 +2984,22 @@
         <v>131</v>
       </c>
       <c r="F10">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G10">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="H10">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I10">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J10">
         <v>3.05</v>
       </c>
       <c r="K10">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3035,7 +3035,7 @@
         <v>1.29</v>
       </c>
       <c r="W10">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="X10">
         <v>11</v>
@@ -3098,10 +3098,10 @@
         <v>9.4</v>
       </c>
       <c r="AR10">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AS10">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT10">
         <v>6.2</v>
@@ -3125,25 +3125,25 @@
         <v>19.5</v>
       </c>
       <c r="BA10">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB10">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BC10">
-        <v>6.6</v>
+        <v>26</v>
       </c>
       <c r="BD10">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BE10">
         <v>7.8</v>
       </c>
       <c r="BF10">
-        <v>6.4</v>
+        <v>23</v>
       </c>
       <c r="BG10">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH10">
         <v>3.2</v>
@@ -3232,16 +3232,16 @@
         <v>1000</v>
       </c>
       <c r="H11">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="I11">
         <v>1000</v>
       </c>
       <c r="J11">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="K11">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3268,10 +3268,10 @@
         <v>1.05</v>
       </c>
       <c r="T11">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="U11">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="V11">
         <v>1.01</v>
@@ -3474,7 +3474,7 @@
         <v>1000</v>
       </c>
       <c r="H12">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="I12">
         <v>1000</v>
@@ -3483,7 +3483,7 @@
         <v>1.03</v>
       </c>
       <c r="K12">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3510,16 +3510,16 @@
         <v>1.05</v>
       </c>
       <c r="T12">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="U12">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="V12">
         <v>1.02</v>
       </c>
       <c r="W12">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3722,10 +3722,10 @@
         <v>1000</v>
       </c>
       <c r="J13">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="K13">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -3952,226 +3952,226 @@
         <v>135</v>
       </c>
       <c r="F14">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="G14">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="H14">
+        <v>15.5</v>
+      </c>
+      <c r="I14">
+        <v>22</v>
+      </c>
+      <c r="J14">
+        <v>6.2</v>
+      </c>
+      <c r="K14">
+        <v>7.4</v>
+      </c>
+      <c r="L14">
+        <v>1.25</v>
+      </c>
+      <c r="M14">
+        <v>1.01</v>
+      </c>
+      <c r="N14">
+        <v>4.7</v>
+      </c>
+      <c r="O14">
+        <v>1.21</v>
+      </c>
+      <c r="P14">
+        <v>2.26</v>
+      </c>
+      <c r="Q14">
+        <v>1.6</v>
+      </c>
+      <c r="R14">
+        <v>1.5</v>
+      </c>
+      <c r="S14">
+        <v>2.54</v>
+      </c>
+      <c r="T14">
+        <v>2.26</v>
+      </c>
+      <c r="U14">
+        <v>1.62</v>
+      </c>
+      <c r="V14">
+        <v>1.05</v>
+      </c>
+      <c r="W14">
+        <v>4.4</v>
+      </c>
+      <c r="X14">
+        <v>28</v>
+      </c>
+      <c r="Y14">
+        <v>60</v>
+      </c>
+      <c r="Z14">
+        <v>210</v>
+      </c>
+      <c r="AA14">
+        <v>1000</v>
+      </c>
+      <c r="AB14">
+        <v>10.5</v>
+      </c>
+      <c r="AC14">
+        <v>19</v>
+      </c>
+      <c r="AD14">
+        <v>75</v>
+      </c>
+      <c r="AE14">
+        <v>420</v>
+      </c>
+      <c r="AF14">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG14">
+        <v>14</v>
+      </c>
+      <c r="AH14">
+        <v>50</v>
+      </c>
+      <c r="AI14">
+        <v>300</v>
+      </c>
+      <c r="AJ14">
+        <v>9.6</v>
+      </c>
+      <c r="AK14">
         <v>18.5</v>
       </c>
-      <c r="I14">
-        <v>25</v>
-      </c>
-      <c r="J14">
-        <v>6.8</v>
-      </c>
-      <c r="K14">
-        <v>8.6</v>
-      </c>
-      <c r="L14">
-        <v>1.01</v>
-      </c>
-      <c r="M14">
-        <v>1.01</v>
-      </c>
-      <c r="N14">
+      <c r="AL14">
+        <v>60</v>
+      </c>
+      <c r="AM14">
+        <v>310</v>
+      </c>
+      <c r="AN14">
+        <v>4.8</v>
+      </c>
+      <c r="AO14">
+        <v>1000</v>
+      </c>
+      <c r="AP14">
+        <v>19.5</v>
+      </c>
+      <c r="AQ14">
+        <v>36</v>
+      </c>
+      <c r="AR14">
+        <v>5.3</v>
+      </c>
+      <c r="AS14">
+        <v>5.4</v>
+      </c>
+      <c r="AT14">
+        <v>7.2</v>
+      </c>
+      <c r="AU14">
+        <v>12.5</v>
+      </c>
+      <c r="AV14">
         <v>5</v>
       </c>
-      <c r="O14">
-        <v>1.19</v>
-      </c>
-      <c r="P14">
-        <v>2.38</v>
-      </c>
-      <c r="Q14">
-        <v>1.58</v>
-      </c>
-      <c r="R14">
-        <v>1.55</v>
-      </c>
-      <c r="S14">
-        <v>2.42</v>
-      </c>
-      <c r="T14">
-        <v>2.38</v>
-      </c>
-      <c r="U14">
-        <v>1.57</v>
-      </c>
-      <c r="V14">
-        <v>1.04</v>
-      </c>
-      <c r="W14">
-        <v>5.1</v>
-      </c>
-      <c r="X14">
-        <v>27</v>
-      </c>
-      <c r="Y14">
-        <v>70</v>
-      </c>
-      <c r="Z14">
-        <v>260</v>
-      </c>
-      <c r="AA14">
-        <v>1000</v>
-      </c>
-      <c r="AB14">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC14">
-        <v>21</v>
-      </c>
-      <c r="AD14">
-        <v>90</v>
-      </c>
-      <c r="AE14">
-        <v>520</v>
-      </c>
-      <c r="AF14">
-        <v>7.6</v>
-      </c>
-      <c r="AG14">
-        <v>15</v>
-      </c>
-      <c r="AH14">
-        <v>55</v>
-      </c>
-      <c r="AI14">
-        <v>360</v>
-      </c>
-      <c r="AJ14">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AK14">
-        <v>16</v>
-      </c>
-      <c r="AL14">
-        <v>55</v>
-      </c>
-      <c r="AM14">
-        <v>350</v>
-      </c>
-      <c r="AN14">
-        <v>4.3</v>
-      </c>
-      <c r="AO14">
-        <v>1000</v>
-      </c>
-      <c r="AP14">
-        <v>21</v>
-      </c>
-      <c r="AQ14">
-        <v>7</v>
-      </c>
-      <c r="AR14">
-        <v>7.6</v>
-      </c>
-      <c r="AS14">
-        <v>7.8</v>
-      </c>
-      <c r="AT14">
-        <v>7.6</v>
-      </c>
-      <c r="AU14">
-        <v>14.5</v>
-      </c>
-      <c r="AV14">
-        <v>7.2</v>
-      </c>
       <c r="AW14">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="AX14">
         <v>6.2</v>
       </c>
       <c r="AY14">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ14">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="BA14">
+        <v>5.3</v>
+      </c>
+      <c r="BB14">
         <v>7.6</v>
-      </c>
-      <c r="BB14">
-        <v>7.2</v>
       </c>
       <c r="BC14">
         <v>12.5</v>
       </c>
       <c r="BD14">
-        <v>6.8</v>
+        <v>5</v>
       </c>
       <c r="BE14">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="BF14">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="BG14">
-        <v>7.8</v>
+        <v>5.4</v>
       </c>
       <c r="BH14">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI14">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BJ14">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK14">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BN14">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BO14">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BP14">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BQ14">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BR14">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS14">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BT14">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BU14">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BV14">
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="CA14">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="CB14" t="s">
         <v>146</v>
@@ -4194,16 +4194,16 @@
         <v>136</v>
       </c>
       <c r="F15">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="G15">
         <v>4.8</v>
       </c>
       <c r="H15">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="I15">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="J15">
         <v>3.45</v>
@@ -4227,10 +4227,10 @@
         <v>1.73</v>
       </c>
       <c r="Q15">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R15">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S15">
         <v>4.3</v>
@@ -4242,10 +4242,10 @@
         <v>1.89</v>
       </c>
       <c r="V15">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="W15">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X15">
         <v>11</v>
@@ -4260,7 +4260,7 @@
         <v>25</v>
       </c>
       <c r="AB15">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC15">
         <v>7.6</v>
@@ -4272,16 +4272,16 @@
         <v>24</v>
       </c>
       <c r="AF15">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG15">
         <v>19</v>
       </c>
       <c r="AH15">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI15">
-        <v>160</v>
+        <v>48</v>
       </c>
       <c r="AJ15">
         <v>120</v>
@@ -4326,10 +4326,10 @@
         <v>21</v>
       </c>
       <c r="AX15">
-        <v>19.5</v>
+        <v>28</v>
       </c>
       <c r="AY15">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AZ15">
         <v>19.5</v>
@@ -4341,7 +4341,7 @@
         <v>38</v>
       </c>
       <c r="BC15">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="BD15">
         <v>36</v>
@@ -4442,7 +4442,7 @@
         <v>2.32</v>
       </c>
       <c r="H16">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I16">
         <v>3.95</v>
@@ -4454,7 +4454,7 @@
         <v>3.45</v>
       </c>
       <c r="L16">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="M16">
         <v>1.09</v>
@@ -4466,10 +4466,10 @@
         <v>1.42</v>
       </c>
       <c r="P16">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="Q16">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R16">
         <v>1.27</v>
@@ -4586,7 +4586,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BD16">
-        <v>10.5</v>
+        <v>40</v>
       </c>
       <c r="BE16">
         <v>12.5</v>
@@ -4598,64 +4598,64 @@
         <v>11</v>
       </c>
       <c r="BH16">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI16">
-        <v>1.04</v>
+        <v>2.54</v>
       </c>
       <c r="BJ16">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK16">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.04</v>
+        <v>13.5</v>
       </c>
       <c r="BN16">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO16">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BP16">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ16">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BR16">
         <v>1000</v>
       </c>
       <c r="BS16">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU16">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BZ16">
         <v>1000</v>
       </c>
       <c r="CA16">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="CB16" t="s">
         <v>146</v>
@@ -4681,10 +4681,10 @@
         <v>1.39</v>
       </c>
       <c r="G17">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H17">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="I17">
         <v>13.5</v>
@@ -4696,7 +4696,7 @@
         <v>5.1</v>
       </c>
       <c r="L17">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="M17">
         <v>1.07</v>
@@ -4729,7 +4729,7 @@
         <v>1.09</v>
       </c>
       <c r="W17">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="X17">
         <v>17.5</v>
@@ -4840,64 +4840,64 @@
         <v>4.6</v>
       </c>
       <c r="BH17">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="BI17">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="BJ17">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK17">
-        <v>1.34</v>
+        <v>6</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>1.34</v>
+        <v>10</v>
       </c>
       <c r="BN17">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BO17">
-        <v>1.34</v>
+        <v>2.88</v>
       </c>
       <c r="BP17">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ17">
-        <v>1.34</v>
+        <v>4.9</v>
       </c>
       <c r="BR17">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS17">
-        <v>1.34</v>
+        <v>8</v>
       </c>
       <c r="BT17">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BU17">
-        <v>1.34</v>
+        <v>6</v>
       </c>
       <c r="BV17">
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>1.34</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>1.34</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ17">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="CA17">
-        <v>1.34</v>
+        <v>6.8</v>
       </c>
       <c r="CB17" t="s">
         <v>146</v>
@@ -4920,10 +4920,10 @@
         <v>139</v>
       </c>
       <c r="F18">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="G18">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="H18">
         <v>4.2</v>
@@ -4932,7 +4932,7 @@
         <v>4.9</v>
       </c>
       <c r="J18">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="K18">
         <v>4.5</v>
@@ -4950,7 +4950,7 @@
         <v>1.25</v>
       </c>
       <c r="P18">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q18">
         <v>1.74</v>
@@ -4971,7 +4971,7 @@
         <v>1.26</v>
       </c>
       <c r="W18">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X18">
         <v>22</v>
@@ -5010,7 +5010,7 @@
         <v>65</v>
       </c>
       <c r="AJ18">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK18">
         <v>21</v>
@@ -5165,7 +5165,7 @@
         <v>4</v>
       </c>
       <c r="G19">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H19">
         <v>1.85</v>
@@ -5174,7 +5174,7 @@
         <v>1.89</v>
       </c>
       <c r="J19">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K19">
         <v>4.7</v>
@@ -5198,7 +5198,7 @@
         <v>1.43</v>
       </c>
       <c r="R19">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="S19">
         <v>2.06</v>
@@ -5213,7 +5213,7 @@
         <v>2.12</v>
       </c>
       <c r="W19">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X19">
         <v>44</v>
@@ -5363,7 +5363,7 @@
         <v>5.6</v>
       </c>
       <c r="BU19">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BV19">
         <v>12</v>
@@ -5407,16 +5407,16 @@
         <v>2.28</v>
       </c>
       <c r="G20">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="H20">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I20">
         <v>3.75</v>
       </c>
       <c r="J20">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K20">
         <v>3.5</v>
@@ -5455,7 +5455,7 @@
         <v>1.36</v>
       </c>
       <c r="W20">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="X20">
         <v>12.5</v>
@@ -5646,7 +5646,7 @@
         <v>142</v>
       </c>
       <c r="F21">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G21">
         <v>2.08</v>
@@ -5655,7 +5655,7 @@
         <v>3.8</v>
       </c>
       <c r="I21">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J21">
         <v>3.8</v>
@@ -5682,7 +5682,7 @@
         <v>1.81</v>
       </c>
       <c r="R21">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S21">
         <v>3.05</v>
@@ -5691,7 +5691,7 @@
         <v>1.71</v>
       </c>
       <c r="U21">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V21">
         <v>1.34</v>
@@ -5790,7 +5790,7 @@
         <v>4.3</v>
       </c>
       <c r="BB21">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="BC21">
         <v>17</v>
@@ -5808,16 +5808,16 @@
         <v>4.2</v>
       </c>
       <c r="BH21">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI21">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BJ21">
-        <v>13.5</v>
+        <v>9.6</v>
       </c>
       <c r="BK21">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BL21">
         <v>1000</v>
@@ -5826,46 +5826,46 @@
         <v>21</v>
       </c>
       <c r="BN21">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="BO21">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="BP21">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="BQ21">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BR21">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="BS21">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BT21">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="BU21">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BV21">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="BW21">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BX21">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BY21">
+        <v>26</v>
+      </c>
+      <c r="BZ21">
         <v>21</v>
       </c>
-      <c r="BZ21">
-        <v>30</v>
-      </c>
       <c r="CA21">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="CB21" t="s">
         <v>146</v>
@@ -5888,7 +5888,7 @@
         <v>143</v>
       </c>
       <c r="F22">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="G22">
         <v>2.02</v>
@@ -5897,7 +5897,7 @@
         <v>3.95</v>
       </c>
       <c r="I22">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J22">
         <v>4</v>
@@ -5912,19 +5912,19 @@
         <v>1.05</v>
       </c>
       <c r="N22">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O22">
         <v>1.27</v>
       </c>
       <c r="P22">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q22">
         <v>1.83</v>
       </c>
       <c r="R22">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S22">
         <v>3.15</v>
@@ -5990,22 +5990,22 @@
         <v>100</v>
       </c>
       <c r="AN22">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO22">
         <v>55</v>
       </c>
       <c r="AP22">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AQ22">
         <v>14</v>
       </c>
       <c r="AR22">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS22">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT22">
         <v>9</v>
@@ -6017,7 +6017,7 @@
         <v>14</v>
       </c>
       <c r="AW22">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AX22">
         <v>11</v>
@@ -6029,7 +6029,7 @@
         <v>14.5</v>
       </c>
       <c r="BA22">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BB22">
         <v>19.5</v>
@@ -6041,7 +6041,7 @@
         <v>4.2</v>
       </c>
       <c r="BE22">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF22">
         <v>10</v>
@@ -6163,13 +6163,13 @@
         <v>2.78</v>
       </c>
       <c r="Q23">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R23">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="S23">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="T23">
         <v>1.55</v>
@@ -6178,7 +6178,7 @@
         <v>2.6</v>
       </c>
       <c r="V23">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W23">
         <v>2.16</v>
@@ -6292,13 +6292,13 @@
         <v>5.1</v>
       </c>
       <c r="BH23">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BI23">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BJ23">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK23">
         <v>5.8</v>
@@ -6310,43 +6310,43 @@
         <v>21</v>
       </c>
       <c r="BN23">
-        <v>6.6</v>
+        <v>5.1</v>
       </c>
       <c r="BO23">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="BP23">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="BQ23">
         <v>7.2</v>
       </c>
       <c r="BR23">
-        <v>28</v>
+        <v>19.5</v>
       </c>
       <c r="BS23">
         <v>12.5</v>
       </c>
       <c r="BT23">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU23">
         <v>5.4</v>
       </c>
       <c r="BV23">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="BW23">
         <v>17.5</v>
       </c>
       <c r="BX23">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="BY23">
         <v>19</v>
       </c>
       <c r="BZ23">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="CA23">
         <v>8.4</v>
@@ -6378,16 +6378,16 @@
         <v>2.2</v>
       </c>
       <c r="H24">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I24">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J24">
         <v>4.3</v>
       </c>
       <c r="K24">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L24">
         <v>1.21</v>
@@ -6405,31 +6405,31 @@
         <v>3.4</v>
       </c>
       <c r="Q24">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="R24">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="S24">
         <v>1.96</v>
       </c>
       <c r="T24">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="U24">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="V24">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W24">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X24">
         <v>42</v>
       </c>
       <c r="Y24">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="Z24">
         <v>34</v>
@@ -6465,10 +6465,10 @@
         <v>32</v>
       </c>
       <c r="AK24">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL24">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM24">
         <v>42</v>
@@ -6480,7 +6480,7 @@
         <v>14</v>
       </c>
       <c r="AP24">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AQ24">
         <v>24</v>
@@ -6534,13 +6534,13 @@
         <v>12</v>
       </c>
       <c r="BH24">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BI24">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BJ24">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="BK24">
         <v>5.1</v>
@@ -6552,43 +6552,43 @@
         <v>21</v>
       </c>
       <c r="BN24">
-        <v>8.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO24">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="BP24">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="BQ24">
         <v>8.199999999999999</v>
       </c>
       <c r="BR24">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="BS24">
         <v>11</v>
       </c>
       <c r="BT24">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="BU24">
         <v>4.8</v>
       </c>
       <c r="BV24">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="BW24">
         <v>12</v>
       </c>
       <c r="BX24">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BY24">
         <v>13.5</v>
       </c>
       <c r="BZ24">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="CA24">
         <v>6.8</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="140">
   <si>
     <t>League</t>
   </si>
@@ -301,9 +301,6 @@
     <t>19:00:00</t>
   </si>
   <si>
-    <t>20:00:00</t>
-  </si>
-  <si>
     <t>21:30:00</t>
   </si>
   <si>
@@ -343,15 +340,6 @@
     <t>Macara</t>
   </si>
   <si>
-    <t>EC Vitoria Salvador</t>
-  </si>
-  <si>
-    <t>Mirassol</t>
-  </si>
-  <si>
-    <t>Botafogo FR</t>
-  </si>
-  <si>
     <t>Independiente (Ecu)</t>
   </si>
   <si>
@@ -367,21 +355,21 @@
     <t>Lexington SC</t>
   </si>
   <si>
+    <t>Goias</t>
+  </si>
+  <si>
+    <t>Columbus</t>
+  </si>
+  <si>
+    <t>New England Revolution</t>
+  </si>
+  <si>
+    <t>Philadelphia</t>
+  </si>
+  <si>
     <t>FC Cincinnati</t>
   </si>
   <si>
-    <t>Goias</t>
-  </si>
-  <si>
-    <t>Columbus</t>
-  </si>
-  <si>
-    <t>New England Revolution</t>
-  </si>
-  <si>
-    <t>Philadelphia</t>
-  </si>
-  <si>
     <t>Inter Miami CF</t>
   </si>
   <si>
@@ -412,15 +400,6 @@
     <t>Deportivo Cuenca</t>
   </si>
   <si>
-    <t>Vasco Da Gama</t>
-  </si>
-  <si>
-    <t>Gremio</t>
-  </si>
-  <si>
-    <t>Santos</t>
-  </si>
-  <si>
     <t>Tecnico Universitario</t>
   </si>
   <si>
@@ -436,25 +415,25 @@
     <t>Oakland Roots</t>
   </si>
   <si>
+    <t>Sport Recife</t>
+  </si>
+  <si>
+    <t>New York City</t>
+  </si>
+  <si>
+    <t>Toronto FC</t>
+  </si>
+  <si>
+    <t>New York Red Bulls</t>
+  </si>
+  <si>
     <t>Vancouver Whitecaps</t>
   </si>
   <si>
-    <t>Sport Recife</t>
-  </si>
-  <si>
-    <t>New York City</t>
-  </si>
-  <si>
-    <t>Toronto FC</t>
-  </si>
-  <si>
-    <t>New York Red Bulls</t>
-  </si>
-  <si>
     <t>Chicago Fire</t>
   </si>
   <si>
-    <t>2026-07-21 05:00:08</t>
+    <t>2026-07-21 07:07:08</t>
   </si>
 </sst>
 </file>
@@ -786,7 +765,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB24"/>
+  <dimension ref="A1:CB21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1042,28 +1021,28 @@
         <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F2">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="G2">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="H2">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="I2">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="J2">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K2">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L2">
         <v>1.43</v>
@@ -1072,22 +1051,22 @@
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="O2">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="P2">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="Q2">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="R2">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S2">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="T2">
         <v>1.88</v>
@@ -1096,76 +1075,76 @@
         <v>2</v>
       </c>
       <c r="V2">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W2">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="X2">
         <v>13</v>
       </c>
       <c r="Y2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA2">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AB2">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD2">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AE2">
         <v>65</v>
       </c>
       <c r="AF2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG2">
         <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI2">
         <v>80</v>
       </c>
       <c r="AJ2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM2">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AN2">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AO2">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AP2">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AQ2">
         <v>13</v>
       </c>
       <c r="AR2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AT2">
         <v>7.2</v>
@@ -1189,88 +1168,88 @@
         <v>17</v>
       </c>
       <c r="BA2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BB2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC2">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BD2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE2">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BF2">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG2">
         <v>55</v>
       </c>
       <c r="BH2">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BI2">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BJ2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BN2">
         <v>4.6</v>
       </c>
       <c r="BO2">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ2">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BR2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BS2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BU2">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV2">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BZ2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="CA2">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB2" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1284,28 +1263,28 @@
         <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F3">
         <v>1.37</v>
       </c>
       <c r="G3">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I3">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J3">
         <v>6</v>
       </c>
       <c r="K3">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L3">
         <v>1.31</v>
@@ -1323,28 +1302,28 @@
         <v>2.52</v>
       </c>
       <c r="Q3">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="R3">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="S3">
         <v>2.6</v>
       </c>
       <c r="T3">
+        <v>1.98</v>
+      </c>
+      <c r="U3">
         <v>1.95</v>
-      </c>
-      <c r="U3">
-        <v>1.98</v>
       </c>
       <c r="V3">
         <v>1.12</v>
       </c>
       <c r="W3">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="X3">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Y3">
         <v>32</v>
@@ -1353,13 +1332,13 @@
         <v>85</v>
       </c>
       <c r="AA3">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AB3">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AC3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD3">
         <v>34</v>
@@ -1368,13 +1347,13 @@
         <v>140</v>
       </c>
       <c r="AF3">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG3">
         <v>10.5</v>
       </c>
       <c r="AH3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI3">
         <v>110</v>
@@ -1392,13 +1371,13 @@
         <v>140</v>
       </c>
       <c r="AN3">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AO3">
         <v>160</v>
       </c>
       <c r="AP3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ3">
         <v>25</v>
@@ -1407,13 +1386,13 @@
         <v>42</v>
       </c>
       <c r="AS3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AT3">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AV3">
         <v>23</v>
@@ -1428,7 +1407,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ3">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA3">
         <v>38</v>
@@ -1440,13 +1419,13 @@
         <v>12.5</v>
       </c>
       <c r="BD3">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="BE3">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="BF3">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BG3">
         <v>48</v>
@@ -1455,7 +1434,7 @@
         <v>4.3</v>
       </c>
       <c r="BI3">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BJ3">
         <v>11.5</v>
@@ -1512,7 +1491,7 @@
         <v>10</v>
       </c>
       <c r="CB3" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1526,10 +1505,10 @@
         <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E4" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F4">
         <v>1.67</v>
@@ -1541,7 +1520,7 @@
         <v>5.1</v>
       </c>
       <c r="I4">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J4">
         <v>4.4</v>
@@ -1553,13 +1532,13 @@
         <v>1.32</v>
       </c>
       <c r="M4">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N4">
         <v>5.1</v>
       </c>
       <c r="O4">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P4">
         <v>2.4</v>
@@ -1568,7 +1547,7 @@
         <v>1.68</v>
       </c>
       <c r="R4">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="S4">
         <v>2.74</v>
@@ -1613,7 +1592,7 @@
         <v>11.5</v>
       </c>
       <c r="AG4">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH4">
         <v>18.5</v>
@@ -1622,13 +1601,13 @@
         <v>60</v>
       </c>
       <c r="AJ4">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AK4">
         <v>15.5</v>
       </c>
       <c r="AL4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AM4">
         <v>85</v>
@@ -1649,13 +1628,13 @@
         <v>38</v>
       </c>
       <c r="AS4">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AT4">
         <v>10</v>
       </c>
       <c r="AU4">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV4">
         <v>18.5</v>
@@ -1688,7 +1667,7 @@
         <v>60</v>
       </c>
       <c r="BF4">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG4">
         <v>44</v>
@@ -1754,7 +1733,7 @@
         <v>6.2</v>
       </c>
       <c r="CB4" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1768,22 +1747,22 @@
         <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E5" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F5">
         <v>3</v>
       </c>
       <c r="G5">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H5">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="I5">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="J5">
         <v>3.1</v>
@@ -1798,16 +1777,16 @@
         <v>1.11</v>
       </c>
       <c r="N5">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="O5">
         <v>1.49</v>
       </c>
       <c r="P5">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q5">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="R5">
         <v>1.23</v>
@@ -1816,7 +1795,7 @@
         <v>5</v>
       </c>
       <c r="T5">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U5">
         <v>1.9</v>
@@ -1825,7 +1804,7 @@
         <v>1.54</v>
       </c>
       <c r="W5">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X5">
         <v>9.800000000000001</v>
@@ -1843,10 +1822,10 @@
         <v>9.4</v>
       </c>
       <c r="AC5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AD5">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AE5">
         <v>44</v>
@@ -1885,13 +1864,13 @@
         <v>9</v>
       </c>
       <c r="AQ5">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AR5">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS5">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AT5">
         <v>8.4</v>
@@ -1903,7 +1882,7 @@
         <v>11.5</v>
       </c>
       <c r="AW5">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AX5">
         <v>16.5</v>
@@ -1915,43 +1894,43 @@
         <v>18</v>
       </c>
       <c r="BA5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB5">
+        <v>10</v>
+      </c>
+      <c r="BC5">
+        <v>9.6</v>
+      </c>
+      <c r="BD5">
+        <v>10</v>
+      </c>
+      <c r="BE5">
+        <v>11</v>
+      </c>
+      <c r="BF5">
+        <v>10</v>
+      </c>
+      <c r="BG5">
         <v>9.4</v>
-      </c>
-      <c r="BC5">
-        <v>9</v>
-      </c>
-      <c r="BD5">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BE5">
-        <v>10.5</v>
-      </c>
-      <c r="BF5">
-        <v>9.4</v>
-      </c>
-      <c r="BG5">
-        <v>8.800000000000001</v>
       </c>
       <c r="BH5">
         <v>2.84</v>
       </c>
       <c r="BI5">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BJ5">
         <v>11</v>
       </c>
       <c r="BK5">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>14.5</v>
+        <v>2.4</v>
       </c>
       <c r="BN5">
         <v>6</v>
@@ -1963,16 +1942,16 @@
         <v>28</v>
       </c>
       <c r="BQ5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT5">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BU5">
         <v>4.4</v>
@@ -1981,22 +1960,22 @@
         <v>24</v>
       </c>
       <c r="BW5">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX5">
         <v>44</v>
       </c>
       <c r="BY5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ5">
         <v>44</v>
       </c>
       <c r="CA5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="CB5" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2010,10 +1989,10 @@
         <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E6" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F6">
         <v>4.7</v>
@@ -2034,7 +2013,7 @@
         <v>3.75</v>
       </c>
       <c r="L6">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="M6">
         <v>1.08</v>
@@ -2046,10 +2025,10 @@
         <v>1.39</v>
       </c>
       <c r="P6">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q6">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R6">
         <v>1.3</v>
@@ -2064,7 +2043,7 @@
         <v>1.94</v>
       </c>
       <c r="V6">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="W6">
         <v>1.25</v>
@@ -2094,10 +2073,10 @@
         <v>23</v>
       </c>
       <c r="AF6">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AG6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH6">
         <v>24</v>
@@ -2187,7 +2166,7 @@
         <v>10.5</v>
       </c>
       <c r="BK6">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL6">
         <v>1000</v>
@@ -2217,7 +2196,7 @@
         <v>4.5</v>
       </c>
       <c r="BU6">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BV6">
         <v>14</v>
@@ -2232,13 +2211,13 @@
         <v>10</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA6">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB6" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2252,16 +2231,16 @@
         <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E7" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F7">
         <v>1.91</v>
       </c>
       <c r="G7">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="H7">
         <v>4.8</v>
@@ -2273,7 +2252,7 @@
         <v>3.4</v>
       </c>
       <c r="K7">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L7">
         <v>1.5</v>
@@ -2306,7 +2285,7 @@
         <v>1.82</v>
       </c>
       <c r="V7">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W7">
         <v>2.02</v>
@@ -2318,7 +2297,7 @@
         <v>14</v>
       </c>
       <c r="Z7">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA7">
         <v>160</v>
@@ -2333,7 +2312,7 @@
         <v>21</v>
       </c>
       <c r="AE7">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AF7">
         <v>11</v>
@@ -2342,7 +2321,7 @@
         <v>12.5</v>
       </c>
       <c r="AH7">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI7">
         <v>110</v>
@@ -2372,10 +2351,10 @@
         <v>12</v>
       </c>
       <c r="AR7">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AS7">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT7">
         <v>6.4</v>
@@ -2387,7 +2366,7 @@
         <v>18</v>
       </c>
       <c r="AW7">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AX7">
         <v>9.199999999999999</v>
@@ -2399,25 +2378,25 @@
         <v>20</v>
       </c>
       <c r="BA7">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB7">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BC7">
         <v>18</v>
       </c>
       <c r="BD7">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE7">
         <v>8.6</v>
-      </c>
-      <c r="BE7">
-        <v>8.800000000000001</v>
       </c>
       <c r="BF7">
         <v>16</v>
       </c>
       <c r="BG7">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH7">
         <v>2.98</v>
@@ -2480,7 +2459,7 @@
         <v>10.5</v>
       </c>
       <c r="CB7" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2494,10 +2473,10 @@
         <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E8" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F8">
         <v>3.4</v>
@@ -2506,13 +2485,13 @@
         <v>3.55</v>
       </c>
       <c r="H8">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="I8">
         <v>2.22</v>
       </c>
       <c r="J8">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="K8">
         <v>4</v>
@@ -2530,7 +2509,7 @@
         <v>1.2</v>
       </c>
       <c r="P8">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="Q8">
         <v>1.6</v>
@@ -2581,7 +2560,7 @@
         <v>32</v>
       </c>
       <c r="AG8">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH8">
         <v>14.5</v>
@@ -2590,7 +2569,7 @@
         <v>27</v>
       </c>
       <c r="AJ8">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AK8">
         <v>34</v>
@@ -2602,7 +2581,7 @@
         <v>55</v>
       </c>
       <c r="AN8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO8">
         <v>10.5</v>
@@ -2617,7 +2596,7 @@
         <v>15</v>
       </c>
       <c r="AS8">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AT8">
         <v>18</v>
@@ -2722,7 +2701,7 @@
         <v>7.8</v>
       </c>
       <c r="CB8" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2736,10 +2715,10 @@
         <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E9" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F9">
         <v>1.13</v>
@@ -2748,16 +2727,16 @@
         <v>1.16</v>
       </c>
       <c r="H9">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="I9">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J9">
         <v>10.5</v>
       </c>
       <c r="K9">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="L9">
         <v>1.14</v>
@@ -2766,28 +2745,28 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="O9">
         <v>1.08</v>
       </c>
       <c r="P9">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q9">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="R9">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="S9">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="T9">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U9">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="V9">
         <v>1.03</v>
@@ -2799,10 +2778,10 @@
         <v>75</v>
       </c>
       <c r="Y9">
-        <v>950</v>
+        <v>940</v>
       </c>
       <c r="Z9">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AA9">
         <v>1000</v>
@@ -2814,94 +2793,94 @@
         <v>29</v>
       </c>
       <c r="AD9">
-        <v>950</v>
+        <v>940</v>
       </c>
       <c r="AE9">
         <v>380</v>
       </c>
       <c r="AF9">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG9">
         <v>15</v>
       </c>
       <c r="AH9">
-        <v>950</v>
+        <v>170</v>
       </c>
       <c r="AI9">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK9">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL9">
         <v>38</v>
       </c>
       <c r="AM9">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AO9">
         <v>360</v>
       </c>
       <c r="AP9">
-        <v>11.5</v>
+        <v>34</v>
       </c>
       <c r="AQ9">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="AR9">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="AS9">
-        <v>13.5</v>
+        <v>60</v>
       </c>
       <c r="AT9">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AU9">
-        <v>9.4</v>
+        <v>19</v>
       </c>
       <c r="AV9">
-        <v>11.5</v>
+        <v>32</v>
       </c>
       <c r="AW9">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="AX9">
         <v>9.6</v>
       </c>
       <c r="AY9">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ9">
-        <v>10.5</v>
+        <v>26</v>
       </c>
       <c r="BA9">
-        <v>12.5</v>
+        <v>46</v>
       </c>
       <c r="BB9">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC9">
         <v>12</v>
       </c>
       <c r="BD9">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="BE9">
-        <v>12.5</v>
+        <v>46</v>
       </c>
       <c r="BF9">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BG9">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="BH9">
         <v>7</v>
@@ -2925,13 +2904,13 @@
         <v>4.4</v>
       </c>
       <c r="BO9">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BP9">
         <v>6.2</v>
       </c>
       <c r="BQ9">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BR9">
         <v>19</v>
@@ -2940,7 +2919,7 @@
         <v>6.6</v>
       </c>
       <c r="BT9">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BU9">
         <v>7</v>
@@ -2949,7 +2928,7 @@
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BX9">
         <v>1000</v>
@@ -2958,13 +2937,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BZ9">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="CA9">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="CB9" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2978,19 +2957,19 @@
         <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E10" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="F10">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G10">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H10">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I10">
         <v>4.4</v>
@@ -3002,7 +2981,7 @@
         <v>3.25</v>
       </c>
       <c r="L10">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M10">
         <v>1.12</v>
@@ -3146,72 +3125,72 @@
         <v>7.4</v>
       </c>
       <c r="BH10">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="BI10">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="BJ10">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BK10">
-        <v>2.9</v>
+        <v>7.2</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>3.55</v>
+        <v>10.5</v>
       </c>
       <c r="BN10">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="BO10">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="BP10">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="BQ10">
-        <v>3.15</v>
+        <v>7.2</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS10">
-        <v>3.35</v>
+        <v>9</v>
       </c>
       <c r="BT10">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="BU10">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW10">
-        <v>3.35</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>3.4</v>
+        <v>9.6</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="CA10">
-        <v>3.35</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB10" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B11" t="s">
         <v>88</v>
@@ -3220,235 +3199,235 @@
         <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E11" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F11">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="G11">
-        <v>1000</v>
+        <v>1.29</v>
       </c>
       <c r="H11">
-        <v>1.15</v>
+        <v>15.5</v>
       </c>
       <c r="I11">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="J11">
-        <v>1.2</v>
+        <v>6.2</v>
       </c>
       <c r="K11">
-        <v>50</v>
+        <v>7.4</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M11">
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>1.09</v>
+        <v>4.7</v>
       </c>
       <c r="O11">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="P11">
-        <v>1.08</v>
+        <v>2.32</v>
       </c>
       <c r="Q11">
-        <v>1.02</v>
+        <v>1.62</v>
       </c>
       <c r="R11">
-        <v>1.08</v>
+        <v>1.51</v>
       </c>
       <c r="S11">
+        <v>2.58</v>
+      </c>
+      <c r="T11">
+        <v>2.28</v>
+      </c>
+      <c r="U11">
+        <v>1.63</v>
+      </c>
+      <c r="V11">
         <v>1.05</v>
       </c>
-      <c r="T11">
-        <v>1.4</v>
-      </c>
-      <c r="U11">
-        <v>1.1</v>
-      </c>
-      <c r="V11">
-        <v>1.01</v>
-      </c>
       <c r="W11">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="X11">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y11">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="Z11">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AA11">
         <v>1000</v>
       </c>
       <c r="AB11">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC11">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AD11">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AE11">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="AF11">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG11">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH11">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AI11">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AJ11">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AK11">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL11">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="AO11">
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AQ11">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="AR11">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AS11">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AT11">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU11">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AV11">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AW11">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AX11">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AY11">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ11">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BA11">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BB11">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BC11">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BD11">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BE11">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BF11">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG11">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI11">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BJ11">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK11">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN11">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="BO11">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BP11">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BQ11">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BR11">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS11">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BU11">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="CA11">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="CB11" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3459,485 +3438,485 @@
         <v>88</v>
       </c>
       <c r="C12" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" t="s">
+        <v>109</v>
+      </c>
+      <c r="E12" t="s">
+        <v>129</v>
+      </c>
+      <c r="F12">
+        <v>4.5</v>
+      </c>
+      <c r="G12">
+        <v>4.8</v>
+      </c>
+      <c r="H12">
+        <v>2</v>
+      </c>
+      <c r="I12">
+        <v>2.06</v>
+      </c>
+      <c r="J12">
+        <v>3.45</v>
+      </c>
+      <c r="K12">
+        <v>3.55</v>
+      </c>
+      <c r="L12">
+        <v>1.46</v>
+      </c>
+      <c r="M12">
+        <v>1.1</v>
+      </c>
+      <c r="N12">
+        <v>3.1</v>
+      </c>
+      <c r="O12">
+        <v>1.41</v>
+      </c>
+      <c r="P12">
+        <v>1.73</v>
+      </c>
+      <c r="Q12">
+        <v>2.26</v>
+      </c>
+      <c r="R12">
+        <v>1.27</v>
+      </c>
+      <c r="S12">
+        <v>4.3</v>
+      </c>
+      <c r="T12">
+        <v>2.02</v>
+      </c>
+      <c r="U12">
+        <v>1.89</v>
+      </c>
+      <c r="V12">
+        <v>1.95</v>
+      </c>
+      <c r="W12">
+        <v>1.27</v>
+      </c>
+      <c r="X12">
+        <v>11</v>
+      </c>
+      <c r="Y12">
+        <v>7.8</v>
+      </c>
+      <c r="Z12">
+        <v>11</v>
+      </c>
+      <c r="AA12">
+        <v>25</v>
+      </c>
+      <c r="AB12">
+        <v>14.5</v>
+      </c>
+      <c r="AC12">
+        <v>7.6</v>
+      </c>
+      <c r="AD12">
+        <v>11</v>
+      </c>
+      <c r="AE12">
+        <v>25</v>
+      </c>
+      <c r="AF12">
+        <v>32</v>
+      </c>
+      <c r="AG12">
+        <v>19</v>
+      </c>
+      <c r="AH12">
+        <v>23</v>
+      </c>
+      <c r="AI12">
+        <v>48</v>
+      </c>
+      <c r="AJ12">
+        <v>120</v>
+      </c>
+      <c r="AK12">
+        <v>70</v>
+      </c>
+      <c r="AL12">
+        <v>1000</v>
+      </c>
+      <c r="AM12">
+        <v>1000</v>
+      </c>
+      <c r="AN12">
         <v>95</v>
       </c>
-      <c r="D12" t="s">
-        <v>110</v>
-      </c>
-      <c r="E12" t="s">
-        <v>133</v>
-      </c>
-      <c r="F12">
-        <v>1.04</v>
-      </c>
-      <c r="G12">
-        <v>1000</v>
-      </c>
-      <c r="H12">
-        <v>1.16</v>
-      </c>
-      <c r="I12">
-        <v>1000</v>
-      </c>
-      <c r="J12">
-        <v>1.03</v>
-      </c>
-      <c r="K12">
-        <v>50</v>
-      </c>
-      <c r="L12">
-        <v>1.01</v>
-      </c>
-      <c r="M12">
-        <v>1.01</v>
-      </c>
-      <c r="N12">
-        <v>1.05</v>
-      </c>
-      <c r="O12">
-        <v>1.01</v>
-      </c>
-      <c r="P12">
-        <v>1.07</v>
-      </c>
-      <c r="Q12">
-        <v>1.02</v>
-      </c>
-      <c r="R12">
-        <v>1.06</v>
-      </c>
-      <c r="S12">
-        <v>1.05</v>
-      </c>
-      <c r="T12">
-        <v>1.1</v>
-      </c>
-      <c r="U12">
-        <v>1.5</v>
-      </c>
-      <c r="V12">
-        <v>1.02</v>
-      </c>
-      <c r="W12">
-        <v>1.13</v>
-      </c>
-      <c r="X12">
-        <v>1000</v>
-      </c>
-      <c r="Y12">
-        <v>1000</v>
-      </c>
-      <c r="Z12">
-        <v>1000</v>
-      </c>
-      <c r="AA12">
-        <v>1000</v>
-      </c>
-      <c r="AB12">
-        <v>1000</v>
-      </c>
-      <c r="AC12">
-        <v>1000</v>
-      </c>
-      <c r="AD12">
-        <v>1000</v>
-      </c>
-      <c r="AE12">
-        <v>1000</v>
-      </c>
-      <c r="AF12">
-        <v>1000</v>
-      </c>
-      <c r="AG12">
-        <v>1000</v>
-      </c>
-      <c r="AH12">
-        <v>1000</v>
-      </c>
-      <c r="AI12">
-        <v>1000</v>
-      </c>
-      <c r="AJ12">
-        <v>1000</v>
-      </c>
-      <c r="AK12">
-        <v>1000</v>
-      </c>
-      <c r="AL12">
-        <v>1000</v>
-      </c>
-      <c r="AM12">
-        <v>1000</v>
-      </c>
-      <c r="AN12">
-        <v>1000</v>
-      </c>
       <c r="AO12">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AP12">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ12">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AR12">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS12">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AT12">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AU12">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV12">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AW12">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AX12">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="AY12">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AZ12">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BA12">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BB12">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BC12">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BD12">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BE12">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BF12">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BG12">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BH12">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI12">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="BJ12">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK12">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.04</v>
+        <v>14</v>
       </c>
       <c r="BN12">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO12">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BP12">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BQ12">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BR12">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BS12">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BT12">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BU12">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BV12">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BW12">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BX12">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY12">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BZ12">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA12">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="CB12" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B13" t="s">
         <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E13" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F13">
-        <v>1.08</v>
+        <v>2.22</v>
       </c>
       <c r="G13">
-        <v>1000</v>
+        <v>2.32</v>
       </c>
       <c r="H13">
-        <v>1.05</v>
+        <v>3.65</v>
       </c>
       <c r="I13">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="J13">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="K13">
-        <v>50</v>
+        <v>3.45</v>
       </c>
       <c r="L13">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M13">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N13">
-        <v>1.08</v>
+        <v>3.05</v>
       </c>
       <c r="O13">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="P13">
-        <v>1.08</v>
+        <v>1.76</v>
       </c>
       <c r="Q13">
-        <v>1.02</v>
+        <v>2.2</v>
       </c>
       <c r="R13">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="S13">
-        <v>1.05</v>
+        <v>4.3</v>
       </c>
       <c r="T13">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="U13">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="V13">
-        <v>1.02</v>
+        <v>1.34</v>
       </c>
       <c r="W13">
-        <v>1.03</v>
+        <v>1.76</v>
       </c>
       <c r="X13">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y13">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z13">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA13">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB13">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC13">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD13">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE13">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF13">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG13">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH13">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI13">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ13">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK13">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL13">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM13">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN13">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO13">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP13">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ13">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR13">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AS13">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AT13">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AU13">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV13">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW13">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AX13">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AY13">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ13">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BA13">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BB13">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BC13">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD13">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BE13">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BF13">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BG13">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BH13">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI13">
-        <v>1.04</v>
+        <v>2.54</v>
       </c>
       <c r="BJ13">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK13">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.04</v>
+        <v>13.5</v>
       </c>
       <c r="BN13">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO13">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BP13">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ13">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU13">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BZ13">
         <v>1000</v>
       </c>
       <c r="CA13">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="CB13" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B14" t="s">
         <v>88</v>
@@ -3946,103 +3925,103 @@
         <v>96</v>
       </c>
       <c r="D14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E14" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F14">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="G14">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="H14">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="I14">
-        <v>22</v>
+        <v>12.5</v>
       </c>
       <c r="J14">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="K14">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="L14">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="M14">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N14">
-        <v>4.7</v>
+        <v>3.55</v>
       </c>
       <c r="O14">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="P14">
-        <v>2.26</v>
+        <v>1.9</v>
       </c>
       <c r="Q14">
-        <v>1.6</v>
+        <v>1.99</v>
       </c>
       <c r="R14">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="S14">
-        <v>2.54</v>
+        <v>3.6</v>
       </c>
       <c r="T14">
         <v>2.26</v>
       </c>
       <c r="U14">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="V14">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="W14">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="X14">
-        <v>28</v>
+        <v>17.5</v>
       </c>
       <c r="Y14">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="Z14">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="AA14">
-        <v>1000</v>
+        <v>560</v>
       </c>
       <c r="AB14">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="AC14">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AD14">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="AE14">
-        <v>420</v>
+        <v>260</v>
       </c>
       <c r="AF14">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AG14">
+        <v>12.5</v>
+      </c>
+      <c r="AH14">
+        <v>40</v>
+      </c>
+      <c r="AI14">
+        <v>220</v>
+      </c>
+      <c r="AJ14">
         <v>14</v>
-      </c>
-      <c r="AH14">
-        <v>50</v>
-      </c>
-      <c r="AI14">
-        <v>300</v>
-      </c>
-      <c r="AJ14">
-        <v>9.6</v>
       </c>
       <c r="AK14">
         <v>18.5</v>
@@ -4051,135 +4030,135 @@
         <v>60</v>
       </c>
       <c r="AM14">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="AN14">
-        <v>4.8</v>
+        <v>10</v>
       </c>
       <c r="AO14">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="AP14">
-        <v>19.5</v>
+        <v>12</v>
       </c>
       <c r="AQ14">
-        <v>36</v>
+        <v>4.2</v>
       </c>
       <c r="AR14">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="AS14">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="AT14">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="AU14">
-        <v>12.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV14">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="AW14">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="AX14">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY14">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ14">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="BA14">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="BB14">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BC14">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD14">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="BE14">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="BF14">
-        <v>3.9</v>
+        <v>7</v>
       </c>
       <c r="BG14">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="BH14">
-        <v>4.4</v>
+        <v>3.55</v>
       </c>
       <c r="BI14">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="BJ14">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BK14">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BN14">
         <v>3.75</v>
       </c>
       <c r="BO14">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="BP14">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ14">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BR14">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BS14">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BT14">
-        <v>18.5</v>
+        <v>14</v>
       </c>
       <c r="BU14">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BV14">
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ14">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="CA14">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="CB14" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B15" t="s">
         <v>88</v>
@@ -4188,235 +4167,235 @@
         <v>97</v>
       </c>
       <c r="D15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E15" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F15">
+        <v>1.8</v>
+      </c>
+      <c r="G15">
+        <v>1.91</v>
+      </c>
+      <c r="H15">
+        <v>4.2</v>
+      </c>
+      <c r="I15">
+        <v>4.9</v>
+      </c>
+      <c r="J15">
+        <v>3.95</v>
+      </c>
+      <c r="K15">
         <v>4.5</v>
       </c>
-      <c r="G15">
-        <v>4.8</v>
-      </c>
-      <c r="H15">
-        <v>2</v>
-      </c>
-      <c r="I15">
-        <v>2.06</v>
-      </c>
-      <c r="J15">
-        <v>3.45</v>
-      </c>
-      <c r="K15">
-        <v>3.55</v>
-      </c>
       <c r="L15">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="M15">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="N15">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="O15">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="P15">
-        <v>1.73</v>
+        <v>2.16</v>
       </c>
       <c r="Q15">
-        <v>2.26</v>
+        <v>1.74</v>
       </c>
       <c r="R15">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="S15">
-        <v>4.3</v>
+        <v>2.88</v>
       </c>
       <c r="T15">
-        <v>2.02</v>
+        <v>1.72</v>
       </c>
       <c r="U15">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="V15">
-        <v>1.96</v>
+        <v>1.26</v>
       </c>
       <c r="W15">
-        <v>1.27</v>
+        <v>2.1</v>
       </c>
       <c r="X15">
+        <v>22</v>
+      </c>
+      <c r="Y15">
+        <v>22</v>
+      </c>
+      <c r="Z15">
+        <v>42</v>
+      </c>
+      <c r="AA15">
+        <v>110</v>
+      </c>
+      <c r="AB15">
+        <v>11.5</v>
+      </c>
+      <c r="AC15">
         <v>11</v>
       </c>
-      <c r="Y15">
+      <c r="AD15">
+        <v>21</v>
+      </c>
+      <c r="AE15">
+        <v>65</v>
+      </c>
+      <c r="AF15">
+        <v>14</v>
+      </c>
+      <c r="AG15">
+        <v>11.5</v>
+      </c>
+      <c r="AH15">
+        <v>21</v>
+      </c>
+      <c r="AI15">
+        <v>65</v>
+      </c>
+      <c r="AJ15">
+        <v>23</v>
+      </c>
+      <c r="AK15">
+        <v>21</v>
+      </c>
+      <c r="AL15">
+        <v>36</v>
+      </c>
+      <c r="AM15">
+        <v>100</v>
+      </c>
+      <c r="AN15">
+        <v>12</v>
+      </c>
+      <c r="AO15">
+        <v>60</v>
+      </c>
+      <c r="AP15">
+        <v>14</v>
+      </c>
+      <c r="AQ15">
+        <v>14</v>
+      </c>
+      <c r="AR15">
+        <v>1.03</v>
+      </c>
+      <c r="AS15">
+        <v>1.03</v>
+      </c>
+      <c r="AT15">
         <v>7.8</v>
       </c>
-      <c r="Z15">
-        <v>11</v>
-      </c>
-      <c r="AA15">
+      <c r="AU15">
+        <v>7.4</v>
+      </c>
+      <c r="AV15">
+        <v>14</v>
+      </c>
+      <c r="AW15">
+        <v>1.03</v>
+      </c>
+      <c r="AX15">
+        <v>9.4</v>
+      </c>
+      <c r="AY15">
+        <v>7.8</v>
+      </c>
+      <c r="AZ15">
+        <v>14</v>
+      </c>
+      <c r="BA15">
+        <v>1.03</v>
+      </c>
+      <c r="BB15">
+        <v>15.5</v>
+      </c>
+      <c r="BC15">
+        <v>14</v>
+      </c>
+      <c r="BD15">
+        <v>1.03</v>
+      </c>
+      <c r="BE15">
+        <v>1.03</v>
+      </c>
+      <c r="BF15">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG15">
+        <v>38</v>
+      </c>
+      <c r="BH15">
+        <v>3.95</v>
+      </c>
+      <c r="BI15">
+        <v>3.1</v>
+      </c>
+      <c r="BJ15">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK15">
+        <v>7.2</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>1.01</v>
+      </c>
+      <c r="BN15">
+        <v>4.9</v>
+      </c>
+      <c r="BO15">
+        <v>3.8</v>
+      </c>
+      <c r="BP15">
+        <v>13</v>
+      </c>
+      <c r="BQ15">
+        <v>9.6</v>
+      </c>
+      <c r="BR15">
+        <v>26</v>
+      </c>
+      <c r="BS15">
+        <v>18.5</v>
+      </c>
+      <c r="BT15">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU15">
+        <v>6.2</v>
+      </c>
+      <c r="BV15">
+        <v>1000</v>
+      </c>
+      <c r="BW15">
         <v>25</v>
       </c>
-      <c r="AB15">
+      <c r="BX15">
+        <v>1000</v>
+      </c>
+      <c r="BY15">
+        <v>30</v>
+      </c>
+      <c r="BZ15">
+        <v>20</v>
+      </c>
+      <c r="CA15">
         <v>14.5</v>
       </c>
-      <c r="AC15">
-        <v>7.6</v>
-      </c>
-      <c r="AD15">
-        <v>11</v>
-      </c>
-      <c r="AE15">
-        <v>24</v>
-      </c>
-      <c r="AF15">
-        <v>32</v>
-      </c>
-      <c r="AG15">
-        <v>19</v>
-      </c>
-      <c r="AH15">
-        <v>23</v>
-      </c>
-      <c r="AI15">
-        <v>48</v>
-      </c>
-      <c r="AJ15">
-        <v>120</v>
-      </c>
-      <c r="AK15">
-        <v>70</v>
-      </c>
-      <c r="AL15">
-        <v>1000</v>
-      </c>
-      <c r="AM15">
-        <v>1000</v>
-      </c>
-      <c r="AN15">
-        <v>95</v>
-      </c>
-      <c r="AO15">
-        <v>20</v>
-      </c>
-      <c r="AP15">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ15">
-        <v>7.2</v>
-      </c>
-      <c r="AR15">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS15">
-        <v>18</v>
-      </c>
-      <c r="AT15">
-        <v>12.5</v>
-      </c>
-      <c r="AU15">
-        <v>7</v>
-      </c>
-      <c r="AV15">
-        <v>9</v>
-      </c>
-      <c r="AW15">
-        <v>21</v>
-      </c>
-      <c r="AX15">
-        <v>28</v>
-      </c>
-      <c r="AY15">
-        <v>14.5</v>
-      </c>
-      <c r="AZ15">
-        <v>19.5</v>
-      </c>
-      <c r="BA15">
-        <v>40</v>
-      </c>
-      <c r="BB15">
-        <v>38</v>
-      </c>
-      <c r="BC15">
-        <v>30</v>
-      </c>
-      <c r="BD15">
-        <v>36</v>
-      </c>
-      <c r="BE15">
-        <v>42</v>
-      </c>
-      <c r="BF15">
-        <v>34</v>
-      </c>
-      <c r="BG15">
-        <v>14.5</v>
-      </c>
-      <c r="BH15">
-        <v>1000</v>
-      </c>
-      <c r="BI15">
-        <v>1.86</v>
-      </c>
-      <c r="BJ15">
-        <v>14.5</v>
-      </c>
-      <c r="BK15">
-        <v>1.65</v>
-      </c>
-      <c r="BL15">
-        <v>1000</v>
-      </c>
-      <c r="BM15">
-        <v>1.86</v>
-      </c>
-      <c r="BN15">
-        <v>10</v>
-      </c>
-      <c r="BO15">
-        <v>5.1</v>
-      </c>
-      <c r="BP15">
-        <v>1000</v>
-      </c>
-      <c r="BQ15">
-        <v>1.8</v>
-      </c>
-      <c r="BR15">
-        <v>1000</v>
-      </c>
-      <c r="BS15">
-        <v>1.81</v>
-      </c>
-      <c r="BT15">
-        <v>6</v>
-      </c>
-      <c r="BU15">
-        <v>3.2</v>
-      </c>
-      <c r="BV15">
-        <v>20</v>
-      </c>
-      <c r="BW15">
-        <v>1.7</v>
-      </c>
-      <c r="BX15">
-        <v>46</v>
-      </c>
-      <c r="BY15">
-        <v>1.79</v>
-      </c>
-      <c r="BZ15">
-        <v>44</v>
-      </c>
-      <c r="CA15">
-        <v>1.78</v>
-      </c>
       <c r="CB15" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4427,49 +4406,49 @@
         <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D16" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E16" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F16">
         <v>2.22</v>
       </c>
       <c r="G16">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H16">
         <v>3.65</v>
       </c>
       <c r="I16">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J16">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K16">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="L16">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M16">
         <v>1.09</v>
       </c>
       <c r="N16">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O16">
         <v>1.42</v>
       </c>
       <c r="P16">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="Q16">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="R16">
         <v>1.27</v>
@@ -4487,73 +4466,73 @@
         <v>1.34</v>
       </c>
       <c r="W16">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="X16">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z16">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA16">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB16">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC16">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AD16">
-        <v>950</v>
+        <v>17.5</v>
       </c>
       <c r="AE16">
+        <v>60</v>
+      </c>
+      <c r="AF16">
+        <v>16</v>
+      </c>
+      <c r="AG16">
+        <v>12.5</v>
+      </c>
+      <c r="AH16">
+        <v>23</v>
+      </c>
+      <c r="AI16">
+        <v>75</v>
+      </c>
+      <c r="AJ16">
+        <v>36</v>
+      </c>
+      <c r="AK16">
+        <v>32</v>
+      </c>
+      <c r="AL16">
         <v>55</v>
-      </c>
-      <c r="AF16">
-        <v>14</v>
-      </c>
-      <c r="AG16">
-        <v>11.5</v>
-      </c>
-      <c r="AH16">
-        <v>950</v>
-      </c>
-      <c r="AI16">
-        <v>65</v>
-      </c>
-      <c r="AJ16">
-        <v>32</v>
-      </c>
-      <c r="AK16">
-        <v>28</v>
-      </c>
-      <c r="AL16">
-        <v>46</v>
       </c>
       <c r="AM16">
         <v>150</v>
       </c>
       <c r="AN16">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AO16">
         <v>65</v>
       </c>
       <c r="AP16">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ16">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR16">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="AS16">
-        <v>11.5</v>
+        <v>5.5</v>
       </c>
       <c r="AT16">
         <v>7.4</v>
@@ -4562,10 +4541,10 @@
         <v>6.6</v>
       </c>
       <c r="AV16">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW16">
-        <v>11</v>
+        <v>5.4</v>
       </c>
       <c r="AX16">
         <v>12</v>
@@ -4574,338 +4553,338 @@
         <v>10</v>
       </c>
       <c r="AZ16">
-        <v>8</v>
+        <v>4.7</v>
       </c>
       <c r="BA16">
-        <v>11</v>
+        <v>5.5</v>
       </c>
       <c r="BB16">
-        <v>9.6</v>
+        <v>5.1</v>
       </c>
       <c r="BC16">
-        <v>9.199999999999999</v>
+        <v>21</v>
       </c>
       <c r="BD16">
-        <v>40</v>
+        <v>5.3</v>
       </c>
       <c r="BE16">
-        <v>12.5</v>
+        <v>5.7</v>
       </c>
       <c r="BF16">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BG16">
-        <v>11</v>
+        <v>5.4</v>
       </c>
       <c r="BH16">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BI16">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BJ16">
         <v>10.5</v>
       </c>
       <c r="BK16">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>13.5</v>
+        <v>21</v>
       </c>
       <c r="BN16">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BO16">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP16">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BR16">
         <v>1000</v>
       </c>
       <c r="BS16">
-        <v>10.5</v>
+        <v>26</v>
       </c>
       <c r="BT16">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU16">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="BZ16">
         <v>1000</v>
       </c>
       <c r="CA16">
-        <v>10.5</v>
+        <v>26</v>
       </c>
       <c r="CB16" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B17" t="s">
         <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D17" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E17" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F17">
-        <v>1.39</v>
+        <v>2.02</v>
       </c>
       <c r="G17">
-        <v>1.45</v>
+        <v>2.08</v>
       </c>
       <c r="H17">
+        <v>3.8</v>
+      </c>
+      <c r="I17">
+        <v>3.95</v>
+      </c>
+      <c r="J17">
+        <v>3.8</v>
+      </c>
+      <c r="K17">
+        <v>4</v>
+      </c>
+      <c r="L17">
+        <v>1.36</v>
+      </c>
+      <c r="M17">
+        <v>1.05</v>
+      </c>
+      <c r="N17">
+        <v>4.4</v>
+      </c>
+      <c r="O17">
+        <v>1.27</v>
+      </c>
+      <c r="P17">
+        <v>2.16</v>
+      </c>
+      <c r="Q17">
+        <v>1.81</v>
+      </c>
+      <c r="R17">
+        <v>1.46</v>
+      </c>
+      <c r="S17">
+        <v>3.05</v>
+      </c>
+      <c r="T17">
+        <v>1.71</v>
+      </c>
+      <c r="U17">
+        <v>2.22</v>
+      </c>
+      <c r="V17">
+        <v>1.34</v>
+      </c>
+      <c r="W17">
+        <v>1.92</v>
+      </c>
+      <c r="X17">
+        <v>21</v>
+      </c>
+      <c r="Y17">
+        <v>19</v>
+      </c>
+      <c r="Z17">
+        <v>36</v>
+      </c>
+      <c r="AA17">
+        <v>80</v>
+      </c>
+      <c r="AB17">
+        <v>11.5</v>
+      </c>
+      <c r="AC17">
         <v>10.5</v>
       </c>
-      <c r="I17">
+      <c r="AD17">
+        <v>19.5</v>
+      </c>
+      <c r="AE17">
+        <v>55</v>
+      </c>
+      <c r="AF17">
+        <v>16.5</v>
+      </c>
+      <c r="AG17">
+        <v>11.5</v>
+      </c>
+      <c r="AH17">
+        <v>21</v>
+      </c>
+      <c r="AI17">
+        <v>60</v>
+      </c>
+      <c r="AJ17">
+        <v>29</v>
+      </c>
+      <c r="AK17">
+        <v>22</v>
+      </c>
+      <c r="AL17">
+        <v>40</v>
+      </c>
+      <c r="AM17">
+        <v>95</v>
+      </c>
+      <c r="AN17">
+        <v>15</v>
+      </c>
+      <c r="AO17">
+        <v>46</v>
+      </c>
+      <c r="AP17">
+        <v>15.5</v>
+      </c>
+      <c r="AQ17">
+        <v>14</v>
+      </c>
+      <c r="AR17">
+        <v>4.5</v>
+      </c>
+      <c r="AS17">
+        <v>4.9</v>
+      </c>
+      <c r="AT17">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU17">
+        <v>7.8</v>
+      </c>
+      <c r="AV17">
         <v>13.5</v>
       </c>
-      <c r="J17">
-        <v>4.5</v>
-      </c>
-      <c r="K17">
-        <v>5.1</v>
-      </c>
-      <c r="L17">
-        <v>1.41</v>
-      </c>
-      <c r="M17">
-        <v>1.07</v>
-      </c>
-      <c r="N17">
-        <v>3.55</v>
-      </c>
-      <c r="O17">
-        <v>1.33</v>
-      </c>
-      <c r="P17">
-        <v>1.9</v>
-      </c>
-      <c r="Q17">
-        <v>1.96</v>
-      </c>
-      <c r="R17">
-        <v>1.33</v>
-      </c>
-      <c r="S17">
-        <v>3.6</v>
-      </c>
-      <c r="T17">
-        <v>2.26</v>
-      </c>
-      <c r="U17">
-        <v>1.66</v>
-      </c>
-      <c r="V17">
-        <v>1.09</v>
-      </c>
-      <c r="W17">
-        <v>3.2</v>
-      </c>
-      <c r="X17">
-        <v>17.5</v>
-      </c>
-      <c r="Y17">
-        <v>34</v>
-      </c>
-      <c r="Z17">
-        <v>120</v>
-      </c>
-      <c r="AA17">
-        <v>560</v>
-      </c>
-      <c r="AB17">
-        <v>8</v>
-      </c>
-      <c r="AC17">
-        <v>13</v>
-      </c>
-      <c r="AD17">
-        <v>48</v>
-      </c>
-      <c r="AE17">
-        <v>260</v>
-      </c>
-      <c r="AF17">
-        <v>9</v>
-      </c>
-      <c r="AG17">
-        <v>12.5</v>
-      </c>
-      <c r="AH17">
-        <v>40</v>
-      </c>
-      <c r="AI17">
-        <v>220</v>
-      </c>
-      <c r="AJ17">
+      <c r="AW17">
+        <v>4.7</v>
+      </c>
+      <c r="AX17">
+        <v>11.5</v>
+      </c>
+      <c r="AY17">
+        <v>9.4</v>
+      </c>
+      <c r="AZ17">
         <v>14</v>
       </c>
-      <c r="AK17">
-        <v>21</v>
-      </c>
-      <c r="AL17">
-        <v>60</v>
-      </c>
-      <c r="AM17">
-        <v>280</v>
-      </c>
-      <c r="AN17">
-        <v>10</v>
-      </c>
-      <c r="AO17">
-        <v>450</v>
-      </c>
-      <c r="AP17">
-        <v>12</v>
-      </c>
-      <c r="AQ17">
-        <v>4</v>
-      </c>
-      <c r="AR17">
+      <c r="BA17">
+        <v>4.8</v>
+      </c>
+      <c r="BB17">
         <v>4.4</v>
       </c>
-      <c r="AS17">
+      <c r="BC17">
+        <v>17</v>
+      </c>
+      <c r="BD17">
         <v>4.6</v>
       </c>
-      <c r="AT17">
-        <v>5.9</v>
-      </c>
-      <c r="AU17">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV17">
-        <v>4.2</v>
-      </c>
-      <c r="AW17">
-        <v>4.5</v>
-      </c>
-      <c r="AX17">
-        <v>6.4</v>
-      </c>
-      <c r="AY17">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ17">
-        <v>4.1</v>
-      </c>
-      <c r="BA17">
-        <v>4.5</v>
-      </c>
-      <c r="BB17">
-        <v>10</v>
-      </c>
-      <c r="BC17">
-        <v>14.5</v>
-      </c>
-      <c r="BD17">
-        <v>4.3</v>
-      </c>
       <c r="BE17">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BF17">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="BG17">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BH17">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="BI17">
         <v>3</v>
       </c>
       <c r="BJ17">
-        <v>13.5</v>
+        <v>9.6</v>
       </c>
       <c r="BK17">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
+        <v>21</v>
+      </c>
+      <c r="BN17">
+        <v>5.1</v>
+      </c>
+      <c r="BO17">
+        <v>3.8</v>
+      </c>
+      <c r="BP17">
+        <v>14.5</v>
+      </c>
+      <c r="BQ17">
         <v>10</v>
       </c>
-      <c r="BN17">
-        <v>3.75</v>
-      </c>
-      <c r="BO17">
-        <v>2.88</v>
-      </c>
-      <c r="BP17">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BQ17">
-        <v>4.9</v>
-      </c>
       <c r="BR17">
+        <v>27</v>
+      </c>
+      <c r="BS17">
+        <v>18</v>
+      </c>
+      <c r="BT17">
+        <v>7.6</v>
+      </c>
+      <c r="BU17">
+        <v>5.5</v>
+      </c>
+      <c r="BV17">
         <v>32</v>
       </c>
-      <c r="BS17">
-        <v>8</v>
-      </c>
-      <c r="BT17">
-        <v>14</v>
-      </c>
-      <c r="BU17">
-        <v>6</v>
-      </c>
-      <c r="BV17">
-        <v>1000</v>
-      </c>
       <c r="BW17">
-        <v>9.800000000000001</v>
+        <v>21</v>
       </c>
       <c r="BX17">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY17">
-        <v>9.800000000000001</v>
+        <v>26</v>
       </c>
       <c r="BZ17">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="CA17">
-        <v>6.8</v>
+        <v>17</v>
       </c>
       <c r="CB17" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B18" t="s">
         <v>88</v>
@@ -4914,235 +4893,235 @@
         <v>98</v>
       </c>
       <c r="D18" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E18" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F18">
-        <v>1.78</v>
+        <v>1.99</v>
       </c>
       <c r="G18">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="H18">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="I18">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="J18">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K18">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="L18">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M18">
         <v>1.05</v>
       </c>
       <c r="N18">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O18">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P18">
         <v>2.16</v>
       </c>
       <c r="Q18">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="R18">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S18">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="T18">
         <v>1.72</v>
       </c>
       <c r="U18">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="V18">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="W18">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="X18">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y18">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="Z18">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AA18">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AB18">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC18">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD18">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AE18">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF18">
         <v>14</v>
       </c>
       <c r="AG18">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AH18">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AI18">
         <v>65</v>
       </c>
       <c r="AJ18">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AK18">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AL18">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AM18">
         <v>100</v>
       </c>
       <c r="AN18">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AO18">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AP18">
-        <v>14</v>
+        <v>4.6</v>
       </c>
       <c r="AQ18">
         <v>14</v>
       </c>
       <c r="AR18">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AS18">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AT18">
+        <v>9</v>
+      </c>
+      <c r="AU18">
+        <v>8</v>
+      </c>
+      <c r="AV18">
+        <v>12</v>
+      </c>
+      <c r="AW18">
+        <v>5.3</v>
+      </c>
+      <c r="AX18">
+        <v>11</v>
+      </c>
+      <c r="AY18">
+        <v>9</v>
+      </c>
+      <c r="AZ18">
+        <v>12.5</v>
+      </c>
+      <c r="BA18">
+        <v>5.4</v>
+      </c>
+      <c r="BB18">
+        <v>19.5</v>
+      </c>
+      <c r="BC18">
+        <v>16.5</v>
+      </c>
+      <c r="BD18">
+        <v>5.1</v>
+      </c>
+      <c r="BE18">
+        <v>5.5</v>
+      </c>
+      <c r="BF18">
+        <v>10</v>
+      </c>
+      <c r="BG18">
+        <v>5.2</v>
+      </c>
+      <c r="BH18">
+        <v>3.85</v>
+      </c>
+      <c r="BI18">
+        <v>2.96</v>
+      </c>
+      <c r="BJ18">
+        <v>9.6</v>
+      </c>
+      <c r="BK18">
+        <v>6.8</v>
+      </c>
+      <c r="BL18">
+        <v>1000</v>
+      </c>
+      <c r="BM18">
+        <v>21</v>
+      </c>
+      <c r="BN18">
+        <v>5.1</v>
+      </c>
+      <c r="BO18">
+        <v>4.2</v>
+      </c>
+      <c r="BP18">
+        <v>14.5</v>
+      </c>
+      <c r="BQ18">
+        <v>8.4</v>
+      </c>
+      <c r="BR18">
+        <v>27</v>
+      </c>
+      <c r="BS18">
+        <v>15.5</v>
+      </c>
+      <c r="BT18">
         <v>7.8</v>
       </c>
-      <c r="AU18">
-        <v>7.4</v>
-      </c>
-      <c r="AV18">
-        <v>14</v>
-      </c>
-      <c r="AW18">
-        <v>1.03</v>
-      </c>
-      <c r="AX18">
-        <v>9.4</v>
-      </c>
-      <c r="AY18">
-        <v>7.8</v>
-      </c>
-      <c r="AZ18">
-        <v>14</v>
-      </c>
-      <c r="BA18">
-        <v>1.03</v>
-      </c>
-      <c r="BB18">
-        <v>15.5</v>
-      </c>
-      <c r="BC18">
-        <v>14</v>
-      </c>
-      <c r="BD18">
-        <v>1.03</v>
-      </c>
-      <c r="BE18">
-        <v>1.03</v>
-      </c>
-      <c r="BF18">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG18">
-        <v>38</v>
-      </c>
-      <c r="BH18">
-        <v>1000</v>
-      </c>
-      <c r="BI18">
-        <v>1.01</v>
-      </c>
-      <c r="BJ18">
-        <v>1000</v>
-      </c>
-      <c r="BK18">
-        <v>1.01</v>
-      </c>
-      <c r="BL18">
-        <v>1000</v>
-      </c>
-      <c r="BM18">
-        <v>1.01</v>
-      </c>
-      <c r="BN18">
-        <v>1000</v>
-      </c>
-      <c r="BO18">
-        <v>1.01</v>
-      </c>
-      <c r="BP18">
-        <v>1000</v>
-      </c>
-      <c r="BQ18">
-        <v>1.01</v>
-      </c>
-      <c r="BR18">
-        <v>1000</v>
-      </c>
-      <c r="BS18">
-        <v>1.01</v>
-      </c>
-      <c r="BT18">
-        <v>1000</v>
-      </c>
       <c r="BU18">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BV18">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW18">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BZ18">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA18">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="CB18" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5153,480 +5132,480 @@
         <v>88</v>
       </c>
       <c r="C19" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D19" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E19" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F19">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="G19">
+        <v>1.85</v>
+      </c>
+      <c r="H19">
         <v>4.3</v>
       </c>
-      <c r="H19">
-        <v>1.85</v>
-      </c>
       <c r="I19">
-        <v>1.89</v>
+        <v>4.5</v>
       </c>
       <c r="J19">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="K19">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L19">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="M19">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N19">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="O19">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="P19">
-        <v>3.15</v>
+        <v>2.78</v>
       </c>
       <c r="Q19">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="R19">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="S19">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="T19">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="U19">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="V19">
-        <v>2.12</v>
+        <v>1.29</v>
       </c>
       <c r="W19">
-        <v>1.3</v>
+        <v>2.16</v>
       </c>
       <c r="X19">
+        <v>32</v>
+      </c>
+      <c r="Y19">
+        <v>28</v>
+      </c>
+      <c r="Z19">
         <v>44</v>
       </c>
-      <c r="Y19">
-        <v>18.5</v>
-      </c>
-      <c r="Z19">
-        <v>18.5</v>
-      </c>
       <c r="AA19">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="AB19">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="AC19">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD19">
-        <v>13.5</v>
+        <v>21</v>
       </c>
       <c r="AE19">
-        <v>17.5</v>
+        <v>48</v>
       </c>
       <c r="AF19">
+        <v>17</v>
+      </c>
+      <c r="AG19">
+        <v>12.5</v>
+      </c>
+      <c r="AH19">
+        <v>17</v>
+      </c>
+      <c r="AI19">
         <v>48</v>
       </c>
-      <c r="AG19">
-        <v>22</v>
-      </c>
-      <c r="AH19">
-        <v>15.5</v>
-      </c>
-      <c r="AI19">
-        <v>27</v>
-      </c>
       <c r="AJ19">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="AK19">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="AL19">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="AM19">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AN19">
-        <v>27</v>
+        <v>7.2</v>
       </c>
       <c r="AO19">
-        <v>6.6</v>
+        <v>32</v>
       </c>
       <c r="AP19">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AQ19">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AR19">
-        <v>15</v>
+        <v>5.8</v>
       </c>
       <c r="AS19">
-        <v>21</v>
+        <v>6.2</v>
       </c>
       <c r="AT19">
-        <v>5.1</v>
+        <v>12.5</v>
       </c>
       <c r="AU19">
         <v>9.6</v>
       </c>
       <c r="AV19">
+        <v>15.5</v>
+      </c>
+      <c r="AW19">
+        <v>5.9</v>
+      </c>
+      <c r="AX19">
+        <v>13</v>
+      </c>
+      <c r="AY19">
         <v>9.6</v>
       </c>
-      <c r="AW19">
+      <c r="AZ19">
         <v>13.5</v>
       </c>
-      <c r="AX19">
-        <v>5.3</v>
-      </c>
-      <c r="AY19">
-        <v>15</v>
-      </c>
-      <c r="AZ19">
-        <v>12</v>
-      </c>
       <c r="BA19">
-        <v>19</v>
+        <v>5.9</v>
       </c>
       <c r="BB19">
+        <v>18</v>
+      </c>
+      <c r="BC19">
+        <v>14.5</v>
+      </c>
+      <c r="BD19">
+        <v>21</v>
+      </c>
+      <c r="BE19">
+        <v>6</v>
+      </c>
+      <c r="BF19">
+        <v>6.4</v>
+      </c>
+      <c r="BG19">
         <v>5.6</v>
       </c>
-      <c r="BC19">
-        <v>5.2</v>
-      </c>
-      <c r="BD19">
-        <v>5.3</v>
-      </c>
-      <c r="BE19">
-        <v>5.4</v>
-      </c>
-      <c r="BF19">
-        <v>16</v>
-      </c>
-      <c r="BG19">
-        <v>6</v>
-      </c>
       <c r="BH19">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BI19">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="BJ19">
         <v>8.800000000000001</v>
       </c>
       <c r="BK19">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BL19">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BM19">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="BN19">
+        <v>5.1</v>
+      </c>
+      <c r="BO19">
+        <v>4.5</v>
+      </c>
+      <c r="BP19">
+        <v>11.5</v>
+      </c>
+      <c r="BQ19">
+        <v>7.2</v>
+      </c>
+      <c r="BR19">
+        <v>19.5</v>
+      </c>
+      <c r="BS19">
+        <v>12.5</v>
+      </c>
+      <c r="BT19">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU19">
+        <v>5.4</v>
+      </c>
+      <c r="BV19">
+        <v>29</v>
+      </c>
+      <c r="BW19">
+        <v>17.5</v>
+      </c>
+      <c r="BX19">
+        <v>32</v>
+      </c>
+      <c r="BY19">
+        <v>19</v>
+      </c>
+      <c r="BZ19">
+        <v>13</v>
+      </c>
+      <c r="CA19">
         <v>8.4</v>
       </c>
-      <c r="BO19">
-        <v>6</v>
-      </c>
-      <c r="BP19">
-        <v>27</v>
-      </c>
-      <c r="BQ19">
-        <v>18.5</v>
-      </c>
-      <c r="BR19">
-        <v>29</v>
-      </c>
-      <c r="BS19">
-        <v>19.5</v>
-      </c>
-      <c r="BT19">
-        <v>5.6</v>
-      </c>
-      <c r="BU19">
-        <v>4.1</v>
-      </c>
-      <c r="BV19">
-        <v>12</v>
-      </c>
-      <c r="BW19">
-        <v>8.4</v>
-      </c>
-      <c r="BX19">
-        <v>19</v>
-      </c>
-      <c r="BY19">
-        <v>13</v>
-      </c>
-      <c r="BZ19">
-        <v>12</v>
-      </c>
-      <c r="CA19">
-        <v>8.199999999999999</v>
-      </c>
       <c r="CB19" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B20" t="s">
         <v>88</v>
       </c>
       <c r="C20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E20" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F20">
-        <v>2.28</v>
+        <v>4</v>
       </c>
       <c r="G20">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="H20">
-        <v>3.5</v>
+        <v>1.86</v>
       </c>
       <c r="I20">
-        <v>3.75</v>
+        <v>1.89</v>
       </c>
       <c r="J20">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="K20">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="L20">
-        <v>1.47</v>
+        <v>1.23</v>
       </c>
       <c r="M20">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="N20">
-        <v>3.1</v>
+        <v>7.4</v>
       </c>
       <c r="O20">
-        <v>1.42</v>
+        <v>1.14</v>
       </c>
       <c r="P20">
-        <v>1.71</v>
+        <v>3.15</v>
       </c>
       <c r="Q20">
-        <v>2.26</v>
+        <v>1.43</v>
       </c>
       <c r="R20">
-        <v>1.27</v>
+        <v>1.88</v>
       </c>
       <c r="S20">
-        <v>4.3</v>
+        <v>2.06</v>
       </c>
       <c r="T20">
-        <v>1.92</v>
+        <v>1.45</v>
       </c>
       <c r="U20">
-        <v>1.96</v>
+        <v>3.05</v>
       </c>
       <c r="V20">
-        <v>1.36</v>
+        <v>2.12</v>
       </c>
       <c r="W20">
-        <v>1.71</v>
+        <v>1.31</v>
       </c>
       <c r="X20">
-        <v>12.5</v>
+        <v>42</v>
       </c>
       <c r="Y20">
+        <v>18.5</v>
+      </c>
+      <c r="Z20">
+        <v>17</v>
+      </c>
+      <c r="AA20">
+        <v>25</v>
+      </c>
+      <c r="AB20">
+        <v>32</v>
+      </c>
+      <c r="AC20">
+        <v>11.5</v>
+      </c>
+      <c r="AD20">
+        <v>11.5</v>
+      </c>
+      <c r="AE20">
+        <v>16.5</v>
+      </c>
+      <c r="AF20">
+        <v>42</v>
+      </c>
+      <c r="AG20">
+        <v>19.5</v>
+      </c>
+      <c r="AH20">
+        <v>15</v>
+      </c>
+      <c r="AI20">
+        <v>23</v>
+      </c>
+      <c r="AJ20">
+        <v>1000</v>
+      </c>
+      <c r="AK20">
+        <v>40</v>
+      </c>
+      <c r="AL20">
+        <v>38</v>
+      </c>
+      <c r="AM20">
+        <v>46</v>
+      </c>
+      <c r="AN20">
+        <v>24</v>
+      </c>
+      <c r="AO20">
+        <v>6.6</v>
+      </c>
+      <c r="AP20">
+        <v>23</v>
+      </c>
+      <c r="AQ20">
+        <v>15.5</v>
+      </c>
+      <c r="AR20">
+        <v>15</v>
+      </c>
+      <c r="AS20">
+        <v>21</v>
+      </c>
+      <c r="AT20">
+        <v>19</v>
+      </c>
+      <c r="AU20">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV20">
+        <v>10</v>
+      </c>
+      <c r="AW20">
+        <v>14.5</v>
+      </c>
+      <c r="AX20">
+        <v>24</v>
+      </c>
+      <c r="AY20">
+        <v>16</v>
+      </c>
+      <c r="AZ20">
         <v>13</v>
       </c>
-      <c r="Z20">
-        <v>28</v>
-      </c>
-      <c r="AA20">
-        <v>85</v>
-      </c>
-      <c r="AB20">
-        <v>9.6</v>
-      </c>
-      <c r="AC20">
-        <v>8.6</v>
-      </c>
-      <c r="AD20">
-        <v>17.5</v>
-      </c>
-      <c r="AE20">
-        <v>60</v>
-      </c>
-      <c r="AF20">
-        <v>16.5</v>
-      </c>
-      <c r="AG20">
-        <v>13.5</v>
-      </c>
-      <c r="AH20">
+      <c r="BA20">
+        <v>19</v>
+      </c>
+      <c r="BB20">
+        <v>36</v>
+      </c>
+      <c r="BC20">
         <v>23</v>
       </c>
-      <c r="AI20">
-        <v>75</v>
-      </c>
-      <c r="AJ20">
-        <v>38</v>
-      </c>
-      <c r="AK20">
-        <v>34</v>
-      </c>
-      <c r="AL20">
-        <v>55</v>
-      </c>
-      <c r="AM20">
-        <v>150</v>
-      </c>
-      <c r="AN20">
+      <c r="BD20">
+        <v>22</v>
+      </c>
+      <c r="BE20">
+        <v>25</v>
+      </c>
+      <c r="BF20">
+        <v>20</v>
+      </c>
+      <c r="BG20">
+        <v>6.2</v>
+      </c>
+      <c r="BH20">
+        <v>5.4</v>
+      </c>
+      <c r="BI20">
+        <v>4</v>
+      </c>
+      <c r="BJ20">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK20">
+        <v>6.2</v>
+      </c>
+      <c r="BL20">
+        <v>65</v>
+      </c>
+      <c r="BM20">
+        <v>42</v>
+      </c>
+      <c r="BN20">
+        <v>8.4</v>
+      </c>
+      <c r="BO20">
+        <v>6</v>
+      </c>
+      <c r="BP20">
+        <v>27</v>
+      </c>
+      <c r="BQ20">
+        <v>18.5</v>
+      </c>
+      <c r="BR20">
         <v>29</v>
       </c>
-      <c r="AO20">
-        <v>65</v>
-      </c>
-      <c r="AP20">
-        <v>9.6</v>
-      </c>
-      <c r="AQ20">
-        <v>10</v>
-      </c>
-      <c r="AR20">
-        <v>21</v>
-      </c>
-      <c r="AS20">
-        <v>5.2</v>
-      </c>
-      <c r="AT20">
-        <v>7.6</v>
-      </c>
-      <c r="AU20">
-        <v>6.6</v>
-      </c>
-      <c r="AV20">
-        <v>13.5</v>
-      </c>
-      <c r="AW20">
-        <v>5.1</v>
-      </c>
-      <c r="AX20">
-        <v>12.5</v>
-      </c>
-      <c r="AY20">
-        <v>10</v>
-      </c>
-      <c r="AZ20">
-        <v>4.4</v>
-      </c>
-      <c r="BA20">
-        <v>5.1</v>
-      </c>
-      <c r="BB20">
-        <v>4.8</v>
-      </c>
-      <c r="BC20">
-        <v>4.7</v>
-      </c>
-      <c r="BD20">
-        <v>5</v>
-      </c>
-      <c r="BE20">
-        <v>5.3</v>
-      </c>
-      <c r="BF20">
+      <c r="BS20">
         <v>19.5</v>
       </c>
-      <c r="BG20">
-        <v>5.1</v>
-      </c>
-      <c r="BH20">
-        <v>3.1</v>
-      </c>
-      <c r="BI20">
-        <v>2.56</v>
-      </c>
-      <c r="BJ20">
-        <v>10.5</v>
-      </c>
-      <c r="BK20">
-        <v>7.8</v>
-      </c>
-      <c r="BL20">
-        <v>1000</v>
-      </c>
-      <c r="BM20">
-        <v>21</v>
-      </c>
-      <c r="BN20">
-        <v>5.1</v>
-      </c>
-      <c r="BO20">
-        <v>4</v>
-      </c>
-      <c r="BP20">
-        <v>1000</v>
-      </c>
-      <c r="BQ20">
-        <v>14</v>
-      </c>
-      <c r="BR20">
-        <v>1000</v>
-      </c>
-      <c r="BS20">
-        <v>26</v>
-      </c>
       <c r="BT20">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="BU20">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="BV20">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BW20">
-        <v>23</v>
+        <v>8.4</v>
       </c>
       <c r="BX20">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BY20">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="BZ20">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="CA20">
-        <v>26</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB20" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5637,187 +5616,187 @@
         <v>88</v>
       </c>
       <c r="C21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D21" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E21" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F21">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="G21">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="H21">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="I21">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="J21">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="K21">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="L21">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="M21">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="N21">
-        <v>4.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O21">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="P21">
-        <v>2.16</v>
+        <v>3.4</v>
       </c>
       <c r="Q21">
-        <v>1.81</v>
+        <v>1.38</v>
       </c>
       <c r="R21">
-        <v>1.45</v>
+        <v>1.98</v>
       </c>
       <c r="S21">
-        <v>3.05</v>
+        <v>1.96</v>
       </c>
       <c r="T21">
-        <v>1.71</v>
+        <v>1.39</v>
       </c>
       <c r="U21">
-        <v>2.22</v>
+        <v>3.4</v>
       </c>
       <c r="V21">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="W21">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="X21">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="Y21">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="Z21">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA21">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AB21">
+        <v>22</v>
+      </c>
+      <c r="AC21">
+        <v>12</v>
+      </c>
+      <c r="AD21">
+        <v>16</v>
+      </c>
+      <c r="AE21">
+        <v>29</v>
+      </c>
+      <c r="AF21">
+        <v>22</v>
+      </c>
+      <c r="AG21">
         <v>12.5</v>
       </c>
-      <c r="AC21">
+      <c r="AH21">
+        <v>14</v>
+      </c>
+      <c r="AI21">
+        <v>28</v>
+      </c>
+      <c r="AJ21">
+        <v>32</v>
+      </c>
+      <c r="AK21">
+        <v>18.5</v>
+      </c>
+      <c r="AL21">
+        <v>22</v>
+      </c>
+      <c r="AM21">
+        <v>42</v>
+      </c>
+      <c r="AN21">
+        <v>7.6</v>
+      </c>
+      <c r="AO21">
+        <v>14</v>
+      </c>
+      <c r="AP21">
+        <v>32</v>
+      </c>
+      <c r="AQ21">
+        <v>24</v>
+      </c>
+      <c r="AR21">
+        <v>29</v>
+      </c>
+      <c r="AS21">
+        <v>46</v>
+      </c>
+      <c r="AT21">
+        <v>19.5</v>
+      </c>
+      <c r="AU21">
         <v>10.5</v>
-      </c>
-      <c r="AD21">
-        <v>19.5</v>
-      </c>
-      <c r="AE21">
-        <v>55</v>
-      </c>
-      <c r="AF21">
-        <v>16.5</v>
-      </c>
-      <c r="AG21">
-        <v>13</v>
-      </c>
-      <c r="AH21">
-        <v>21</v>
-      </c>
-      <c r="AI21">
-        <v>60</v>
-      </c>
-      <c r="AJ21">
-        <v>29</v>
-      </c>
-      <c r="AK21">
-        <v>25</v>
-      </c>
-      <c r="AL21">
-        <v>40</v>
-      </c>
-      <c r="AM21">
-        <v>95</v>
-      </c>
-      <c r="AN21">
-        <v>15</v>
-      </c>
-      <c r="AO21">
-        <v>46</v>
-      </c>
-      <c r="AP21">
-        <v>15.5</v>
-      </c>
-      <c r="AQ21">
-        <v>14</v>
-      </c>
-      <c r="AR21">
-        <v>4.1</v>
-      </c>
-      <c r="AS21">
-        <v>4.4</v>
-      </c>
-      <c r="AT21">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU21">
-        <v>7.8</v>
       </c>
       <c r="AV21">
         <v>13.5</v>
       </c>
       <c r="AW21">
-        <v>4.2</v>
+        <v>25</v>
       </c>
       <c r="AX21">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="AY21">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AZ21">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA21">
-        <v>4.3</v>
+        <v>24</v>
       </c>
       <c r="BB21">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="BC21">
         <v>17</v>
       </c>
       <c r="BD21">
-        <v>4.1</v>
+        <v>19</v>
       </c>
       <c r="BE21">
-        <v>4.4</v>
+        <v>34</v>
       </c>
       <c r="BF21">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="BG21">
-        <v>4.2</v>
+        <v>12.5</v>
       </c>
       <c r="BH21">
-        <v>3.9</v>
+        <v>5.9</v>
       </c>
       <c r="BI21">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="BJ21">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="BK21">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BL21">
         <v>1000</v>
@@ -5826,775 +5805,49 @@
         <v>21</v>
       </c>
       <c r="BN21">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BO21">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="BP21">
+        <v>14</v>
+      </c>
+      <c r="BQ21">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR21">
+        <v>19</v>
+      </c>
+      <c r="BS21">
+        <v>11</v>
+      </c>
+      <c r="BT21">
+        <v>7.8</v>
+      </c>
+      <c r="BU21">
+        <v>4.8</v>
+      </c>
+      <c r="BV21">
+        <v>21</v>
+      </c>
+      <c r="BW21">
         <v>14.5</v>
       </c>
-      <c r="BQ21">
-        <v>10</v>
-      </c>
-      <c r="BR21">
-        <v>27</v>
-      </c>
-      <c r="BS21">
-        <v>18</v>
-      </c>
-      <c r="BT21">
-        <v>7.6</v>
-      </c>
-      <c r="BU21">
-        <v>5.5</v>
-      </c>
-      <c r="BV21">
-        <v>32</v>
-      </c>
-      <c r="BW21">
-        <v>21</v>
-      </c>
       <c r="BX21">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="BY21">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="BZ21">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="CA21">
-        <v>14.5</v>
+        <v>7.8</v>
       </c>
       <c r="CB21" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="22" spans="1:80">
-      <c r="A22" t="s">
-        <v>87</v>
-      </c>
-      <c r="B22" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22" t="s">
-        <v>99</v>
-      </c>
-      <c r="D22" t="s">
-        <v>120</v>
-      </c>
-      <c r="E22" t="s">
-        <v>143</v>
-      </c>
-      <c r="F22">
-        <v>1.99</v>
-      </c>
-      <c r="G22">
-        <v>2.02</v>
-      </c>
-      <c r="H22">
-        <v>3.95</v>
-      </c>
-      <c r="I22">
-        <v>4.1</v>
-      </c>
-      <c r="J22">
-        <v>4</v>
-      </c>
-      <c r="K22">
-        <v>4.1</v>
-      </c>
-      <c r="L22">
-        <v>1.37</v>
-      </c>
-      <c r="M22">
-        <v>1.05</v>
-      </c>
-      <c r="N22">
-        <v>4.3</v>
-      </c>
-      <c r="O22">
-        <v>1.27</v>
-      </c>
-      <c r="P22">
-        <v>2.16</v>
-      </c>
-      <c r="Q22">
-        <v>1.83</v>
-      </c>
-      <c r="R22">
-        <v>1.44</v>
-      </c>
-      <c r="S22">
-        <v>3.15</v>
-      </c>
-      <c r="T22">
-        <v>1.73</v>
-      </c>
-      <c r="U22">
-        <v>2.22</v>
-      </c>
-      <c r="V22">
-        <v>1.32</v>
-      </c>
-      <c r="W22">
-        <v>1.98</v>
-      </c>
-      <c r="X22">
-        <v>21</v>
-      </c>
-      <c r="Y22">
-        <v>20</v>
-      </c>
-      <c r="Z22">
-        <v>38</v>
-      </c>
-      <c r="AA22">
-        <v>95</v>
-      </c>
-      <c r="AB22">
-        <v>12.5</v>
-      </c>
-      <c r="AC22">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD22">
-        <v>21</v>
-      </c>
-      <c r="AE22">
-        <v>60</v>
-      </c>
-      <c r="AF22">
-        <v>16</v>
-      </c>
-      <c r="AG22">
-        <v>13</v>
-      </c>
-      <c r="AH22">
-        <v>21</v>
-      </c>
-      <c r="AI22">
-        <v>65</v>
-      </c>
-      <c r="AJ22">
-        <v>28</v>
-      </c>
-      <c r="AK22">
-        <v>24</v>
-      </c>
-      <c r="AL22">
-        <v>40</v>
-      </c>
-      <c r="AM22">
-        <v>100</v>
-      </c>
-      <c r="AN22">
-        <v>14.5</v>
-      </c>
-      <c r="AO22">
-        <v>55</v>
-      </c>
-      <c r="AP22">
-        <v>3.85</v>
-      </c>
-      <c r="AQ22">
-        <v>14</v>
-      </c>
-      <c r="AR22">
-        <v>4.2</v>
-      </c>
-      <c r="AS22">
-        <v>4.5</v>
-      </c>
-      <c r="AT22">
-        <v>9</v>
-      </c>
-      <c r="AU22">
-        <v>8</v>
-      </c>
-      <c r="AV22">
-        <v>14</v>
-      </c>
-      <c r="AW22">
-        <v>4.4</v>
-      </c>
-      <c r="AX22">
-        <v>11</v>
-      </c>
-      <c r="AY22">
-        <v>9</v>
-      </c>
-      <c r="AZ22">
-        <v>14.5</v>
-      </c>
-      <c r="BA22">
-        <v>4.4</v>
-      </c>
-      <c r="BB22">
-        <v>19.5</v>
-      </c>
-      <c r="BC22">
-        <v>16.5</v>
-      </c>
-      <c r="BD22">
-        <v>4.2</v>
-      </c>
-      <c r="BE22">
-        <v>4.5</v>
-      </c>
-      <c r="BF22">
-        <v>10</v>
-      </c>
-      <c r="BG22">
-        <v>4.3</v>
-      </c>
-      <c r="BH22">
-        <v>3.85</v>
-      </c>
-      <c r="BI22">
-        <v>2.96</v>
-      </c>
-      <c r="BJ22">
-        <v>9.6</v>
-      </c>
-      <c r="BK22">
-        <v>6.8</v>
-      </c>
-      <c r="BL22">
-        <v>1000</v>
-      </c>
-      <c r="BM22">
-        <v>21</v>
-      </c>
-      <c r="BN22">
-        <v>5.1</v>
-      </c>
-      <c r="BO22">
-        <v>4.2</v>
-      </c>
-      <c r="BP22">
-        <v>14.5</v>
-      </c>
-      <c r="BQ22">
-        <v>8.4</v>
-      </c>
-      <c r="BR22">
-        <v>27</v>
-      </c>
-      <c r="BS22">
-        <v>15.5</v>
-      </c>
-      <c r="BT22">
-        <v>7.8</v>
-      </c>
-      <c r="BU22">
-        <v>4.8</v>
-      </c>
-      <c r="BV22">
-        <v>32</v>
-      </c>
-      <c r="BW22">
-        <v>18.5</v>
-      </c>
-      <c r="BX22">
-        <v>1000</v>
-      </c>
-      <c r="BY22">
-        <v>21</v>
-      </c>
-      <c r="BZ22">
-        <v>22</v>
-      </c>
-      <c r="CA22">
-        <v>12.5</v>
-      </c>
-      <c r="CB22" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="23" spans="1:80">
-      <c r="A23" t="s">
-        <v>87</v>
-      </c>
-      <c r="B23" t="s">
-        <v>88</v>
-      </c>
-      <c r="C23" t="s">
-        <v>99</v>
-      </c>
-      <c r="D23" t="s">
-        <v>121</v>
-      </c>
-      <c r="E23" t="s">
-        <v>144</v>
-      </c>
-      <c r="F23">
-        <v>1.81</v>
-      </c>
-      <c r="G23">
-        <v>1.86</v>
-      </c>
-      <c r="H23">
-        <v>4.2</v>
-      </c>
-      <c r="I23">
-        <v>4.5</v>
-      </c>
-      <c r="J23">
-        <v>4.3</v>
-      </c>
-      <c r="K23">
-        <v>4.7</v>
-      </c>
-      <c r="L23">
-        <v>1.26</v>
-      </c>
-      <c r="M23">
-        <v>1.03</v>
-      </c>
-      <c r="N23">
-        <v>6.2</v>
-      </c>
-      <c r="O23">
-        <v>1.17</v>
-      </c>
-      <c r="P23">
-        <v>2.78</v>
-      </c>
-      <c r="Q23">
-        <v>1.52</v>
-      </c>
-      <c r="R23">
-        <v>1.72</v>
-      </c>
-      <c r="S23">
-        <v>2.3</v>
-      </c>
-      <c r="T23">
-        <v>1.55</v>
-      </c>
-      <c r="U23">
-        <v>2.6</v>
-      </c>
-      <c r="V23">
-        <v>1.28</v>
-      </c>
-      <c r="W23">
-        <v>2.16</v>
-      </c>
-      <c r="X23">
-        <v>32</v>
-      </c>
-      <c r="Y23">
-        <v>28</v>
-      </c>
-      <c r="Z23">
-        <v>44</v>
-      </c>
-      <c r="AA23">
-        <v>95</v>
-      </c>
-      <c r="AB23">
-        <v>16.5</v>
-      </c>
-      <c r="AC23">
-        <v>12.5</v>
-      </c>
-      <c r="AD23">
-        <v>21</v>
-      </c>
-      <c r="AE23">
-        <v>48</v>
-      </c>
-      <c r="AF23">
-        <v>17.5</v>
-      </c>
-      <c r="AG23">
-        <v>12.5</v>
-      </c>
-      <c r="AH23">
-        <v>17</v>
-      </c>
-      <c r="AI23">
-        <v>48</v>
-      </c>
-      <c r="AJ23">
-        <v>24</v>
-      </c>
-      <c r="AK23">
-        <v>19.5</v>
-      </c>
-      <c r="AL23">
-        <v>29</v>
-      </c>
-      <c r="AM23">
-        <v>65</v>
-      </c>
-      <c r="AN23">
-        <v>7.4</v>
-      </c>
-      <c r="AO23">
-        <v>36</v>
-      </c>
-      <c r="AP23">
-        <v>5.1</v>
-      </c>
-      <c r="AQ23">
-        <v>20</v>
-      </c>
-      <c r="AR23">
-        <v>5.3</v>
-      </c>
-      <c r="AS23">
-        <v>5.7</v>
-      </c>
-      <c r="AT23">
-        <v>12.5</v>
-      </c>
-      <c r="AU23">
-        <v>9.6</v>
-      </c>
-      <c r="AV23">
-        <v>15.5</v>
-      </c>
-      <c r="AW23">
-        <v>5.4</v>
-      </c>
-      <c r="AX23">
-        <v>13</v>
-      </c>
-      <c r="AY23">
-        <v>9.6</v>
-      </c>
-      <c r="AZ23">
-        <v>13.5</v>
-      </c>
-      <c r="BA23">
-        <v>5.4</v>
-      </c>
-      <c r="BB23">
-        <v>18</v>
-      </c>
-      <c r="BC23">
-        <v>14.5</v>
-      </c>
-      <c r="BD23">
-        <v>21</v>
-      </c>
-      <c r="BE23">
-        <v>5.5</v>
-      </c>
-      <c r="BF23">
-        <v>6.4</v>
-      </c>
-      <c r="BG23">
-        <v>5.1</v>
-      </c>
-      <c r="BH23">
-        <v>4.8</v>
-      </c>
-      <c r="BI23">
-        <v>3.8</v>
-      </c>
-      <c r="BJ23">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK23">
-        <v>5.8</v>
-      </c>
-      <c r="BL23">
-        <v>1000</v>
-      </c>
-      <c r="BM23">
-        <v>21</v>
-      </c>
-      <c r="BN23">
-        <v>5.1</v>
-      </c>
-      <c r="BO23">
-        <v>4.5</v>
-      </c>
-      <c r="BP23">
-        <v>11.5</v>
-      </c>
-      <c r="BQ23">
-        <v>7.2</v>
-      </c>
-      <c r="BR23">
-        <v>19.5</v>
-      </c>
-      <c r="BS23">
-        <v>12.5</v>
-      </c>
-      <c r="BT23">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BU23">
-        <v>5.4</v>
-      </c>
-      <c r="BV23">
-        <v>29</v>
-      </c>
-      <c r="BW23">
-        <v>17.5</v>
-      </c>
-      <c r="BX23">
-        <v>32</v>
-      </c>
-      <c r="BY23">
-        <v>19</v>
-      </c>
-      <c r="BZ23">
-        <v>13</v>
-      </c>
-      <c r="CA23">
-        <v>8.4</v>
-      </c>
-      <c r="CB23" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="24" spans="1:80">
-      <c r="A24" t="s">
-        <v>87</v>
-      </c>
-      <c r="B24" t="s">
-        <v>88</v>
-      </c>
-      <c r="C24" t="s">
-        <v>99</v>
-      </c>
-      <c r="D24" t="s">
-        <v>122</v>
-      </c>
-      <c r="E24" t="s">
-        <v>145</v>
-      </c>
-      <c r="F24">
-        <v>2.16</v>
-      </c>
-      <c r="G24">
-        <v>2.2</v>
-      </c>
-      <c r="H24">
-        <v>3.15</v>
-      </c>
-      <c r="I24">
-        <v>3.2</v>
-      </c>
-      <c r="J24">
-        <v>4.3</v>
-      </c>
-      <c r="K24">
-        <v>4.4</v>
-      </c>
-      <c r="L24">
-        <v>1.21</v>
-      </c>
-      <c r="M24">
-        <v>1.02</v>
-      </c>
-      <c r="N24">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="O24">
-        <v>1.12</v>
-      </c>
-      <c r="P24">
-        <v>3.4</v>
-      </c>
-      <c r="Q24">
-        <v>1.38</v>
-      </c>
-      <c r="R24">
-        <v>1.99</v>
-      </c>
-      <c r="S24">
-        <v>1.96</v>
-      </c>
-      <c r="T24">
-        <v>1.39</v>
-      </c>
-      <c r="U24">
-        <v>3.4</v>
-      </c>
-      <c r="V24">
-        <v>1.44</v>
-      </c>
-      <c r="W24">
-        <v>1.84</v>
-      </c>
-      <c r="X24">
-        <v>42</v>
-      </c>
-      <c r="Y24">
-        <v>40</v>
-      </c>
-      <c r="Z24">
-        <v>34</v>
-      </c>
-      <c r="AA24">
-        <v>60</v>
-      </c>
-      <c r="AB24">
-        <v>22</v>
-      </c>
-      <c r="AC24">
-        <v>12</v>
-      </c>
-      <c r="AD24">
-        <v>15.5</v>
-      </c>
-      <c r="AE24">
-        <v>29</v>
-      </c>
-      <c r="AF24">
-        <v>22</v>
-      </c>
-      <c r="AG24">
-        <v>12.5</v>
-      </c>
-      <c r="AH24">
-        <v>14</v>
-      </c>
-      <c r="AI24">
-        <v>28</v>
-      </c>
-      <c r="AJ24">
-        <v>32</v>
-      </c>
-      <c r="AK24">
-        <v>18.5</v>
-      </c>
-      <c r="AL24">
-        <v>22</v>
-      </c>
-      <c r="AM24">
-        <v>42</v>
-      </c>
-      <c r="AN24">
-        <v>7.6</v>
-      </c>
-      <c r="AO24">
-        <v>14</v>
-      </c>
-      <c r="AP24">
-        <v>32</v>
-      </c>
-      <c r="AQ24">
-        <v>24</v>
-      </c>
-      <c r="AR24">
-        <v>29</v>
-      </c>
-      <c r="AS24">
-        <v>46</v>
-      </c>
-      <c r="AT24">
-        <v>19.5</v>
-      </c>
-      <c r="AU24">
-        <v>10.5</v>
-      </c>
-      <c r="AV24">
-        <v>13.5</v>
-      </c>
-      <c r="AW24">
-        <v>25</v>
-      </c>
-      <c r="AX24">
-        <v>19</v>
-      </c>
-      <c r="AY24">
-        <v>11</v>
-      </c>
-      <c r="AZ24">
-        <v>12</v>
-      </c>
-      <c r="BA24">
-        <v>24</v>
-      </c>
-      <c r="BB24">
-        <v>27</v>
-      </c>
-      <c r="BC24">
-        <v>17</v>
-      </c>
-      <c r="BD24">
-        <v>19</v>
-      </c>
-      <c r="BE24">
-        <v>34</v>
-      </c>
-      <c r="BF24">
-        <v>7</v>
-      </c>
-      <c r="BG24">
-        <v>12</v>
-      </c>
-      <c r="BH24">
-        <v>5.8</v>
-      </c>
-      <c r="BI24">
-        <v>4.2</v>
-      </c>
-      <c r="BJ24">
-        <v>8.4</v>
-      </c>
-      <c r="BK24">
-        <v>5.1</v>
-      </c>
-      <c r="BL24">
-        <v>1000</v>
-      </c>
-      <c r="BM24">
-        <v>21</v>
-      </c>
-      <c r="BN24">
-        <v>6.4</v>
-      </c>
-      <c r="BO24">
-        <v>5.2</v>
-      </c>
-      <c r="BP24">
-        <v>14</v>
-      </c>
-      <c r="BQ24">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR24">
-        <v>19</v>
-      </c>
-      <c r="BS24">
-        <v>11</v>
-      </c>
-      <c r="BT24">
-        <v>7.8</v>
-      </c>
-      <c r="BU24">
-        <v>4.8</v>
-      </c>
-      <c r="BV24">
-        <v>21</v>
-      </c>
-      <c r="BW24">
-        <v>12</v>
-      </c>
-      <c r="BX24">
-        <v>24</v>
-      </c>
-      <c r="BY24">
-        <v>13.5</v>
-      </c>
-      <c r="BZ24">
-        <v>11</v>
-      </c>
-      <c r="CA24">
-        <v>6.8</v>
-      </c>
-      <c r="CB24" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
@@ -442,7 +442,7 @@
     <t>Chicago Fire</t>
   </si>
   <si>
-    <t>2026-07-21 09:14:34</t>
+    <t>2026-07-21 11:21:35</t>
   </si>
 </sst>
 </file>
@@ -1036,22 +1036,22 @@
         <v>121</v>
       </c>
       <c r="F2">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="G2">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="H2">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="I2">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="J2">
         <v>3.55</v>
       </c>
       <c r="K2">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L2">
         <v>1.44</v>
@@ -1063,58 +1063,58 @@
         <v>3.6</v>
       </c>
       <c r="O2">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P2">
         <v>1.87</v>
       </c>
       <c r="Q2">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R2">
         <v>1.33</v>
       </c>
       <c r="S2">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T2">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U2">
         <v>2</v>
       </c>
       <c r="V2">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="W2">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="X2">
         <v>13</v>
       </c>
       <c r="Y2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA2">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="AB2">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AC2">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD2">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG2">
         <v>10.5</v>
@@ -1123,25 +1123,25 @@
         <v>20</v>
       </c>
       <c r="AI2">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AJ2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AK2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM2">
         <v>120</v>
       </c>
       <c r="AN2">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO2">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AP2">
         <v>11.5</v>
@@ -1150,22 +1150,22 @@
         <v>13</v>
       </c>
       <c r="AR2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AS2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AT2">
         <v>7.6</v>
       </c>
       <c r="AU2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AW2">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AX2">
         <v>10</v>
@@ -1174,10 +1174,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BB2">
         <v>20</v>
@@ -1189,16 +1189,16 @@
         <v>34</v>
       </c>
       <c r="BE2">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BF2">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG2">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="BH2">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI2">
         <v>2.78</v>
@@ -1207,55 +1207,55 @@
         <v>10</v>
       </c>
       <c r="BK2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BN2">
         <v>4.6</v>
       </c>
       <c r="BO2">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="BP2">
+        <v>14.5</v>
+      </c>
+      <c r="BQ2">
+        <v>10.5</v>
+      </c>
+      <c r="BR2">
+        <v>30</v>
+      </c>
+      <c r="BS2">
+        <v>12</v>
+      </c>
+      <c r="BT2">
+        <v>7.6</v>
+      </c>
+      <c r="BU2">
+        <v>6</v>
+      </c>
+      <c r="BV2">
+        <v>38</v>
+      </c>
+      <c r="BW2">
+        <v>13</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
         <v>14</v>
       </c>
-      <c r="BQ2">
-        <v>10</v>
-      </c>
-      <c r="BR2">
-        <v>29</v>
-      </c>
-      <c r="BS2">
-        <v>11</v>
-      </c>
-      <c r="BT2">
-        <v>7.8</v>
-      </c>
-      <c r="BU2">
-        <v>5.4</v>
-      </c>
-      <c r="BV2">
-        <v>40</v>
-      </c>
-      <c r="BW2">
-        <v>12</v>
-      </c>
-      <c r="BX2">
-        <v>1000</v>
-      </c>
-      <c r="BY2">
-        <v>13</v>
-      </c>
       <c r="BZ2">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="CB2" t="s">
         <v>142</v>
@@ -1281,16 +1281,16 @@
         <v>2.6</v>
       </c>
       <c r="G3">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="H3">
         <v>3.2</v>
       </c>
       <c r="I3">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K3">
         <v>3.2</v>
@@ -1305,13 +1305,13 @@
         <v>3</v>
       </c>
       <c r="O3">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P3">
         <v>1.64</v>
       </c>
       <c r="Q3">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="R3">
         <v>1.24</v>
@@ -1320,121 +1320,121 @@
         <v>4.8</v>
       </c>
       <c r="T3">
+        <v>1.97</v>
+      </c>
+      <c r="U3">
         <v>1.92</v>
       </c>
-      <c r="U3">
-        <v>1.89</v>
-      </c>
       <c r="V3">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W3">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X3">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="Y3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA3">
         <v>65</v>
       </c>
       <c r="AB3">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AC3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD3">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AE3">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF3">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG3">
         <v>13</v>
       </c>
       <c r="AH3">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI3">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AJ3">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK3">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AL3">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AM3">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AN3">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AO3">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP3">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ3">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR3">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS3">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="AT3">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AU3">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW3">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="AX3">
         <v>13.5</v>
       </c>
       <c r="AY3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ3">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BA3">
-        <v>5.1</v>
+        <v>48</v>
       </c>
       <c r="BB3">
-        <v>4.9</v>
+        <v>23</v>
       </c>
       <c r="BC3">
-        <v>5.4</v>
+        <v>26</v>
       </c>
       <c r="BD3">
-        <v>5.1</v>
+        <v>40</v>
       </c>
       <c r="BE3">
-        <v>5.3</v>
+        <v>44</v>
       </c>
       <c r="BF3">
-        <v>5.3</v>
+        <v>30</v>
       </c>
       <c r="BG3">
         <v>38</v>
@@ -1443,19 +1443,19 @@
         <v>2.96</v>
       </c>
       <c r="BI3">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BJ3">
         <v>11</v>
       </c>
       <c r="BK3">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BM3">
-        <v>22</v>
+        <v>1.04</v>
       </c>
       <c r="BN3">
         <v>5.5</v>
@@ -1467,13 +1467,13 @@
         <v>23</v>
       </c>
       <c r="BQ3">
-        <v>18</v>
+        <v>1.04</v>
       </c>
       <c r="BR3">
         <v>42</v>
       </c>
       <c r="BS3">
-        <v>22</v>
+        <v>1.04</v>
       </c>
       <c r="BT3">
         <v>6.4</v>
@@ -1482,22 +1482,22 @@
         <v>5.3</v>
       </c>
       <c r="BV3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BW3">
-        <v>21</v>
+        <v>1.04</v>
       </c>
       <c r="BX3">
         <v>48</v>
       </c>
       <c r="BY3">
-        <v>22</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3">
         <v>42</v>
       </c>
       <c r="CA3">
-        <v>22</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="s">
         <v>142</v>
@@ -1526,7 +1526,7 @@
         <v>1.39</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="I4">
         <v>9.199999999999999</v>
@@ -1544,28 +1544,28 @@
         <v>1.04</v>
       </c>
       <c r="N4">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O4">
         <v>1.21</v>
       </c>
       <c r="P4">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Q4">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="R4">
         <v>1.58</v>
       </c>
       <c r="S4">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="T4">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="U4">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V4">
         <v>1.12</v>
@@ -1586,25 +1586,25 @@
         <v>300</v>
       </c>
       <c r="AB4">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC4">
         <v>13.5</v>
       </c>
       <c r="AD4">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE4">
         <v>130</v>
       </c>
       <c r="AF4">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AG4">
         <v>10.5</v>
       </c>
       <c r="AH4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI4">
         <v>110</v>
@@ -1631,10 +1631,10 @@
         <v>22</v>
       </c>
       <c r="AQ4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR4">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AS4">
         <v>55</v>
@@ -1655,10 +1655,10 @@
         <v>8</v>
       </c>
       <c r="AY4">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA4">
         <v>38</v>
@@ -1670,13 +1670,13 @@
         <v>12.5</v>
       </c>
       <c r="BD4">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="BE4">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="BF4">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BG4">
         <v>48</v>
@@ -1685,25 +1685,25 @@
         <v>4.3</v>
       </c>
       <c r="BI4">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BJ4">
         <v>11.5</v>
       </c>
       <c r="BK4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BN4">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BO4">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BP4">
         <v>8</v>
@@ -1715,7 +1715,7 @@
         <v>22</v>
       </c>
       <c r="BS4">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT4">
         <v>12.5</v>
@@ -1727,13 +1727,13 @@
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BX4">
         <v>70</v>
       </c>
       <c r="BY4">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BZ4">
         <v>12</v>
@@ -1762,16 +1762,16 @@
         <v>124</v>
       </c>
       <c r="F5">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="G5">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="H5">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I5">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J5">
         <v>4.4</v>
@@ -1792,16 +1792,16 @@
         <v>1.23</v>
       </c>
       <c r="P5">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q5">
         <v>1.68</v>
       </c>
       <c r="R5">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="S5">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="T5">
         <v>1.73</v>
@@ -1810,22 +1810,22 @@
         <v>2.3</v>
       </c>
       <c r="V5">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W5">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="X5">
         <v>22</v>
       </c>
       <c r="Y5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z5">
         <v>46</v>
       </c>
       <c r="AA5">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB5">
         <v>11</v>
@@ -1837,7 +1837,7 @@
         <v>20</v>
       </c>
       <c r="AE5">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF5">
         <v>11.5</v>
@@ -1846,7 +1846,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH5">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AI5">
         <v>60</v>
@@ -1864,22 +1864,22 @@
         <v>85</v>
       </c>
       <c r="AN5">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AO5">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ5">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AR5">
         <v>38</v>
       </c>
       <c r="AS5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT5">
         <v>10</v>
@@ -1900,7 +1900,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA5">
         <v>50</v>
@@ -1912,76 +1912,76 @@
         <v>14</v>
       </c>
       <c r="BD5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE5">
         <v>60</v>
       </c>
       <c r="BF5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG5">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BH5">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BI5">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="BJ5">
         <v>10</v>
       </c>
       <c r="BK5">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BL5">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BN5">
         <v>4.7</v>
       </c>
       <c r="BO5">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="BP5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BQ5">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BR5">
         <v>23</v>
       </c>
       <c r="BS5">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT5">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU5">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="BV5">
         <v>42</v>
       </c>
       <c r="BW5">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BX5">
         <v>46</v>
       </c>
       <c r="BY5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BZ5">
         <v>16.5</v>
       </c>
       <c r="CA5">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="CB5" t="s">
         <v>142</v>
@@ -2013,43 +2013,43 @@
         <v>2.66</v>
       </c>
       <c r="I6">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="J6">
         <v>3.1</v>
       </c>
       <c r="K6">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L6">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="M6">
         <v>1.11</v>
       </c>
       <c r="N6">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="O6">
         <v>1.49</v>
       </c>
       <c r="P6">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Q6">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="R6">
         <v>1.23</v>
       </c>
       <c r="S6">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="T6">
         <v>2.02</v>
       </c>
       <c r="U6">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V6">
         <v>1.56</v>
@@ -2058,7 +2058,7 @@
         <v>1.46</v>
       </c>
       <c r="X6">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Y6">
         <v>8.6</v>
@@ -2079,13 +2079,13 @@
         <v>13</v>
       </c>
       <c r="AE6">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AF6">
         <v>19</v>
       </c>
       <c r="AG6">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH6">
         <v>21</v>
@@ -2094,13 +2094,13 @@
         <v>70</v>
       </c>
       <c r="AJ6">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AK6">
         <v>48</v>
       </c>
       <c r="AL6">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM6">
         <v>170</v>
@@ -2109,7 +2109,7 @@
         <v>55</v>
       </c>
       <c r="AO6">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AP6">
         <v>9</v>
@@ -2133,7 +2133,7 @@
         <v>11.5</v>
       </c>
       <c r="AW6">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AX6">
         <v>16.5</v>
@@ -2148,13 +2148,13 @@
         <v>10.5</v>
       </c>
       <c r="BB6">
+        <v>10.5</v>
+      </c>
+      <c r="BC6">
         <v>10</v>
       </c>
-      <c r="BC6">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BD6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BE6">
         <v>11.5</v>
@@ -2166,16 +2166,16 @@
         <v>9.6</v>
       </c>
       <c r="BH6">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="BI6">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="BJ6">
         <v>10.5</v>
       </c>
       <c r="BK6">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BL6">
         <v>1000</v>
@@ -2187,43 +2187,43 @@
         <v>6</v>
       </c>
       <c r="BO6">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="BP6">
         <v>28</v>
       </c>
       <c r="BQ6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BR6">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BT6">
         <v>5.5</v>
       </c>
       <c r="BU6">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="BV6">
         <v>24</v>
       </c>
       <c r="BW6">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX6">
         <v>44</v>
       </c>
       <c r="BY6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BZ6">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="CA6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="CB6" t="s">
         <v>142</v>
@@ -2249,28 +2249,28 @@
         <v>4.7</v>
       </c>
       <c r="G7">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="H7">
         <v>1.9</v>
       </c>
       <c r="I7">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="J7">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K7">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L7">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="M7">
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O7">
         <v>1.39</v>
@@ -2279,7 +2279,7 @@
         <v>1.8</v>
       </c>
       <c r="Q7">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R7">
         <v>1.3</v>
@@ -2291,7 +2291,7 @@
         <v>1.99</v>
       </c>
       <c r="U7">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V7">
         <v>2.04</v>
@@ -2303,7 +2303,7 @@
         <v>12.5</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z7">
         <v>11</v>
@@ -2324,16 +2324,16 @@
         <v>23</v>
       </c>
       <c r="AF7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AG7">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH7">
         <v>24</v>
       </c>
       <c r="AI7">
-        <v>55</v>
+        <v>140</v>
       </c>
       <c r="AJ7">
         <v>1000</v>
@@ -2363,7 +2363,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AS7">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AT7">
         <v>13</v>
@@ -2372,19 +2372,19 @@
         <v>7.2</v>
       </c>
       <c r="AV7">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW7">
         <v>18.5</v>
       </c>
       <c r="AX7">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AY7">
         <v>16.5</v>
       </c>
       <c r="AZ7">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA7">
         <v>36</v>
@@ -2411,61 +2411,61 @@
         <v>3.2</v>
       </c>
       <c r="BI7">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="BJ7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK7">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN7">
         <v>8.199999999999999</v>
       </c>
       <c r="BO7">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BT7">
         <v>4.5</v>
       </c>
       <c r="BU7">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="BV7">
         <v>14</v>
       </c>
       <c r="BW7">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="BX7">
         <v>32</v>
       </c>
       <c r="BY7">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ7">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="CB7" t="s">
         <v>142</v>
@@ -2491,28 +2491,28 @@
         <v>1.91</v>
       </c>
       <c r="G8">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="H8">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="I8">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J8">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K8">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L8">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M8">
         <v>1.1</v>
       </c>
       <c r="N8">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="O8">
         <v>1.45</v>
@@ -2521,28 +2521,28 @@
         <v>1.68</v>
       </c>
       <c r="Q8">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R8">
         <v>1.25</v>
       </c>
       <c r="S8">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T8">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U8">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="V8">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W8">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="X8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y8">
         <v>14</v>
@@ -2560,7 +2560,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE8">
         <v>85</v>
@@ -2569,7 +2569,7 @@
         <v>11</v>
       </c>
       <c r="AG8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH8">
         <v>24</v>
@@ -2581,10 +2581,10 @@
         <v>23</v>
       </c>
       <c r="AK8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL8">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AM8">
         <v>190</v>
@@ -2602,10 +2602,10 @@
         <v>12</v>
       </c>
       <c r="AR8">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AS8">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT8">
         <v>6.4</v>
@@ -2614,40 +2614,40 @@
         <v>7.2</v>
       </c>
       <c r="AV8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW8">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AX8">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY8">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ8">
         <v>20</v>
       </c>
       <c r="BA8">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BB8">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BC8">
         <v>18</v>
       </c>
       <c r="BD8">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE8">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF8">
         <v>16</v>
       </c>
       <c r="BG8">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH8">
         <v>2.98</v>
@@ -2659,25 +2659,25 @@
         <v>11</v>
       </c>
       <c r="BK8">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BN8">
         <v>4.4</v>
       </c>
       <c r="BO8">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BP8">
         <v>14.5</v>
       </c>
       <c r="BQ8">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="BR8">
         <v>36</v>
@@ -2689,16 +2689,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BU8">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BV8">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
         <v>12.5</v>
       </c>
       <c r="BX8">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
         <v>13.5</v>
@@ -2707,7 +2707,7 @@
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CB8" t="s">
         <v>142</v>
@@ -2730,16 +2730,16 @@
         <v>128</v>
       </c>
       <c r="F9">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="G9">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H9">
         <v>2.18</v>
       </c>
       <c r="I9">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="J9">
         <v>3.8</v>
@@ -2757,7 +2757,7 @@
         <v>5.6</v>
       </c>
       <c r="O9">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P9">
         <v>2.52</v>
@@ -2766,7 +2766,7 @@
         <v>1.6</v>
       </c>
       <c r="R9">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="S9">
         <v>2.48</v>
@@ -2775,7 +2775,7 @@
         <v>1.55</v>
       </c>
       <c r="U9">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="V9">
         <v>1.67</v>
@@ -2790,13 +2790,13 @@
         <v>15</v>
       </c>
       <c r="Z9">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AA9">
         <v>28</v>
       </c>
       <c r="AB9">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AC9">
         <v>9.4</v>
@@ -2805,19 +2805,19 @@
         <v>11.5</v>
       </c>
       <c r="AE9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF9">
         <v>32</v>
       </c>
       <c r="AG9">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH9">
         <v>14.5</v>
       </c>
       <c r="AI9">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ9">
         <v>60</v>
@@ -2832,10 +2832,10 @@
         <v>55</v>
       </c>
       <c r="AN9">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AO9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AP9">
         <v>21</v>
@@ -2847,7 +2847,7 @@
         <v>15</v>
       </c>
       <c r="AS9">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AT9">
         <v>17.5</v>
@@ -2889,10 +2889,10 @@
         <v>20</v>
       </c>
       <c r="BG9">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH9">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BI9">
         <v>4</v>
@@ -2901,55 +2901,55 @@
         <v>8.6</v>
       </c>
       <c r="BK9">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL9">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BM9">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BN9">
         <v>7</v>
       </c>
       <c r="BO9">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BP9">
         <v>23</v>
       </c>
       <c r="BQ9">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR9">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BS9">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BT9">
         <v>5.5</v>
       </c>
       <c r="BU9">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV9">
         <v>14.5</v>
       </c>
       <c r="BW9">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BX9">
         <v>23</v>
       </c>
       <c r="BY9">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ9">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="CA9">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB9" t="s">
         <v>142</v>
@@ -2987,7 +2987,7 @@
         <v>10.5</v>
       </c>
       <c r="K10">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="L10">
         <v>1.14</v>
@@ -3014,10 +3014,10 @@
         <v>1.69</v>
       </c>
       <c r="T10">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U10">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="V10">
         <v>1.03</v>
@@ -3038,10 +3038,10 @@
         <v>1000</v>
       </c>
       <c r="AB10">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC10">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="AD10">
         <v>940</v>
@@ -3056,13 +3056,13 @@
         <v>15</v>
       </c>
       <c r="AH10">
-        <v>55</v>
+        <v>160</v>
       </c>
       <c r="AI10">
         <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK10">
         <v>14</v>
@@ -3077,7 +3077,7 @@
         <v>2.4</v>
       </c>
       <c r="AO10">
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="AP10">
         <v>32</v>
@@ -3128,13 +3128,13 @@
         <v>46</v>
       </c>
       <c r="BF10">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="BG10">
         <v>95</v>
       </c>
       <c r="BH10">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BI10">
         <v>5</v>
@@ -3143,55 +3143,55 @@
         <v>14</v>
       </c>
       <c r="BK10">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BN10">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BO10">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BP10">
         <v>6.2</v>
       </c>
       <c r="BQ10">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BR10">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BS10">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BT10">
         <v>23</v>
       </c>
       <c r="BU10">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ10">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="CA10">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="CB10" t="s">
         <v>142</v>
@@ -3214,22 +3214,22 @@
         <v>130</v>
       </c>
       <c r="F11">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G11">
         <v>2.32</v>
       </c>
       <c r="H11">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I11">
         <v>4.4</v>
       </c>
       <c r="J11">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K11">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L11">
         <v>1.48</v>
@@ -3238,34 +3238,34 @@
         <v>1.12</v>
       </c>
       <c r="N11">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="O11">
+        <v>1.54</v>
+      </c>
+      <c r="P11">
         <v>1.52</v>
       </c>
-      <c r="P11">
-        <v>1.56</v>
-      </c>
       <c r="Q11">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R11">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S11">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="T11">
         <v>2.1</v>
       </c>
       <c r="U11">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="V11">
         <v>1.29</v>
       </c>
       <c r="W11">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X11">
         <v>11</v>
@@ -3289,7 +3289,7 @@
         <v>18.5</v>
       </c>
       <c r="AE11">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AF11">
         <v>13.5</v>
@@ -3310,7 +3310,7 @@
         <v>38</v>
       </c>
       <c r="AL11">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM11">
         <v>220</v>
@@ -3328,31 +3328,31 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR11">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS11">
         <v>7.6</v>
       </c>
       <c r="AT11">
-        <v>6.2</v>
+        <v>3.8</v>
       </c>
       <c r="AU11">
         <v>6.2</v>
       </c>
       <c r="AV11">
-        <v>5.6</v>
+        <v>15.5</v>
       </c>
       <c r="AW11">
         <v>7.4</v>
       </c>
       <c r="AX11">
-        <v>5.1</v>
+        <v>10.5</v>
       </c>
       <c r="AY11">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="AZ11">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="BA11">
         <v>7.6</v>
@@ -3361,7 +3361,7 @@
         <v>6.6</v>
       </c>
       <c r="BC11">
-        <v>20</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD11">
         <v>7.2</v>
@@ -3379,13 +3379,13 @@
         <v>2.78</v>
       </c>
       <c r="BI11">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="BJ11">
         <v>12</v>
       </c>
       <c r="BK11">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BL11">
         <v>1000</v>
@@ -3397,10 +3397,10 @@
         <v>5</v>
       </c>
       <c r="BO11">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="BP11">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ11">
         <v>7.2</v>
@@ -3409,7 +3409,7 @@
         <v>65</v>
       </c>
       <c r="BS11">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT11">
         <v>7.4</v>
@@ -3421,19 +3421,19 @@
         <v>1000</v>
       </c>
       <c r="BW11">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX11">
+        <v>1000</v>
+      </c>
+      <c r="BY11">
+        <v>9.4</v>
+      </c>
+      <c r="BZ11">
+        <v>1000</v>
+      </c>
+      <c r="CA11">
         <v>9</v>
-      </c>
-      <c r="BX11">
-        <v>1000</v>
-      </c>
-      <c r="BY11">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BZ11">
-        <v>1000</v>
-      </c>
-      <c r="CA11">
-        <v>9.199999999999999</v>
       </c>
       <c r="CB11" t="s">
         <v>142</v>
@@ -3471,7 +3471,7 @@
         <v>6.2</v>
       </c>
       <c r="K12">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="L12">
         <v>1.25</v>
@@ -3480,28 +3480,28 @@
         <v>1.04</v>
       </c>
       <c r="N12">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O12">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P12">
+        <v>2.24</v>
+      </c>
+      <c r="Q12">
+        <v>1.61</v>
+      </c>
+      <c r="R12">
+        <v>1.49</v>
+      </c>
+      <c r="S12">
+        <v>2.64</v>
+      </c>
+      <c r="T12">
         <v>2.32</v>
       </c>
-      <c r="Q12">
-        <v>1.62</v>
-      </c>
-      <c r="R12">
-        <v>1.54</v>
-      </c>
-      <c r="S12">
-        <v>2.56</v>
-      </c>
-      <c r="T12">
-        <v>2.28</v>
-      </c>
       <c r="U12">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="V12">
         <v>1.05</v>
@@ -3510,22 +3510,22 @@
         <v>4.4</v>
       </c>
       <c r="X12">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y12">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="Z12">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AA12">
         <v>1000</v>
       </c>
       <c r="AB12">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AC12">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AD12">
         <v>65</v>
@@ -3534,7 +3534,7 @@
         <v>410</v>
       </c>
       <c r="AF12">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AG12">
         <v>14</v>
@@ -3555,25 +3555,25 @@
         <v>60</v>
       </c>
       <c r="AM12">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AN12">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AO12">
         <v>1000</v>
       </c>
       <c r="AP12">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AQ12">
+        <v>5.5</v>
+      </c>
+      <c r="AR12">
         <v>6</v>
       </c>
-      <c r="AR12">
-        <v>6.4</v>
-      </c>
       <c r="AS12">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AT12">
         <v>7.2</v>
@@ -3582,40 +3582,40 @@
         <v>13</v>
       </c>
       <c r="AV12">
+        <v>5.6</v>
+      </c>
+      <c r="AW12">
         <v>6</v>
       </c>
-      <c r="AW12">
-        <v>6.6</v>
-      </c>
       <c r="AX12">
-        <v>6.4</v>
+        <v>3.4</v>
       </c>
       <c r="AY12">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ12">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BA12">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BB12">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC12">
-        <v>12.5</v>
+        <v>4.6</v>
       </c>
       <c r="BD12">
+        <v>5.6</v>
+      </c>
+      <c r="BE12">
         <v>6</v>
-      </c>
-      <c r="BE12">
-        <v>6.4</v>
       </c>
       <c r="BF12">
         <v>4</v>
       </c>
       <c r="BG12">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BH12">
         <v>4.4</v>
@@ -3624,7 +3624,7 @@
         <v>3.7</v>
       </c>
       <c r="BJ12">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BK12">
         <v>6.2</v>
@@ -3633,13 +3633,13 @@
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN12">
         <v>3.7</v>
       </c>
       <c r="BO12">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="BP12">
         <v>7</v>
@@ -3651,10 +3651,10 @@
         <v>27</v>
       </c>
       <c r="BS12">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT12">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BU12">
         <v>6.8</v>
@@ -3663,19 +3663,19 @@
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ12">
         <v>11</v>
       </c>
       <c r="CA12">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="CB12" t="s">
         <v>142</v>
@@ -3701,7 +3701,7 @@
         <v>4.5</v>
       </c>
       <c r="G13">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H13">
         <v>1.98</v>
@@ -3719,19 +3719,19 @@
         <v>1.48</v>
       </c>
       <c r="M13">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N13">
         <v>3.1</v>
       </c>
       <c r="O13">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P13">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="Q13">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R13">
         <v>1.26</v>
@@ -3740,7 +3740,7 @@
         <v>4.3</v>
       </c>
       <c r="T13">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="U13">
         <v>1.86</v>
@@ -3758,31 +3758,31 @@
         <v>7.8</v>
       </c>
       <c r="Z13">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA13">
         <v>25</v>
       </c>
       <c r="AB13">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AC13">
         <v>7.6</v>
       </c>
       <c r="AD13">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE13">
+        <v>25</v>
+      </c>
+      <c r="AF13">
         <v>34</v>
       </c>
-      <c r="AF13">
-        <v>32</v>
-      </c>
       <c r="AG13">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="AH13">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="AI13">
         <v>48</v>
@@ -3791,7 +3791,7 @@
         <v>120</v>
       </c>
       <c r="AK13">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL13">
         <v>1000</v>
@@ -3803,19 +3803,19 @@
         <v>95</v>
       </c>
       <c r="AO13">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AP13">
         <v>9.800000000000001</v>
       </c>
       <c r="AQ13">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AR13">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AS13">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AT13">
         <v>12.5</v>
@@ -3824,13 +3824,13 @@
         <v>7</v>
       </c>
       <c r="AV13">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW13">
         <v>21</v>
       </c>
       <c r="AX13">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AY13">
         <v>14.5</v>
@@ -3857,7 +3857,7 @@
         <v>36</v>
       </c>
       <c r="BG13">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BH13">
         <v>3</v>
@@ -3940,7 +3940,7 @@
         <v>133</v>
       </c>
       <c r="F14">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G14">
         <v>2.32</v>
@@ -3955,10 +3955,10 @@
         <v>3.4</v>
       </c>
       <c r="K14">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L14">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M14">
         <v>1.09</v>
@@ -3970,22 +3970,22 @@
         <v>1.42</v>
       </c>
       <c r="P14">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q14">
         <v>2.22</v>
       </c>
       <c r="R14">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S14">
         <v>4.2</v>
       </c>
       <c r="T14">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="U14">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V14">
         <v>1.34</v>
@@ -3994,10 +3994,10 @@
         <v>1.76</v>
       </c>
       <c r="X14">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Y14">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z14">
         <v>27</v>
@@ -4006,7 +4006,7 @@
         <v>80</v>
       </c>
       <c r="AB14">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC14">
         <v>7.6</v>
@@ -4030,7 +4030,7 @@
         <v>65</v>
       </c>
       <c r="AJ14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK14">
         <v>28</v>
@@ -4039,13 +4039,13 @@
         <v>46</v>
       </c>
       <c r="AM14">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN14">
         <v>24</v>
       </c>
       <c r="AO14">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AP14">
         <v>9.800000000000001</v>
@@ -4054,10 +4054,10 @@
         <v>10.5</v>
       </c>
       <c r="AR14">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="AS14">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="AT14">
         <v>7.4</v>
@@ -4069,7 +4069,7 @@
         <v>14</v>
       </c>
       <c r="AW14">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="AX14">
         <v>12</v>
@@ -4078,46 +4078,46 @@
         <v>10</v>
       </c>
       <c r="AZ14">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="BA14">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="BB14">
-        <v>9.6</v>
+        <v>7.4</v>
       </c>
       <c r="BC14">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BD14">
-        <v>10.5</v>
+        <v>38</v>
       </c>
       <c r="BE14">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="BF14">
         <v>20</v>
       </c>
       <c r="BG14">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="BH14">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI14">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="BJ14">
         <v>10.5</v>
       </c>
       <c r="BK14">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BN14">
         <v>5</v>
@@ -4126,10 +4126,10 @@
         <v>3.95</v>
       </c>
       <c r="BP14">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ14">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BR14">
         <v>1000</v>
@@ -4138,7 +4138,7 @@
         <v>10.5</v>
       </c>
       <c r="BT14">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BU14">
         <v>5.4</v>
@@ -4147,13 +4147,13 @@
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BZ14">
         <v>1000</v>
@@ -4248,7 +4248,7 @@
         <v>560</v>
       </c>
       <c r="AB15">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC15">
         <v>11.5</v>
@@ -4260,7 +4260,7 @@
         <v>260</v>
       </c>
       <c r="AF15">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AG15">
         <v>12.5</v>
@@ -4284,7 +4284,7 @@
         <v>280</v>
       </c>
       <c r="AN15">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO15">
         <v>450</v>
@@ -4293,13 +4293,13 @@
         <v>12</v>
       </c>
       <c r="AQ15">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="AR15">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="AS15">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="AT15">
         <v>5.9</v>
@@ -4308,10 +4308,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV15">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="AW15">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="AX15">
         <v>6.4</v>
@@ -4320,10 +4320,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ15">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BA15">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BB15">
         <v>10</v>
@@ -4332,28 +4332,28 @@
         <v>14.5</v>
       </c>
       <c r="BD15">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BE15">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BF15">
         <v>7</v>
       </c>
       <c r="BG15">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BH15">
         <v>3.55</v>
       </c>
       <c r="BI15">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="BJ15">
         <v>13.5</v>
       </c>
       <c r="BK15">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BL15">
         <v>1000</v>
@@ -4424,58 +4424,58 @@
         <v>135</v>
       </c>
       <c r="F16">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="G16">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="H16">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I16">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J16">
         <v>3.95</v>
       </c>
       <c r="K16">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L16">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M16">
         <v>1.05</v>
       </c>
       <c r="N16">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O16">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P16">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="Q16">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="R16">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S16">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="T16">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="U16">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="V16">
         <v>1.27</v>
       </c>
       <c r="W16">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X16">
         <v>22</v>
@@ -4499,7 +4499,7 @@
         <v>21</v>
       </c>
       <c r="AE16">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF16">
         <v>14</v>
@@ -4511,7 +4511,7 @@
         <v>21</v>
       </c>
       <c r="AI16">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ16">
         <v>23</v>
@@ -4520,22 +4520,22 @@
         <v>21</v>
       </c>
       <c r="AL16">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM16">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN16">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO16">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP16">
         <v>1.03</v>
       </c>
       <c r="AQ16">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AR16">
         <v>1.03</v>
@@ -4547,10 +4547,10 @@
         <v>1.03</v>
       </c>
       <c r="AU16">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV16">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AW16">
         <v>1.03</v>
@@ -4559,19 +4559,19 @@
         <v>1.03</v>
       </c>
       <c r="AY16">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BA16">
         <v>1.03</v>
       </c>
       <c r="BB16">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC16">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BD16">
         <v>1.03</v>
@@ -4595,13 +4595,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK16">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BN16">
         <v>4.9</v>
@@ -4613,37 +4613,37 @@
         <v>13</v>
       </c>
       <c r="BQ16">
-        <v>9.6</v>
+        <v>5.7</v>
       </c>
       <c r="BR16">
         <v>26</v>
       </c>
       <c r="BS16">
-        <v>18.5</v>
+        <v>7.4</v>
       </c>
       <c r="BT16">
         <v>8.4</v>
       </c>
       <c r="BU16">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>30</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ16">
         <v>20</v>
       </c>
       <c r="CA16">
-        <v>14.5</v>
+        <v>6.8</v>
       </c>
       <c r="CB16" t="s">
         <v>142</v>
@@ -4672,7 +4672,7 @@
         <v>2.3</v>
       </c>
       <c r="H17">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I17">
         <v>3.9</v>
@@ -4681,7 +4681,7 @@
         <v>3.35</v>
       </c>
       <c r="K17">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L17">
         <v>1.49</v>
@@ -4690,13 +4690,13 @@
         <v>1.09</v>
       </c>
       <c r="N17">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O17">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P17">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q17">
         <v>2.24</v>
@@ -4711,13 +4711,13 @@
         <v>1.95</v>
       </c>
       <c r="U17">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="V17">
         <v>1.34</v>
       </c>
       <c r="W17">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="X17">
         <v>12.5</v>
@@ -4732,7 +4732,7 @@
         <v>85</v>
       </c>
       <c r="AB17">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC17">
         <v>8.6</v>
@@ -4744,7 +4744,7 @@
         <v>60</v>
       </c>
       <c r="AF17">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AG17">
         <v>12.5</v>
@@ -4783,10 +4783,10 @@
         <v>21</v>
       </c>
       <c r="AS17">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT17">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU17">
         <v>6.6</v>
@@ -4795,7 +4795,7 @@
         <v>13.5</v>
       </c>
       <c r="AW17">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AX17">
         <v>12</v>
@@ -4804,28 +4804,28 @@
         <v>10</v>
       </c>
       <c r="AZ17">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BA17">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BB17">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BC17">
         <v>21</v>
       </c>
       <c r="BD17">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE17">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF17">
         <v>19.5</v>
       </c>
       <c r="BG17">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BH17">
         <v>3.05</v>
@@ -4837,13 +4837,13 @@
         <v>10.5</v>
       </c>
       <c r="BK17">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>21</v>
+        <v>1.04</v>
       </c>
       <c r="BN17">
         <v>5</v>
@@ -4855,13 +4855,13 @@
         <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>14</v>
+        <v>1.04</v>
       </c>
       <c r="BR17">
         <v>1000</v>
       </c>
       <c r="BS17">
-        <v>26</v>
+        <v>1.04</v>
       </c>
       <c r="BT17">
         <v>6.8</v>
@@ -4873,19 +4873,19 @@
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>23</v>
+        <v>1.04</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>34</v>
+        <v>1.04</v>
       </c>
       <c r="BZ17">
         <v>1000</v>
       </c>
       <c r="CA17">
-        <v>26</v>
+        <v>1.04</v>
       </c>
       <c r="CB17" t="s">
         <v>142</v>
@@ -4914,13 +4914,13 @@
         <v>2.1</v>
       </c>
       <c r="H18">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="I18">
         <v>4</v>
       </c>
       <c r="J18">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K18">
         <v>3.95</v>
@@ -4932,40 +4932,40 @@
         <v>1.05</v>
       </c>
       <c r="N18">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O18">
         <v>1.27</v>
       </c>
       <c r="P18">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="Q18">
         <v>1.81</v>
       </c>
       <c r="R18">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S18">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T18">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U18">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V18">
         <v>1.34</v>
       </c>
       <c r="W18">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="X18">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="Y18">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z18">
         <v>36</v>
@@ -4977,16 +4977,16 @@
         <v>11.5</v>
       </c>
       <c r="AC18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD18">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE18">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AF18">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG18">
         <v>11</v>
@@ -4995,25 +4995,25 @@
         <v>21</v>
       </c>
       <c r="AI18">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AJ18">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK18">
         <v>22</v>
       </c>
       <c r="AL18">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM18">
         <v>95</v>
       </c>
       <c r="AN18">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AO18">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AP18">
         <v>15.5</v>
@@ -5022,13 +5022,13 @@
         <v>14</v>
       </c>
       <c r="AR18">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS18">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AT18">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AU18">
         <v>7.8</v>
@@ -5037,97 +5037,97 @@
         <v>13.5</v>
       </c>
       <c r="AW18">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AX18">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY18">
         <v>9.6</v>
       </c>
       <c r="AZ18">
-        <v>15</v>
+        <v>6.6</v>
       </c>
       <c r="BA18">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC18">
         <v>17.5</v>
       </c>
       <c r="BD18">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE18">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF18">
         <v>10.5</v>
       </c>
       <c r="BG18">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH18">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BI18">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BJ18">
         <v>9.199999999999999</v>
       </c>
       <c r="BK18">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="BN18">
         <v>5</v>
       </c>
       <c r="BO18">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP18">
         <v>14.5</v>
       </c>
       <c r="BQ18">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="BR18">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BS18">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="BT18">
         <v>7.4</v>
       </c>
       <c r="BU18">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="BV18">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BW18">
-        <v>20</v>
+        <v>9.6</v>
       </c>
       <c r="BX18">
         <v>38</v>
       </c>
       <c r="BY18">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="BZ18">
         <v>21</v>
       </c>
       <c r="CA18">
-        <v>14</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB18" t="s">
         <v>142</v>
@@ -5150,22 +5150,22 @@
         <v>138</v>
       </c>
       <c r="F19">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="G19">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H19">
         <v>3.95</v>
       </c>
       <c r="I19">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J19">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K19">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L19">
         <v>1.37</v>
@@ -5180,7 +5180,7 @@
         <v>1.27</v>
       </c>
       <c r="P19">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q19">
         <v>1.8</v>
@@ -5198,22 +5198,22 @@
         <v>2.26</v>
       </c>
       <c r="V19">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W19">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="X19">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="Y19">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z19">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA19">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB19">
         <v>11</v>
@@ -5222,154 +5222,154 @@
         <v>9</v>
       </c>
       <c r="AD19">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AE19">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AF19">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG19">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH19">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI19">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ19">
         <v>25</v>
       </c>
       <c r="AK19">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL19">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM19">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AN19">
         <v>12</v>
       </c>
       <c r="AO19">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AP19">
+        <v>7.8</v>
+      </c>
+      <c r="AQ19">
         <v>15.5</v>
       </c>
-      <c r="AQ19">
-        <v>14</v>
-      </c>
       <c r="AR19">
-        <v>6.8</v>
+        <v>27</v>
       </c>
       <c r="AS19">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="AT19">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU19">
         <v>8</v>
       </c>
       <c r="AV19">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW19">
-        <v>7.4</v>
+        <v>40</v>
       </c>
       <c r="AX19">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY19">
         <v>9.4</v>
       </c>
       <c r="AZ19">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA19">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="BB19">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC19">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD19">
-        <v>6.8</v>
+        <v>28</v>
       </c>
       <c r="BE19">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="BF19">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG19">
-        <v>7.2</v>
+        <v>34</v>
       </c>
       <c r="BH19">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BI19">
-        <v>3.45</v>
+        <v>2.96</v>
       </c>
       <c r="BJ19">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BK19">
-        <v>8.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>21</v>
+        <v>9.6</v>
       </c>
       <c r="BN19">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BO19">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BP19">
         <v>14.5</v>
       </c>
       <c r="BQ19">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BR19">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BS19">
-        <v>15.5</v>
+        <v>7.4</v>
       </c>
       <c r="BT19">
         <v>7.8</v>
       </c>
       <c r="BU19">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="BV19">
         <v>32</v>
       </c>
       <c r="BW19">
-        <v>18.5</v>
+        <v>7.8</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>21</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ19">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CA19">
-        <v>12.5</v>
+        <v>7</v>
       </c>
       <c r="CB19" t="s">
         <v>142</v>
@@ -5392,7 +5392,7 @@
         <v>139</v>
       </c>
       <c r="F20">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G20">
         <v>1.85</v>
@@ -5401,7 +5401,7 @@
         <v>4.3</v>
       </c>
       <c r="I20">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J20">
         <v>4.3</v>
@@ -5410,7 +5410,7 @@
         <v>4.7</v>
       </c>
       <c r="L20">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M20">
         <v>1.03</v>
@@ -5425,19 +5425,19 @@
         <v>2.78</v>
       </c>
       <c r="Q20">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R20">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="S20">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="T20">
         <v>1.55</v>
       </c>
       <c r="U20">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V20">
         <v>1.28</v>
@@ -5449,10 +5449,10 @@
         <v>32</v>
       </c>
       <c r="Y20">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Z20">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AA20">
         <v>95</v>
@@ -5464,7 +5464,7 @@
         <v>11</v>
       </c>
       <c r="AD20">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE20">
         <v>48</v>
@@ -5473,13 +5473,13 @@
         <v>15.5</v>
       </c>
       <c r="AG20">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH20">
         <v>17</v>
       </c>
       <c r="AI20">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ20">
         <v>24</v>
@@ -5497,7 +5497,7 @@
         <v>7.2</v>
       </c>
       <c r="AO20">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AP20">
         <v>7.2</v>
@@ -5515,7 +5515,7 @@
         <v>12.5</v>
       </c>
       <c r="AU20">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV20">
         <v>15.5</v>
@@ -5545,7 +5545,7 @@
         <v>21</v>
       </c>
       <c r="BE20">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF20">
         <v>6.4</v>
@@ -5557,7 +5557,7 @@
         <v>4.8</v>
       </c>
       <c r="BI20">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="BJ20">
         <v>8.800000000000001</v>
@@ -5569,7 +5569,7 @@
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="BN20">
         <v>5.1</v>
@@ -5587,7 +5587,7 @@
         <v>19.5</v>
       </c>
       <c r="BS20">
-        <v>12.5</v>
+        <v>8.6</v>
       </c>
       <c r="BT20">
         <v>8.199999999999999</v>
@@ -5599,13 +5599,13 @@
         <v>29</v>
       </c>
       <c r="BW20">
-        <v>17.5</v>
+        <v>10</v>
       </c>
       <c r="BX20">
         <v>32</v>
       </c>
       <c r="BY20">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="BZ20">
         <v>13</v>
@@ -5637,10 +5637,10 @@
         <v>4</v>
       </c>
       <c r="G21">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H21">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="I21">
         <v>1.88</v>
@@ -5649,7 +5649,7 @@
         <v>4.4</v>
       </c>
       <c r="K21">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L21">
         <v>1.24</v>
@@ -5676,10 +5676,10 @@
         <v>2.06</v>
       </c>
       <c r="T21">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="U21">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="V21">
         <v>2.14</v>
@@ -5700,7 +5700,7 @@
         <v>24</v>
       </c>
       <c r="AB21">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AC21">
         <v>11.5</v>
@@ -5733,7 +5733,7 @@
         <v>38</v>
       </c>
       <c r="AM21">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AN21">
         <v>24</v>
@@ -5754,10 +5754,10 @@
         <v>20</v>
       </c>
       <c r="AT21">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AU21">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV21">
         <v>10</v>
@@ -5766,7 +5766,7 @@
         <v>14.5</v>
       </c>
       <c r="AX21">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY21">
         <v>16</v>
@@ -5796,64 +5796,64 @@
         <v>6</v>
       </c>
       <c r="BH21">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BI21">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="BJ21">
         <v>8.800000000000001</v>
       </c>
       <c r="BK21">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BL21">
         <v>65</v>
       </c>
       <c r="BM21">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BN21">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BO21">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BP21">
         <v>27</v>
       </c>
       <c r="BQ21">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR21">
         <v>29</v>
       </c>
       <c r="BS21">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT21">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BU21">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BV21">
         <v>12</v>
       </c>
       <c r="BW21">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BX21">
         <v>19</v>
       </c>
       <c r="BY21">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BZ21">
         <v>12</v>
       </c>
       <c r="CA21">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="CB21" t="s">
         <v>142</v>
@@ -5885,7 +5885,7 @@
         <v>3.2</v>
       </c>
       <c r="I22">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J22">
         <v>4.2</v>
@@ -5894,7 +5894,7 @@
         <v>4.4</v>
       </c>
       <c r="L22">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="M22">
         <v>1.02</v>
@@ -5906,25 +5906,25 @@
         <v>1.12</v>
       </c>
       <c r="P22">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="Q22">
         <v>1.39</v>
       </c>
       <c r="R22">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="S22">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="T22">
         <v>1.4</v>
       </c>
       <c r="U22">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="V22">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W22">
         <v>1.84</v>
@@ -5981,7 +5981,7 @@
         <v>7.6</v>
       </c>
       <c r="AO22">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AP22">
         <v>32</v>
@@ -6011,7 +6011,7 @@
         <v>19</v>
       </c>
       <c r="AY22">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ22">
         <v>12</v>
@@ -6023,7 +6023,7 @@
         <v>27</v>
       </c>
       <c r="BC22">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD22">
         <v>19</v>
@@ -6032,34 +6032,34 @@
         <v>34</v>
       </c>
       <c r="BF22">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BG22">
         <v>12.5</v>
       </c>
       <c r="BH22">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BI22">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="BJ22">
+        <v>8.6</v>
+      </c>
+      <c r="BK22">
+        <v>4.5</v>
+      </c>
+      <c r="BL22">
+        <v>1000</v>
+      </c>
+      <c r="BM22">
         <v>8.199999999999999</v>
       </c>
-      <c r="BK22">
-        <v>7</v>
-      </c>
-      <c r="BL22">
-        <v>1000</v>
-      </c>
-      <c r="BM22">
-        <v>21</v>
-      </c>
       <c r="BN22">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BO22">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="BP22">
         <v>14</v>
@@ -6071,25 +6071,25 @@
         <v>19</v>
       </c>
       <c r="BS22">
-        <v>11</v>
+        <v>6.4</v>
       </c>
       <c r="BT22">
         <v>7.8</v>
       </c>
       <c r="BU22">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="BV22">
         <v>21</v>
       </c>
       <c r="BW22">
-        <v>15</v>
+        <v>6.6</v>
       </c>
       <c r="BX22">
         <v>24</v>
       </c>
       <c r="BY22">
-        <v>16.5</v>
+        <v>6.8</v>
       </c>
       <c r="BZ22">
         <v>11.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
@@ -442,7 +442,7 @@
     <t>Chicago Fire</t>
   </si>
   <si>
-    <t>2026-07-21 11:21:35</t>
+    <t>2026-07-21 13:28:27</t>
   </si>
 </sst>
 </file>
@@ -1036,22 +1036,22 @@
         <v>121</v>
       </c>
       <c r="F2">
+        <v>1.97</v>
+      </c>
+      <c r="G2">
         <v>2.04</v>
       </c>
-      <c r="G2">
-        <v>2.08</v>
-      </c>
       <c r="H2">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I2">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="J2">
         <v>3.55</v>
       </c>
       <c r="K2">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L2">
         <v>1.44</v>
@@ -1063,31 +1063,31 @@
         <v>3.6</v>
       </c>
       <c r="O2">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P2">
         <v>1.87</v>
       </c>
       <c r="Q2">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R2">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S2">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="T2">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U2">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V2">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W2">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="X2">
         <v>13</v>
@@ -1099,13 +1099,13 @@
         <v>32</v>
       </c>
       <c r="AA2">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AB2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC2">
         <v>9</v>
-      </c>
-      <c r="AC2">
-        <v>8.800000000000001</v>
       </c>
       <c r="AD2">
         <v>17.5</v>
@@ -1120,16 +1120,16 @@
         <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI2">
         <v>70</v>
       </c>
       <c r="AJ2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL2">
         <v>40</v>
@@ -1138,10 +1138,10 @@
         <v>120</v>
       </c>
       <c r="AN2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO2">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AP2">
         <v>11.5</v>
@@ -1153,7 +1153,7 @@
         <v>27</v>
       </c>
       <c r="AS2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AT2">
         <v>7.6</v>
@@ -1195,67 +1195,67 @@
         <v>14.5</v>
       </c>
       <c r="BG2">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BH2">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BI2">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="BJ2">
         <v>10</v>
       </c>
       <c r="BK2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="BN2">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO2">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="BP2">
         <v>14.5</v>
       </c>
       <c r="BQ2">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="BR2">
         <v>30</v>
       </c>
       <c r="BS2">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BT2">
         <v>7.6</v>
       </c>
       <c r="BU2">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BV2">
         <v>38</v>
       </c>
       <c r="BW2">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="CA2">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="CB2" t="s">
         <v>142</v>
@@ -1278,22 +1278,22 @@
         <v>122</v>
       </c>
       <c r="F3">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="G3">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H3">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I3">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J3">
         <v>3.1</v>
       </c>
       <c r="K3">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L3">
         <v>1.52</v>
@@ -1302,13 +1302,13 @@
         <v>1.11</v>
       </c>
       <c r="N3">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O3">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P3">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="Q3">
         <v>2.44</v>
@@ -1317,25 +1317,25 @@
         <v>1.24</v>
       </c>
       <c r="S3">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T3">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="U3">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V3">
         <v>1.42</v>
       </c>
       <c r="W3">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X3">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="Y3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z3">
         <v>21</v>
@@ -1368,7 +1368,7 @@
         <v>65</v>
       </c>
       <c r="AJ3">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AK3">
         <v>36</v>
@@ -1377,31 +1377,31 @@
         <v>60</v>
       </c>
       <c r="AM3">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN3">
         <v>34</v>
       </c>
       <c r="AO3">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AP3">
         <v>8.800000000000001</v>
       </c>
       <c r="AQ3">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR3">
         <v>17.5</v>
       </c>
       <c r="AS3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT3">
         <v>8</v>
       </c>
       <c r="AU3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV3">
         <v>13</v>
@@ -1416,28 +1416,28 @@
         <v>11</v>
       </c>
       <c r="AZ3">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA3">
         <v>48</v>
       </c>
       <c r="BB3">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BC3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD3">
         <v>40</v>
       </c>
       <c r="BE3">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BF3">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BG3">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BH3">
         <v>2.96</v>
@@ -1449,13 +1449,13 @@
         <v>11</v>
       </c>
       <c r="BK3">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BL3">
         <v>170</v>
       </c>
       <c r="BM3">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BN3">
         <v>5.5</v>
@@ -1467,13 +1467,13 @@
         <v>23</v>
       </c>
       <c r="BQ3">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BR3">
         <v>42</v>
       </c>
       <c r="BS3">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BT3">
         <v>6.4</v>
@@ -1485,19 +1485,19 @@
         <v>29</v>
       </c>
       <c r="BW3">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BX3">
         <v>48</v>
       </c>
       <c r="BY3">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ3">
         <v>42</v>
       </c>
       <c r="CA3">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="CB3" t="s">
         <v>142</v>
@@ -1520,76 +1520,76 @@
         <v>123</v>
       </c>
       <c r="F4">
+        <v>1.37</v>
+      </c>
+      <c r="G4">
         <v>1.38</v>
       </c>
-      <c r="G4">
-        <v>1.39</v>
-      </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I4">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="J4">
         <v>6</v>
       </c>
       <c r="K4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="L4">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M4">
         <v>1.04</v>
       </c>
       <c r="N4">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O4">
         <v>1.21</v>
       </c>
       <c r="P4">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="Q4">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="R4">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="S4">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="T4">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="U4">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V4">
         <v>1.12</v>
       </c>
       <c r="W4">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="X4">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Y4">
         <v>32</v>
       </c>
       <c r="Z4">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AA4">
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="AB4">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC4">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AD4">
         <v>32</v>
@@ -1598,34 +1598,34 @@
         <v>130</v>
       </c>
       <c r="AF4">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG4">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH4">
         <v>29</v>
       </c>
       <c r="AI4">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ4">
         <v>11.5</v>
       </c>
       <c r="AK4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL4">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM4">
         <v>140</v>
       </c>
       <c r="AN4">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AO4">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AP4">
         <v>22</v>
@@ -1634,22 +1634,22 @@
         <v>27</v>
       </c>
       <c r="AR4">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AS4">
         <v>55</v>
       </c>
       <c r="AT4">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU4">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AV4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AW4">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="AX4">
         <v>8</v>
@@ -1661,7 +1661,7 @@
         <v>24</v>
       </c>
       <c r="BA4">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="BB4">
         <v>10.5</v>
@@ -1670,34 +1670,34 @@
         <v>12.5</v>
       </c>
       <c r="BD4">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BE4">
         <v>44</v>
       </c>
       <c r="BF4">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BG4">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="BH4">
         <v>4.3</v>
       </c>
       <c r="BI4">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BJ4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BN4">
         <v>3.9</v>
@@ -1709,13 +1709,13 @@
         <v>8</v>
       </c>
       <c r="BQ4">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BR4">
         <v>22</v>
       </c>
       <c r="BS4">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BT4">
         <v>12.5</v>
@@ -1727,19 +1727,19 @@
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BX4">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BY4">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BZ4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CA4">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="CB4" t="s">
         <v>142</v>
@@ -1762,7 +1762,7 @@
         <v>124</v>
       </c>
       <c r="F5">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="G5">
         <v>1.71</v>
@@ -1771,19 +1771,19 @@
         <v>5.1</v>
       </c>
       <c r="I5">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J5">
         <v>4.4</v>
       </c>
       <c r="K5">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L5">
         <v>1.32</v>
       </c>
       <c r="M5">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N5">
         <v>5.1</v>
@@ -1795,10 +1795,10 @@
         <v>2.38</v>
       </c>
       <c r="Q5">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R5">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="S5">
         <v>2.76</v>
@@ -1810,7 +1810,7 @@
         <v>2.3</v>
       </c>
       <c r="V5">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W5">
         <v>2.4</v>
@@ -1912,7 +1912,7 @@
         <v>14</v>
       </c>
       <c r="BD5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE5">
         <v>60</v>
@@ -1921,10 +1921,10 @@
         <v>7.2</v>
       </c>
       <c r="BG5">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BH5">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI5">
         <v>3.3</v>
@@ -1933,37 +1933,37 @@
         <v>10</v>
       </c>
       <c r="BK5">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL5">
         <v>110</v>
       </c>
       <c r="BM5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN5">
         <v>4.7</v>
       </c>
       <c r="BO5">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="BP5">
         <v>11.5</v>
       </c>
       <c r="BQ5">
-        <v>5.3</v>
+        <v>8.4</v>
       </c>
       <c r="BR5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BS5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BT5">
         <v>9.199999999999999</v>
       </c>
       <c r="BU5">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BV5">
         <v>42</v>
@@ -1975,10 +1975,10 @@
         <v>46</v>
       </c>
       <c r="BY5">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ5">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="CA5">
         <v>6.2</v>
@@ -2013,7 +2013,7 @@
         <v>2.66</v>
       </c>
       <c r="I6">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="J6">
         <v>3.1</v>
@@ -2022,7 +2022,7 @@
         <v>3.25</v>
       </c>
       <c r="L6">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M6">
         <v>1.11</v>
@@ -2034,7 +2034,7 @@
         <v>1.49</v>
       </c>
       <c r="P6">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q6">
         <v>2.46</v>
@@ -2067,7 +2067,7 @@
         <v>19.5</v>
       </c>
       <c r="AA6">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB6">
         <v>9.4</v>
@@ -2082,7 +2082,7 @@
         <v>38</v>
       </c>
       <c r="AF6">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AG6">
         <v>15.5</v>
@@ -2109,7 +2109,7 @@
         <v>55</v>
       </c>
       <c r="AO6">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AP6">
         <v>9</v>
@@ -2121,10 +2121,10 @@
         <v>14.5</v>
       </c>
       <c r="AS6">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT6">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU6">
         <v>6.4</v>
@@ -2133,7 +2133,7 @@
         <v>11.5</v>
       </c>
       <c r="AW6">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX6">
         <v>16.5</v>
@@ -2148,13 +2148,13 @@
         <v>10.5</v>
       </c>
       <c r="BB6">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BC6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BD6">
         <v>10</v>
-      </c>
-      <c r="BD6">
-        <v>10.5</v>
       </c>
       <c r="BE6">
         <v>11.5</v>
@@ -2163,16 +2163,16 @@
         <v>10</v>
       </c>
       <c r="BG6">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH6">
         <v>2.84</v>
       </c>
       <c r="BI6">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="BJ6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK6">
         <v>6.6</v>
@@ -2181,7 +2181,7 @@
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BN6">
         <v>6</v>
@@ -2193,13 +2193,13 @@
         <v>28</v>
       </c>
       <c r="BQ6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BT6">
         <v>5.5</v>
@@ -2211,19 +2211,19 @@
         <v>24</v>
       </c>
       <c r="BW6">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX6">
         <v>44</v>
       </c>
       <c r="BY6">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BZ6">
         <v>44</v>
       </c>
       <c r="CA6">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CB6" t="s">
         <v>142</v>
@@ -2252,34 +2252,34 @@
         <v>5</v>
       </c>
       <c r="H7">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="I7">
         <v>1.95</v>
       </c>
       <c r="J7">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K7">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L7">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="M7">
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O7">
         <v>1.39</v>
       </c>
       <c r="P7">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q7">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R7">
         <v>1.3</v>
@@ -2288,10 +2288,10 @@
         <v>4</v>
       </c>
       <c r="T7">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U7">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V7">
         <v>2.04</v>
@@ -2309,19 +2309,19 @@
         <v>11</v>
       </c>
       <c r="AA7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB7">
         <v>15</v>
       </c>
       <c r="AC7">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD7">
         <v>10.5</v>
       </c>
       <c r="AE7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF7">
         <v>40</v>
@@ -2363,16 +2363,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AS7">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AT7">
         <v>13</v>
       </c>
       <c r="AU7">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV7">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW7">
         <v>18.5</v>
@@ -2384,7 +2384,7 @@
         <v>16.5</v>
       </c>
       <c r="AZ7">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA7">
         <v>36</v>
@@ -2453,7 +2453,7 @@
         <v>14</v>
       </c>
       <c r="BW7">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="BX7">
         <v>32</v>
@@ -2462,7 +2462,7 @@
         <v>10</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA7">
         <v>10</v>
@@ -2497,13 +2497,13 @@
         <v>4.7</v>
       </c>
       <c r="I8">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J8">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K8">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L8">
         <v>1.5</v>
@@ -2512,7 +2512,7 @@
         <v>1.1</v>
       </c>
       <c r="N8">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="O8">
         <v>1.45</v>
@@ -2521,7 +2521,7 @@
         <v>1.68</v>
       </c>
       <c r="Q8">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R8">
         <v>1.25</v>
@@ -2530,13 +2530,13 @@
         <v>4.5</v>
       </c>
       <c r="T8">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U8">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="V8">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W8">
         <v>2</v>
@@ -2548,16 +2548,16 @@
         <v>14</v>
       </c>
       <c r="Z8">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA8">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB8">
         <v>7.2</v>
       </c>
       <c r="AC8">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD8">
         <v>22</v>
@@ -2590,7 +2590,7 @@
         <v>190</v>
       </c>
       <c r="AN8">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AO8">
         <v>140</v>
@@ -2608,7 +2608,7 @@
         <v>10</v>
       </c>
       <c r="AT8">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU8">
         <v>7.2</v>
@@ -2617,13 +2617,13 @@
         <v>17</v>
       </c>
       <c r="AW8">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX8">
         <v>9.4</v>
       </c>
       <c r="AY8">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ8">
         <v>20</v>
@@ -2638,10 +2638,10 @@
         <v>18</v>
       </c>
       <c r="BD8">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BE8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF8">
         <v>16</v>
@@ -2650,7 +2650,7 @@
         <v>10</v>
       </c>
       <c r="BH8">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="BI8">
         <v>2.72</v>
@@ -2659,13 +2659,13 @@
         <v>11</v>
       </c>
       <c r="BK8">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BN8">
         <v>4.4</v>
@@ -2677,13 +2677,13 @@
         <v>14.5</v>
       </c>
       <c r="BQ8">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR8">
         <v>36</v>
       </c>
       <c r="BS8">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT8">
         <v>8.199999999999999</v>
@@ -2695,13 +2695,13 @@
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
@@ -2733,19 +2733,19 @@
         <v>3.35</v>
       </c>
       <c r="G9">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H9">
         <v>2.18</v>
       </c>
       <c r="I9">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="J9">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="K9">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L9">
         <v>1.3</v>
@@ -2763,10 +2763,10 @@
         <v>2.52</v>
       </c>
       <c r="Q9">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R9">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S9">
         <v>2.48</v>
@@ -2775,7 +2775,7 @@
         <v>1.55</v>
       </c>
       <c r="U9">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="V9">
         <v>1.67</v>
@@ -2811,7 +2811,7 @@
         <v>32</v>
       </c>
       <c r="AG9">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH9">
         <v>14.5</v>
@@ -2820,7 +2820,7 @@
         <v>28</v>
       </c>
       <c r="AJ9">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK9">
         <v>34</v>
@@ -2886,7 +2886,7 @@
         <v>48</v>
       </c>
       <c r="BF9">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BG9">
         <v>9.800000000000001</v>
@@ -2901,13 +2901,13 @@
         <v>8.6</v>
       </c>
       <c r="BK9">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN9">
         <v>7</v>
@@ -2919,13 +2919,13 @@
         <v>23</v>
       </c>
       <c r="BQ9">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BR9">
         <v>28</v>
       </c>
       <c r="BS9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT9">
         <v>5.5</v>
@@ -2937,10 +2937,10 @@
         <v>14.5</v>
       </c>
       <c r="BW9">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BX9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BY9">
         <v>9.800000000000001</v>
@@ -2975,22 +2975,22 @@
         <v>1.13</v>
       </c>
       <c r="G10">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="H10">
         <v>27</v>
       </c>
       <c r="I10">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J10">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="K10">
         <v>13</v>
       </c>
       <c r="L10">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="M10">
         <v>1.01</v>
@@ -3032,7 +3032,7 @@
         <v>940</v>
       </c>
       <c r="Z10">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AA10">
         <v>1000</v>
@@ -3056,7 +3056,7 @@
         <v>15</v>
       </c>
       <c r="AH10">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AI10">
         <v>1000</v>
@@ -3229,7 +3229,7 @@
         <v>2.98</v>
       </c>
       <c r="K11">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L11">
         <v>1.48</v>
@@ -3244,16 +3244,16 @@
         <v>1.54</v>
       </c>
       <c r="P11">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="Q11">
         <v>2.62</v>
       </c>
       <c r="R11">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S11">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T11">
         <v>2.1</v>
@@ -3385,7 +3385,7 @@
         <v>12</v>
       </c>
       <c r="BK11">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BL11">
         <v>1000</v>
@@ -3474,10 +3474,10 @@
         <v>7.4</v>
       </c>
       <c r="L12">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="M12">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N12">
         <v>4.6</v>
@@ -3486,22 +3486,22 @@
         <v>1.22</v>
       </c>
       <c r="P12">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q12">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="R12">
         <v>1.49</v>
       </c>
       <c r="S12">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="T12">
         <v>2.32</v>
       </c>
       <c r="U12">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="V12">
         <v>1.05</v>
@@ -3698,22 +3698,22 @@
         <v>132</v>
       </c>
       <c r="F13">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="G13">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="H13">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="I13">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="J13">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K13">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L13">
         <v>1.48</v>
@@ -3722,79 +3722,79 @@
         <v>1.09</v>
       </c>
       <c r="N13">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O13">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P13">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q13">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R13">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S13">
         <v>4.3</v>
       </c>
       <c r="T13">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U13">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="V13">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="W13">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="X13">
         <v>11</v>
       </c>
       <c r="Y13">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Z13">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AA13">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AB13">
         <v>14.5</v>
       </c>
       <c r="AC13">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AD13">
         <v>10.5</v>
       </c>
       <c r="AE13">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AF13">
         <v>34</v>
       </c>
       <c r="AG13">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH13">
         <v>22</v>
       </c>
       <c r="AI13">
-        <v>48</v>
+        <v>170</v>
       </c>
       <c r="AJ13">
         <v>120</v>
       </c>
       <c r="AK13">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AL13">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM13">
         <v>1000</v>
@@ -3803,37 +3803,37 @@
         <v>95</v>
       </c>
       <c r="AO13">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AP13">
         <v>9.800000000000001</v>
       </c>
       <c r="AQ13">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AR13">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AS13">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AT13">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU13">
         <v>7</v>
       </c>
       <c r="AV13">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AW13">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX13">
         <v>29</v>
       </c>
       <c r="AY13">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AZ13">
         <v>19.5</v>
@@ -3857,13 +3857,13 @@
         <v>36</v>
       </c>
       <c r="BG13">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BH13">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BI13">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BJ13">
         <v>11</v>
@@ -3878,16 +3878,16 @@
         <v>16.5</v>
       </c>
       <c r="BN13">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BO13">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BP13">
         <v>55</v>
       </c>
       <c r="BQ13">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BR13">
         <v>75</v>
@@ -3896,25 +3896,25 @@
         <v>14</v>
       </c>
       <c r="BT13">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BU13">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BV13">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BW13">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BX13">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="BY13">
         <v>11.5</v>
       </c>
       <c r="BZ13">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA13">
         <v>11.5</v>
@@ -3955,7 +3955,7 @@
         <v>3.4</v>
       </c>
       <c r="K14">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L14">
         <v>1.48</v>
@@ -3964,7 +3964,7 @@
         <v>1.09</v>
       </c>
       <c r="N14">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O14">
         <v>1.42</v>
@@ -3973,16 +3973,16 @@
         <v>1.78</v>
       </c>
       <c r="Q14">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="R14">
         <v>1.29</v>
       </c>
       <c r="S14">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T14">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U14">
         <v>1.98</v>
@@ -4009,7 +4009,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AC14">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD14">
         <v>950</v>
@@ -4045,7 +4045,7 @@
         <v>24</v>
       </c>
       <c r="AO14">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AP14">
         <v>9.800000000000001</v>
@@ -4054,10 +4054,10 @@
         <v>10.5</v>
       </c>
       <c r="AR14">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS14">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT14">
         <v>7.4</v>
@@ -4081,25 +4081,25 @@
         <v>17</v>
       </c>
       <c r="BA14">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB14">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC14">
-        <v>7.2</v>
+        <v>23</v>
       </c>
       <c r="BD14">
         <v>38</v>
       </c>
       <c r="BE14">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BF14">
         <v>20</v>
       </c>
       <c r="BG14">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH14">
         <v>3.05</v>
@@ -4200,7 +4200,7 @@
         <v>4.9</v>
       </c>
       <c r="L15">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M15">
         <v>1.07</v>
@@ -4212,10 +4212,10 @@
         <v>1.34</v>
       </c>
       <c r="P15">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q15">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R15">
         <v>1.33</v>
@@ -4230,7 +4230,7 @@
         <v>1.66</v>
       </c>
       <c r="V15">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W15">
         <v>3.2</v>
@@ -4347,7 +4347,7 @@
         <v>3.55</v>
       </c>
       <c r="BI15">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BJ15">
         <v>13.5</v>
@@ -4424,7 +4424,7 @@
         <v>135</v>
       </c>
       <c r="F16">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G16">
         <v>1.88</v>
@@ -4831,19 +4831,19 @@
         <v>3.05</v>
       </c>
       <c r="BI17">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BJ17">
         <v>10.5</v>
       </c>
       <c r="BK17">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>1.04</v>
+        <v>15.5</v>
       </c>
       <c r="BN17">
         <v>5</v>
@@ -4855,13 +4855,13 @@
         <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR17">
         <v>1000</v>
       </c>
       <c r="BS17">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BT17">
         <v>6.8</v>
@@ -4873,19 +4873,19 @@
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="BZ17">
         <v>1000</v>
       </c>
       <c r="CA17">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="CB17" t="s">
         <v>142</v>
@@ -4926,61 +4926,61 @@
         <v>3.95</v>
       </c>
       <c r="L18">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="M18">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N18">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O18">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P18">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="Q18">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="R18">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S18">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="T18">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U18">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="V18">
         <v>1.34</v>
       </c>
       <c r="W18">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="X18">
         <v>17.5</v>
       </c>
       <c r="Y18">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z18">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA18">
         <v>75</v>
       </c>
       <c r="AB18">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC18">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AD18">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE18">
         <v>46</v>
@@ -4998,46 +4998,46 @@
         <v>50</v>
       </c>
       <c r="AJ18">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK18">
         <v>22</v>
       </c>
       <c r="AL18">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AM18">
         <v>95</v>
       </c>
       <c r="AN18">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO18">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AP18">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AQ18">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR18">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS18">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AT18">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AU18">
         <v>7.8</v>
       </c>
       <c r="AV18">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW18">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AX18">
         <v>12</v>
@@ -5046,40 +5046,40 @@
         <v>9.6</v>
       </c>
       <c r="AZ18">
+        <v>15</v>
+      </c>
+      <c r="BA18">
+        <v>7.6</v>
+      </c>
+      <c r="BB18">
         <v>6.6</v>
       </c>
-      <c r="BA18">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB18">
+      <c r="BC18">
+        <v>18</v>
+      </c>
+      <c r="BD18">
         <v>7</v>
       </c>
-      <c r="BC18">
-        <v>17.5</v>
-      </c>
-      <c r="BD18">
+      <c r="BE18">
+        <v>8</v>
+      </c>
+      <c r="BF18">
+        <v>11</v>
+      </c>
+      <c r="BG18">
         <v>7.6</v>
       </c>
-      <c r="BE18">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF18">
-        <v>10.5</v>
-      </c>
-      <c r="BG18">
-        <v>7.8</v>
-      </c>
       <c r="BH18">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BI18">
-        <v>3.4</v>
+        <v>2.94</v>
       </c>
       <c r="BJ18">
         <v>9.199999999999999</v>
       </c>
       <c r="BK18">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BL18">
         <v>1000</v>
@@ -5109,13 +5109,13 @@
         <v>7.4</v>
       </c>
       <c r="BU18">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV18">
         <v>32</v>
       </c>
       <c r="BW18">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX18">
         <v>38</v>
@@ -5124,10 +5124,10 @@
         <v>10</v>
       </c>
       <c r="BZ18">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="CA18">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="CB18" t="s">
         <v>142</v>
@@ -5150,10 +5150,10 @@
         <v>138</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="G19">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H19">
         <v>3.95</v>
@@ -5162,13 +5162,13 @@
         <v>4.1</v>
       </c>
       <c r="J19">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K19">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L19">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M19">
         <v>1.05</v>
@@ -5180,34 +5180,34 @@
         <v>1.27</v>
       </c>
       <c r="P19">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q19">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="R19">
         <v>1.45</v>
       </c>
       <c r="S19">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T19">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U19">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V19">
         <v>1.32</v>
       </c>
       <c r="W19">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X19">
         <v>18.5</v>
       </c>
       <c r="Y19">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z19">
         <v>32</v>
@@ -5219,7 +5219,7 @@
         <v>11</v>
       </c>
       <c r="AC19">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD19">
         <v>16.5</v>
@@ -5228,7 +5228,7 @@
         <v>48</v>
       </c>
       <c r="AF19">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG19">
         <v>11</v>
@@ -5252,13 +5252,13 @@
         <v>85</v>
       </c>
       <c r="AN19">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AO19">
         <v>42</v>
       </c>
       <c r="AP19">
-        <v>7.8</v>
+        <v>15.5</v>
       </c>
       <c r="AQ19">
         <v>15.5</v>
@@ -5267,7 +5267,7 @@
         <v>27</v>
       </c>
       <c r="AS19">
-        <v>11.5</v>
+        <v>34</v>
       </c>
       <c r="AT19">
         <v>9.800000000000001</v>
@@ -5285,7 +5285,7 @@
         <v>11.5</v>
       </c>
       <c r="AY19">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ19">
         <v>15.5</v>
@@ -5303,7 +5303,7 @@
         <v>28</v>
       </c>
       <c r="BE19">
-        <v>11.5</v>
+        <v>36</v>
       </c>
       <c r="BF19">
         <v>11</v>
@@ -5333,13 +5333,13 @@
         <v>5.1</v>
       </c>
       <c r="BO19">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="BP19">
         <v>14.5</v>
       </c>
       <c r="BQ19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BR19">
         <v>27</v>
@@ -5360,7 +5360,7 @@
         <v>7.8</v>
       </c>
       <c r="BX19">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY19">
         <v>8.199999999999999</v>
@@ -5392,40 +5392,40 @@
         <v>139</v>
       </c>
       <c r="F20">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G20">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="H20">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I20">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J20">
         <v>4.3</v>
       </c>
       <c r="K20">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L20">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M20">
         <v>1.03</v>
       </c>
       <c r="N20">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O20">
         <v>1.17</v>
       </c>
       <c r="P20">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q20">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R20">
         <v>1.71</v>
@@ -5437,10 +5437,10 @@
         <v>1.55</v>
       </c>
       <c r="U20">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="V20">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W20">
         <v>2.16</v>
@@ -5464,34 +5464,34 @@
         <v>11</v>
       </c>
       <c r="AD20">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE20">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF20">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG20">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH20">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI20">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="AJ20">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AK20">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL20">
         <v>26</v>
       </c>
       <c r="AM20">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN20">
         <v>7.2</v>
@@ -5500,19 +5500,19 @@
         <v>34</v>
       </c>
       <c r="AP20">
-        <v>7.2</v>
+        <v>25</v>
       </c>
       <c r="AQ20">
         <v>20</v>
       </c>
       <c r="AR20">
-        <v>7.6</v>
+        <v>23</v>
       </c>
       <c r="AS20">
-        <v>8.6</v>
+        <v>36</v>
       </c>
       <c r="AT20">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU20">
         <v>9.800000000000001</v>
@@ -5521,7 +5521,7 @@
         <v>15.5</v>
       </c>
       <c r="AW20">
-        <v>7.8</v>
+        <v>24</v>
       </c>
       <c r="AX20">
         <v>13</v>
@@ -5533,7 +5533,7 @@
         <v>13.5</v>
       </c>
       <c r="BA20">
-        <v>7.8</v>
+        <v>23</v>
       </c>
       <c r="BB20">
         <v>18</v>
@@ -5545,13 +5545,13 @@
         <v>21</v>
       </c>
       <c r="BE20">
-        <v>8.4</v>
+        <v>28</v>
       </c>
       <c r="BF20">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG20">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="BH20">
         <v>4.8</v>
@@ -5640,7 +5640,7 @@
         <v>4.3</v>
       </c>
       <c r="H21">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="I21">
         <v>1.88</v>
@@ -5652,37 +5652,37 @@
         <v>4.7</v>
       </c>
       <c r="L21">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M21">
         <v>1.02</v>
       </c>
       <c r="N21">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="O21">
         <v>1.14</v>
       </c>
       <c r="P21">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q21">
         <v>1.43</v>
       </c>
       <c r="R21">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="S21">
         <v>2.06</v>
       </c>
       <c r="T21">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="U21">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="V21">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="W21">
         <v>1.31</v>
@@ -5733,7 +5733,7 @@
         <v>38</v>
       </c>
       <c r="AM21">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AN21">
         <v>24</v>
@@ -5757,7 +5757,7 @@
         <v>18.5</v>
       </c>
       <c r="AU21">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV21">
         <v>10</v>
@@ -5793,7 +5793,7 @@
         <v>20</v>
       </c>
       <c r="BG21">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BH21">
         <v>5.4</v>
@@ -5835,7 +5835,7 @@
         <v>5.6</v>
       </c>
       <c r="BU21">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BV21">
         <v>12</v>
@@ -5879,13 +5879,13 @@
         <v>2.14</v>
       </c>
       <c r="G22">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H22">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I22">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J22">
         <v>4.2</v>
@@ -5906,16 +5906,16 @@
         <v>1.12</v>
       </c>
       <c r="P22">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q22">
         <v>1.39</v>
       </c>
       <c r="R22">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="S22">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="T22">
         <v>1.4</v>
@@ -5924,10 +5924,10 @@
         <v>3.35</v>
       </c>
       <c r="V22">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W22">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X22">
         <v>42</v>
@@ -5939,13 +5939,13 @@
         <v>34</v>
       </c>
       <c r="AA22">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="AB22">
         <v>22</v>
       </c>
       <c r="AC22">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD22">
         <v>15.5</v>
@@ -5969,7 +5969,7 @@
         <v>32</v>
       </c>
       <c r="AK22">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL22">
         <v>22</v>
@@ -5999,7 +5999,7 @@
         <v>19.5</v>
       </c>
       <c r="AU22">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AV22">
         <v>13.5</v>
@@ -6023,7 +6023,7 @@
         <v>27</v>
       </c>
       <c r="BC22">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD22">
         <v>19</v>
@@ -6032,10 +6032,10 @@
         <v>34</v>
       </c>
       <c r="BF22">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BG22">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BH22">
         <v>5.8</v>
@@ -6047,7 +6047,7 @@
         <v>8.6</v>
       </c>
       <c r="BK22">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BL22">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="147">
   <si>
     <t>League</t>
   </si>
@@ -271,6 +271,9 @@
     <t>Norwegian Eliteserien</t>
   </si>
   <si>
+    <t>Ecuadorian Serie B</t>
+  </si>
+  <si>
     <t>Brazilian Serie A</t>
   </si>
   <si>
@@ -304,6 +307,9 @@
     <t>19:00:00</t>
   </si>
   <si>
+    <t>20:30:00</t>
+  </si>
+  <si>
     <t>21:30:00</t>
   </si>
   <si>
@@ -346,6 +352,9 @@
     <t>Macara</t>
   </si>
   <si>
+    <t>San Antonio FC</t>
+  </si>
+  <si>
     <t>Independiente (Ecu)</t>
   </si>
   <si>
@@ -409,6 +418,9 @@
     <t>Deportivo Cuenca</t>
   </si>
   <si>
+    <t>Cumbaya FC</t>
+  </si>
+  <si>
     <t>Tecnico Universitario</t>
   </si>
   <si>
@@ -442,7 +454,7 @@
     <t>Chicago Fire</t>
   </si>
   <si>
-    <t>2026-07-21 13:28:27</t>
+    <t>2026-07-21 15:35:26</t>
   </si>
 </sst>
 </file>
@@ -774,7 +786,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB22"/>
+  <dimension ref="A1:CB23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1024,34 +1036,34 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F2">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="G2">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H2">
         <v>4.3</v>
       </c>
       <c r="I2">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J2">
         <v>3.55</v>
       </c>
       <c r="K2">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L2">
         <v>1.44</v>
@@ -1066,19 +1078,19 @@
         <v>1.36</v>
       </c>
       <c r="P2">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q2">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="R2">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S2">
         <v>3.75</v>
       </c>
       <c r="T2">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U2">
         <v>2.02</v>
@@ -1087,7 +1099,7 @@
         <v>1.27</v>
       </c>
       <c r="W2">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X2">
         <v>13</v>
@@ -1102,10 +1114,10 @@
         <v>100</v>
       </c>
       <c r="AB2">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC2">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD2">
         <v>17.5</v>
@@ -1141,7 +1153,7 @@
         <v>16</v>
       </c>
       <c r="AO2">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AP2">
         <v>11.5</v>
@@ -1153,7 +1165,7 @@
         <v>27</v>
       </c>
       <c r="AS2">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AT2">
         <v>7.6</v>
@@ -1189,10 +1201,10 @@
         <v>34</v>
       </c>
       <c r="BE2">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BF2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BG2">
         <v>50</v>
@@ -1201,7 +1213,7 @@
         <v>3.3</v>
       </c>
       <c r="BI2">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="BJ2">
         <v>10</v>
@@ -1213,52 +1225,52 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BN2">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO2">
         <v>4.1</v>
       </c>
       <c r="BP2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ2">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR2">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT2">
         <v>7.6</v>
       </c>
       <c r="BU2">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BV2">
         <v>38</v>
       </c>
       <c r="BW2">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BZ2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="CA2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CB2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1266,34 +1278,34 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F3">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G3">
         <v>2.68</v>
       </c>
       <c r="H3">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I3">
         <v>3.4</v>
       </c>
       <c r="J3">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K3">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L3">
         <v>1.52</v>
@@ -1302,7 +1314,7 @@
         <v>1.11</v>
       </c>
       <c r="N3">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O3">
         <v>1.46</v>
@@ -1317,13 +1329,13 @@
         <v>1.24</v>
       </c>
       <c r="S3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T3">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="U3">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="V3">
         <v>1.42</v>
@@ -1338,13 +1350,13 @@
         <v>10.5</v>
       </c>
       <c r="Z3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA3">
         <v>65</v>
       </c>
       <c r="AB3">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC3">
         <v>7.2</v>
@@ -1395,7 +1407,7 @@
         <v>17.5</v>
       </c>
       <c r="AS3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT3">
         <v>8</v>
@@ -1437,7 +1449,7 @@
         <v>26</v>
       </c>
       <c r="BG3">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="BH3">
         <v>2.96</v>
@@ -1500,7 +1512,7 @@
         <v>9.4</v>
       </c>
       <c r="CB3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1508,34 +1520,34 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F4">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="G4">
         <v>1.38</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I4">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J4">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="K4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="L4">
         <v>1.3</v>
@@ -1556,16 +1568,16 @@
         <v>1.63</v>
       </c>
       <c r="R4">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S4">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="T4">
         <v>1.97</v>
       </c>
       <c r="U4">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V4">
         <v>1.12</v>
@@ -1589,7 +1601,7 @@
         <v>9.6</v>
       </c>
       <c r="AC4">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD4">
         <v>32</v>
@@ -1598,10 +1610,10 @@
         <v>130</v>
       </c>
       <c r="AF4">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG4">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AH4">
         <v>29</v>
@@ -1646,10 +1658,10 @@
         <v>12.5</v>
       </c>
       <c r="AV4">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AW4">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="AX4">
         <v>8</v>
@@ -1658,7 +1670,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA4">
         <v>85</v>
@@ -1676,10 +1688,10 @@
         <v>44</v>
       </c>
       <c r="BF4">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BG4">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="BH4">
         <v>4.3</v>
@@ -1709,7 +1721,7 @@
         <v>8</v>
       </c>
       <c r="BQ4">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BR4">
         <v>22</v>
@@ -1742,7 +1754,7 @@
         <v>7.4</v>
       </c>
       <c r="CB4" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1750,34 +1762,34 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E5" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F5">
+        <v>1.68</v>
+      </c>
+      <c r="G5">
         <v>1.69</v>
       </c>
-      <c r="G5">
-        <v>1.71</v>
-      </c>
       <c r="H5">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I5">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J5">
         <v>4.4</v>
       </c>
       <c r="K5">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L5">
         <v>1.32</v>
@@ -1798,22 +1810,22 @@
         <v>1.69</v>
       </c>
       <c r="R5">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S5">
         <v>2.76</v>
       </c>
       <c r="T5">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U5">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V5">
         <v>1.22</v>
       </c>
       <c r="W5">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="X5">
         <v>22</v>
@@ -1837,7 +1849,7 @@
         <v>20</v>
       </c>
       <c r="AE5">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF5">
         <v>11.5</v>
@@ -1873,13 +1885,13 @@
         <v>19</v>
       </c>
       <c r="AQ5">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AR5">
         <v>38</v>
       </c>
       <c r="AS5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT5">
         <v>10</v>
@@ -1921,7 +1933,7 @@
         <v>7.2</v>
       </c>
       <c r="BG5">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="BH5">
         <v>4.2</v>
@@ -1939,13 +1951,13 @@
         <v>110</v>
       </c>
       <c r="BM5">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BN5">
         <v>4.7</v>
       </c>
       <c r="BO5">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="BP5">
         <v>11.5</v>
@@ -1960,13 +1972,13 @@
         <v>7</v>
       </c>
       <c r="BT5">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BU5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BV5">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BW5">
         <v>8</v>
@@ -1978,13 +1990,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BZ5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="CA5">
         <v>6.2</v>
       </c>
       <c r="CB5" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1992,16 +2004,16 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F6">
         <v>3.05</v>
@@ -2013,10 +2025,10 @@
         <v>2.66</v>
       </c>
       <c r="I6">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="J6">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K6">
         <v>3.25</v>
@@ -2046,10 +2058,10 @@
         <v>5</v>
       </c>
       <c r="T6">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U6">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="V6">
         <v>1.56</v>
@@ -2073,7 +2085,7 @@
         <v>9.4</v>
       </c>
       <c r="AC6">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD6">
         <v>13</v>
@@ -2109,7 +2121,7 @@
         <v>55</v>
       </c>
       <c r="AO6">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP6">
         <v>9</v>
@@ -2121,7 +2133,7 @@
         <v>14.5</v>
       </c>
       <c r="AS6">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT6">
         <v>8.6</v>
@@ -2133,7 +2145,7 @@
         <v>11.5</v>
       </c>
       <c r="AW6">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AX6">
         <v>16.5</v>
@@ -2145,25 +2157,25 @@
         <v>18</v>
       </c>
       <c r="BA6">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BB6">
         <v>10</v>
       </c>
       <c r="BC6">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BD6">
         <v>10</v>
       </c>
       <c r="BE6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BF6">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG6">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH6">
         <v>2.84</v>
@@ -2226,7 +2238,7 @@
         <v>12</v>
       </c>
       <c r="CB6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2234,16 +2246,16 @@
         <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E7" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F7">
         <v>4.7</v>
@@ -2255,7 +2267,7 @@
         <v>1.89</v>
       </c>
       <c r="I7">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="J7">
         <v>3.6</v>
@@ -2267,16 +2279,16 @@
         <v>1.46</v>
       </c>
       <c r="M7">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N7">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O7">
         <v>1.39</v>
       </c>
       <c r="P7">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="Q7">
         <v>2.16</v>
@@ -2288,13 +2300,13 @@
         <v>4</v>
       </c>
       <c r="T7">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U7">
         <v>1.94</v>
       </c>
       <c r="V7">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="W7">
         <v>1.25</v>
@@ -2315,7 +2327,7 @@
         <v>15</v>
       </c>
       <c r="AC7">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD7">
         <v>10.5</v>
@@ -2324,7 +2336,7 @@
         <v>24</v>
       </c>
       <c r="AF7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AG7">
         <v>20</v>
@@ -2369,22 +2381,22 @@
         <v>13</v>
       </c>
       <c r="AU7">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV7">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW7">
         <v>18.5</v>
       </c>
       <c r="AX7">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AY7">
         <v>16.5</v>
       </c>
       <c r="AZ7">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA7">
         <v>36</v>
@@ -2468,7 +2480,7 @@
         <v>10</v>
       </c>
       <c r="CB7" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2476,16 +2488,16 @@
         <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E8" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F8">
         <v>1.91</v>
@@ -2497,13 +2509,13 @@
         <v>4.7</v>
       </c>
       <c r="I8">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J8">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K8">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L8">
         <v>1.5</v>
@@ -2518,10 +2530,10 @@
         <v>1.45</v>
       </c>
       <c r="P8">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q8">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R8">
         <v>1.25</v>
@@ -2536,7 +2548,7 @@
         <v>1.85</v>
       </c>
       <c r="V8">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W8">
         <v>2</v>
@@ -2575,7 +2587,7 @@
         <v>24</v>
       </c>
       <c r="AI8">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ8">
         <v>23</v>
@@ -2584,7 +2596,7 @@
         <v>26</v>
       </c>
       <c r="AL8">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM8">
         <v>190</v>
@@ -2593,7 +2605,7 @@
         <v>21</v>
       </c>
       <c r="AO8">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP8">
         <v>9.6</v>
@@ -2602,10 +2614,10 @@
         <v>12</v>
       </c>
       <c r="AR8">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AS8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT8">
         <v>6.6</v>
@@ -2620,7 +2632,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AX8">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY8">
         <v>9.6</v>
@@ -2665,7 +2677,7 @@
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BN8">
         <v>4.4</v>
@@ -2677,10 +2689,10 @@
         <v>14.5</v>
       </c>
       <c r="BQ8">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR8">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
         <v>12</v>
@@ -2695,22 +2707,22 @@
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="CB8" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2718,34 +2730,34 @@
         <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E9" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F9">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="G9">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="H9">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="I9">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="K9">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L9">
         <v>1.3</v>
@@ -2754,16 +2766,16 @@
         <v>1.04</v>
       </c>
       <c r="N9">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O9">
         <v>1.19</v>
       </c>
       <c r="P9">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q9">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="R9">
         <v>1.62</v>
@@ -2775,28 +2787,28 @@
         <v>1.55</v>
       </c>
       <c r="U9">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="V9">
         <v>1.67</v>
       </c>
       <c r="W9">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="X9">
         <v>24</v>
       </c>
       <c r="Y9">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z9">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA9">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AB9">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC9">
         <v>9.4</v>
@@ -2805,7 +2817,7 @@
         <v>11.5</v>
       </c>
       <c r="AE9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF9">
         <v>32</v>
@@ -2820,10 +2832,10 @@
         <v>28</v>
       </c>
       <c r="AJ9">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AK9">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AL9">
         <v>36</v>
@@ -2832,10 +2844,10 @@
         <v>55</v>
       </c>
       <c r="AN9">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="AO9">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP9">
         <v>21</v>
@@ -2844,52 +2856,52 @@
         <v>13</v>
       </c>
       <c r="AR9">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AS9">
         <v>26</v>
       </c>
       <c r="AT9">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AU9">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV9">
         <v>10</v>
       </c>
       <c r="AW9">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AX9">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AY9">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ9">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA9">
         <v>24</v>
       </c>
       <c r="BB9">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BC9">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="BD9">
         <v>30</v>
       </c>
       <c r="BE9">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BF9">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="BG9">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BH9">
         <v>4.3</v>
@@ -2910,49 +2922,49 @@
         <v>14.5</v>
       </c>
       <c r="BN9">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BO9">
         <v>5</v>
       </c>
       <c r="BP9">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BQ9">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR9">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BS9">
         <v>11</v>
       </c>
       <c r="BT9">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BU9">
         <v>5</v>
       </c>
       <c r="BV9">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BW9">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BX9">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BY9">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ9">
         <v>15.5</v>
       </c>
       <c r="CA9">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="CB9" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2960,34 +2972,34 @@
         <v>84</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D10" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E10" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F10">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="G10">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="H10">
         <v>27</v>
       </c>
       <c r="I10">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="J10">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="K10">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="L10">
         <v>1.17</v>
@@ -3002,19 +3014,19 @@
         <v>1.09</v>
       </c>
       <c r="P10">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q10">
         <v>1.28</v>
       </c>
       <c r="R10">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="S10">
         <v>1.69</v>
       </c>
       <c r="T10">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U10">
         <v>1.87</v>
@@ -3032,7 +3044,7 @@
         <v>940</v>
       </c>
       <c r="Z10">
-        <v>300</v>
+        <v>410</v>
       </c>
       <c r="AA10">
         <v>1000</v>
@@ -3041,22 +3053,22 @@
         <v>17</v>
       </c>
       <c r="AC10">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AD10">
         <v>940</v>
       </c>
       <c r="AE10">
-        <v>380</v>
+        <v>500</v>
       </c>
       <c r="AF10">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG10">
         <v>15</v>
       </c>
       <c r="AH10">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="AI10">
         <v>1000</v>
@@ -3077,13 +3089,13 @@
         <v>2.4</v>
       </c>
       <c r="AO10">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AP10">
         <v>32</v>
       </c>
       <c r="AQ10">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AR10">
         <v>95</v>
@@ -3092,13 +3104,13 @@
         <v>60</v>
       </c>
       <c r="AT10">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AU10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV10">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AW10">
         <v>95</v>
@@ -3107,10 +3119,10 @@
         <v>9.6</v>
       </c>
       <c r="AY10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ10">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="BA10">
         <v>48</v>
@@ -3122,7 +3134,7 @@
         <v>12</v>
       </c>
       <c r="BD10">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BE10">
         <v>46</v>
@@ -3143,22 +3155,22 @@
         <v>14</v>
       </c>
       <c r="BK10">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BN10">
         <v>4.4</v>
       </c>
       <c r="BO10">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BP10">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BQ10">
         <v>4.4</v>
@@ -3167,25 +3179,25 @@
         <v>19</v>
       </c>
       <c r="BS10">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT10">
         <v>23</v>
       </c>
       <c r="BU10">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ10">
         <v>5.6</v>
@@ -3194,7 +3206,7 @@
         <v>4.1</v>
       </c>
       <c r="CB10" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3202,16 +3214,16 @@
         <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E11" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F11">
         <v>2.18</v>
@@ -3229,13 +3241,13 @@
         <v>2.98</v>
       </c>
       <c r="K11">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L11">
         <v>1.48</v>
       </c>
       <c r="M11">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N11">
         <v>2.58</v>
@@ -3244,13 +3256,13 @@
         <v>1.54</v>
       </c>
       <c r="P11">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q11">
         <v>2.62</v>
       </c>
       <c r="R11">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S11">
         <v>5.2</v>
@@ -3436,733 +3448,733 @@
         <v>9</v>
       </c>
       <c r="CB11" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E12" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F12">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="G12">
-        <v>1.28</v>
+        <v>990</v>
       </c>
       <c r="H12">
-        <v>15.5</v>
+        <v>1.04</v>
       </c>
       <c r="I12">
-        <v>22</v>
+        <v>990</v>
       </c>
       <c r="J12">
-        <v>6.2</v>
+        <v>1.02</v>
       </c>
       <c r="K12">
-        <v>7.4</v>
+        <v>950</v>
       </c>
       <c r="L12">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M12">
+        <v>1.01</v>
+      </c>
+      <c r="N12">
+        <v>1.1</v>
+      </c>
+      <c r="O12">
+        <v>1.01</v>
+      </c>
+      <c r="P12">
+        <v>1.08</v>
+      </c>
+      <c r="Q12">
+        <v>1.45</v>
+      </c>
+      <c r="R12">
+        <v>1.07</v>
+      </c>
+      <c r="S12">
+        <v>1.44</v>
+      </c>
+      <c r="T12">
+        <v>1.11</v>
+      </c>
+      <c r="U12">
+        <v>1.11</v>
+      </c>
+      <c r="V12">
+        <v>1.01</v>
+      </c>
+      <c r="W12">
+        <v>1.01</v>
+      </c>
+      <c r="X12">
+        <v>1000</v>
+      </c>
+      <c r="Y12">
+        <v>1000</v>
+      </c>
+      <c r="Z12">
+        <v>1000</v>
+      </c>
+      <c r="AA12">
+        <v>1000</v>
+      </c>
+      <c r="AB12">
+        <v>1000</v>
+      </c>
+      <c r="AC12">
+        <v>1000</v>
+      </c>
+      <c r="AD12">
+        <v>1000</v>
+      </c>
+      <c r="AE12">
+        <v>1000</v>
+      </c>
+      <c r="AF12">
+        <v>1000</v>
+      </c>
+      <c r="AG12">
+        <v>1000</v>
+      </c>
+      <c r="AH12">
+        <v>1000</v>
+      </c>
+      <c r="AI12">
+        <v>1000</v>
+      </c>
+      <c r="AJ12">
+        <v>1000</v>
+      </c>
+      <c r="AK12">
+        <v>1000</v>
+      </c>
+      <c r="AL12">
+        <v>1000</v>
+      </c>
+      <c r="AM12">
+        <v>1000</v>
+      </c>
+      <c r="AN12">
+        <v>1000</v>
+      </c>
+      <c r="AO12">
+        <v>1000</v>
+      </c>
+      <c r="AP12">
         <v>1.03</v>
       </c>
-      <c r="N12">
-        <v>4.6</v>
-      </c>
-      <c r="O12">
-        <v>1.22</v>
-      </c>
-      <c r="P12">
-        <v>2.28</v>
-      </c>
-      <c r="Q12">
-        <v>1.65</v>
-      </c>
-      <c r="R12">
-        <v>1.49</v>
-      </c>
-      <c r="S12">
-        <v>2.62</v>
-      </c>
-      <c r="T12">
-        <v>2.32</v>
-      </c>
-      <c r="U12">
-        <v>1.6</v>
-      </c>
-      <c r="V12">
-        <v>1.05</v>
-      </c>
-      <c r="W12">
-        <v>4.4</v>
-      </c>
-      <c r="X12">
-        <v>27</v>
-      </c>
-      <c r="Y12">
-        <v>55</v>
-      </c>
-      <c r="Z12">
-        <v>200</v>
-      </c>
-      <c r="AA12">
-        <v>1000</v>
-      </c>
-      <c r="AB12">
-        <v>8.6</v>
-      </c>
-      <c r="AC12">
-        <v>18</v>
-      </c>
-      <c r="AD12">
-        <v>65</v>
-      </c>
-      <c r="AE12">
-        <v>410</v>
-      </c>
-      <c r="AF12">
-        <v>7.6</v>
-      </c>
-      <c r="AG12">
-        <v>14</v>
-      </c>
-      <c r="AH12">
-        <v>48</v>
-      </c>
-      <c r="AI12">
-        <v>290</v>
-      </c>
-      <c r="AJ12">
-        <v>9.4</v>
-      </c>
-      <c r="AK12">
-        <v>18.5</v>
-      </c>
-      <c r="AL12">
-        <v>60</v>
-      </c>
-      <c r="AM12">
-        <v>300</v>
-      </c>
-      <c r="AN12">
-        <v>5.5</v>
-      </c>
-      <c r="AO12">
-        <v>1000</v>
-      </c>
-      <c r="AP12">
-        <v>19</v>
-      </c>
       <c r="AQ12">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR12">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AS12">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT12">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU12">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AV12">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW12">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AX12">
-        <v>3.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY12">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA12">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="BB12">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="BC12">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BD12">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="BE12">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="BF12">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BG12">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH12">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BI12">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BN12">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="BP12">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BR12">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BT12">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV12">
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="CA12">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E13" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F13">
+        <v>1.22</v>
+      </c>
+      <c r="G13">
+        <v>1.28</v>
+      </c>
+      <c r="H13">
+        <v>15.5</v>
+      </c>
+      <c r="I13">
+        <v>22</v>
+      </c>
+      <c r="J13">
+        <v>6.2</v>
+      </c>
+      <c r="K13">
+        <v>7.8</v>
+      </c>
+      <c r="L13">
+        <v>1.29</v>
+      </c>
+      <c r="M13">
+        <v>1.05</v>
+      </c>
+      <c r="N13">
         <v>4.7</v>
       </c>
-      <c r="G13">
-        <v>4.9</v>
-      </c>
-      <c r="H13">
-        <v>1.94</v>
-      </c>
-      <c r="I13">
-        <v>1.95</v>
-      </c>
-      <c r="J13">
-        <v>3.5</v>
-      </c>
-      <c r="K13">
-        <v>3.6</v>
-      </c>
-      <c r="L13">
-        <v>1.48</v>
-      </c>
-      <c r="M13">
-        <v>1.09</v>
-      </c>
-      <c r="N13">
-        <v>3.25</v>
-      </c>
       <c r="O13">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="P13">
-        <v>1.73</v>
+        <v>2.26</v>
       </c>
       <c r="Q13">
-        <v>2.24</v>
+        <v>1.64</v>
       </c>
       <c r="R13">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="S13">
-        <v>4.3</v>
+        <v>2.6</v>
       </c>
       <c r="T13">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="U13">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="V13">
-        <v>2.04</v>
+        <v>1.05</v>
       </c>
       <c r="W13">
-        <v>1.25</v>
+        <v>4.5</v>
       </c>
       <c r="X13">
+        <v>27</v>
+      </c>
+      <c r="Y13">
+        <v>55</v>
+      </c>
+      <c r="Z13">
+        <v>200</v>
+      </c>
+      <c r="AA13">
+        <v>1000</v>
+      </c>
+      <c r="AB13">
+        <v>8.4</v>
+      </c>
+      <c r="AC13">
+        <v>18</v>
+      </c>
+      <c r="AD13">
+        <v>65</v>
+      </c>
+      <c r="AE13">
+        <v>410</v>
+      </c>
+      <c r="AF13">
+        <v>7.4</v>
+      </c>
+      <c r="AG13">
+        <v>14</v>
+      </c>
+      <c r="AH13">
+        <v>48</v>
+      </c>
+      <c r="AI13">
+        <v>290</v>
+      </c>
+      <c r="AJ13">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AK13">
+        <v>18.5</v>
+      </c>
+      <c r="AL13">
+        <v>60</v>
+      </c>
+      <c r="AM13">
+        <v>300</v>
+      </c>
+      <c r="AN13">
+        <v>5.5</v>
+      </c>
+      <c r="AO13">
+        <v>1000</v>
+      </c>
+      <c r="AP13">
+        <v>19</v>
+      </c>
+      <c r="AQ13">
+        <v>5.8</v>
+      </c>
+      <c r="AR13">
+        <v>6.2</v>
+      </c>
+      <c r="AS13">
+        <v>6.4</v>
+      </c>
+      <c r="AT13">
+        <v>7.2</v>
+      </c>
+      <c r="AU13">
+        <v>13</v>
+      </c>
+      <c r="AV13">
+        <v>5.9</v>
+      </c>
+      <c r="AW13">
+        <v>6.4</v>
+      </c>
+      <c r="AX13">
+        <v>3.45</v>
+      </c>
+      <c r="AY13">
+        <v>10</v>
+      </c>
+      <c r="AZ13">
+        <v>5.7</v>
+      </c>
+      <c r="BA13">
+        <v>6.4</v>
+      </c>
+      <c r="BB13">
+        <v>7.8</v>
+      </c>
+      <c r="BC13">
+        <v>12.5</v>
+      </c>
+      <c r="BD13">
+        <v>5.9</v>
+      </c>
+      <c r="BE13">
+        <v>6.4</v>
+      </c>
+      <c r="BF13">
+        <v>4</v>
+      </c>
+      <c r="BG13">
+        <v>6.4</v>
+      </c>
+      <c r="BH13">
+        <v>4.4</v>
+      </c>
+      <c r="BI13">
+        <v>3.3</v>
+      </c>
+      <c r="BJ13">
+        <v>15</v>
+      </c>
+      <c r="BK13">
+        <v>6.2</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>10</v>
+      </c>
+      <c r="BN13">
+        <v>3.7</v>
+      </c>
+      <c r="BO13">
+        <v>3.15</v>
+      </c>
+      <c r="BP13">
+        <v>7</v>
+      </c>
+      <c r="BQ13">
+        <v>5.1</v>
+      </c>
+      <c r="BR13">
+        <v>27</v>
+      </c>
+      <c r="BS13">
+        <v>7.6</v>
+      </c>
+      <c r="BT13">
+        <v>18.5</v>
+      </c>
+      <c r="BU13">
+        <v>6.8</v>
+      </c>
+      <c r="BV13">
+        <v>1000</v>
+      </c>
+      <c r="BW13">
+        <v>10</v>
+      </c>
+      <c r="BX13">
+        <v>1000</v>
+      </c>
+      <c r="BY13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BZ13">
         <v>11</v>
       </c>
-      <c r="Y13">
-        <v>7.6</v>
-      </c>
-      <c r="Z13">
-        <v>10.5</v>
-      </c>
-      <c r="AA13">
-        <v>23</v>
-      </c>
-      <c r="AB13">
-        <v>14.5</v>
-      </c>
-      <c r="AC13">
-        <v>8</v>
-      </c>
-      <c r="AD13">
-        <v>10.5</v>
-      </c>
-      <c r="AE13">
-        <v>23</v>
-      </c>
-      <c r="AF13">
-        <v>34</v>
-      </c>
-      <c r="AG13">
-        <v>20</v>
-      </c>
-      <c r="AH13">
-        <v>22</v>
-      </c>
-      <c r="AI13">
-        <v>170</v>
-      </c>
-      <c r="AJ13">
-        <v>120</v>
-      </c>
-      <c r="AK13">
-        <v>75</v>
-      </c>
-      <c r="AL13">
-        <v>90</v>
-      </c>
-      <c r="AM13">
-        <v>1000</v>
-      </c>
-      <c r="AN13">
-        <v>95</v>
-      </c>
-      <c r="AO13">
-        <v>17.5</v>
-      </c>
-      <c r="AP13">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ13">
-        <v>7.2</v>
-      </c>
-      <c r="AR13">
-        <v>9.4</v>
-      </c>
-      <c r="AS13">
-        <v>20</v>
-      </c>
-      <c r="AT13">
-        <v>13.5</v>
-      </c>
-      <c r="AU13">
-        <v>7</v>
-      </c>
-      <c r="AV13">
-        <v>9</v>
-      </c>
-      <c r="AW13">
-        <v>20</v>
-      </c>
-      <c r="AX13">
-        <v>29</v>
-      </c>
-      <c r="AY13">
-        <v>15</v>
-      </c>
-      <c r="AZ13">
-        <v>19.5</v>
-      </c>
-      <c r="BA13">
-        <v>40</v>
-      </c>
-      <c r="BB13">
-        <v>38</v>
-      </c>
-      <c r="BC13">
-        <v>32</v>
-      </c>
-      <c r="BD13">
-        <v>36</v>
-      </c>
-      <c r="BE13">
-        <v>44</v>
-      </c>
-      <c r="BF13">
-        <v>36</v>
-      </c>
-      <c r="BG13">
-        <v>14.5</v>
-      </c>
-      <c r="BH13">
-        <v>3.05</v>
-      </c>
-      <c r="BI13">
-        <v>2.62</v>
-      </c>
-      <c r="BJ13">
-        <v>11</v>
-      </c>
-      <c r="BK13">
-        <v>6.8</v>
-      </c>
-      <c r="BL13">
-        <v>1000</v>
-      </c>
-      <c r="BM13">
-        <v>16.5</v>
-      </c>
-      <c r="BN13">
-        <v>8</v>
-      </c>
-      <c r="BO13">
-        <v>5.6</v>
-      </c>
-      <c r="BP13">
-        <v>55</v>
-      </c>
-      <c r="BQ13">
-        <v>13</v>
-      </c>
-      <c r="BR13">
-        <v>75</v>
-      </c>
-      <c r="BS13">
-        <v>14</v>
-      </c>
-      <c r="BT13">
-        <v>4.4</v>
-      </c>
-      <c r="BU13">
-        <v>4</v>
-      </c>
-      <c r="BV13">
-        <v>14.5</v>
-      </c>
-      <c r="BW13">
-        <v>8</v>
-      </c>
-      <c r="BX13">
-        <v>46</v>
-      </c>
-      <c r="BY13">
-        <v>11.5</v>
-      </c>
-      <c r="BZ13">
-        <v>1000</v>
-      </c>
       <c r="CA13">
-        <v>11.5</v>
+        <v>5.4</v>
       </c>
       <c r="CB13" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C14" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E14" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F14">
-        <v>2.2</v>
+        <v>5.1</v>
       </c>
       <c r="G14">
-        <v>2.32</v>
+        <v>5.2</v>
       </c>
       <c r="H14">
+        <v>1.89</v>
+      </c>
+      <c r="I14">
+        <v>1.9</v>
+      </c>
+      <c r="J14">
+        <v>3.6</v>
+      </c>
+      <c r="K14">
         <v>3.65</v>
       </c>
-      <c r="I14">
-        <v>3.95</v>
-      </c>
-      <c r="J14">
-        <v>3.4</v>
-      </c>
-      <c r="K14">
-        <v>3.5</v>
-      </c>
       <c r="L14">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="M14">
         <v>1.09</v>
       </c>
       <c r="N14">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O14">
         <v>1.42</v>
       </c>
       <c r="P14">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="Q14">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="R14">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="S14">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T14">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="U14">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="V14">
-        <v>1.34</v>
+        <v>2.1</v>
       </c>
       <c r="W14">
-        <v>1.76</v>
+        <v>1.23</v>
       </c>
       <c r="X14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y14">
-        <v>12.5</v>
+        <v>7.6</v>
       </c>
       <c r="Z14">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="AA14">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="AB14">
-        <v>9.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="AC14">
+        <v>8</v>
+      </c>
+      <c r="AD14">
+        <v>10.5</v>
+      </c>
+      <c r="AE14">
+        <v>22</v>
+      </c>
+      <c r="AF14">
+        <v>42</v>
+      </c>
+      <c r="AG14">
+        <v>21</v>
+      </c>
+      <c r="AH14">
+        <v>23</v>
+      </c>
+      <c r="AI14">
+        <v>50</v>
+      </c>
+      <c r="AJ14">
+        <v>150</v>
+      </c>
+      <c r="AK14">
+        <v>1000</v>
+      </c>
+      <c r="AL14">
+        <v>95</v>
+      </c>
+      <c r="AM14">
+        <v>1000</v>
+      </c>
+      <c r="AN14">
+        <v>110</v>
+      </c>
+      <c r="AO14">
+        <v>16</v>
+      </c>
+      <c r="AP14">
+        <v>9.4</v>
+      </c>
+      <c r="AQ14">
+        <v>7</v>
+      </c>
+      <c r="AR14">
+        <v>9</v>
+      </c>
+      <c r="AS14">
+        <v>18</v>
+      </c>
+      <c r="AT14">
+        <v>14</v>
+      </c>
+      <c r="AU14">
         <v>7.4</v>
       </c>
-      <c r="AD14">
-        <v>950</v>
-      </c>
-      <c r="AE14">
-        <v>55</v>
-      </c>
-      <c r="AF14">
-        <v>14</v>
-      </c>
-      <c r="AG14">
-        <v>11.5</v>
-      </c>
-      <c r="AH14">
-        <v>950</v>
-      </c>
-      <c r="AI14">
-        <v>65</v>
-      </c>
-      <c r="AJ14">
-        <v>30</v>
-      </c>
-      <c r="AK14">
-        <v>28</v>
-      </c>
-      <c r="AL14">
-        <v>46</v>
-      </c>
-      <c r="AM14">
-        <v>140</v>
-      </c>
-      <c r="AN14">
-        <v>24</v>
-      </c>
-      <c r="AO14">
-        <v>65</v>
-      </c>
-      <c r="AP14">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ14">
-        <v>10.5</v>
-      </c>
-      <c r="AR14">
-        <v>7.4</v>
-      </c>
-      <c r="AS14">
+      <c r="AV14">
         <v>9</v>
       </c>
-      <c r="AT14">
-        <v>7.4</v>
-      </c>
-      <c r="AU14">
-        <v>6.6</v>
-      </c>
-      <c r="AV14">
-        <v>14</v>
-      </c>
       <c r="AW14">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="AX14">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="AY14">
-        <v>10</v>
+        <v>18.5</v>
       </c>
       <c r="AZ14">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BA14">
-        <v>8.800000000000001</v>
+        <v>40</v>
       </c>
       <c r="BB14">
-        <v>7.6</v>
+        <v>40</v>
       </c>
       <c r="BC14">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="BD14">
         <v>38</v>
       </c>
       <c r="BE14">
-        <v>9.6</v>
+        <v>44</v>
       </c>
       <c r="BF14">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="BG14">
-        <v>8.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="BH14">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BI14">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="BJ14">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK14">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
+        <v>17</v>
+      </c>
+      <c r="BN14">
+        <v>8.4</v>
+      </c>
+      <c r="BO14">
+        <v>5.8</v>
+      </c>
+      <c r="BP14">
+        <v>1000</v>
+      </c>
+      <c r="BQ14">
         <v>13.5</v>
       </c>
-      <c r="BN14">
-        <v>5</v>
-      </c>
-      <c r="BO14">
-        <v>3.95</v>
-      </c>
-      <c r="BP14">
-        <v>18</v>
-      </c>
-      <c r="BQ14">
-        <v>8</v>
-      </c>
       <c r="BR14">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BS14">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="BT14">
-        <v>7</v>
+        <v>4.3</v>
       </c>
       <c r="BU14">
-        <v>5.4</v>
+        <v>3.55</v>
       </c>
       <c r="BV14">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BW14">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="BX14">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY14">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="CA14">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="CB14" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4170,1935 +4182,2177 @@
         <v>81</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D15" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E15" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F15">
-        <v>1.41</v>
+        <v>2.22</v>
       </c>
       <c r="G15">
-        <v>1.45</v>
+        <v>2.32</v>
       </c>
       <c r="H15">
+        <v>3.65</v>
+      </c>
+      <c r="I15">
+        <v>3.9</v>
+      </c>
+      <c r="J15">
+        <v>3.3</v>
+      </c>
+      <c r="K15">
+        <v>3.45</v>
+      </c>
+      <c r="L15">
+        <v>1.48</v>
+      </c>
+      <c r="M15">
+        <v>1.09</v>
+      </c>
+      <c r="N15">
+        <v>3.1</v>
+      </c>
+      <c r="O15">
+        <v>1.42</v>
+      </c>
+      <c r="P15">
+        <v>1.78</v>
+      </c>
+      <c r="Q15">
+        <v>2.18</v>
+      </c>
+      <c r="R15">
+        <v>1.27</v>
+      </c>
+      <c r="S15">
+        <v>4.1</v>
+      </c>
+      <c r="T15">
+        <v>1.92</v>
+      </c>
+      <c r="U15">
+        <v>1.98</v>
+      </c>
+      <c r="V15">
+        <v>1.36</v>
+      </c>
+      <c r="W15">
+        <v>1.76</v>
+      </c>
+      <c r="X15">
+        <v>13</v>
+      </c>
+      <c r="Y15">
+        <v>12.5</v>
+      </c>
+      <c r="Z15">
+        <v>27</v>
+      </c>
+      <c r="AA15">
+        <v>80</v>
+      </c>
+      <c r="AB15">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC15">
+        <v>7.6</v>
+      </c>
+      <c r="AD15">
+        <v>950</v>
+      </c>
+      <c r="AE15">
+        <v>55</v>
+      </c>
+      <c r="AF15">
+        <v>14</v>
+      </c>
+      <c r="AG15">
+        <v>11.5</v>
+      </c>
+      <c r="AH15">
+        <v>950</v>
+      </c>
+      <c r="AI15">
+        <v>65</v>
+      </c>
+      <c r="AJ15">
+        <v>30</v>
+      </c>
+      <c r="AK15">
+        <v>28</v>
+      </c>
+      <c r="AL15">
+        <v>46</v>
+      </c>
+      <c r="AM15">
+        <v>140</v>
+      </c>
+      <c r="AN15">
+        <v>24</v>
+      </c>
+      <c r="AO15">
+        <v>65</v>
+      </c>
+      <c r="AP15">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ15">
         <v>10.5</v>
       </c>
-      <c r="I15">
-        <v>12.5</v>
-      </c>
-      <c r="J15">
-        <v>4.6</v>
-      </c>
-      <c r="K15">
-        <v>4.9</v>
-      </c>
-      <c r="L15">
-        <v>1.4</v>
-      </c>
-      <c r="M15">
-        <v>1.07</v>
-      </c>
-      <c r="N15">
-        <v>3.55</v>
-      </c>
-      <c r="O15">
-        <v>1.34</v>
-      </c>
-      <c r="P15">
-        <v>1.91</v>
-      </c>
-      <c r="Q15">
-        <v>1.98</v>
-      </c>
-      <c r="R15">
-        <v>1.33</v>
-      </c>
-      <c r="S15">
-        <v>3.6</v>
-      </c>
-      <c r="T15">
-        <v>2.26</v>
-      </c>
-      <c r="U15">
-        <v>1.66</v>
-      </c>
-      <c r="V15">
-        <v>1.09</v>
-      </c>
-      <c r="W15">
-        <v>3.2</v>
-      </c>
-      <c r="X15">
-        <v>17.5</v>
-      </c>
-      <c r="Y15">
-        <v>34</v>
-      </c>
-      <c r="Z15">
-        <v>120</v>
-      </c>
-      <c r="AA15">
-        <v>560</v>
-      </c>
-      <c r="AB15">
+      <c r="AR15">
+        <v>7.2</v>
+      </c>
+      <c r="AS15">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT15">
+        <v>7.4</v>
+      </c>
+      <c r="AU15">
+        <v>6.6</v>
+      </c>
+      <c r="AV15">
+        <v>14</v>
+      </c>
+      <c r="AW15">
+        <v>44</v>
+      </c>
+      <c r="AX15">
+        <v>12</v>
+      </c>
+      <c r="AY15">
+        <v>10</v>
+      </c>
+      <c r="AZ15">
+        <v>17</v>
+      </c>
+      <c r="BA15">
+        <v>8.6</v>
+      </c>
+      <c r="BB15">
+        <v>7.4</v>
+      </c>
+      <c r="BC15">
+        <v>23</v>
+      </c>
+      <c r="BD15">
+        <v>38</v>
+      </c>
+      <c r="BE15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF15">
+        <v>20</v>
+      </c>
+      <c r="BG15">
+        <v>8.6</v>
+      </c>
+      <c r="BH15">
+        <v>3.05</v>
+      </c>
+      <c r="BI15">
+        <v>2.54</v>
+      </c>
+      <c r="BJ15">
+        <v>10.5</v>
+      </c>
+      <c r="BK15">
+        <v>6</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>13.5</v>
+      </c>
+      <c r="BN15">
+        <v>5</v>
+      </c>
+      <c r="BO15">
+        <v>3.95</v>
+      </c>
+      <c r="BP15">
+        <v>18</v>
+      </c>
+      <c r="BQ15">
+        <v>8</v>
+      </c>
+      <c r="BR15">
+        <v>1000</v>
+      </c>
+      <c r="BS15">
+        <v>10.5</v>
+      </c>
+      <c r="BT15">
         <v>7</v>
       </c>
-      <c r="AC15">
-        <v>11.5</v>
-      </c>
-      <c r="AD15">
-        <v>46</v>
-      </c>
-      <c r="AE15">
-        <v>260</v>
-      </c>
-      <c r="AF15">
-        <v>7.8</v>
-      </c>
-      <c r="AG15">
-        <v>12.5</v>
-      </c>
-      <c r="AH15">
-        <v>40</v>
-      </c>
-      <c r="AI15">
-        <v>220</v>
-      </c>
-      <c r="AJ15">
-        <v>14</v>
-      </c>
-      <c r="AK15">
-        <v>18</v>
-      </c>
-      <c r="AL15">
-        <v>60</v>
-      </c>
-      <c r="AM15">
-        <v>280</v>
-      </c>
-      <c r="AN15">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AO15">
-        <v>450</v>
-      </c>
-      <c r="AP15">
-        <v>12</v>
-      </c>
-      <c r="AQ15">
-        <v>5.7</v>
-      </c>
-      <c r="AR15">
-        <v>6.6</v>
-      </c>
-      <c r="AS15">
-        <v>6.8</v>
-      </c>
-      <c r="AT15">
-        <v>5.9</v>
-      </c>
-      <c r="AU15">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV15">
-        <v>32</v>
-      </c>
-      <c r="AW15">
-        <v>6.8</v>
-      </c>
-      <c r="AX15">
-        <v>6.4</v>
-      </c>
-      <c r="AY15">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ15">
-        <v>6</v>
-      </c>
-      <c r="BA15">
-        <v>6.8</v>
-      </c>
-      <c r="BB15">
+      <c r="BU15">
+        <v>5.4</v>
+      </c>
+      <c r="BV15">
+        <v>1000</v>
+      </c>
+      <c r="BW15">
         <v>10</v>
       </c>
-      <c r="BC15">
-        <v>14.5</v>
-      </c>
-      <c r="BD15">
-        <v>6.2</v>
-      </c>
-      <c r="BE15">
-        <v>6.8</v>
-      </c>
-      <c r="BF15">
-        <v>7</v>
-      </c>
-      <c r="BG15">
-        <v>6.8</v>
-      </c>
-      <c r="BH15">
-        <v>3.55</v>
-      </c>
-      <c r="BI15">
-        <v>2.74</v>
-      </c>
-      <c r="BJ15">
-        <v>13.5</v>
-      </c>
-      <c r="BK15">
-        <v>8.4</v>
-      </c>
-      <c r="BL15">
-        <v>1000</v>
-      </c>
-      <c r="BM15">
-        <v>10</v>
-      </c>
-      <c r="BN15">
-        <v>3.75</v>
-      </c>
-      <c r="BO15">
-        <v>2.9</v>
-      </c>
-      <c r="BP15">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BQ15">
-        <v>5</v>
-      </c>
-      <c r="BR15">
-        <v>32</v>
-      </c>
-      <c r="BS15">
-        <v>8</v>
-      </c>
-      <c r="BT15">
-        <v>14</v>
-      </c>
-      <c r="BU15">
-        <v>6</v>
-      </c>
-      <c r="BV15">
-        <v>1000</v>
-      </c>
-      <c r="BW15">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BZ15">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="CB15" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C16" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D16" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E16" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F16">
-        <v>1.81</v>
+        <v>1.41</v>
       </c>
       <c r="G16">
-        <v>1.88</v>
+        <v>1.45</v>
       </c>
       <c r="H16">
-        <v>4.3</v>
+        <v>10.5</v>
       </c>
       <c r="I16">
-        <v>4.8</v>
+        <v>12.5</v>
       </c>
       <c r="J16">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="K16">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="L16">
+        <v>1.4</v>
+      </c>
+      <c r="M16">
+        <v>1.07</v>
+      </c>
+      <c r="N16">
+        <v>3.55</v>
+      </c>
+      <c r="O16">
         <v>1.34</v>
       </c>
-      <c r="M16">
-        <v>1.05</v>
-      </c>
-      <c r="N16">
-        <v>4.4</v>
-      </c>
-      <c r="O16">
-        <v>1.24</v>
-      </c>
       <c r="P16">
-        <v>2.24</v>
+        <v>1.9</v>
       </c>
       <c r="Q16">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="R16">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="S16">
-        <v>2.78</v>
+        <v>3.6</v>
       </c>
       <c r="T16">
-        <v>1.68</v>
+        <v>2.26</v>
       </c>
       <c r="U16">
-        <v>2.24</v>
+        <v>1.66</v>
       </c>
       <c r="V16">
-        <v>1.27</v>
+        <v>1.09</v>
       </c>
       <c r="W16">
-        <v>2.12</v>
+        <v>3.2</v>
       </c>
       <c r="X16">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="Y16">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="Z16">
-        <v>42</v>
+        <v>120</v>
       </c>
       <c r="AA16">
-        <v>110</v>
+        <v>560</v>
       </c>
       <c r="AB16">
+        <v>7</v>
+      </c>
+      <c r="AC16">
         <v>11.5</v>
       </c>
-      <c r="AC16">
-        <v>11</v>
-      </c>
       <c r="AD16">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="AE16">
+        <v>260</v>
+      </c>
+      <c r="AF16">
+        <v>7.8</v>
+      </c>
+      <c r="AG16">
+        <v>12.5</v>
+      </c>
+      <c r="AH16">
+        <v>40</v>
+      </c>
+      <c r="AI16">
+        <v>220</v>
+      </c>
+      <c r="AJ16">
+        <v>14</v>
+      </c>
+      <c r="AK16">
+        <v>18</v>
+      </c>
+      <c r="AL16">
         <v>60</v>
       </c>
-      <c r="AF16">
-        <v>14</v>
-      </c>
-      <c r="AG16">
-        <v>11.5</v>
-      </c>
-      <c r="AH16">
-        <v>21</v>
-      </c>
-      <c r="AI16">
-        <v>60</v>
-      </c>
-      <c r="AJ16">
-        <v>23</v>
-      </c>
-      <c r="AK16">
-        <v>21</v>
-      </c>
-      <c r="AL16">
-        <v>34</v>
-      </c>
       <c r="AM16">
-        <v>95</v>
+        <v>280</v>
       </c>
       <c r="AN16">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO16">
-        <v>55</v>
+        <v>450</v>
       </c>
       <c r="AP16">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AQ16">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AR16">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AS16">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AT16">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AU16">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV16">
-        <v>1.03</v>
+        <v>32</v>
       </c>
       <c r="AW16">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AX16">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AY16">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ16">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BA16">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BB16">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="BC16">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BD16">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BE16">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BF16">
+        <v>7</v>
+      </c>
+      <c r="BG16">
+        <v>6.8</v>
+      </c>
+      <c r="BH16">
+        <v>3.55</v>
+      </c>
+      <c r="BI16">
+        <v>2.74</v>
+      </c>
+      <c r="BJ16">
+        <v>13.5</v>
+      </c>
+      <c r="BK16">
+        <v>8.4</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>10.5</v>
+      </c>
+      <c r="BN16">
+        <v>3.75</v>
+      </c>
+      <c r="BO16">
+        <v>2.9</v>
+      </c>
+      <c r="BP16">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BQ16">
+        <v>5</v>
+      </c>
+      <c r="BR16">
+        <v>32</v>
+      </c>
+      <c r="BS16">
         <v>8.199999999999999</v>
       </c>
-      <c r="BG16">
-        <v>1.01</v>
-      </c>
-      <c r="BH16">
-        <v>3.95</v>
-      </c>
-      <c r="BI16">
-        <v>3.1</v>
-      </c>
-      <c r="BJ16">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK16">
-        <v>5</v>
-      </c>
-      <c r="BL16">
-        <v>1000</v>
-      </c>
-      <c r="BM16">
-        <v>9.4</v>
-      </c>
-      <c r="BN16">
-        <v>4.9</v>
-      </c>
-      <c r="BO16">
-        <v>3.8</v>
-      </c>
-      <c r="BP16">
-        <v>13</v>
-      </c>
-      <c r="BQ16">
-        <v>5.7</v>
-      </c>
-      <c r="BR16">
-        <v>26</v>
-      </c>
-      <c r="BS16">
-        <v>7.4</v>
-      </c>
       <c r="BT16">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="BU16">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BZ16">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="CA16">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB16" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D17" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E17" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F17">
-        <v>2.22</v>
+        <v>1.82</v>
       </c>
       <c r="G17">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="H17">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="I17">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="J17">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="K17">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="L17">
-        <v>1.49</v>
+        <v>1.34</v>
       </c>
       <c r="M17">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="N17">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="O17">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="P17">
-        <v>1.72</v>
+        <v>2.24</v>
       </c>
       <c r="Q17">
+        <v>1.7</v>
+      </c>
+      <c r="R17">
+        <v>1.48</v>
+      </c>
+      <c r="S17">
+        <v>2.78</v>
+      </c>
+      <c r="T17">
+        <v>1.68</v>
+      </c>
+      <c r="U17">
         <v>2.24</v>
       </c>
-      <c r="R17">
-        <v>1.27</v>
-      </c>
-      <c r="S17">
-        <v>4.3</v>
-      </c>
-      <c r="T17">
-        <v>1.95</v>
-      </c>
-      <c r="U17">
-        <v>1.95</v>
-      </c>
       <c r="V17">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="W17">
-        <v>1.78</v>
+        <v>2.12</v>
       </c>
       <c r="X17">
-        <v>12.5</v>
+        <v>22</v>
       </c>
       <c r="Y17">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="Z17">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="AA17">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AB17">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AC17">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="AD17">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AE17">
         <v>60</v>
       </c>
       <c r="AF17">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG17">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH17">
+        <v>21</v>
+      </c>
+      <c r="AI17">
+        <v>60</v>
+      </c>
+      <c r="AJ17">
         <v>23</v>
       </c>
-      <c r="AI17">
-        <v>75</v>
-      </c>
-      <c r="AJ17">
-        <v>36</v>
-      </c>
       <c r="AK17">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AL17">
+        <v>34</v>
+      </c>
+      <c r="AM17">
+        <v>95</v>
+      </c>
+      <c r="AN17">
+        <v>11.5</v>
+      </c>
+      <c r="AO17">
         <v>55</v>
       </c>
-      <c r="AM17">
-        <v>150</v>
-      </c>
-      <c r="AN17">
-        <v>28</v>
-      </c>
-      <c r="AO17">
-        <v>65</v>
-      </c>
       <c r="AP17">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AR17">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AS17">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT17">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU17">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV17">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW17">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AX17">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AY17">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="BA17">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="BB17">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="BC17">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BD17">
+        <v>1.03</v>
+      </c>
+      <c r="BE17">
+        <v>1.03</v>
+      </c>
+      <c r="BF17">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG17">
+        <v>1.01</v>
+      </c>
+      <c r="BH17">
+        <v>3.95</v>
+      </c>
+      <c r="BI17">
+        <v>3.1</v>
+      </c>
+      <c r="BJ17">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK17">
+        <v>5</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
+        <v>9.4</v>
+      </c>
+      <c r="BN17">
+        <v>4.9</v>
+      </c>
+      <c r="BO17">
+        <v>3.8</v>
+      </c>
+      <c r="BP17">
+        <v>13</v>
+      </c>
+      <c r="BQ17">
+        <v>5.7</v>
+      </c>
+      <c r="BR17">
+        <v>26</v>
+      </c>
+      <c r="BS17">
+        <v>7.4</v>
+      </c>
+      <c r="BT17">
+        <v>8.4</v>
+      </c>
+      <c r="BU17">
+        <v>4.6</v>
+      </c>
+      <c r="BV17">
+        <v>1000</v>
+      </c>
+      <c r="BW17">
+        <v>8</v>
+      </c>
+      <c r="BX17">
+        <v>1000</v>
+      </c>
+      <c r="BY17">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BZ17">
+        <v>20</v>
+      </c>
+      <c r="CA17">
         <v>6.8</v>
       </c>
-      <c r="BE17">
-        <v>7.4</v>
-      </c>
-      <c r="BF17">
-        <v>19.5</v>
-      </c>
-      <c r="BG17">
-        <v>7</v>
-      </c>
-      <c r="BH17">
-        <v>3.05</v>
-      </c>
-      <c r="BI17">
-        <v>2.58</v>
-      </c>
-      <c r="BJ17">
-        <v>10.5</v>
-      </c>
-      <c r="BK17">
-        <v>6.4</v>
-      </c>
-      <c r="BL17">
-        <v>1000</v>
-      </c>
-      <c r="BM17">
-        <v>15.5</v>
-      </c>
-      <c r="BN17">
-        <v>5</v>
-      </c>
-      <c r="BO17">
-        <v>4</v>
-      </c>
-      <c r="BP17">
-        <v>1000</v>
-      </c>
-      <c r="BQ17">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BR17">
-        <v>1000</v>
-      </c>
-      <c r="BS17">
-        <v>11.5</v>
-      </c>
-      <c r="BT17">
-        <v>6.8</v>
-      </c>
-      <c r="BU17">
-        <v>5.3</v>
-      </c>
-      <c r="BV17">
-        <v>1000</v>
-      </c>
-      <c r="BW17">
-        <v>11</v>
-      </c>
-      <c r="BX17">
-        <v>1000</v>
-      </c>
-      <c r="BY17">
-        <v>12.5</v>
-      </c>
-      <c r="BZ17">
-        <v>1000</v>
-      </c>
-      <c r="CA17">
-        <v>11.5</v>
-      </c>
       <c r="CB17" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D18" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E18" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F18">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="G18">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="H18">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="I18">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="J18">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="K18">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="L18">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="M18">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="N18">
+        <v>3.1</v>
+      </c>
+      <c r="O18">
+        <v>1.43</v>
+      </c>
+      <c r="P18">
+        <v>1.72</v>
+      </c>
+      <c r="Q18">
+        <v>2.24</v>
+      </c>
+      <c r="R18">
+        <v>1.27</v>
+      </c>
+      <c r="S18">
         <v>4.3</v>
       </c>
-      <c r="O18">
-        <v>1.29</v>
-      </c>
-      <c r="P18">
-        <v>2.1</v>
-      </c>
-      <c r="Q18">
-        <v>1.85</v>
-      </c>
-      <c r="R18">
-        <v>1.43</v>
-      </c>
-      <c r="S18">
-        <v>3.15</v>
-      </c>
       <c r="T18">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="U18">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="V18">
         <v>1.34</v>
       </c>
       <c r="W18">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="X18">
+        <v>12.5</v>
+      </c>
+      <c r="Y18">
+        <v>13</v>
+      </c>
+      <c r="Z18">
+        <v>28</v>
+      </c>
+      <c r="AA18">
+        <v>85</v>
+      </c>
+      <c r="AB18">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC18">
+        <v>8.6</v>
+      </c>
+      <c r="AD18">
         <v>17.5</v>
       </c>
-      <c r="Y18">
-        <v>16</v>
-      </c>
-      <c r="Z18">
+      <c r="AE18">
+        <v>60</v>
+      </c>
+      <c r="AF18">
+        <v>13.5</v>
+      </c>
+      <c r="AG18">
+        <v>12.5</v>
+      </c>
+      <c r="AH18">
+        <v>23</v>
+      </c>
+      <c r="AI18">
+        <v>75</v>
+      </c>
+      <c r="AJ18">
+        <v>36</v>
+      </c>
+      <c r="AK18">
         <v>32</v>
       </c>
-      <c r="AA18">
-        <v>75</v>
-      </c>
-      <c r="AB18">
-        <v>11</v>
-      </c>
-      <c r="AC18">
-        <v>11</v>
-      </c>
-      <c r="AD18">
-        <v>16.5</v>
-      </c>
-      <c r="AE18">
-        <v>46</v>
-      </c>
-      <c r="AF18">
-        <v>14</v>
-      </c>
-      <c r="AG18">
-        <v>11</v>
-      </c>
-      <c r="AH18">
+      <c r="AL18">
+        <v>55</v>
+      </c>
+      <c r="AM18">
+        <v>150</v>
+      </c>
+      <c r="AN18">
+        <v>28</v>
+      </c>
+      <c r="AO18">
+        <v>65</v>
+      </c>
+      <c r="AP18">
+        <v>9.6</v>
+      </c>
+      <c r="AQ18">
+        <v>10</v>
+      </c>
+      <c r="AR18">
         <v>21</v>
       </c>
-      <c r="AI18">
-        <v>50</v>
-      </c>
-      <c r="AJ18">
-        <v>26</v>
-      </c>
-      <c r="AK18">
-        <v>22</v>
-      </c>
-      <c r="AL18">
-        <v>38</v>
-      </c>
-      <c r="AM18">
-        <v>95</v>
-      </c>
-      <c r="AN18">
-        <v>14</v>
-      </c>
-      <c r="AO18">
-        <v>50</v>
-      </c>
-      <c r="AP18">
-        <v>15</v>
-      </c>
-      <c r="AQ18">
+      <c r="AS18">
+        <v>7.8</v>
+      </c>
+      <c r="AT18">
+        <v>7.2</v>
+      </c>
+      <c r="AU18">
+        <v>6.6</v>
+      </c>
+      <c r="AV18">
         <v>13.5</v>
       </c>
-      <c r="AR18">
-        <v>6.8</v>
-      </c>
-      <c r="AS18">
-        <v>8</v>
-      </c>
-      <c r="AT18">
-        <v>9</v>
-      </c>
-      <c r="AU18">
-        <v>7.8</v>
-      </c>
-      <c r="AV18">
-        <v>14</v>
-      </c>
       <c r="AW18">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX18">
         <v>12</v>
       </c>
       <c r="AY18">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ18">
-        <v>15</v>
+        <v>6.2</v>
       </c>
       <c r="BA18">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB18">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BC18">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BD18">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE18">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF18">
-        <v>11</v>
+        <v>19.5</v>
       </c>
       <c r="BG18">
         <v>7.6</v>
       </c>
       <c r="BH18">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="BI18">
-        <v>2.94</v>
+        <v>2.58</v>
       </c>
       <c r="BJ18">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BK18">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="BN18">
         <v>5</v>
       </c>
       <c r="BO18">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BP18">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR18">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BS18">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="BT18">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BU18">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BV18">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW18">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BX18">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY18">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BZ18">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="CA18">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="CB18" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C19" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D19" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E19" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F19">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="G19">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="H19">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="I19">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J19">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K19">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L19">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="M19">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N19">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O19">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P19">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="Q19">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="R19">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="S19">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T19">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U19">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V19">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W19">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="X19">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y19">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Z19">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA19">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB19">
         <v>11</v>
       </c>
       <c r="AC19">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD19">
         <v>16.5</v>
       </c>
       <c r="AE19">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="AF19">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG19">
         <v>11</v>
       </c>
       <c r="AH19">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AI19">
-        <v>55</v>
+        <v>200</v>
       </c>
       <c r="AJ19">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK19">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AL19">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AM19">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN19">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO19">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AP19">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AQ19">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR19">
-        <v>27</v>
+        <v>18.5</v>
       </c>
       <c r="AS19">
         <v>34</v>
       </c>
       <c r="AT19">
+        <v>9.6</v>
+      </c>
+      <c r="AU19">
+        <v>7.8</v>
+      </c>
+      <c r="AV19">
+        <v>14</v>
+      </c>
+      <c r="AW19">
+        <v>24</v>
+      </c>
+      <c r="AX19">
+        <v>12</v>
+      </c>
+      <c r="AY19">
         <v>9.800000000000001</v>
       </c>
-      <c r="AU19">
-        <v>8</v>
-      </c>
-      <c r="AV19">
-        <v>14.5</v>
-      </c>
-      <c r="AW19">
-        <v>40</v>
-      </c>
-      <c r="AX19">
-        <v>11.5</v>
-      </c>
-      <c r="AY19">
-        <v>9.6</v>
-      </c>
       <c r="AZ19">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA19">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="BB19">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BC19">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD19">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="BE19">
         <v>36</v>
       </c>
       <c r="BF19">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BG19">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="BH19">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BI19">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="BJ19">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK19">
+        <v>5.4</v>
+      </c>
+      <c r="BL19">
+        <v>1000</v>
+      </c>
+      <c r="BM19">
+        <v>12</v>
+      </c>
+      <c r="BN19">
         <v>5</v>
       </c>
-      <c r="BL19">
-        <v>1000</v>
-      </c>
-      <c r="BM19">
-        <v>9.6</v>
-      </c>
-      <c r="BN19">
-        <v>5.1</v>
-      </c>
       <c r="BO19">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="BP19">
         <v>14.5</v>
       </c>
       <c r="BQ19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BR19">
         <v>27</v>
       </c>
       <c r="BS19">
+        <v>9</v>
+      </c>
+      <c r="BT19">
         <v>7.4</v>
       </c>
-      <c r="BT19">
-        <v>7.8</v>
-      </c>
       <c r="BU19">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV19">
         <v>32</v>
       </c>
       <c r="BW19">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="BX19">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BY19">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BZ19">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CA19">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="CB19" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C20" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D20" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E20" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F20">
+        <v>2</v>
+      </c>
+      <c r="G20">
+        <v>2.04</v>
+      </c>
+      <c r="H20">
+        <v>3.95</v>
+      </c>
+      <c r="I20">
+        <v>4.2</v>
+      </c>
+      <c r="J20">
+        <v>3.8</v>
+      </c>
+      <c r="K20">
+        <v>3.9</v>
+      </c>
+      <c r="L20">
+        <v>1.36</v>
+      </c>
+      <c r="M20">
+        <v>1.06</v>
+      </c>
+      <c r="N20">
+        <v>4.4</v>
+      </c>
+      <c r="O20">
+        <v>1.27</v>
+      </c>
+      <c r="P20">
+        <v>2.16</v>
+      </c>
+      <c r="Q20">
         <v>1.82</v>
       </c>
-      <c r="G20">
-        <v>1.86</v>
-      </c>
-      <c r="H20">
-        <v>4.2</v>
-      </c>
-      <c r="I20">
-        <v>4.5</v>
-      </c>
-      <c r="J20">
-        <v>4.3</v>
-      </c>
-      <c r="K20">
-        <v>4.6</v>
-      </c>
-      <c r="L20">
-        <v>1.27</v>
-      </c>
-      <c r="M20">
-        <v>1.03</v>
-      </c>
-      <c r="N20">
-        <v>6.4</v>
-      </c>
-      <c r="O20">
-        <v>1.17</v>
-      </c>
-      <c r="P20">
-        <v>2.8</v>
-      </c>
-      <c r="Q20">
-        <v>1.52</v>
-      </c>
       <c r="R20">
-        <v>1.71</v>
+        <v>1.45</v>
       </c>
       <c r="S20">
-        <v>2.32</v>
+        <v>3.1</v>
       </c>
       <c r="T20">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="U20">
-        <v>2.66</v>
+        <v>2.28</v>
       </c>
       <c r="V20">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W20">
-        <v>2.16</v>
+        <v>1.96</v>
       </c>
       <c r="X20">
+        <v>18.5</v>
+      </c>
+      <c r="Y20">
+        <v>17.5</v>
+      </c>
+      <c r="Z20">
         <v>32</v>
       </c>
-      <c r="Y20">
-        <v>26</v>
-      </c>
-      <c r="Z20">
+      <c r="AA20">
+        <v>1000</v>
+      </c>
+      <c r="AB20">
+        <v>11</v>
+      </c>
+      <c r="AC20">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD20">
+        <v>16.5</v>
+      </c>
+      <c r="AE20">
+        <v>48</v>
+      </c>
+      <c r="AF20">
+        <v>13</v>
+      </c>
+      <c r="AG20">
+        <v>11</v>
+      </c>
+      <c r="AH20">
+        <v>17.5</v>
+      </c>
+      <c r="AI20">
+        <v>55</v>
+      </c>
+      <c r="AJ20">
+        <v>25</v>
+      </c>
+      <c r="AK20">
+        <v>20</v>
+      </c>
+      <c r="AL20">
+        <v>32</v>
+      </c>
+      <c r="AM20">
+        <v>85</v>
+      </c>
+      <c r="AN20">
+        <v>12.5</v>
+      </c>
+      <c r="AO20">
+        <v>42</v>
+      </c>
+      <c r="AP20">
+        <v>15.5</v>
+      </c>
+      <c r="AQ20">
+        <v>15.5</v>
+      </c>
+      <c r="AR20">
+        <v>27</v>
+      </c>
+      <c r="AS20">
+        <v>34</v>
+      </c>
+      <c r="AT20">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU20">
+        <v>8</v>
+      </c>
+      <c r="AV20">
+        <v>14.5</v>
+      </c>
+      <c r="AW20">
         <v>40</v>
       </c>
-      <c r="AA20">
-        <v>95</v>
-      </c>
-      <c r="AB20">
-        <v>15</v>
-      </c>
-      <c r="AC20">
-        <v>11</v>
-      </c>
-      <c r="AD20">
-        <v>18.5</v>
-      </c>
-      <c r="AE20">
-        <v>46</v>
-      </c>
-      <c r="AF20">
-        <v>15</v>
-      </c>
-      <c r="AG20">
-        <v>12</v>
-      </c>
-      <c r="AH20">
-        <v>16.5</v>
-      </c>
-      <c r="AI20">
-        <v>90</v>
-      </c>
-      <c r="AJ20">
-        <v>22</v>
-      </c>
-      <c r="AK20">
-        <v>16.5</v>
-      </c>
-      <c r="AL20">
-        <v>26</v>
-      </c>
-      <c r="AM20">
-        <v>60</v>
-      </c>
-      <c r="AN20">
-        <v>7.2</v>
-      </c>
-      <c r="AO20">
-        <v>34</v>
-      </c>
-      <c r="AP20">
-        <v>25</v>
-      </c>
-      <c r="AQ20">
-        <v>20</v>
-      </c>
-      <c r="AR20">
-        <v>23</v>
-      </c>
-      <c r="AS20">
-        <v>36</v>
-      </c>
-      <c r="AT20">
-        <v>13</v>
-      </c>
-      <c r="AU20">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV20">
-        <v>15.5</v>
-      </c>
-      <c r="AW20">
-        <v>24</v>
-      </c>
       <c r="AX20">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AY20">
         <v>9.6</v>
       </c>
       <c r="AZ20">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA20">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="BB20">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BC20">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD20">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BE20">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="BF20">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="BG20">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="BH20">
-        <v>4.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI20">
-        <v>3.8</v>
+        <v>2.96</v>
       </c>
       <c r="BJ20">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK20">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>12.5</v>
+        <v>9.6</v>
       </c>
       <c r="BN20">
         <v>5.1</v>
       </c>
       <c r="BO20">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="BP20">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="BQ20">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="BR20">
-        <v>19.5</v>
+        <v>27</v>
       </c>
       <c r="BS20">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT20">
+        <v>7.8</v>
+      </c>
+      <c r="BU20">
+        <v>5.5</v>
+      </c>
+      <c r="BV20">
+        <v>32</v>
+      </c>
+      <c r="BW20">
+        <v>7.8</v>
+      </c>
+      <c r="BX20">
+        <v>40</v>
+      </c>
+      <c r="BY20">
         <v>8.199999999999999</v>
       </c>
-      <c r="BU20">
-        <v>5.4</v>
-      </c>
-      <c r="BV20">
-        <v>29</v>
-      </c>
-      <c r="BW20">
-        <v>10</v>
-      </c>
-      <c r="BX20">
-        <v>32</v>
-      </c>
-      <c r="BY20">
-        <v>10</v>
-      </c>
       <c r="BZ20">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="CA20">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="CB20" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D21" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E21" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F21">
-        <v>4</v>
+        <v>1.81</v>
       </c>
       <c r="G21">
-        <v>4.3</v>
+        <v>1.84</v>
       </c>
       <c r="H21">
-        <v>1.84</v>
+        <v>4.2</v>
       </c>
       <c r="I21">
-        <v>1.88</v>
+        <v>4.5</v>
       </c>
       <c r="J21">
         <v>4.4</v>
       </c>
       <c r="K21">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L21">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="M21">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N21">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="O21">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="P21">
-        <v>3.2</v>
+        <v>2.78</v>
       </c>
       <c r="Q21">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="R21">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="S21">
-        <v>2.06</v>
+        <v>2.32</v>
       </c>
       <c r="T21">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="U21">
-        <v>3.05</v>
+        <v>2.66</v>
       </c>
       <c r="V21">
-        <v>2.12</v>
+        <v>1.28</v>
       </c>
       <c r="W21">
-        <v>1.31</v>
+        <v>2.18</v>
       </c>
       <c r="X21">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="Y21">
+        <v>26</v>
+      </c>
+      <c r="Z21">
+        <v>42</v>
+      </c>
+      <c r="AA21">
+        <v>95</v>
+      </c>
+      <c r="AB21">
+        <v>15</v>
+      </c>
+      <c r="AC21">
+        <v>11</v>
+      </c>
+      <c r="AD21">
         <v>18.5</v>
       </c>
-      <c r="Z21">
-        <v>17.5</v>
-      </c>
-      <c r="AA21">
+      <c r="AE21">
+        <v>44</v>
+      </c>
+      <c r="AF21">
+        <v>15</v>
+      </c>
+      <c r="AG21">
+        <v>12</v>
+      </c>
+      <c r="AH21">
+        <v>16.5</v>
+      </c>
+      <c r="AI21">
+        <v>100</v>
+      </c>
+      <c r="AJ21">
+        <v>23</v>
+      </c>
+      <c r="AK21">
+        <v>16.5</v>
+      </c>
+      <c r="AL21">
+        <v>26</v>
+      </c>
+      <c r="AM21">
+        <v>60</v>
+      </c>
+      <c r="AN21">
+        <v>7.2</v>
+      </c>
+      <c r="AO21">
+        <v>34</v>
+      </c>
+      <c r="AP21">
+        <v>19.5</v>
+      </c>
+      <c r="AQ21">
+        <v>20</v>
+      </c>
+      <c r="AR21">
+        <v>23</v>
+      </c>
+      <c r="AS21">
+        <v>36</v>
+      </c>
+      <c r="AT21">
+        <v>12.5</v>
+      </c>
+      <c r="AU21">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV21">
+        <v>15.5</v>
+      </c>
+      <c r="AW21">
         <v>24</v>
       </c>
-      <c r="AB21">
-        <v>29</v>
-      </c>
-      <c r="AC21">
-        <v>11.5</v>
-      </c>
-      <c r="AD21">
-        <v>11.5</v>
-      </c>
-      <c r="AE21">
-        <v>16.5</v>
-      </c>
-      <c r="AF21">
-        <v>42</v>
-      </c>
-      <c r="AG21">
-        <v>18.5</v>
-      </c>
-      <c r="AH21">
-        <v>15</v>
-      </c>
-      <c r="AI21">
-        <v>23</v>
-      </c>
-      <c r="AJ21">
-        <v>1000</v>
-      </c>
-      <c r="AK21">
-        <v>40</v>
-      </c>
-      <c r="AL21">
-        <v>38</v>
-      </c>
-      <c r="AM21">
-        <v>48</v>
-      </c>
-      <c r="AN21">
+      <c r="AX21">
+        <v>13</v>
+      </c>
+      <c r="AY21">
+        <v>9.6</v>
+      </c>
+      <c r="AZ21">
+        <v>13.5</v>
+      </c>
+      <c r="BA21">
         <v>24</v>
       </c>
-      <c r="AO21">
+      <c r="BB21">
+        <v>18</v>
+      </c>
+      <c r="BC21">
+        <v>14.5</v>
+      </c>
+      <c r="BD21">
+        <v>21</v>
+      </c>
+      <c r="BE21">
+        <v>28</v>
+      </c>
+      <c r="BF21">
         <v>6.6</v>
       </c>
-      <c r="AP21">
-        <v>23</v>
-      </c>
-      <c r="AQ21">
-        <v>15.5</v>
-      </c>
-      <c r="AR21">
-        <v>15</v>
-      </c>
-      <c r="AS21">
-        <v>20</v>
-      </c>
-      <c r="AT21">
-        <v>18.5</v>
-      </c>
-      <c r="AU21">
-        <v>10</v>
-      </c>
-      <c r="AV21">
-        <v>10</v>
-      </c>
-      <c r="AW21">
-        <v>14.5</v>
-      </c>
-      <c r="AX21">
-        <v>23</v>
-      </c>
-      <c r="AY21">
-        <v>16</v>
-      </c>
-      <c r="AZ21">
-        <v>13</v>
-      </c>
-      <c r="BA21">
-        <v>19</v>
-      </c>
-      <c r="BB21">
-        <v>36</v>
-      </c>
-      <c r="BC21">
-        <v>23</v>
-      </c>
-      <c r="BD21">
-        <v>22</v>
-      </c>
-      <c r="BE21">
-        <v>25</v>
-      </c>
-      <c r="BF21">
-        <v>20</v>
-      </c>
       <c r="BG21">
-        <v>5.9</v>
+        <v>21</v>
       </c>
       <c r="BH21">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BI21">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="BJ21">
         <v>8.800000000000001</v>
       </c>
       <c r="BK21">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL21">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BM21">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="BN21">
-        <v>8.6</v>
+        <v>5.1</v>
       </c>
       <c r="BO21">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="BP21">
-        <v>27</v>
+        <v>11.5</v>
       </c>
       <c r="BQ21">
         <v>7.2</v>
       </c>
       <c r="BR21">
+        <v>20</v>
+      </c>
+      <c r="BS21">
+        <v>8.6</v>
+      </c>
+      <c r="BT21">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU21">
+        <v>5.4</v>
+      </c>
+      <c r="BV21">
         <v>29</v>
       </c>
-      <c r="BS21">
-        <v>7.4</v>
-      </c>
-      <c r="BT21">
-        <v>5.6</v>
-      </c>
-      <c r="BU21">
-        <v>4.1</v>
-      </c>
-      <c r="BV21">
-        <v>12</v>
-      </c>
       <c r="BW21">
-        <v>5.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX21">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="BY21">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="BZ21">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CA21">
-        <v>5.4</v>
+        <v>10</v>
       </c>
       <c r="CB21" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D22" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E22" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F22">
-        <v>2.14</v>
+        <v>4</v>
       </c>
       <c r="G22">
-        <v>2.16</v>
+        <v>4.2</v>
       </c>
       <c r="H22">
-        <v>3.25</v>
+        <v>1.85</v>
       </c>
       <c r="I22">
-        <v>3.35</v>
+        <v>1.89</v>
       </c>
       <c r="J22">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K22">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="L22">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="M22">
         <v>1.02</v>
       </c>
       <c r="N22">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="O22">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="P22">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="Q22">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="R22">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="S22">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="T22">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="U22">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="V22">
-        <v>1.42</v>
+        <v>2.12</v>
       </c>
       <c r="W22">
-        <v>1.86</v>
+        <v>1.31</v>
       </c>
       <c r="X22">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Y22">
-        <v>30</v>
+        <v>18.5</v>
       </c>
       <c r="Z22">
-        <v>34</v>
+        <v>17.5</v>
       </c>
       <c r="AA22">
-        <v>380</v>
+        <v>24</v>
       </c>
       <c r="AB22">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AC22">
         <v>11.5</v>
       </c>
       <c r="AD22">
+        <v>11.5</v>
+      </c>
+      <c r="AE22">
+        <v>16.5</v>
+      </c>
+      <c r="AF22">
+        <v>42</v>
+      </c>
+      <c r="AG22">
+        <v>18.5</v>
+      </c>
+      <c r="AH22">
+        <v>15</v>
+      </c>
+      <c r="AI22">
+        <v>23</v>
+      </c>
+      <c r="AJ22">
+        <v>1000</v>
+      </c>
+      <c r="AK22">
+        <v>40</v>
+      </c>
+      <c r="AL22">
+        <v>38</v>
+      </c>
+      <c r="AM22">
+        <v>48</v>
+      </c>
+      <c r="AN22">
+        <v>24</v>
+      </c>
+      <c r="AO22">
+        <v>6.6</v>
+      </c>
+      <c r="AP22">
+        <v>23</v>
+      </c>
+      <c r="AQ22">
         <v>15.5</v>
       </c>
-      <c r="AE22">
-        <v>29</v>
-      </c>
-      <c r="AF22">
-        <v>22</v>
-      </c>
-      <c r="AG22">
-        <v>12.5</v>
-      </c>
-      <c r="AH22">
-        <v>14</v>
-      </c>
-      <c r="AI22">
-        <v>28</v>
-      </c>
-      <c r="AJ22">
-        <v>32</v>
-      </c>
-      <c r="AK22">
+      <c r="AR22">
+        <v>15</v>
+      </c>
+      <c r="AS22">
+        <v>20</v>
+      </c>
+      <c r="AT22">
         <v>18.5</v>
-      </c>
-      <c r="AL22">
-        <v>22</v>
-      </c>
-      <c r="AM22">
-        <v>42</v>
-      </c>
-      <c r="AN22">
-        <v>7.6</v>
-      </c>
-      <c r="AO22">
-        <v>14.5</v>
-      </c>
-      <c r="AP22">
-        <v>32</v>
-      </c>
-      <c r="AQ22">
-        <v>24</v>
-      </c>
-      <c r="AR22">
-        <v>29</v>
-      </c>
-      <c r="AS22">
-        <v>46</v>
-      </c>
-      <c r="AT22">
-        <v>19.5</v>
       </c>
       <c r="AU22">
         <v>10</v>
       </c>
       <c r="AV22">
+        <v>10</v>
+      </c>
+      <c r="AW22">
+        <v>14.5</v>
+      </c>
+      <c r="AX22">
+        <v>23</v>
+      </c>
+      <c r="AY22">
+        <v>16</v>
+      </c>
+      <c r="AZ22">
+        <v>13</v>
+      </c>
+      <c r="BA22">
+        <v>19</v>
+      </c>
+      <c r="BB22">
+        <v>36</v>
+      </c>
+      <c r="BC22">
+        <v>23</v>
+      </c>
+      <c r="BD22">
+        <v>22</v>
+      </c>
+      <c r="BE22">
+        <v>25</v>
+      </c>
+      <c r="BF22">
+        <v>20</v>
+      </c>
+      <c r="BG22">
+        <v>5.9</v>
+      </c>
+      <c r="BH22">
+        <v>5.4</v>
+      </c>
+      <c r="BI22">
+        <v>4</v>
+      </c>
+      <c r="BJ22">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK22">
+        <v>4.6</v>
+      </c>
+      <c r="BL22">
+        <v>65</v>
+      </c>
+      <c r="BM22">
+        <v>8.6</v>
+      </c>
+      <c r="BN22">
+        <v>8.6</v>
+      </c>
+      <c r="BO22">
+        <v>6</v>
+      </c>
+      <c r="BP22">
+        <v>27</v>
+      </c>
+      <c r="BQ22">
+        <v>7.2</v>
+      </c>
+      <c r="BR22">
+        <v>29</v>
+      </c>
+      <c r="BS22">
+        <v>7.4</v>
+      </c>
+      <c r="BT22">
+        <v>5.6</v>
+      </c>
+      <c r="BU22">
+        <v>4.1</v>
+      </c>
+      <c r="BV22">
+        <v>12</v>
+      </c>
+      <c r="BW22">
+        <v>5.4</v>
+      </c>
+      <c r="BX22">
+        <v>19</v>
+      </c>
+      <c r="BY22">
+        <v>6.4</v>
+      </c>
+      <c r="BZ22">
+        <v>12</v>
+      </c>
+      <c r="CA22">
+        <v>5.4</v>
+      </c>
+      <c r="CB22" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80">
+      <c r="A23" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23" t="s">
+        <v>123</v>
+      </c>
+      <c r="E23" t="s">
+        <v>145</v>
+      </c>
+      <c r="F23">
+        <v>2.18</v>
+      </c>
+      <c r="G23">
+        <v>2.2</v>
+      </c>
+      <c r="H23">
+        <v>3.15</v>
+      </c>
+      <c r="I23">
+        <v>3.2</v>
+      </c>
+      <c r="J23">
+        <v>4.2</v>
+      </c>
+      <c r="K23">
+        <v>4.4</v>
+      </c>
+      <c r="L23">
+        <v>1.21</v>
+      </c>
+      <c r="M23">
+        <v>1.02</v>
+      </c>
+      <c r="N23">
+        <v>8.4</v>
+      </c>
+      <c r="O23">
+        <v>1.12</v>
+      </c>
+      <c r="P23">
+        <v>3.4</v>
+      </c>
+      <c r="Q23">
+        <v>1.38</v>
+      </c>
+      <c r="R23">
+        <v>1.99</v>
+      </c>
+      <c r="S23">
+        <v>1.96</v>
+      </c>
+      <c r="T23">
+        <v>1.39</v>
+      </c>
+      <c r="U23">
+        <v>3.35</v>
+      </c>
+      <c r="V23">
+        <v>1.45</v>
+      </c>
+      <c r="W23">
+        <v>1.83</v>
+      </c>
+      <c r="X23">
+        <v>42</v>
+      </c>
+      <c r="Y23">
+        <v>30</v>
+      </c>
+      <c r="Z23">
+        <v>34</v>
+      </c>
+      <c r="AA23">
+        <v>230</v>
+      </c>
+      <c r="AB23">
+        <v>22</v>
+      </c>
+      <c r="AC23">
+        <v>12</v>
+      </c>
+      <c r="AD23">
+        <v>15.5</v>
+      </c>
+      <c r="AE23">
+        <v>29</v>
+      </c>
+      <c r="AF23">
+        <v>22</v>
+      </c>
+      <c r="AG23">
+        <v>12.5</v>
+      </c>
+      <c r="AH23">
+        <v>14</v>
+      </c>
+      <c r="AI23">
+        <v>28</v>
+      </c>
+      <c r="AJ23">
+        <v>32</v>
+      </c>
+      <c r="AK23">
+        <v>19</v>
+      </c>
+      <c r="AL23">
+        <v>23</v>
+      </c>
+      <c r="AM23">
+        <v>42</v>
+      </c>
+      <c r="AN23">
+        <v>7.6</v>
+      </c>
+      <c r="AO23">
+        <v>14</v>
+      </c>
+      <c r="AP23">
+        <v>32</v>
+      </c>
+      <c r="AQ23">
+        <v>24</v>
+      </c>
+      <c r="AR23">
+        <v>29</v>
+      </c>
+      <c r="AS23">
+        <v>46</v>
+      </c>
+      <c r="AT23">
+        <v>19.5</v>
+      </c>
+      <c r="AU23">
+        <v>10.5</v>
+      </c>
+      <c r="AV23">
         <v>13.5</v>
       </c>
-      <c r="AW22">
+      <c r="AW23">
         <v>25</v>
       </c>
-      <c r="AX22">
+      <c r="AX23">
         <v>19</v>
       </c>
-      <c r="AY22">
-        <v>10.5</v>
-      </c>
-      <c r="AZ22">
+      <c r="AY23">
+        <v>11</v>
+      </c>
+      <c r="AZ23">
         <v>12</v>
       </c>
-      <c r="BA22">
+      <c r="BA23">
         <v>24</v>
       </c>
-      <c r="BB22">
+      <c r="BB23">
         <v>27</v>
       </c>
-      <c r="BC22">
+      <c r="BC23">
         <v>16.5</v>
       </c>
-      <c r="BD22">
+      <c r="BD23">
         <v>19</v>
       </c>
-      <c r="BE22">
+      <c r="BE23">
         <v>34</v>
       </c>
-      <c r="BF22">
+      <c r="BF23">
         <v>6.8</v>
       </c>
-      <c r="BG22">
-        <v>13</v>
-      </c>
-      <c r="BH22">
+      <c r="BG23">
+        <v>12</v>
+      </c>
+      <c r="BH23">
         <v>5.8</v>
       </c>
-      <c r="BI22">
+      <c r="BI23">
         <v>4.2</v>
       </c>
-      <c r="BJ22">
-        <v>8.6</v>
-      </c>
-      <c r="BK22">
+      <c r="BJ23">
+        <v>8.4</v>
+      </c>
+      <c r="BK23">
         <v>6</v>
       </c>
-      <c r="BL22">
-        <v>1000</v>
-      </c>
-      <c r="BM22">
+      <c r="BL23">
+        <v>1000</v>
+      </c>
+      <c r="BM23">
+        <v>8</v>
+      </c>
+      <c r="BN23">
+        <v>6.4</v>
+      </c>
+      <c r="BO23">
+        <v>4.6</v>
+      </c>
+      <c r="BP23">
+        <v>14.5</v>
+      </c>
+      <c r="BQ23">
         <v>8.199999999999999</v>
       </c>
-      <c r="BN22">
-        <v>6.2</v>
-      </c>
-      <c r="BO22">
-        <v>4.5</v>
-      </c>
-      <c r="BP22">
-        <v>14</v>
-      </c>
-      <c r="BQ22">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR22">
-        <v>19</v>
-      </c>
-      <c r="BS22">
+      <c r="BR23">
+        <v>19.5</v>
+      </c>
+      <c r="BS23">
         <v>6.4</v>
       </c>
-      <c r="BT22">
-        <v>7.8</v>
-      </c>
-      <c r="BU22">
-        <v>5.6</v>
-      </c>
-      <c r="BV22">
+      <c r="BT23">
+        <v>7.6</v>
+      </c>
+      <c r="BU23">
+        <v>5.5</v>
+      </c>
+      <c r="BV23">
         <v>21</v>
       </c>
-      <c r="BW22">
+      <c r="BW23">
+        <v>6.4</v>
+      </c>
+      <c r="BX23">
+        <v>23</v>
+      </c>
+      <c r="BY23">
         <v>6.6</v>
       </c>
-      <c r="BX22">
-        <v>24</v>
-      </c>
-      <c r="BY22">
-        <v>6.8</v>
-      </c>
-      <c r="BZ22">
+      <c r="BZ23">
         <v>11.5</v>
       </c>
-      <c r="CA22">
+      <c r="CA23">
         <v>8</v>
       </c>
-      <c r="CB22" t="s">
-        <v>142</v>
+      <c r="CB23" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
@@ -454,7 +454,7 @@
     <t>Chicago Fire</t>
   </si>
   <si>
-    <t>2026-07-21 15:35:26</t>
+    <t>2026-07-21 17:42:25</t>
   </si>
 </sst>
 </file>
@@ -1048,19 +1048,19 @@
         <v>124</v>
       </c>
       <c r="F2">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="G2">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="H2">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I2">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="J2">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K2">
         <v>3.6</v>
@@ -1078,49 +1078,49 @@
         <v>1.36</v>
       </c>
       <c r="P2">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q2">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="R2">
         <v>1.33</v>
       </c>
       <c r="S2">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T2">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U2">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V2">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W2">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="X2">
         <v>13</v>
       </c>
       <c r="Y2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z2">
         <v>32</v>
       </c>
       <c r="AA2">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB2">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD2">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE2">
         <v>60</v>
@@ -1132,7 +1132,7 @@
         <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI2">
         <v>70</v>
@@ -1141,34 +1141,34 @@
         <v>24</v>
       </c>
       <c r="AK2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL2">
         <v>40</v>
       </c>
       <c r="AM2">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO2">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AP2">
         <v>11.5</v>
       </c>
       <c r="AQ2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR2">
         <v>27</v>
       </c>
       <c r="AS2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AT2">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AU2">
         <v>7.4</v>
@@ -1177,10 +1177,10 @@
         <v>15.5</v>
       </c>
       <c r="AW2">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AX2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY2">
         <v>9.4</v>
@@ -1201,7 +1201,7 @@
         <v>34</v>
       </c>
       <c r="BE2">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BF2">
         <v>14</v>
@@ -1225,19 +1225,19 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BN2">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO2">
         <v>4.1</v>
       </c>
       <c r="BP2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BQ2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BR2">
         <v>1000</v>
@@ -1246,22 +1246,22 @@
         <v>11.5</v>
       </c>
       <c r="BT2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU2">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BV2">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BZ2">
         <v>26</v>
@@ -1290,13 +1290,13 @@
         <v>125</v>
       </c>
       <c r="F3">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="G3">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="H3">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I3">
         <v>3.4</v>
@@ -1305,7 +1305,7 @@
         <v>3.05</v>
       </c>
       <c r="K3">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L3">
         <v>1.52</v>
@@ -1317,13 +1317,13 @@
         <v>3</v>
       </c>
       <c r="O3">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P3">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q3">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R3">
         <v>1.24</v>
@@ -1332,34 +1332,34 @@
         <v>4.8</v>
       </c>
       <c r="T3">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="U3">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V3">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W3">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X3">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="Y3">
         <v>10.5</v>
       </c>
       <c r="Z3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA3">
         <v>65</v>
       </c>
       <c r="AB3">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD3">
         <v>15</v>
@@ -1371,16 +1371,16 @@
         <v>15.5</v>
       </c>
       <c r="AG3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI3">
         <v>65</v>
       </c>
       <c r="AJ3">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK3">
         <v>36</v>
@@ -1401,16 +1401,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ3">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR3">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AS3">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="AT3">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU3">
         <v>6.4</v>
@@ -1419,7 +1419,7 @@
         <v>13</v>
       </c>
       <c r="AW3">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AX3">
         <v>13.5</v>
@@ -1428,28 +1428,28 @@
         <v>11</v>
       </c>
       <c r="AZ3">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA3">
+        <v>55</v>
+      </c>
+      <c r="BB3">
+        <v>34</v>
+      </c>
+      <c r="BC3">
+        <v>30</v>
+      </c>
+      <c r="BD3">
         <v>48</v>
-      </c>
-      <c r="BB3">
-        <v>30</v>
-      </c>
-      <c r="BC3">
-        <v>27</v>
-      </c>
-      <c r="BD3">
-        <v>40</v>
       </c>
       <c r="BE3">
         <v>42</v>
       </c>
       <c r="BF3">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BG3">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="BH3">
         <v>2.96</v>
@@ -1532,25 +1532,25 @@
         <v>126</v>
       </c>
       <c r="F4">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="G4">
         <v>1.38</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I4">
         <v>9.199999999999999</v>
       </c>
       <c r="J4">
+        <v>6</v>
+      </c>
+      <c r="K4">
         <v>6.2</v>
       </c>
-      <c r="K4">
-        <v>6.6</v>
-      </c>
       <c r="L4">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M4">
         <v>1.04</v>
@@ -1562,13 +1562,13 @@
         <v>1.21</v>
       </c>
       <c r="P4">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="Q4">
         <v>1.63</v>
       </c>
       <c r="R4">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="S4">
         <v>2.6</v>
@@ -1586,13 +1586,13 @@
         <v>3.6</v>
       </c>
       <c r="X4">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Y4">
         <v>32</v>
       </c>
       <c r="Z4">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AA4">
         <v>340</v>
@@ -1601,7 +1601,7 @@
         <v>9.6</v>
       </c>
       <c r="AC4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD4">
         <v>32</v>
@@ -1610,13 +1610,13 @@
         <v>130</v>
       </c>
       <c r="AF4">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG4">
         <v>10.5</v>
       </c>
       <c r="AH4">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AI4">
         <v>120</v>
@@ -1625,13 +1625,13 @@
         <v>11.5</v>
       </c>
       <c r="AK4">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AL4">
         <v>32</v>
       </c>
       <c r="AM4">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN4">
         <v>5.2</v>
@@ -1640,13 +1640,13 @@
         <v>140</v>
       </c>
       <c r="AP4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AR4">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AS4">
         <v>55</v>
@@ -1655,13 +1655,13 @@
         <v>9</v>
       </c>
       <c r="AU4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AV4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AW4">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="AX4">
         <v>8</v>
@@ -1670,10 +1670,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA4">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="BB4">
         <v>10.5</v>
@@ -1682,13 +1682,13 @@
         <v>12.5</v>
       </c>
       <c r="BD4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE4">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="BF4">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BG4">
         <v>90</v>
@@ -1700,58 +1700,58 @@
         <v>4</v>
       </c>
       <c r="BJ4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK4">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM4">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="BN4">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BO4">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP4">
         <v>8</v>
       </c>
       <c r="BQ4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR4">
         <v>22</v>
       </c>
       <c r="BS4">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BT4">
         <v>12.5</v>
       </c>
       <c r="BU4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BW4">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="BX4">
         <v>65</v>
       </c>
       <c r="BY4">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BZ4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="CA4">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="CB4" t="s">
         <v>146</v>
@@ -1774,22 +1774,22 @@
         <v>127</v>
       </c>
       <c r="F5">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="G5">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="H5">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="I5">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="J5">
         <v>4.4</v>
       </c>
       <c r="K5">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L5">
         <v>1.32</v>
@@ -1804,28 +1804,28 @@
         <v>1.23</v>
       </c>
       <c r="P5">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q5">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R5">
         <v>1.54</v>
       </c>
       <c r="S5">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="T5">
         <v>1.74</v>
       </c>
       <c r="U5">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V5">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W5">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="X5">
         <v>22</v>
@@ -1837,7 +1837,7 @@
         <v>46</v>
       </c>
       <c r="AA5">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AB5">
         <v>11</v>
@@ -1846,7 +1846,7 @@
         <v>10.5</v>
       </c>
       <c r="AD5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE5">
         <v>65</v>
@@ -1858,16 +1858,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH5">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI5">
         <v>60</v>
       </c>
       <c r="AJ5">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AK5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL5">
         <v>29</v>
@@ -1876,10 +1876,10 @@
         <v>85</v>
       </c>
       <c r="AN5">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AO5">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AP5">
         <v>19</v>
@@ -1891,7 +1891,7 @@
         <v>38</v>
       </c>
       <c r="AS5">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="AT5">
         <v>10</v>
@@ -1924,76 +1924,76 @@
         <v>14</v>
       </c>
       <c r="BD5">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BE5">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BF5">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BG5">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="BH5">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI5">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="BJ5">
         <v>10</v>
       </c>
       <c r="BK5">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="BL5">
         <v>110</v>
       </c>
       <c r="BM5">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BN5">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO5">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="BP5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ5">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BS5">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BT5">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BU5">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BV5">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BW5">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX5">
         <v>46</v>
       </c>
       <c r="BY5">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ5">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="CA5">
-        <v>6.2</v>
+        <v>12.5</v>
       </c>
       <c r="CB5" t="s">
         <v>146</v>
@@ -2025,25 +2025,25 @@
         <v>2.66</v>
       </c>
       <c r="I6">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="J6">
         <v>3.15</v>
       </c>
       <c r="K6">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L6">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="M6">
         <v>1.11</v>
       </c>
       <c r="N6">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="O6">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P6">
         <v>1.63</v>
@@ -2061,19 +2061,19 @@
         <v>2.04</v>
       </c>
       <c r="U6">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="V6">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W6">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X6">
         <v>10</v>
       </c>
       <c r="Y6">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z6">
         <v>19.5</v>
@@ -2121,31 +2121,31 @@
         <v>55</v>
       </c>
       <c r="AO6">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP6">
         <v>9</v>
       </c>
       <c r="AQ6">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR6">
         <v>14.5</v>
       </c>
       <c r="AS6">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT6">
         <v>8.6</v>
       </c>
       <c r="AU6">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV6">
         <v>11.5</v>
       </c>
       <c r="AW6">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AX6">
         <v>16.5</v>
@@ -2157,25 +2157,25 @@
         <v>18</v>
       </c>
       <c r="BA6">
+        <v>10.5</v>
+      </c>
+      <c r="BB6">
+        <v>10.5</v>
+      </c>
+      <c r="BC6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BD6">
+        <v>10.5</v>
+      </c>
+      <c r="BE6">
+        <v>11.5</v>
+      </c>
+      <c r="BF6">
         <v>10</v>
       </c>
-      <c r="BB6">
-        <v>10</v>
-      </c>
-      <c r="BC6">
+      <c r="BG6">
         <v>9.4</v>
-      </c>
-      <c r="BD6">
-        <v>10</v>
-      </c>
-      <c r="BE6">
-        <v>11</v>
-      </c>
-      <c r="BF6">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BG6">
-        <v>9.199999999999999</v>
       </c>
       <c r="BH6">
         <v>2.84</v>
@@ -2208,7 +2208,7 @@
         <v>10.5</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS6">
         <v>12</v>
@@ -2217,7 +2217,7 @@
         <v>5.5</v>
       </c>
       <c r="BU6">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BV6">
         <v>24</v>
@@ -2258,16 +2258,16 @@
         <v>129</v>
       </c>
       <c r="F7">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="G7">
         <v>5</v>
       </c>
       <c r="H7">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="I7">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="J7">
         <v>3.6</v>
@@ -2276,22 +2276,22 @@
         <v>3.75</v>
       </c>
       <c r="L7">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="M7">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O7">
         <v>1.39</v>
       </c>
       <c r="P7">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q7">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R7">
         <v>1.3</v>
@@ -2303,10 +2303,10 @@
         <v>1.99</v>
       </c>
       <c r="U7">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V7">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="W7">
         <v>1.25</v>
@@ -2315,7 +2315,7 @@
         <v>12.5</v>
       </c>
       <c r="Y7">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="Z7">
         <v>11</v>
@@ -2336,7 +2336,7 @@
         <v>24</v>
       </c>
       <c r="AF7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AG7">
         <v>20</v>
@@ -2375,7 +2375,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AS7">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AT7">
         <v>13</v>
@@ -2384,22 +2384,22 @@
         <v>7.2</v>
       </c>
       <c r="AV7">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW7">
         <v>18.5</v>
       </c>
       <c r="AX7">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="AY7">
         <v>16.5</v>
       </c>
       <c r="AZ7">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA7">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="BB7">
         <v>40</v>
@@ -2435,7 +2435,7 @@
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN7">
         <v>8.199999999999999</v>
@@ -2447,7 +2447,7 @@
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BR7">
         <v>1000</v>
@@ -2459,7 +2459,7 @@
         <v>4.5</v>
       </c>
       <c r="BU7">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BV7">
         <v>14</v>
@@ -2471,7 +2471,7 @@
         <v>32</v>
       </c>
       <c r="BY7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ7">
         <v>29</v>
@@ -2500,25 +2500,25 @@
         <v>130</v>
       </c>
       <c r="F8">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="G8">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="H8">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I8">
         <v>5.1</v>
       </c>
       <c r="J8">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K8">
         <v>3.65</v>
       </c>
       <c r="L8">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="M8">
         <v>1.1</v>
@@ -2527,13 +2527,13 @@
         <v>3.05</v>
       </c>
       <c r="O8">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P8">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q8">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="R8">
         <v>1.25</v>
@@ -2542,7 +2542,7 @@
         <v>4.5</v>
       </c>
       <c r="T8">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U8">
         <v>1.85</v>
@@ -2551,10 +2551,10 @@
         <v>1.24</v>
       </c>
       <c r="W8">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X8">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y8">
         <v>14</v>
@@ -2563,7 +2563,7 @@
         <v>40</v>
       </c>
       <c r="AA8">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
         <v>7.2</v>
@@ -2575,49 +2575,49 @@
         <v>22</v>
       </c>
       <c r="AE8">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
+        <v>10.5</v>
+      </c>
+      <c r="AG8">
         <v>11</v>
-      </c>
-      <c r="AG8">
-        <v>12.5</v>
       </c>
       <c r="AH8">
         <v>24</v>
       </c>
       <c r="AI8">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
         <v>23</v>
       </c>
       <c r="AK8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL8">
-        <v>48</v>
+        <v>320</v>
       </c>
       <c r="AM8">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AO8">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ8">
         <v>12</v>
       </c>
       <c r="AR8">
-        <v>8.6</v>
+        <v>20</v>
       </c>
       <c r="AS8">
-        <v>10.5</v>
+        <v>40</v>
       </c>
       <c r="AT8">
         <v>6.6</v>
@@ -2629,37 +2629,37 @@
         <v>17</v>
       </c>
       <c r="AW8">
-        <v>9.800000000000001</v>
+        <v>32</v>
       </c>
       <c r="AX8">
         <v>9.6</v>
       </c>
       <c r="AY8">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ8">
         <v>20</v>
       </c>
       <c r="BA8">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="BB8">
-        <v>7.4</v>
+        <v>15</v>
       </c>
       <c r="BC8">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BD8">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="BE8">
-        <v>10.5</v>
+        <v>46</v>
       </c>
       <c r="BF8">
         <v>16</v>
       </c>
       <c r="BG8">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="BH8">
         <v>2.96</v>
@@ -2716,7 +2716,7 @@
         <v>14.5</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA8">
         <v>12</v>
@@ -2745,19 +2745,19 @@
         <v>3.1</v>
       </c>
       <c r="G9">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="H9">
         <v>2.34</v>
       </c>
       <c r="I9">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="J9">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K9">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L9">
         <v>1.3</v>
@@ -2766,19 +2766,19 @@
         <v>1.04</v>
       </c>
       <c r="N9">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="O9">
         <v>1.19</v>
       </c>
       <c r="P9">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="Q9">
         <v>1.6</v>
       </c>
       <c r="R9">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="S9">
         <v>2.48</v>
@@ -2787,7 +2787,7 @@
         <v>1.55</v>
       </c>
       <c r="U9">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="V9">
         <v>1.67</v>
@@ -2799,16 +2799,16 @@
         <v>24</v>
       </c>
       <c r="Y9">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z9">
         <v>18</v>
       </c>
       <c r="AA9">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AB9">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AC9">
         <v>9.4</v>
@@ -2817,7 +2817,7 @@
         <v>11.5</v>
       </c>
       <c r="AE9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF9">
         <v>32</v>
@@ -2832,7 +2832,7 @@
         <v>28</v>
       </c>
       <c r="AJ9">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AK9">
         <v>30</v>
@@ -2856,16 +2856,16 @@
         <v>13</v>
       </c>
       <c r="AR9">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AS9">
         <v>26</v>
       </c>
       <c r="AT9">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AU9">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV9">
         <v>10</v>
@@ -2886,7 +2886,7 @@
         <v>24</v>
       </c>
       <c r="BB9">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BC9">
         <v>26</v>
@@ -2895,13 +2895,13 @@
         <v>30</v>
       </c>
       <c r="BE9">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BF9">
         <v>17</v>
       </c>
       <c r="BG9">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH9">
         <v>4.3</v>
@@ -2993,13 +2993,13 @@
         <v>27</v>
       </c>
       <c r="I10">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="J10">
         <v>11.5</v>
       </c>
       <c r="K10">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="L10">
         <v>1.17</v>
@@ -3023,19 +3023,19 @@
         <v>2.28</v>
       </c>
       <c r="S10">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="T10">
         <v>2.04</v>
       </c>
       <c r="U10">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="V10">
         <v>1.03</v>
       </c>
       <c r="W10">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="X10">
         <v>940</v>
@@ -3062,22 +3062,22 @@
         <v>500</v>
       </c>
       <c r="AF10">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG10">
         <v>15</v>
       </c>
       <c r="AH10">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="AI10">
         <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AK10">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL10">
         <v>38</v>
@@ -3086,13 +3086,13 @@
         <v>1000</v>
       </c>
       <c r="AN10">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AO10">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="AP10">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AQ10">
         <v>38</v>
@@ -3107,7 +3107,7 @@
         <v>14.5</v>
       </c>
       <c r="AU10">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AV10">
         <v>36</v>
@@ -3119,7 +3119,7 @@
         <v>9.6</v>
       </c>
       <c r="AY10">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ10">
         <v>36</v>
@@ -3140,13 +3140,13 @@
         <v>46</v>
       </c>
       <c r="BF10">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BG10">
         <v>95</v>
       </c>
       <c r="BH10">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BI10">
         <v>5</v>
@@ -3155,7 +3155,7 @@
         <v>14</v>
       </c>
       <c r="BK10">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL10">
         <v>1000</v>
@@ -3179,25 +3179,25 @@
         <v>19</v>
       </c>
       <c r="BS10">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BT10">
         <v>23</v>
       </c>
       <c r="BU10">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
+        <v>10.5</v>
+      </c>
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
         <v>10</v>
-      </c>
-      <c r="BX10">
-        <v>1000</v>
-      </c>
-      <c r="BY10">
-        <v>9.800000000000001</v>
       </c>
       <c r="BZ10">
         <v>5.6</v>
@@ -3226,10 +3226,10 @@
         <v>133</v>
       </c>
       <c r="F11">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G11">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H11">
         <v>3.95</v>
@@ -3238,10 +3238,10 @@
         <v>4.4</v>
       </c>
       <c r="J11">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K11">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L11">
         <v>1.48</v>
@@ -3250,7 +3250,7 @@
         <v>1.13</v>
       </c>
       <c r="N11">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O11">
         <v>1.54</v>
@@ -3259,7 +3259,7 @@
         <v>1.55</v>
       </c>
       <c r="Q11">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="R11">
         <v>1.18</v>
@@ -3277,13 +3277,13 @@
         <v>1.29</v>
       </c>
       <c r="W11">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="X11">
         <v>11</v>
       </c>
       <c r="Y11">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Z11">
         <v>32</v>
@@ -3370,7 +3370,7 @@
         <v>7.6</v>
       </c>
       <c r="BB11">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC11">
         <v>9.199999999999999</v>
@@ -3480,7 +3480,7 @@
         <v>990</v>
       </c>
       <c r="J12">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K12">
         <v>950</v>
@@ -3501,13 +3501,13 @@
         <v>1.08</v>
       </c>
       <c r="Q12">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R12">
         <v>1.07</v>
       </c>
       <c r="S12">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T12">
         <v>1.11</v>
@@ -3633,55 +3633,55 @@
         <v>1000</v>
       </c>
       <c r="BI12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12">
         <v>1000</v>
       </c>
       <c r="BK12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN12">
         <v>1000</v>
       </c>
       <c r="BO12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP12">
         <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT12">
         <v>1000</v>
       </c>
       <c r="BU12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV12">
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12">
         <v>0</v>
@@ -3740,7 +3740,7 @@
         <v>1.22</v>
       </c>
       <c r="P13">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q13">
         <v>1.64</v>
@@ -3752,7 +3752,7 @@
         <v>2.6</v>
       </c>
       <c r="T13">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="U13">
         <v>1.6</v>
@@ -3812,7 +3812,7 @@
         <v>300</v>
       </c>
       <c r="AN13">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AO13">
         <v>1000</v>
@@ -3821,13 +3821,13 @@
         <v>19</v>
       </c>
       <c r="AQ13">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AR13">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS13">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT13">
         <v>7.2</v>
@@ -3836,19 +3836,19 @@
         <v>13</v>
       </c>
       <c r="AV13">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AW13">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX13">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AY13">
         <v>10</v>
       </c>
       <c r="AZ13">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BA13">
         <v>6.4</v>
@@ -3860,7 +3860,7 @@
         <v>12.5</v>
       </c>
       <c r="BD13">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BE13">
         <v>6.4</v>
@@ -3869,7 +3869,7 @@
         <v>4</v>
       </c>
       <c r="BG13">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH13">
         <v>4.4</v>
@@ -3952,19 +3952,19 @@
         <v>136</v>
       </c>
       <c r="F14">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="G14">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="H14">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="I14">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="J14">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K14">
         <v>3.65</v>
@@ -3988,7 +3988,7 @@
         <v>2.24</v>
       </c>
       <c r="R14">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S14">
         <v>4.2</v>
@@ -3997,10 +3997,10 @@
         <v>2.06</v>
       </c>
       <c r="U14">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="V14">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="W14">
         <v>1.23</v>
@@ -4045,7 +4045,7 @@
         <v>150</v>
       </c>
       <c r="AK14">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AL14">
         <v>95</v>
@@ -4063,7 +4063,7 @@
         <v>9.4</v>
       </c>
       <c r="AQ14">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AR14">
         <v>9</v>
@@ -4081,13 +4081,13 @@
         <v>9</v>
       </c>
       <c r="AW14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AX14">
         <v>29</v>
       </c>
       <c r="AY14">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AZ14">
         <v>19.5</v>
@@ -4132,10 +4132,10 @@
         <v>17</v>
       </c>
       <c r="BN14">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO14">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BP14">
         <v>1000</v>
@@ -4156,10 +4156,10 @@
         <v>3.55</v>
       </c>
       <c r="BV14">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BW14">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BX14">
         <v>46</v>
@@ -4209,7 +4209,7 @@
         <v>3.3</v>
       </c>
       <c r="K15">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L15">
         <v>1.48</v>
@@ -4227,19 +4227,19 @@
         <v>1.78</v>
       </c>
       <c r="Q15">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="R15">
         <v>1.27</v>
       </c>
       <c r="S15">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T15">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U15">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="V15">
         <v>1.36</v>
@@ -4251,7 +4251,7 @@
         <v>13</v>
       </c>
       <c r="Y15">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z15">
         <v>27</v>
@@ -4308,10 +4308,10 @@
         <v>10.5</v>
       </c>
       <c r="AR15">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS15">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT15">
         <v>7.4</v>
@@ -4323,7 +4323,7 @@
         <v>14</v>
       </c>
       <c r="AW15">
-        <v>44</v>
+        <v>8.6</v>
       </c>
       <c r="AX15">
         <v>12</v>
@@ -4335,25 +4335,25 @@
         <v>17</v>
       </c>
       <c r="BA15">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB15">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC15">
         <v>23</v>
       </c>
       <c r="BD15">
-        <v>38</v>
+        <v>8.4</v>
       </c>
       <c r="BE15">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF15">
         <v>20</v>
       </c>
       <c r="BG15">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH15">
         <v>3.05</v>
@@ -4436,7 +4436,7 @@
         <v>138</v>
       </c>
       <c r="F16">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="G16">
         <v>1.45</v>
@@ -4454,7 +4454,7 @@
         <v>5</v>
       </c>
       <c r="L16">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M16">
         <v>1.07</v>
@@ -4469,7 +4469,7 @@
         <v>1.9</v>
       </c>
       <c r="Q16">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R16">
         <v>1.33</v>
@@ -4481,7 +4481,7 @@
         <v>2.26</v>
       </c>
       <c r="U16">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="V16">
         <v>1.09</v>
@@ -4499,7 +4499,7 @@
         <v>120</v>
       </c>
       <c r="AA16">
-        <v>560</v>
+        <v>590</v>
       </c>
       <c r="AB16">
         <v>7</v>
@@ -4541,13 +4541,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AO16">
-        <v>450</v>
+        <v>480</v>
       </c>
       <c r="AP16">
         <v>12</v>
       </c>
       <c r="AQ16">
-        <v>5.7</v>
+        <v>19.5</v>
       </c>
       <c r="AR16">
         <v>6.6</v>
@@ -4562,7 +4562,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV16">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="AW16">
         <v>6.8</v>
@@ -4571,19 +4571,19 @@
         <v>6.4</v>
       </c>
       <c r="AY16">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AZ16">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="BA16">
         <v>6.8</v>
       </c>
       <c r="BB16">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BC16">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD16">
         <v>6.2</v>
@@ -4601,13 +4601,13 @@
         <v>3.55</v>
       </c>
       <c r="BI16">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="BJ16">
         <v>13.5</v>
       </c>
       <c r="BK16">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="BL16">
         <v>1000</v>
@@ -4619,7 +4619,7 @@
         <v>3.75</v>
       </c>
       <c r="BO16">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="BP16">
         <v>9.199999999999999</v>
@@ -4678,16 +4678,16 @@
         <v>139</v>
       </c>
       <c r="F17">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="G17">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="H17">
         <v>4.3</v>
       </c>
       <c r="I17">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J17">
         <v>3.95</v>
@@ -4726,7 +4726,7 @@
         <v>2.24</v>
       </c>
       <c r="V17">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W17">
         <v>2.12</v>
@@ -4786,55 +4786,55 @@
         <v>55</v>
       </c>
       <c r="AP17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU17">
         <v>7.8</v>
       </c>
       <c r="AV17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF17">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG17">
         <v>1.01</v>
@@ -4923,7 +4923,7 @@
         <v>2.22</v>
       </c>
       <c r="G18">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H18">
         <v>3.7</v>
@@ -4977,7 +4977,7 @@
         <v>12.5</v>
       </c>
       <c r="Y18">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z18">
         <v>28</v>
@@ -4986,7 +4986,7 @@
         <v>85</v>
       </c>
       <c r="AB18">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC18">
         <v>8.6</v>
@@ -4998,7 +4998,7 @@
         <v>60</v>
       </c>
       <c r="AF18">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG18">
         <v>12.5</v>
@@ -5043,13 +5043,13 @@
         <v>7.2</v>
       </c>
       <c r="AU18">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV18">
         <v>13.5</v>
       </c>
       <c r="AW18">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX18">
         <v>12</v>
@@ -5061,19 +5061,19 @@
         <v>6.2</v>
       </c>
       <c r="BA18">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB18">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BC18">
-        <v>21</v>
+        <v>6.6</v>
       </c>
       <c r="BD18">
         <v>7.4</v>
       </c>
       <c r="BE18">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BF18">
         <v>19.5</v>
@@ -5195,7 +5195,7 @@
         <v>2.1</v>
       </c>
       <c r="Q19">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="R19">
         <v>1.43</v>
@@ -5204,7 +5204,7 @@
         <v>3.15</v>
       </c>
       <c r="T19">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U19">
         <v>2.26</v>
@@ -5246,7 +5246,7 @@
         <v>11</v>
       </c>
       <c r="AH19">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI19">
         <v>200</v>
@@ -5279,7 +5279,7 @@
         <v>18.5</v>
       </c>
       <c r="AS19">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AT19">
         <v>9.6</v>
@@ -5321,7 +5321,7 @@
         <v>12</v>
       </c>
       <c r="BG19">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BH19">
         <v>3.75</v>
@@ -5413,10 +5413,10 @@
         <v>3.95</v>
       </c>
       <c r="I20">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J20">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K20">
         <v>3.9</v>
@@ -5440,7 +5440,7 @@
         <v>1.82</v>
       </c>
       <c r="R20">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S20">
         <v>3.1</v>
@@ -5458,7 +5458,7 @@
         <v>1.96</v>
       </c>
       <c r="X20">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y20">
         <v>17.5</v>
@@ -5587,7 +5587,7 @@
         <v>5.1</v>
       </c>
       <c r="BO20">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="BP20">
         <v>14.5</v>
@@ -5646,10 +5646,10 @@
         <v>143</v>
       </c>
       <c r="F21">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G21">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="H21">
         <v>4.2</v>
@@ -5658,7 +5658,7 @@
         <v>4.5</v>
       </c>
       <c r="J21">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K21">
         <v>4.6</v>
@@ -5697,7 +5697,7 @@
         <v>1.28</v>
       </c>
       <c r="W21">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="X21">
         <v>32</v>
@@ -5715,7 +5715,7 @@
         <v>15</v>
       </c>
       <c r="AC21">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD21">
         <v>18.5</v>
@@ -5751,7 +5751,7 @@
         <v>7.2</v>
       </c>
       <c r="AO21">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AP21">
         <v>19.5</v>
@@ -5805,7 +5805,7 @@
         <v>6.6</v>
       </c>
       <c r="BG21">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BH21">
         <v>4.8</v>
@@ -5865,7 +5865,7 @@
         <v>13</v>
       </c>
       <c r="CA21">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="CB21" t="s">
         <v>146</v>
@@ -5888,22 +5888,22 @@
         <v>144</v>
       </c>
       <c r="F22">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G22">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H22">
         <v>1.85</v>
       </c>
       <c r="I22">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="J22">
         <v>4.4</v>
       </c>
       <c r="K22">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L22">
         <v>1.23</v>
@@ -5930,7 +5930,7 @@
         <v>2.06</v>
       </c>
       <c r="T22">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="U22">
         <v>3.05</v>
@@ -5939,7 +5939,7 @@
         <v>2.12</v>
       </c>
       <c r="W22">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X22">
         <v>38</v>
@@ -5987,7 +5987,7 @@
         <v>38</v>
       </c>
       <c r="AM22">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AN22">
         <v>24</v>
@@ -6133,7 +6133,7 @@
         <v>2.18</v>
       </c>
       <c r="G23">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H23">
         <v>3.15</v>
@@ -6154,7 +6154,7 @@
         <v>1.02</v>
       </c>
       <c r="N23">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O23">
         <v>1.12</v>
@@ -6166,13 +6166,13 @@
         <v>1.38</v>
       </c>
       <c r="R23">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="S23">
         <v>1.96</v>
       </c>
       <c r="T23">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="U23">
         <v>3.35</v>
@@ -6181,7 +6181,7 @@
         <v>1.45</v>
       </c>
       <c r="W23">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="X23">
         <v>42</v>
@@ -6193,7 +6193,7 @@
         <v>34</v>
       </c>
       <c r="AA23">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AB23">
         <v>22</v>
@@ -6217,7 +6217,7 @@
         <v>14</v>
       </c>
       <c r="AI23">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AJ23">
         <v>32</v>
@@ -6253,7 +6253,7 @@
         <v>19.5</v>
       </c>
       <c r="AU23">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AV23">
         <v>13.5</v>
@@ -6280,7 +6280,7 @@
         <v>16.5</v>
       </c>
       <c r="BD23">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BE23">
         <v>34</v>
@@ -6292,13 +6292,13 @@
         <v>12</v>
       </c>
       <c r="BH23">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BI23">
         <v>4.2</v>
       </c>
       <c r="BJ23">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BK23">
         <v>6</v>
@@ -6307,16 +6307,16 @@
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN23">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO23">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP23">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ23">
         <v>8.199999999999999</v>
@@ -6328,7 +6328,7 @@
         <v>6.4</v>
       </c>
       <c r="BT23">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BU23">
         <v>5.5</v>
@@ -6337,13 +6337,13 @@
         <v>21</v>
       </c>
       <c r="BW23">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX23">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BY23">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BZ23">
         <v>11.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
@@ -454,7 +454,7 @@
     <t>Chicago Fire</t>
   </si>
   <si>
-    <t>2026-07-21 17:42:25</t>
+    <t>2026-07-21 19:49:04</t>
   </si>
 </sst>
 </file>
@@ -1048,22 +1048,22 @@
         <v>124</v>
       </c>
       <c r="F2">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="G2">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="H2">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="I2">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="J2">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K2">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L2">
         <v>1.44</v>
@@ -1072,115 +1072,115 @@
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O2">
         <v>1.36</v>
       </c>
       <c r="P2">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="Q2">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R2">
         <v>1.33</v>
       </c>
       <c r="S2">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T2">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="U2">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="V2">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W2">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="X2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA2">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AB2">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AC2">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AD2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AE2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AI2">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AJ2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL2">
         <v>40</v>
       </c>
       <c r="AM2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN2">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO2">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AP2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ2">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AS2">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AT2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AU2">
         <v>7.4</v>
       </c>
       <c r="AV2">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW2">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AX2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY2">
         <v>9.4</v>
@@ -1189,85 +1189,85 @@
         <v>18</v>
       </c>
       <c r="BA2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BB2">
         <v>20</v>
       </c>
       <c r="BC2">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE2">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BF2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BG2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BH2">
         <v>3.3</v>
       </c>
       <c r="BI2">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="BJ2">
         <v>10</v>
       </c>
       <c r="BK2">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>17</v>
+        <v>110</v>
       </c>
       <c r="BN2">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO2">
         <v>4.1</v>
       </c>
       <c r="BP2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BT2">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BU2">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BX2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BY2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BZ2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CA2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CB2" t="s">
         <v>146</v>
@@ -1290,25 +1290,25 @@
         <v>125</v>
       </c>
       <c r="F3">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="G3">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="H3">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="I3">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J3">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K3">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L3">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="M3">
         <v>1.11</v>
@@ -1317,10 +1317,10 @@
         <v>3</v>
       </c>
       <c r="O3">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P3">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Q3">
         <v>2.46</v>
@@ -1332,16 +1332,16 @@
         <v>4.8</v>
       </c>
       <c r="T3">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="U3">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V3">
         <v>1.41</v>
       </c>
       <c r="W3">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="X3">
         <v>9.6</v>
@@ -1350,13 +1350,13 @@
         <v>10.5</v>
       </c>
       <c r="Z3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA3">
         <v>65</v>
       </c>
       <c r="AB3">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC3">
         <v>7</v>
@@ -1365,7 +1365,7 @@
         <v>15</v>
       </c>
       <c r="AE3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF3">
         <v>15.5</v>
@@ -1374,7 +1374,7 @@
         <v>12.5</v>
       </c>
       <c r="AH3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI3">
         <v>65</v>
@@ -1383,10 +1383,10 @@
         <v>40</v>
       </c>
       <c r="AK3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM3">
         <v>140</v>
@@ -1404,25 +1404,25 @@
         <v>9.6</v>
       </c>
       <c r="AR3">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AS3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AT3">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU3">
         <v>6.4</v>
       </c>
       <c r="AV3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW3">
         <v>40</v>
       </c>
       <c r="AX3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY3">
         <v>11</v>
@@ -1440,76 +1440,76 @@
         <v>30</v>
       </c>
       <c r="BD3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BE3">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="BF3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BG3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BH3">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="BI3">
-        <v>2.38</v>
+        <v>2.68</v>
       </c>
       <c r="BJ3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK3">
-        <v>5.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL3">
         <v>170</v>
       </c>
       <c r="BM3">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN3">
         <v>5.5</v>
       </c>
       <c r="BO3">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BP3">
         <v>23</v>
       </c>
       <c r="BQ3">
-        <v>8</v>
+        <v>15.5</v>
       </c>
       <c r="BR3">
         <v>42</v>
       </c>
       <c r="BS3">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BT3">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU3">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BV3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BW3">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX3">
         <v>48</v>
       </c>
       <c r="BY3">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BZ3">
         <v>42</v>
       </c>
       <c r="CA3">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="CB3" t="s">
         <v>146</v>
@@ -1535,7 +1535,7 @@
         <v>1.37</v>
       </c>
       <c r="G4">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="H4">
         <v>8.800000000000001</v>
@@ -1547,31 +1547,31 @@
         <v>6</v>
       </c>
       <c r="K4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="L4">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M4">
         <v>1.04</v>
       </c>
       <c r="N4">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O4">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P4">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="Q4">
         <v>1.63</v>
       </c>
       <c r="R4">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S4">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="T4">
         <v>1.97</v>
@@ -1586,7 +1586,7 @@
         <v>3.6</v>
       </c>
       <c r="X4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y4">
         <v>32</v>
@@ -1598,7 +1598,7 @@
         <v>340</v>
       </c>
       <c r="AB4">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC4">
         <v>13.5</v>
@@ -1610,22 +1610,22 @@
         <v>130</v>
       </c>
       <c r="AF4">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG4">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI4">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AJ4">
         <v>11.5</v>
       </c>
       <c r="AK4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL4">
         <v>32</v>
@@ -1634,13 +1634,13 @@
         <v>130</v>
       </c>
       <c r="AN4">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AO4">
         <v>140</v>
       </c>
       <c r="AP4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ4">
         <v>28</v>
@@ -1661,10 +1661,10 @@
         <v>29</v>
       </c>
       <c r="AW4">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="AX4">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY4">
         <v>9.4</v>
@@ -1673,7 +1673,7 @@
         <v>24</v>
       </c>
       <c r="BA4">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="BB4">
         <v>10.5</v>
@@ -1688,10 +1688,10 @@
         <v>80</v>
       </c>
       <c r="BF4">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BG4">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="BH4">
         <v>4.3</v>
@@ -1700,16 +1700,16 @@
         <v>4</v>
       </c>
       <c r="BJ4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK4">
         <v>9.800000000000001</v>
       </c>
       <c r="BL4">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="BM4">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BN4">
         <v>3.95</v>
@@ -1727,31 +1727,31 @@
         <v>22</v>
       </c>
       <c r="BS4">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BT4">
         <v>12.5</v>
       </c>
       <c r="BU4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BV4">
         <v>75</v>
       </c>
       <c r="BW4">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BX4">
         <v>65</v>
       </c>
       <c r="BY4">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BZ4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CA4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CB4" t="s">
         <v>146</v>
@@ -1774,22 +1774,22 @@
         <v>127</v>
       </c>
       <c r="F5">
+        <v>1.63</v>
+      </c>
+      <c r="G5">
         <v>1.65</v>
       </c>
-      <c r="G5">
-        <v>1.66</v>
-      </c>
       <c r="H5">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="I5">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J5">
         <v>4.4</v>
       </c>
       <c r="K5">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L5">
         <v>1.32</v>
@@ -1798,43 +1798,43 @@
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O5">
         <v>1.23</v>
       </c>
       <c r="P5">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="Q5">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R5">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="S5">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="T5">
         <v>1.74</v>
       </c>
       <c r="U5">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V5">
         <v>1.2</v>
       </c>
       <c r="W5">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="X5">
         <v>22</v>
       </c>
       <c r="Y5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z5">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AA5">
         <v>140</v>
@@ -1858,7 +1858,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI5">
         <v>60</v>
@@ -1870,25 +1870,25 @@
         <v>15.5</v>
       </c>
       <c r="AL5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM5">
         <v>85</v>
       </c>
       <c r="AN5">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AO5">
         <v>65</v>
       </c>
       <c r="AP5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR5">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AS5">
         <v>50</v>
@@ -1897,25 +1897,25 @@
         <v>10</v>
       </c>
       <c r="AU5">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV5">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AW5">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX5">
         <v>10</v>
       </c>
       <c r="AY5">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ5">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA5">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB5">
         <v>15</v>
@@ -1927,10 +1927,10 @@
         <v>26</v>
       </c>
       <c r="BE5">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BF5">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BG5">
         <v>55</v>
@@ -1945,19 +1945,19 @@
         <v>10</v>
       </c>
       <c r="BK5">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL5">
         <v>110</v>
       </c>
       <c r="BM5">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN5">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BO5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP5">
         <v>11</v>
@@ -1969,7 +1969,7 @@
         <v>23</v>
       </c>
       <c r="BS5">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BT5">
         <v>9.6</v>
@@ -1978,22 +1978,22 @@
         <v>7.8</v>
       </c>
       <c r="BV5">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BW5">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BX5">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BY5">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BZ5">
         <v>16</v>
       </c>
       <c r="CA5">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="CB5" t="s">
         <v>146</v>
@@ -2025,7 +2025,7 @@
         <v>2.66</v>
       </c>
       <c r="I6">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="J6">
         <v>3.15</v>
@@ -2034,7 +2034,7 @@
         <v>3.3</v>
       </c>
       <c r="L6">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M6">
         <v>1.11</v>
@@ -2049,7 +2049,7 @@
         <v>1.63</v>
       </c>
       <c r="Q6">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R6">
         <v>1.23</v>
@@ -2064,28 +2064,28 @@
         <v>1.87</v>
       </c>
       <c r="V6">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W6">
         <v>1.45</v>
       </c>
       <c r="X6">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="Y6">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="Z6">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA6">
         <v>50</v>
       </c>
       <c r="AB6">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC6">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD6">
         <v>13</v>
@@ -2097,43 +2097,43 @@
         <v>19.5</v>
       </c>
       <c r="AG6">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH6">
         <v>21</v>
       </c>
       <c r="AI6">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="AJ6">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK6">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL6">
-        <v>65</v>
+        <v>380</v>
       </c>
       <c r="AM6">
-        <v>170</v>
+        <v>580</v>
       </c>
       <c r="AN6">
         <v>55</v>
       </c>
       <c r="AO6">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AP6">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ6">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR6">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AS6">
-        <v>9.6</v>
+        <v>17.5</v>
       </c>
       <c r="AT6">
         <v>8.6</v>
@@ -2145,46 +2145,46 @@
         <v>11.5</v>
       </c>
       <c r="AW6">
-        <v>9.4</v>
+        <v>32</v>
       </c>
       <c r="AX6">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AY6">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ6">
         <v>18</v>
       </c>
       <c r="BA6">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BB6">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="BC6">
-        <v>9.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="BD6">
-        <v>10.5</v>
+        <v>28</v>
       </c>
       <c r="BE6">
+        <v>15</v>
+      </c>
+      <c r="BF6">
+        <v>12.5</v>
+      </c>
+      <c r="BG6">
         <v>11.5</v>
-      </c>
-      <c r="BF6">
-        <v>10</v>
-      </c>
-      <c r="BG6">
-        <v>9.4</v>
       </c>
       <c r="BH6">
         <v>2.84</v>
       </c>
       <c r="BI6">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BJ6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK6">
         <v>6.6</v>
@@ -2193,7 +2193,7 @@
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>2.4</v>
+        <v>16.5</v>
       </c>
       <c r="BN6">
         <v>6</v>
@@ -2205,13 +2205,13 @@
         <v>28</v>
       </c>
       <c r="BQ6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BR6">
         <v>48</v>
       </c>
       <c r="BS6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BT6">
         <v>5.5</v>
@@ -2223,19 +2223,19 @@
         <v>24</v>
       </c>
       <c r="BW6">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX6">
         <v>44</v>
       </c>
       <c r="BY6">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ6">
         <v>44</v>
       </c>
       <c r="CA6">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="CB6" t="s">
         <v>146</v>
@@ -2261,19 +2261,19 @@
         <v>4.6</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H7">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="I7">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="J7">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K7">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L7">
         <v>1.48</v>
@@ -2282,7 +2282,7 @@
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O7">
         <v>1.39</v>
@@ -2291,10 +2291,10 @@
         <v>1.8</v>
       </c>
       <c r="Q7">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="R7">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S7">
         <v>4</v>
@@ -2324,7 +2324,7 @@
         <v>23</v>
       </c>
       <c r="AB7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC7">
         <v>8</v>
@@ -2333,34 +2333,34 @@
         <v>10.5</v>
       </c>
       <c r="AE7">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF7">
         <v>40</v>
       </c>
       <c r="AG7">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH7">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI7">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="AJ7">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AK7">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AL7">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AM7">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AO7">
         <v>16</v>
@@ -2372,13 +2372,13 @@
         <v>7.2</v>
       </c>
       <c r="AR7">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS7">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AT7">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AU7">
         <v>7.2</v>
@@ -2387,7 +2387,7 @@
         <v>9.6</v>
       </c>
       <c r="AW7">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX7">
         <v>21</v>
@@ -2408,7 +2408,7 @@
         <v>32</v>
       </c>
       <c r="BD7">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BE7">
         <v>42</v>
@@ -2417,43 +2417,43 @@
         <v>36</v>
       </c>
       <c r="BG7">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BH7">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI7">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BJ7">
         <v>10.5</v>
       </c>
       <c r="BK7">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BN7">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BO7">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BT7">
         <v>4.5</v>
@@ -2462,22 +2462,22 @@
         <v>3.6</v>
       </c>
       <c r="BV7">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BW7">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BX7">
         <v>32</v>
       </c>
       <c r="BY7">
+        <v>11</v>
+      </c>
+      <c r="BZ7">
+        <v>30</v>
+      </c>
+      <c r="CA7">
         <v>10.5</v>
-      </c>
-      <c r="BZ7">
-        <v>29</v>
-      </c>
-      <c r="CA7">
-        <v>10</v>
       </c>
       <c r="CB7" t="s">
         <v>146</v>
@@ -2500,22 +2500,22 @@
         <v>130</v>
       </c>
       <c r="F8">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="G8">
         <v>1.97</v>
       </c>
       <c r="H8">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I8">
         <v>5.1</v>
       </c>
       <c r="J8">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K8">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L8">
         <v>1.53</v>
@@ -2524,19 +2524,19 @@
         <v>1.1</v>
       </c>
       <c r="N8">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O8">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P8">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q8">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R8">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S8">
         <v>4.5</v>
@@ -2545,7 +2545,7 @@
         <v>2.1</v>
       </c>
       <c r="U8">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="V8">
         <v>1.24</v>
@@ -2566,16 +2566,16 @@
         <v>1000</v>
       </c>
       <c r="AB8">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AC8">
         <v>8</v>
       </c>
       <c r="AD8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF8">
         <v>10.5</v>
@@ -2584,37 +2584,37 @@
         <v>11</v>
       </c>
       <c r="AH8">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AJ8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK8">
         <v>25</v>
       </c>
       <c r="AL8">
-        <v>320</v>
+        <v>100</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>570</v>
       </c>
       <c r="AN8">
         <v>18.5</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AP8">
         <v>9.800000000000001</v>
       </c>
       <c r="AQ8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR8">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AS8">
         <v>40</v>
@@ -2629,7 +2629,7 @@
         <v>17</v>
       </c>
       <c r="AW8">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AX8">
         <v>9.6</v>
@@ -2638,88 +2638,88 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA8">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="BB8">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BC8">
         <v>20</v>
       </c>
       <c r="BD8">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BE8">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="BF8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BG8">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="BH8">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="BI8">
-        <v>2.72</v>
+        <v>2.56</v>
       </c>
       <c r="BJ8">
         <v>11</v>
       </c>
       <c r="BK8">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BN8">
         <v>4.4</v>
       </c>
       <c r="BO8">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="BP8">
         <v>14.5</v>
       </c>
       <c r="BQ8">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BT8">
         <v>8.199999999999999</v>
       </c>
       <c r="BU8">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BZ8">
         <v>34</v>
       </c>
       <c r="CA8">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CB8" t="s">
         <v>146</v>
@@ -2742,40 +2742,40 @@
         <v>131</v>
       </c>
       <c r="F9">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G9">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="H9">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="I9">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="J9">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K9">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L9">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="M9">
         <v>1.04</v>
       </c>
       <c r="N9">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="O9">
         <v>1.19</v>
       </c>
       <c r="P9">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="Q9">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R9">
         <v>1.63</v>
@@ -2790,10 +2790,10 @@
         <v>2.74</v>
       </c>
       <c r="V9">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="W9">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="X9">
         <v>24</v>
@@ -2802,13 +2802,13 @@
         <v>16</v>
       </c>
       <c r="Z9">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA9">
         <v>30</v>
       </c>
       <c r="AB9">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AC9">
         <v>9.4</v>
@@ -2820,43 +2820,43 @@
         <v>21</v>
       </c>
       <c r="AF9">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AG9">
         <v>14.5</v>
       </c>
       <c r="AH9">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI9">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ9">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AK9">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL9">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM9">
         <v>55</v>
       </c>
       <c r="AN9">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AO9">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AP9">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AQ9">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR9">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AS9">
         <v>26</v>
@@ -2865,19 +2865,19 @@
         <v>17</v>
       </c>
       <c r="AU9">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW9">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AX9">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY9">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ9">
         <v>13</v>
@@ -2886,82 +2886,82 @@
         <v>24</v>
       </c>
       <c r="BB9">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BC9">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD9">
         <v>30</v>
       </c>
       <c r="BE9">
-        <v>48</v>
+        <v>12.5</v>
       </c>
       <c r="BF9">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BG9">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BH9">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BI9">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="BJ9">
         <v>8.6</v>
       </c>
       <c r="BK9">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BL9">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BM9">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN9">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BO9">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BP9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BQ9">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BR9">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BS9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BT9">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BU9">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="BV9">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BW9">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX9">
         <v>23</v>
       </c>
       <c r="BY9">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ9">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="CA9">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="CB9" t="s">
         <v>146</v>
@@ -2987,58 +2987,58 @@
         <v>1.12</v>
       </c>
       <c r="G10">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="H10">
         <v>27</v>
       </c>
       <c r="I10">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="J10">
         <v>11.5</v>
       </c>
       <c r="K10">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="L10">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="M10">
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O10">
         <v>1.09</v>
       </c>
       <c r="P10">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q10">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="R10">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S10">
         <v>1.68</v>
       </c>
       <c r="T10">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U10">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="V10">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W10">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="X10">
-        <v>940</v>
+        <v>490</v>
       </c>
       <c r="Y10">
         <v>940</v>
@@ -3050,7 +3050,7 @@
         <v>1000</v>
       </c>
       <c r="AB10">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AC10">
         <v>32</v>
@@ -3059,16 +3059,16 @@
         <v>940</v>
       </c>
       <c r="AE10">
-        <v>500</v>
+        <v>470</v>
       </c>
       <c r="AF10">
         <v>11</v>
       </c>
       <c r="AG10">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH10">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AI10">
         <v>1000</v>
@@ -3077,19 +3077,19 @@
         <v>9.4</v>
       </c>
       <c r="AK10">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AL10">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AM10">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AN10">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="AO10">
-        <v>490</v>
+        <v>470</v>
       </c>
       <c r="AP10">
         <v>34</v>
@@ -3098,112 +3098,112 @@
         <v>38</v>
       </c>
       <c r="AR10">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="AS10">
-        <v>60</v>
+        <v>15.5</v>
       </c>
       <c r="AT10">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU10">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="AV10">
         <v>36</v>
       </c>
       <c r="AW10">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="AX10">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY10">
         <v>13</v>
       </c>
       <c r="AZ10">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BA10">
         <v>48</v>
       </c>
       <c r="BB10">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC10">
         <v>12</v>
       </c>
       <c r="BD10">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="BE10">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="BF10">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="BG10">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="BH10">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BI10">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BJ10">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BK10">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN10">
         <v>4.4</v>
       </c>
       <c r="BO10">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="BP10">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BQ10">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BR10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BS10">
         <v>7</v>
       </c>
       <c r="BT10">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BU10">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ10">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="CA10">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="CB10" t="s">
         <v>146</v>
@@ -3226,7 +3226,7 @@
         <v>133</v>
       </c>
       <c r="F11">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G11">
         <v>2.34</v>
@@ -3241,34 +3241,34 @@
         <v>3</v>
       </c>
       <c r="K11">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L11">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="M11">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N11">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="O11">
         <v>1.54</v>
       </c>
       <c r="P11">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q11">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R11">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S11">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="T11">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="U11">
         <v>1.74</v>
@@ -3277,31 +3277,31 @@
         <v>1.29</v>
       </c>
       <c r="W11">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="X11">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Y11">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z11">
         <v>32</v>
       </c>
       <c r="AA11">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AB11">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AC11">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD11">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AE11">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AF11">
         <v>13.5</v>
@@ -3310,52 +3310,52 @@
         <v>12.5</v>
       </c>
       <c r="AH11">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI11">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AJ11">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="AK11">
         <v>38</v>
       </c>
       <c r="AL11">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AM11">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AN11">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AO11">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AP11">
         <v>7.6</v>
       </c>
       <c r="AQ11">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR11">
-        <v>9.199999999999999</v>
+        <v>21</v>
       </c>
       <c r="AS11">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT11">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="AU11">
         <v>6.2</v>
       </c>
       <c r="AV11">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AW11">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX11">
         <v>10.5</v>
@@ -3367,85 +3367,85 @@
         <v>20</v>
       </c>
       <c r="BA11">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BB11">
-        <v>9.199999999999999</v>
+        <v>24</v>
       </c>
       <c r="BC11">
-        <v>9.199999999999999</v>
+        <v>24</v>
       </c>
       <c r="BD11">
-        <v>7.2</v>
+        <v>28</v>
       </c>
       <c r="BE11">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF11">
+        <v>24</v>
+      </c>
+      <c r="BG11">
+        <v>8</v>
+      </c>
+      <c r="BH11">
+        <v>1000</v>
+      </c>
+      <c r="BI11">
+        <v>1.62</v>
+      </c>
+      <c r="BJ11">
+        <v>17</v>
+      </c>
+      <c r="BK11">
+        <v>1.48</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>1.62</v>
+      </c>
+      <c r="BN11">
         <v>6.6</v>
       </c>
-      <c r="BG11">
-        <v>7.6</v>
-      </c>
-      <c r="BH11">
-        <v>2.78</v>
-      </c>
-      <c r="BI11">
-        <v>2.22</v>
-      </c>
-      <c r="BJ11">
-        <v>12</v>
-      </c>
-      <c r="BK11">
-        <v>8.6</v>
-      </c>
-      <c r="BL11">
-        <v>1000</v>
-      </c>
-      <c r="BM11">
-        <v>10.5</v>
-      </c>
-      <c r="BN11">
-        <v>5</v>
-      </c>
       <c r="BO11">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="BP11">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>7.2</v>
+        <v>1.62</v>
       </c>
       <c r="BR11">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
+        <v>1.58</v>
+      </c>
+      <c r="BT11">
         <v>8.800000000000001</v>
       </c>
-      <c r="BT11">
-        <v>7.4</v>
-      </c>
       <c r="BU11">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>8.800000000000001</v>
+        <v>1.58</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>9.4</v>
+        <v>1.59</v>
       </c>
       <c r="BZ11">
         <v>1000</v>
       </c>
       <c r="CA11">
-        <v>9</v>
+        <v>1.58</v>
       </c>
       <c r="CB11" t="s">
         <v>146</v>
@@ -3468,22 +3468,22 @@
         <v>134</v>
       </c>
       <c r="F12">
-        <v>1.04</v>
+        <v>1.46</v>
       </c>
       <c r="G12">
-        <v>990</v>
+        <v>46</v>
       </c>
       <c r="H12">
-        <v>1.04</v>
+        <v>1.72</v>
       </c>
       <c r="I12">
-        <v>990</v>
+        <v>200</v>
       </c>
       <c r="J12">
-        <v>1.03</v>
+        <v>2.7</v>
       </c>
       <c r="K12">
-        <v>950</v>
+        <v>5.2</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3495,16 +3495,16 @@
         <v>1.1</v>
       </c>
       <c r="O12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P12">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q12">
         <v>1.46</v>
       </c>
       <c r="R12">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="S12">
         <v>1.45</v>
@@ -3516,118 +3516,118 @@
         <v>1.11</v>
       </c>
       <c r="V12">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="W12">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="X12">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y12">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z12">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA12">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB12">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC12">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD12">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE12">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF12">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG12">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH12">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI12">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ12">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK12">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL12">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM12">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN12">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO12">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP12">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AQ12">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AR12">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AS12">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AT12">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AU12">
         <v>1.03</v>
       </c>
       <c r="AV12">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AW12">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AX12">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AY12">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AZ12">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BA12">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BB12">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BC12">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BD12">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BE12">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BF12">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG12">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3713,22 +3713,22 @@
         <v>1.22</v>
       </c>
       <c r="G13">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="H13">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="I13">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J13">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="K13">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="L13">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M13">
         <v>1.05</v>
@@ -3740,16 +3740,16 @@
         <v>1.22</v>
       </c>
       <c r="P13">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q13">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="R13">
         <v>1.5</v>
       </c>
       <c r="S13">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="T13">
         <v>2.32</v>
@@ -3761,43 +3761,43 @@
         <v>1.05</v>
       </c>
       <c r="W13">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="X13">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Y13">
-        <v>55</v>
+        <v>380</v>
       </c>
       <c r="Z13">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="AA13">
         <v>1000</v>
       </c>
       <c r="AB13">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC13">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AD13">
-        <v>65</v>
+        <v>510</v>
       </c>
       <c r="AE13">
-        <v>410</v>
+        <v>450</v>
       </c>
       <c r="AF13">
         <v>7.4</v>
       </c>
       <c r="AG13">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AH13">
-        <v>48</v>
+        <v>130</v>
       </c>
       <c r="AI13">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="AJ13">
         <v>9.199999999999999</v>
@@ -3806,52 +3806,52 @@
         <v>18.5</v>
       </c>
       <c r="AL13">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM13">
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="AN13">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="AO13">
         <v>1000</v>
       </c>
       <c r="AP13">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ13">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AR13">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS13">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT13">
         <v>7.2</v>
       </c>
       <c r="AU13">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AV13">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AW13">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AX13">
-        <v>3.5</v>
+        <v>6.2</v>
       </c>
       <c r="AY13">
         <v>10</v>
       </c>
       <c r="AZ13">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BA13">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB13">
         <v>7.8</v>
@@ -3860,16 +3860,16 @@
         <v>12.5</v>
       </c>
       <c r="BD13">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE13">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF13">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BG13">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH13">
         <v>4.4</v>
@@ -3881,16 +3881,16 @@
         <v>15</v>
       </c>
       <c r="BK13">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN13">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BO13">
         <v>3.15</v>
@@ -3905,31 +3905,31 @@
         <v>27</v>
       </c>
       <c r="BS13">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT13">
         <v>18.5</v>
       </c>
       <c r="BU13">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
+        <v>10.5</v>
+      </c>
+      <c r="BX13">
+        <v>1000</v>
+      </c>
+      <c r="BY13">
         <v>10</v>
-      </c>
-      <c r="BX13">
-        <v>1000</v>
-      </c>
-      <c r="BY13">
-        <v>9.800000000000001</v>
       </c>
       <c r="BZ13">
         <v>11</v>
       </c>
       <c r="CA13">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="CB13" t="s">
         <v>146</v>
@@ -3952,40 +3952,40 @@
         <v>136</v>
       </c>
       <c r="F14">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="G14">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="H14">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="I14">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="J14">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K14">
         <v>3.65</v>
       </c>
       <c r="L14">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="M14">
         <v>1.09</v>
       </c>
       <c r="N14">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O14">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P14">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="Q14">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R14">
         <v>1.28</v>
@@ -3997,13 +3997,13 @@
         <v>2.06</v>
       </c>
       <c r="U14">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="V14">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="W14">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X14">
         <v>11</v>
@@ -4012,13 +4012,13 @@
         <v>7.6</v>
       </c>
       <c r="Z14">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA14">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AB14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC14">
         <v>8</v>
@@ -4030,7 +4030,7 @@
         <v>22</v>
       </c>
       <c r="AF14">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AG14">
         <v>21</v>
@@ -4045,31 +4045,31 @@
         <v>150</v>
       </c>
       <c r="AK14">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AL14">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AM14">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AN14">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AO14">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AP14">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AQ14">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AR14">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AS14">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AT14">
         <v>14</v>
@@ -4078,19 +4078,19 @@
         <v>7.4</v>
       </c>
       <c r="AV14">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW14">
         <v>15</v>
       </c>
       <c r="AX14">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AY14">
         <v>19</v>
       </c>
       <c r="AZ14">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BA14">
         <v>40</v>
@@ -4105,46 +4105,46 @@
         <v>38</v>
       </c>
       <c r="BE14">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="BF14">
         <v>38</v>
       </c>
       <c r="BG14">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BH14">
         <v>3.1</v>
       </c>
       <c r="BI14">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BJ14">
         <v>11</v>
       </c>
       <c r="BK14">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BN14">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BO14">
         <v>5.7</v>
       </c>
       <c r="BP14">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BQ14">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BR14">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="BS14">
         <v>14</v>
@@ -4153,16 +4153,16 @@
         <v>4.3</v>
       </c>
       <c r="BU14">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BV14">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BW14">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BX14">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="BY14">
         <v>11.5</v>
@@ -4171,7 +4171,7 @@
         <v>30</v>
       </c>
       <c r="CA14">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CB14" t="s">
         <v>146</v>
@@ -4197,7 +4197,7 @@
         <v>2.22</v>
       </c>
       <c r="G15">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="H15">
         <v>3.65</v>
@@ -4206,10 +4206,10 @@
         <v>3.9</v>
       </c>
       <c r="J15">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K15">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L15">
         <v>1.48</v>
@@ -4236,40 +4236,40 @@
         <v>4.2</v>
       </c>
       <c r="T15">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U15">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V15">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W15">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="X15">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Y15">
         <v>12</v>
       </c>
       <c r="Z15">
-        <v>27</v>
+        <v>110</v>
       </c>
       <c r="AA15">
-        <v>80</v>
+        <v>900</v>
       </c>
       <c r="AB15">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AC15">
         <v>7.6</v>
       </c>
       <c r="AD15">
-        <v>950</v>
+        <v>80</v>
       </c>
       <c r="AE15">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AF15">
         <v>14</v>
@@ -4278,52 +4278,52 @@
         <v>11.5</v>
       </c>
       <c r="AH15">
-        <v>950</v>
+        <v>34</v>
       </c>
       <c r="AI15">
+        <v>500</v>
+      </c>
+      <c r="AJ15">
+        <v>32</v>
+      </c>
+      <c r="AK15">
         <v>65</v>
       </c>
-      <c r="AJ15">
-        <v>30</v>
-      </c>
-      <c r="AK15">
-        <v>28</v>
-      </c>
       <c r="AL15">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AM15">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN15">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AO15">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AP15">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ15">
         <v>10.5</v>
       </c>
       <c r="AR15">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS15">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AT15">
         <v>7.4</v>
       </c>
       <c r="AU15">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV15">
         <v>14</v>
       </c>
       <c r="AW15">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="AX15">
         <v>12</v>
@@ -4332,28 +4332,28 @@
         <v>10</v>
       </c>
       <c r="AZ15">
-        <v>17</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA15">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BB15">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="BC15">
-        <v>23</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD15">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BE15">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="BF15">
         <v>20</v>
       </c>
       <c r="BG15">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BH15">
         <v>3.05</v>
@@ -4439,13 +4439,13 @@
         <v>1.4</v>
       </c>
       <c r="G16">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="H16">
         <v>10.5</v>
       </c>
       <c r="I16">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="J16">
         <v>4.6</v>
@@ -4460,7 +4460,7 @@
         <v>1.07</v>
       </c>
       <c r="N16">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="O16">
         <v>1.34</v>
@@ -4469,16 +4469,16 @@
         <v>1.9</v>
       </c>
       <c r="Q16">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="R16">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S16">
         <v>3.6</v>
       </c>
       <c r="T16">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U16">
         <v>1.64</v>
@@ -4490,13 +4490,13 @@
         <v>3.2</v>
       </c>
       <c r="X16">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="Y16">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="Z16">
-        <v>120</v>
+        <v>540</v>
       </c>
       <c r="AA16">
         <v>590</v>
@@ -4508,37 +4508,37 @@
         <v>11.5</v>
       </c>
       <c r="AD16">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="AE16">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AF16">
         <v>7.8</v>
       </c>
       <c r="AG16">
+        <v>11</v>
+      </c>
+      <c r="AH16">
+        <v>85</v>
+      </c>
+      <c r="AI16">
+        <v>230</v>
+      </c>
+      <c r="AJ16">
         <v>12.5</v>
       </c>
-      <c r="AH16">
-        <v>40</v>
-      </c>
-      <c r="AI16">
-        <v>220</v>
-      </c>
-      <c r="AJ16">
-        <v>14</v>
-      </c>
       <c r="AK16">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AL16">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AM16">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="AN16">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AO16">
         <v>480</v>
@@ -4547,13 +4547,13 @@
         <v>12</v>
       </c>
       <c r="AQ16">
-        <v>19.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR16">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS16">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="AT16">
         <v>5.9</v>
@@ -4562,43 +4562,43 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV16">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="AW16">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX16">
         <v>6.4</v>
       </c>
       <c r="AY16">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ16">
-        <v>23</v>
+        <v>14.5</v>
       </c>
       <c r="BA16">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB16">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BC16">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD16">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BE16">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF16">
         <v>7</v>
       </c>
       <c r="BG16">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="BH16">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BI16">
         <v>2.72</v>
@@ -4607,13 +4607,13 @@
         <v>13.5</v>
       </c>
       <c r="BK16">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN16">
         <v>3.75</v>
@@ -4625,37 +4625,37 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BQ16">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BR16">
         <v>32</v>
       </c>
       <c r="BS16">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT16">
         <v>13.5</v>
       </c>
       <c r="BU16">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ16">
         <v>19</v>
       </c>
       <c r="CA16">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB16" t="s">
         <v>146</v>
@@ -4684,19 +4684,19 @@
         <v>1.89</v>
       </c>
       <c r="H17">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I17">
         <v>4.8</v>
       </c>
       <c r="J17">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K17">
         <v>4.2</v>
       </c>
       <c r="L17">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="M17">
         <v>1.05</v>
@@ -4714,16 +4714,16 @@
         <v>1.7</v>
       </c>
       <c r="R17">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S17">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T17">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U17">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="V17">
         <v>1.27</v>
@@ -4732,22 +4732,22 @@
         <v>2.12</v>
       </c>
       <c r="X17">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y17">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z17">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA17">
         <v>110</v>
       </c>
       <c r="AB17">
+        <v>12.5</v>
+      </c>
+      <c r="AC17">
         <v>11.5</v>
-      </c>
-      <c r="AC17">
-        <v>11</v>
       </c>
       <c r="AD17">
         <v>21</v>
@@ -4756,7 +4756,7 @@
         <v>60</v>
       </c>
       <c r="AF17">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG17">
         <v>11.5</v>
@@ -4765,7 +4765,7 @@
         <v>21</v>
       </c>
       <c r="AI17">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ17">
         <v>23</v>
@@ -4774,7 +4774,7 @@
         <v>21</v>
       </c>
       <c r="AL17">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM17">
         <v>95</v>
@@ -4783,58 +4783,58 @@
         <v>11.5</v>
       </c>
       <c r="AO17">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP17">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AQ17">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AR17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS17">
         <v>1.01</v>
       </c>
       <c r="AT17">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU17">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV17">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AW17">
         <v>1.01</v>
       </c>
       <c r="AX17">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY17">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AZ17">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA17">
         <v>1.01</v>
       </c>
       <c r="BB17">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BC17">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BD17">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BE17">
         <v>1.01</v>
       </c>
       <c r="BF17">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BG17">
         <v>1.01</v>
@@ -4923,7 +4923,7 @@
         <v>2.22</v>
       </c>
       <c r="G18">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H18">
         <v>3.7</v>
@@ -4938,7 +4938,7 @@
         <v>3.45</v>
       </c>
       <c r="L18">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M18">
         <v>1.09</v>
@@ -4947,7 +4947,7 @@
         <v>3.1</v>
       </c>
       <c r="O18">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P18">
         <v>1.72</v>
@@ -4959,40 +4959,40 @@
         <v>1.27</v>
       </c>
       <c r="S18">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T18">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U18">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V18">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W18">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X18">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y18">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z18">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA18">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AB18">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC18">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD18">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE18">
         <v>60</v>
@@ -5001,7 +5001,7 @@
         <v>14</v>
       </c>
       <c r="AG18">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH18">
         <v>23</v>
@@ -5013,43 +5013,43 @@
         <v>36</v>
       </c>
       <c r="AK18">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AL18">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM18">
         <v>150</v>
       </c>
       <c r="AN18">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AO18">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AP18">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AQ18">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR18">
-        <v>21</v>
+        <v>6.8</v>
       </c>
       <c r="AS18">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT18">
+        <v>7.4</v>
+      </c>
+      <c r="AU18">
+        <v>6.8</v>
+      </c>
+      <c r="AV18">
+        <v>14</v>
+      </c>
+      <c r="AW18">
         <v>7.8</v>
-      </c>
-      <c r="AT18">
-        <v>7.2</v>
-      </c>
-      <c r="AU18">
-        <v>7</v>
-      </c>
-      <c r="AV18">
-        <v>13.5</v>
-      </c>
-      <c r="AW18">
-        <v>7.4</v>
       </c>
       <c r="AX18">
         <v>12</v>
@@ -5058,88 +5058,88 @@
         <v>10</v>
       </c>
       <c r="AZ18">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BA18">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB18">
+        <v>7.2</v>
+      </c>
+      <c r="BC18">
+        <v>6.8</v>
+      </c>
+      <c r="BD18">
         <v>7.6</v>
       </c>
-      <c r="BB18">
-        <v>6.8</v>
-      </c>
-      <c r="BC18">
-        <v>6.6</v>
-      </c>
-      <c r="BD18">
-        <v>7.4</v>
-      </c>
       <c r="BE18">
+        <v>8.6</v>
+      </c>
+      <c r="BF18">
+        <v>20</v>
+      </c>
+      <c r="BG18">
         <v>8</v>
       </c>
-      <c r="BF18">
-        <v>19.5</v>
-      </c>
-      <c r="BG18">
-        <v>7.6</v>
-      </c>
       <c r="BH18">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="BI18">
-        <v>2.58</v>
+        <v>1.96</v>
       </c>
       <c r="BJ18">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="BK18">
-        <v>6.4</v>
+        <v>1.73</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>15.5</v>
+        <v>1.96</v>
       </c>
       <c r="BN18">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BO18">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="BP18">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ18">
-        <v>8.800000000000001</v>
+        <v>1.82</v>
       </c>
       <c r="BR18">
         <v>1000</v>
       </c>
       <c r="BS18">
-        <v>11.5</v>
+        <v>1.88</v>
       </c>
       <c r="BT18">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BU18">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="BV18">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW18">
-        <v>11</v>
+        <v>1.88</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>12.5</v>
+        <v>1.9</v>
       </c>
       <c r="BZ18">
         <v>1000</v>
       </c>
       <c r="CA18">
-        <v>11.5</v>
+        <v>1.87</v>
       </c>
       <c r="CB18" t="s">
         <v>146</v>
@@ -5162,19 +5162,19 @@
         <v>141</v>
       </c>
       <c r="F19">
+        <v>2.02</v>
+      </c>
+      <c r="G19">
         <v>2.04</v>
       </c>
-      <c r="G19">
-        <v>2.1</v>
-      </c>
       <c r="H19">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I19">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J19">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K19">
         <v>3.9</v>
@@ -5189,7 +5189,7 @@
         <v>4.3</v>
       </c>
       <c r="O19">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P19">
         <v>2.1</v>
@@ -5204,22 +5204,22 @@
         <v>3.15</v>
       </c>
       <c r="T19">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U19">
         <v>2.26</v>
       </c>
       <c r="V19">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W19">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="X19">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y19">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z19">
         <v>30</v>
@@ -5228,34 +5228,34 @@
         <v>1000</v>
       </c>
       <c r="AB19">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC19">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD19">
         <v>16.5</v>
       </c>
       <c r="AE19">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AF19">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG19">
         <v>11</v>
       </c>
       <c r="AH19">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI19">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AJ19">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK19">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL19">
         <v>38</v>
@@ -5267,34 +5267,34 @@
         <v>13.5</v>
       </c>
       <c r="AO19">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="AP19">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ19">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR19">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AS19">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AT19">
         <v>9.6</v>
       </c>
       <c r="AU19">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV19">
         <v>14</v>
       </c>
       <c r="AW19">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AX19">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY19">
         <v>9.800000000000001</v>
@@ -5303,22 +5303,22 @@
         <v>15</v>
       </c>
       <c r="BA19">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="BB19">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BC19">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD19">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BE19">
         <v>36</v>
       </c>
       <c r="BF19">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG19">
         <v>24</v>
@@ -5327,61 +5327,61 @@
         <v>3.75</v>
       </c>
       <c r="BI19">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="BJ19">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK19">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="BN19">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BO19">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="BP19">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BQ19">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BR19">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BS19">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="BT19">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BU19">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BV19">
         <v>32</v>
       </c>
       <c r="BW19">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="BX19">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BY19">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="BZ19">
         <v>23</v>
       </c>
       <c r="CA19">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="CB19" t="s">
         <v>146</v>
@@ -5407,19 +5407,19 @@
         <v>2</v>
       </c>
       <c r="G20">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H20">
         <v>3.95</v>
       </c>
       <c r="I20">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J20">
         <v>3.85</v>
       </c>
       <c r="K20">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L20">
         <v>1.36</v>
@@ -5440,13 +5440,13 @@
         <v>1.82</v>
       </c>
       <c r="R20">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S20">
         <v>3.1</v>
       </c>
       <c r="T20">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U20">
         <v>2.28</v>
@@ -5455,13 +5455,13 @@
         <v>1.32</v>
       </c>
       <c r="W20">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X20">
         <v>17.5</v>
       </c>
       <c r="Y20">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z20">
         <v>32</v>
@@ -5479,22 +5479,22 @@
         <v>16.5</v>
       </c>
       <c r="AE20">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF20">
         <v>13</v>
       </c>
       <c r="AG20">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH20">
         <v>17.5</v>
       </c>
       <c r="AI20">
-        <v>55</v>
+        <v>230</v>
       </c>
       <c r="AJ20">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK20">
         <v>20</v>
@@ -5563,67 +5563,67 @@
         <v>11</v>
       </c>
       <c r="BG20">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="BH20">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BI20">
-        <v>2.96</v>
+        <v>1.59</v>
       </c>
       <c r="BJ20">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="BK20">
-        <v>5</v>
+        <v>1.42</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>9.6</v>
+        <v>1.59</v>
       </c>
       <c r="BN20">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BO20">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="BP20">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="BQ20">
-        <v>6</v>
+        <v>1.47</v>
       </c>
       <c r="BR20">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="BS20">
-        <v>7.4</v>
+        <v>1.53</v>
       </c>
       <c r="BT20">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU20">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="BV20">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="BW20">
-        <v>7.8</v>
+        <v>1.54</v>
       </c>
       <c r="BX20">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY20">
-        <v>8.199999999999999</v>
+        <v>1.55</v>
       </c>
       <c r="BZ20">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="CA20">
-        <v>7</v>
+        <v>1.51</v>
       </c>
       <c r="CB20" t="s">
         <v>146</v>
@@ -5646,16 +5646,16 @@
         <v>143</v>
       </c>
       <c r="F21">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="G21">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="H21">
         <v>4.2</v>
       </c>
       <c r="I21">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J21">
         <v>4.3</v>
@@ -5679,10 +5679,10 @@
         <v>2.78</v>
       </c>
       <c r="Q21">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R21">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="S21">
         <v>2.32</v>
@@ -5694,25 +5694,25 @@
         <v>2.66</v>
       </c>
       <c r="V21">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W21">
         <v>2.16</v>
       </c>
       <c r="X21">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Y21">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z21">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="AA21">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB21">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC21">
         <v>10.5</v>
@@ -5727,55 +5727,55 @@
         <v>15</v>
       </c>
       <c r="AG21">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH21">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI21">
         <v>100</v>
       </c>
       <c r="AJ21">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK21">
         <v>16.5</v>
       </c>
       <c r="AL21">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM21">
-        <v>60</v>
+        <v>310</v>
       </c>
       <c r="AN21">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AO21">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="AP21">
         <v>19.5</v>
       </c>
       <c r="AQ21">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR21">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AS21">
         <v>36</v>
       </c>
       <c r="AT21">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU21">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AV21">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW21">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="AX21">
         <v>13</v>
@@ -5787,10 +5787,10 @@
         <v>13.5</v>
       </c>
       <c r="BA21">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BB21">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC21">
         <v>14.5</v>
@@ -5799,7 +5799,7 @@
         <v>21</v>
       </c>
       <c r="BE21">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="BF21">
         <v>6.6</v>
@@ -5808,64 +5808,64 @@
         <v>20</v>
       </c>
       <c r="BH21">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BI21">
-        <v>3.8</v>
+        <v>2.14</v>
       </c>
       <c r="BJ21">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BK21">
-        <v>5.8</v>
+        <v>1.81</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>12</v>
+        <v>2.1</v>
       </c>
       <c r="BN21">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BO21">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="BP21">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="BQ21">
-        <v>7.2</v>
+        <v>1.89</v>
       </c>
       <c r="BR21">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="BS21">
-        <v>8.6</v>
+        <v>1.99</v>
       </c>
       <c r="BT21">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BU21">
-        <v>5.4</v>
+        <v>1.79</v>
       </c>
       <c r="BV21">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="BW21">
-        <v>9.800000000000001</v>
+        <v>2.02</v>
       </c>
       <c r="BX21">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="BY21">
-        <v>10</v>
+        <v>2.04</v>
       </c>
       <c r="BZ21">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="CA21">
-        <v>6.8</v>
+        <v>1.91</v>
       </c>
       <c r="CB21" t="s">
         <v>146</v>
@@ -5894,10 +5894,10 @@
         <v>4.3</v>
       </c>
       <c r="H22">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="I22">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="J22">
         <v>4.4</v>
@@ -5915,7 +5915,7 @@
         <v>7.6</v>
       </c>
       <c r="O22">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P22">
         <v>3.2</v>
@@ -5924,13 +5924,13 @@
         <v>1.42</v>
       </c>
       <c r="R22">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="S22">
         <v>2.06</v>
       </c>
       <c r="T22">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="U22">
         <v>3.05</v>
@@ -5939,19 +5939,19 @@
         <v>2.12</v>
       </c>
       <c r="W22">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X22">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Y22">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z22">
         <v>17.5</v>
       </c>
       <c r="AA22">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB22">
         <v>29</v>
@@ -5969,10 +5969,10 @@
         <v>42</v>
       </c>
       <c r="AG22">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH22">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI22">
         <v>23</v>
@@ -5993,13 +5993,13 @@
         <v>24</v>
       </c>
       <c r="AO22">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AP22">
         <v>23</v>
       </c>
       <c r="AQ22">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AR22">
         <v>15</v>
@@ -6008,7 +6008,7 @@
         <v>20</v>
       </c>
       <c r="AT22">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AU22">
         <v>10</v>
@@ -6020,16 +6020,16 @@
         <v>14.5</v>
       </c>
       <c r="AX22">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY22">
         <v>16</v>
       </c>
       <c r="AZ22">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA22">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BB22">
         <v>36</v>
@@ -6047,7 +6047,7 @@
         <v>20</v>
       </c>
       <c r="BG22">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BH22">
         <v>5.4</v>
@@ -6089,7 +6089,7 @@
         <v>5.6</v>
       </c>
       <c r="BU22">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BV22">
         <v>12</v>
@@ -6130,13 +6130,13 @@
         <v>145</v>
       </c>
       <c r="F23">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="G23">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H23">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I23">
         <v>3.2</v>
@@ -6160,28 +6160,28 @@
         <v>1.12</v>
       </c>
       <c r="P23">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="Q23">
         <v>1.38</v>
       </c>
       <c r="R23">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="S23">
         <v>1.96</v>
       </c>
       <c r="T23">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="U23">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="V23">
         <v>1.45</v>
       </c>
       <c r="W23">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="X23">
         <v>42</v>
@@ -6193,16 +6193,16 @@
         <v>34</v>
       </c>
       <c r="AA23">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AB23">
         <v>22</v>
       </c>
       <c r="AC23">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD23">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE23">
         <v>29</v>
@@ -6217,7 +6217,7 @@
         <v>14</v>
       </c>
       <c r="AI23">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ23">
         <v>32</v>
@@ -6229,7 +6229,7 @@
         <v>23</v>
       </c>
       <c r="AM23">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="AN23">
         <v>7.6</v>
@@ -6247,7 +6247,7 @@
         <v>29</v>
       </c>
       <c r="AS23">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AT23">
         <v>19.5</v>
@@ -6271,7 +6271,7 @@
         <v>12</v>
       </c>
       <c r="BA23">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB23">
         <v>27</v>
@@ -6286,7 +6286,7 @@
         <v>34</v>
       </c>
       <c r="BF23">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG23">
         <v>12</v>
@@ -6301,7 +6301,7 @@
         <v>8.6</v>
       </c>
       <c r="BK23">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="BL23">
         <v>1000</v>
@@ -6313,13 +6313,13 @@
         <v>6.2</v>
       </c>
       <c r="BO23">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BP23">
         <v>14</v>
       </c>
       <c r="BQ23">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR23">
         <v>19.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
@@ -454,7 +454,7 @@
     <t>Chicago Fire</t>
   </si>
   <si>
-    <t>2026-07-21 19:49:04</t>
+    <t>2026-07-21 21:55:49</t>
   </si>
 </sst>
 </file>
@@ -1048,226 +1048,226 @@
         <v>124</v>
       </c>
       <c r="F2">
-        <v>1.94</v>
+        <v>1.26</v>
       </c>
       <c r="G2">
-        <v>1.98</v>
+        <v>1.28</v>
       </c>
       <c r="H2">
+        <v>18.5</v>
+      </c>
+      <c r="I2">
+        <v>21</v>
+      </c>
+      <c r="J2">
+        <v>6</v>
+      </c>
+      <c r="K2">
+        <v>6.6</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>4.9</v>
+      </c>
+      <c r="O2">
+        <v>1.25</v>
+      </c>
+      <c r="P2">
+        <v>1.84</v>
+      </c>
+      <c r="Q2">
+        <v>2.16</v>
+      </c>
+      <c r="R2">
+        <v>1.24</v>
+      </c>
+      <c r="S2">
+        <v>4.9</v>
+      </c>
+      <c r="T2">
+        <v>2.22</v>
+      </c>
+      <c r="U2">
+        <v>1.74</v>
+      </c>
+      <c r="V2">
+        <v>1.05</v>
+      </c>
+      <c r="W2">
         <v>4.5</v>
       </c>
-      <c r="I2">
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>1000</v>
+      </c>
+      <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>5.1</v>
+      </c>
+      <c r="AC2">
+        <v>8.6</v>
+      </c>
+      <c r="AD2">
+        <v>30</v>
+      </c>
+      <c r="AE2">
+        <v>190</v>
+      </c>
+      <c r="AF2">
+        <v>4.9</v>
+      </c>
+      <c r="AG2">
+        <v>8.4</v>
+      </c>
+      <c r="AH2">
+        <v>34</v>
+      </c>
+      <c r="AI2">
+        <v>180</v>
+      </c>
+      <c r="AJ2">
+        <v>10</v>
+      </c>
+      <c r="AK2">
+        <v>18.5</v>
+      </c>
+      <c r="AL2">
+        <v>70</v>
+      </c>
+      <c r="AM2">
+        <v>380</v>
+      </c>
+      <c r="AN2">
+        <v>15</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>18.5</v>
+      </c>
+      <c r="AQ2">
+        <v>18.5</v>
+      </c>
+      <c r="AR2">
+        <v>18.5</v>
+      </c>
+      <c r="AS2">
+        <v>18.5</v>
+      </c>
+      <c r="AT2">
         <v>4.8</v>
       </c>
-      <c r="J2">
-        <v>3.55</v>
-      </c>
-      <c r="K2">
-        <v>3.7</v>
-      </c>
-      <c r="L2">
-        <v>1.44</v>
-      </c>
-      <c r="M2">
-        <v>1.08</v>
-      </c>
-      <c r="N2">
-        <v>3.55</v>
-      </c>
-      <c r="O2">
-        <v>1.36</v>
-      </c>
-      <c r="P2">
-        <v>1.86</v>
-      </c>
-      <c r="Q2">
-        <v>2.08</v>
-      </c>
-      <c r="R2">
-        <v>1.33</v>
-      </c>
-      <c r="S2">
-        <v>3.85</v>
-      </c>
-      <c r="T2">
-        <v>1.89</v>
-      </c>
-      <c r="U2">
-        <v>1.99</v>
-      </c>
-      <c r="V2">
-        <v>1.27</v>
-      </c>
-      <c r="W2">
-        <v>2.02</v>
-      </c>
-      <c r="X2">
-        <v>12.5</v>
-      </c>
-      <c r="Y2">
-        <v>15.5</v>
-      </c>
-      <c r="Z2">
-        <v>34</v>
-      </c>
-      <c r="AA2">
+      <c r="AU2">
+        <v>7.8</v>
+      </c>
+      <c r="AV2">
+        <v>25</v>
+      </c>
+      <c r="AW2">
+        <v>120</v>
+      </c>
+      <c r="AX2">
+        <v>4.5</v>
+      </c>
+      <c r="AY2">
+        <v>7.6</v>
+      </c>
+      <c r="AZ2">
+        <v>27</v>
+      </c>
+      <c r="BA2">
         <v>110</v>
       </c>
-      <c r="AB2">
-        <v>8.4</v>
-      </c>
-      <c r="AC2">
-        <v>8</v>
-      </c>
-      <c r="AD2">
-        <v>18</v>
-      </c>
-      <c r="AE2">
-        <v>65</v>
-      </c>
-      <c r="AF2">
-        <v>11.5</v>
-      </c>
-      <c r="AG2">
-        <v>10</v>
-      </c>
-      <c r="AH2">
-        <v>21</v>
-      </c>
-      <c r="AI2">
-        <v>75</v>
-      </c>
-      <c r="AJ2">
-        <v>23</v>
-      </c>
-      <c r="AK2">
-        <v>22</v>
-      </c>
-      <c r="AL2">
-        <v>40</v>
-      </c>
-      <c r="AM2">
-        <v>120</v>
-      </c>
-      <c r="AN2">
-        <v>16.5</v>
-      </c>
-      <c r="AO2">
-        <v>80</v>
-      </c>
-      <c r="AP2">
-        <v>11</v>
-      </c>
-      <c r="AQ2">
-        <v>14</v>
-      </c>
-      <c r="AR2">
-        <v>30</v>
-      </c>
-      <c r="AS2">
-        <v>90</v>
-      </c>
-      <c r="AT2">
-        <v>7.6</v>
-      </c>
-      <c r="AU2">
-        <v>7.4</v>
-      </c>
-      <c r="AV2">
-        <v>16.5</v>
-      </c>
-      <c r="AW2">
-        <v>55</v>
-      </c>
-      <c r="AX2">
-        <v>10</v>
-      </c>
-      <c r="AY2">
-        <v>9.4</v>
-      </c>
-      <c r="AZ2">
-        <v>18</v>
-      </c>
-      <c r="BA2">
-        <v>60</v>
-      </c>
       <c r="BB2">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="BC2">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="BD2">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="BE2">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="BF2">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BG2">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="BH2">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
         <v>146</v>
@@ -1290,226 +1290,226 @@
         <v>125</v>
       </c>
       <c r="F3">
-        <v>2.56</v>
+        <v>1.43</v>
       </c>
       <c r="G3">
-        <v>2.6</v>
+        <v>1.44</v>
       </c>
       <c r="H3">
-        <v>3.35</v>
+        <v>11</v>
       </c>
       <c r="I3">
-        <v>3.45</v>
+        <v>12</v>
       </c>
       <c r="J3">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="K3">
+        <v>4.7</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>6.2</v>
+      </c>
+      <c r="O3">
+        <v>1.18</v>
+      </c>
+      <c r="P3">
+        <v>2.2</v>
+      </c>
+      <c r="Q3">
+        <v>1.82</v>
+      </c>
+      <c r="R3">
+        <v>1.37</v>
+      </c>
+      <c r="S3">
+        <v>3.5</v>
+      </c>
+      <c r="T3">
+        <v>1.59</v>
+      </c>
+      <c r="U3">
+        <v>2.48</v>
+      </c>
+      <c r="V3">
+        <v>1.09</v>
+      </c>
+      <c r="W3">
         <v>3.2</v>
       </c>
-      <c r="L3">
-        <v>1.54</v>
-      </c>
-      <c r="M3">
-        <v>1.11</v>
-      </c>
-      <c r="N3">
-        <v>3</v>
-      </c>
-      <c r="O3">
-        <v>1.48</v>
-      </c>
-      <c r="P3">
-        <v>1.65</v>
-      </c>
-      <c r="Q3">
-        <v>2.46</v>
-      </c>
-      <c r="R3">
-        <v>1.24</v>
-      </c>
-      <c r="S3">
-        <v>4.8</v>
-      </c>
-      <c r="T3">
-        <v>2</v>
-      </c>
-      <c r="U3">
-        <v>1.94</v>
-      </c>
-      <c r="V3">
-        <v>1.41</v>
-      </c>
-      <c r="W3">
-        <v>1.62</v>
-      </c>
       <c r="X3">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="Y3">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z3">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA3">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="AC3">
+        <v>7.4</v>
+      </c>
+      <c r="AD3">
+        <v>21</v>
+      </c>
+      <c r="AE3">
+        <v>110</v>
+      </c>
+      <c r="AF3">
         <v>7</v>
       </c>
-      <c r="AD3">
-        <v>15</v>
-      </c>
-      <c r="AE3">
-        <v>46</v>
-      </c>
-      <c r="AF3">
-        <v>15.5</v>
-      </c>
       <c r="AG3">
-        <v>12.5</v>
+        <v>7.2</v>
       </c>
       <c r="AH3">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AI3">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="AJ3">
-        <v>40</v>
+        <v>14.5</v>
       </c>
       <c r="AK3">
-        <v>34</v>
+        <v>16.5</v>
       </c>
       <c r="AL3">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
         <v>140</v>
       </c>
       <c r="AN3">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="AO3">
-        <v>55</v>
+        <v>200</v>
       </c>
       <c r="AP3">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AQ3">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AR3">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AS3">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="AT3">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="AU3">
+        <v>7</v>
+      </c>
+      <c r="AV3">
+        <v>17.5</v>
+      </c>
+      <c r="AW3">
+        <v>75</v>
+      </c>
+      <c r="AX3">
         <v>6.4</v>
       </c>
-      <c r="AV3">
+      <c r="AY3">
+        <v>6.6</v>
+      </c>
+      <c r="AZ3">
+        <v>15</v>
+      </c>
+      <c r="BA3">
+        <v>60</v>
+      </c>
+      <c r="BB3">
+        <v>12.5</v>
+      </c>
+      <c r="BC3">
+        <v>14.5</v>
+      </c>
+      <c r="BD3">
+        <v>32</v>
+      </c>
+      <c r="BE3">
+        <v>110</v>
+      </c>
+      <c r="BF3">
         <v>13.5</v>
       </c>
-      <c r="AW3">
-        <v>40</v>
-      </c>
-      <c r="AX3">
-        <v>14</v>
-      </c>
-      <c r="AY3">
-        <v>11</v>
-      </c>
-      <c r="AZ3">
-        <v>18</v>
-      </c>
-      <c r="BA3">
-        <v>55</v>
-      </c>
-      <c r="BB3">
-        <v>34</v>
-      </c>
-      <c r="BC3">
-        <v>30</v>
-      </c>
-      <c r="BD3">
-        <v>46</v>
-      </c>
-      <c r="BE3">
-        <v>70</v>
-      </c>
-      <c r="BF3">
-        <v>29</v>
-      </c>
       <c r="BG3">
-        <v>46</v>
+        <v>130</v>
       </c>
       <c r="BH3">
-        <v>2.92</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>2.68</v>
+        <v>11.5</v>
       </c>
       <c r="BJ3">
-        <v>10.5</v>
+        <v>6.4</v>
       </c>
       <c r="BK3">
-        <v>9.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="BL3">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="BM3">
-        <v>13.5</v>
+        <v>100</v>
       </c>
       <c r="BN3">
-        <v>5.5</v>
+        <v>1.95</v>
       </c>
       <c r="BO3">
-        <v>4.8</v>
+        <v>1.83</v>
       </c>
       <c r="BP3">
-        <v>23</v>
+        <v>5.9</v>
       </c>
       <c r="BQ3">
-        <v>15.5</v>
+        <v>5.1</v>
       </c>
       <c r="BR3">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="BS3">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="BT3">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="BV3">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BX3">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="BY3">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="BZ3">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="CA3">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="CB3" t="s">
         <v>146</v>
@@ -1532,22 +1532,22 @@
         <v>126</v>
       </c>
       <c r="F4">
+        <v>1.36</v>
+      </c>
+      <c r="G4">
         <v>1.37</v>
       </c>
-      <c r="G4">
-        <v>1.39</v>
-      </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="I4">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="J4">
         <v>6</v>
       </c>
       <c r="K4">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L4">
         <v>1.3</v>
@@ -1556,43 +1556,43 @@
         <v>1.04</v>
       </c>
       <c r="N4">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O4">
         <v>1.2</v>
       </c>
       <c r="P4">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="Q4">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="R4">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="S4">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="T4">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="U4">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V4">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W4">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="X4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Z4">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AA4">
         <v>340</v>
@@ -1610,16 +1610,16 @@
         <v>130</v>
       </c>
       <c r="AF4">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AG4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH4">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI4">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AJ4">
         <v>11.5</v>
@@ -1631,10 +1631,10 @@
         <v>32</v>
       </c>
       <c r="AM4">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN4">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AO4">
         <v>140</v>
@@ -1643,37 +1643,37 @@
         <v>24</v>
       </c>
       <c r="AQ4">
+        <v>29</v>
+      </c>
+      <c r="AR4">
+        <v>75</v>
+      </c>
+      <c r="AS4">
+        <v>65</v>
+      </c>
+      <c r="AT4">
+        <v>9.4</v>
+      </c>
+      <c r="AU4">
+        <v>12.5</v>
+      </c>
+      <c r="AV4">
         <v>28</v>
       </c>
-      <c r="AR4">
-        <v>65</v>
-      </c>
-      <c r="AS4">
-        <v>55</v>
-      </c>
-      <c r="AT4">
-        <v>9</v>
-      </c>
-      <c r="AU4">
-        <v>12</v>
-      </c>
-      <c r="AV4">
-        <v>29</v>
-      </c>
       <c r="AW4">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="AX4">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AY4">
         <v>9.4</v>
       </c>
       <c r="AZ4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA4">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BB4">
         <v>10.5</v>
@@ -1685,70 +1685,70 @@
         <v>29</v>
       </c>
       <c r="BE4">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="BF4">
         <v>4.8</v>
       </c>
       <c r="BG4">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="BH4">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BI4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BJ4">
         <v>11</v>
       </c>
       <c r="BK4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BL4">
         <v>120</v>
       </c>
       <c r="BM4">
-        <v>17</v>
+        <v>110</v>
       </c>
       <c r="BN4">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BO4">
         <v>3.7</v>
       </c>
       <c r="BP4">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BQ4">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BS4">
-        <v>10.5</v>
+        <v>18.5</v>
       </c>
       <c r="BT4">
         <v>12.5</v>
       </c>
       <c r="BU4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BV4">
         <v>75</v>
       </c>
       <c r="BW4">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BX4">
         <v>65</v>
       </c>
       <c r="BY4">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BZ4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CA4">
         <v>10</v>
@@ -1774,22 +1774,22 @@
         <v>127</v>
       </c>
       <c r="F5">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="G5">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H5">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="I5">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K5">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L5">
         <v>1.32</v>
@@ -1810,22 +1810,22 @@
         <v>1.67</v>
       </c>
       <c r="R5">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S5">
         <v>2.72</v>
       </c>
       <c r="T5">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U5">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V5">
         <v>1.2</v>
       </c>
       <c r="W5">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="X5">
         <v>22</v>
@@ -1834,34 +1834,34 @@
         <v>24</v>
       </c>
       <c r="Z5">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AA5">
         <v>140</v>
       </c>
       <c r="AB5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC5">
         <v>10.5</v>
       </c>
       <c r="AD5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE5">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG5">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AH5">
         <v>19</v>
       </c>
       <c r="AI5">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ5">
         <v>16.5</v>
@@ -1873,22 +1873,22 @@
         <v>28</v>
       </c>
       <c r="AM5">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN5">
         <v>7.4</v>
       </c>
       <c r="AO5">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AP5">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AQ5">
         <v>21</v>
       </c>
       <c r="AR5">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AS5">
         <v>50</v>
@@ -1897,7 +1897,7 @@
         <v>10</v>
       </c>
       <c r="AU5">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV5">
         <v>19.5</v>
@@ -1912,7 +1912,7 @@
         <v>9</v>
       </c>
       <c r="AZ5">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA5">
         <v>55</v>
@@ -1927,13 +1927,13 @@
         <v>26</v>
       </c>
       <c r="BE5">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BF5">
         <v>6.8</v>
       </c>
       <c r="BG5">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BH5">
         <v>4.1</v>
@@ -1942,58 +1942,58 @@
         <v>3.8</v>
       </c>
       <c r="BJ5">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BK5">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BL5">
         <v>110</v>
       </c>
       <c r="BM5">
-        <v>11.5</v>
+        <v>85</v>
       </c>
       <c r="BN5">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO5">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BQ5">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR5">
         <v>23</v>
       </c>
       <c r="BS5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BT5">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU5">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV5">
         <v>44</v>
       </c>
       <c r="BW5">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BX5">
         <v>48</v>
       </c>
       <c r="BY5">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="BZ5">
         <v>16</v>
       </c>
       <c r="CA5">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="CB5" t="s">
         <v>146</v>
@@ -2070,7 +2070,7 @@
         <v>1.45</v>
       </c>
       <c r="X6">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y6">
         <v>8.6</v>
@@ -2133,7 +2133,7 @@
         <v>14</v>
       </c>
       <c r="AS6">
-        <v>17.5</v>
+        <v>36</v>
       </c>
       <c r="AT6">
         <v>8.6</v>
@@ -2157,25 +2157,25 @@
         <v>18</v>
       </c>
       <c r="BA6">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="BB6">
+        <v>26</v>
+      </c>
+      <c r="BC6">
         <v>20</v>
-      </c>
-      <c r="BC6">
-        <v>18</v>
       </c>
       <c r="BD6">
         <v>28</v>
       </c>
       <c r="BE6">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BF6">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BG6">
-        <v>11.5</v>
+        <v>27</v>
       </c>
       <c r="BH6">
         <v>2.84</v>
@@ -2264,16 +2264,16 @@
         <v>4.9</v>
       </c>
       <c r="H7">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="I7">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="J7">
         <v>3.55</v>
       </c>
       <c r="K7">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L7">
         <v>1.48</v>
@@ -2294,7 +2294,7 @@
         <v>2.18</v>
       </c>
       <c r="R7">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S7">
         <v>4</v>
@@ -2306,16 +2306,16 @@
         <v>1.95</v>
       </c>
       <c r="V7">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="W7">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X7">
         <v>12.5</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z7">
         <v>11</v>
@@ -2339,7 +2339,7 @@
         <v>40</v>
       </c>
       <c r="AG7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH7">
         <v>23</v>
@@ -2363,7 +2363,7 @@
         <v>170</v>
       </c>
       <c r="AO7">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AP7">
         <v>11</v>
@@ -2384,10 +2384,10 @@
         <v>7.2</v>
       </c>
       <c r="AV7">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW7">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AX7">
         <v>21</v>
@@ -2399,22 +2399,22 @@
         <v>18.5</v>
       </c>
       <c r="BA7">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB7">
         <v>40</v>
       </c>
       <c r="BC7">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="BD7">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BE7">
         <v>42</v>
       </c>
       <c r="BF7">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="BG7">
         <v>14.5</v>
@@ -2459,7 +2459,7 @@
         <v>4.5</v>
       </c>
       <c r="BU7">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BV7">
         <v>14.5</v>
@@ -2503,10 +2503,10 @@
         <v>1.91</v>
       </c>
       <c r="G8">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H8">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I8">
         <v>5.1</v>
@@ -2527,13 +2527,13 @@
         <v>3.1</v>
       </c>
       <c r="O8">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P8">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q8">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R8">
         <v>1.26</v>
@@ -2545,13 +2545,13 @@
         <v>2.1</v>
       </c>
       <c r="U8">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V8">
         <v>1.24</v>
       </c>
       <c r="W8">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X8">
         <v>11</v>
@@ -2560,10 +2560,10 @@
         <v>14</v>
       </c>
       <c r="Z8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>690</v>
       </c>
       <c r="AB8">
         <v>7.4</v>
@@ -2572,7 +2572,7 @@
         <v>8</v>
       </c>
       <c r="AD8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE8">
         <v>160</v>
@@ -2584,7 +2584,7 @@
         <v>11</v>
       </c>
       <c r="AH8">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AI8">
         <v>190</v>
@@ -2602,7 +2602,7 @@
         <v>570</v>
       </c>
       <c r="AN8">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO8">
         <v>490</v>
@@ -2626,10 +2626,10 @@
         <v>7.2</v>
       </c>
       <c r="AV8">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AW8">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AX8">
         <v>9.6</v>
@@ -2638,34 +2638,34 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA8">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="BB8">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BC8">
         <v>20</v>
       </c>
       <c r="BD8">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BE8">
         <v>70</v>
       </c>
       <c r="BF8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BG8">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="BH8">
         <v>2.98</v>
       </c>
       <c r="BI8">
-        <v>2.56</v>
+        <v>2.76</v>
       </c>
       <c r="BJ8">
         <v>11</v>
@@ -2683,7 +2683,7 @@
         <v>4.4</v>
       </c>
       <c r="BO8">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="BP8">
         <v>14.5</v>
@@ -2701,7 +2701,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BU8">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV8">
         <v>1000</v>
@@ -2742,22 +2742,22 @@
         <v>131</v>
       </c>
       <c r="F9">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="G9">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="H9">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I9">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="J9">
         <v>3.85</v>
       </c>
       <c r="K9">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L9">
         <v>1.24</v>
@@ -2775,7 +2775,7 @@
         <v>2.54</v>
       </c>
       <c r="Q9">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="R9">
         <v>1.63</v>
@@ -2808,7 +2808,7 @@
         <v>30</v>
       </c>
       <c r="AB9">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AC9">
         <v>9.4</v>
@@ -2820,7 +2820,7 @@
         <v>21</v>
       </c>
       <c r="AF9">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG9">
         <v>14.5</v>
@@ -2829,7 +2829,7 @@
         <v>14</v>
       </c>
       <c r="AI9">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ9">
         <v>55</v>
@@ -2856,13 +2856,13 @@
         <v>14</v>
       </c>
       <c r="AR9">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AS9">
         <v>26</v>
       </c>
       <c r="AT9">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AU9">
         <v>8.4</v>
@@ -2886,7 +2886,7 @@
         <v>24</v>
       </c>
       <c r="BB9">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="BC9">
         <v>27</v>
@@ -2895,7 +2895,7 @@
         <v>30</v>
       </c>
       <c r="BE9">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF9">
         <v>18</v>
@@ -3011,10 +3011,10 @@
         <v>11</v>
       </c>
       <c r="O10">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="P10">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q10">
         <v>1.27</v>
@@ -3023,19 +3023,19 @@
         <v>2.3</v>
       </c>
       <c r="S10">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="T10">
         <v>2.06</v>
       </c>
       <c r="U10">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="V10">
         <v>1.02</v>
       </c>
       <c r="W10">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>490</v>
@@ -3241,7 +3241,7 @@
         <v>3</v>
       </c>
       <c r="K11">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L11">
         <v>1.52</v>
@@ -3256,10 +3256,10 @@
         <v>1.54</v>
       </c>
       <c r="P11">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="Q11">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="R11">
         <v>1.19</v>
@@ -3283,7 +3283,7 @@
         <v>9</v>
       </c>
       <c r="Y11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z11">
         <v>32</v>
@@ -3295,7 +3295,7 @@
         <v>7.4</v>
       </c>
       <c r="AC11">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD11">
         <v>19</v>
@@ -3343,7 +3343,7 @@
         <v>21</v>
       </c>
       <c r="AS11">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AT11">
         <v>6</v>
@@ -3355,7 +3355,7 @@
         <v>15</v>
       </c>
       <c r="AW11">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX11">
         <v>10.5</v>
@@ -3367,7 +3367,7 @@
         <v>20</v>
       </c>
       <c r="BA11">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BB11">
         <v>24</v>
@@ -3379,13 +3379,13 @@
         <v>28</v>
       </c>
       <c r="BE11">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BF11">
         <v>24</v>
       </c>
       <c r="BG11">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3468,10 +3468,10 @@
         <v>134</v>
       </c>
       <c r="F12">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="G12">
-        <v>46</v>
+        <v>8.4</v>
       </c>
       <c r="H12">
         <v>1.72</v>
@@ -3507,7 +3507,7 @@
         <v>1.09</v>
       </c>
       <c r="S12">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T12">
         <v>1.11</v>
@@ -3713,13 +3713,13 @@
         <v>1.22</v>
       </c>
       <c r="G13">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="H13">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="I13">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J13">
         <v>6.4</v>
@@ -3743,7 +3743,7 @@
         <v>2.3</v>
       </c>
       <c r="Q13">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="R13">
         <v>1.5</v>
@@ -3929,7 +3929,7 @@
         <v>11</v>
       </c>
       <c r="CA13">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="CB13" t="s">
         <v>146</v>
@@ -3964,10 +3964,10 @@
         <v>1.86</v>
       </c>
       <c r="J14">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K14">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L14">
         <v>1.47</v>
@@ -3982,22 +3982,22 @@
         <v>1.41</v>
       </c>
       <c r="P14">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q14">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R14">
         <v>1.28</v>
       </c>
       <c r="S14">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T14">
         <v>2.06</v>
       </c>
       <c r="U14">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V14">
         <v>2.16</v>
@@ -4009,37 +4009,37 @@
         <v>11</v>
       </c>
       <c r="Y14">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z14">
         <v>9.800000000000001</v>
       </c>
       <c r="AA14">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AB14">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AC14">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD14">
         <v>10.5</v>
       </c>
       <c r="AE14">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AF14">
         <v>40</v>
       </c>
       <c r="AG14">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AH14">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AI14">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="AJ14">
         <v>150</v>
@@ -4048,7 +4048,7 @@
         <v>85</v>
       </c>
       <c r="AL14">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AM14">
         <v>440</v>
@@ -4057,7 +4057,7 @@
         <v>120</v>
       </c>
       <c r="AO14">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AP14">
         <v>10</v>
@@ -4066,7 +4066,7 @@
         <v>7</v>
       </c>
       <c r="AR14">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS14">
         <v>17.5</v>
@@ -4078,10 +4078,10 @@
         <v>7.4</v>
       </c>
       <c r="AV14">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AW14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AX14">
         <v>34</v>
@@ -4096,13 +4096,13 @@
         <v>40</v>
       </c>
       <c r="BB14">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BC14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BD14">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE14">
         <v>70</v>
@@ -4111,7 +4111,7 @@
         <v>38</v>
       </c>
       <c r="BG14">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH14">
         <v>3.1</v>
@@ -4209,7 +4209,7 @@
         <v>3.4</v>
       </c>
       <c r="K15">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L15">
         <v>1.48</v>
@@ -4242,7 +4242,7 @@
         <v>1.95</v>
       </c>
       <c r="V15">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W15">
         <v>1.78</v>
@@ -4254,7 +4254,7 @@
         <v>12</v>
       </c>
       <c r="Z15">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AA15">
         <v>900</v>
@@ -4269,7 +4269,7 @@
         <v>80</v>
       </c>
       <c r="AE15">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AF15">
         <v>14</v>
@@ -4284,7 +4284,7 @@
         <v>500</v>
       </c>
       <c r="AJ15">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AK15">
         <v>65</v>
@@ -4311,7 +4311,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AS15">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT15">
         <v>7.4</v>
@@ -4335,13 +4335,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BA15">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BB15">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC15">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BD15">
         <v>10.5</v>
@@ -4353,7 +4353,7 @@
         <v>20</v>
       </c>
       <c r="BG15">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH15">
         <v>3.05</v>
@@ -4442,7 +4442,7 @@
         <v>1.44</v>
       </c>
       <c r="H16">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="I16">
         <v>12</v>
@@ -4469,10 +4469,10 @@
         <v>1.9</v>
       </c>
       <c r="Q16">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="R16">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S16">
         <v>3.6</v>
@@ -4601,7 +4601,7 @@
         <v>3.5</v>
       </c>
       <c r="BI16">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BJ16">
         <v>13.5</v>
@@ -4696,7 +4696,7 @@
         <v>4.2</v>
       </c>
       <c r="L17">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="M17">
         <v>1.05</v>
@@ -4708,10 +4708,10 @@
         <v>1.24</v>
       </c>
       <c r="P17">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q17">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R17">
         <v>1.47</v>
@@ -4720,10 +4720,10 @@
         <v>2.8</v>
       </c>
       <c r="T17">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U17">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V17">
         <v>1.27</v>
@@ -4735,16 +4735,16 @@
         <v>23</v>
       </c>
       <c r="Y17">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z17">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA17">
         <v>110</v>
       </c>
       <c r="AB17">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC17">
         <v>11.5</v>
@@ -4950,7 +4950,7 @@
         <v>1.42</v>
       </c>
       <c r="P18">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q18">
         <v>2.24</v>
@@ -5195,13 +5195,13 @@
         <v>2.1</v>
       </c>
       <c r="Q19">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R19">
         <v>1.43</v>
       </c>
       <c r="S19">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T19">
         <v>1.75</v>
@@ -5222,7 +5222,7 @@
         <v>16.5</v>
       </c>
       <c r="Z19">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="AA19">
         <v>1000</v>
@@ -5231,7 +5231,7 @@
         <v>10.5</v>
       </c>
       <c r="AC19">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD19">
         <v>16.5</v>
@@ -5240,7 +5240,7 @@
         <v>120</v>
       </c>
       <c r="AF19">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG19">
         <v>11</v>
@@ -5249,7 +5249,7 @@
         <v>18</v>
       </c>
       <c r="AI19">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="AJ19">
         <v>25</v>
@@ -5270,7 +5270,7 @@
         <v>100</v>
       </c>
       <c r="AP19">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ19">
         <v>14</v>
@@ -5282,28 +5282,28 @@
         <v>34</v>
       </c>
       <c r="AT19">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AU19">
         <v>7.6</v>
       </c>
       <c r="AV19">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW19">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AX19">
         <v>11.5</v>
       </c>
       <c r="AY19">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ19">
         <v>15</v>
       </c>
       <c r="BA19">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="BB19">
         <v>20</v>
@@ -5404,7 +5404,7 @@
         <v>142</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="G20">
         <v>2.02</v>
@@ -5416,10 +5416,10 @@
         <v>4.2</v>
       </c>
       <c r="J20">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K20">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L20">
         <v>1.36</v>
@@ -5440,19 +5440,19 @@
         <v>1.82</v>
       </c>
       <c r="R20">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S20">
         <v>3.1</v>
       </c>
       <c r="T20">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U20">
         <v>2.28</v>
       </c>
       <c r="V20">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W20">
         <v>1.98</v>
@@ -5467,7 +5467,7 @@
         <v>32</v>
       </c>
       <c r="AA20">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB20">
         <v>11</v>
@@ -5491,7 +5491,7 @@
         <v>17.5</v>
       </c>
       <c r="AI20">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AJ20">
         <v>24</v>
@@ -5563,7 +5563,7 @@
         <v>11</v>
       </c>
       <c r="BG20">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5649,13 +5649,13 @@
         <v>1.83</v>
       </c>
       <c r="G21">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H21">
         <v>4.2</v>
       </c>
       <c r="I21">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J21">
         <v>4.3</v>
@@ -5691,7 +5691,7 @@
         <v>1.55</v>
       </c>
       <c r="U21">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="V21">
         <v>1.29</v>
@@ -5700,7 +5700,7 @@
         <v>2.16</v>
       </c>
       <c r="X21">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Y21">
         <v>25</v>
@@ -5721,7 +5721,7 @@
         <v>18.5</v>
       </c>
       <c r="AE21">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF21">
         <v>15</v>
@@ -5745,13 +5745,13 @@
         <v>25</v>
       </c>
       <c r="AM21">
-        <v>310</v>
+        <v>60</v>
       </c>
       <c r="AN21">
         <v>7.4</v>
       </c>
       <c r="AO21">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="AP21">
         <v>19.5</v>
@@ -5760,7 +5760,7 @@
         <v>21</v>
       </c>
       <c r="AR21">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AS21">
         <v>36</v>
@@ -5775,7 +5775,7 @@
         <v>16</v>
       </c>
       <c r="AW21">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AX21">
         <v>13</v>
@@ -5787,7 +5787,7 @@
         <v>13.5</v>
       </c>
       <c r="BA21">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB21">
         <v>19</v>
@@ -5799,10 +5799,10 @@
         <v>21</v>
       </c>
       <c r="BE21">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BF21">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG21">
         <v>20</v>
@@ -5811,40 +5811,40 @@
         <v>1000</v>
       </c>
       <c r="BI21">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="BJ21">
         <v>12</v>
       </c>
       <c r="BK21">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="BN21">
         <v>6.8</v>
       </c>
       <c r="BO21">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="BP21">
         <v>16</v>
       </c>
       <c r="BQ21">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="BR21">
         <v>28</v>
       </c>
       <c r="BS21">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="BT21">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU21">
         <v>1.79</v>
@@ -5853,19 +5853,19 @@
         <v>40</v>
       </c>
       <c r="BW21">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="BX21">
         <v>44</v>
       </c>
       <c r="BY21">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="BZ21">
         <v>18</v>
       </c>
       <c r="CA21">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="CB21" t="s">
         <v>146</v>
@@ -5927,22 +5927,22 @@
         <v>1.9</v>
       </c>
       <c r="S22">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="T22">
         <v>1.46</v>
       </c>
       <c r="U22">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="V22">
         <v>2.12</v>
       </c>
       <c r="W22">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X22">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Y22">
         <v>18</v>
@@ -5951,7 +5951,7 @@
         <v>17.5</v>
       </c>
       <c r="AA22">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB22">
         <v>29</v>
@@ -6035,7 +6035,7 @@
         <v>36</v>
       </c>
       <c r="BC22">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BD22">
         <v>22</v>
@@ -6056,10 +6056,10 @@
         <v>4</v>
       </c>
       <c r="BJ22">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BK22">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BL22">
         <v>65</v>
@@ -6068,7 +6068,7 @@
         <v>8.6</v>
       </c>
       <c r="BN22">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BO22">
         <v>6</v>
@@ -6148,7 +6148,7 @@
         <v>4.4</v>
       </c>
       <c r="L23">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M23">
         <v>1.02</v>
@@ -6169,13 +6169,13 @@
         <v>1.99</v>
       </c>
       <c r="S23">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="T23">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="U23">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="V23">
         <v>1.45</v>
@@ -6199,7 +6199,7 @@
         <v>22</v>
       </c>
       <c r="AC23">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD23">
         <v>15</v>
@@ -6223,13 +6223,13 @@
         <v>32</v>
       </c>
       <c r="AK23">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AL23">
         <v>23</v>
       </c>
       <c r="AM23">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN23">
         <v>7.6</v>
@@ -6253,7 +6253,7 @@
         <v>19.5</v>
       </c>
       <c r="AU23">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV23">
         <v>13.5</v>
@@ -6301,7 +6301,7 @@
         <v>8.6</v>
       </c>
       <c r="BK23">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BL23">
         <v>1000</v>
@@ -6319,7 +6319,7 @@
         <v>14</v>
       </c>
       <c r="BQ23">
-        <v>9.800000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="BR23">
         <v>19.5</v>
@@ -6349,7 +6349,7 @@
         <v>11.5</v>
       </c>
       <c r="CA23">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="CB23" t="s">
         <v>146</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
@@ -415,7 +415,7 @@
     <t>Chicago Fire</t>
   </si>
   <si>
-    <t>2026-07-22 02:10:19</t>
+    <t>2026-07-22 04:17:51</t>
   </si>
 </sst>
 </file>
@@ -1009,7 +1009,7 @@
         <v>115</v>
       </c>
       <c r="F2">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G2">
         <v>3.25</v>
@@ -1021,40 +1021,40 @@
         <v>2.72</v>
       </c>
       <c r="J2">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K2">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L2">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="M2">
         <v>1.11</v>
       </c>
       <c r="N2">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O2">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P2">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Q2">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="R2">
         <v>1.23</v>
       </c>
       <c r="S2">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="T2">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="U2">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="V2">
         <v>1.58</v>
@@ -1069,43 +1069,43 @@
         <v>8.6</v>
       </c>
       <c r="Z2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AB2">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AC2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AD2">
         <v>12.5</v>
       </c>
       <c r="AE2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AF2">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AG2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH2">
         <v>21</v>
       </c>
       <c r="AI2">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="AJ2">
         <v>60</v>
       </c>
       <c r="AK2">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AL2">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="AM2">
         <v>580</v>
@@ -1120,25 +1120,25 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS2">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AT2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AX2">
         <v>17</v>
@@ -1147,7 +1147,7 @@
         <v>12.5</v>
       </c>
       <c r="AZ2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA2">
         <v>28</v>
@@ -1156,79 +1156,79 @@
         <v>26</v>
       </c>
       <c r="BC2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BD2">
         <v>28</v>
       </c>
       <c r="BE2">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BF2">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG2">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BH2">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="BI2">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="BJ2">
         <v>10.5</v>
       </c>
       <c r="BK2">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>2.48</v>
+        <v>20</v>
       </c>
       <c r="BN2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BO2">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BP2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BQ2">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BR2">
         <v>48</v>
       </c>
       <c r="BS2">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="BT2">
         <v>5.3</v>
       </c>
       <c r="BU2">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BV2">
         <v>23</v>
       </c>
       <c r="BW2">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BX2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BY2">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="BZ2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="CA2">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="CB2" t="s">
         <v>133</v>
@@ -1251,73 +1251,73 @@
         <v>116</v>
       </c>
       <c r="F3">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="G3">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H3">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="J3">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K3">
         <v>3.6</v>
       </c>
       <c r="L3">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M3">
         <v>1.09</v>
       </c>
       <c r="N3">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O3">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P3">
         <v>1.77</v>
       </c>
       <c r="Q3">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R3">
         <v>1.29</v>
       </c>
       <c r="S3">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T3">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="U3">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="V3">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="W3">
         <v>1.27</v>
       </c>
       <c r="X3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y3">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="Z3">
         <v>11.5</v>
       </c>
       <c r="AA3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC3">
         <v>7.8</v>
@@ -1326,151 +1326,151 @@
         <v>10.5</v>
       </c>
       <c r="AE3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF3">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AG3">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AH3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI3">
         <v>55</v>
       </c>
       <c r="AJ3">
-        <v>330</v>
+        <v>110</v>
       </c>
       <c r="AK3">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AL3">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AM3">
-        <v>440</v>
+        <v>140</v>
       </c>
       <c r="AN3">
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="AO3">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AP3">
         <v>10.5</v>
       </c>
       <c r="AQ3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS3">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AT3">
         <v>12.5</v>
       </c>
       <c r="AU3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV3">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW3">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AX3">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AY3">
         <v>16.5</v>
       </c>
       <c r="AZ3">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BA3">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="BB3">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BC3">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BD3">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="BE3">
         <v>42</v>
       </c>
       <c r="BF3">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="BG3">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="BH3">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="BI3">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="BJ3">
         <v>10.5</v>
       </c>
       <c r="BK3">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BN3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BO3">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BP3">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BQ3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BT3">
         <v>4.5</v>
       </c>
       <c r="BU3">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BV3">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BW3">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BX3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BY3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BZ3">
         <v>32</v>
       </c>
       <c r="CA3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="CB3" t="s">
         <v>133</v>
@@ -1493,13 +1493,13 @@
         <v>117</v>
       </c>
       <c r="F4">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="G4">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="H4">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I4">
         <v>5.2</v>
@@ -1511,40 +1511,40 @@
         <v>3.6</v>
       </c>
       <c r="L4">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M4">
         <v>1.1</v>
       </c>
       <c r="N4">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O4">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P4">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q4">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="R4">
         <v>1.26</v>
       </c>
       <c r="S4">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T4">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U4">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="V4">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W4">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X4">
         <v>11</v>
@@ -1568,16 +1568,16 @@
         <v>21</v>
       </c>
       <c r="AE4">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="AF4">
         <v>10.5</v>
       </c>
       <c r="AG4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH4">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AI4">
         <v>190</v>
@@ -1586,10 +1586,10 @@
         <v>22</v>
       </c>
       <c r="AK4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL4">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="AM4">
         <v>570</v>
@@ -1598,31 +1598,31 @@
         <v>18</v>
       </c>
       <c r="AO4">
-        <v>490</v>
+        <v>110</v>
       </c>
       <c r="AP4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS4">
         <v>40</v>
       </c>
       <c r="AT4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU4">
         <v>7.2</v>
       </c>
       <c r="AV4">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AW4">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="AX4">
         <v>9.6</v>
@@ -1631,19 +1631,19 @@
         <v>9.6</v>
       </c>
       <c r="AZ4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA4">
         <v>42</v>
       </c>
       <c r="BB4">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BC4">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD4">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="BE4">
         <v>70</v>
@@ -1652,13 +1652,13 @@
         <v>15.5</v>
       </c>
       <c r="BG4">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BH4">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="BI4">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="BJ4">
         <v>11</v>
@@ -1670,7 +1670,7 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BN4">
         <v>4.3</v>
@@ -1688,7 +1688,7 @@
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BT4">
         <v>8.199999999999999</v>
@@ -1700,19 +1700,19 @@
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BZ4">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="CA4">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="CB4" t="s">
         <v>133</v>
@@ -1738,13 +1738,13 @@
         <v>3.2</v>
       </c>
       <c r="G5">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H5">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="I5">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="J5">
         <v>3.9</v>
@@ -1759,13 +1759,13 @@
         <v>1.04</v>
       </c>
       <c r="N5">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O5">
         <v>1.19</v>
       </c>
       <c r="P5">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q5">
         <v>1.6</v>
@@ -1774,7 +1774,7 @@
         <v>1.64</v>
       </c>
       <c r="S5">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="T5">
         <v>1.55</v>
@@ -1783,10 +1783,10 @@
         <v>2.74</v>
       </c>
       <c r="V5">
-        <v>1.59</v>
+        <v>1.76</v>
       </c>
       <c r="W5">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="X5">
         <v>24</v>
@@ -1801,7 +1801,7 @@
         <v>30</v>
       </c>
       <c r="AB5">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AC5">
         <v>9.4</v>
@@ -1813,16 +1813,16 @@
         <v>21</v>
       </c>
       <c r="AF5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG5">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH5">
         <v>14</v>
       </c>
       <c r="AI5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ5">
         <v>50</v>
@@ -1843,7 +1843,7 @@
         <v>11.5</v>
       </c>
       <c r="AP5">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AQ5">
         <v>14</v>
@@ -1852,13 +1852,13 @@
         <v>16</v>
       </c>
       <c r="AS5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AT5">
         <v>17.5</v>
       </c>
       <c r="AU5">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV5">
         <v>10.5</v>
@@ -1867,7 +1867,7 @@
         <v>19</v>
       </c>
       <c r="AX5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY5">
         <v>13</v>
@@ -1879,7 +1879,7 @@
         <v>24</v>
       </c>
       <c r="BB5">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BC5">
         <v>27</v>
@@ -1888,10 +1888,10 @@
         <v>30</v>
       </c>
       <c r="BE5">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BF5">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BG5">
         <v>10.5</v>
@@ -1980,19 +1980,19 @@
         <v>1.12</v>
       </c>
       <c r="G6">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="H6">
         <v>27</v>
       </c>
       <c r="I6">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J6">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="K6">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="L6">
         <v>1.17</v>
@@ -2001,31 +2001,31 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O6">
         <v>1.08</v>
       </c>
       <c r="P6">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="Q6">
         <v>1.27</v>
       </c>
       <c r="R6">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="S6">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="T6">
         <v>2.08</v>
       </c>
       <c r="U6">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="V6">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W6">
         <v>8</v>
@@ -2037,82 +2037,82 @@
         <v>940</v>
       </c>
       <c r="Z6">
-        <v>400</v>
+        <v>370</v>
       </c>
       <c r="AA6">
         <v>1000</v>
       </c>
       <c r="AB6">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AC6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AD6">
         <v>940</v>
       </c>
       <c r="AE6">
-        <v>470</v>
+        <v>410</v>
       </c>
       <c r="AF6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG6">
         <v>15.5</v>
       </c>
       <c r="AH6">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AI6">
         <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK6">
         <v>14.5</v>
       </c>
       <c r="AL6">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AM6">
         <v>490</v>
       </c>
       <c r="AN6">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="AO6">
-        <v>460</v>
+        <v>380</v>
       </c>
       <c r="AP6">
         <v>38</v>
       </c>
       <c r="AQ6">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AR6">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AS6">
+        <v>90</v>
+      </c>
+      <c r="AT6">
         <v>16.5</v>
       </c>
-      <c r="AT6">
-        <v>15</v>
-      </c>
       <c r="AU6">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AV6">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AW6">
         <v>55</v>
       </c>
       <c r="AX6">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY6">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ6">
         <v>38</v>
@@ -2133,16 +2133,16 @@
         <v>70</v>
       </c>
       <c r="BF6">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="BG6">
         <v>55</v>
       </c>
       <c r="BH6">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BI6">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BJ6">
         <v>14.5</v>
@@ -2157,28 +2157,28 @@
         <v>12.5</v>
       </c>
       <c r="BN6">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BO6">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="BP6">
         <v>5.8</v>
       </c>
       <c r="BQ6">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BR6">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BS6">
         <v>8</v>
       </c>
       <c r="BT6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BU6">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BV6">
         <v>1000</v>
@@ -2193,7 +2193,7 @@
         <v>12</v>
       </c>
       <c r="BZ6">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="CA6">
         <v>4.5</v>
@@ -2219,19 +2219,19 @@
         <v>120</v>
       </c>
       <c r="F7">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="G7">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="H7">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I7">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J7">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="K7">
         <v>3.2</v>
@@ -2243,46 +2243,46 @@
         <v>1.13</v>
       </c>
       <c r="N7">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O7">
         <v>1.57</v>
       </c>
       <c r="P7">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="Q7">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="R7">
         <v>1.18</v>
       </c>
       <c r="S7">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="T7">
         <v>2.14</v>
       </c>
       <c r="U7">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V7">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W7">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="X7">
         <v>8.6</v>
       </c>
       <c r="Y7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z7">
         <v>32</v>
       </c>
       <c r="AA7">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB7">
         <v>7.2</v>
@@ -2294,10 +2294,10 @@
         <v>18</v>
       </c>
       <c r="AE7">
-        <v>370</v>
+        <v>100</v>
       </c>
       <c r="AF7">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG7">
         <v>12.5</v>
@@ -2306,49 +2306,49 @@
         <v>29</v>
       </c>
       <c r="AI7">
-        <v>500</v>
+        <v>380</v>
       </c>
       <c r="AJ7">
-        <v>120</v>
+        <v>38</v>
       </c>
       <c r="AK7">
         <v>38</v>
       </c>
       <c r="AL7">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="AM7">
         <v>500</v>
       </c>
       <c r="AN7">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AO7">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP7">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AQ7">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR7">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="AS7">
-        <v>9.6</v>
+        <v>60</v>
       </c>
       <c r="AT7">
         <v>6</v>
       </c>
       <c r="AU7">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV7">
         <v>15</v>
       </c>
       <c r="AW7">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="AX7">
         <v>10.5</v>
@@ -2360,31 +2360,31 @@
         <v>20</v>
       </c>
       <c r="BA7">
-        <v>9.6</v>
+        <v>55</v>
       </c>
       <c r="BB7">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="BC7">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="BD7">
         <v>40</v>
       </c>
       <c r="BE7">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="BF7">
-        <v>8.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="BG7">
-        <v>9.6</v>
+        <v>65</v>
       </c>
       <c r="BH7">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="BI7">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="BJ7">
         <v>12</v>
@@ -2396,25 +2396,25 @@
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BN7">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO7">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BP7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ7">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BR7">
         <v>65</v>
       </c>
       <c r="BS7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT7">
         <v>7.2</v>
@@ -2426,19 +2426,19 @@
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="CB7" t="s">
         <v>133</v>
@@ -2461,16 +2461,16 @@
         <v>121</v>
       </c>
       <c r="F8">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="G8">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="H8">
         <v>1.72</v>
       </c>
       <c r="I8">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="J8">
         <v>2.7</v>
@@ -2485,22 +2485,22 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="O8">
         <v>1.02</v>
       </c>
       <c r="P8">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Q8">
         <v>1.01</v>
       </c>
       <c r="R8">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="S8">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T8">
         <v>1.11</v>
@@ -2509,10 +2509,10 @@
         <v>1.11</v>
       </c>
       <c r="V8">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W8">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X8">
         <v>950</v>
@@ -2524,7 +2524,7 @@
         <v>500</v>
       </c>
       <c r="AA8">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB8">
         <v>950</v>
@@ -2703,10 +2703,10 @@
         <v>122</v>
       </c>
       <c r="F9">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="G9">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="H9">
         <v>17</v>
@@ -2715,34 +2715,34 @@
         <v>21</v>
       </c>
       <c r="J9">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="K9">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="L9">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M9">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N9">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="O9">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P9">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q9">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="R9">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="S9">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="T9">
         <v>2.32</v>
@@ -2754,7 +2754,7 @@
         <v>1.05</v>
       </c>
       <c r="W9">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="X9">
         <v>28</v>
@@ -2772,13 +2772,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AC9">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AD9">
         <v>510</v>
       </c>
       <c r="AE9">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="AF9">
         <v>7.4</v>
@@ -2787,10 +2787,10 @@
         <v>12</v>
       </c>
       <c r="AH9">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AI9">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AJ9">
         <v>9.199999999999999</v>
@@ -2799,13 +2799,13 @@
         <v>16</v>
       </c>
       <c r="AL9">
-        <v>330</v>
+        <v>50</v>
       </c>
       <c r="AM9">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AN9">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AO9">
         <v>1000</v>
@@ -2814,13 +2814,13 @@
         <v>20</v>
       </c>
       <c r="AQ9">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR9">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AS9">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT9">
         <v>7.2</v>
@@ -2829,10 +2829,10 @@
         <v>13.5</v>
       </c>
       <c r="AV9">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AW9">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AX9">
         <v>6.2</v>
@@ -2841,10 +2841,10 @@
         <v>10</v>
       </c>
       <c r="AZ9">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BA9">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB9">
         <v>7.8</v>
@@ -2853,40 +2853,40 @@
         <v>12.5</v>
       </c>
       <c r="BD9">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE9">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF9">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BG9">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH9">
         <v>4.3</v>
       </c>
       <c r="BI9">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ9">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BK9">
-        <v>6.8</v>
+        <v>2.38</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>12</v>
+        <v>2.8</v>
       </c>
       <c r="BN9">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BP9">
         <v>7</v>
@@ -2895,28 +2895,28 @@
         <v>5.8</v>
       </c>
       <c r="BR9">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BS9">
-        <v>8.6</v>
+        <v>2.56</v>
       </c>
       <c r="BT9">
         <v>18</v>
       </c>
       <c r="BU9">
-        <v>7.4</v>
+        <v>2.46</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>11.5</v>
+        <v>2.8</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>11.5</v>
+        <v>2.78</v>
       </c>
       <c r="BZ9">
         <v>11</v>
@@ -2945,7 +2945,7 @@
         <v>123</v>
       </c>
       <c r="F10">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="G10">
         <v>1.42</v>
@@ -2954,7 +2954,7 @@
         <v>10</v>
       </c>
       <c r="I10">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J10">
         <v>5</v>
@@ -2975,7 +2975,7 @@
         <v>1.34</v>
       </c>
       <c r="P10">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="Q10">
         <v>2.02</v>
@@ -2987,10 +2987,10 @@
         <v>3.75</v>
       </c>
       <c r="T10">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="U10">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="V10">
         <v>1.1</v>
@@ -2999,16 +2999,16 @@
         <v>3.35</v>
       </c>
       <c r="X10">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y10">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="Z10">
         <v>540</v>
       </c>
       <c r="AA10">
-        <v>590</v>
+        <v>550</v>
       </c>
       <c r="AB10">
         <v>7</v>
@@ -3020,7 +3020,7 @@
         <v>95</v>
       </c>
       <c r="AE10">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="AF10">
         <v>7.8</v>
@@ -3032,7 +3032,7 @@
         <v>85</v>
       </c>
       <c r="AI10">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AJ10">
         <v>12</v>
@@ -3044,13 +3044,13 @@
         <v>130</v>
       </c>
       <c r="AM10">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="AN10">
         <v>8.4</v>
       </c>
       <c r="AO10">
-        <v>470</v>
+        <v>430</v>
       </c>
       <c r="AP10">
         <v>12</v>
@@ -3062,7 +3062,7 @@
         <v>9.6</v>
       </c>
       <c r="AS10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT10">
         <v>5.9</v>
@@ -3077,7 +3077,7 @@
         <v>10</v>
       </c>
       <c r="AX10">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY10">
         <v>9.199999999999999</v>
@@ -3095,7 +3095,7 @@
         <v>14.5</v>
       </c>
       <c r="BD10">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE10">
         <v>10</v>
@@ -3128,7 +3128,7 @@
         <v>3.7</v>
       </c>
       <c r="BO10">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="BP10">
         <v>9</v>
@@ -3193,19 +3193,19 @@
         <v>5</v>
       </c>
       <c r="H11">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="I11">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="J11">
         <v>3.5</v>
       </c>
       <c r="K11">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L11">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M11">
         <v>1.09</v>
@@ -3220,7 +3220,7 @@
         <v>1.74</v>
       </c>
       <c r="Q11">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R11">
         <v>1.27</v>
@@ -3232,7 +3232,7 @@
         <v>2.02</v>
       </c>
       <c r="U11">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V11">
         <v>2.04</v>
@@ -3250,7 +3250,7 @@
         <v>10.5</v>
       </c>
       <c r="AA11">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AB11">
         <v>14.5</v>
@@ -3271,7 +3271,7 @@
         <v>19</v>
       </c>
       <c r="AH11">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI11">
         <v>46</v>
@@ -3289,7 +3289,7 @@
         <v>440</v>
       </c>
       <c r="AN11">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AO11">
         <v>17.5</v>
@@ -3298,19 +3298,19 @@
         <v>10</v>
       </c>
       <c r="AQ11">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR11">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AS11">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AT11">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU11">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV11">
         <v>9.800000000000001</v>
@@ -3343,31 +3343,31 @@
         <v>70</v>
       </c>
       <c r="BF11">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="BG11">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BH11">
         <v>3.05</v>
       </c>
       <c r="BI11">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BJ11">
         <v>11</v>
       </c>
       <c r="BK11">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BN11">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BO11">
         <v>5.5</v>
@@ -3376,37 +3376,37 @@
         <v>44</v>
       </c>
       <c r="BQ11">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BR11">
         <v>60</v>
       </c>
       <c r="BS11">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BT11">
         <v>4.4</v>
       </c>
       <c r="BU11">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BV11">
         <v>14.5</v>
       </c>
       <c r="BW11">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX11">
         <v>34</v>
       </c>
       <c r="BY11">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ11">
         <v>32</v>
       </c>
       <c r="CA11">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="CB11" t="s">
         <v>133</v>
@@ -3432,61 +3432,61 @@
         <v>2.24</v>
       </c>
       <c r="G12">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H12">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I12">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J12">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K12">
         <v>3.45</v>
       </c>
       <c r="L12">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="M12">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N12">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="O12">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="P12">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="Q12">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="R12">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="S12">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="T12">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="U12">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="V12">
         <v>1.35</v>
       </c>
       <c r="W12">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X12">
+        <v>10.5</v>
+      </c>
+      <c r="Y12">
         <v>11.5</v>
-      </c>
-      <c r="Y12">
-        <v>12</v>
       </c>
       <c r="Z12">
         <v>500</v>
@@ -3495,10 +3495,10 @@
         <v>900</v>
       </c>
       <c r="AB12">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC12">
-        <v>7.6</v>
+        <v>13.5</v>
       </c>
       <c r="AD12">
         <v>80</v>
@@ -3507,10 +3507,10 @@
         <v>500</v>
       </c>
       <c r="AF12">
-        <v>65</v>
+        <v>13.5</v>
       </c>
       <c r="AG12">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH12">
         <v>34</v>
@@ -3519,7 +3519,7 @@
         <v>500</v>
       </c>
       <c r="AJ12">
-        <v>65</v>
+        <v>900</v>
       </c>
       <c r="AK12">
         <v>500</v>
@@ -3537,16 +3537,16 @@
         <v>500</v>
       </c>
       <c r="AP12">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AQ12">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR12">
         <v>9.4</v>
       </c>
       <c r="AS12">
-        <v>12.5</v>
+        <v>7</v>
       </c>
       <c r="AT12">
         <v>7.4</v>
@@ -3555,76 +3555,76 @@
         <v>6.8</v>
       </c>
       <c r="AV12">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW12">
+        <v>6.8</v>
+      </c>
+      <c r="AX12">
         <v>11.5</v>
-      </c>
-      <c r="AX12">
-        <v>12</v>
       </c>
       <c r="AY12">
         <v>10</v>
       </c>
       <c r="AZ12">
-        <v>8.6</v>
+        <v>18</v>
       </c>
       <c r="BA12">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="BB12">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="BC12">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD12">
         <v>11</v>
       </c>
       <c r="BE12">
-        <v>13.5</v>
+        <v>7.4</v>
       </c>
       <c r="BF12">
-        <v>20</v>
+        <v>9.4</v>
       </c>
       <c r="BG12">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="BH12">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="BI12">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="BJ12">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK12">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BN12">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO12">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BP12">
         <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT12">
         <v>7</v>
@@ -3636,19 +3636,19 @@
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ12">
         <v>1000</v>
       </c>
       <c r="CA12">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="CB12" t="s">
         <v>133</v>
@@ -3680,7 +3680,7 @@
         <v>4.3</v>
       </c>
       <c r="I13">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J13">
         <v>4</v>
@@ -3689,34 +3689,34 @@
         <v>4.2</v>
       </c>
       <c r="L13">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M13">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N13">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="O13">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P13">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="Q13">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="R13">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="S13">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="T13">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="U13">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V13">
         <v>1.27</v>
@@ -3734,7 +3734,7 @@
         <v>42</v>
       </c>
       <c r="AA13">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB13">
         <v>12</v>
@@ -3755,28 +3755,28 @@
         <v>11.5</v>
       </c>
       <c r="AH13">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI13">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ13">
         <v>23</v>
       </c>
       <c r="AK13">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL13">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM13">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN13">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO13">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AP13">
         <v>15</v>
@@ -3791,10 +3791,10 @@
         <v>1.01</v>
       </c>
       <c r="AT13">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU13">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV13">
         <v>13.5</v>
@@ -3833,22 +3833,22 @@
         <v>1.01</v>
       </c>
       <c r="BH13">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BI13">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BJ13">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK13">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN13">
         <v>4.9</v>
@@ -3863,10 +3863,10 @@
         <v>5.7</v>
       </c>
       <c r="BR13">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS13">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT13">
         <v>8.4</v>
@@ -3878,19 +3878,19 @@
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ13">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="CA13">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="CB13" t="s">
         <v>133</v>
@@ -3913,13 +3913,13 @@
         <v>127</v>
       </c>
       <c r="F14">
+        <v>4</v>
+      </c>
+      <c r="G14">
         <v>4.2</v>
       </c>
-      <c r="G14">
-        <v>4.3</v>
-      </c>
       <c r="H14">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="I14">
         <v>1.88</v>
@@ -3931,64 +3931,64 @@
         <v>4.6</v>
       </c>
       <c r="L14">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M14">
         <v>1.02</v>
       </c>
       <c r="N14">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="O14">
         <v>1.13</v>
       </c>
       <c r="P14">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q14">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="R14">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="S14">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="T14">
         <v>1.45</v>
       </c>
       <c r="U14">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="V14">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="W14">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="X14">
         <v>38</v>
       </c>
       <c r="Y14">
+        <v>18.5</v>
+      </c>
+      <c r="Z14">
         <v>18</v>
-      </c>
-      <c r="Z14">
-        <v>17</v>
       </c>
       <c r="AA14">
         <v>24</v>
       </c>
       <c r="AB14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AC14">
         <v>11.5</v>
       </c>
       <c r="AD14">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE14">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AF14">
         <v>42</v>
@@ -4006,22 +4006,22 @@
         <v>1000</v>
       </c>
       <c r="AK14">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL14">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM14">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AN14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO14">
         <v>6.4</v>
       </c>
       <c r="AP14">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AQ14">
         <v>16</v>
@@ -4030,7 +4030,7 @@
         <v>15</v>
       </c>
       <c r="AS14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT14">
         <v>27</v>
@@ -4054,13 +4054,13 @@
         <v>13</v>
       </c>
       <c r="BA14">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BB14">
         <v>36</v>
       </c>
       <c r="BC14">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BD14">
         <v>30</v>
@@ -4072,43 +4072,43 @@
         <v>19.5</v>
       </c>
       <c r="BG14">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BH14">
         <v>5.4</v>
       </c>
       <c r="BI14">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BJ14">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK14">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL14">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BM14">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BN14">
         <v>8.4</v>
       </c>
       <c r="BO14">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP14">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BQ14">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR14">
         <v>28</v>
       </c>
       <c r="BS14">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BT14">
         <v>5.6</v>
@@ -4120,19 +4120,19 @@
         <v>12</v>
       </c>
       <c r="BW14">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BX14">
         <v>18.5</v>
       </c>
       <c r="BY14">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BZ14">
         <v>11.5</v>
       </c>
       <c r="CA14">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="CB14" t="s">
         <v>133</v>
@@ -4158,13 +4158,13 @@
         <v>2.24</v>
       </c>
       <c r="G15">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H15">
         <v>3.75</v>
       </c>
       <c r="I15">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J15">
         <v>3.35</v>
@@ -4173,43 +4173,43 @@
         <v>3.45</v>
       </c>
       <c r="L15">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M15">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N15">
         <v>3.2</v>
       </c>
       <c r="O15">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="P15">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="Q15">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R15">
         <v>1.27</v>
       </c>
       <c r="S15">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T15">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U15">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V15">
         <v>1.35</v>
       </c>
       <c r="W15">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X15">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y15">
         <v>12</v>
@@ -4221,7 +4221,7 @@
         <v>90</v>
       </c>
       <c r="AB15">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC15">
         <v>8.6</v>
@@ -4233,7 +4233,7 @@
         <v>65</v>
       </c>
       <c r="AF15">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG15">
         <v>11.5</v>
@@ -4263,19 +4263,19 @@
         <v>70</v>
       </c>
       <c r="AP15">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AQ15">
         <v>10.5</v>
       </c>
       <c r="AR15">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS15">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT15">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AU15">
         <v>6.8</v>
@@ -4284,58 +4284,58 @@
         <v>14</v>
       </c>
       <c r="AW15">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX15">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY15">
         <v>10</v>
       </c>
       <c r="AZ15">
-        <v>6.4</v>
+        <v>18</v>
       </c>
       <c r="BA15">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB15">
-        <v>7.2</v>
+        <v>24</v>
       </c>
       <c r="BC15">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BD15">
-        <v>7.6</v>
+        <v>38</v>
       </c>
       <c r="BE15">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BF15">
         <v>20</v>
       </c>
       <c r="BG15">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BH15">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="BI15">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="BJ15">
         <v>10.5</v>
       </c>
       <c r="BK15">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BN15">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO15">
         <v>4.5</v>
@@ -4344,13 +4344,13 @@
         <v>25</v>
       </c>
       <c r="BQ15">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR15">
         <v>44</v>
       </c>
       <c r="BS15">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BT15">
         <v>6.8</v>
@@ -4359,22 +4359,22 @@
         <v>6</v>
       </c>
       <c r="BV15">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW15">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BX15">
         <v>65</v>
       </c>
       <c r="BY15">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BZ15">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="CA15">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="CB15" t="s">
         <v>133</v>
@@ -4397,22 +4397,22 @@
         <v>129</v>
       </c>
       <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16">
         <v>2.04</v>
       </c>
-      <c r="G16">
-        <v>2.08</v>
-      </c>
       <c r="H16">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I16">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J16">
         <v>3.8</v>
       </c>
       <c r="K16">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L16">
         <v>1.38</v>
@@ -4424,16 +4424,16 @@
         <v>4.3</v>
       </c>
       <c r="O16">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P16">
         <v>2.1</v>
       </c>
       <c r="Q16">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R16">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S16">
         <v>3.2</v>
@@ -4442,13 +4442,13 @@
         <v>1.75</v>
       </c>
       <c r="U16">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="V16">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W16">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="X16">
         <v>17</v>
@@ -4469,19 +4469,19 @@
         <v>8.6</v>
       </c>
       <c r="AD16">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE16">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF16">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG16">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH16">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI16">
         <v>55</v>
@@ -4493,7 +4493,7 @@
         <v>21</v>
       </c>
       <c r="AL16">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AM16">
         <v>1000</v>
@@ -4505,7 +4505,7 @@
         <v>44</v>
       </c>
       <c r="AP16">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ16">
         <v>14.5</v>
@@ -4517,7 +4517,7 @@
         <v>34</v>
       </c>
       <c r="AT16">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AU16">
         <v>7.8</v>
@@ -4526,10 +4526,10 @@
         <v>14.5</v>
       </c>
       <c r="AW16">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="AX16">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY16">
         <v>9.6</v>
@@ -4556,7 +4556,7 @@
         <v>12</v>
       </c>
       <c r="BG16">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH16">
         <v>3.75</v>
@@ -4568,22 +4568,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK16">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN16">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO16">
         <v>3.8</v>
       </c>
       <c r="BP16">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BQ16">
         <v>6.2</v>
@@ -4592,31 +4592,31 @@
         <v>28</v>
       </c>
       <c r="BS16">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BT16">
         <v>7.6</v>
       </c>
       <c r="BU16">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV16">
         <v>32</v>
       </c>
       <c r="BW16">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BX16">
         <v>42</v>
       </c>
       <c r="BY16">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ16">
         <v>23</v>
       </c>
       <c r="CA16">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="CB16" t="s">
         <v>133</v>
@@ -4639,13 +4639,13 @@
         <v>130</v>
       </c>
       <c r="F17">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="G17">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H17">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I17">
         <v>4.2</v>
@@ -4663,34 +4663,34 @@
         <v>1.05</v>
       </c>
       <c r="N17">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O17">
         <v>1.26</v>
       </c>
       <c r="P17">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q17">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="R17">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S17">
         <v>3.05</v>
       </c>
       <c r="T17">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="U17">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V17">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W17">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X17">
         <v>17.5</v>
@@ -4732,7 +4732,7 @@
         <v>24</v>
       </c>
       <c r="AK17">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL17">
         <v>32</v>
@@ -4780,7 +4780,7 @@
         <v>15.5</v>
       </c>
       <c r="BA17">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BB17">
         <v>20</v>
@@ -4795,16 +4795,16 @@
         <v>60</v>
       </c>
       <c r="BF17">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BG17">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BH17">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BI17">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BJ17">
         <v>9.6</v>
@@ -4816,7 +4816,7 @@
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BN17">
         <v>5.1</v>
@@ -4831,7 +4831,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BR17">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BS17">
         <v>7.4</v>
@@ -4840,10 +4840,10 @@
         <v>7.8</v>
       </c>
       <c r="BU17">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV17">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BW17">
         <v>7.8</v>
@@ -4852,13 +4852,13 @@
         <v>40</v>
       </c>
       <c r="BY17">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ17">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CA17">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB17" t="s">
         <v>133</v>
@@ -4881,19 +4881,19 @@
         <v>131</v>
       </c>
       <c r="F18">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="G18">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="H18">
+        <v>4.5</v>
+      </c>
+      <c r="I18">
         <v>4.6</v>
       </c>
-      <c r="I18">
-        <v>4.8</v>
-      </c>
       <c r="J18">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K18">
         <v>4.6</v>
@@ -4905,19 +4905,19 @@
         <v>1.03</v>
       </c>
       <c r="N18">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O18">
         <v>1.17</v>
       </c>
       <c r="P18">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="Q18">
         <v>1.53</v>
       </c>
       <c r="R18">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="S18">
         <v>2.32</v>
@@ -4926,10 +4926,10 @@
         <v>1.57</v>
       </c>
       <c r="U18">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="V18">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W18">
         <v>2.28</v>
@@ -4938,13 +4938,13 @@
         <v>28</v>
       </c>
       <c r="Y18">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Z18">
         <v>42</v>
       </c>
       <c r="AA18">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB18">
         <v>14</v>
@@ -4953,7 +4953,7 @@
         <v>11</v>
       </c>
       <c r="AD18">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE18">
         <v>48</v>
@@ -4965,13 +4965,13 @@
         <v>10.5</v>
       </c>
       <c r="AH18">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI18">
         <v>44</v>
       </c>
       <c r="AJ18">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AK18">
         <v>16</v>
@@ -4989,7 +4989,7 @@
         <v>34</v>
       </c>
       <c r="AP18">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ18">
         <v>22</v>
@@ -5007,16 +5007,16 @@
         <v>10</v>
       </c>
       <c r="AV18">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AW18">
         <v>36</v>
       </c>
       <c r="AX18">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY18">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ18">
         <v>14.5</v>
@@ -5025,10 +5025,10 @@
         <v>38</v>
       </c>
       <c r="BB18">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC18">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD18">
         <v>21</v>
@@ -5037,28 +5037,28 @@
         <v>50</v>
       </c>
       <c r="BF18">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG18">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BH18">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI18">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BJ18">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BK18">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN18">
         <v>4.9</v>
@@ -5070,13 +5070,13 @@
         <v>11</v>
       </c>
       <c r="BQ18">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR18">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BS18">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT18">
         <v>8.6</v>
@@ -5088,7 +5088,7 @@
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX18">
         <v>34</v>
@@ -5100,7 +5100,7 @@
         <v>12.5</v>
       </c>
       <c r="CA18">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB18" t="s">
         <v>133</v>
@@ -5123,16 +5123,16 @@
         <v>132</v>
       </c>
       <c r="F19">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G19">
         <v>2.24</v>
       </c>
       <c r="H19">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I19">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J19">
         <v>4.3</v>
@@ -5156,13 +5156,13 @@
         <v>3.5</v>
       </c>
       <c r="Q19">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="R19">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S19">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="T19">
         <v>1.39</v>
@@ -5180,13 +5180,13 @@
         <v>38</v>
       </c>
       <c r="Y19">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z19">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AA19">
-        <v>230</v>
+        <v>55</v>
       </c>
       <c r="AB19">
         <v>23</v>
@@ -5195,7 +5195,7 @@
         <v>11.5</v>
       </c>
       <c r="AD19">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE19">
         <v>28</v>
@@ -5204,7 +5204,7 @@
         <v>23</v>
       </c>
       <c r="AG19">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH19">
         <v>13.5</v>
@@ -5213,7 +5213,7 @@
         <v>28</v>
       </c>
       <c r="AJ19">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK19">
         <v>19</v>
@@ -5225,7 +5225,7 @@
         <v>40</v>
       </c>
       <c r="AN19">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AO19">
         <v>13</v>
@@ -5252,13 +5252,13 @@
         <v>13.5</v>
       </c>
       <c r="AW19">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX19">
         <v>20</v>
       </c>
       <c r="AY19">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ19">
         <v>12</v>
@@ -5282,7 +5282,7 @@
         <v>7</v>
       </c>
       <c r="BG19">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BH19">
         <v>5.7</v>
@@ -5306,7 +5306,7 @@
         <v>6.2</v>
       </c>
       <c r="BO19">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BP19">
         <v>14</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
@@ -415,7 +415,7 @@
     <t>Chicago Fire</t>
   </si>
   <si>
-    <t>2026-07-22 04:17:51</t>
+    <t>2026-07-22 06:25:20</t>
   </si>
 </sst>
 </file>
@@ -1009,226 +1009,226 @@
         <v>115</v>
       </c>
       <c r="F2">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="G2">
         <v>3.25</v>
       </c>
       <c r="H2">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="I2">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="J2">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K2">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="L2">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="M2">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N2">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="O2">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="P2">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="Q2">
-        <v>2.48</v>
+        <v>2.14</v>
       </c>
       <c r="R2">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="S2">
-        <v>5</v>
+        <v>3.95</v>
       </c>
       <c r="T2">
+        <v>1.73</v>
+      </c>
+      <c r="U2">
         <v>1.99</v>
-      </c>
-      <c r="U2">
-        <v>1.94</v>
       </c>
       <c r="V2">
         <v>1.58</v>
       </c>
       <c r="W2">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X2">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="Y2">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="Z2">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AA2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AB2">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AC2">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AD2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE2">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AF2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AG2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AI2">
+        <v>50</v>
+      </c>
+      <c r="AJ2">
         <v>55</v>
       </c>
-      <c r="AJ2">
-        <v>60</v>
-      </c>
       <c r="AK2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AL2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM2">
-        <v>580</v>
+        <v>110</v>
       </c>
       <c r="AN2">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AO2">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AP2">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AQ2">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR2">
         <v>14.5</v>
       </c>
       <c r="AS2">
+        <v>32</v>
+      </c>
+      <c r="AT2">
+        <v>10.5</v>
+      </c>
+      <c r="AU2">
+        <v>6.6</v>
+      </c>
+      <c r="AV2">
+        <v>10.5</v>
+      </c>
+      <c r="AW2">
+        <v>26</v>
+      </c>
+      <c r="AX2">
+        <v>18.5</v>
+      </c>
+      <c r="AY2">
+        <v>12</v>
+      </c>
+      <c r="AZ2">
+        <v>13.5</v>
+      </c>
+      <c r="BA2">
         <v>29</v>
       </c>
-      <c r="AT2">
-        <v>9</v>
-      </c>
-      <c r="AU2">
-        <v>6.4</v>
-      </c>
-      <c r="AV2">
-        <v>11</v>
-      </c>
-      <c r="AW2">
-        <v>32</v>
-      </c>
-      <c r="AX2">
-        <v>17</v>
-      </c>
-      <c r="AY2">
-        <v>12.5</v>
-      </c>
-      <c r="AZ2">
-        <v>18</v>
-      </c>
-      <c r="BA2">
-        <v>28</v>
-      </c>
       <c r="BB2">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="BC2">
         <v>32</v>
       </c>
       <c r="BD2">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BE2">
-        <v>16.5</v>
+        <v>55</v>
       </c>
       <c r="BF2">
-        <v>13.5</v>
+        <v>30</v>
       </c>
       <c r="BG2">
-        <v>32</v>
+        <v>8.6</v>
       </c>
       <c r="BH2">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="BI2">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="BJ2">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="BN2">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="BO2">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP2">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>12.5</v>
+        <v>3.25</v>
       </c>
       <c r="BR2">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>15.5</v>
+        <v>3.25</v>
       </c>
       <c r="BT2">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BU2">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BV2">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>11.5</v>
+        <v>3.25</v>
       </c>
       <c r="BX2">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>15</v>
+        <v>3.25</v>
       </c>
       <c r="BZ2">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>15</v>
+        <v>3.25</v>
       </c>
       <c r="CB2" t="s">
         <v>133</v>
@@ -1251,130 +1251,130 @@
         <v>116</v>
       </c>
       <c r="F3">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="G3">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="I3">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="J3">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K3">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="L3">
         <v>1.51</v>
       </c>
       <c r="M3">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N3">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O3">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P3">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q3">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="R3">
+        <v>1.3</v>
+      </c>
+      <c r="S3">
+        <v>4.2</v>
+      </c>
+      <c r="T3">
+        <v>1.95</v>
+      </c>
+      <c r="U3">
+        <v>1.97</v>
+      </c>
+      <c r="V3">
+        <v>1.9</v>
+      </c>
+      <c r="W3">
         <v>1.29</v>
       </c>
-      <c r="S3">
-        <v>4.4</v>
-      </c>
-      <c r="T3">
-        <v>2</v>
-      </c>
-      <c r="U3">
-        <v>1.93</v>
-      </c>
-      <c r="V3">
-        <v>1.98</v>
-      </c>
-      <c r="W3">
-        <v>1.27</v>
-      </c>
       <c r="X3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y3">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z3">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AA3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AB3">
         <v>13.5</v>
       </c>
       <c r="AC3">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AE3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AF3">
         <v>32</v>
       </c>
       <c r="AG3">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AH3">
         <v>21</v>
       </c>
       <c r="AI3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ3">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AK3">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AL3">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AM3">
-        <v>140</v>
+        <v>440</v>
       </c>
       <c r="AN3">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AO3">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AP3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ3">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AR3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AT3">
         <v>12.5</v>
       </c>
       <c r="AU3">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV3">
         <v>9.800000000000001</v>
@@ -1383,94 +1383,94 @@
         <v>21</v>
       </c>
       <c r="AX3">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AY3">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AZ3">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BA3">
         <v>40</v>
       </c>
       <c r="BB3">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="BC3">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BD3">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="BE3">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="BF3">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="BG3">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BH3">
         <v>3</v>
       </c>
       <c r="BI3">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BJ3">
+        <v>970</v>
+      </c>
+      <c r="BK3">
+        <v>8.4</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>130</v>
+      </c>
+      <c r="BN3">
         <v>10.5</v>
       </c>
-      <c r="BK3">
-        <v>9.4</v>
-      </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>19</v>
-      </c>
-      <c r="BN3">
-        <v>7.6</v>
-      </c>
       <c r="BO3">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BP3">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>14</v>
+        <v>3.7</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>15.5</v>
+        <v>3.6</v>
       </c>
       <c r="BT3">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BU3">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BV3">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX3">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>13</v>
+        <v>3.6</v>
       </c>
       <c r="BZ3">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>12.5</v>
+        <v>3.7</v>
       </c>
       <c r="CB3" t="s">
         <v>133</v>
@@ -1493,67 +1493,67 @@
         <v>117</v>
       </c>
       <c r="F4">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="G4">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="H4">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="I4">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="J4">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K4">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L4">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="M4">
         <v>1.1</v>
       </c>
       <c r="N4">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O4">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P4">
         <v>1.72</v>
       </c>
       <c r="Q4">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R4">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S4">
         <v>4.5</v>
       </c>
       <c r="T4">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U4">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="V4">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="W4">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="X4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y4">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="Z4">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AA4">
         <v>690</v>
@@ -1565,154 +1565,154 @@
         <v>7.8</v>
       </c>
       <c r="AD4">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AE4">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AF4">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AG4">
         <v>10.5</v>
       </c>
       <c r="AH4">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AI4">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="AJ4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK4">
         <v>23</v>
       </c>
       <c r="AL4">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AM4">
         <v>570</v>
       </c>
       <c r="AN4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO4">
-        <v>110</v>
+        <v>180</v>
       </c>
       <c r="AP4">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR4">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AS4">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AT4">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AU4">
         <v>7.2</v>
       </c>
       <c r="AV4">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW4">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="AX4">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AY4">
         <v>9.6</v>
       </c>
       <c r="AZ4">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BA4">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BB4">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC4">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BD4">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BE4">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="BF4">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BG4">
         <v>42</v>
       </c>
       <c r="BH4">
-        <v>2.98</v>
+        <v>2.86</v>
       </c>
       <c r="BI4">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="BJ4">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>7.4</v>
+        <v>3.15</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>18.5</v>
+        <v>140</v>
       </c>
       <c r="BN4">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BO4">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="BP4">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>9.6</v>
+        <v>3.3</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>12</v>
+        <v>3.6</v>
       </c>
       <c r="BT4">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>13.5</v>
+        <v>3.6</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>14.5</v>
+        <v>3.6</v>
       </c>
       <c r="BZ4">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>11.5</v>
+        <v>3.6</v>
       </c>
       <c r="CB4" t="s">
         <v>133</v>
@@ -1735,25 +1735,25 @@
         <v>118</v>
       </c>
       <c r="F5">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G5">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H5">
+        <v>2.24</v>
+      </c>
+      <c r="I5">
         <v>2.26</v>
-      </c>
-      <c r="I5">
-        <v>2.3</v>
       </c>
       <c r="J5">
         <v>3.9</v>
       </c>
       <c r="K5">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M5">
         <v>1.04</v>
@@ -1771,37 +1771,37 @@
         <v>1.6</v>
       </c>
       <c r="R5">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S5">
         <v>2.48</v>
       </c>
       <c r="T5">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="U5">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="V5">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="W5">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X5">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Y5">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z5">
         <v>17.5</v>
       </c>
       <c r="AA5">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AB5">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC5">
         <v>9.4</v>
@@ -1810,13 +1810,13 @@
         <v>11.5</v>
       </c>
       <c r="AE5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF5">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AG5">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH5">
         <v>14</v>
@@ -1825,34 +1825,34 @@
         <v>27</v>
       </c>
       <c r="AJ5">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="AK5">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="AL5">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="AM5">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AN5">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AO5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AP5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ5">
         <v>14</v>
       </c>
       <c r="AR5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AS5">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AT5">
         <v>17.5</v>
@@ -1861,10 +1861,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW5">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AX5">
         <v>24</v>
@@ -1879,82 +1879,82 @@
         <v>24</v>
       </c>
       <c r="BB5">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BC5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD5">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BE5">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="BF5">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BG5">
         <v>10.5</v>
       </c>
       <c r="BH5">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BK5">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL5">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BM5">
-        <v>13</v>
+        <v>1.04</v>
       </c>
       <c r="BN5">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BP5">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BR5">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BT5">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV5">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX5">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="CA5">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="s">
         <v>133</v>
@@ -1986,25 +1986,25 @@
         <v>27</v>
       </c>
       <c r="I6">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K6">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="L6">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="M6">
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="O6">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="P6">
         <v>4.6</v>
@@ -2013,109 +2013,109 @@
         <v>1.27</v>
       </c>
       <c r="R6">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="S6">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="T6">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U6">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="V6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="X6">
-        <v>490</v>
+        <v>200</v>
       </c>
       <c r="Y6">
         <v>940</v>
       </c>
       <c r="Z6">
-        <v>370</v>
+        <v>1000</v>
       </c>
       <c r="AA6">
         <v>1000</v>
       </c>
       <c r="AB6">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AC6">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AD6">
-        <v>940</v>
+        <v>920</v>
       </c>
       <c r="AE6">
-        <v>410</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG6">
+        <v>19.5</v>
+      </c>
+      <c r="AH6">
+        <v>120</v>
+      </c>
+      <c r="AI6">
+        <v>1000</v>
+      </c>
+      <c r="AJ6">
+        <v>10</v>
+      </c>
+      <c r="AK6">
         <v>15.5</v>
       </c>
-      <c r="AH6">
-        <v>48</v>
-      </c>
-      <c r="AI6">
-        <v>1000</v>
-      </c>
-      <c r="AJ6">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AK6">
-        <v>14.5</v>
-      </c>
       <c r="AL6">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AM6">
         <v>490</v>
       </c>
       <c r="AN6">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AO6">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AQ6">
+        <v>50</v>
+      </c>
+      <c r="AR6">
+        <v>40</v>
+      </c>
+      <c r="AS6">
         <v>60</v>
       </c>
-      <c r="AR6">
-        <v>75</v>
-      </c>
-      <c r="AS6">
-        <v>90</v>
-      </c>
       <c r="AT6">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AU6">
         <v>22</v>
       </c>
       <c r="AV6">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AW6">
         <v>55</v>
       </c>
       <c r="AX6">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY6">
         <v>13.5</v>
       </c>
       <c r="AZ6">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="BA6">
         <v>48</v>
@@ -2133,70 +2133,70 @@
         <v>70</v>
       </c>
       <c r="BF6">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="BG6">
         <v>55</v>
       </c>
       <c r="BH6">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>6</v>
+        <v>1.21</v>
       </c>
       <c r="BJ6">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>7</v>
+        <v>1.21</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>12.5</v>
+        <v>1.21</v>
       </c>
       <c r="BN6">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>3.8</v>
+        <v>1.21</v>
       </c>
       <c r="BP6">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>5.1</v>
+        <v>1.21</v>
       </c>
       <c r="BR6">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>8</v>
+        <v>1.21</v>
       </c>
       <c r="BT6">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>9.199999999999999</v>
+        <v>1.21</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>12.5</v>
+        <v>1.21</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>12</v>
+        <v>1.21</v>
       </c>
       <c r="BZ6">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="s">
         <v>133</v>
@@ -2219,7 +2219,7 @@
         <v>120</v>
       </c>
       <c r="F7">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G7">
         <v>2.4</v>
@@ -2228,217 +2228,217 @@
         <v>3.85</v>
       </c>
       <c r="I7">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="K7">
         <v>3.2</v>
       </c>
       <c r="L7">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="M7">
         <v>1.13</v>
       </c>
       <c r="N7">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="O7">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="P7">
         <v>1.55</v>
       </c>
       <c r="Q7">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="R7">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S7">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="T7">
-        <v>2.14</v>
+        <v>1.77</v>
       </c>
       <c r="U7">
-        <v>1.75</v>
+        <v>1.37</v>
       </c>
       <c r="V7">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W7">
         <v>1.71</v>
       </c>
       <c r="X7">
-        <v>8.6</v>
+        <v>970</v>
       </c>
       <c r="Y7">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="Z7">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AA7">
+        <v>900</v>
+      </c>
+      <c r="AB7">
+        <v>970</v>
+      </c>
+      <c r="AC7">
+        <v>42</v>
+      </c>
+      <c r="AD7">
+        <v>970</v>
+      </c>
+      <c r="AE7">
         <v>500</v>
       </c>
-      <c r="AB7">
-        <v>7.2</v>
-      </c>
-      <c r="AC7">
-        <v>7.6</v>
-      </c>
-      <c r="AD7">
-        <v>18</v>
-      </c>
-      <c r="AE7">
-        <v>100</v>
-      </c>
       <c r="AF7">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AG7">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AH7">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="AI7">
-        <v>380</v>
+        <v>500</v>
       </c>
       <c r="AJ7">
-        <v>38</v>
+        <v>900</v>
       </c>
       <c r="AK7">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AL7">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AM7">
         <v>500</v>
       </c>
       <c r="AN7">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AO7">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AP7">
-        <v>7.6</v>
+        <v>4.9</v>
       </c>
       <c r="AQ7">
-        <v>9.6</v>
+        <v>5.6</v>
       </c>
       <c r="AR7">
-        <v>20</v>
+        <v>2.04</v>
       </c>
       <c r="AS7">
-        <v>60</v>
+        <v>1.98</v>
       </c>
       <c r="AT7">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="AU7">
+        <v>4.2</v>
+      </c>
+      <c r="AV7">
+        <v>2</v>
+      </c>
+      <c r="AW7">
+        <v>1.97</v>
+      </c>
+      <c r="AX7">
+        <v>6.2</v>
+      </c>
+      <c r="AY7">
         <v>6.4</v>
       </c>
-      <c r="AV7">
-        <v>15</v>
-      </c>
-      <c r="AW7">
-        <v>42</v>
-      </c>
-      <c r="AX7">
-        <v>10.5</v>
-      </c>
-      <c r="AY7">
-        <v>10</v>
-      </c>
       <c r="AZ7">
-        <v>20</v>
+        <v>2.06</v>
       </c>
       <c r="BA7">
-        <v>55</v>
+        <v>1.98</v>
       </c>
       <c r="BB7">
-        <v>23</v>
+        <v>2.1</v>
       </c>
       <c r="BC7">
-        <v>23</v>
+        <v>2.06</v>
       </c>
       <c r="BD7">
-        <v>40</v>
+        <v>1.97</v>
       </c>
       <c r="BE7">
-        <v>28</v>
+        <v>1.99</v>
       </c>
       <c r="BF7">
-        <v>27</v>
+        <v>1.97</v>
       </c>
       <c r="BG7">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="BH7">
-        <v>2.68</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>2.44</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN7">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP7">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR7">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BT7">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="s">
         <v>133</v>
@@ -2461,46 +2461,46 @@
         <v>121</v>
       </c>
       <c r="F8">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="G8">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="H8">
-        <v>1.72</v>
+        <v>2.12</v>
       </c>
       <c r="I8">
-        <v>12.5</v>
+        <v>6</v>
       </c>
       <c r="J8">
         <v>2.7</v>
       </c>
       <c r="K8">
-        <v>5.2</v>
+        <v>3.6</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N8">
-        <v>1.12</v>
+        <v>1.51</v>
       </c>
       <c r="O8">
+        <v>1.46</v>
+      </c>
+      <c r="P8">
+        <v>1.47</v>
+      </c>
+      <c r="Q8">
         <v>1.02</v>
       </c>
-      <c r="P8">
-        <v>1.12</v>
-      </c>
-      <c r="Q8">
-        <v>1.01</v>
-      </c>
       <c r="R8">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="S8">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="T8">
         <v>1.11</v>
@@ -2509,13 +2509,13 @@
         <v>1.11</v>
       </c>
       <c r="V8">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="W8">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="X8">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="Y8">
         <v>950</v>
@@ -2563,64 +2563,64 @@
         <v>500</v>
       </c>
       <c r="AN8">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO8">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP8">
-        <v>1.05</v>
+        <v>1.29</v>
       </c>
       <c r="AQ8">
-        <v>1.05</v>
+        <v>1.32</v>
       </c>
       <c r="AR8">
-        <v>1.05</v>
+        <v>1.39</v>
       </c>
       <c r="AS8">
-        <v>1.05</v>
+        <v>1.4</v>
       </c>
       <c r="AT8">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="AU8">
-        <v>1.03</v>
+        <v>1.36</v>
       </c>
       <c r="AV8">
-        <v>1.05</v>
+        <v>1.38</v>
       </c>
       <c r="AW8">
-        <v>1.05</v>
+        <v>1.4</v>
       </c>
       <c r="AX8">
-        <v>1.05</v>
+        <v>1.38</v>
       </c>
       <c r="AY8">
-        <v>1.05</v>
+        <v>1.35</v>
       </c>
       <c r="AZ8">
-        <v>1.05</v>
+        <v>1.38</v>
       </c>
       <c r="BA8">
-        <v>1.05</v>
+        <v>1.4</v>
       </c>
       <c r="BB8">
-        <v>1.05</v>
+        <v>1.4</v>
       </c>
       <c r="BC8">
-        <v>1.05</v>
+        <v>1.38</v>
       </c>
       <c r="BD8">
-        <v>1.05</v>
+        <v>1.4</v>
       </c>
       <c r="BE8">
-        <v>1.05</v>
+        <v>1.41</v>
       </c>
       <c r="BF8">
         <v>1.55</v>
       </c>
       <c r="BG8">
-        <v>1.05</v>
+        <v>1.56</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2706,22 +2706,22 @@
         <v>1.23</v>
       </c>
       <c r="G9">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="H9">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I9">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J9">
         <v>7.2</v>
       </c>
       <c r="K9">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L9">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M9">
         <v>1.03</v>
@@ -2730,22 +2730,22 @@
         <v>5.2</v>
       </c>
       <c r="O9">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P9">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="Q9">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R9">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="S9">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="T9">
-        <v>2.32</v>
+        <v>1.98</v>
       </c>
       <c r="U9">
         <v>1.64</v>
@@ -2757,172 +2757,172 @@
         <v>5</v>
       </c>
       <c r="X9">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Y9">
-        <v>380</v>
+        <v>950</v>
       </c>
       <c r="Z9">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AA9">
         <v>1000</v>
       </c>
       <c r="AB9">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC9">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AD9">
-        <v>510</v>
+        <v>950</v>
       </c>
       <c r="AE9">
-        <v>410</v>
+        <v>1000</v>
       </c>
       <c r="AF9">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AG9">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH9">
-        <v>44</v>
+        <v>950</v>
       </c>
       <c r="AI9">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AK9">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AL9">
-        <v>50</v>
+        <v>330</v>
       </c>
       <c r="AM9">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
-        <v>4.6</v>
+        <v>29</v>
       </c>
       <c r="AO9">
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>20</v>
+        <v>1.13</v>
       </c>
       <c r="AQ9">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="AR9">
-        <v>8.4</v>
+        <v>4.2</v>
       </c>
       <c r="AS9">
-        <v>8.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="AT9">
-        <v>7.2</v>
+        <v>1.13</v>
       </c>
       <c r="AU9">
-        <v>13.5</v>
+        <v>1.13</v>
       </c>
       <c r="AV9">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="AW9">
-        <v>8.6</v>
+        <v>4.2</v>
       </c>
       <c r="AX9">
-        <v>6.2</v>
+        <v>1.13</v>
       </c>
       <c r="AY9">
-        <v>10</v>
+        <v>1.13</v>
       </c>
       <c r="AZ9">
-        <v>7.2</v>
+        <v>1.13</v>
       </c>
       <c r="BA9">
-        <v>8.4</v>
+        <v>4.2</v>
       </c>
       <c r="BB9">
-        <v>7.8</v>
+        <v>4.9</v>
       </c>
       <c r="BC9">
-        <v>12.5</v>
+        <v>1.13</v>
       </c>
       <c r="BD9">
-        <v>7.4</v>
+        <v>1.13</v>
       </c>
       <c r="BE9">
-        <v>8.4</v>
+        <v>1.13</v>
       </c>
       <c r="BF9">
-        <v>3.95</v>
+        <v>1.05</v>
       </c>
       <c r="BG9">
-        <v>8.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="BH9">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>2.38</v>
+        <v>1.04</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>2.8</v>
+        <v>1.04</v>
       </c>
       <c r="BN9">
         <v>1000</v>
       </c>
       <c r="BO9">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP9">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR9">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>2.56</v>
+        <v>1.04</v>
       </c>
       <c r="BT9">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>2.46</v>
+        <v>1.04</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>2.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>2.78</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="s">
         <v>133</v>
@@ -2945,76 +2945,76 @@
         <v>123</v>
       </c>
       <c r="F10">
+        <v>1.39</v>
+      </c>
+      <c r="G10">
+        <v>1.4</v>
+      </c>
+      <c r="H10">
+        <v>10.5</v>
+      </c>
+      <c r="I10">
+        <v>12</v>
+      </c>
+      <c r="J10">
+        <v>5.2</v>
+      </c>
+      <c r="K10">
+        <v>5.3</v>
+      </c>
+      <c r="L10">
         <v>1.41</v>
-      </c>
-      <c r="G10">
-        <v>1.42</v>
-      </c>
-      <c r="H10">
-        <v>10</v>
-      </c>
-      <c r="I10">
-        <v>11.5</v>
-      </c>
-      <c r="J10">
-        <v>5</v>
-      </c>
-      <c r="K10">
-        <v>5.1</v>
-      </c>
-      <c r="L10">
-        <v>1.42</v>
       </c>
       <c r="M10">
         <v>1.07</v>
       </c>
       <c r="N10">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="O10">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="P10">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="Q10">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="R10">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S10">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="T10">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="U10">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="V10">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W10">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="X10">
-        <v>15.5</v>
+        <v>26</v>
       </c>
       <c r="Y10">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="Z10">
-        <v>540</v>
+        <v>110</v>
       </c>
       <c r="AA10">
-        <v>550</v>
+        <v>520</v>
       </c>
       <c r="AB10">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC10">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="AD10">
         <v>95</v>
@@ -3023,148 +3023,148 @@
         <v>250</v>
       </c>
       <c r="AF10">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AG10">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="AH10">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="AI10">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="AJ10">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AK10">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL10">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="AM10">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="AN10">
+        <v>8</v>
+      </c>
+      <c r="AO10">
+        <v>380</v>
+      </c>
+      <c r="AP10">
+        <v>6.4</v>
+      </c>
+      <c r="AQ10">
+        <v>24</v>
+      </c>
+      <c r="AR10">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS10">
+        <v>6</v>
+      </c>
+      <c r="AT10">
+        <v>6.2</v>
+      </c>
+      <c r="AU10">
+        <v>10</v>
+      </c>
+      <c r="AV10">
+        <v>34</v>
+      </c>
+      <c r="AW10">
         <v>8.4</v>
-      </c>
-      <c r="AO10">
-        <v>430</v>
-      </c>
-      <c r="AP10">
-        <v>12</v>
-      </c>
-      <c r="AQ10">
-        <v>11.5</v>
-      </c>
-      <c r="AR10">
-        <v>9.6</v>
-      </c>
-      <c r="AS10">
-        <v>10.5</v>
-      </c>
-      <c r="AT10">
-        <v>5.9</v>
-      </c>
-      <c r="AU10">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV10">
-        <v>32</v>
-      </c>
-      <c r="AW10">
-        <v>10</v>
       </c>
       <c r="AX10">
         <v>6.6</v>
       </c>
       <c r="AY10">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ10">
-        <v>14.5</v>
+        <v>28</v>
       </c>
       <c r="BA10">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="BB10">
-        <v>10</v>
+        <v>5.8</v>
       </c>
       <c r="BC10">
         <v>14.5</v>
       </c>
       <c r="BD10">
-        <v>8.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="BE10">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BF10">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BG10">
-        <v>15</v>
+        <v>8.6</v>
       </c>
       <c r="BH10">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>2.78</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN10">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP10">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BR10">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BT10">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="s">
         <v>133</v>
@@ -3187,22 +3187,22 @@
         <v>124</v>
       </c>
       <c r="F11">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="G11">
         <v>5</v>
       </c>
       <c r="H11">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="I11">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="J11">
+        <v>3.45</v>
+      </c>
+      <c r="K11">
         <v>3.5</v>
-      </c>
-      <c r="K11">
-        <v>3.55</v>
       </c>
       <c r="L11">
         <v>1.49</v>
@@ -3217,25 +3217,25 @@
         <v>1.42</v>
       </c>
       <c r="P11">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q11">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R11">
         <v>1.27</v>
       </c>
       <c r="S11">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T11">
+        <v>2</v>
+      </c>
+      <c r="U11">
+        <v>1.86</v>
+      </c>
+      <c r="V11">
         <v>2.02</v>
-      </c>
-      <c r="U11">
-        <v>1.92</v>
-      </c>
-      <c r="V11">
-        <v>2.04</v>
       </c>
       <c r="W11">
         <v>1.25</v>
@@ -3244,7 +3244,7 @@
         <v>11</v>
       </c>
       <c r="Y11">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Z11">
         <v>10.5</v>
@@ -3253,25 +3253,25 @@
         <v>23</v>
       </c>
       <c r="AB11">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC11">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD11">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE11">
         <v>23</v>
       </c>
       <c r="AF11">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AG11">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI11">
         <v>46</v>
@@ -3289,10 +3289,10 @@
         <v>440</v>
       </c>
       <c r="AN11">
-        <v>95</v>
+        <v>490</v>
       </c>
       <c r="AO11">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="AP11">
         <v>10</v>
@@ -3301,31 +3301,31 @@
         <v>7.2</v>
       </c>
       <c r="AR11">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS11">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AT11">
         <v>13</v>
       </c>
       <c r="AU11">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV11">
         <v>9.800000000000001</v>
       </c>
       <c r="AW11">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AX11">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AY11">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AZ11">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BA11">
         <v>40</v>
@@ -3334,79 +3334,79 @@
         <v>48</v>
       </c>
       <c r="BC11">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BD11">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="BE11">
         <v>70</v>
       </c>
       <c r="BF11">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="BG11">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BH11">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>2.64</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>17.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN11">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BP11">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR11">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>14.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT11">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="BV11">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BX11">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="s">
         <v>133</v>
@@ -3435,7 +3435,7 @@
         <v>2.3</v>
       </c>
       <c r="H12">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I12">
         <v>3.85</v>
@@ -3444,16 +3444,16 @@
         <v>3.3</v>
       </c>
       <c r="K12">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L12">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="M12">
         <v>1.1</v>
       </c>
       <c r="N12">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O12">
         <v>1.45</v>
@@ -3462,31 +3462,31 @@
         <v>1.68</v>
       </c>
       <c r="Q12">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R12">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S12">
         <v>4.7</v>
       </c>
       <c r="T12">
-        <v>1.98</v>
+        <v>1.5</v>
       </c>
       <c r="U12">
-        <v>1.91</v>
+        <v>1.64</v>
       </c>
       <c r="V12">
         <v>1.35</v>
       </c>
       <c r="W12">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="X12">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="Y12">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Z12">
         <v>500</v>
@@ -3495,25 +3495,25 @@
         <v>900</v>
       </c>
       <c r="AB12">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AC12">
-        <v>13.5</v>
+        <v>42</v>
       </c>
       <c r="AD12">
-        <v>80</v>
+        <v>970</v>
       </c>
       <c r="AE12">
         <v>500</v>
       </c>
       <c r="AF12">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AG12">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AH12">
-        <v>34</v>
+        <v>950</v>
       </c>
       <c r="AI12">
         <v>500</v>
@@ -3534,121 +3534,121 @@
         <v>500</v>
       </c>
       <c r="AO12">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AP12">
-        <v>9.4</v>
+        <v>1.49</v>
       </c>
       <c r="AQ12">
-        <v>9.800000000000001</v>
+        <v>1.47</v>
       </c>
       <c r="AR12">
-        <v>9.4</v>
+        <v>1.57</v>
       </c>
       <c r="AS12">
-        <v>7</v>
+        <v>1.58</v>
       </c>
       <c r="AT12">
-        <v>7.4</v>
+        <v>1.53</v>
       </c>
       <c r="AU12">
-        <v>6.8</v>
+        <v>1.43</v>
       </c>
       <c r="AV12">
-        <v>13.5</v>
+        <v>1.56</v>
       </c>
       <c r="AW12">
-        <v>6.8</v>
+        <v>1.57</v>
       </c>
       <c r="AX12">
-        <v>11.5</v>
+        <v>1.55</v>
       </c>
       <c r="AY12">
-        <v>10</v>
+        <v>1.47</v>
       </c>
       <c r="AZ12">
-        <v>18</v>
+        <v>1.52</v>
       </c>
       <c r="BA12">
-        <v>7</v>
+        <v>1.57</v>
       </c>
       <c r="BB12">
-        <v>10</v>
+        <v>1.55</v>
       </c>
       <c r="BC12">
-        <v>9.800000000000001</v>
+        <v>1.55</v>
       </c>
       <c r="BD12">
-        <v>11</v>
+        <v>1.57</v>
       </c>
       <c r="BE12">
-        <v>7.4</v>
+        <v>1.59</v>
       </c>
       <c r="BF12">
-        <v>9.4</v>
+        <v>1.59</v>
       </c>
       <c r="BG12">
-        <v>7</v>
+        <v>1.59</v>
       </c>
       <c r="BH12">
-        <v>2.9</v>
+        <v>1000</v>
       </c>
       <c r="BI12">
-        <v>2.46</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>15</v>
+        <v>1.04</v>
       </c>
       <c r="BN12">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="BP12">
         <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT12">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV12">
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12">
         <v>1000</v>
       </c>
       <c r="CA12">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="s">
         <v>133</v>
@@ -3674,223 +3674,223 @@
         <v>1.85</v>
       </c>
       <c r="G13">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="H13">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I13">
         <v>4.7</v>
       </c>
       <c r="J13">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K13">
         <v>4.2</v>
       </c>
       <c r="L13">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="M13">
         <v>1.04</v>
       </c>
       <c r="N13">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="O13">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="P13">
         <v>2.28</v>
       </c>
       <c r="Q13">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="R13">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S13">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="T13">
-        <v>1.65</v>
+        <v>1.11</v>
       </c>
       <c r="U13">
-        <v>2.26</v>
+        <v>1.11</v>
       </c>
       <c r="V13">
         <v>1.27</v>
       </c>
       <c r="W13">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="X13">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y13">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z13">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA13">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB13">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC13">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD13">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE13">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF13">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AG13">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH13">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI13">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ13">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK13">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AL13">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM13">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN13">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AO13">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AP13">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS13">
         <v>1.01</v>
       </c>
       <c r="AT13">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU13">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV13">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW13">
         <v>1.01</v>
       </c>
       <c r="AX13">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY13">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA13">
         <v>1.01</v>
       </c>
       <c r="BB13">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BC13">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD13">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BE13">
         <v>1.01</v>
       </c>
       <c r="BF13">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG13">
         <v>1.01</v>
       </c>
       <c r="BH13">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI13">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="BJ13">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BN13">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BO13">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="BP13">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BT13">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BU13">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BZ13">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="CA13">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB13" t="s">
         <v>133</v>
@@ -3916,7 +3916,7 @@
         <v>4</v>
       </c>
       <c r="G14">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H14">
         <v>1.86</v>
@@ -3925,7 +3925,7 @@
         <v>1.88</v>
       </c>
       <c r="J14">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K14">
         <v>4.6</v>
@@ -3937,7 +3937,7 @@
         <v>1.02</v>
       </c>
       <c r="N14">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="O14">
         <v>1.13</v>
@@ -3955,19 +3955,19 @@
         <v>2.02</v>
       </c>
       <c r="T14">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="U14">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="V14">
         <v>2.12</v>
       </c>
       <c r="W14">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="X14">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Y14">
         <v>18.5</v>
@@ -3976,7 +3976,7 @@
         <v>18</v>
       </c>
       <c r="AA14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB14">
         <v>30</v>
@@ -3988,7 +3988,7 @@
         <v>11.5</v>
       </c>
       <c r="AE14">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AF14">
         <v>42</v>
@@ -3997,7 +3997,7 @@
         <v>17.5</v>
       </c>
       <c r="AH14">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AI14">
         <v>22</v>
@@ -4009,19 +4009,19 @@
         <v>38</v>
       </c>
       <c r="AL14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM14">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AN14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AO14">
         <v>6.4</v>
       </c>
       <c r="AP14">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AQ14">
         <v>16</v>
@@ -4030,10 +4030,10 @@
         <v>15</v>
       </c>
       <c r="AS14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT14">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="AU14">
         <v>10.5</v>
@@ -4060,7 +4060,7 @@
         <v>36</v>
       </c>
       <c r="BC14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BD14">
         <v>30</v>
@@ -4069,70 +4069,70 @@
         <v>38</v>
       </c>
       <c r="BF14">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BG14">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BH14">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BI14">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BJ14">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK14">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL14">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BM14">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN14">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BO14">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BP14">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR14">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BT14">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BU14">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV14">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BW14">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX14">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BY14">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="CA14">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="CB14" t="s">
         <v>133</v>
@@ -4161,7 +4161,7 @@
         <v>2.26</v>
       </c>
       <c r="H15">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I15">
         <v>3.8</v>
@@ -4179,28 +4179,28 @@
         <v>1.1</v>
       </c>
       <c r="N15">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O15">
         <v>1.44</v>
       </c>
       <c r="P15">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q15">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R15">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S15">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T15">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="U15">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="V15">
         <v>1.35</v>
@@ -4209,172 +4209,172 @@
         <v>1.79</v>
       </c>
       <c r="X15">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y15">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Z15">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA15">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB15">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AC15">
         <v>8.6</v>
       </c>
       <c r="AD15">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AE15">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF15">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG15">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH15">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI15">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ15">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK15">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL15">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM15">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN15">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AO15">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP15">
-        <v>8.4</v>
+        <v>1.13</v>
       </c>
       <c r="AQ15">
-        <v>10.5</v>
+        <v>1.13</v>
       </c>
       <c r="AR15">
-        <v>7</v>
+        <v>1.14</v>
       </c>
       <c r="AS15">
-        <v>8.6</v>
+        <v>1.14</v>
       </c>
       <c r="AT15">
-        <v>7</v>
+        <v>1.13</v>
       </c>
       <c r="AU15">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV15">
-        <v>14</v>
+        <v>1.13</v>
       </c>
       <c r="AW15">
-        <v>8.199999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="AX15">
-        <v>11.5</v>
+        <v>1.13</v>
       </c>
       <c r="AY15">
-        <v>10</v>
+        <v>1.13</v>
       </c>
       <c r="AZ15">
-        <v>18</v>
+        <v>1.13</v>
       </c>
       <c r="BA15">
-        <v>8.4</v>
+        <v>1.14</v>
       </c>
       <c r="BB15">
-        <v>24</v>
+        <v>1.14</v>
       </c>
       <c r="BC15">
-        <v>7</v>
+        <v>1.14</v>
       </c>
       <c r="BD15">
-        <v>38</v>
+        <v>1.14</v>
       </c>
       <c r="BE15">
-        <v>9</v>
+        <v>1.14</v>
       </c>
       <c r="BF15">
-        <v>20</v>
+        <v>1.14</v>
       </c>
       <c r="BG15">
-        <v>8.4</v>
+        <v>1.14</v>
       </c>
       <c r="BH15">
-        <v>3</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>2.82</v>
+        <v>1.04</v>
       </c>
       <c r="BJ15">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>17</v>
+        <v>1.04</v>
       </c>
       <c r="BN15">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BP15">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BR15">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS15">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT15">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BV15">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BW15">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BX15">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY15">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="s">
         <v>133</v>
@@ -4400,10 +4400,10 @@
         <v>2</v>
       </c>
       <c r="G16">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H16">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I16">
         <v>4.1</v>
@@ -4421,46 +4421,46 @@
         <v>1.06</v>
       </c>
       <c r="N16">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O16">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P16">
         <v>2.1</v>
       </c>
       <c r="Q16">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R16">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S16">
         <v>3.2</v>
       </c>
       <c r="T16">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="U16">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="V16">
         <v>1.32</v>
       </c>
       <c r="W16">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X16">
         <v>17</v>
       </c>
       <c r="Y16">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z16">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AA16">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AB16">
         <v>10.5</v>
@@ -4469,10 +4469,10 @@
         <v>8.6</v>
       </c>
       <c r="AD16">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE16">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="AF16">
         <v>13</v>
@@ -4481,7 +4481,7 @@
         <v>10.5</v>
       </c>
       <c r="AH16">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI16">
         <v>55</v>
@@ -4496,16 +4496,16 @@
         <v>34</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN16">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AO16">
         <v>44</v>
       </c>
       <c r="AP16">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ16">
         <v>14.5</v>
@@ -4526,25 +4526,25 @@
         <v>14.5</v>
       </c>
       <c r="AW16">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AX16">
         <v>11.5</v>
       </c>
       <c r="AY16">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ16">
         <v>15.5</v>
       </c>
       <c r="BA16">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="BB16">
         <v>21</v>
       </c>
       <c r="BC16">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BD16">
         <v>29</v>
@@ -4559,64 +4559,64 @@
         <v>36</v>
       </c>
       <c r="BH16">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>2.88</v>
+        <v>1.04</v>
       </c>
       <c r="BJ16">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BN16">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="BP16">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR16">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BT16">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV16">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX16">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="CA16">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB16" t="s">
         <v>133</v>
@@ -4639,7 +4639,7 @@
         <v>130</v>
       </c>
       <c r="F17">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -4651,7 +4651,7 @@
         <v>4.2</v>
       </c>
       <c r="J17">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K17">
         <v>4</v>
@@ -4678,7 +4678,7 @@
         <v>1.46</v>
       </c>
       <c r="S17">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T17">
         <v>1.71</v>
@@ -4696,19 +4696,19 @@
         <v>17.5</v>
       </c>
       <c r="Y17">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z17">
         <v>32</v>
       </c>
       <c r="AA17">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB17">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC17">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD17">
         <v>16.5</v>
@@ -4720,7 +4720,7 @@
         <v>13</v>
       </c>
       <c r="AG17">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AH17">
         <v>17.5</v>
@@ -4729,10 +4729,10 @@
         <v>55</v>
       </c>
       <c r="AJ17">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AK17">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AL17">
         <v>32</v>
@@ -4741,7 +4741,7 @@
         <v>85</v>
       </c>
       <c r="AN17">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AO17">
         <v>42</v>
@@ -4759,7 +4759,7 @@
         <v>34</v>
       </c>
       <c r="AT17">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU17">
         <v>8</v>
@@ -4768,19 +4768,19 @@
         <v>14.5</v>
       </c>
       <c r="AW17">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="AX17">
         <v>11.5</v>
       </c>
       <c r="AY17">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ17">
         <v>15.5</v>
       </c>
       <c r="BA17">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="BB17">
         <v>20</v>
@@ -4792,73 +4792,73 @@
         <v>28</v>
       </c>
       <c r="BE17">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="BF17">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BG17">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="BH17">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="BI17">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="BJ17">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK17">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN17">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO17">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP17">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BR17">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS17">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT17">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU17">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV17">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW17">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX17">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY17">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BZ17">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA17">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="CB17" t="s">
         <v>133</v>
@@ -4881,22 +4881,22 @@
         <v>131</v>
       </c>
       <c r="F18">
+        <v>1.74</v>
+      </c>
+      <c r="G18">
         <v>1.76</v>
       </c>
-      <c r="G18">
-        <v>1.78</v>
-      </c>
       <c r="H18">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I18">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="J18">
         <v>4.5</v>
       </c>
       <c r="K18">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L18">
         <v>1.27</v>
@@ -4911,46 +4911,46 @@
         <v>1.17</v>
       </c>
       <c r="P18">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="Q18">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R18">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="S18">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="T18">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="U18">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="V18">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W18">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X18">
+        <v>34</v>
+      </c>
+      <c r="Y18">
         <v>28</v>
       </c>
-      <c r="Y18">
-        <v>26</v>
-      </c>
       <c r="Z18">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AA18">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AB18">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC18">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD18">
         <v>18.5</v>
@@ -4959,7 +4959,7 @@
         <v>48</v>
       </c>
       <c r="AF18">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG18">
         <v>10.5</v>
@@ -4968,13 +4968,13 @@
         <v>15.5</v>
       </c>
       <c r="AI18">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AJ18">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AK18">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AL18">
         <v>24</v>
@@ -4989,7 +4989,7 @@
         <v>34</v>
       </c>
       <c r="AP18">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ18">
         <v>22</v>
@@ -5004,16 +5004,16 @@
         <v>13</v>
       </c>
       <c r="AU18">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV18">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW18">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AX18">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY18">
         <v>9.6</v>
@@ -5031,76 +5031,76 @@
         <v>14.5</v>
       </c>
       <c r="BD18">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BE18">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="BF18">
         <v>6.2</v>
       </c>
       <c r="BG18">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="BH18">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BI18">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="BJ18">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK18">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN18">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BO18">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="BP18">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR18">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BS18">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BT18">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BU18">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV18">
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BX18">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY18">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BZ18">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="CA18">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="CB18" t="s">
         <v>133</v>
@@ -5123,19 +5123,19 @@
         <v>132</v>
       </c>
       <c r="F19">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G19">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H19">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I19">
         <v>3.15</v>
       </c>
       <c r="J19">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K19">
         <v>4.4</v>
@@ -5147,7 +5147,7 @@
         <v>1.02</v>
       </c>
       <c r="N19">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="O19">
         <v>1.12</v>
@@ -5165,16 +5165,16 @@
         <v>1.95</v>
       </c>
       <c r="T19">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="U19">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="V19">
         <v>1.46</v>
       </c>
       <c r="W19">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="X19">
         <v>38</v>
@@ -5183,10 +5183,10 @@
         <v>28</v>
       </c>
       <c r="Z19">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA19">
-        <v>55</v>
+        <v>220</v>
       </c>
       <c r="AB19">
         <v>23</v>
@@ -5195,16 +5195,16 @@
         <v>11.5</v>
       </c>
       <c r="AD19">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="AE19">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF19">
         <v>23</v>
       </c>
       <c r="AG19">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH19">
         <v>13.5</v>
@@ -5216,19 +5216,19 @@
         <v>34</v>
       </c>
       <c r="AK19">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AL19">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM19">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AN19">
         <v>7.6</v>
       </c>
       <c r="AO19">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP19">
         <v>32</v>
@@ -5240,7 +5240,7 @@
         <v>29</v>
       </c>
       <c r="AS19">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="AT19">
         <v>20</v>
@@ -5252,16 +5252,16 @@
         <v>13.5</v>
       </c>
       <c r="AW19">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AX19">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AY19">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ19">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA19">
         <v>25</v>
@@ -5270,7 +5270,7 @@
         <v>29</v>
       </c>
       <c r="BC19">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD19">
         <v>20</v>
@@ -5282,67 +5282,67 @@
         <v>7</v>
       </c>
       <c r="BG19">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH19">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BI19">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BJ19">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BK19">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN19">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO19">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP19">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR19">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BS19">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BT19">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU19">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV19">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BW19">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BX19">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BY19">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ19">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="CA19">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB19" t="s">
         <v>133</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
@@ -415,7 +415,7 @@
     <t>Chicago Fire</t>
   </si>
   <si>
-    <t>2026-07-22 06:25:20</t>
+    <t>2026-07-22 08:32:45</t>
   </si>
 </sst>
 </file>
@@ -1009,226 +1009,226 @@
         <v>115</v>
       </c>
       <c r="F2">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="G2">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="H2">
         <v>2.64</v>
       </c>
       <c r="I2">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="J2">
+        <v>2.78</v>
+      </c>
+      <c r="K2">
+        <v>2.86</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>5.5</v>
+      </c>
+      <c r="Q2">
+        <v>1.21</v>
+      </c>
+      <c r="R2">
+        <v>1.9</v>
+      </c>
+      <c r="S2">
+        <v>2.06</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>1.54</v>
+      </c>
+      <c r="W2">
+        <v>1.37</v>
+      </c>
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>1000</v>
+      </c>
+      <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>1000</v>
+      </c>
+      <c r="AC2">
+        <v>5.7</v>
+      </c>
+      <c r="AD2">
+        <v>5.9</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>1000</v>
+      </c>
+      <c r="AG2">
+        <v>7.8</v>
+      </c>
+      <c r="AH2">
+        <v>7.4</v>
+      </c>
+      <c r="AI2">
+        <v>100</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>100</v>
+      </c>
+      <c r="AO2">
+        <v>40</v>
+      </c>
+      <c r="AP2">
+        <v>3.35</v>
+      </c>
+      <c r="AQ2">
+        <v>3.05</v>
+      </c>
+      <c r="AR2">
+        <v>3.05</v>
+      </c>
+      <c r="AS2">
+        <v>3.05</v>
+      </c>
+      <c r="AT2">
         <v>3.15</v>
       </c>
-      <c r="K2">
-        <v>3.35</v>
-      </c>
-      <c r="L2">
-        <v>1.5</v>
-      </c>
-      <c r="M2">
-        <v>1.09</v>
-      </c>
-      <c r="N2">
-        <v>3.6</v>
-      </c>
-      <c r="O2">
-        <v>1.37</v>
-      </c>
-      <c r="P2">
-        <v>1.85</v>
-      </c>
-      <c r="Q2">
-        <v>2.14</v>
-      </c>
-      <c r="R2">
-        <v>1.32</v>
-      </c>
-      <c r="S2">
-        <v>3.95</v>
-      </c>
-      <c r="T2">
-        <v>1.73</v>
-      </c>
-      <c r="U2">
-        <v>1.99</v>
-      </c>
-      <c r="V2">
-        <v>1.58</v>
-      </c>
-      <c r="W2">
-        <v>1.45</v>
-      </c>
-      <c r="X2">
-        <v>13</v>
-      </c>
-      <c r="Y2">
-        <v>10.5</v>
-      </c>
-      <c r="Z2">
-        <v>17.5</v>
-      </c>
-      <c r="AA2">
-        <v>40</v>
-      </c>
-      <c r="AB2">
-        <v>14</v>
-      </c>
-      <c r="AC2">
-        <v>7.2</v>
-      </c>
-      <c r="AD2">
+      <c r="AU2">
+        <v>4.8</v>
+      </c>
+      <c r="AV2">
+        <v>5.1</v>
+      </c>
+      <c r="AW2">
         <v>12</v>
       </c>
-      <c r="AE2">
-        <v>32</v>
-      </c>
-      <c r="AF2">
-        <v>24</v>
-      </c>
-      <c r="AG2">
-        <v>13</v>
-      </c>
-      <c r="AH2">
-        <v>18</v>
-      </c>
-      <c r="AI2">
-        <v>50</v>
-      </c>
-      <c r="AJ2">
-        <v>55</v>
-      </c>
-      <c r="AK2">
-        <v>40</v>
-      </c>
-      <c r="AL2">
-        <v>65</v>
-      </c>
-      <c r="AM2">
-        <v>110</v>
-      </c>
-      <c r="AN2">
-        <v>42</v>
-      </c>
-      <c r="AO2">
-        <v>29</v>
-      </c>
-      <c r="AP2">
-        <v>11</v>
-      </c>
-      <c r="AQ2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR2">
-        <v>14.5</v>
-      </c>
-      <c r="AS2">
-        <v>32</v>
-      </c>
-      <c r="AT2">
-        <v>10.5</v>
-      </c>
-      <c r="AU2">
-        <v>6.6</v>
-      </c>
-      <c r="AV2">
-        <v>10.5</v>
-      </c>
-      <c r="AW2">
-        <v>26</v>
-      </c>
       <c r="AX2">
-        <v>18.5</v>
+        <v>3.15</v>
       </c>
       <c r="AY2">
-        <v>12</v>
+        <v>5.6</v>
       </c>
       <c r="AZ2">
-        <v>13.5</v>
+        <v>6.2</v>
       </c>
       <c r="BA2">
-        <v>29</v>
+        <v>4.8</v>
       </c>
       <c r="BB2">
-        <v>44</v>
+        <v>3.15</v>
       </c>
       <c r="BC2">
-        <v>32</v>
+        <v>3.55</v>
       </c>
       <c r="BD2">
-        <v>34</v>
+        <v>3.8</v>
       </c>
       <c r="BE2">
-        <v>55</v>
+        <v>3.15</v>
       </c>
       <c r="BF2">
-        <v>30</v>
+        <v>3.75</v>
       </c>
       <c r="BG2">
-        <v>8.6</v>
+        <v>3.1</v>
       </c>
       <c r="BH2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
         <v>133</v>
@@ -1251,226 +1251,226 @@
         <v>116</v>
       </c>
       <c r="F3">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="G3">
+        <v>5.5</v>
+      </c>
+      <c r="H3">
+        <v>2.2</v>
+      </c>
+      <c r="I3">
+        <v>2.3</v>
+      </c>
+      <c r="J3">
+        <v>2.66</v>
+      </c>
+      <c r="K3">
+        <v>2.72</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>4.2</v>
+      </c>
+      <c r="Q3">
+        <v>1.29</v>
+      </c>
+      <c r="R3">
+        <v>1.68</v>
+      </c>
+      <c r="S3">
+        <v>2.36</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>1.77</v>
+      </c>
+      <c r="W3">
+        <v>1.22</v>
+      </c>
+      <c r="X3">
+        <v>1000</v>
+      </c>
+      <c r="Y3">
+        <v>1000</v>
+      </c>
+      <c r="Z3">
+        <v>1000</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>1000</v>
+      </c>
+      <c r="AC3">
+        <v>4.6</v>
+      </c>
+      <c r="AD3">
         <v>4.5</v>
       </c>
-      <c r="H3">
-        <v>2.08</v>
-      </c>
-      <c r="I3">
-        <v>2.1</v>
-      </c>
-      <c r="J3">
-        <v>3.35</v>
-      </c>
-      <c r="K3">
-        <v>3.4</v>
-      </c>
-      <c r="L3">
-        <v>1.51</v>
-      </c>
-      <c r="M3">
-        <v>1.1</v>
-      </c>
-      <c r="N3">
-        <v>3.35</v>
-      </c>
-      <c r="O3">
-        <v>1.41</v>
-      </c>
-      <c r="P3">
-        <v>1.78</v>
-      </c>
-      <c r="Q3">
-        <v>2.22</v>
-      </c>
-      <c r="R3">
-        <v>1.3</v>
-      </c>
-      <c r="S3">
+      <c r="AE3">
+        <v>11</v>
+      </c>
+      <c r="AF3">
+        <v>1000</v>
+      </c>
+      <c r="AG3">
+        <v>9</v>
+      </c>
+      <c r="AH3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AI3">
+        <v>19.5</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>40</v>
+      </c>
+      <c r="AL3">
+        <v>38</v>
+      </c>
+      <c r="AM3">
+        <v>90</v>
+      </c>
+      <c r="AN3">
+        <v>110</v>
+      </c>
+      <c r="AO3">
+        <v>19</v>
+      </c>
+      <c r="AP3">
+        <v>16</v>
+      </c>
+      <c r="AQ3">
+        <v>16</v>
+      </c>
+      <c r="AR3">
+        <v>16</v>
+      </c>
+      <c r="AS3">
+        <v>16</v>
+      </c>
+      <c r="AT3">
+        <v>16</v>
+      </c>
+      <c r="AU3">
         <v>4.2</v>
       </c>
-      <c r="T3">
-        <v>1.95</v>
-      </c>
-      <c r="U3">
-        <v>1.97</v>
-      </c>
-      <c r="V3">
-        <v>1.9</v>
-      </c>
-      <c r="W3">
-        <v>1.29</v>
-      </c>
-      <c r="X3">
-        <v>11</v>
-      </c>
-      <c r="Y3">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Z3">
-        <v>12.5</v>
-      </c>
-      <c r="AA3">
-        <v>26</v>
-      </c>
-      <c r="AB3">
-        <v>13.5</v>
-      </c>
-      <c r="AC3">
-        <v>7.4</v>
-      </c>
-      <c r="AD3">
-        <v>11</v>
-      </c>
-      <c r="AE3">
-        <v>26</v>
-      </c>
-      <c r="AF3">
+      <c r="AV3">
+        <v>4.1</v>
+      </c>
+      <c r="AW3">
+        <v>9.4</v>
+      </c>
+      <c r="AX3">
+        <v>16</v>
+      </c>
+      <c r="AY3">
+        <v>8</v>
+      </c>
+      <c r="AZ3">
+        <v>7.6</v>
+      </c>
+      <c r="BA3">
+        <v>17.5</v>
+      </c>
+      <c r="BB3">
+        <v>16</v>
+      </c>
+      <c r="BC3">
         <v>32</v>
       </c>
-      <c r="AG3">
-        <v>17.5</v>
-      </c>
-      <c r="AH3">
-        <v>21</v>
-      </c>
-      <c r="AI3">
+      <c r="BD3">
+        <v>30</v>
+      </c>
+      <c r="BE3">
         <v>60</v>
       </c>
-      <c r="AJ3">
-        <v>100</v>
-      </c>
-      <c r="AK3">
+      <c r="BF3">
         <v>65</v>
       </c>
-      <c r="AL3">
-        <v>80</v>
-      </c>
-      <c r="AM3">
-        <v>440</v>
-      </c>
-      <c r="AN3">
-        <v>85</v>
-      </c>
-      <c r="AO3">
-        <v>19.5</v>
-      </c>
-      <c r="AP3">
-        <v>10</v>
-      </c>
-      <c r="AQ3">
-        <v>7.6</v>
-      </c>
-      <c r="AR3">
-        <v>11</v>
-      </c>
-      <c r="AS3">
-        <v>23</v>
-      </c>
-      <c r="AT3">
-        <v>12.5</v>
-      </c>
-      <c r="AU3">
-        <v>6.8</v>
-      </c>
-      <c r="AV3">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW3">
-        <v>21</v>
-      </c>
-      <c r="AX3">
-        <v>25</v>
-      </c>
-      <c r="AY3">
-        <v>14</v>
-      </c>
-      <c r="AZ3">
-        <v>18.5</v>
-      </c>
-      <c r="BA3">
-        <v>40</v>
-      </c>
-      <c r="BB3">
-        <v>38</v>
-      </c>
-      <c r="BC3">
-        <v>46</v>
-      </c>
-      <c r="BD3">
-        <v>48</v>
-      </c>
-      <c r="BE3">
-        <v>100</v>
-      </c>
-      <c r="BF3">
-        <v>34</v>
-      </c>
       <c r="BG3">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BH3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI3">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="BJ3">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="BK3">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="BN3">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BO3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ3">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS3">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BT3">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BU3">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW3">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY3">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA3">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="s">
         <v>133</v>
@@ -1493,226 +1493,226 @@
         <v>117</v>
       </c>
       <c r="F4">
-        <v>1.84</v>
+        <v>1.25</v>
       </c>
       <c r="G4">
-        <v>1.87</v>
+        <v>1.26</v>
       </c>
       <c r="H4">
-        <v>5.3</v>
+        <v>23</v>
       </c>
       <c r="I4">
-        <v>5.5</v>
+        <v>24</v>
       </c>
       <c r="J4">
-        <v>3.55</v>
+        <v>6</v>
       </c>
       <c r="K4">
-        <v>3.65</v>
+        <v>6.4</v>
       </c>
       <c r="L4">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="O4">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="P4">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="Q4">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="R4">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="S4">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="T4">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="U4">
-        <v>1.82</v>
+        <v>1.64</v>
       </c>
       <c r="V4">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="W4">
-        <v>2.18</v>
+        <v>4.7</v>
       </c>
       <c r="X4">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AA4">
-        <v>690</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>7.2</v>
+        <v>4.3</v>
       </c>
       <c r="AC4">
         <v>7.8</v>
       </c>
       <c r="AD4">
+        <v>36</v>
+      </c>
+      <c r="AE4">
+        <v>290</v>
+      </c>
+      <c r="AF4">
+        <v>4.8</v>
+      </c>
+      <c r="AG4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AH4">
+        <v>34</v>
+      </c>
+      <c r="AI4">
+        <v>320</v>
+      </c>
+      <c r="AJ4">
+        <v>11</v>
+      </c>
+      <c r="AK4">
+        <v>21</v>
+      </c>
+      <c r="AL4">
+        <v>100</v>
+      </c>
+      <c r="AM4">
+        <v>1000</v>
+      </c>
+      <c r="AN4">
+        <v>20</v>
+      </c>
+      <c r="AO4">
+        <v>1000</v>
+      </c>
+      <c r="AP4">
+        <v>18.5</v>
+      </c>
+      <c r="AQ4">
+        <v>18.5</v>
+      </c>
+      <c r="AR4">
+        <v>18.5</v>
+      </c>
+      <c r="AS4">
+        <v>18.5</v>
+      </c>
+      <c r="AT4">
+        <v>4</v>
+      </c>
+      <c r="AU4">
+        <v>7</v>
+      </c>
+      <c r="AV4">
+        <v>29</v>
+      </c>
+      <c r="AW4">
+        <v>17.5</v>
+      </c>
+      <c r="AX4">
+        <v>4.4</v>
+      </c>
+      <c r="AY4">
+        <v>7.8</v>
+      </c>
+      <c r="AZ4">
+        <v>30</v>
+      </c>
+      <c r="BA4">
+        <v>17.5</v>
+      </c>
+      <c r="BB4">
+        <v>10</v>
+      </c>
+      <c r="BC4">
+        <v>19</v>
+      </c>
+      <c r="BD4">
+        <v>60</v>
+      </c>
+      <c r="BE4">
+        <v>130</v>
+      </c>
+      <c r="BF4">
+        <v>17.5</v>
+      </c>
+      <c r="BG4">
         <v>24</v>
       </c>
-      <c r="AE4">
-        <v>130</v>
-      </c>
-      <c r="AF4">
-        <v>9</v>
-      </c>
-      <c r="AG4">
-        <v>10.5</v>
-      </c>
-      <c r="AH4">
-        <v>28</v>
-      </c>
-      <c r="AI4">
-        <v>160</v>
-      </c>
-      <c r="AJ4">
-        <v>21</v>
-      </c>
-      <c r="AK4">
-        <v>23</v>
-      </c>
-      <c r="AL4">
-        <v>50</v>
-      </c>
-      <c r="AM4">
-        <v>570</v>
-      </c>
-      <c r="AN4">
-        <v>19</v>
-      </c>
-      <c r="AO4">
-        <v>180</v>
-      </c>
-      <c r="AP4">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ4">
-        <v>14</v>
-      </c>
-      <c r="AR4">
-        <v>36</v>
-      </c>
-      <c r="AS4">
-        <v>42</v>
-      </c>
-      <c r="AT4">
-        <v>6.4</v>
-      </c>
-      <c r="AU4">
-        <v>7.2</v>
-      </c>
-      <c r="AV4">
-        <v>19</v>
-      </c>
-      <c r="AW4">
-        <v>36</v>
-      </c>
-      <c r="AX4">
-        <v>8.6</v>
-      </c>
-      <c r="AY4">
-        <v>9.6</v>
-      </c>
-      <c r="AZ4">
-        <v>23</v>
-      </c>
-      <c r="BA4">
-        <v>46</v>
-      </c>
-      <c r="BB4">
-        <v>16.5</v>
-      </c>
-      <c r="BC4">
-        <v>18.5</v>
-      </c>
-      <c r="BD4">
-        <v>34</v>
-      </c>
-      <c r="BE4">
-        <v>120</v>
-      </c>
-      <c r="BF4">
-        <v>14</v>
-      </c>
-      <c r="BG4">
-        <v>42</v>
-      </c>
       <c r="BH4">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="BI4">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK4">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM4">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="BN4">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BO4">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ4">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS4">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU4">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW4">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY4">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA4">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="s">
         <v>133</v>
@@ -1738,70 +1738,70 @@
         <v>3.25</v>
       </c>
       <c r="G5">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H5">
         <v>2.24</v>
       </c>
       <c r="I5">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="J5">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K5">
         <v>4</v>
       </c>
       <c r="L5">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M5">
         <v>1.04</v>
       </c>
       <c r="N5">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O5">
         <v>1.19</v>
       </c>
       <c r="P5">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="Q5">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="R5">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="S5">
         <v>2.48</v>
       </c>
       <c r="T5">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U5">
         <v>2.76</v>
       </c>
       <c r="V5">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="W5">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X5">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Y5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z5">
         <v>17.5</v>
       </c>
       <c r="AA5">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AB5">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AC5">
         <v>9.4</v>
@@ -1810,13 +1810,13 @@
         <v>11.5</v>
       </c>
       <c r="AE5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF5">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AG5">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH5">
         <v>14</v>
@@ -1825,31 +1825,31 @@
         <v>27</v>
       </c>
       <c r="AJ5">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="AK5">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="AL5">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="AM5">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AN5">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AO5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP5">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AQ5">
         <v>14</v>
       </c>
       <c r="AR5">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AS5">
         <v>26</v>
@@ -1858,13 +1858,13 @@
         <v>17.5</v>
       </c>
       <c r="AU5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW5">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AX5">
         <v>24</v>
@@ -1879,82 +1879,82 @@
         <v>24</v>
       </c>
       <c r="BB5">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BC5">
         <v>28</v>
       </c>
       <c r="BD5">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BE5">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="BF5">
         <v>18</v>
       </c>
       <c r="BG5">
+        <v>10</v>
+      </c>
+      <c r="BH5">
+        <v>4.4</v>
+      </c>
+      <c r="BI5">
+        <v>4</v>
+      </c>
+      <c r="BJ5">
+        <v>8.6</v>
+      </c>
+      <c r="BK5">
+        <v>6</v>
+      </c>
+      <c r="BL5">
+        <v>70</v>
+      </c>
+      <c r="BM5">
+        <v>15.5</v>
+      </c>
+      <c r="BN5">
+        <v>6.6</v>
+      </c>
+      <c r="BO5">
+        <v>6.2</v>
+      </c>
+      <c r="BP5">
+        <v>22</v>
+      </c>
+      <c r="BQ5">
         <v>10.5</v>
       </c>
-      <c r="BH5">
-        <v>1000</v>
-      </c>
-      <c r="BI5">
-        <v>1.04</v>
-      </c>
-      <c r="BJ5">
-        <v>1000</v>
-      </c>
-      <c r="BK5">
-        <v>1.04</v>
-      </c>
-      <c r="BL5">
-        <v>1000</v>
-      </c>
-      <c r="BM5">
-        <v>1.04</v>
-      </c>
-      <c r="BN5">
-        <v>1000</v>
-      </c>
-      <c r="BO5">
-        <v>1.04</v>
-      </c>
-      <c r="BP5">
-        <v>1000</v>
-      </c>
-      <c r="BQ5">
-        <v>1.04</v>
-      </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS5">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BU5">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BW5">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BY5">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="CA5">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="CB5" t="s">
         <v>133</v>
@@ -1983,19 +1983,19 @@
         <v>1.13</v>
       </c>
       <c r="H6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I6">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J6">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="K6">
         <v>14</v>
       </c>
       <c r="L6">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="M6">
         <v>1.01</v>
@@ -2007,61 +2007,61 @@
         <v>1.07</v>
       </c>
       <c r="P6">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Q6">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="R6">
         <v>2.48</v>
       </c>
       <c r="S6">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="T6">
         <v>2.06</v>
       </c>
       <c r="U6">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="V6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W6">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="X6">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="Y6">
-        <v>940</v>
+        <v>120</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AA6">
         <v>1000</v>
       </c>
       <c r="AB6">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="AC6">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="AD6">
-        <v>920</v>
+        <v>100</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>430</v>
       </c>
       <c r="AF6">
         <v>11</v>
       </c>
       <c r="AG6">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH6">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AI6">
         <v>1000</v>
@@ -2070,37 +2070,37 @@
         <v>10</v>
       </c>
       <c r="AK6">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AL6">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="AM6">
-        <v>490</v>
+        <v>190</v>
       </c>
       <c r="AN6">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AP6">
         <v>55</v>
       </c>
       <c r="AQ6">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AR6">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="AS6">
         <v>60</v>
       </c>
       <c r="AT6">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AU6">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AV6">
         <v>40</v>
@@ -2109,25 +2109,25 @@
         <v>55</v>
       </c>
       <c r="AX6">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AY6">
         <v>13.5</v>
       </c>
       <c r="AZ6">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="BA6">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BB6">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC6">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BD6">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BE6">
         <v>70</v>
@@ -2139,64 +2139,64 @@
         <v>55</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BI6">
-        <v>1.21</v>
+        <v>6</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK6">
-        <v>1.21</v>
+        <v>6.4</v>
       </c>
       <c r="BL6">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM6">
-        <v>1.21</v>
+        <v>10.5</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO6">
-        <v>1.21</v>
+        <v>3.9</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BQ6">
-        <v>1.21</v>
+        <v>5.1</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BS6">
-        <v>1.21</v>
+        <v>7.2</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BU6">
-        <v>1.21</v>
+        <v>8</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="BW6">
-        <v>1.21</v>
+        <v>11</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BY6">
-        <v>1.21</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="CA6">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="CB6" t="s">
         <v>133</v>
@@ -2219,226 +2219,226 @@
         <v>120</v>
       </c>
       <c r="F7">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="G7">
         <v>2.4</v>
       </c>
       <c r="H7">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="I7">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J7">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="K7">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L7">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="M7">
         <v>1.13</v>
       </c>
       <c r="N7">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="O7">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="P7">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="Q7">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="R7">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="S7">
         <v>5.3</v>
       </c>
       <c r="T7">
-        <v>1.77</v>
+        <v>2.04</v>
       </c>
       <c r="U7">
-        <v>1.37</v>
+        <v>1.81</v>
       </c>
       <c r="V7">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W7">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X7">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="Y7">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="Z7">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AA7">
         <v>900</v>
       </c>
       <c r="AB7">
-        <v>970</v>
+        <v>7.6</v>
       </c>
       <c r="AC7">
-        <v>42</v>
+        <v>7.4</v>
       </c>
       <c r="AD7">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AE7">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AF7">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AG7">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AH7">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="AI7">
-        <v>500</v>
+        <v>380</v>
       </c>
       <c r="AJ7">
-        <v>900</v>
+        <v>36</v>
       </c>
       <c r="AK7">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AL7">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AM7">
         <v>500</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP7">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ7">
+        <v>9.6</v>
+      </c>
+      <c r="AR7">
+        <v>12.5</v>
+      </c>
+      <c r="AS7">
+        <v>10</v>
+      </c>
+      <c r="AT7">
+        <v>6.4</v>
+      </c>
+      <c r="AU7">
+        <v>6.4</v>
+      </c>
+      <c r="AV7">
+        <v>11.5</v>
+      </c>
+      <c r="AW7">
+        <v>44</v>
+      </c>
+      <c r="AX7">
+        <v>11</v>
+      </c>
+      <c r="AY7">
+        <v>10</v>
+      </c>
+      <c r="AZ7">
+        <v>19</v>
+      </c>
+      <c r="BA7">
+        <v>10</v>
+      </c>
+      <c r="BB7">
+        <v>24</v>
+      </c>
+      <c r="BC7">
+        <v>23</v>
+      </c>
+      <c r="BD7">
+        <v>29</v>
+      </c>
+      <c r="BE7">
+        <v>10.5</v>
+      </c>
+      <c r="BF7">
+        <v>8.4</v>
+      </c>
+      <c r="BG7">
+        <v>10</v>
+      </c>
+      <c r="BH7">
+        <v>2.78</v>
+      </c>
+      <c r="BI7">
+        <v>2.56</v>
+      </c>
+      <c r="BJ7">
+        <v>11</v>
+      </c>
+      <c r="BK7">
+        <v>6.6</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
+        <v>15.5</v>
+      </c>
+      <c r="BN7">
         <v>4.9</v>
       </c>
-      <c r="AQ7">
-        <v>5.6</v>
-      </c>
-      <c r="AR7">
-        <v>2.04</v>
-      </c>
-      <c r="AS7">
-        <v>1.98</v>
-      </c>
-      <c r="AT7">
-        <v>4.2</v>
-      </c>
-      <c r="AU7">
-        <v>4.2</v>
-      </c>
-      <c r="AV7">
-        <v>2</v>
-      </c>
-      <c r="AW7">
-        <v>1.97</v>
-      </c>
-      <c r="AX7">
-        <v>6.2</v>
-      </c>
-      <c r="AY7">
-        <v>6.4</v>
-      </c>
-      <c r="AZ7">
-        <v>2.06</v>
-      </c>
-      <c r="BA7">
-        <v>1.98</v>
-      </c>
-      <c r="BB7">
-        <v>2.1</v>
-      </c>
-      <c r="BC7">
-        <v>2.06</v>
-      </c>
-      <c r="BD7">
-        <v>1.97</v>
-      </c>
-      <c r="BE7">
-        <v>1.99</v>
-      </c>
-      <c r="BF7">
-        <v>1.97</v>
-      </c>
-      <c r="BG7">
-        <v>2</v>
-      </c>
-      <c r="BH7">
-        <v>1000</v>
-      </c>
-      <c r="BI7">
-        <v>1.04</v>
-      </c>
-      <c r="BJ7">
-        <v>1000</v>
-      </c>
-      <c r="BK7">
-        <v>1.04</v>
-      </c>
-      <c r="BL7">
-        <v>1000</v>
-      </c>
-      <c r="BM7">
-        <v>1.04</v>
-      </c>
-      <c r="BN7">
-        <v>1000</v>
-      </c>
       <c r="BO7">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ7">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU7">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="CB7" t="s">
         <v>133</v>
@@ -2461,220 +2461,220 @@
         <v>121</v>
       </c>
       <c r="F8">
-        <v>1.7</v>
+        <v>2.36</v>
       </c>
       <c r="G8">
-        <v>5.5</v>
+        <v>2.62</v>
       </c>
       <c r="H8">
-        <v>2.12</v>
+        <v>3.5</v>
       </c>
       <c r="I8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J8">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="K8">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="L8">
+        <v>1.55</v>
+      </c>
+      <c r="M8">
+        <v>1.12</v>
+      </c>
+      <c r="N8">
+        <v>2.62</v>
+      </c>
+      <c r="O8">
         <v>1.52</v>
       </c>
-      <c r="M8">
-        <v>1.1</v>
-      </c>
-      <c r="N8">
-        <v>1.51</v>
-      </c>
-      <c r="O8">
-        <v>1.46</v>
-      </c>
       <c r="P8">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="Q8">
-        <v>1.02</v>
+        <v>2.54</v>
       </c>
       <c r="R8">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S8">
-        <v>1.49</v>
+        <v>5.2</v>
       </c>
       <c r="T8">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="U8">
-        <v>1.11</v>
+        <v>1.81</v>
       </c>
       <c r="V8">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="W8">
-        <v>1.26</v>
+        <v>1.61</v>
       </c>
       <c r="X8">
-        <v>500</v>
+        <v>9</v>
       </c>
       <c r="Y8">
-        <v>950</v>
+        <v>11</v>
       </c>
       <c r="Z8">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="AA8">
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="AB8">
-        <v>950</v>
+        <v>8</v>
       </c>
       <c r="AC8">
-        <v>500</v>
+        <v>7.2</v>
       </c>
       <c r="AD8">
-        <v>950</v>
+        <v>17.5</v>
       </c>
       <c r="AE8">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AF8">
-        <v>500</v>
+        <v>15.5</v>
       </c>
       <c r="AG8">
-        <v>950</v>
+        <v>13</v>
       </c>
       <c r="AH8">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="AI8">
-        <v>500</v>
+        <v>190</v>
       </c>
       <c r="AJ8">
-        <v>900</v>
+        <v>40</v>
       </c>
       <c r="AK8">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AL8">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AM8">
         <v>500</v>
       </c>
       <c r="AN8">
-        <v>600</v>
+        <v>38</v>
       </c>
       <c r="AO8">
-        <v>600</v>
+        <v>95</v>
       </c>
       <c r="AP8">
-        <v>1.29</v>
+        <v>7.6</v>
       </c>
       <c r="AQ8">
-        <v>1.32</v>
+        <v>9</v>
       </c>
       <c r="AR8">
-        <v>1.39</v>
+        <v>20</v>
       </c>
       <c r="AS8">
-        <v>1.4</v>
+        <v>20</v>
       </c>
       <c r="AT8">
-        <v>1.36</v>
+        <v>6.6</v>
       </c>
       <c r="AU8">
-        <v>1.36</v>
+        <v>6</v>
       </c>
       <c r="AV8">
-        <v>1.38</v>
+        <v>14</v>
       </c>
       <c r="AW8">
-        <v>1.4</v>
+        <v>17.5</v>
       </c>
       <c r="AX8">
-        <v>1.38</v>
+        <v>12</v>
       </c>
       <c r="AY8">
-        <v>1.35</v>
+        <v>10.5</v>
       </c>
       <c r="AZ8">
-        <v>1.38</v>
+        <v>18</v>
       </c>
       <c r="BA8">
-        <v>1.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB8">
-        <v>1.4</v>
+        <v>14.5</v>
       </c>
       <c r="BC8">
-        <v>1.38</v>
+        <v>16</v>
       </c>
       <c r="BD8">
-        <v>1.4</v>
+        <v>19.5</v>
       </c>
       <c r="BE8">
-        <v>1.41</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF8">
-        <v>1.55</v>
+        <v>12</v>
       </c>
       <c r="BG8">
-        <v>1.56</v>
+        <v>11</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>2.82</v>
       </c>
       <c r="BI8">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK8">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO8">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ8">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS8">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU8">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW8">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY8">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BZ8">
         <v>0</v>
@@ -2709,16 +2709,16 @@
         <v>1.24</v>
       </c>
       <c r="H9">
-        <v>10</v>
+        <v>17.5</v>
       </c>
       <c r="I9">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J9">
         <v>7.2</v>
       </c>
       <c r="K9">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="L9">
         <v>1.3</v>
@@ -2730,22 +2730,22 @@
         <v>5.2</v>
       </c>
       <c r="O9">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P9">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="Q9">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R9">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="S9">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="T9">
-        <v>1.98</v>
+        <v>2.34</v>
       </c>
       <c r="U9">
         <v>1.64</v>
@@ -2754,175 +2754,175 @@
         <v>1.05</v>
       </c>
       <c r="W9">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="X9">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Y9">
-        <v>950</v>
+        <v>55</v>
       </c>
       <c r="Z9">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AA9">
         <v>1000</v>
       </c>
       <c r="AB9">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC9">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AD9">
-        <v>950</v>
+        <v>510</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AF9">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AG9">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH9">
-        <v>950</v>
+        <v>130</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AJ9">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AK9">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AL9">
         <v>330</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AN9">
-        <v>29</v>
+        <v>4.5</v>
       </c>
       <c r="AO9">
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>1.13</v>
+        <v>21</v>
       </c>
       <c r="AQ9">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="AR9">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="AS9">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT9">
-        <v>1.13</v>
+        <v>7.4</v>
       </c>
       <c r="AU9">
-        <v>1.13</v>
+        <v>14</v>
       </c>
       <c r="AV9">
-        <v>4.2</v>
+        <v>23</v>
       </c>
       <c r="AW9">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="AX9">
-        <v>1.13</v>
+        <v>6.4</v>
       </c>
       <c r="AY9">
-        <v>1.13</v>
+        <v>10</v>
       </c>
       <c r="AZ9">
-        <v>1.13</v>
+        <v>6.8</v>
       </c>
       <c r="BA9">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="BB9">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="BC9">
-        <v>1.13</v>
+        <v>12.5</v>
       </c>
       <c r="BD9">
-        <v>1.13</v>
+        <v>6.8</v>
       </c>
       <c r="BE9">
-        <v>1.13</v>
+        <v>7.2</v>
       </c>
       <c r="BF9">
-        <v>1.05</v>
+        <v>3.9</v>
       </c>
       <c r="BG9">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH9">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI9">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK9">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="BO9">
-        <v>1.04</v>
+        <v>2.86</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BQ9">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS9">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BU9">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="CA9">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="CB9" t="s">
         <v>133</v>
@@ -2945,79 +2945,79 @@
         <v>123</v>
       </c>
       <c r="F10">
+        <v>1.37</v>
+      </c>
+      <c r="G10">
         <v>1.39</v>
       </c>
-      <c r="G10">
+      <c r="H10">
+        <v>12.5</v>
+      </c>
+      <c r="I10">
+        <v>13</v>
+      </c>
+      <c r="J10">
+        <v>5</v>
+      </c>
+      <c r="K10">
+        <v>5.4</v>
+      </c>
+      <c r="L10">
         <v>1.4</v>
-      </c>
-      <c r="H10">
-        <v>10.5</v>
-      </c>
-      <c r="I10">
-        <v>12</v>
-      </c>
-      <c r="J10">
-        <v>5.2</v>
-      </c>
-      <c r="K10">
-        <v>5.3</v>
-      </c>
-      <c r="L10">
-        <v>1.41</v>
       </c>
       <c r="M10">
         <v>1.07</v>
       </c>
       <c r="N10">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O10">
         <v>1.32</v>
       </c>
       <c r="P10">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="Q10">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="R10">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="S10">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T10">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="U10">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="V10">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W10">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="X10">
-        <v>26</v>
+        <v>16.5</v>
       </c>
       <c r="Y10">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z10">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AA10">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="AB10">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="AC10">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AD10">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="AE10">
         <v>250</v>
@@ -3026,55 +3026,55 @@
         <v>7.6</v>
       </c>
       <c r="AG10">
-        <v>34</v>
+        <v>10.5</v>
       </c>
       <c r="AH10">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AI10">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="AJ10">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AK10">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL10">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AM10">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="AN10">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AO10">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="AP10">
+        <v>14.5</v>
+      </c>
+      <c r="AQ10">
+        <v>29</v>
+      </c>
+      <c r="AR10">
+        <v>13.5</v>
+      </c>
+      <c r="AS10">
+        <v>14</v>
+      </c>
+      <c r="AT10">
         <v>6.4</v>
       </c>
-      <c r="AQ10">
-        <v>24</v>
-      </c>
-      <c r="AR10">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS10">
-        <v>6</v>
-      </c>
-      <c r="AT10">
-        <v>6.2</v>
-      </c>
       <c r="AU10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV10">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AW10">
-        <v>8.4</v>
+        <v>14.5</v>
       </c>
       <c r="AX10">
         <v>6.6</v>
@@ -3083,88 +3083,88 @@
         <v>9.4</v>
       </c>
       <c r="AZ10">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BA10">
-        <v>8.4</v>
+        <v>14.5</v>
       </c>
       <c r="BB10">
-        <v>5.8</v>
+        <v>9.6</v>
       </c>
       <c r="BC10">
         <v>14.5</v>
       </c>
       <c r="BD10">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="BE10">
+        <v>14.5</v>
+      </c>
+      <c r="BF10">
+        <v>6.2</v>
+      </c>
+      <c r="BG10">
+        <v>15</v>
+      </c>
+      <c r="BH10">
+        <v>3.75</v>
+      </c>
+      <c r="BI10">
+        <v>2.88</v>
+      </c>
+      <c r="BJ10">
+        <v>13.5</v>
+      </c>
+      <c r="BK10">
+        <v>8.4</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>10.5</v>
+      </c>
+      <c r="BN10">
+        <v>3.75</v>
+      </c>
+      <c r="BO10">
+        <v>3.2</v>
+      </c>
+      <c r="BP10">
         <v>8.6</v>
       </c>
-      <c r="BF10">
-        <v>6.8</v>
-      </c>
-      <c r="BG10">
-        <v>8.6</v>
-      </c>
-      <c r="BH10">
-        <v>1000</v>
-      </c>
-      <c r="BI10">
-        <v>1.04</v>
-      </c>
-      <c r="BJ10">
-        <v>1000</v>
-      </c>
-      <c r="BK10">
-        <v>1.04</v>
-      </c>
-      <c r="BL10">
-        <v>1000</v>
-      </c>
-      <c r="BM10">
-        <v>1.04</v>
-      </c>
-      <c r="BN10">
-        <v>1000</v>
-      </c>
-      <c r="BO10">
-        <v>1.04</v>
-      </c>
-      <c r="BP10">
-        <v>1000</v>
-      </c>
       <c r="BQ10">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS10">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BU10">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="CA10">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="CB10" t="s">
         <v>133</v>
@@ -3187,16 +3187,16 @@
         <v>124</v>
       </c>
       <c r="F11">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H11">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="I11">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="J11">
         <v>3.45</v>
@@ -3220,7 +3220,7 @@
         <v>1.73</v>
       </c>
       <c r="Q11">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R11">
         <v>1.27</v>
@@ -3229,13 +3229,13 @@
         <v>4.5</v>
       </c>
       <c r="T11">
+        <v>2.02</v>
+      </c>
+      <c r="U11">
+        <v>1.9</v>
+      </c>
+      <c r="V11">
         <v>2</v>
-      </c>
-      <c r="U11">
-        <v>1.86</v>
-      </c>
-      <c r="V11">
-        <v>2.02</v>
       </c>
       <c r="W11">
         <v>1.25</v>
@@ -3253,28 +3253,28 @@
         <v>23</v>
       </c>
       <c r="AB11">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC11">
         <v>7.4</v>
       </c>
       <c r="AD11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AE11">
         <v>23</v>
       </c>
       <c r="AF11">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AG11">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH11">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI11">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AJ11">
         <v>120</v>
@@ -3283,7 +3283,7 @@
         <v>75</v>
       </c>
       <c r="AL11">
-        <v>200</v>
+        <v>85</v>
       </c>
       <c r="AM11">
         <v>440</v>
@@ -3292,7 +3292,7 @@
         <v>490</v>
       </c>
       <c r="AO11">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AP11">
         <v>10</v>
@@ -3301,10 +3301,10 @@
         <v>7.2</v>
       </c>
       <c r="AR11">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS11">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AT11">
         <v>13</v>
@@ -3313,7 +3313,7 @@
         <v>7</v>
       </c>
       <c r="AV11">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW11">
         <v>21</v>
@@ -3322,7 +3322,7 @@
         <v>30</v>
       </c>
       <c r="AY11">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AZ11">
         <v>21</v>
@@ -3331,7 +3331,7 @@
         <v>40</v>
       </c>
       <c r="BB11">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BC11">
         <v>50</v>
@@ -3343,70 +3343,70 @@
         <v>70</v>
       </c>
       <c r="BF11">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="BG11">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI11">
-        <v>1.04</v>
+        <v>2.84</v>
       </c>
       <c r="BJ11">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK11">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.04</v>
+        <v>15</v>
       </c>
       <c r="BN11">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO11">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BP11">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BQ11">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BR11">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS11">
-        <v>1.04</v>
+        <v>13</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BU11">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BW11">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY11">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA11">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="CB11" t="s">
         <v>133</v>
@@ -3429,13 +3429,13 @@
         <v>125</v>
       </c>
       <c r="F12">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G12">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H12">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I12">
         <v>3.85</v>
@@ -3444,16 +3444,16 @@
         <v>3.3</v>
       </c>
       <c r="K12">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L12">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="M12">
         <v>1.1</v>
       </c>
       <c r="N12">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O12">
         <v>1.45</v>
@@ -3462,31 +3462,31 @@
         <v>1.68</v>
       </c>
       <c r="Q12">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="R12">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S12">
         <v>4.7</v>
       </c>
       <c r="T12">
-        <v>1.5</v>
+        <v>1.98</v>
       </c>
       <c r="U12">
-        <v>1.64</v>
+        <v>1.94</v>
       </c>
       <c r="V12">
         <v>1.35</v>
       </c>
       <c r="W12">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="X12">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="Y12">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="Z12">
         <v>500</v>
@@ -3495,160 +3495,160 @@
         <v>900</v>
       </c>
       <c r="AB12">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC12">
-        <v>42</v>
+        <v>7.6</v>
       </c>
       <c r="AD12">
-        <v>970</v>
+        <v>80</v>
       </c>
       <c r="AE12">
         <v>500</v>
       </c>
       <c r="AF12">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AG12">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AH12">
-        <v>950</v>
+        <v>34</v>
       </c>
       <c r="AI12">
         <v>500</v>
       </c>
       <c r="AJ12">
-        <v>900</v>
+        <v>65</v>
       </c>
       <c r="AK12">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AL12">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AM12">
         <v>580</v>
       </c>
       <c r="AN12">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="AO12">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP12">
-        <v>1.49</v>
+        <v>9.4</v>
       </c>
       <c r="AQ12">
-        <v>1.47</v>
+        <v>10</v>
       </c>
       <c r="AR12">
-        <v>1.57</v>
+        <v>19</v>
       </c>
       <c r="AS12">
-        <v>1.58</v>
+        <v>12.5</v>
       </c>
       <c r="AT12">
-        <v>1.53</v>
+        <v>7.2</v>
       </c>
       <c r="AU12">
-        <v>1.43</v>
+        <v>6.6</v>
       </c>
       <c r="AV12">
-        <v>1.56</v>
+        <v>13.5</v>
       </c>
       <c r="AW12">
-        <v>1.57</v>
+        <v>11.5</v>
       </c>
       <c r="AX12">
-        <v>1.55</v>
+        <v>11.5</v>
       </c>
       <c r="AY12">
-        <v>1.47</v>
+        <v>9.6</v>
       </c>
       <c r="AZ12">
-        <v>1.52</v>
+        <v>17</v>
       </c>
       <c r="BA12">
-        <v>1.57</v>
+        <v>12</v>
       </c>
       <c r="BB12">
-        <v>1.55</v>
+        <v>23</v>
       </c>
       <c r="BC12">
-        <v>1.55</v>
+        <v>22</v>
       </c>
       <c r="BD12">
-        <v>1.57</v>
+        <v>20</v>
       </c>
       <c r="BE12">
-        <v>1.59</v>
+        <v>13.5</v>
       </c>
       <c r="BF12">
-        <v>1.59</v>
+        <v>20</v>
       </c>
       <c r="BG12">
-        <v>1.59</v>
+        <v>12</v>
       </c>
       <c r="BH12">
-        <v>1000</v>
+        <v>2.88</v>
       </c>
       <c r="BI12">
-        <v>1.04</v>
+        <v>2.48</v>
       </c>
       <c r="BJ12">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK12">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.04</v>
+        <v>16.5</v>
       </c>
       <c r="BN12">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO12">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BP12">
         <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="BT12">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU12">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BV12">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW12">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>1.04</v>
+        <v>13.5</v>
       </c>
       <c r="BZ12">
         <v>1000</v>
       </c>
       <c r="CA12">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="CB12" t="s">
         <v>133</v>
@@ -3674,223 +3674,223 @@
         <v>1.85</v>
       </c>
       <c r="G13">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="H13">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I13">
         <v>4.7</v>
       </c>
       <c r="J13">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K13">
         <v>4.2</v>
       </c>
       <c r="L13">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M13">
         <v>1.04</v>
       </c>
       <c r="N13">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="O13">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P13">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="Q13">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="R13">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="S13">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="T13">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="U13">
-        <v>1.11</v>
+        <v>2.32</v>
       </c>
       <c r="V13">
         <v>1.27</v>
       </c>
       <c r="W13">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="X13">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y13">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z13">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA13">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB13">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC13">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD13">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE13">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF13">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG13">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH13">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI13">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ13">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK13">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AL13">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM13">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN13">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AO13">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP13">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AQ13">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AR13">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="AS13">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="AT13">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU13">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV13">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AW13">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="AX13">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY13">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ13">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA13">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BB13">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BC13">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BD13">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BE13">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BF13">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BG13">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BH13">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI13">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BJ13">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK13">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BN13">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO13">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BP13">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ13">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BR13">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS13">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU13">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ13">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="CA13">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="CB13" t="s">
         <v>133</v>
@@ -3916,13 +3916,13 @@
         <v>4</v>
       </c>
       <c r="G14">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H14">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="I14">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="J14">
         <v>4.3</v>
@@ -3937,7 +3937,7 @@
         <v>1.02</v>
       </c>
       <c r="N14">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="O14">
         <v>1.13</v>
@@ -3949,16 +3949,16 @@
         <v>1.41</v>
       </c>
       <c r="R14">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="S14">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="T14">
         <v>1.44</v>
       </c>
       <c r="U14">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="V14">
         <v>2.12</v>
@@ -3970,13 +3970,13 @@
         <v>34</v>
       </c>
       <c r="Y14">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z14">
         <v>18</v>
       </c>
       <c r="AA14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AB14">
         <v>30</v>
@@ -3988,52 +3988,52 @@
         <v>11.5</v>
       </c>
       <c r="AE14">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AF14">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AG14">
         <v>17.5</v>
       </c>
       <c r="AH14">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI14">
         <v>22</v>
       </c>
       <c r="AJ14">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AK14">
         <v>38</v>
       </c>
       <c r="AL14">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM14">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AN14">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO14">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AP14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AQ14">
+        <v>17</v>
+      </c>
+      <c r="AR14">
         <v>16</v>
       </c>
-      <c r="AR14">
-        <v>15</v>
-      </c>
       <c r="AS14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT14">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="AU14">
         <v>10.5</v>
@@ -4042,7 +4042,7 @@
         <v>10</v>
       </c>
       <c r="AW14">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AX14">
         <v>36</v>
@@ -4054,13 +4054,13 @@
         <v>13</v>
       </c>
       <c r="BA14">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BB14">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="BC14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BD14">
         <v>30</v>
@@ -4069,70 +4069,70 @@
         <v>38</v>
       </c>
       <c r="BF14">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BG14">
+        <v>5.9</v>
+      </c>
+      <c r="BH14">
+        <v>5.6</v>
+      </c>
+      <c r="BI14">
+        <v>4.1</v>
+      </c>
+      <c r="BJ14">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK14">
+        <v>4.7</v>
+      </c>
+      <c r="BL14">
+        <v>60</v>
+      </c>
+      <c r="BM14">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN14">
+        <v>8.6</v>
+      </c>
+      <c r="BO14">
         <v>6</v>
       </c>
-      <c r="BH14">
-        <v>1000</v>
-      </c>
-      <c r="BI14">
-        <v>1.04</v>
-      </c>
-      <c r="BJ14">
-        <v>1000</v>
-      </c>
-      <c r="BK14">
-        <v>1.04</v>
-      </c>
-      <c r="BL14">
-        <v>1000</v>
-      </c>
-      <c r="BM14">
-        <v>1.04</v>
-      </c>
-      <c r="BN14">
-        <v>1000</v>
-      </c>
-      <c r="BO14">
-        <v>1.04</v>
-      </c>
       <c r="BP14">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ14">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BR14">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS14">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BT14">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BU14">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BV14">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BW14">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BX14">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BY14">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="CA14">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="CB14" t="s">
         <v>133</v>
@@ -4155,16 +4155,16 @@
         <v>128</v>
       </c>
       <c r="F15">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="G15">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="H15">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="I15">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="J15">
         <v>3.35</v>
@@ -4173,22 +4173,22 @@
         <v>3.45</v>
       </c>
       <c r="L15">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M15">
         <v>1.1</v>
       </c>
       <c r="N15">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O15">
         <v>1.44</v>
       </c>
       <c r="P15">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q15">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="R15">
         <v>1.26</v>
@@ -4197,184 +4197,184 @@
         <v>4.5</v>
       </c>
       <c r="T15">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="U15">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="V15">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W15">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="X15">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y15">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z15">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA15">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB15">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AC15">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD15">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE15">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF15">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG15">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH15">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI15">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ15">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK15">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL15">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM15">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN15">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO15">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP15">
-        <v>1.13</v>
+        <v>9.6</v>
       </c>
       <c r="AQ15">
-        <v>1.13</v>
+        <v>11</v>
       </c>
       <c r="AR15">
-        <v>1.14</v>
+        <v>7.4</v>
       </c>
       <c r="AS15">
-        <v>1.14</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT15">
-        <v>1.13</v>
+        <v>7</v>
       </c>
       <c r="AU15">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV15">
-        <v>1.13</v>
+        <v>13</v>
       </c>
       <c r="AW15">
-        <v>1.14</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX15">
-        <v>1.13</v>
+        <v>11</v>
       </c>
       <c r="AY15">
-        <v>1.13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ15">
-        <v>1.13</v>
+        <v>6.8</v>
       </c>
       <c r="BA15">
-        <v>1.14</v>
+        <v>9</v>
       </c>
       <c r="BB15">
-        <v>1.14</v>
+        <v>7.6</v>
       </c>
       <c r="BC15">
-        <v>1.14</v>
+        <v>20</v>
       </c>
       <c r="BD15">
-        <v>1.14</v>
+        <v>38</v>
       </c>
       <c r="BE15">
-        <v>1.14</v>
+        <v>9.4</v>
       </c>
       <c r="BF15">
-        <v>1.14</v>
+        <v>19</v>
       </c>
       <c r="BG15">
-        <v>1.14</v>
+        <v>9</v>
       </c>
       <c r="BH15">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="BI15">
-        <v>1.04</v>
+        <v>2.76</v>
       </c>
       <c r="BJ15">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK15">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.04</v>
+        <v>15</v>
       </c>
       <c r="BN15">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO15">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BP15">
         <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BT15">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU15">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="BZ15">
         <v>1000</v>
       </c>
       <c r="CA15">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="CB15" t="s">
         <v>133</v>
@@ -4397,13 +4397,13 @@
         <v>129</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G16">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="H16">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="I16">
         <v>4.1</v>
@@ -4412,7 +4412,7 @@
         <v>3.8</v>
       </c>
       <c r="K16">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L16">
         <v>1.38</v>
@@ -4421,10 +4421,10 @@
         <v>1.06</v>
       </c>
       <c r="N16">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O16">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P16">
         <v>2.1</v>
@@ -4439,40 +4439,40 @@
         <v>3.2</v>
       </c>
       <c r="T16">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U16">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V16">
         <v>1.32</v>
       </c>
       <c r="W16">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="X16">
         <v>17</v>
       </c>
       <c r="Y16">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z16">
         <v>32</v>
       </c>
       <c r="AA16">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB16">
         <v>10.5</v>
       </c>
       <c r="AC16">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD16">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE16">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="AF16">
         <v>13</v>
@@ -4481,13 +4481,13 @@
         <v>10.5</v>
       </c>
       <c r="AH16">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI16">
         <v>55</v>
       </c>
       <c r="AJ16">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK16">
         <v>21</v>
@@ -4496,25 +4496,25 @@
         <v>34</v>
       </c>
       <c r="AM16">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AN16">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AO16">
         <v>44</v>
       </c>
       <c r="AP16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ16">
         <v>14.5</v>
       </c>
       <c r="AR16">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AS16">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AT16">
         <v>9.4</v>
@@ -4526,7 +4526,7 @@
         <v>14.5</v>
       </c>
       <c r="AW16">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="AX16">
         <v>11.5</v>
@@ -4538,85 +4538,85 @@
         <v>15.5</v>
       </c>
       <c r="BA16">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="BB16">
         <v>21</v>
       </c>
       <c r="BC16">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD16">
         <v>29</v>
       </c>
       <c r="BE16">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="BF16">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG16">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="BH16">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI16">
-        <v>1.04</v>
+        <v>2.88</v>
       </c>
       <c r="BJ16">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK16">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN16">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO16">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BP16">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ16">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BR16">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS16">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU16">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BV16">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW16">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BX16">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY16">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA16">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="CB16" t="s">
         <v>133</v>
@@ -4639,7 +4639,7 @@
         <v>130</v>
       </c>
       <c r="F17">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -4648,43 +4648,43 @@
         <v>4</v>
       </c>
       <c r="I17">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J17">
+        <v>3.9</v>
+      </c>
+      <c r="K17">
         <v>3.95</v>
-      </c>
-      <c r="K17">
-        <v>4</v>
       </c>
       <c r="L17">
         <v>1.36</v>
       </c>
       <c r="M17">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N17">
         <v>4.6</v>
       </c>
       <c r="O17">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P17">
         <v>2.2</v>
       </c>
       <c r="Q17">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R17">
         <v>1.46</v>
       </c>
       <c r="S17">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T17">
         <v>1.71</v>
       </c>
       <c r="U17">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V17">
         <v>1.32</v>
@@ -4696,16 +4696,16 @@
         <v>17.5</v>
       </c>
       <c r="Y17">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z17">
         <v>32</v>
       </c>
       <c r="AA17">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB17">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC17">
         <v>8.800000000000001</v>
@@ -4714,37 +4714,37 @@
         <v>16.5</v>
       </c>
       <c r="AE17">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF17">
         <v>13</v>
       </c>
       <c r="AG17">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH17">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI17">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ17">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AK17">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL17">
         <v>32</v>
       </c>
       <c r="AM17">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN17">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AO17">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP17">
         <v>16</v>
@@ -4756,31 +4756,31 @@
         <v>27</v>
       </c>
       <c r="AS17">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AT17">
         <v>10</v>
       </c>
       <c r="AU17">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV17">
         <v>14.5</v>
       </c>
       <c r="AW17">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AX17">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY17">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ17">
         <v>15.5</v>
       </c>
       <c r="BA17">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="BB17">
         <v>20</v>
@@ -4792,73 +4792,73 @@
         <v>28</v>
       </c>
       <c r="BE17">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="BF17">
+        <v>10.5</v>
+      </c>
+      <c r="BG17">
+        <v>34</v>
+      </c>
+      <c r="BH17">
+        <v>3.95</v>
+      </c>
+      <c r="BI17">
+        <v>3</v>
+      </c>
+      <c r="BJ17">
         <v>9.6</v>
       </c>
-      <c r="BG17">
-        <v>24</v>
-      </c>
-      <c r="BH17">
-        <v>1000</v>
-      </c>
-      <c r="BI17">
-        <v>1.04</v>
-      </c>
-      <c r="BJ17">
-        <v>1000</v>
-      </c>
       <c r="BK17">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BN17">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO17">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BP17">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ17">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BR17">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS17">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BT17">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU17">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BV17">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW17">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BX17">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY17">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ17">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA17">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="CB17" t="s">
         <v>133</v>
@@ -4881,22 +4881,22 @@
         <v>131</v>
       </c>
       <c r="F18">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="G18">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="H18">
         <v>4.6</v>
       </c>
       <c r="I18">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J18">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K18">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L18">
         <v>1.27</v>
@@ -4908,46 +4908,46 @@
         <v>6.4</v>
       </c>
       <c r="O18">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P18">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="Q18">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="R18">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="S18">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="T18">
         <v>1.56</v>
       </c>
       <c r="U18">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="V18">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W18">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="X18">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Y18">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Z18">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AA18">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AB18">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC18">
         <v>11.5</v>
@@ -4959,7 +4959,7 @@
         <v>48</v>
       </c>
       <c r="AF18">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG18">
         <v>10.5</v>
@@ -4968,13 +4968,13 @@
         <v>15.5</v>
       </c>
       <c r="AI18">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ18">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AK18">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AL18">
         <v>24</v>
@@ -4983,16 +4983,16 @@
         <v>60</v>
       </c>
       <c r="AN18">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AO18">
         <v>34</v>
       </c>
       <c r="AP18">
+        <v>26</v>
+      </c>
+      <c r="AQ18">
         <v>24</v>
-      </c>
-      <c r="AQ18">
-        <v>22</v>
       </c>
       <c r="AR18">
         <v>38</v>
@@ -5004,16 +5004,16 @@
         <v>13</v>
       </c>
       <c r="AU18">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV18">
         <v>17</v>
       </c>
       <c r="AW18">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AX18">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY18">
         <v>9.6</v>
@@ -5022,7 +5022,7 @@
         <v>14.5</v>
       </c>
       <c r="BA18">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB18">
         <v>18</v>
@@ -5031,76 +5031,76 @@
         <v>14.5</v>
       </c>
       <c r="BD18">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BE18">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="BF18">
         <v>6.2</v>
       </c>
       <c r="BG18">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="BH18">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BI18">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BJ18">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK18">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BL18">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BM18">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BN18">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO18">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BP18">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ18">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BR18">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BS18">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT18">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU18">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BV18">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW18">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BX18">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY18">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BZ18">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="CA18">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="CB18" t="s">
         <v>133</v>
@@ -5126,13 +5126,13 @@
         <v>2.24</v>
       </c>
       <c r="G19">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H19">
+        <v>3</v>
+      </c>
+      <c r="I19">
         <v>3.1</v>
-      </c>
-      <c r="I19">
-        <v>3.15</v>
       </c>
       <c r="J19">
         <v>4.2</v>
@@ -5147,61 +5147,61 @@
         <v>1.02</v>
       </c>
       <c r="N19">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O19">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P19">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="Q19">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="R19">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="S19">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="T19">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="U19">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="V19">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W19">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X19">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="Y19">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="Z19">
         <v>32</v>
       </c>
       <c r="AA19">
-        <v>220</v>
+        <v>55</v>
       </c>
       <c r="AB19">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC19">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD19">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE19">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF19">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG19">
         <v>12.5</v>
@@ -5210,7 +5210,7 @@
         <v>13.5</v>
       </c>
       <c r="AI19">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AJ19">
         <v>34</v>
@@ -5219,58 +5219,58 @@
         <v>19.5</v>
       </c>
       <c r="AL19">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AM19">
         <v>42</v>
       </c>
       <c r="AN19">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AO19">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP19">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AQ19">
         <v>24</v>
       </c>
       <c r="AR19">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS19">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="AT19">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU19">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV19">
         <v>13.5</v>
       </c>
       <c r="AW19">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AX19">
+        <v>21</v>
+      </c>
+      <c r="AY19">
+        <v>11.5</v>
+      </c>
+      <c r="AZ19">
+        <v>12</v>
+      </c>
+      <c r="BA19">
+        <v>24</v>
+      </c>
+      <c r="BB19">
+        <v>30</v>
+      </c>
+      <c r="BC19">
         <v>17</v>
-      </c>
-      <c r="AY19">
-        <v>11</v>
-      </c>
-      <c r="AZ19">
-        <v>12.5</v>
-      </c>
-      <c r="BA19">
-        <v>25</v>
-      </c>
-      <c r="BB19">
-        <v>29</v>
-      </c>
-      <c r="BC19">
-        <v>17.5</v>
       </c>
       <c r="BD19">
         <v>20</v>
@@ -5285,64 +5285,64 @@
         <v>12</v>
       </c>
       <c r="BH19">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BI19">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BJ19">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BK19">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL19">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BM19">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN19">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO19">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BP19">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ19">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BR19">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BS19">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BT19">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU19">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BV19">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BW19">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BX19">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BY19">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BZ19">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="CA19">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="CB19" t="s">
         <v>133</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
@@ -391,7 +391,7 @@
     <t>Chicago Fire</t>
   </si>
   <si>
-    <t>2026-07-22 10:40:06</t>
+    <t>2026-07-22 12:47:32</t>
   </si>
 </sst>
 </file>
@@ -985,73 +985,73 @@
         <v>110</v>
       </c>
       <c r="F2">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G2">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H2">
         <v>2.22</v>
       </c>
       <c r="I2">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="J2">
         <v>3.95</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L2">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M2">
         <v>1.04</v>
       </c>
       <c r="N2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O2">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P2">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="Q2">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="R2">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="S2">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="T2">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="U2">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="V2">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W2">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA2">
         <v>28</v>
       </c>
       <c r="AB2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AC2">
         <v>9.4</v>
@@ -1063,16 +1063,16 @@
         <v>20</v>
       </c>
       <c r="AF2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AG2">
         <v>14.5</v>
       </c>
       <c r="AH2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AI2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ2">
         <v>55</v>
@@ -1084,31 +1084,31 @@
         <v>34</v>
       </c>
       <c r="AM2">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AN2">
         <v>19.5</v>
       </c>
       <c r="AO2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AP2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR2">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT2">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AU2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV2">
         <v>10.5</v>
@@ -1117,10 +1117,10 @@
         <v>18.5</v>
       </c>
       <c r="AX2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ2">
         <v>13</v>
@@ -1135,31 +1135,31 @@
         <v>28</v>
       </c>
       <c r="BD2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BE2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BF2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BG2">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BH2">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BI2">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BJ2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BL2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BM2">
         <v>55</v>
@@ -1171,16 +1171,16 @@
         <v>6.2</v>
       </c>
       <c r="BP2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BQ2">
         <v>19</v>
       </c>
       <c r="BR2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BS2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BT2">
         <v>5.5</v>
@@ -1189,22 +1189,22 @@
         <v>5.1</v>
       </c>
       <c r="BV2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BW2">
-        <v>8.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BX2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BY2">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="BZ2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="CA2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="CB2" t="s">
         <v>125</v>
@@ -1227,22 +1227,22 @@
         <v>111</v>
       </c>
       <c r="F3">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="G3">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="H3">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I3">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J3">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="K3">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="L3">
         <v>1.17</v>
@@ -1251,28 +1251,28 @@
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="O3">
         <v>1.07</v>
       </c>
       <c r="P3">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="Q3">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="R3">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="S3">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="T3">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="U3">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="V3">
         <v>1.01</v>
@@ -1281,13 +1281,13 @@
         <v>1.01</v>
       </c>
       <c r="X3">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="Y3">
         <v>940</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="AA3">
         <v>1000</v>
@@ -1302,34 +1302,34 @@
         <v>940</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>720</v>
       </c>
       <c r="AF3">
         <v>11</v>
       </c>
       <c r="AG3">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AH3">
-        <v>120</v>
+        <v>450</v>
       </c>
       <c r="AI3">
         <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AK3">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM3">
-        <v>490</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AO3">
         <v>1000</v>
@@ -1338,67 +1338,67 @@
         <v>55</v>
       </c>
       <c r="AQ3">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AR3">
-        <v>110</v>
+        <v>34</v>
       </c>
       <c r="AS3">
         <v>1000</v>
       </c>
       <c r="AT3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AU3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV3">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AW3">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AX3">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AZ3">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="BA3">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BB3">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BC3">
         <v>12.5</v>
       </c>
       <c r="BD3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BE3">
         <v>150</v>
       </c>
       <c r="BF3">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="BG3">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BI3">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>1.21</v>
+        <v>2.5</v>
       </c>
       <c r="BL3">
         <v>1000</v>
@@ -1407,10 +1407,10 @@
         <v>180</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO3">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="BP3">
         <v>1000</v>
@@ -1422,31 +1422,31 @@
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.21</v>
+        <v>3</v>
       </c>
       <c r="BT3">
         <v>1000</v>
       </c>
       <c r="BU3">
-        <v>1.21</v>
+        <v>3</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.21</v>
+        <v>2.94</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.21</v>
+        <v>2.94</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="CB3" t="s">
         <v>125</v>
@@ -1472,22 +1472,22 @@
         <v>2.38</v>
       </c>
       <c r="G4">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H4">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I4">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J4">
         <v>3</v>
       </c>
       <c r="K4">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L4">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="M4">
         <v>1.13</v>
@@ -1496,13 +1496,13 @@
         <v>2.84</v>
       </c>
       <c r="O4">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="P4">
         <v>1.58</v>
       </c>
       <c r="Q4">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R4">
         <v>1.21</v>
@@ -1511,19 +1511,19 @@
         <v>5.2</v>
       </c>
       <c r="T4">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U4">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="V4">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W4">
         <v>1.7</v>
       </c>
       <c r="X4">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y4">
         <v>12</v>
@@ -1556,7 +1556,7 @@
         <v>23</v>
       </c>
       <c r="AI4">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="AJ4">
         <v>36</v>
@@ -1571,22 +1571,22 @@
         <v>500</v>
       </c>
       <c r="AN4">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AO4">
         <v>110</v>
       </c>
       <c r="AP4">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AQ4">
         <v>9.6</v>
       </c>
       <c r="AR4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS4">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AT4">
         <v>6.4</v>
@@ -1595,7 +1595,7 @@
         <v>6.4</v>
       </c>
       <c r="AV4">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW4">
         <v>44</v>
@@ -1616,7 +1616,7 @@
         <v>24</v>
       </c>
       <c r="BC4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD4">
         <v>40</v>
@@ -1625,7 +1625,7 @@
         <v>65</v>
       </c>
       <c r="BF4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BG4">
         <v>55</v>
@@ -1711,16 +1711,16 @@
         <v>113</v>
       </c>
       <c r="F5">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="G5">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="H5">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="J5">
         <v>2.9</v>
@@ -1729,85 +1729,85 @@
         <v>3.15</v>
       </c>
       <c r="L5">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="M5">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N5">
-        <v>2.68</v>
+        <v>2.86</v>
       </c>
       <c r="O5">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="P5">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="Q5">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="R5">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S5">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="T5">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="U5">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="V5">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="W5">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="X5">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Y5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z5">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AA5">
         <v>250</v>
       </c>
       <c r="AB5">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC5">
         <v>7.2</v>
       </c>
       <c r="AD5">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE5">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="AF5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AG5">
         <v>13</v>
       </c>
       <c r="AH5">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI5">
         <v>190</v>
       </c>
       <c r="AJ5">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AK5">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AL5">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="AM5">
         <v>500</v>
@@ -1816,115 +1816,115 @@
         <v>38</v>
       </c>
       <c r="AO5">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="AP5">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ5">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR5">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AS5">
         <v>9.4</v>
       </c>
       <c r="AT5">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV5">
+        <v>12.5</v>
+      </c>
+      <c r="AW5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX5">
         <v>14</v>
-      </c>
-      <c r="AW5">
-        <v>23</v>
-      </c>
-      <c r="AX5">
-        <v>12</v>
       </c>
       <c r="AY5">
         <v>10.5</v>
       </c>
       <c r="AZ5">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA5">
-        <v>28</v>
+        <v>9.4</v>
       </c>
       <c r="BB5">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="BC5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD5">
-        <v>23</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE5">
         <v>10</v>
       </c>
       <c r="BF5">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH5">
+        <v>2.88</v>
+      </c>
+      <c r="BI5">
+        <v>2.34</v>
+      </c>
+      <c r="BJ5">
         <v>11</v>
       </c>
-      <c r="BH5">
-        <v>2.82</v>
-      </c>
-      <c r="BI5">
-        <v>2.26</v>
-      </c>
-      <c r="BJ5">
-        <v>11.5</v>
-      </c>
       <c r="BK5">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BN5">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BO5">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BP5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BQ5">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR5">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BS5">
+        <v>10</v>
+      </c>
+      <c r="BT5">
+        <v>6.4</v>
+      </c>
+      <c r="BU5">
+        <v>4.7</v>
+      </c>
+      <c r="BV5">
+        <v>30</v>
+      </c>
+      <c r="BW5">
         <v>9</v>
       </c>
-      <c r="BT5">
-        <v>6.8</v>
-      </c>
-      <c r="BU5">
-        <v>5</v>
-      </c>
-      <c r="BV5">
-        <v>38</v>
-      </c>
-      <c r="BW5">
-        <v>8.6</v>
-      </c>
       <c r="BX5">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BZ5">
         <v>0</v>
@@ -1983,22 +1983,22 @@
         <v>1.21</v>
       </c>
       <c r="P6">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q6">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R6">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S6">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T6">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="U6">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="V6">
         <v>1.05</v>
@@ -2019,13 +2019,13 @@
         <v>1000</v>
       </c>
       <c r="AB6">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AC6">
         <v>21</v>
       </c>
       <c r="AD6">
-        <v>510</v>
+        <v>950</v>
       </c>
       <c r="AE6">
         <v>440</v>
@@ -2040,10 +2040,10 @@
         <v>130</v>
       </c>
       <c r="AI6">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AJ6">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AK6">
         <v>15</v>
@@ -2052,7 +2052,7 @@
         <v>330</v>
       </c>
       <c r="AM6">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="AN6">
         <v>4.5</v>
@@ -2061,19 +2061,19 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ6">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AR6">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS6">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AT6">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU6">
         <v>14.5</v>
@@ -2082,61 +2082,61 @@
         <v>23</v>
       </c>
       <c r="AW6">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX6">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AY6">
         <v>10</v>
       </c>
       <c r="AZ6">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="BA6">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB6">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BC6">
         <v>12.5</v>
       </c>
       <c r="BD6">
-        <v>7.8</v>
+        <v>40</v>
       </c>
       <c r="BE6">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF6">
         <v>3.9</v>
       </c>
       <c r="BG6">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BH6">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BI6">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BJ6">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BK6">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN6">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BO6">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="BP6">
         <v>6.6</v>
@@ -2148,31 +2148,31 @@
         <v>26</v>
       </c>
       <c r="BS6">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BT6">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BU6">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ6">
         <v>10</v>
       </c>
       <c r="CA6">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="CB6" t="s">
         <v>125</v>
@@ -2201,40 +2201,40 @@
         <v>4.4</v>
       </c>
       <c r="H7">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="I7">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="J7">
+        <v>3.25</v>
+      </c>
+      <c r="K7">
         <v>3.3</v>
       </c>
-      <c r="K7">
-        <v>3.35</v>
-      </c>
       <c r="L7">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="M7">
         <v>1.1</v>
       </c>
       <c r="N7">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O7">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P7">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Q7">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="R7">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S7">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="T7">
         <v>2.04</v>
@@ -2243,7 +2243,7 @@
         <v>1.92</v>
       </c>
       <c r="V7">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="W7">
         <v>1.29</v>
@@ -2252,100 +2252,100 @@
         <v>10.5</v>
       </c>
       <c r="Y7">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="Z7">
         <v>11.5</v>
       </c>
       <c r="AA7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB7">
         <v>13</v>
       </c>
       <c r="AC7">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD7">
         <v>11</v>
       </c>
       <c r="AE7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF7">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AG7">
         <v>17.5</v>
       </c>
       <c r="AH7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI7">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AJ7">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AK7">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AL7">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="AM7">
         <v>490</v>
       </c>
       <c r="AN7">
-        <v>90</v>
+        <v>590</v>
       </c>
       <c r="AO7">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AP7">
         <v>9.800000000000001</v>
       </c>
       <c r="AQ7">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS7">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AT7">
         <v>12</v>
       </c>
       <c r="AU7">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW7">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AX7">
         <v>27</v>
       </c>
       <c r="AY7">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AZ7">
         <v>20</v>
       </c>
       <c r="BA7">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB7">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BC7">
         <v>55</v>
       </c>
       <c r="BD7">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BE7">
         <v>120</v>
@@ -2354,19 +2354,19 @@
         <v>75</v>
       </c>
       <c r="BG7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BH7">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BI7">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="BJ7">
         <v>10.5</v>
       </c>
       <c r="BK7">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BL7">
         <v>1000</v>
@@ -2378,10 +2378,10 @@
         <v>7.2</v>
       </c>
       <c r="BO7">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="BP7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BQ7">
         <v>13</v>
@@ -2390,7 +2390,7 @@
         <v>60</v>
       </c>
       <c r="BS7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BT7">
         <v>4.6</v>
@@ -2402,16 +2402,16 @@
         <v>16</v>
       </c>
       <c r="BW7">
-        <v>8.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="BX7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BY7">
         <v>12.5</v>
       </c>
       <c r="BZ7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CA7">
         <v>12.5</v>
@@ -2437,16 +2437,16 @@
         <v>116</v>
       </c>
       <c r="F8">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="G8">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="H8">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="I8">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="J8">
         <v>3.25</v>
@@ -2455,67 +2455,67 @@
         <v>3.35</v>
       </c>
       <c r="L8">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="M8">
         <v>1.11</v>
       </c>
       <c r="N8">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O8">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P8">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q8">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="R8">
         <v>1.25</v>
       </c>
       <c r="S8">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T8">
         <v>2.02</v>
       </c>
       <c r="U8">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="V8">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="W8">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="X8">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y8">
         <v>11.5</v>
       </c>
       <c r="Z8">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="AA8">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AB8">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AC8">
         <v>7.4</v>
       </c>
       <c r="AD8">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE8">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF8">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG8">
         <v>11.5</v>
@@ -2524,16 +2524,16 @@
         <v>21</v>
       </c>
       <c r="AI8">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ8">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK8">
         <v>30</v>
       </c>
       <c r="AL8">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AM8">
         <v>580</v>
@@ -2542,121 +2542,121 @@
         <v>28</v>
       </c>
       <c r="AO8">
-        <v>600</v>
+        <v>65</v>
       </c>
       <c r="AP8">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AQ8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS8">
+        <v>55</v>
+      </c>
+      <c r="AT8">
+        <v>7.4</v>
+      </c>
+      <c r="AU8">
+        <v>6.8</v>
+      </c>
+      <c r="AV8">
+        <v>14</v>
+      </c>
+      <c r="AW8">
+        <v>44</v>
+      </c>
+      <c r="AX8">
         <v>12.5</v>
       </c>
-      <c r="AT8">
+      <c r="AY8">
+        <v>10.5</v>
+      </c>
+      <c r="AZ8">
+        <v>19</v>
+      </c>
+      <c r="BA8">
+        <v>48</v>
+      </c>
+      <c r="BB8">
+        <v>27</v>
+      </c>
+      <c r="BC8">
+        <v>25</v>
+      </c>
+      <c r="BD8">
+        <v>44</v>
+      </c>
+      <c r="BE8">
+        <v>28</v>
+      </c>
+      <c r="BF8">
+        <v>23</v>
+      </c>
+      <c r="BG8">
+        <v>50</v>
+      </c>
+      <c r="BH8">
+        <v>2.92</v>
+      </c>
+      <c r="BI8">
+        <v>2.56</v>
+      </c>
+      <c r="BJ8">
+        <v>10.5</v>
+      </c>
+      <c r="BK8">
         <v>7</v>
-      </c>
-      <c r="AU8">
-        <v>6.6</v>
-      </c>
-      <c r="AV8">
-        <v>13.5</v>
-      </c>
-      <c r="AW8">
-        <v>38</v>
-      </c>
-      <c r="AX8">
-        <v>11.5</v>
-      </c>
-      <c r="AY8">
-        <v>10</v>
-      </c>
-      <c r="AZ8">
-        <v>18.5</v>
-      </c>
-      <c r="BA8">
-        <v>32</v>
-      </c>
-      <c r="BB8">
-        <v>23</v>
-      </c>
-      <c r="BC8">
-        <v>22</v>
-      </c>
-      <c r="BD8">
-        <v>36</v>
-      </c>
-      <c r="BE8">
-        <v>13</v>
-      </c>
-      <c r="BF8">
-        <v>20</v>
-      </c>
-      <c r="BG8">
-        <v>12</v>
-      </c>
-      <c r="BH8">
-        <v>2.88</v>
-      </c>
-      <c r="BI8">
-        <v>2.48</v>
-      </c>
-      <c r="BJ8">
-        <v>11</v>
-      </c>
-      <c r="BK8">
-        <v>6.8</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BN8">
         <v>4.9</v>
       </c>
       <c r="BO8">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP8">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BQ8">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BR8">
         <v>38</v>
       </c>
       <c r="BS8">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BT8">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU8">
         <v>5.4</v>
       </c>
       <c r="BV8">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BW8">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BX8">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BY8">
+        <v>15</v>
+      </c>
+      <c r="BZ8">
+        <v>38</v>
+      </c>
+      <c r="CA8">
         <v>13.5</v>
-      </c>
-      <c r="BZ8">
-        <v>40</v>
-      </c>
-      <c r="CA8">
-        <v>12.5</v>
       </c>
       <c r="CB8" t="s">
         <v>125</v>
@@ -2688,13 +2688,13 @@
         <v>11</v>
       </c>
       <c r="I9">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="J9">
         <v>5</v>
       </c>
       <c r="K9">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="L9">
         <v>1.4</v>
@@ -2703,7 +2703,7 @@
         <v>1.07</v>
       </c>
       <c r="N9">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O9">
         <v>1.32</v>
@@ -2724,25 +2724,25 @@
         <v>2.28</v>
       </c>
       <c r="U9">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V9">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W9">
         <v>3.55</v>
       </c>
       <c r="X9">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Y9">
         <v>34</v>
       </c>
       <c r="Z9">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AA9">
-        <v>520</v>
+        <v>610</v>
       </c>
       <c r="AB9">
         <v>7.2</v>
@@ -2754,7 +2754,7 @@
         <v>50</v>
       </c>
       <c r="AE9">
-        <v>280</v>
+        <v>240</v>
       </c>
       <c r="AF9">
         <v>7.6</v>
@@ -2763,7 +2763,7 @@
         <v>10.5</v>
       </c>
       <c r="AH9">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="AI9">
         <v>200</v>
@@ -2775,7 +2775,7 @@
         <v>16.5</v>
       </c>
       <c r="AL9">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="AM9">
         <v>240</v>
@@ -2793,13 +2793,13 @@
         <v>29</v>
       </c>
       <c r="AR9">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AS9">
         <v>16.5</v>
       </c>
       <c r="AT9">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU9">
         <v>10.5</v>
@@ -2808,13 +2808,13 @@
         <v>38</v>
       </c>
       <c r="AW9">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AX9">
         <v>6.6</v>
       </c>
       <c r="AY9">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ9">
         <v>30</v>
@@ -2826,7 +2826,7 @@
         <v>9.6</v>
       </c>
       <c r="BC9">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD9">
         <v>40</v>
@@ -2838,7 +2838,7 @@
         <v>6.2</v>
       </c>
       <c r="BG9">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BH9">
         <v>3.75</v>
@@ -2850,7 +2850,7 @@
         <v>13.5</v>
       </c>
       <c r="BK9">
-        <v>6</v>
+        <v>9.4</v>
       </c>
       <c r="BL9">
         <v>1000</v>
@@ -2862,13 +2862,13 @@
         <v>3.75</v>
       </c>
       <c r="BO9">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="BP9">
         <v>8.6</v>
       </c>
       <c r="BQ9">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BR9">
         <v>29</v>
@@ -2880,7 +2880,7 @@
         <v>14.5</v>
       </c>
       <c r="BU9">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BV9">
         <v>120</v>
@@ -2921,67 +2921,67 @@
         <v>118</v>
       </c>
       <c r="F10">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="G10">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="H10">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I10">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J10">
         <v>4.1</v>
       </c>
       <c r="K10">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L10">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M10">
         <v>1.04</v>
       </c>
       <c r="N10">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O10">
         <v>1.21</v>
       </c>
       <c r="P10">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q10">
+        <v>1.66</v>
+      </c>
+      <c r="R10">
+        <v>1.58</v>
+      </c>
+      <c r="S10">
+        <v>2.64</v>
+      </c>
+      <c r="T10">
         <v>1.64</v>
       </c>
-      <c r="R10">
-        <v>1.56</v>
-      </c>
-      <c r="S10">
-        <v>2.62</v>
-      </c>
-      <c r="T10">
-        <v>1.65</v>
-      </c>
       <c r="U10">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V10">
         <v>1.27</v>
       </c>
       <c r="W10">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="X10">
         <v>25</v>
       </c>
       <c r="Y10">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z10">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA10">
         <v>110</v>
@@ -2993,16 +2993,16 @@
         <v>10.5</v>
       </c>
       <c r="AD10">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE10">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF10">
         <v>14</v>
       </c>
       <c r="AG10">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH10">
         <v>18</v>
@@ -3017,19 +3017,19 @@
         <v>18</v>
       </c>
       <c r="AL10">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM10">
         <v>90</v>
       </c>
       <c r="AN10">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO10">
         <v>44</v>
       </c>
       <c r="AP10">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AQ10">
         <v>17.5</v>
@@ -3041,16 +3041,16 @@
         <v>60</v>
       </c>
       <c r="AT10">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AU10">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV10">
         <v>15</v>
       </c>
       <c r="AW10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AX10">
         <v>11</v>
@@ -3059,25 +3059,25 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ10">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BA10">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB10">
+        <v>16</v>
+      </c>
+      <c r="BC10">
         <v>14.5</v>
       </c>
-      <c r="BC10">
-        <v>13</v>
-      </c>
       <c r="BD10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE10">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF10">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BG10">
         <v>25</v>
@@ -3086,7 +3086,7 @@
         <v>4.3</v>
       </c>
       <c r="BI10">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BJ10">
         <v>9.4</v>
@@ -3110,13 +3110,13 @@
         <v>12.5</v>
       </c>
       <c r="BQ10">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BR10">
         <v>23</v>
       </c>
       <c r="BS10">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT10">
         <v>8.4</v>
@@ -3128,16 +3128,16 @@
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ10">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="CA10">
         <v>6.4</v>
@@ -3163,7 +3163,7 @@
         <v>119</v>
       </c>
       <c r="F11">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G11">
         <v>2.22</v>
@@ -3181,7 +3181,7 @@
         <v>3.4</v>
       </c>
       <c r="L11">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M11">
         <v>1.1</v>
@@ -3205,13 +3205,13 @@
         <v>4.5</v>
       </c>
       <c r="T11">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="U11">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V11">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W11">
         <v>1.81</v>
@@ -3226,7 +3226,7 @@
         <v>28</v>
       </c>
       <c r="AA11">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="AB11">
         <v>8</v>
@@ -3238,7 +3238,7 @@
         <v>17</v>
       </c>
       <c r="AE11">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="AF11">
         <v>13</v>
@@ -3250,10 +3250,10 @@
         <v>23</v>
       </c>
       <c r="AI11">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="AJ11">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AK11">
         <v>27</v>
@@ -3271,7 +3271,7 @@
         <v>85</v>
       </c>
       <c r="AP11">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ11">
         <v>11</v>
@@ -3280,7 +3280,7 @@
         <v>22</v>
       </c>
       <c r="AS11">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AT11">
         <v>7.2</v>
@@ -3292,7 +3292,7 @@
         <v>15</v>
       </c>
       <c r="AW11">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AX11">
         <v>11</v>
@@ -3301,10 +3301,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ11">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA11">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BB11">
         <v>25</v>
@@ -3316,10 +3316,10 @@
         <v>38</v>
       </c>
       <c r="BE11">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BF11">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BG11">
         <v>46</v>
@@ -3328,7 +3328,7 @@
         <v>3</v>
       </c>
       <c r="BI11">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BJ11">
         <v>10.5</v>
@@ -3358,7 +3358,7 @@
         <v>36</v>
       </c>
       <c r="BS11">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT11">
         <v>7.2</v>
@@ -3382,7 +3382,7 @@
         <v>36</v>
       </c>
       <c r="CA11">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CB11" t="s">
         <v>125</v>
@@ -3405,226 +3405,226 @@
         <v>120</v>
       </c>
       <c r="F12">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="G12">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="H12">
+        <v>4.2</v>
+      </c>
+      <c r="I12">
+        <v>4.4</v>
+      </c>
+      <c r="J12">
+        <v>3.85</v>
+      </c>
+      <c r="K12">
         <v>3.95</v>
       </c>
-      <c r="I12">
-        <v>4.1</v>
-      </c>
-      <c r="J12">
-        <v>3.8</v>
-      </c>
-      <c r="K12">
-        <v>3.9</v>
-      </c>
       <c r="L12">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M12">
         <v>1.06</v>
       </c>
       <c r="N12">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O12">
         <v>1.29</v>
       </c>
       <c r="P12">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="Q12">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="R12">
         <v>1.42</v>
       </c>
       <c r="S12">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T12">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="U12">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="V12">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="W12">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="X12">
+        <v>16</v>
+      </c>
+      <c r="Y12">
         <v>17</v>
       </c>
-      <c r="Y12">
-        <v>16.5</v>
-      </c>
       <c r="Z12">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AA12">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB12">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC12">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD12">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AE12">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AF12">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG12">
         <v>10.5</v>
       </c>
       <c r="AH12">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI12">
         <v>55</v>
       </c>
       <c r="AJ12">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AK12">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AL12">
         <v>34</v>
       </c>
       <c r="AM12">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AN12">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO12">
+        <v>55</v>
+      </c>
+      <c r="AP12">
+        <v>14.5</v>
+      </c>
+      <c r="AQ12">
+        <v>15</v>
+      </c>
+      <c r="AR12">
+        <v>29</v>
+      </c>
+      <c r="AS12">
+        <v>60</v>
+      </c>
+      <c r="AT12">
+        <v>9</v>
+      </c>
+      <c r="AU12">
+        <v>8</v>
+      </c>
+      <c r="AV12">
+        <v>15.5</v>
+      </c>
+      <c r="AW12">
         <v>44</v>
       </c>
-      <c r="AP12">
-        <v>15</v>
-      </c>
-      <c r="AQ12">
-        <v>14.5</v>
-      </c>
-      <c r="AR12">
-        <v>26</v>
-      </c>
-      <c r="AS12">
-        <v>55</v>
-      </c>
-      <c r="AT12">
-        <v>9.4</v>
-      </c>
-      <c r="AU12">
-        <v>7.8</v>
-      </c>
-      <c r="AV12">
-        <v>14.5</v>
-      </c>
-      <c r="AW12">
-        <v>36</v>
-      </c>
       <c r="AX12">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY12">
         <v>9.6</v>
       </c>
       <c r="AZ12">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA12">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="BB12">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BC12">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE12">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="BF12">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BG12">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BH12">
         <v>3.7</v>
       </c>
       <c r="BI12">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="BJ12">
         <v>9.800000000000001</v>
       </c>
       <c r="BK12">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BL12">
         <v>120</v>
       </c>
       <c r="BM12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN12">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO12">
         <v>3.75</v>
       </c>
       <c r="BP12">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BQ12">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR12">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BS12">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BT12">
         <v>7.8</v>
       </c>
       <c r="BU12">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BV12">
         <v>34</v>
       </c>
       <c r="BW12">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX12">
         <v>42</v>
       </c>
       <c r="BY12">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BZ12">
         <v>23</v>
       </c>
       <c r="CA12">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="CB12" t="s">
         <v>125</v>
@@ -3656,55 +3656,55 @@
         <v>3.7</v>
       </c>
       <c r="I13">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J13">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K13">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L13">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M13">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N13">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O13">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P13">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q13">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="R13">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S13">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="T13">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U13">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V13">
         <v>1.36</v>
       </c>
       <c r="W13">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="X13">
         <v>17.5</v>
       </c>
       <c r="Y13">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z13">
         <v>28</v>
@@ -3716,7 +3716,7 @@
         <v>11.5</v>
       </c>
       <c r="AC13">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD13">
         <v>15</v>
@@ -3725,19 +3725,19 @@
         <v>40</v>
       </c>
       <c r="AF13">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG13">
         <v>11</v>
       </c>
       <c r="AH13">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI13">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ13">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK13">
         <v>21</v>
@@ -3746,13 +3746,13 @@
         <v>32</v>
       </c>
       <c r="AM13">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN13">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO13">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP13">
         <v>16</v>
@@ -3764,7 +3764,7 @@
         <v>25</v>
       </c>
       <c r="AS13">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AT13">
         <v>10</v>
@@ -3776,16 +3776,16 @@
         <v>14</v>
       </c>
       <c r="AW13">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AX13">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY13">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ13">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA13">
         <v>40</v>
@@ -3794,7 +3794,7 @@
         <v>22</v>
       </c>
       <c r="BC13">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD13">
         <v>28</v>
@@ -3806,22 +3806,22 @@
         <v>11</v>
       </c>
       <c r="BG13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BH13">
         <v>3.9</v>
       </c>
       <c r="BI13">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="BJ13">
         <v>9.4</v>
       </c>
       <c r="BK13">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BL13">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BM13">
         <v>11</v>
@@ -3830,43 +3830,43 @@
         <v>5.1</v>
       </c>
       <c r="BO13">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="BP13">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BQ13">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR13">
         <v>26</v>
       </c>
       <c r="BS13">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT13">
         <v>7.4</v>
       </c>
       <c r="BU13">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BV13">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BW13">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BX13">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BY13">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ13">
         <v>21</v>
       </c>
       <c r="CA13">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB13" t="s">
         <v>125</v>
@@ -3913,22 +3913,22 @@
         <v>1.03</v>
       </c>
       <c r="N14">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O14">
         <v>1.16</v>
       </c>
       <c r="P14">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="Q14">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="R14">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="S14">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="T14">
         <v>1.56</v>
@@ -3940,7 +3940,7 @@
         <v>1.27</v>
       </c>
       <c r="W14">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X14">
         <v>29</v>
@@ -3952,16 +3952,16 @@
         <v>42</v>
       </c>
       <c r="AA14">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB14">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC14">
         <v>11</v>
       </c>
       <c r="AD14">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE14">
         <v>46</v>
@@ -3982,7 +3982,7 @@
         <v>20</v>
       </c>
       <c r="AK14">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL14">
         <v>24</v>
@@ -4021,13 +4021,13 @@
         <v>40</v>
       </c>
       <c r="AX14">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY14">
         <v>9.6</v>
       </c>
       <c r="AZ14">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA14">
         <v>38</v>
@@ -4045,58 +4045,58 @@
         <v>50</v>
       </c>
       <c r="BF14">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG14">
         <v>28</v>
       </c>
       <c r="BH14">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI14">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BJ14">
         <v>8.800000000000001</v>
       </c>
       <c r="BK14">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL14">
         <v>75</v>
       </c>
       <c r="BM14">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN14">
         <v>4.9</v>
       </c>
       <c r="BO14">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BP14">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BQ14">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR14">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BS14">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT14">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BU14">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BV14">
         <v>32</v>
       </c>
       <c r="BW14">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX14">
         <v>34</v>
@@ -4108,7 +4108,7 @@
         <v>12.5</v>
       </c>
       <c r="CA14">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB14" t="s">
         <v>125</v>
@@ -4131,22 +4131,22 @@
         <v>123</v>
       </c>
       <c r="F15">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="G15">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H15">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="I15">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="J15">
         <v>4.4</v>
       </c>
       <c r="K15">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L15">
         <v>1.23</v>
@@ -4161,34 +4161,34 @@
         <v>1.13</v>
       </c>
       <c r="P15">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="Q15">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="R15">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="S15">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="T15">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="U15">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="V15">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="W15">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X15">
         <v>36</v>
       </c>
       <c r="Y15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z15">
         <v>18</v>
@@ -4206,7 +4206,7 @@
         <v>11.5</v>
       </c>
       <c r="AE15">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AF15">
         <v>40</v>
@@ -4221,19 +4221,19 @@
         <v>21</v>
       </c>
       <c r="AJ15">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AK15">
         <v>36</v>
       </c>
       <c r="AL15">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM15">
         <v>42</v>
       </c>
       <c r="AN15">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO15">
         <v>6.2</v>
@@ -4242,7 +4242,7 @@
         <v>32</v>
       </c>
       <c r="AQ15">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR15">
         <v>16</v>
@@ -4254,16 +4254,16 @@
         <v>27</v>
       </c>
       <c r="AU15">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AV15">
         <v>10.5</v>
       </c>
       <c r="AW15">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AX15">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AY15">
         <v>16</v>
@@ -4272,7 +4272,7 @@
         <v>13</v>
       </c>
       <c r="BA15">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BB15">
         <v>60</v>
@@ -4281,16 +4281,16 @@
         <v>32</v>
       </c>
       <c r="BD15">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BE15">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BF15">
         <v>18</v>
       </c>
       <c r="BG15">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BH15">
         <v>5.6</v>
@@ -4308,7 +4308,7 @@
         <v>60</v>
       </c>
       <c r="BM15">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN15">
         <v>8.4</v>
@@ -4317,7 +4317,7 @@
         <v>6</v>
       </c>
       <c r="BP15">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BQ15">
         <v>7.6</v>
@@ -4332,13 +4332,13 @@
         <v>5.7</v>
       </c>
       <c r="BU15">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BV15">
         <v>12</v>
       </c>
       <c r="BW15">
-        <v>5.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX15">
         <v>18.5</v>
@@ -4350,7 +4350,7 @@
         <v>11</v>
       </c>
       <c r="CA15">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="CB15" t="s">
         <v>125</v>
@@ -4373,16 +4373,16 @@
         <v>124</v>
       </c>
       <c r="F16">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="G16">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="H16">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="I16">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="J16">
         <v>4.2</v>
@@ -4403,79 +4403,79 @@
         <v>1.11</v>
       </c>
       <c r="P16">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="Q16">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="R16">
         <v>2.04</v>
       </c>
       <c r="S16">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="T16">
         <v>1.38</v>
       </c>
       <c r="U16">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="V16">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="W16">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="X16">
         <v>40</v>
       </c>
       <c r="Y16">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Z16">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA16">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB16">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AC16">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD16">
         <v>14.5</v>
       </c>
       <c r="AE16">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AF16">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG16">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH16">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AI16">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ16">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK16">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM16">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AN16">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AO16">
         <v>12</v>
@@ -4487,22 +4487,22 @@
         <v>24</v>
       </c>
       <c r="AR16">
-        <v>27</v>
+        <v>19.5</v>
       </c>
       <c r="AS16">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AT16">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU16">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV16">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW16">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX16">
         <v>22</v>
@@ -4520,37 +4520,37 @@
         <v>34</v>
       </c>
       <c r="BC16">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD16">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE16">
         <v>34</v>
       </c>
       <c r="BF16">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG16">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH16">
         <v>5.9</v>
       </c>
       <c r="BI16">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BJ16">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK16">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL16">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BM16">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BN16">
         <v>6.6</v>
@@ -4562,13 +4562,13 @@
         <v>15.5</v>
       </c>
       <c r="BQ16">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR16">
         <v>19.5</v>
       </c>
       <c r="BS16">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT16">
         <v>7.2</v>
@@ -4577,7 +4577,7 @@
         <v>6</v>
       </c>
       <c r="BV16">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BW16">
         <v>11</v>
@@ -4586,7 +4586,7 @@
         <v>21</v>
       </c>
       <c r="BY16">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ16">
         <v>10.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
@@ -391,7 +391,7 @@
     <t>Chicago Fire</t>
   </si>
   <si>
-    <t>2026-07-22 12:47:32</t>
+    <t>2026-07-22 14:55:41</t>
   </si>
 </sst>
 </file>
@@ -985,226 +985,226 @@
         <v>110</v>
       </c>
       <c r="F2">
-        <v>3.3</v>
+        <v>10.5</v>
       </c>
       <c r="G2">
-        <v>3.4</v>
+        <v>11</v>
       </c>
       <c r="H2">
+        <v>1.41</v>
+      </c>
+      <c r="I2">
+        <v>1.42</v>
+      </c>
+      <c r="J2">
+        <v>4.9</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>6.4</v>
+      </c>
+      <c r="O2">
+        <v>1.17</v>
+      </c>
+      <c r="P2">
         <v>2.22</v>
       </c>
-      <c r="I2">
-        <v>2.24</v>
-      </c>
-      <c r="J2">
-        <v>3.95</v>
-      </c>
-      <c r="K2">
-        <v>4.1</v>
-      </c>
-      <c r="L2">
-        <v>1.28</v>
-      </c>
-      <c r="M2">
-        <v>1.04</v>
-      </c>
-      <c r="N2">
+      <c r="Q2">
+        <v>1.8</v>
+      </c>
+      <c r="R2">
+        <v>1.38</v>
+      </c>
+      <c r="S2">
+        <v>3.55</v>
+      </c>
+      <c r="T2">
+        <v>1.64</v>
+      </c>
+      <c r="U2">
+        <v>2.2</v>
+      </c>
+      <c r="V2">
+        <v>3.35</v>
+      </c>
+      <c r="W2">
+        <v>1.1</v>
+      </c>
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>7</v>
+      </c>
+      <c r="Z2">
+        <v>7.4</v>
+      </c>
+      <c r="AA2">
+        <v>13</v>
+      </c>
+      <c r="AB2">
+        <v>1000</v>
+      </c>
+      <c r="AC2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD2">
+        <v>7.8</v>
+      </c>
+      <c r="AE2">
+        <v>60</v>
+      </c>
+      <c r="AF2">
+        <v>1000</v>
+      </c>
+      <c r="AG2">
+        <v>790</v>
+      </c>
+      <c r="AH2">
+        <v>990</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>13.5</v>
+      </c>
+      <c r="AP2">
+        <v>5.4</v>
+      </c>
+      <c r="AQ2">
         <v>6.2</v>
       </c>
-      <c r="O2">
-        <v>1.18</v>
-      </c>
-      <c r="P2">
-        <v>2.74</v>
-      </c>
-      <c r="Q2">
-        <v>1.55</v>
-      </c>
-      <c r="R2">
-        <v>1.7</v>
-      </c>
-      <c r="S2">
-        <v>2.38</v>
-      </c>
-      <c r="T2">
-        <v>1.51</v>
-      </c>
-      <c r="U2">
-        <v>2.84</v>
-      </c>
-      <c r="V2">
-        <v>1.8</v>
-      </c>
-      <c r="W2">
-        <v>1.41</v>
-      </c>
-      <c r="X2">
-        <v>26</v>
-      </c>
-      <c r="Y2">
-        <v>16</v>
-      </c>
-      <c r="Z2">
-        <v>17.5</v>
-      </c>
-      <c r="AA2">
+      <c r="AR2">
+        <v>6.2</v>
+      </c>
+      <c r="AS2">
+        <v>10.5</v>
+      </c>
+      <c r="AT2">
+        <v>4.2</v>
+      </c>
+      <c r="AU2">
+        <v>6.6</v>
+      </c>
+      <c r="AV2">
+        <v>6.2</v>
+      </c>
+      <c r="AW2">
+        <v>13.5</v>
+      </c>
+      <c r="AX2">
+        <v>4.3</v>
+      </c>
+      <c r="AY2">
+        <v>11</v>
+      </c>
+      <c r="AZ2">
+        <v>14.5</v>
+      </c>
+      <c r="BA2">
         <v>28</v>
       </c>
-      <c r="AB2">
-        <v>21</v>
-      </c>
-      <c r="AC2">
-        <v>9.4</v>
-      </c>
-      <c r="AD2">
+      <c r="BB2">
+        <v>4.3</v>
+      </c>
+      <c r="BC2">
+        <v>60</v>
+      </c>
+      <c r="BD2">
+        <v>55</v>
+      </c>
+      <c r="BE2">
+        <v>95</v>
+      </c>
+      <c r="BF2">
+        <v>100</v>
+      </c>
+      <c r="BG2">
         <v>11.5</v>
       </c>
-      <c r="AE2">
-        <v>20</v>
-      </c>
-      <c r="AF2">
-        <v>28</v>
-      </c>
-      <c r="AG2">
-        <v>14.5</v>
-      </c>
-      <c r="AH2">
-        <v>13.5</v>
-      </c>
-      <c r="AI2">
-        <v>26</v>
-      </c>
-      <c r="AJ2">
-        <v>55</v>
-      </c>
-      <c r="AK2">
-        <v>30</v>
-      </c>
-      <c r="AL2">
-        <v>34</v>
-      </c>
-      <c r="AM2">
-        <v>48</v>
-      </c>
-      <c r="AN2">
-        <v>19.5</v>
-      </c>
-      <c r="AO2">
-        <v>10.5</v>
-      </c>
-      <c r="AP2">
-        <v>23</v>
-      </c>
-      <c r="AQ2">
-        <v>14.5</v>
-      </c>
-      <c r="AR2">
-        <v>16.5</v>
-      </c>
-      <c r="AS2">
-        <v>26</v>
-      </c>
-      <c r="AT2">
-        <v>19</v>
-      </c>
-      <c r="AU2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV2">
-        <v>10.5</v>
-      </c>
-      <c r="AW2">
-        <v>18.5</v>
-      </c>
-      <c r="AX2">
-        <v>25</v>
-      </c>
-      <c r="AY2">
-        <v>13.5</v>
-      </c>
-      <c r="AZ2">
-        <v>13</v>
-      </c>
-      <c r="BA2">
-        <v>24</v>
-      </c>
-      <c r="BB2">
-        <v>46</v>
-      </c>
-      <c r="BC2">
-        <v>28</v>
-      </c>
-      <c r="BD2">
-        <v>29</v>
-      </c>
-      <c r="BE2">
-        <v>42</v>
-      </c>
-      <c r="BF2">
-        <v>17</v>
-      </c>
-      <c r="BG2">
-        <v>9.6</v>
-      </c>
       <c r="BH2">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
         <v>125</v>
@@ -1227,226 +1227,226 @@
         <v>111</v>
       </c>
       <c r="F3">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="G3">
+        <v>1.06</v>
+      </c>
+      <c r="H3">
+        <v>100</v>
+      </c>
+      <c r="I3">
+        <v>1000</v>
+      </c>
+      <c r="J3">
+        <v>19</v>
+      </c>
+      <c r="K3">
+        <v>22</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>10</v>
+      </c>
+      <c r="O3">
         <v>1.1</v>
       </c>
-      <c r="H3">
-        <v>38</v>
-      </c>
-      <c r="I3">
-        <v>44</v>
-      </c>
-      <c r="J3">
-        <v>14.5</v>
-      </c>
-      <c r="K3">
-        <v>16.5</v>
-      </c>
-      <c r="L3">
-        <v>1.17</v>
-      </c>
-      <c r="M3">
-        <v>1.01</v>
-      </c>
-      <c r="N3">
-        <v>13</v>
-      </c>
-      <c r="O3">
-        <v>1.07</v>
-      </c>
       <c r="P3">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="Q3">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="R3">
-        <v>2.56</v>
+        <v>1.7</v>
       </c>
       <c r="S3">
-        <v>1.63</v>
+        <v>2.4</v>
       </c>
       <c r="T3">
-        <v>2.16</v>
+        <v>2.96</v>
       </c>
       <c r="U3">
-        <v>1.83</v>
+        <v>1.43</v>
       </c>
       <c r="V3">
         <v>1.01</v>
       </c>
       <c r="W3">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="X3">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="Y3">
-        <v>940</v>
+        <v>1000</v>
       </c>
       <c r="Z3">
-        <v>420</v>
+        <v>1000</v>
       </c>
       <c r="AA3">
         <v>1000</v>
       </c>
       <c r="AB3">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="AC3">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AD3">
-        <v>940</v>
+        <v>880</v>
       </c>
       <c r="AE3">
-        <v>720</v>
+        <v>1000</v>
       </c>
       <c r="AF3">
-        <v>11</v>
+        <v>5.7</v>
       </c>
       <c r="AG3">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AH3">
-        <v>450</v>
+        <v>990</v>
       </c>
       <c r="AI3">
         <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="AK3">
-        <v>14.5</v>
+        <v>980</v>
       </c>
       <c r="AL3">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
         <v>1000</v>
       </c>
       <c r="AN3">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="AO3">
         <v>1000</v>
       </c>
       <c r="AP3">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AQ3">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AR3">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AS3">
         <v>1000</v>
       </c>
       <c r="AT3">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AU3">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="AV3">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="AW3">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="AX3">
-        <v>9.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="AY3">
-        <v>14</v>
+        <v>4.6</v>
       </c>
       <c r="AZ3">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="BA3">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="BB3">
+        <v>4.5</v>
+      </c>
+      <c r="BC3">
+        <v>9.6</v>
+      </c>
+      <c r="BD3">
+        <v>17</v>
+      </c>
+      <c r="BE3">
+        <v>46</v>
+      </c>
+      <c r="BF3">
+        <v>3.1</v>
+      </c>
+      <c r="BG3">
         <v>7.8</v>
       </c>
-      <c r="BC3">
-        <v>12.5</v>
-      </c>
-      <c r="BD3">
-        <v>28</v>
-      </c>
-      <c r="BE3">
-        <v>150</v>
-      </c>
-      <c r="BF3">
-        <v>2.04</v>
-      </c>
-      <c r="BG3">
-        <v>55</v>
-      </c>
       <c r="BH3">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BI3">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK3">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="BN3">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BO3">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ3">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW3">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY3">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA3">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="s">
         <v>125</v>
@@ -1469,22 +1469,22 @@
         <v>112</v>
       </c>
       <c r="F4">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="G4">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H4">
         <v>3.85</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K4">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L4">
         <v>1.58</v>
@@ -1493,7 +1493,7 @@
         <v>1.13</v>
       </c>
       <c r="N4">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="O4">
         <v>1.51</v>
@@ -1502,34 +1502,34 @@
         <v>1.58</v>
       </c>
       <c r="Q4">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="R4">
         <v>1.21</v>
       </c>
       <c r="S4">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="T4">
         <v>2.06</v>
       </c>
       <c r="U4">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V4">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W4">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="X4">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y4">
         <v>12</v>
       </c>
       <c r="Z4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA4">
         <v>290</v>
@@ -1538,13 +1538,13 @@
         <v>7.6</v>
       </c>
       <c r="AC4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD4">
         <v>17.5</v>
       </c>
       <c r="AE4">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="AF4">
         <v>13.5</v>
@@ -1556,10 +1556,10 @@
         <v>23</v>
       </c>
       <c r="AI4">
-        <v>110</v>
+        <v>380</v>
       </c>
       <c r="AJ4">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK4">
         <v>34</v>
@@ -1571,46 +1571,46 @@
         <v>500</v>
       </c>
       <c r="AN4">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AO4">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP4">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AQ4">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AR4">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="AS4">
-        <v>55</v>
+        <v>11.5</v>
       </c>
       <c r="AT4">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU4">
         <v>6.4</v>
       </c>
       <c r="AV4">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW4">
         <v>44</v>
       </c>
       <c r="AX4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ4">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="BA4">
-        <v>55</v>
+        <v>11.5</v>
       </c>
       <c r="BB4">
         <v>24</v>
@@ -1619,16 +1619,16 @@
         <v>24</v>
       </c>
       <c r="BD4">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="BE4">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="BF4">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BG4">
-        <v>55</v>
+        <v>10.5</v>
       </c>
       <c r="BH4">
         <v>2.78</v>
@@ -1646,7 +1646,7 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN4">
         <v>5</v>
@@ -1658,7 +1658,7 @@
         <v>21</v>
       </c>
       <c r="BQ4">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR4">
         <v>1000</v>
@@ -1682,13 +1682,13 @@
         <v>60</v>
       </c>
       <c r="BY4">
+        <v>12</v>
+      </c>
+      <c r="BZ4">
+        <v>1000</v>
+      </c>
+      <c r="CA4">
         <v>11.5</v>
-      </c>
-      <c r="BZ4">
-        <v>48</v>
-      </c>
-      <c r="CA4">
-        <v>11</v>
       </c>
       <c r="CB4" t="s">
         <v>125</v>
@@ -1711,16 +1711,16 @@
         <v>113</v>
       </c>
       <c r="F5">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G5">
         <v>2.78</v>
       </c>
       <c r="H5">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I5">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J5">
         <v>2.9</v>
@@ -1738,31 +1738,31 @@
         <v>2.86</v>
       </c>
       <c r="O5">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P5">
         <v>1.59</v>
       </c>
       <c r="Q5">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="R5">
         <v>1.22</v>
       </c>
       <c r="S5">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T5">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U5">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="V5">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W5">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X5">
         <v>9.6</v>
@@ -1771,13 +1771,13 @@
         <v>10.5</v>
       </c>
       <c r="Z5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA5">
-        <v>250</v>
+        <v>85</v>
       </c>
       <c r="AB5">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC5">
         <v>7.2</v>
@@ -1786,10 +1786,10 @@
         <v>15.5</v>
       </c>
       <c r="AE5">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="AF5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG5">
         <v>13</v>
@@ -1798,16 +1798,16 @@
         <v>21</v>
       </c>
       <c r="AI5">
-        <v>190</v>
+        <v>100</v>
       </c>
       <c r="AJ5">
         <v>44</v>
       </c>
       <c r="AK5">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL5">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AM5">
         <v>500</v>
@@ -1816,19 +1816,19 @@
         <v>38</v>
       </c>
       <c r="AO5">
-        <v>180</v>
+        <v>85</v>
       </c>
       <c r="AP5">
         <v>8.199999999999999</v>
       </c>
       <c r="AQ5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR5">
         <v>18.5</v>
       </c>
       <c r="AS5">
-        <v>9.4</v>
+        <v>46</v>
       </c>
       <c r="AT5">
         <v>7.4</v>
@@ -1840,10 +1840,10 @@
         <v>12.5</v>
       </c>
       <c r="AW5">
-        <v>8.800000000000001</v>
+        <v>29</v>
       </c>
       <c r="AX5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY5">
         <v>10.5</v>
@@ -1852,25 +1852,25 @@
         <v>18</v>
       </c>
       <c r="BA5">
-        <v>9.4</v>
+        <v>42</v>
       </c>
       <c r="BB5">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="BC5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD5">
-        <v>9.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="BE5">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="BF5">
-        <v>8.4</v>
+        <v>24</v>
       </c>
       <c r="BG5">
-        <v>9.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="BH5">
         <v>2.88</v>
@@ -1891,13 +1891,13 @@
         <v>12</v>
       </c>
       <c r="BN5">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BO5">
         <v>4.1</v>
       </c>
       <c r="BP5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BQ5">
         <v>8.199999999999999</v>
@@ -1906,16 +1906,16 @@
         <v>44</v>
       </c>
       <c r="BS5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT5">
         <v>6.4</v>
       </c>
       <c r="BU5">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV5">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BW5">
         <v>9</v>
@@ -1959,52 +1959,52 @@
         <v>1.24</v>
       </c>
       <c r="H6">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="I6">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="J6">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="K6">
         <v>7.8</v>
       </c>
       <c r="L6">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M6">
         <v>1.04</v>
       </c>
       <c r="N6">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O6">
         <v>1.21</v>
       </c>
       <c r="P6">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="Q6">
         <v>1.63</v>
       </c>
       <c r="R6">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S6">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="T6">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U6">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="V6">
         <v>1.05</v>
       </c>
       <c r="W6">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="X6">
         <v>30</v>
@@ -2013,22 +2013,22 @@
         <v>55</v>
       </c>
       <c r="Z6">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AA6">
         <v>1000</v>
       </c>
       <c r="AB6">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AC6">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AD6">
         <v>950</v>
       </c>
       <c r="AE6">
-        <v>440</v>
+        <v>410</v>
       </c>
       <c r="AF6">
         <v>7.4</v>
@@ -2037,13 +2037,13 @@
         <v>14.5</v>
       </c>
       <c r="AH6">
-        <v>130</v>
+        <v>950</v>
       </c>
       <c r="AI6">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="AJ6">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AK6">
         <v>15</v>
@@ -2055,46 +2055,46 @@
         <v>320</v>
       </c>
       <c r="AN6">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AO6">
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AQ6">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="AR6">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="AS6">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT6">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU6">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AV6">
-        <v>23</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW6">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="AX6">
         <v>6.2</v>
       </c>
       <c r="AY6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ6">
         <v>36</v>
       </c>
       <c r="BA6">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="BB6">
         <v>7.4</v>
@@ -2106,34 +2106,34 @@
         <v>40</v>
       </c>
       <c r="BE6">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="BF6">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BG6">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BH6">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BI6">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BJ6">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BK6">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="BN6">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BO6">
         <v>3.2</v>
@@ -2142,37 +2142,37 @@
         <v>6.6</v>
       </c>
       <c r="BQ6">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BR6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BS6">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BT6">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BU6">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BZ6">
         <v>10</v>
       </c>
       <c r="CA6">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="CB6" t="s">
         <v>125</v>
@@ -2195,16 +2195,16 @@
         <v>115</v>
       </c>
       <c r="F7">
+        <v>4.2</v>
+      </c>
+      <c r="G7">
         <v>4.3</v>
       </c>
-      <c r="G7">
-        <v>4.4</v>
-      </c>
       <c r="H7">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="I7">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="J7">
         <v>3.25</v>
@@ -2213,22 +2213,22 @@
         <v>3.3</v>
       </c>
       <c r="L7">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M7">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N7">
         <v>3.1</v>
       </c>
       <c r="O7">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P7">
         <v>1.67</v>
       </c>
       <c r="Q7">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R7">
         <v>1.25</v>
@@ -2243,31 +2243,31 @@
         <v>1.92</v>
       </c>
       <c r="V7">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="W7">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X7">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="Y7">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="Z7">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AA7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB7">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC7">
         <v>7</v>
       </c>
       <c r="AD7">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE7">
         <v>26</v>
@@ -2276,61 +2276,61 @@
         <v>29</v>
       </c>
       <c r="AG7">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH7">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI7">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ7">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AK7">
         <v>65</v>
       </c>
       <c r="AL7">
-        <v>200</v>
+        <v>85</v>
       </c>
       <c r="AM7">
         <v>490</v>
       </c>
       <c r="AN7">
-        <v>590</v>
+        <v>490</v>
       </c>
       <c r="AO7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP7">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ7">
         <v>7.4</v>
       </c>
       <c r="AR7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS7">
         <v>24</v>
       </c>
       <c r="AT7">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU7">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV7">
         <v>10.5</v>
       </c>
       <c r="AW7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX7">
         <v>27</v>
       </c>
       <c r="AY7">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AZ7">
         <v>20</v>
@@ -2339,7 +2339,7 @@
         <v>48</v>
       </c>
       <c r="BB7">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BC7">
         <v>55</v>
@@ -2354,19 +2354,19 @@
         <v>75</v>
       </c>
       <c r="BG7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BH7">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="BI7">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="BJ7">
         <v>10.5</v>
       </c>
       <c r="BK7">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BL7">
         <v>1000</v>
@@ -2375,46 +2375,46 @@
         <v>140</v>
       </c>
       <c r="BN7">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BO7">
         <v>5.3</v>
       </c>
       <c r="BP7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BQ7">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="BR7">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BS7">
         <v>15</v>
       </c>
       <c r="BT7">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BU7">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BV7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BW7">
-        <v>14.5</v>
+        <v>9.4</v>
       </c>
       <c r="BX7">
         <v>36</v>
       </c>
       <c r="BY7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ7">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CA7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="CB7" t="s">
         <v>125</v>
@@ -2437,25 +2437,25 @@
         <v>116</v>
       </c>
       <c r="F8">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G8">
         <v>2.4</v>
       </c>
       <c r="H8">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="I8">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="J8">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K8">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L8">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M8">
         <v>1.11</v>
@@ -2464,19 +2464,19 @@
         <v>3.05</v>
       </c>
       <c r="O8">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P8">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q8">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="R8">
         <v>1.25</v>
       </c>
       <c r="S8">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T8">
         <v>2.02</v>
@@ -2485,10 +2485,10 @@
         <v>1.92</v>
       </c>
       <c r="V8">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W8">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X8">
         <v>10</v>
@@ -2503,7 +2503,7 @@
         <v>75</v>
       </c>
       <c r="AB8">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AC8">
         <v>7.4</v>
@@ -2515,7 +2515,7 @@
         <v>55</v>
       </c>
       <c r="AF8">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG8">
         <v>11.5</v>
@@ -2524,28 +2524,28 @@
         <v>21</v>
       </c>
       <c r="AI8">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="AJ8">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK8">
         <v>30</v>
       </c>
       <c r="AL8">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AM8">
-        <v>580</v>
+        <v>150</v>
       </c>
       <c r="AN8">
         <v>28</v>
       </c>
       <c r="AO8">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AP8">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ8">
         <v>10.5</v>
@@ -2566,10 +2566,10 @@
         <v>14</v>
       </c>
       <c r="AW8">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AX8">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY8">
         <v>10.5</v>
@@ -2578,10 +2578,10 @@
         <v>19</v>
       </c>
       <c r="BA8">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="BB8">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BC8">
         <v>25</v>
@@ -2593,70 +2593,70 @@
         <v>28</v>
       </c>
       <c r="BF8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BG8">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BH8">
         <v>2.92</v>
       </c>
       <c r="BI8">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="BJ8">
         <v>10.5</v>
       </c>
       <c r="BK8">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BN8">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BO8">
         <v>4</v>
       </c>
       <c r="BP8">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BQ8">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR8">
         <v>38</v>
       </c>
       <c r="BS8">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BT8">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU8">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV8">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BW8">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BX8">
         <v>50</v>
       </c>
       <c r="BY8">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BZ8">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="CA8">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="CB8" t="s">
         <v>125</v>
@@ -2679,31 +2679,31 @@
         <v>117</v>
       </c>
       <c r="F9">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="G9">
         <v>1.39</v>
       </c>
       <c r="H9">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="I9">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="J9">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K9">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="L9">
         <v>1.4</v>
       </c>
       <c r="M9">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N9">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O9">
         <v>1.32</v>
@@ -2712,7 +2712,7 @@
         <v>2.02</v>
       </c>
       <c r="Q9">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R9">
         <v>1.38</v>
@@ -2724,7 +2724,7 @@
         <v>2.28</v>
       </c>
       <c r="U9">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V9">
         <v>1.08</v>
@@ -2742,7 +2742,7 @@
         <v>110</v>
       </c>
       <c r="AA9">
-        <v>610</v>
+        <v>640</v>
       </c>
       <c r="AB9">
         <v>7.2</v>
@@ -2793,13 +2793,13 @@
         <v>29</v>
       </c>
       <c r="AR9">
-        <v>14.5</v>
+        <v>28</v>
       </c>
       <c r="AS9">
         <v>16.5</v>
       </c>
       <c r="AT9">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU9">
         <v>10.5</v>
@@ -2844,13 +2844,13 @@
         <v>3.75</v>
       </c>
       <c r="BI9">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="BJ9">
         <v>13.5</v>
       </c>
       <c r="BK9">
-        <v>9.4</v>
+        <v>6</v>
       </c>
       <c r="BL9">
         <v>1000</v>
@@ -2868,7 +2868,7 @@
         <v>8.6</v>
       </c>
       <c r="BQ9">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="BR9">
         <v>29</v>
@@ -2880,7 +2880,7 @@
         <v>14.5</v>
       </c>
       <c r="BU9">
-        <v>8.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="BV9">
         <v>120</v>
@@ -2895,7 +2895,7 @@
         <v>10</v>
       </c>
       <c r="BZ9">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="CA9">
         <v>6.6</v>
@@ -2924,7 +2924,7 @@
         <v>1.82</v>
       </c>
       <c r="G10">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="H10">
         <v>4.3</v>
@@ -2945,43 +2945,43 @@
         <v>1.04</v>
       </c>
       <c r="N10">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O10">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P10">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="Q10">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="R10">
         <v>1.58</v>
       </c>
       <c r="S10">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="T10">
         <v>1.64</v>
       </c>
       <c r="U10">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V10">
         <v>1.27</v>
       </c>
       <c r="W10">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="X10">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z10">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AA10">
         <v>110</v>
@@ -2996,7 +2996,7 @@
         <v>18.5</v>
       </c>
       <c r="AE10">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF10">
         <v>14</v>
@@ -3026,19 +3026,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AO10">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP10">
         <v>20</v>
       </c>
       <c r="AQ10">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AR10">
         <v>29</v>
       </c>
       <c r="AS10">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AT10">
         <v>10.5</v>
@@ -3080,28 +3080,28 @@
         <v>7.4</v>
       </c>
       <c r="BG10">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BH10">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BI10">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BJ10">
         <v>9.4</v>
       </c>
       <c r="BK10">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN10">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BO10">
         <v>3.9</v>
@@ -3110,37 +3110,37 @@
         <v>12.5</v>
       </c>
       <c r="BQ10">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BR10">
         <v>23</v>
       </c>
       <c r="BS10">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BT10">
         <v>8.4</v>
       </c>
       <c r="BU10">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW10">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BZ10">
         <v>16.5</v>
       </c>
       <c r="CA10">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="CB10" t="s">
         <v>125</v>
@@ -3166,7 +3166,7 @@
         <v>2.16</v>
       </c>
       <c r="G11">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H11">
         <v>4</v>
@@ -3193,7 +3193,7 @@
         <v>1.44</v>
       </c>
       <c r="P11">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q11">
         <v>2.32</v>
@@ -3214,19 +3214,19 @@
         <v>1.31</v>
       </c>
       <c r="W11">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X11">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y11">
         <v>12.5</v>
       </c>
       <c r="Z11">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA11">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB11">
         <v>8</v>
@@ -3238,10 +3238,10 @@
         <v>17</v>
       </c>
       <c r="AE11">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AF11">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG11">
         <v>11</v>
@@ -3250,22 +3250,22 @@
         <v>23</v>
       </c>
       <c r="AI11">
-        <v>130</v>
+        <v>75</v>
       </c>
       <c r="AJ11">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK11">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL11">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AM11">
         <v>160</v>
       </c>
       <c r="AN11">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AO11">
         <v>85</v>
@@ -3274,37 +3274,37 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ11">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR11">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AS11">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="AT11">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU11">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV11">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW11">
-        <v>11.5</v>
+        <v>38</v>
       </c>
       <c r="AX11">
         <v>11</v>
       </c>
       <c r="AY11">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ11">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA11">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="BB11">
         <v>25</v>
@@ -3313,16 +3313,16 @@
         <v>23</v>
       </c>
       <c r="BD11">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BE11">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="BF11">
         <v>20</v>
       </c>
       <c r="BG11">
-        <v>46</v>
+        <v>16.5</v>
       </c>
       <c r="BH11">
         <v>3</v>
@@ -3340,7 +3340,7 @@
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BN11">
         <v>4.8</v>
@@ -3349,7 +3349,7 @@
         <v>4.3</v>
       </c>
       <c r="BP11">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BQ11">
         <v>8.4</v>
@@ -3364,7 +3364,7 @@
         <v>7.2</v>
       </c>
       <c r="BU11">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BV11">
         <v>38</v>
@@ -3376,7 +3376,7 @@
         <v>55</v>
       </c>
       <c r="BY11">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ11">
         <v>36</v>
@@ -3405,10 +3405,10 @@
         <v>120</v>
       </c>
       <c r="F12">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="G12">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="H12">
         <v>4.2</v>
@@ -3420,7 +3420,7 @@
         <v>3.85</v>
       </c>
       <c r="K12">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L12">
         <v>1.39</v>
@@ -3441,7 +3441,7 @@
         <v>1.9</v>
       </c>
       <c r="R12">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S12">
         <v>3.25</v>
@@ -3450,19 +3450,19 @@
         <v>1.78</v>
       </c>
       <c r="U12">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V12">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W12">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X12">
         <v>16</v>
       </c>
       <c r="Y12">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z12">
         <v>34</v>
@@ -3477,7 +3477,7 @@
         <v>8.6</v>
       </c>
       <c r="AD12">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE12">
         <v>55</v>
@@ -3489,7 +3489,7 @@
         <v>10.5</v>
       </c>
       <c r="AH12">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI12">
         <v>55</v>
@@ -3498,7 +3498,7 @@
         <v>22</v>
       </c>
       <c r="AK12">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AL12">
         <v>34</v>
@@ -3522,13 +3522,13 @@
         <v>29</v>
       </c>
       <c r="AS12">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AT12">
         <v>9</v>
       </c>
       <c r="AU12">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV12">
         <v>15.5</v>
@@ -3546,19 +3546,19 @@
         <v>16.5</v>
       </c>
       <c r="BA12">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="BB12">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC12">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD12">
         <v>30</v>
       </c>
       <c r="BE12">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="BF12">
         <v>11</v>
@@ -3567,64 +3567,64 @@
         <v>42</v>
       </c>
       <c r="BH12">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="BI12">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="BJ12">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BK12">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="BL12">
         <v>120</v>
       </c>
       <c r="BM12">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="BN12">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BO12">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="BP12">
         <v>13.5</v>
       </c>
       <c r="BQ12">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="BR12">
         <v>27</v>
       </c>
       <c r="BS12">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="BT12">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU12">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BV12">
         <v>34</v>
       </c>
       <c r="BW12">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BX12">
         <v>42</v>
       </c>
       <c r="BY12">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="BZ12">
         <v>23</v>
       </c>
       <c r="CA12">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="CB12" t="s">
         <v>125</v>
@@ -3647,22 +3647,22 @@
         <v>121</v>
       </c>
       <c r="F13">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="G13">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="H13">
+        <v>3.6</v>
+      </c>
+      <c r="I13">
         <v>3.7</v>
       </c>
-      <c r="I13">
-        <v>3.75</v>
-      </c>
       <c r="J13">
+        <v>3.8</v>
+      </c>
+      <c r="K13">
         <v>3.85</v>
-      </c>
-      <c r="K13">
-        <v>3.9</v>
       </c>
       <c r="L13">
         <v>1.36</v>
@@ -3689,16 +3689,16 @@
         <v>2.98</v>
       </c>
       <c r="T13">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U13">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V13">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W13">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="X13">
         <v>17.5</v>
@@ -3710,13 +3710,13 @@
         <v>28</v>
       </c>
       <c r="AA13">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB13">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC13">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD13">
         <v>15</v>
@@ -3725,13 +3725,13 @@
         <v>40</v>
       </c>
       <c r="AF13">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG13">
         <v>11</v>
       </c>
       <c r="AH13">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI13">
         <v>46</v>
@@ -3761,19 +3761,19 @@
         <v>14.5</v>
       </c>
       <c r="AR13">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS13">
         <v>55</v>
       </c>
       <c r="AT13">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU13">
         <v>8</v>
       </c>
       <c r="AV13">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW13">
         <v>34</v>
@@ -3785,13 +3785,13 @@
         <v>10</v>
       </c>
       <c r="AZ13">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA13">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB13">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BC13">
         <v>18.5</v>
@@ -3800,73 +3800,73 @@
         <v>28</v>
       </c>
       <c r="BE13">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BF13">
         <v>11</v>
       </c>
       <c r="BG13">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BH13">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BI13">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BJ13">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BK13">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="BL13">
         <v>95</v>
       </c>
       <c r="BM13">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BN13">
         <v>5.1</v>
       </c>
       <c r="BO13">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP13">
         <v>15</v>
       </c>
       <c r="BQ13">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BR13">
         <v>26</v>
       </c>
       <c r="BS13">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BT13">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BU13">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BV13">
         <v>28</v>
       </c>
       <c r="BW13">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BX13">
         <v>36</v>
       </c>
       <c r="BY13">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BZ13">
         <v>21</v>
       </c>
       <c r="CA13">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB13" t="s">
         <v>125</v>
@@ -3889,22 +3889,22 @@
         <v>122</v>
       </c>
       <c r="F14">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="G14">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="H14">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="I14">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J14">
         <v>4.4</v>
       </c>
       <c r="K14">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L14">
         <v>1.27</v>
@@ -3916,13 +3916,13 @@
         <v>6.6</v>
       </c>
       <c r="O14">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P14">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="Q14">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R14">
         <v>1.76</v>
@@ -3931,28 +3931,28 @@
         <v>2.26</v>
       </c>
       <c r="T14">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="U14">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="V14">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W14">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="X14">
         <v>29</v>
       </c>
       <c r="Y14">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z14">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AA14">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB14">
         <v>14.5</v>
@@ -3964,37 +3964,37 @@
         <v>18</v>
       </c>
       <c r="AE14">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF14">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG14">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH14">
         <v>15.5</v>
       </c>
       <c r="AI14">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK14">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL14">
         <v>24</v>
       </c>
       <c r="AM14">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN14">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AO14">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AP14">
         <v>26</v>
@@ -4003,34 +4003,34 @@
         <v>24</v>
       </c>
       <c r="AR14">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AS14">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AT14">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU14">
         <v>10</v>
       </c>
       <c r="AV14">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AW14">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AX14">
         <v>13.5</v>
       </c>
       <c r="AY14">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ14">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA14">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BB14">
         <v>18.5</v>
@@ -4042,13 +4042,13 @@
         <v>21</v>
       </c>
       <c r="BE14">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BF14">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG14">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="BH14">
         <v>4.7</v>
@@ -4063,13 +4063,13 @@
         <v>6</v>
       </c>
       <c r="BL14">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BM14">
         <v>14.5</v>
       </c>
       <c r="BN14">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BO14">
         <v>4.5</v>
@@ -4078,7 +4078,7 @@
         <v>11</v>
       </c>
       <c r="BQ14">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BR14">
         <v>19.5</v>
@@ -4087,28 +4087,28 @@
         <v>9.4</v>
       </c>
       <c r="BT14">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU14">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BV14">
+        <v>30</v>
+      </c>
+      <c r="BW14">
+        <v>11</v>
+      </c>
+      <c r="BX14">
         <v>32</v>
-      </c>
-      <c r="BW14">
-        <v>11.5</v>
-      </c>
-      <c r="BX14">
-        <v>34</v>
       </c>
       <c r="BY14">
         <v>11.5</v>
       </c>
       <c r="BZ14">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="CA14">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB14" t="s">
         <v>125</v>
@@ -4134,7 +4134,7 @@
         <v>3.9</v>
       </c>
       <c r="G15">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H15">
         <v>1.91</v>
@@ -4143,10 +4143,10 @@
         <v>1.93</v>
       </c>
       <c r="J15">
+        <v>4.3</v>
+      </c>
+      <c r="K15">
         <v>4.4</v>
-      </c>
-      <c r="K15">
-        <v>4.5</v>
       </c>
       <c r="L15">
         <v>1.23</v>
@@ -4167,7 +4167,7 @@
         <v>1.4</v>
       </c>
       <c r="R15">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="S15">
         <v>2</v>
@@ -4218,7 +4218,7 @@
         <v>14</v>
       </c>
       <c r="AI15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ15">
         <v>75</v>
@@ -4233,7 +4233,7 @@
         <v>42</v>
       </c>
       <c r="AN15">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO15">
         <v>6.2</v>
@@ -4248,7 +4248,7 @@
         <v>16</v>
       </c>
       <c r="AS15">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT15">
         <v>27</v>
@@ -4260,10 +4260,10 @@
         <v>10.5</v>
       </c>
       <c r="AW15">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AX15">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AY15">
         <v>16</v>
@@ -4275,13 +4275,13 @@
         <v>20</v>
       </c>
       <c r="BB15">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BC15">
         <v>32</v>
       </c>
       <c r="BD15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE15">
         <v>36</v>
@@ -4293,64 +4293,64 @@
         <v>6</v>
       </c>
       <c r="BH15">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BI15">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BJ15">
         <v>8.800000000000001</v>
       </c>
       <c r="BK15">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BL15">
         <v>60</v>
       </c>
       <c r="BM15">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN15">
         <v>8.4</v>
       </c>
       <c r="BO15">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BP15">
         <v>25</v>
       </c>
       <c r="BQ15">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BR15">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BS15">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BT15">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BU15">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BV15">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BW15">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="BX15">
         <v>18.5</v>
       </c>
       <c r="BY15">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BZ15">
         <v>11</v>
       </c>
       <c r="CA15">
-        <v>7.8</v>
+        <v>5.7</v>
       </c>
       <c r="CB15" t="s">
         <v>125</v>
@@ -4373,22 +4373,22 @@
         <v>124</v>
       </c>
       <c r="F16">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="G16">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="H16">
+        <v>2.76</v>
+      </c>
+      <c r="I16">
         <v>2.8</v>
-      </c>
-      <c r="I16">
-        <v>2.84</v>
       </c>
       <c r="J16">
         <v>4.2</v>
       </c>
       <c r="K16">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L16">
         <v>1.22</v>
@@ -4400,7 +4400,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="O16">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P16">
         <v>3.5</v>
@@ -4421,79 +4421,79 @@
         <v>3.4</v>
       </c>
       <c r="V16">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W16">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="X16">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Y16">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z16">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA16">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC16">
         <v>11.5</v>
       </c>
       <c r="AD16">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE16">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AF16">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG16">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH16">
         <v>12.5</v>
       </c>
       <c r="AI16">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AJ16">
         <v>38</v>
       </c>
       <c r="AK16">
+        <v>21</v>
+      </c>
+      <c r="AL16">
+        <v>23</v>
+      </c>
+      <c r="AM16">
+        <v>38</v>
+      </c>
+      <c r="AN16">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO16">
+        <v>11</v>
+      </c>
+      <c r="AP16">
+        <v>36</v>
+      </c>
+      <c r="AQ16">
         <v>22</v>
       </c>
-      <c r="AL16">
-        <v>24</v>
-      </c>
-      <c r="AM16">
-        <v>42</v>
-      </c>
-      <c r="AN16">
-        <v>8.4</v>
-      </c>
-      <c r="AO16">
-        <v>12</v>
-      </c>
-      <c r="AP16">
-        <v>34</v>
-      </c>
-      <c r="AQ16">
-        <v>24</v>
-      </c>
       <c r="AR16">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="AS16">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AT16">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU16">
         <v>11</v>
@@ -4502,13 +4502,13 @@
         <v>13</v>
       </c>
       <c r="AW16">
+        <v>22</v>
+      </c>
+      <c r="AX16">
         <v>23</v>
       </c>
-      <c r="AX16">
-        <v>22</v>
-      </c>
       <c r="AY16">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ16">
         <v>12</v>
@@ -4517,76 +4517,76 @@
         <v>23</v>
       </c>
       <c r="BB16">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BC16">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BD16">
         <v>21</v>
       </c>
       <c r="BE16">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BF16">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG16">
+        <v>10</v>
+      </c>
+      <c r="BH16">
+        <v>5.7</v>
+      </c>
+      <c r="BI16">
+        <v>5.2</v>
+      </c>
+      <c r="BJ16">
+        <v>8</v>
+      </c>
+      <c r="BK16">
+        <v>7</v>
+      </c>
+      <c r="BL16">
+        <v>50</v>
+      </c>
+      <c r="BM16">
         <v>10.5</v>
-      </c>
-      <c r="BH16">
-        <v>5.9</v>
-      </c>
-      <c r="BI16">
-        <v>5.1</v>
-      </c>
-      <c r="BJ16">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BK16">
-        <v>6.2</v>
-      </c>
-      <c r="BL16">
-        <v>1000</v>
-      </c>
-      <c r="BM16">
-        <v>9.6</v>
       </c>
       <c r="BN16">
         <v>6.6</v>
       </c>
       <c r="BO16">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BP16">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BQ16">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BR16">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BS16">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BT16">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU16">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV16">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BW16">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BX16">
         <v>21</v>
       </c>
       <c r="BY16">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ16">
         <v>10.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-22.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="117">
   <si>
     <t>League</t>
   </si>
@@ -256,12 +256,12 @@
     <t>SnapshotTS</t>
   </si>
   <si>
+    <t>Ecuadorian Serie B</t>
+  </si>
+  <si>
     <t>Ecuadorian Serie A</t>
   </si>
   <si>
-    <t>Ecuadorian Serie B</t>
-  </si>
-  <si>
     <t>Brazilian Serie A</t>
   </si>
   <si>
@@ -277,9 +277,6 @@
     <t>2026-07-22</t>
   </si>
   <si>
-    <t>19:00:00</t>
-  </si>
-  <si>
     <t>20:30:00</t>
   </si>
   <si>
@@ -295,9 +292,6 @@
     <t>23:30:00</t>
   </si>
   <si>
-    <t>Macara</t>
-  </si>
-  <si>
     <t>San Antonio FC</t>
   </si>
   <si>
@@ -334,9 +328,6 @@
     <t>Inter Miami CF</t>
   </si>
   <si>
-    <t>Deportivo Cuenca</t>
-  </si>
-  <si>
     <t>Cumbaya FC</t>
   </si>
   <si>
@@ -373,7 +364,7 @@
     <t>Chicago Fire</t>
   </si>
   <si>
-    <t>2026-07-22 17:04:10</t>
+    <t>2026-07-22 19:12:56</t>
   </si>
 </sst>
 </file>
@@ -705,7 +696,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB14"/>
+  <dimension ref="A1:CB13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -961,172 +952,172 @@
         <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F2">
-        <v>1.39</v>
+        <v>5.8</v>
       </c>
       <c r="G2">
+        <v>6.6</v>
+      </c>
+      <c r="H2">
+        <v>7.6</v>
+      </c>
+      <c r="I2">
+        <v>8.6</v>
+      </c>
+      <c r="J2">
         <v>1.4</v>
       </c>
-      <c r="H2">
-        <v>14.5</v>
-      </c>
-      <c r="I2">
-        <v>16</v>
-      </c>
-      <c r="J2">
-        <v>4.6</v>
-      </c>
       <c r="K2">
-        <v>4.8</v>
+        <v>1.43</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N2">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="O2">
-        <v>1.36</v>
+        <v>22</v>
       </c>
       <c r="P2">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="Q2">
-        <v>2.68</v>
+        <v>140</v>
       </c>
       <c r="R2">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="S2">
-        <v>7.4</v>
+        <v>420</v>
       </c>
       <c r="T2">
-        <v>2.12</v>
+        <v>20</v>
       </c>
       <c r="U2">
-        <v>1.83</v>
+        <v>1.02</v>
       </c>
       <c r="V2">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="W2">
-        <v>3.5</v>
+        <v>1.16</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>1.46</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AA2">
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>3.85</v>
+        <v>7.4</v>
       </c>
       <c r="AC2">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="AD2">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE2">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
-        <v>5.6</v>
+        <v>110</v>
       </c>
       <c r="AG2">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AH2">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI2">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AK2">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL2">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AM2">
-        <v>620</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AO2">
         <v>1000</v>
       </c>
       <c r="AP2">
-        <v>1000</v>
+        <v>1.41</v>
       </c>
       <c r="AQ2">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AR2">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AS2">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AT2">
-        <v>3.65</v>
+        <v>6.4</v>
       </c>
       <c r="AU2">
-        <v>5.4</v>
+        <v>34</v>
       </c>
       <c r="AV2">
-        <v>18</v>
+        <v>230</v>
       </c>
       <c r="AW2">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="AX2">
-        <v>5.2</v>
+        <v>65</v>
       </c>
       <c r="AY2">
-        <v>7.6</v>
+        <v>180</v>
       </c>
       <c r="AZ2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA2">
-        <v>110</v>
+        <v>19.5</v>
       </c>
       <c r="BB2">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="BC2">
-        <v>25</v>
+        <v>190</v>
       </c>
       <c r="BD2">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="BE2">
-        <v>240</v>
+        <v>100</v>
       </c>
       <c r="BF2">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="BG2">
-        <v>230</v>
+        <v>130</v>
       </c>
       <c r="BH2">
         <v>0</v>
@@ -1189,7 +1180,7 @@
         <v>0</v>
       </c>
       <c r="CB2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1203,240 +1194,240 @@
         <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F3">
-        <v>2.6</v>
+        <v>1.11</v>
       </c>
       <c r="G3">
-        <v>2.78</v>
+        <v>1.12</v>
       </c>
       <c r="H3">
-        <v>3.25</v>
+        <v>30</v>
       </c>
       <c r="I3">
-        <v>3.45</v>
+        <v>100</v>
       </c>
       <c r="J3">
-        <v>2.92</v>
+        <v>10</v>
       </c>
       <c r="K3">
-        <v>3.2</v>
+        <v>12</v>
       </c>
       <c r="L3">
-        <v>1.55</v>
+        <v>3.9</v>
       </c>
       <c r="M3">
+        <v>1.15</v>
+      </c>
+      <c r="N3">
+        <v>7</v>
+      </c>
+      <c r="O3">
+        <v>1.14</v>
+      </c>
+      <c r="P3">
+        <v>1.41</v>
+      </c>
+      <c r="Q3">
+        <v>3.35</v>
+      </c>
+      <c r="R3">
         <v>1.12</v>
       </c>
-      <c r="N3">
-        <v>2.82</v>
-      </c>
-      <c r="O3">
-        <v>1.5</v>
-      </c>
-      <c r="P3">
-        <v>1.58</v>
-      </c>
-      <c r="Q3">
-        <v>2.58</v>
-      </c>
-      <c r="R3">
-        <v>1.23</v>
-      </c>
       <c r="S3">
-        <v>5.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="T3">
-        <v>2.02</v>
+        <v>3.5</v>
       </c>
       <c r="U3">
-        <v>1.86</v>
+        <v>1.36</v>
       </c>
       <c r="V3">
-        <v>1.41</v>
+        <v>1.1</v>
       </c>
       <c r="W3">
-        <v>1.56</v>
+        <v>2.84</v>
       </c>
       <c r="X3">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Y3">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z3">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA3">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC3">
-        <v>7.2</v>
+        <v>970</v>
       </c>
       <c r="AD3">
-        <v>15.5</v>
+        <v>880</v>
       </c>
       <c r="AE3">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF3">
-        <v>16</v>
+        <v>780</v>
       </c>
       <c r="AG3">
-        <v>13</v>
+        <v>990</v>
       </c>
       <c r="AH3">
-        <v>23</v>
+        <v>990</v>
       </c>
       <c r="AI3">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="AK3">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL3">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
-        <v>42</v>
+        <v>7.8</v>
       </c>
       <c r="AO3">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP3">
-        <v>8.199999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="AQ3">
-        <v>9</v>
+        <v>18.5</v>
       </c>
       <c r="AR3">
         <v>18.5</v>
       </c>
       <c r="AS3">
-        <v>44</v>
+        <v>18.5</v>
       </c>
       <c r="AT3">
-        <v>7.4</v>
+        <v>1.22</v>
       </c>
       <c r="AU3">
-        <v>6.2</v>
+        <v>3.25</v>
       </c>
       <c r="AV3">
-        <v>13</v>
+        <v>1.42</v>
       </c>
       <c r="AW3">
-        <v>32</v>
+        <v>1.42</v>
       </c>
       <c r="AX3">
-        <v>13</v>
+        <v>1.42</v>
       </c>
       <c r="AY3">
-        <v>11</v>
+        <v>1.42</v>
       </c>
       <c r="AZ3">
-        <v>18</v>
+        <v>3.25</v>
       </c>
       <c r="BA3">
-        <v>44</v>
+        <v>2.9</v>
       </c>
       <c r="BB3">
-        <v>30</v>
+        <v>1.33</v>
       </c>
       <c r="BC3">
-        <v>27</v>
+        <v>1.42</v>
       </c>
       <c r="BD3">
-        <v>40</v>
+        <v>2.9</v>
       </c>
       <c r="BE3">
-        <v>100</v>
+        <v>3.25</v>
       </c>
       <c r="BF3">
-        <v>27</v>
+        <v>3.9</v>
       </c>
       <c r="BG3">
-        <v>36</v>
+        <v>1.42</v>
       </c>
       <c r="BH3">
-        <v>2.8</v>
+        <v>1.35</v>
       </c>
       <c r="BI3">
-        <v>2.54</v>
+        <v>1.29</v>
       </c>
       <c r="BJ3">
-        <v>11</v>
+        <v>380</v>
       </c>
       <c r="BK3">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>70</v>
+        <v>8.4</v>
       </c>
       <c r="BN3">
-        <v>5.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO3">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BP3">
-        <v>24</v>
+        <v>210</v>
       </c>
       <c r="BQ3">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BR3">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="BT3">
-        <v>6.2</v>
+        <v>42</v>
       </c>
       <c r="BU3">
-        <v>5.5</v>
+        <v>18.5</v>
       </c>
       <c r="BV3">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX3">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="BZ3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="CB3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:80">
       <c r="A4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s">
         <v>86</v>
@@ -1445,477 +1436,477 @@
         <v>89</v>
       </c>
       <c r="D4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F4">
+        <v>4.6</v>
+      </c>
+      <c r="G4">
+        <v>4.7</v>
+      </c>
+      <c r="H4">
+        <v>2.08</v>
+      </c>
+      <c r="I4">
+        <v>2.1</v>
+      </c>
+      <c r="J4">
+        <v>3.25</v>
+      </c>
+      <c r="K4">
+        <v>3.3</v>
+      </c>
+      <c r="L4">
+        <v>1.53</v>
+      </c>
+      <c r="M4">
+        <v>1.12</v>
+      </c>
+      <c r="N4">
+        <v>3</v>
+      </c>
+      <c r="O4">
+        <v>1.48</v>
+      </c>
+      <c r="P4">
+        <v>1.64</v>
+      </c>
+      <c r="Q4">
+        <v>2.52</v>
+      </c>
+      <c r="R4">
+        <v>1.23</v>
+      </c>
+      <c r="S4">
+        <v>5.1</v>
+      </c>
+      <c r="T4">
+        <v>2.08</v>
+      </c>
+      <c r="U4">
+        <v>1.88</v>
+      </c>
+      <c r="V4">
+        <v>1.9</v>
+      </c>
+      <c r="W4">
+        <v>1.27</v>
+      </c>
+      <c r="X4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y4">
+        <v>7</v>
+      </c>
+      <c r="Z4">
+        <v>10.5</v>
+      </c>
+      <c r="AA4">
+        <v>26</v>
+      </c>
+      <c r="AB4">
+        <v>12.5</v>
+      </c>
+      <c r="AC4">
+        <v>7.2</v>
+      </c>
+      <c r="AD4">
+        <v>10.5</v>
+      </c>
+      <c r="AE4">
+        <v>26</v>
+      </c>
+      <c r="AF4">
+        <v>34</v>
+      </c>
+      <c r="AG4">
+        <v>17.5</v>
+      </c>
+      <c r="AH4">
+        <v>23</v>
+      </c>
+      <c r="AI4">
+        <v>55</v>
+      </c>
+      <c r="AJ4">
+        <v>120</v>
+      </c>
+      <c r="AK4">
+        <v>85</v>
+      </c>
+      <c r="AL4">
         <v>95</v>
       </c>
-      <c r="E4" t="s">
-        <v>108</v>
-      </c>
-      <c r="F4">
-        <v>1.23</v>
-      </c>
-      <c r="G4">
-        <v>1.24</v>
-      </c>
-      <c r="H4">
-        <v>18.5</v>
-      </c>
-      <c r="I4">
+      <c r="AM4">
+        <v>180</v>
+      </c>
+      <c r="AN4">
+        <v>130</v>
+      </c>
+      <c r="AO4">
+        <v>24</v>
+      </c>
+      <c r="AP4">
+        <v>9</v>
+      </c>
+      <c r="AQ4">
+        <v>6.8</v>
+      </c>
+      <c r="AR4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS4">
+        <v>25</v>
+      </c>
+      <c r="AT4">
+        <v>12</v>
+      </c>
+      <c r="AU4">
+        <v>6.8</v>
+      </c>
+      <c r="AV4">
+        <v>10</v>
+      </c>
+      <c r="AW4">
+        <v>25</v>
+      </c>
+      <c r="AX4">
+        <v>30</v>
+      </c>
+      <c r="AY4">
+        <v>17</v>
+      </c>
+      <c r="AZ4">
+        <v>22</v>
+      </c>
+      <c r="BA4">
+        <v>50</v>
+      </c>
+      <c r="BB4">
+        <v>100</v>
+      </c>
+      <c r="BC4">
+        <v>70</v>
+      </c>
+      <c r="BD4">
+        <v>80</v>
+      </c>
+      <c r="BE4">
+        <v>120</v>
+      </c>
+      <c r="BF4">
+        <v>100</v>
+      </c>
+      <c r="BG4">
+        <v>22</v>
+      </c>
+      <c r="BH4">
+        <v>2.88</v>
+      </c>
+      <c r="BI4">
+        <v>2.76</v>
+      </c>
+      <c r="BJ4">
+        <v>11</v>
+      </c>
+      <c r="BK4">
+        <v>9.4</v>
+      </c>
+      <c r="BL4">
+        <v>190</v>
+      </c>
+      <c r="BM4">
+        <v>140</v>
+      </c>
+      <c r="BN4">
+        <v>7.4</v>
+      </c>
+      <c r="BO4">
+        <v>6.8</v>
+      </c>
+      <c r="BP4">
+        <v>42</v>
+      </c>
+      <c r="BQ4">
+        <v>22</v>
+      </c>
+      <c r="BR4">
+        <v>60</v>
+      </c>
+      <c r="BS4">
+        <v>16.5</v>
+      </c>
+      <c r="BT4">
+        <v>4.5</v>
+      </c>
+      <c r="BU4">
+        <v>4.3</v>
+      </c>
+      <c r="BV4">
+        <v>16</v>
+      </c>
+      <c r="BW4">
+        <v>14.5</v>
+      </c>
+      <c r="BX4">
+        <v>38</v>
+      </c>
+      <c r="BY4">
+        <v>30</v>
+      </c>
+      <c r="BZ4">
+        <v>38</v>
+      </c>
+      <c r="CA4">
         <v>19</v>
       </c>
-      <c r="J4">
-        <v>7</v>
-      </c>
-      <c r="K4">
-        <v>7.6</v>
-      </c>
-      <c r="L4">
-        <v>1.3</v>
-      </c>
-      <c r="M4">
-        <v>1.04</v>
-      </c>
-      <c r="N4">
-        <v>5.4</v>
-      </c>
-      <c r="O4">
-        <v>1.21</v>
-      </c>
-      <c r="P4">
-        <v>2.46</v>
-      </c>
-      <c r="Q4">
-        <v>1.63</v>
-      </c>
-      <c r="R4">
-        <v>1.57</v>
-      </c>
-      <c r="S4">
-        <v>2.62</v>
-      </c>
-      <c r="T4">
-        <v>2.46</v>
-      </c>
-      <c r="U4">
-        <v>1.6</v>
-      </c>
-      <c r="V4">
-        <v>1.05</v>
-      </c>
-      <c r="W4">
-        <v>5.2</v>
-      </c>
-      <c r="X4">
-        <v>29</v>
-      </c>
-      <c r="Y4">
-        <v>60</v>
-      </c>
-      <c r="Z4">
-        <v>240</v>
-      </c>
-      <c r="AA4">
-        <v>1000</v>
-      </c>
-      <c r="AB4">
-        <v>10.5</v>
-      </c>
-      <c r="AC4">
-        <v>21</v>
-      </c>
-      <c r="AD4">
-        <v>950</v>
-      </c>
-      <c r="AE4">
-        <v>490</v>
-      </c>
-      <c r="AF4">
-        <v>7.4</v>
-      </c>
-      <c r="AG4">
-        <v>13.5</v>
-      </c>
-      <c r="AH4">
-        <v>950</v>
-      </c>
-      <c r="AI4">
-        <v>280</v>
-      </c>
-      <c r="AJ4">
-        <v>8.4</v>
-      </c>
-      <c r="AK4">
-        <v>15.5</v>
-      </c>
-      <c r="AL4">
-        <v>330</v>
-      </c>
-      <c r="AM4">
-        <v>320</v>
-      </c>
-      <c r="AN4">
-        <v>4.4</v>
-      </c>
-      <c r="AO4">
-        <v>1000</v>
-      </c>
-      <c r="AP4">
-        <v>16.5</v>
-      </c>
-      <c r="AQ4">
-        <v>20</v>
-      </c>
-      <c r="AR4">
-        <v>8.4</v>
-      </c>
-      <c r="AS4">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT4">
-        <v>7.6</v>
-      </c>
-      <c r="AU4">
-        <v>15</v>
-      </c>
-      <c r="AV4">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW4">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX4">
-        <v>6.2</v>
-      </c>
-      <c r="AY4">
-        <v>10.5</v>
-      </c>
-      <c r="AZ4">
-        <v>36</v>
-      </c>
-      <c r="BA4">
-        <v>8.6</v>
-      </c>
-      <c r="BB4">
-        <v>7.8</v>
-      </c>
-      <c r="BC4">
-        <v>12.5</v>
-      </c>
-      <c r="BD4">
-        <v>40</v>
-      </c>
-      <c r="BE4">
-        <v>8.6</v>
-      </c>
-      <c r="BF4">
-        <v>3.9</v>
-      </c>
-      <c r="BG4">
-        <v>11.5</v>
-      </c>
-      <c r="BH4">
-        <v>4.3</v>
-      </c>
-      <c r="BI4">
-        <v>3.85</v>
-      </c>
-      <c r="BJ4">
-        <v>15</v>
-      </c>
-      <c r="BK4">
-        <v>10.5</v>
-      </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
-        <v>15.5</v>
-      </c>
-      <c r="BN4">
-        <v>3.55</v>
-      </c>
-      <c r="BO4">
-        <v>3.2</v>
-      </c>
-      <c r="BP4">
-        <v>6.6</v>
-      </c>
-      <c r="BQ4">
-        <v>5.7</v>
-      </c>
-      <c r="BR4">
-        <v>26</v>
-      </c>
-      <c r="BS4">
-        <v>10</v>
-      </c>
-      <c r="BT4">
-        <v>19</v>
-      </c>
-      <c r="BU4">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BV4">
-        <v>1000</v>
-      </c>
-      <c r="BW4">
-        <v>15</v>
-      </c>
-      <c r="BX4">
-        <v>1000</v>
-      </c>
-      <c r="BY4">
-        <v>15</v>
-      </c>
-      <c r="BZ4">
-        <v>10</v>
-      </c>
-      <c r="CA4">
-        <v>7.2</v>
-      </c>
       <c r="CB4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B5" t="s">
         <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F5">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="G5">
-        <v>4.4</v>
+        <v>2.32</v>
       </c>
       <c r="H5">
-        <v>2.18</v>
+        <v>3.6</v>
       </c>
       <c r="I5">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="J5">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="K5">
+        <v>3.4</v>
+      </c>
+      <c r="L5">
+        <v>1.51</v>
+      </c>
+      <c r="M5">
+        <v>1.1</v>
+      </c>
+      <c r="N5">
         <v>3.2</v>
       </c>
-      <c r="L5">
-        <v>1.53</v>
-      </c>
-      <c r="M5">
-        <v>1.11</v>
-      </c>
-      <c r="N5">
-        <v>3.05</v>
-      </c>
       <c r="O5">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="P5">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="Q5">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="R5">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S5">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="T5">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="U5">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="V5">
-        <v>1.83</v>
+        <v>1.37</v>
       </c>
       <c r="W5">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="X5">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="Y5">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="Z5">
-        <v>11.5</v>
+        <v>25</v>
       </c>
       <c r="AA5">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="AB5">
-        <v>13</v>
+        <v>8.4</v>
       </c>
       <c r="AC5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AD5">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE5">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="AF5">
-        <v>30</v>
+        <v>13.5</v>
       </c>
       <c r="AG5">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AH5">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI5">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AJ5">
-        <v>280</v>
+        <v>34</v>
       </c>
       <c r="AK5">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="AL5">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="AM5">
         <v>160</v>
       </c>
       <c r="AN5">
-        <v>110</v>
+        <v>24</v>
       </c>
       <c r="AO5">
+        <v>60</v>
+      </c>
+      <c r="AP5">
+        <v>10</v>
+      </c>
+      <c r="AQ5">
+        <v>11</v>
+      </c>
+      <c r="AR5">
+        <v>22</v>
+      </c>
+      <c r="AS5">
+        <v>65</v>
+      </c>
+      <c r="AT5">
+        <v>7.8</v>
+      </c>
+      <c r="AU5">
+        <v>7</v>
+      </c>
+      <c r="AV5">
+        <v>14</v>
+      </c>
+      <c r="AW5">
+        <v>44</v>
+      </c>
+      <c r="AX5">
+        <v>12.5</v>
+      </c>
+      <c r="AY5">
+        <v>10</v>
+      </c>
+      <c r="AZ5">
+        <v>18</v>
+      </c>
+      <c r="BA5">
+        <v>55</v>
+      </c>
+      <c r="BB5">
+        <v>29</v>
+      </c>
+      <c r="BC5">
         <v>25</v>
       </c>
-      <c r="AP5">
-        <v>9</v>
-      </c>
-      <c r="AQ5">
-        <v>7.4</v>
-      </c>
-      <c r="AR5">
-        <v>10.5</v>
-      </c>
-      <c r="AS5">
-        <v>24</v>
-      </c>
-      <c r="AT5">
-        <v>11.5</v>
-      </c>
-      <c r="AU5">
-        <v>6.8</v>
-      </c>
-      <c r="AV5">
-        <v>10.5</v>
-      </c>
-      <c r="AW5">
-        <v>25</v>
-      </c>
-      <c r="AX5">
-        <v>26</v>
-      </c>
-      <c r="AY5">
-        <v>16</v>
-      </c>
-      <c r="AZ5">
-        <v>19.5</v>
-      </c>
-      <c r="BA5">
-        <v>48</v>
-      </c>
-      <c r="BB5">
-        <v>85</v>
-      </c>
-      <c r="BC5">
-        <v>55</v>
-      </c>
       <c r="BD5">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="BE5">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="BF5">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="BG5">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="BH5">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="BI5">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="BJ5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK5">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>140</v>
+        <v>18</v>
       </c>
       <c r="BN5">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="BO5">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="BP5">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="BQ5">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BR5">
+        <v>36</v>
+      </c>
+      <c r="BS5">
+        <v>27</v>
+      </c>
+      <c r="BT5">
+        <v>6.6</v>
+      </c>
+      <c r="BU5">
+        <v>6</v>
+      </c>
+      <c r="BV5">
+        <v>32</v>
+      </c>
+      <c r="BW5">
+        <v>13.5</v>
+      </c>
+      <c r="BX5">
         <v>55</v>
       </c>
-      <c r="BS5">
-        <v>16</v>
-      </c>
-      <c r="BT5">
-        <v>4.6</v>
-      </c>
-      <c r="BU5">
-        <v>4.3</v>
-      </c>
-      <c r="BV5">
-        <v>17</v>
-      </c>
-      <c r="BW5">
-        <v>9.6</v>
-      </c>
-      <c r="BX5">
+      <c r="BY5">
+        <v>16.5</v>
+      </c>
+      <c r="BZ5">
         <v>36</v>
-      </c>
-      <c r="BY5">
-        <v>14</v>
-      </c>
-      <c r="BZ5">
-        <v>38</v>
       </c>
       <c r="CA5">
         <v>14</v>
       </c>
       <c r="CB5" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1926,243 +1917,243 @@
         <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F6">
-        <v>2.34</v>
+        <v>1.36</v>
       </c>
       <c r="G6">
-        <v>2.4</v>
+        <v>1.38</v>
       </c>
       <c r="H6">
-        <v>3.6</v>
+        <v>12</v>
       </c>
       <c r="I6">
-        <v>3.7</v>
+        <v>13</v>
       </c>
       <c r="J6">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="K6">
-        <v>3.3</v>
+        <v>5.3</v>
       </c>
       <c r="L6">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="M6">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="N6">
-        <v>3.05</v>
+        <v>3.95</v>
       </c>
       <c r="O6">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="P6">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="Q6">
-        <v>2.42</v>
+        <v>1.96</v>
       </c>
       <c r="R6">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="S6">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="T6">
-        <v>2.02</v>
+        <v>2.38</v>
       </c>
       <c r="U6">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="V6">
-        <v>1.37</v>
+        <v>1.08</v>
       </c>
       <c r="W6">
-        <v>1.71</v>
+        <v>3.65</v>
       </c>
       <c r="X6">
+        <v>16</v>
+      </c>
+      <c r="Y6">
+        <v>36</v>
+      </c>
+      <c r="Z6">
+        <v>120</v>
+      </c>
+      <c r="AA6">
+        <v>580</v>
+      </c>
+      <c r="AB6">
+        <v>6.8</v>
+      </c>
+      <c r="AC6">
+        <v>12.5</v>
+      </c>
+      <c r="AD6">
+        <v>44</v>
+      </c>
+      <c r="AE6">
+        <v>310</v>
+      </c>
+      <c r="AF6">
+        <v>7</v>
+      </c>
+      <c r="AG6">
+        <v>9.6</v>
+      </c>
+      <c r="AH6">
+        <v>38</v>
+      </c>
+      <c r="AI6">
+        <v>240</v>
+      </c>
+      <c r="AJ6">
         <v>10.5</v>
       </c>
-      <c r="Y6">
-        <v>11.5</v>
-      </c>
-      <c r="Z6">
-        <v>25</v>
-      </c>
-      <c r="AA6">
-        <v>75</v>
-      </c>
-      <c r="AB6">
-        <v>8</v>
-      </c>
-      <c r="AC6">
-        <v>7.4</v>
-      </c>
-      <c r="AD6">
+      <c r="AK6">
         <v>15.5</v>
-      </c>
-      <c r="AE6">
-        <v>55</v>
-      </c>
-      <c r="AF6">
-        <v>14</v>
-      </c>
-      <c r="AG6">
-        <v>11.5</v>
-      </c>
-      <c r="AH6">
-        <v>21</v>
-      </c>
-      <c r="AI6">
-        <v>130</v>
-      </c>
-      <c r="AJ6">
-        <v>32</v>
-      </c>
-      <c r="AK6">
-        <v>29</v>
       </c>
       <c r="AL6">
         <v>55</v>
       </c>
       <c r="AM6">
-        <v>580</v>
+        <v>290</v>
       </c>
       <c r="AN6">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="AO6">
-        <v>90</v>
+        <v>410</v>
       </c>
       <c r="AP6">
-        <v>9.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="AQ6">
-        <v>10.5</v>
+        <v>30</v>
       </c>
       <c r="AR6">
-        <v>22</v>
+        <v>95</v>
       </c>
       <c r="AS6">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="AT6">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU6">
+        <v>11</v>
+      </c>
+      <c r="AV6">
+        <v>38</v>
+      </c>
+      <c r="AW6">
+        <v>24</v>
+      </c>
+      <c r="AX6">
         <v>6.8</v>
       </c>
-      <c r="AV6">
-        <v>14</v>
-      </c>
-      <c r="AW6">
-        <v>46</v>
-      </c>
-      <c r="AX6">
-        <v>12</v>
-      </c>
       <c r="AY6">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AZ6">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="BA6">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="BB6">
-        <v>29</v>
+        <v>9.6</v>
       </c>
       <c r="BC6">
-        <v>25</v>
+        <v>14.5</v>
       </c>
       <c r="BD6">
         <v>44</v>
       </c>
       <c r="BE6">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="BF6">
-        <v>24</v>
+        <v>6.6</v>
       </c>
       <c r="BG6">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="BH6">
-        <v>2.92</v>
+        <v>3.55</v>
       </c>
       <c r="BI6">
-        <v>2.52</v>
+        <v>3.25</v>
       </c>
       <c r="BJ6">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BK6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>16.5</v>
+        <v>75</v>
       </c>
       <c r="BN6">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="BO6">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="BP6">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="BQ6">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BR6">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="BS6">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="BT6">
-        <v>6.8</v>
+        <v>15</v>
       </c>
       <c r="BU6">
-        <v>5.3</v>
+        <v>12.5</v>
       </c>
       <c r="BV6">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="BW6">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="BX6">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="BY6">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BZ6">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="CA6">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CB6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s">
         <v>86</v>
@@ -2171,240 +2162,240 @@
         <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F7">
-        <v>1.37</v>
+        <v>1.82</v>
       </c>
       <c r="G7">
-        <v>1.38</v>
+        <v>1.86</v>
       </c>
       <c r="H7">
+        <v>4.2</v>
+      </c>
+      <c r="I7">
+        <v>4.6</v>
+      </c>
+      <c r="J7">
+        <v>4.1</v>
+      </c>
+      <c r="K7">
+        <v>4.5</v>
+      </c>
+      <c r="L7">
+        <v>1.31</v>
+      </c>
+      <c r="M7">
+        <v>1.04</v>
+      </c>
+      <c r="N7">
+        <v>5.4</v>
+      </c>
+      <c r="O7">
+        <v>1.2</v>
+      </c>
+      <c r="P7">
+        <v>2.5</v>
+      </c>
+      <c r="Q7">
+        <v>1.63</v>
+      </c>
+      <c r="R7">
+        <v>1.59</v>
+      </c>
+      <c r="S7">
+        <v>2.6</v>
+      </c>
+      <c r="T7">
+        <v>1.6</v>
+      </c>
+      <c r="U7">
+        <v>2.48</v>
+      </c>
+      <c r="V7">
+        <v>1.27</v>
+      </c>
+      <c r="W7">
+        <v>2.16</v>
+      </c>
+      <c r="X7">
+        <v>26</v>
+      </c>
+      <c r="Y7">
+        <v>23</v>
+      </c>
+      <c r="Z7">
+        <v>46</v>
+      </c>
+      <c r="AA7">
+        <v>90</v>
+      </c>
+      <c r="AB7">
+        <v>13</v>
+      </c>
+      <c r="AC7">
+        <v>10.5</v>
+      </c>
+      <c r="AD7">
+        <v>18</v>
+      </c>
+      <c r="AE7">
+        <v>80</v>
+      </c>
+      <c r="AF7">
+        <v>14.5</v>
+      </c>
+      <c r="AG7">
+        <v>11</v>
+      </c>
+      <c r="AH7">
+        <v>17</v>
+      </c>
+      <c r="AI7">
+        <v>60</v>
+      </c>
+      <c r="AJ7">
+        <v>21</v>
+      </c>
+      <c r="AK7">
+        <v>18</v>
+      </c>
+      <c r="AL7">
+        <v>36</v>
+      </c>
+      <c r="AM7">
+        <v>85</v>
+      </c>
+      <c r="AN7">
+        <v>8.6</v>
+      </c>
+      <c r="AO7">
+        <v>60</v>
+      </c>
+      <c r="AP7">
+        <v>20</v>
+      </c>
+      <c r="AQ7">
+        <v>18</v>
+      </c>
+      <c r="AR7">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT7">
+        <v>11</v>
+      </c>
+      <c r="AU7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV7">
+        <v>14</v>
+      </c>
+      <c r="AW7">
+        <v>8.4</v>
+      </c>
+      <c r="AX7">
         <v>11.5</v>
       </c>
-      <c r="I7">
-        <v>12.5</v>
-      </c>
-      <c r="J7">
-        <v>5.3</v>
-      </c>
-      <c r="K7">
-        <v>5.4</v>
-      </c>
-      <c r="L7">
-        <v>1.39</v>
-      </c>
-      <c r="M7">
-        <v>1.06</v>
-      </c>
-      <c r="N7">
-        <v>4</v>
-      </c>
-      <c r="O7">
-        <v>1.31</v>
-      </c>
-      <c r="P7">
-        <v>2.02</v>
-      </c>
-      <c r="Q7">
-        <v>1.95</v>
-      </c>
-      <c r="R7">
-        <v>1.39</v>
-      </c>
-      <c r="S7">
-        <v>3.5</v>
-      </c>
-      <c r="T7">
-        <v>2.3</v>
-      </c>
-      <c r="U7">
-        <v>1.7</v>
-      </c>
-      <c r="V7">
-        <v>1.08</v>
-      </c>
-      <c r="W7">
-        <v>3.65</v>
-      </c>
-      <c r="X7">
-        <v>17</v>
-      </c>
-      <c r="Y7">
-        <v>34</v>
-      </c>
-      <c r="Z7">
-        <v>110</v>
-      </c>
-      <c r="AA7">
-        <v>550</v>
-      </c>
-      <c r="AB7">
-        <v>7.2</v>
-      </c>
-      <c r="AC7">
-        <v>12</v>
-      </c>
-      <c r="AD7">
-        <v>50</v>
-      </c>
-      <c r="AE7">
-        <v>240</v>
-      </c>
-      <c r="AF7">
-        <v>7.2</v>
-      </c>
-      <c r="AG7">
-        <v>10.5</v>
-      </c>
-      <c r="AH7">
-        <v>36</v>
-      </c>
-      <c r="AI7">
-        <v>210</v>
-      </c>
-      <c r="AJ7">
-        <v>10.5</v>
-      </c>
-      <c r="AK7">
-        <v>16</v>
-      </c>
-      <c r="AL7">
-        <v>70</v>
-      </c>
-      <c r="AM7">
-        <v>240</v>
-      </c>
-      <c r="AN7">
-        <v>7</v>
-      </c>
-      <c r="AO7">
-        <v>380</v>
-      </c>
-      <c r="AP7">
-        <v>15</v>
-      </c>
-      <c r="AQ7">
-        <v>29</v>
-      </c>
-      <c r="AR7">
-        <v>95</v>
-      </c>
-      <c r="AS7">
-        <v>16.5</v>
-      </c>
-      <c r="AT7">
-        <v>6.6</v>
-      </c>
-      <c r="AU7">
-        <v>10.5</v>
-      </c>
-      <c r="AV7">
-        <v>38</v>
-      </c>
-      <c r="AW7">
-        <v>18</v>
-      </c>
-      <c r="AX7">
-        <v>6.6</v>
-      </c>
       <c r="AY7">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AZ7">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="BA7">
+        <v>8.4</v>
+      </c>
+      <c r="BB7">
         <v>19</v>
       </c>
-      <c r="BB7">
-        <v>9.6</v>
-      </c>
       <c r="BC7">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD7">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="BE7">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="BF7">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG7">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="BH7">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="BI7">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="BJ7">
-        <v>13.5</v>
+        <v>9.4</v>
       </c>
       <c r="BK7">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="BN7">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="BO7">
-        <v>2.92</v>
+        <v>3.9</v>
       </c>
       <c r="BP7">
-        <v>8.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BQ7">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="BR7">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="BS7">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="BT7">
-        <v>14.5</v>
+        <v>8.4</v>
       </c>
       <c r="BU7">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="BV7">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="BW7">
-        <v>13</v>
+        <v>7.8</v>
       </c>
       <c r="BX7">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>12.5</v>
+        <v>8</v>
       </c>
       <c r="BZ7">
         <v>16</v>
       </c>
       <c r="CA7">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="CB7" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B8" t="s">
         <v>86</v>
@@ -2413,477 +2404,477 @@
         <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F8">
-        <v>1.82</v>
+        <v>2.14</v>
       </c>
       <c r="G8">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="H8">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="I8">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="J8">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="K8">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="L8">
+        <v>1.5</v>
+      </c>
+      <c r="M8">
+        <v>1.1</v>
+      </c>
+      <c r="N8">
+        <v>3.2</v>
+      </c>
+      <c r="O8">
+        <v>1.44</v>
+      </c>
+      <c r="P8">
+        <v>1.72</v>
+      </c>
+      <c r="Q8">
+        <v>2.32</v>
+      </c>
+      <c r="R8">
+        <v>1.27</v>
+      </c>
+      <c r="S8">
+        <v>4.5</v>
+      </c>
+      <c r="T8">
+        <v>2</v>
+      </c>
+      <c r="U8">
+        <v>1.95</v>
+      </c>
+      <c r="V8">
         <v>1.31</v>
       </c>
-      <c r="M8">
-        <v>1.04</v>
-      </c>
-      <c r="N8">
-        <v>5.4</v>
-      </c>
-      <c r="O8">
-        <v>1.21</v>
-      </c>
-      <c r="P8">
-        <v>2.48</v>
-      </c>
-      <c r="Q8">
-        <v>1.62</v>
-      </c>
-      <c r="R8">
-        <v>1.58</v>
-      </c>
-      <c r="S8">
-        <v>2.58</v>
-      </c>
-      <c r="T8">
-        <v>1.61</v>
-      </c>
-      <c r="U8">
-        <v>2.4</v>
-      </c>
-      <c r="V8">
-        <v>1.27</v>
-      </c>
       <c r="W8">
-        <v>2.16</v>
+        <v>1.84</v>
       </c>
       <c r="X8">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="Y8">
-        <v>23</v>
+        <v>12.5</v>
       </c>
       <c r="Z8">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="AA8">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AB8">
+        <v>8</v>
+      </c>
+      <c r="AC8">
+        <v>7.4</v>
+      </c>
+      <c r="AD8">
+        <v>17</v>
+      </c>
+      <c r="AE8">
+        <v>60</v>
+      </c>
+      <c r="AF8">
         <v>12.5</v>
-      </c>
-      <c r="AC8">
-        <v>10.5</v>
-      </c>
-      <c r="AD8">
-        <v>18.5</v>
-      </c>
-      <c r="AE8">
-        <v>65</v>
-      </c>
-      <c r="AF8">
-        <v>14</v>
       </c>
       <c r="AG8">
         <v>10.5</v>
       </c>
       <c r="AH8">
-        <v>17.5</v>
+        <v>520</v>
       </c>
       <c r="AI8">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AJ8">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AK8">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="AL8">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AM8">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="AN8">
-        <v>8.6</v>
+        <v>23</v>
       </c>
       <c r="AO8">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="AP8">
-        <v>20</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ8">
-        <v>19</v>
+        <v>11.5</v>
       </c>
       <c r="AR8">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AS8">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AT8">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="AU8">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="AV8">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AW8">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AX8">
         <v>11</v>
       </c>
       <c r="AY8">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ8">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA8">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="BB8">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="BC8">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="BD8">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="BE8">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="BF8">
+        <v>22</v>
+      </c>
+      <c r="BG8">
+        <v>55</v>
+      </c>
+      <c r="BH8">
+        <v>2.98</v>
+      </c>
+      <c r="BI8">
+        <v>2.8</v>
+      </c>
+      <c r="BJ8">
+        <v>10.5</v>
+      </c>
+      <c r="BK8">
         <v>7.4</v>
-      </c>
-      <c r="BG8">
-        <v>23</v>
-      </c>
-      <c r="BH8">
-        <v>4.4</v>
-      </c>
-      <c r="BI8">
-        <v>3.45</v>
-      </c>
-      <c r="BJ8">
-        <v>9.4</v>
-      </c>
-      <c r="BK8">
-        <v>4.8</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>9</v>
+        <v>16.5</v>
       </c>
       <c r="BN8">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BO8">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="BP8">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="BQ8">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="BR8">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="BS8">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="BT8">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU8">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BV8">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BW8">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY8">
-        <v>8</v>
+        <v>13.5</v>
       </c>
       <c r="BZ8">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="CA8">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="CB8" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B9" t="s">
         <v>86</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F9">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="G9">
+        <v>1.99</v>
+      </c>
+      <c r="H9">
+        <v>4.2</v>
+      </c>
+      <c r="I9">
+        <v>4.3</v>
+      </c>
+      <c r="J9">
+        <v>3.8</v>
+      </c>
+      <c r="K9">
+        <v>3.9</v>
+      </c>
+      <c r="L9">
+        <v>1.4</v>
+      </c>
+      <c r="M9">
+        <v>1.06</v>
+      </c>
+      <c r="N9">
+        <v>4.1</v>
+      </c>
+      <c r="O9">
+        <v>1.3</v>
+      </c>
+      <c r="P9">
+        <v>2.06</v>
+      </c>
+      <c r="Q9">
+        <v>1.91</v>
+      </c>
+      <c r="R9">
+        <v>1.41</v>
+      </c>
+      <c r="S9">
+        <v>3.3</v>
+      </c>
+      <c r="T9">
+        <v>1.78</v>
+      </c>
+      <c r="U9">
         <v>2.2</v>
       </c>
-      <c r="H9">
-        <v>4</v>
-      </c>
-      <c r="I9">
-        <v>4.1</v>
-      </c>
-      <c r="J9">
-        <v>3.35</v>
-      </c>
-      <c r="K9">
-        <v>3.45</v>
-      </c>
-      <c r="L9">
-        <v>1.5</v>
-      </c>
-      <c r="M9">
-        <v>1.1</v>
-      </c>
-      <c r="N9">
-        <v>3.2</v>
-      </c>
-      <c r="O9">
-        <v>1.44</v>
-      </c>
-      <c r="P9">
-        <v>1.72</v>
-      </c>
-      <c r="Q9">
-        <v>2.32</v>
-      </c>
-      <c r="R9">
-        <v>1.27</v>
-      </c>
-      <c r="S9">
-        <v>4.5</v>
-      </c>
-      <c r="T9">
-        <v>1.98</v>
-      </c>
-      <c r="U9">
-        <v>1.94</v>
-      </c>
       <c r="V9">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W9">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="X9">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="Y9">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="Z9">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA9">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB9">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="AC9">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AD9">
         <v>17</v>
       </c>
       <c r="AE9">
+        <v>55</v>
+      </c>
+      <c r="AF9">
+        <v>12</v>
+      </c>
+      <c r="AG9">
+        <v>10.5</v>
+      </c>
+      <c r="AH9">
+        <v>18</v>
+      </c>
+      <c r="AI9">
         <v>60</v>
       </c>
-      <c r="AF9">
-        <v>12.5</v>
-      </c>
-      <c r="AG9">
-        <v>11</v>
-      </c>
-      <c r="AH9">
-        <v>23</v>
-      </c>
-      <c r="AI9">
+      <c r="AJ9">
+        <v>22</v>
+      </c>
+      <c r="AK9">
+        <v>20</v>
+      </c>
+      <c r="AL9">
+        <v>34</v>
+      </c>
+      <c r="AM9">
+        <v>95</v>
+      </c>
+      <c r="AN9">
+        <v>13</v>
+      </c>
+      <c r="AO9">
+        <v>55</v>
+      </c>
+      <c r="AP9">
+        <v>14.5</v>
+      </c>
+      <c r="AQ9">
+        <v>15</v>
+      </c>
+      <c r="AR9">
+        <v>29</v>
+      </c>
+      <c r="AS9">
         <v>75</v>
       </c>
-      <c r="AJ9">
-        <v>28</v>
-      </c>
-      <c r="AK9">
-        <v>26</v>
-      </c>
-      <c r="AL9">
-        <v>48</v>
-      </c>
-      <c r="AM9">
-        <v>160</v>
-      </c>
-      <c r="AN9">
-        <v>23</v>
-      </c>
-      <c r="AO9">
-        <v>85</v>
-      </c>
-      <c r="AP9">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ9">
-        <v>11.5</v>
-      </c>
-      <c r="AR9">
-        <v>24</v>
-      </c>
-      <c r="AS9">
-        <v>17</v>
-      </c>
       <c r="AT9">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV9">
         <v>15.5</v>
       </c>
       <c r="AW9">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AX9">
         <v>11</v>
       </c>
       <c r="AY9">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ9">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA9">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="BB9">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BC9">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="BD9">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="BE9">
-        <v>18.5</v>
+        <v>36</v>
       </c>
       <c r="BF9">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="BG9">
+        <v>44</v>
+      </c>
+      <c r="BH9">
+        <v>3.5</v>
+      </c>
+      <c r="BI9">
+        <v>3.3</v>
+      </c>
+      <c r="BJ9">
+        <v>9.6</v>
+      </c>
+      <c r="BK9">
+        <v>8.6</v>
+      </c>
+      <c r="BL9">
+        <v>120</v>
+      </c>
+      <c r="BM9">
         <v>16.5</v>
       </c>
-      <c r="BH9">
-        <v>3</v>
-      </c>
-      <c r="BI9">
-        <v>2.76</v>
-      </c>
-      <c r="BJ9">
-        <v>10.5</v>
-      </c>
-      <c r="BK9">
-        <v>6.4</v>
-      </c>
-      <c r="BL9">
-        <v>1000</v>
-      </c>
-      <c r="BM9">
-        <v>15.5</v>
-      </c>
       <c r="BN9">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BO9">
         <v>4.3</v>
       </c>
       <c r="BP9">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="BQ9">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="BR9">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="BS9">
         <v>11.5</v>
       </c>
       <c r="BT9">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BU9">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BV9">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BW9">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX9">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="BY9">
         <v>13</v>
       </c>
       <c r="BZ9">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="CA9">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="CB9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2894,238 +2885,238 @@
         <v>86</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F10">
-        <v>1.94</v>
+        <v>2.22</v>
       </c>
       <c r="G10">
-        <v>1.96</v>
+        <v>2.24</v>
       </c>
       <c r="H10">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="I10">
-        <v>4.4</v>
+        <v>3.55</v>
       </c>
       <c r="J10">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K10">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L10">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="M10">
         <v>1.06</v>
       </c>
       <c r="N10">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="O10">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="P10">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="Q10">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="R10">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="S10">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="T10">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="U10">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="V10">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="W10">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
       <c r="X10">
+        <v>17.5</v>
+      </c>
+      <c r="Y10">
         <v>16</v>
       </c>
-      <c r="Y10">
+      <c r="Z10">
+        <v>26</v>
+      </c>
+      <c r="AA10">
+        <v>60</v>
+      </c>
+      <c r="AB10">
+        <v>12</v>
+      </c>
+      <c r="AC10">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD10">
+        <v>14.5</v>
+      </c>
+      <c r="AE10">
+        <v>36</v>
+      </c>
+      <c r="AF10">
+        <v>15</v>
+      </c>
+      <c r="AG10">
+        <v>11</v>
+      </c>
+      <c r="AH10">
+        <v>15.5</v>
+      </c>
+      <c r="AI10">
+        <v>40</v>
+      </c>
+      <c r="AJ10">
+        <v>27</v>
+      </c>
+      <c r="AK10">
+        <v>21</v>
+      </c>
+      <c r="AL10">
+        <v>32</v>
+      </c>
+      <c r="AM10">
+        <v>70</v>
+      </c>
+      <c r="AN10">
+        <v>13.5</v>
+      </c>
+      <c r="AO10">
+        <v>30</v>
+      </c>
+      <c r="AP10">
         <v>16.5</v>
       </c>
-      <c r="Z10">
+      <c r="AQ10">
+        <v>14.5</v>
+      </c>
+      <c r="AR10">
+        <v>23</v>
+      </c>
+      <c r="AS10">
+        <v>55</v>
+      </c>
+      <c r="AT10">
+        <v>11</v>
+      </c>
+      <c r="AU10">
+        <v>8</v>
+      </c>
+      <c r="AV10">
+        <v>13.5</v>
+      </c>
+      <c r="AW10">
+        <v>32</v>
+      </c>
+      <c r="AX10">
+        <v>14</v>
+      </c>
+      <c r="AY10">
+        <v>10</v>
+      </c>
+      <c r="AZ10">
+        <v>14.5</v>
+      </c>
+      <c r="BA10">
+        <v>38</v>
+      </c>
+      <c r="BB10">
+        <v>25</v>
+      </c>
+      <c r="BC10">
+        <v>19</v>
+      </c>
+      <c r="BD10">
+        <v>28</v>
+      </c>
+      <c r="BE10">
+        <v>60</v>
+      </c>
+      <c r="BF10">
+        <v>12.5</v>
+      </c>
+      <c r="BG10">
+        <v>26</v>
+      </c>
+      <c r="BH10">
+        <v>3.8</v>
+      </c>
+      <c r="BI10">
+        <v>3.6</v>
+      </c>
+      <c r="BJ10">
+        <v>9</v>
+      </c>
+      <c r="BK10">
+        <v>8</v>
+      </c>
+      <c r="BL10">
+        <v>95</v>
+      </c>
+      <c r="BM10">
+        <v>14</v>
+      </c>
+      <c r="BN10">
+        <v>5.2</v>
+      </c>
+      <c r="BO10">
+        <v>4.7</v>
+      </c>
+      <c r="BP10">
+        <v>15.5</v>
+      </c>
+      <c r="BQ10">
+        <v>13.5</v>
+      </c>
+      <c r="BR10">
+        <v>26</v>
+      </c>
+      <c r="BS10">
+        <v>10</v>
+      </c>
+      <c r="BT10">
+        <v>6.8</v>
+      </c>
+      <c r="BU10">
+        <v>6.2</v>
+      </c>
+      <c r="BV10">
+        <v>26</v>
+      </c>
+      <c r="BW10">
+        <v>10</v>
+      </c>
+      <c r="BX10">
         <v>34</v>
       </c>
-      <c r="AA10">
-        <v>95</v>
-      </c>
-      <c r="AB10">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC10">
-        <v>8.4</v>
-      </c>
-      <c r="AD10">
-        <v>17</v>
-      </c>
-      <c r="AE10">
-        <v>55</v>
-      </c>
-      <c r="AF10">
-        <v>12</v>
-      </c>
-      <c r="AG10">
-        <v>10.5</v>
-      </c>
-      <c r="AH10">
-        <v>18</v>
-      </c>
-      <c r="AI10">
-        <v>55</v>
-      </c>
-      <c r="AJ10">
-        <v>22</v>
-      </c>
-      <c r="AK10">
-        <v>20</v>
-      </c>
-      <c r="AL10">
-        <v>34</v>
-      </c>
-      <c r="AM10">
-        <v>95</v>
-      </c>
-      <c r="AN10">
-        <v>12.5</v>
-      </c>
-      <c r="AO10">
-        <v>55</v>
-      </c>
-      <c r="AP10">
-        <v>14.5</v>
-      </c>
-      <c r="AQ10">
-        <v>15</v>
-      </c>
-      <c r="AR10">
-        <v>29</v>
-      </c>
-      <c r="AS10">
-        <v>75</v>
-      </c>
-      <c r="AT10">
-        <v>9</v>
-      </c>
-      <c r="AU10">
-        <v>7.8</v>
-      </c>
-      <c r="AV10">
-        <v>16</v>
-      </c>
-      <c r="AW10">
-        <v>44</v>
-      </c>
-      <c r="AX10">
-        <v>11</v>
-      </c>
-      <c r="AY10">
-        <v>9.6</v>
-      </c>
-      <c r="AZ10">
-        <v>16.5</v>
-      </c>
-      <c r="BA10">
-        <v>48</v>
-      </c>
-      <c r="BB10">
-        <v>20</v>
-      </c>
-      <c r="BC10">
-        <v>18</v>
-      </c>
-      <c r="BD10">
-        <v>30</v>
-      </c>
-      <c r="BE10">
-        <v>70</v>
-      </c>
-      <c r="BF10">
-        <v>11</v>
-      </c>
-      <c r="BG10">
-        <v>46</v>
-      </c>
-      <c r="BH10">
-        <v>3.55</v>
-      </c>
-      <c r="BI10">
-        <v>3.3</v>
-      </c>
-      <c r="BJ10">
+      <c r="BY10">
+        <v>11.5</v>
+      </c>
+      <c r="BZ10">
+        <v>21</v>
+      </c>
+      <c r="CA10">
         <v>9.4</v>
       </c>
-      <c r="BK10">
-        <v>8.4</v>
-      </c>
-      <c r="BL10">
-        <v>120</v>
-      </c>
-      <c r="BM10">
-        <v>15.5</v>
-      </c>
-      <c r="BN10">
-        <v>4.7</v>
-      </c>
-      <c r="BO10">
-        <v>4.3</v>
-      </c>
-      <c r="BP10">
-        <v>13.5</v>
-      </c>
-      <c r="BQ10">
-        <v>11.5</v>
-      </c>
-      <c r="BR10">
-        <v>27</v>
-      </c>
-      <c r="BS10">
-        <v>10.5</v>
-      </c>
-      <c r="BT10">
-        <v>7.6</v>
-      </c>
-      <c r="BU10">
-        <v>6.8</v>
-      </c>
-      <c r="BV10">
-        <v>38</v>
-      </c>
-      <c r="BW10">
-        <v>12</v>
-      </c>
-      <c r="BX10">
-        <v>42</v>
-      </c>
-      <c r="BY10">
-        <v>12.5</v>
-      </c>
-      <c r="BZ10">
-        <v>23</v>
-      </c>
-      <c r="CA10">
-        <v>10</v>
-      </c>
       <c r="CB10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3136,238 +3127,238 @@
         <v>86</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E11" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F11">
-        <v>2.16</v>
+        <v>1.81</v>
       </c>
       <c r="G11">
-        <v>2.18</v>
+        <v>1.83</v>
       </c>
       <c r="H11">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="I11">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="J11">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="K11">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="L11">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="M11">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N11">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="O11">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="P11">
-        <v>2.24</v>
+        <v>2.86</v>
       </c>
       <c r="Q11">
-        <v>1.78</v>
+        <v>1.51</v>
       </c>
       <c r="R11">
-        <v>1.48</v>
+        <v>1.74</v>
       </c>
       <c r="S11">
-        <v>2.96</v>
+        <v>2.28</v>
       </c>
       <c r="T11">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="U11">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="V11">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="W11">
-        <v>1.84</v>
+        <v>2.2</v>
       </c>
       <c r="X11">
-        <v>17.5</v>
+        <v>29</v>
       </c>
       <c r="Y11">
+        <v>25</v>
+      </c>
+      <c r="Z11">
+        <v>40</v>
+      </c>
+      <c r="AA11">
+        <v>85</v>
+      </c>
+      <c r="AB11">
+        <v>15</v>
+      </c>
+      <c r="AC11">
+        <v>10.5</v>
+      </c>
+      <c r="AD11">
+        <v>18</v>
+      </c>
+      <c r="AE11">
+        <v>44</v>
+      </c>
+      <c r="AF11">
+        <v>14.5</v>
+      </c>
+      <c r="AG11">
+        <v>10.5</v>
+      </c>
+      <c r="AH11">
+        <v>15.5</v>
+      </c>
+      <c r="AI11">
+        <v>42</v>
+      </c>
+      <c r="AJ11">
+        <v>21</v>
+      </c>
+      <c r="AK11">
+        <v>16</v>
+      </c>
+      <c r="AL11">
+        <v>23</v>
+      </c>
+      <c r="AM11">
+        <v>55</v>
+      </c>
+      <c r="AN11">
+        <v>7</v>
+      </c>
+      <c r="AO11">
+        <v>29</v>
+      </c>
+      <c r="AP11">
+        <v>26</v>
+      </c>
+      <c r="AQ11">
+        <v>22</v>
+      </c>
+      <c r="AR11">
+        <v>36</v>
+      </c>
+      <c r="AS11">
+        <v>75</v>
+      </c>
+      <c r="AT11">
+        <v>13.5</v>
+      </c>
+      <c r="AU11">
+        <v>10</v>
+      </c>
+      <c r="AV11">
         <v>16.5</v>
       </c>
-      <c r="Z11">
-        <v>27</v>
-      </c>
-      <c r="AA11">
-        <v>65</v>
-      </c>
-      <c r="AB11">
-        <v>12</v>
-      </c>
-      <c r="AC11">
-        <v>8.6</v>
-      </c>
-      <c r="AD11">
-        <v>14.5</v>
-      </c>
-      <c r="AE11">
-        <v>40</v>
-      </c>
-      <c r="AF11">
-        <v>15</v>
-      </c>
-      <c r="AG11">
-        <v>11</v>
-      </c>
-      <c r="AH11">
-        <v>16</v>
-      </c>
-      <c r="AI11">
-        <v>46</v>
-      </c>
-      <c r="AJ11">
-        <v>26</v>
-      </c>
-      <c r="AK11">
-        <v>21</v>
-      </c>
-      <c r="AL11">
-        <v>32</v>
-      </c>
-      <c r="AM11">
-        <v>70</v>
-      </c>
-      <c r="AN11">
-        <v>13</v>
-      </c>
-      <c r="AO11">
-        <v>32</v>
-      </c>
-      <c r="AP11">
-        <v>16</v>
-      </c>
-      <c r="AQ11">
-        <v>14.5</v>
-      </c>
-      <c r="AR11">
-        <v>24</v>
-      </c>
-      <c r="AS11">
-        <v>55</v>
-      </c>
-      <c r="AT11">
-        <v>10.5</v>
-      </c>
-      <c r="AU11">
-        <v>8</v>
-      </c>
-      <c r="AV11">
-        <v>13.5</v>
-      </c>
       <c r="AW11">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AX11">
         <v>13.5</v>
       </c>
       <c r="AY11">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ11">
         <v>14.5</v>
       </c>
       <c r="BA11">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BB11">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="BC11">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD11">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="BE11">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="BF11">
-        <v>11.5</v>
+        <v>6.4</v>
       </c>
       <c r="BG11">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BH11">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="BI11">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="BJ11">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK11">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BL11">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="BM11">
         <v>14</v>
       </c>
       <c r="BN11">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO11">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BP11">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BQ11">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR11">
-        <v>26</v>
+        <v>19.5</v>
       </c>
       <c r="BS11">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT11">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BU11">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BV11">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BW11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX11">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BY11">
         <v>11</v>
       </c>
       <c r="BZ11">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="CA11">
-        <v>9.4</v>
+        <v>7.4</v>
       </c>
       <c r="CB11" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3378,238 +3369,238 @@
         <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F12">
-        <v>1.81</v>
+        <v>3.85</v>
       </c>
       <c r="G12">
-        <v>1.83</v>
+        <v>3.95</v>
       </c>
       <c r="H12">
-        <v>4.4</v>
+        <v>1.93</v>
       </c>
       <c r="I12">
-        <v>4.5</v>
+        <v>1.95</v>
       </c>
       <c r="J12">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K12">
         <v>4.5</v>
       </c>
       <c r="L12">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="M12">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N12">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="O12">
+        <v>1.13</v>
+      </c>
+      <c r="P12">
+        <v>3.3</v>
+      </c>
+      <c r="Q12">
+        <v>1.42</v>
+      </c>
+      <c r="R12">
+        <v>1.96</v>
+      </c>
+      <c r="S12">
+        <v>2</v>
+      </c>
+      <c r="T12">
+        <v>1.44</v>
+      </c>
+      <c r="U12">
+        <v>3.1</v>
+      </c>
+      <c r="V12">
+        <v>2.06</v>
+      </c>
+      <c r="W12">
+        <v>1.33</v>
+      </c>
+      <c r="X12">
+        <v>36</v>
+      </c>
+      <c r="Y12">
+        <v>18.5</v>
+      </c>
+      <c r="Z12">
+        <v>18</v>
+      </c>
+      <c r="AA12">
+        <v>24</v>
+      </c>
+      <c r="AB12">
+        <v>29</v>
+      </c>
+      <c r="AC12">
+        <v>11.5</v>
+      </c>
+      <c r="AD12">
+        <v>11.5</v>
+      </c>
+      <c r="AE12">
+        <v>16.5</v>
+      </c>
+      <c r="AF12">
+        <v>38</v>
+      </c>
+      <c r="AG12">
+        <v>17</v>
+      </c>
+      <c r="AH12">
+        <v>13.5</v>
+      </c>
+      <c r="AI12">
+        <v>21</v>
+      </c>
+      <c r="AJ12">
+        <v>75</v>
+      </c>
+      <c r="AK12">
+        <v>36</v>
+      </c>
+      <c r="AL12">
+        <v>32</v>
+      </c>
+      <c r="AM12">
+        <v>42</v>
+      </c>
+      <c r="AN12">
+        <v>21</v>
+      </c>
+      <c r="AO12">
         <v>6.6</v>
       </c>
-      <c r="O12">
-        <v>1.17</v>
-      </c>
-      <c r="P12">
-        <v>2.86</v>
-      </c>
-      <c r="Q12">
-        <v>1.51</v>
-      </c>
-      <c r="R12">
-        <v>1.75</v>
-      </c>
-      <c r="S12">
-        <v>2.26</v>
-      </c>
-      <c r="T12">
-        <v>1.55</v>
-      </c>
-      <c r="U12">
-        <v>2.7</v>
-      </c>
-      <c r="V12">
-        <v>1.28</v>
-      </c>
-      <c r="W12">
-        <v>2.2</v>
-      </c>
-      <c r="X12">
+      <c r="AP12">
+        <v>34</v>
+      </c>
+      <c r="AQ12">
+        <v>17.5</v>
+      </c>
+      <c r="AR12">
+        <v>16</v>
+      </c>
+      <c r="AS12">
+        <v>22</v>
+      </c>
+      <c r="AT12">
+        <v>27</v>
+      </c>
+      <c r="AU12">
+        <v>10.5</v>
+      </c>
+      <c r="AV12">
+        <v>10.5</v>
+      </c>
+      <c r="AW12">
+        <v>15</v>
+      </c>
+      <c r="AX12">
+        <v>32</v>
+      </c>
+      <c r="AY12">
+        <v>15.5</v>
+      </c>
+      <c r="AZ12">
+        <v>13</v>
+      </c>
+      <c r="BA12">
+        <v>19.5</v>
+      </c>
+      <c r="BB12">
+        <v>65</v>
+      </c>
+      <c r="BC12">
+        <v>30</v>
+      </c>
+      <c r="BD12">
         <v>29</v>
       </c>
-      <c r="Y12">
+      <c r="BE12">
+        <v>38</v>
+      </c>
+      <c r="BF12">
+        <v>18</v>
+      </c>
+      <c r="BG12">
+        <v>6</v>
+      </c>
+      <c r="BH12">
+        <v>5.5</v>
+      </c>
+      <c r="BI12">
+        <v>5</v>
+      </c>
+      <c r="BJ12">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BK12">
+        <v>7.2</v>
+      </c>
+      <c r="BL12">
+        <v>60</v>
+      </c>
+      <c r="BM12">
+        <v>11</v>
+      </c>
+      <c r="BN12">
+        <v>8</v>
+      </c>
+      <c r="BO12">
+        <v>7.2</v>
+      </c>
+      <c r="BP12">
         <v>25</v>
       </c>
-      <c r="Z12">
-        <v>40</v>
-      </c>
-      <c r="AA12">
-        <v>85</v>
-      </c>
-      <c r="AB12">
-        <v>14.5</v>
-      </c>
-      <c r="AC12">
-        <v>11</v>
-      </c>
-      <c r="AD12">
-        <v>17.5</v>
-      </c>
-      <c r="AE12">
-        <v>44</v>
-      </c>
-      <c r="AF12">
-        <v>15</v>
-      </c>
-      <c r="AG12">
-        <v>11</v>
-      </c>
-      <c r="AH12">
-        <v>15.5</v>
-      </c>
-      <c r="AI12">
-        <v>40</v>
-      </c>
-      <c r="AJ12">
-        <v>21</v>
-      </c>
-      <c r="AK12">
-        <v>16.5</v>
-      </c>
-      <c r="AL12">
-        <v>24</v>
-      </c>
-      <c r="AM12">
-        <v>55</v>
-      </c>
-      <c r="AN12">
-        <v>6.8</v>
-      </c>
-      <c r="AO12">
-        <v>29</v>
-      </c>
-      <c r="AP12">
+      <c r="BQ12">
+        <v>19</v>
+      </c>
+      <c r="BR12">
         <v>26</v>
-      </c>
-      <c r="AQ12">
-        <v>22</v>
-      </c>
-      <c r="AR12">
-        <v>36</v>
-      </c>
-      <c r="AS12">
-        <v>70</v>
-      </c>
-      <c r="AT12">
-        <v>13.5</v>
-      </c>
-      <c r="AU12">
-        <v>10</v>
-      </c>
-      <c r="AV12">
-        <v>16.5</v>
-      </c>
-      <c r="AW12">
-        <v>38</v>
-      </c>
-      <c r="AX12">
-        <v>13.5</v>
-      </c>
-      <c r="AY12">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ12">
-        <v>14</v>
-      </c>
-      <c r="BA12">
-        <v>36</v>
-      </c>
-      <c r="BB12">
-        <v>18.5</v>
-      </c>
-      <c r="BC12">
-        <v>14.5</v>
-      </c>
-      <c r="BD12">
-        <v>21</v>
-      </c>
-      <c r="BE12">
-        <v>48</v>
-      </c>
-      <c r="BF12">
-        <v>6.4</v>
-      </c>
-      <c r="BG12">
-        <v>26</v>
-      </c>
-      <c r="BH12">
-        <v>4.7</v>
-      </c>
-      <c r="BI12">
-        <v>4.3</v>
-      </c>
-      <c r="BJ12">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK12">
-        <v>6.6</v>
-      </c>
-      <c r="BL12">
-        <v>70</v>
-      </c>
-      <c r="BM12">
-        <v>14.5</v>
-      </c>
-      <c r="BN12">
-        <v>5</v>
-      </c>
-      <c r="BO12">
-        <v>4.5</v>
-      </c>
-      <c r="BP12">
-        <v>11</v>
-      </c>
-      <c r="BQ12">
-        <v>6.8</v>
-      </c>
-      <c r="BR12">
-        <v>19.5</v>
       </c>
       <c r="BS12">
         <v>9.4</v>
       </c>
       <c r="BT12">
-        <v>8.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="BU12">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV12">
-        <v>30</v>
+        <v>12.5</v>
       </c>
       <c r="BW12">
+        <v>10.5</v>
+      </c>
+      <c r="BX12">
+        <v>18.5</v>
+      </c>
+      <c r="BY12">
+        <v>15</v>
+      </c>
+      <c r="BZ12">
         <v>11</v>
       </c>
-      <c r="BX12">
-        <v>32</v>
-      </c>
-      <c r="BY12">
-        <v>11.5</v>
-      </c>
-      <c r="BZ12">
-        <v>13</v>
-      </c>
       <c r="CA12">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB12" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3620,480 +3611,238 @@
         <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E13" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F13">
-        <v>3.85</v>
+        <v>2.48</v>
       </c>
       <c r="G13">
-        <v>3.9</v>
+        <v>2.52</v>
       </c>
       <c r="H13">
-        <v>1.94</v>
+        <v>2.7</v>
       </c>
       <c r="I13">
-        <v>1.96</v>
+        <v>2.76</v>
       </c>
       <c r="J13">
+        <v>4.2</v>
+      </c>
+      <c r="K13">
         <v>4.3</v>
       </c>
-      <c r="K13">
-        <v>4.5</v>
-      </c>
       <c r="L13">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M13">
         <v>1.02</v>
       </c>
       <c r="N13">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="O13">
         <v>1.12</v>
       </c>
       <c r="P13">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="Q13">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="R13">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="S13">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="T13">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="U13">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="V13">
-        <v>2.04</v>
+        <v>1.57</v>
       </c>
       <c r="W13">
-        <v>1.34</v>
+        <v>1.65</v>
       </c>
       <c r="X13">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Y13">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="Z13">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="AA13">
+        <v>46</v>
+      </c>
+      <c r="AB13">
         <v>24</v>
-      </c>
-      <c r="AB13">
-        <v>29</v>
       </c>
       <c r="AC13">
         <v>11.5</v>
       </c>
       <c r="AD13">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AE13">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AF13">
+        <v>25</v>
+      </c>
+      <c r="AG13">
+        <v>13</v>
+      </c>
+      <c r="AH13">
+        <v>13</v>
+      </c>
+      <c r="AI13">
+        <v>24</v>
+      </c>
+      <c r="AJ13">
+        <v>38</v>
+      </c>
+      <c r="AK13">
+        <v>21</v>
+      </c>
+      <c r="AL13">
+        <v>23</v>
+      </c>
+      <c r="AM13">
+        <v>36</v>
+      </c>
+      <c r="AN13">
+        <v>9</v>
+      </c>
+      <c r="AO13">
+        <v>10.5</v>
+      </c>
+      <c r="AP13">
+        <v>34</v>
+      </c>
+      <c r="AQ13">
+        <v>23</v>
+      </c>
+      <c r="AR13">
+        <v>25</v>
+      </c>
+      <c r="AS13">
         <v>40</v>
       </c>
-      <c r="AG13">
-        <v>17</v>
-      </c>
-      <c r="AH13">
-        <v>13.5</v>
-      </c>
-      <c r="AI13">
+      <c r="AT13">
         <v>22</v>
-      </c>
-      <c r="AJ13">
-        <v>75</v>
-      </c>
-      <c r="AK13">
-        <v>36</v>
-      </c>
-      <c r="AL13">
-        <v>32</v>
-      </c>
-      <c r="AM13">
-        <v>42</v>
-      </c>
-      <c r="AN13">
-        <v>20</v>
-      </c>
-      <c r="AO13">
-        <v>6.4</v>
-      </c>
-      <c r="AP13">
-        <v>32</v>
-      </c>
-      <c r="AQ13">
-        <v>17.5</v>
-      </c>
-      <c r="AR13">
-        <v>16</v>
-      </c>
-      <c r="AS13">
-        <v>22</v>
-      </c>
-      <c r="AT13">
-        <v>27</v>
       </c>
       <c r="AU13">
         <v>10.5</v>
       </c>
       <c r="AV13">
+        <v>13</v>
+      </c>
+      <c r="AW13">
+        <v>22</v>
+      </c>
+      <c r="AX13">
+        <v>23</v>
+      </c>
+      <c r="AY13">
+        <v>12</v>
+      </c>
+      <c r="AZ13">
+        <v>12</v>
+      </c>
+      <c r="BA13">
+        <v>23</v>
+      </c>
+      <c r="BB13">
+        <v>34</v>
+      </c>
+      <c r="BC13">
+        <v>19.5</v>
+      </c>
+      <c r="BD13">
+        <v>21</v>
+      </c>
+      <c r="BE13">
+        <v>30</v>
+      </c>
+      <c r="BF13">
+        <v>8.4</v>
+      </c>
+      <c r="BG13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BH13">
+        <v>5.6</v>
+      </c>
+      <c r="BI13">
+        <v>5.2</v>
+      </c>
+      <c r="BJ13">
+        <v>7.8</v>
+      </c>
+      <c r="BK13">
+        <v>7.2</v>
+      </c>
+      <c r="BL13">
+        <v>48</v>
+      </c>
+      <c r="BM13">
+        <v>25</v>
+      </c>
+      <c r="BN13">
+        <v>6.6</v>
+      </c>
+      <c r="BO13">
+        <v>5.9</v>
+      </c>
+      <c r="BP13">
+        <v>15.5</v>
+      </c>
+      <c r="BQ13">
+        <v>13.5</v>
+      </c>
+      <c r="BR13">
+        <v>19</v>
+      </c>
+      <c r="BS13">
+        <v>16</v>
+      </c>
+      <c r="BT13">
+        <v>6.6</v>
+      </c>
+      <c r="BU13">
+        <v>6.2</v>
+      </c>
+      <c r="BV13">
+        <v>16.5</v>
+      </c>
+      <c r="BW13">
+        <v>15</v>
+      </c>
+      <c r="BX13">
+        <v>20</v>
+      </c>
+      <c r="BY13">
+        <v>17</v>
+      </c>
+      <c r="BZ13">
         <v>10.5</v>
       </c>
-      <c r="AW13">
-        <v>15</v>
-      </c>
-      <c r="AX13">
-        <v>34</v>
-      </c>
-      <c r="AY13">
-        <v>15.5</v>
-      </c>
-      <c r="AZ13">
-        <v>13</v>
-      </c>
-      <c r="BA13">
-        <v>19.5</v>
-      </c>
-      <c r="BB13">
-        <v>65</v>
-      </c>
-      <c r="BC13">
-        <v>32</v>
-      </c>
-      <c r="BD13">
-        <v>29</v>
-      </c>
-      <c r="BE13">
-        <v>38</v>
-      </c>
-      <c r="BF13">
-        <v>18</v>
-      </c>
-      <c r="BG13">
-        <v>6</v>
-      </c>
-      <c r="BH13">
-        <v>5.5</v>
-      </c>
-      <c r="BI13">
-        <v>4.8</v>
-      </c>
-      <c r="BJ13">
-        <v>8.6</v>
-      </c>
-      <c r="BK13">
-        <v>7.4</v>
-      </c>
-      <c r="BL13">
-        <v>60</v>
-      </c>
-      <c r="BM13">
-        <v>10</v>
-      </c>
-      <c r="BN13">
-        <v>8.4</v>
-      </c>
-      <c r="BO13">
-        <v>7.2</v>
-      </c>
-      <c r="BP13">
-        <v>25</v>
-      </c>
-      <c r="BQ13">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR13">
-        <v>26</v>
-      </c>
-      <c r="BS13">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT13">
-        <v>5.5</v>
-      </c>
-      <c r="BU13">
-        <v>5</v>
-      </c>
-      <c r="BV13">
-        <v>12.5</v>
-      </c>
-      <c r="BW13">
-        <v>10.5</v>
-      </c>
-      <c r="BX13">
-        <v>18.5</v>
-      </c>
-      <c r="BY13">
-        <v>7.4</v>
-      </c>
-      <c r="BZ13">
-        <v>11</v>
-      </c>
       <c r="CA13">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB13" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="14" spans="1:80">
-      <c r="A14" t="s">
-        <v>85</v>
-      </c>
-      <c r="B14" t="s">
-        <v>86</v>
-      </c>
-      <c r="C14" t="s">
-        <v>92</v>
-      </c>
-      <c r="D14" t="s">
-        <v>105</v>
-      </c>
-      <c r="E14" t="s">
-        <v>118</v>
-      </c>
-      <c r="F14">
-        <v>2.46</v>
-      </c>
-      <c r="G14">
-        <v>2.48</v>
-      </c>
-      <c r="H14">
-        <v>2.76</v>
-      </c>
-      <c r="I14">
-        <v>2.8</v>
-      </c>
-      <c r="J14">
-        <v>4.2</v>
-      </c>
-      <c r="K14">
-        <v>4.3</v>
-      </c>
-      <c r="L14">
-        <v>1.22</v>
-      </c>
-      <c r="M14">
-        <v>1.02</v>
-      </c>
-      <c r="N14">
-        <v>8.6</v>
-      </c>
-      <c r="O14">
-        <v>1.12</v>
-      </c>
-      <c r="P14">
-        <v>3.45</v>
-      </c>
-      <c r="Q14">
-        <v>1.39</v>
-      </c>
-      <c r="R14">
-        <v>2</v>
-      </c>
-      <c r="S14">
-        <v>1.97</v>
-      </c>
-      <c r="T14">
-        <v>1.38</v>
-      </c>
-      <c r="U14">
-        <v>3.4</v>
-      </c>
-      <c r="V14">
-        <v>1.55</v>
-      </c>
-      <c r="W14">
-        <v>1.67</v>
-      </c>
-      <c r="X14">
-        <v>38</v>
-      </c>
-      <c r="Y14">
-        <v>25</v>
-      </c>
-      <c r="Z14">
-        <v>28</v>
-      </c>
-      <c r="AA14">
-        <v>46</v>
-      </c>
-      <c r="AB14">
-        <v>24</v>
-      </c>
-      <c r="AC14">
-        <v>11.5</v>
-      </c>
-      <c r="AD14">
-        <v>14</v>
-      </c>
-      <c r="AE14">
-        <v>25</v>
-      </c>
-      <c r="AF14">
-        <v>25</v>
-      </c>
-      <c r="AG14">
-        <v>13</v>
-      </c>
-      <c r="AH14">
-        <v>12.5</v>
-      </c>
-      <c r="AI14">
-        <v>25</v>
-      </c>
-      <c r="AJ14">
-        <v>38</v>
-      </c>
-      <c r="AK14">
-        <v>21</v>
-      </c>
-      <c r="AL14">
-        <v>23</v>
-      </c>
-      <c r="AM14">
-        <v>38</v>
-      </c>
-      <c r="AN14">
-        <v>9</v>
-      </c>
-      <c r="AO14">
-        <v>11</v>
-      </c>
-      <c r="AP14">
-        <v>34</v>
-      </c>
-      <c r="AQ14">
-        <v>22</v>
-      </c>
-      <c r="AR14">
-        <v>25</v>
-      </c>
-      <c r="AS14">
-        <v>40</v>
-      </c>
-      <c r="AT14">
-        <v>21</v>
-      </c>
-      <c r="AU14">
-        <v>10.5</v>
-      </c>
-      <c r="AV14">
-        <v>12.5</v>
-      </c>
-      <c r="AW14">
-        <v>22</v>
-      </c>
-      <c r="AX14">
-        <v>23</v>
-      </c>
-      <c r="AY14">
-        <v>12</v>
-      </c>
-      <c r="AZ14">
-        <v>12</v>
-      </c>
-      <c r="BA14">
-        <v>23</v>
-      </c>
-      <c r="BB14">
-        <v>34</v>
-      </c>
-      <c r="BC14">
-        <v>19.5</v>
-      </c>
-      <c r="BD14">
-        <v>21</v>
-      </c>
-      <c r="BE14">
-        <v>32</v>
-      </c>
-      <c r="BF14">
-        <v>8.4</v>
-      </c>
-      <c r="BG14">
-        <v>10</v>
-      </c>
-      <c r="BH14">
-        <v>5.7</v>
-      </c>
-      <c r="BI14">
-        <v>5.2</v>
-      </c>
-      <c r="BJ14">
-        <v>8</v>
-      </c>
-      <c r="BK14">
-        <v>7</v>
-      </c>
-      <c r="BL14">
-        <v>50</v>
-      </c>
-      <c r="BM14">
-        <v>13.5</v>
-      </c>
-      <c r="BN14">
-        <v>6.4</v>
-      </c>
-      <c r="BO14">
-        <v>5.9</v>
-      </c>
-      <c r="BP14">
-        <v>15.5</v>
-      </c>
-      <c r="BQ14">
-        <v>13.5</v>
-      </c>
-      <c r="BR14">
-        <v>19</v>
-      </c>
-      <c r="BS14">
-        <v>10</v>
-      </c>
-      <c r="BT14">
-        <v>6.8</v>
-      </c>
-      <c r="BU14">
-        <v>6.2</v>
-      </c>
-      <c r="BV14">
-        <v>16.5</v>
-      </c>
-      <c r="BW14">
-        <v>14.5</v>
-      </c>
-      <c r="BX14">
-        <v>20</v>
-      </c>
-      <c r="BY14">
-        <v>10</v>
-      </c>
-      <c r="BZ14">
-        <v>10.5</v>
-      </c>
-      <c r="CA14">
-        <v>7.6</v>
-      </c>
-      <c r="CB14" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
